--- a/data/LUVE.MI.xlsx
+++ b/data/LUVE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="1110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1111" uniqueCount="1111">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,103 +38,103 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30043411254883</t>
+    <t xml:space="preserve">8.3004322052002</t>
   </si>
   <si>
     <t xml:space="preserve">LUVE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31703472137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2838306427002</t>
+    <t xml:space="preserve">8.3170337677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28383159637451</t>
   </si>
   <si>
     <t xml:space="preserve">8.09292316436768</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19667625427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07631969451904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15102481842041</t>
+    <t xml:space="preserve">8.19667911529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07632160186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15102672576904</t>
   </si>
   <si>
     <t xml:space="preserve">8.17177867889404</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03896903991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08462238311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06802082061768</t>
+    <t xml:space="preserve">8.03896999359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08462142944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06802272796631</t>
   </si>
   <si>
     <t xml:space="preserve">7.9684157371521</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01821899414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9974684715271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91861438751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91446399688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91031312942505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88541126251221</t>
+    <t xml:space="preserve">8.01821804046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99746751785278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91861248016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91446208953857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91031408309937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88541316986084</t>
   </si>
   <si>
     <t xml:space="preserve">7.87711143493652</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85221099853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.648850440979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7194037437439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70280075073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69035148620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.619797706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55754375457764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55339527130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.636399269104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76920652389526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80240774154663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93521547317505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10122203826904</t>
+    <t xml:space="preserve">7.85220956802368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64885091781616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71940326690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70280170440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69035196304321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61979818344116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55754470825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55339574813843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63639736175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76920604705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80240678787231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93521642684937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10122299194336</t>
   </si>
   <si>
     <t xml:space="preserve">8.05142116546631</t>
@@ -158,25 +158,25 @@
     <t xml:space="preserve">8.35853672027588</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32533550262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29213428497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20082664489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15932655334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30336380004883</t>
+    <t xml:space="preserve">8.3253345489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29213333129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20082759857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15932559967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30336284637451</t>
   </si>
   <si>
     <t xml:space="preserve">8.36267280578613</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43045616149902</t>
+    <t xml:space="preserve">8.43045520782471</t>
   </si>
   <si>
     <t xml:space="preserve">8.15085315704346</t>
@@ -188,52 +188,52 @@
     <t xml:space="preserve">8.2059268951416</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1339054107666</t>
+    <t xml:space="preserve">8.13390827178955</t>
   </si>
   <si>
     <t xml:space="preserve">8.11696243286133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21863460540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21016216278076</t>
+    <t xml:space="preserve">8.21863555908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21016311645508</t>
   </si>
   <si>
     <t xml:space="preserve">8.21439838409424</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20169067382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26099967956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09154415130615</t>
+    <t xml:space="preserve">8.20169162750244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26100063323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09154224395752</t>
   </si>
   <si>
     <t xml:space="preserve">8.10848903656006</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04917907714844</t>
+    <t xml:space="preserve">8.04918003082275</t>
   </si>
   <si>
     <t xml:space="preserve">7.96445083618164</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92208766937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.879723072052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83735752105713</t>
+    <t xml:space="preserve">7.92208862304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87972259521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8373589515686</t>
   </si>
   <si>
     <t xml:space="preserve">8.12543487548828</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93479537963867</t>
+    <t xml:space="preserve">7.9347972869873</t>
   </si>
   <si>
     <t xml:space="preserve">7.75263023376465</t>
@@ -242,22 +242,22 @@
     <t xml:space="preserve">7.71026754379272</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93903303146362</t>
+    <t xml:space="preserve">7.93903207778931</t>
   </si>
   <si>
     <t xml:space="preserve">7.81193971633911</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79499530792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62553930282593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66790294647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84583187103271</t>
+    <t xml:space="preserve">7.79499340057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62553834915161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66790342330933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84583234786987</t>
   </si>
   <si>
     <t xml:space="preserve">8.19321727752686</t>
@@ -266,16 +266,16 @@
     <t xml:space="preserve">8.47281932830811</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5151834487915</t>
+    <t xml:space="preserve">8.51518535614014</t>
   </si>
   <si>
     <t xml:space="preserve">8.52365779876709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59991073608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78631401062012</t>
+    <t xml:space="preserve">8.5999116897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78631496429443</t>
   </si>
   <si>
     <t xml:space="preserve">8.71853160858154</t>
@@ -287,79 +287,79 @@
     <t xml:space="preserve">8.540602684021</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46858310699463</t>
+    <t xml:space="preserve">8.46858406066895</t>
   </si>
   <si>
     <t xml:space="preserve">8.46434783935547</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55754947662354</t>
+    <t xml:space="preserve">8.55754852294922</t>
   </si>
   <si>
     <t xml:space="preserve">8.57449531555176</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81173324584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72700500488281</t>
+    <t xml:space="preserve">8.81173229217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7270040512085</t>
   </si>
   <si>
     <t xml:space="preserve">8.64227771759033</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89646148681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0235538482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09980869293213</t>
+    <t xml:space="preserve">8.89646053314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02355289459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09980964660645</t>
   </si>
   <si>
     <t xml:space="preserve">9.06591701507568</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10828304290771</t>
+    <t xml:space="preserve">9.1082820892334</t>
   </si>
   <si>
     <t xml:space="preserve">9.27773761749268</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19300937652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18453788757324</t>
+    <t xml:space="preserve">9.1930103302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18453598022461</t>
   </si>
   <si>
     <t xml:space="preserve">9.07439041137695</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09133720397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30315494537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32010173797607</t>
+    <t xml:space="preserve">9.09133529663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30315589904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32010269165039</t>
   </si>
   <si>
     <t xml:space="preserve">9.1252269744873</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60817718505859</t>
+    <t xml:space="preserve">9.60817813873291</t>
   </si>
   <si>
     <t xml:space="preserve">9.40483093261719</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4895601272583</t>
+    <t xml:space="preserve">9.48955726623535</t>
   </si>
   <si>
     <t xml:space="preserve">9.38788509368896</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53192234039307</t>
+    <t xml:space="preserve">9.5319242477417</t>
   </si>
   <si>
     <t xml:space="preserve">9.4810848236084</t>
@@ -368,19 +368,19 @@
     <t xml:space="preserve">9.44719505310059</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54039573669434</t>
+    <t xml:space="preserve">9.54039669036865</t>
   </si>
   <si>
     <t xml:space="preserve">9.57428741455078</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47261428833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41330528259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42177486419678</t>
+    <t xml:space="preserve">9.47261333465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41330432891846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42177677154541</t>
   </si>
   <si>
     <t xml:space="preserve">9.51497745513916</t>
@@ -392,43 +392,43 @@
     <t xml:space="preserve">9.74374294281006</t>
   </si>
   <si>
-    <t xml:space="preserve">10.065710067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2521123886108</t>
+    <t xml:space="preserve">10.0657110214233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2521114349365</t>
   </si>
   <si>
     <t xml:space="preserve">10.1334924697876</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99792766571045</t>
+    <t xml:space="preserve">9.99792861938477</t>
   </si>
   <si>
     <t xml:space="preserve">9.95556259155273</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98098278045654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88778018951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91319942474365</t>
+    <t xml:space="preserve">9.98098182678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88778209686279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91320037841797</t>
   </si>
   <si>
     <t xml:space="preserve">10.0148735046387</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1589117050171</t>
+    <t xml:space="preserve">10.1589126586914</t>
   </si>
   <si>
     <t xml:space="preserve">10.0402927398682</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70137882232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73526859283447</t>
+    <t xml:space="preserve">9.70137977600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73526954650879</t>
   </si>
   <si>
     <t xml:space="preserve">9.70985317230225</t>
@@ -443,7 +443,7 @@
     <t xml:space="preserve">10.1250200271606</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2944765090942</t>
+    <t xml:space="preserve">10.2944774627686</t>
   </si>
   <si>
     <t xml:space="preserve">10.4808778762817</t>
@@ -452,7 +452,7 @@
     <t xml:space="preserve">10.5317163467407</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5147695541382</t>
+    <t xml:space="preserve">10.5147705078125</t>
   </si>
   <si>
     <t xml:space="preserve">10.802845954895</t>
@@ -464,214 +464,214 @@
     <t xml:space="preserve">10.8621559143066</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0146675109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0570316314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2773246765137</t>
+    <t xml:space="preserve">11.014666557312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0570306777954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2773237228394</t>
   </si>
   <si>
     <t xml:space="preserve">11.4383068084717</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6586008071899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5823459625244</t>
+    <t xml:space="preserve">11.6586017608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5823450088501</t>
   </si>
   <si>
     <t xml:space="preserve">11.4806718826294</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5908184051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7009649276733</t>
+    <t xml:space="preserve">11.5908193588257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7009658813477</t>
   </si>
   <si>
     <t xml:space="preserve">11.7772207260132</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8111124038696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8365306854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6670732498169</t>
+    <t xml:space="preserve">11.8111114501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8365297317505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6670742034912</t>
   </si>
   <si>
     <t xml:space="preserve">11.5992918014526</t>
   </si>
   <si>
+    <t xml:space="preserve">11.5230369567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6077632904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6263818740845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7297267913818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6952772140503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6780548095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7986249923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8847465515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9105815887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0656003952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3153514862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3584117889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0569877624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1431083679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9967021942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8416843414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7555627822876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7125043869019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8502969741821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9191932678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9622554779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0397644042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.048376083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7900114059448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0311527252197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9450302124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8158483505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8933582305908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8761320114136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8244600296021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8675203323364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.901969909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.927806854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7211141586304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6694412231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6349945068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6091556549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5747079849243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5316476821899</t>
+  </si>
+  <si>
     <t xml:space="preserve">11.5230360031128</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6077632904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6263818740845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7297267913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6952772140503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6780548095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7986249923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8847455978394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9105825424194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0656003952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3153505325317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3584146499634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0569877624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1431083679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9967031478882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8416843414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7555627822876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7125024795532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8502960205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9191942214966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.962254524231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0397624969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0483751296997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7900114059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0311517715454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9450302124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8158473968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8933582305908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8761329650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8244590759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8675203323364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.901967048645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.927806854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7211132049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6694412231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6349935531616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6091566085815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.57470703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5316486358643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5230369567871</t>
-  </si>
-  <si>
     <t xml:space="preserve">11.3680171966553</t>
   </si>
   <si>
     <t xml:space="preserve">11.3594045639038</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2818956375122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2302227020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1957740783691</t>
+    <t xml:space="preserve">11.2818965911865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2302217483521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1957731246948</t>
   </si>
   <si>
     <t xml:space="preserve">11.1871633529663</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1096525192261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0579814910889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1785516738892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1268768310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9374103546143</t>
+    <t xml:space="preserve">11.1096534729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0579805374146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1785507202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.126877784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9374113082886</t>
   </si>
   <si>
     <t xml:space="preserve">11.066593170166</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0235319137573</t>
+    <t xml:space="preserve">11.023530960083</t>
   </si>
   <si>
     <t xml:space="preserve">11.083815574646</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1354894638062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2043867111206</t>
+    <t xml:space="preserve">11.1354904174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2043857574463</t>
   </si>
   <si>
     <t xml:space="preserve">11.3163433074951</t>
@@ -686,52 +686,52 @@
     <t xml:space="preserve">11.411078453064</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2905082702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1613254547119</t>
+    <t xml:space="preserve">11.2905073165894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1613273620605</t>
   </si>
   <si>
     <t xml:space="preserve">11.2646722793579</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1527137756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0407571792603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4196910858154</t>
+    <t xml:space="preserve">11.1527128219604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0407562255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4196901321411</t>
   </si>
   <si>
     <t xml:space="preserve">11.2216100692749</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2388362884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3421802520752</t>
+    <t xml:space="preserve">11.2388343811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3421812057495</t>
   </si>
   <si>
     <t xml:space="preserve">10.9546346664429</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9632453918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0063076019287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0924291610718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74032592773438</t>
+    <t xml:space="preserve">10.96324634552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0063066482544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0924272537231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74032306671143</t>
   </si>
   <si>
     <t xml:space="preserve">9.01690483093262</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21498203277588</t>
+    <t xml:space="preserve">9.2149829864502</t>
   </si>
   <si>
     <t xml:space="preserve">9.37861442565918</t>
@@ -740,16 +740,16 @@
     <t xml:space="preserve">9.49057197570801</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50779724121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.593918800354</t>
+    <t xml:space="preserve">9.50779628753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59391689300537</t>
   </si>
   <si>
     <t xml:space="preserve">9.60252952575684</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6886510848999</t>
+    <t xml:space="preserve">9.68865203857422</t>
   </si>
   <si>
     <t xml:space="preserve">9.56808090209961</t>
@@ -758,10 +758,10 @@
     <t xml:space="preserve">9.39583778381348</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34416389465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25804424285889</t>
+    <t xml:space="preserve">9.34416484832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25804328918457</t>
   </si>
   <si>
     <t xml:space="preserve">9.30110549926758</t>
@@ -773,31 +773,31 @@
     <t xml:space="preserve">9.28388118743896</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24081993103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12886142730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02551555633545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20637130737305</t>
+    <t xml:space="preserve">9.24081897735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12886238098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02551651000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20637035369873</t>
   </si>
   <si>
     <t xml:space="preserve">9.26665592193604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69726276397705</t>
+    <t xml:space="preserve">9.69726467132568</t>
   </si>
   <si>
     <t xml:space="preserve">9.65420246124268</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66281509399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64559078216553</t>
+    <t xml:space="preserve">9.66281414031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64558887481689</t>
   </si>
   <si>
     <t xml:space="preserve">9.67142581939697</t>
@@ -809,34 +809,34 @@
     <t xml:space="preserve">9.71448707580566</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09441375732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9393949508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14608669281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1202507019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83505630493164</t>
+    <t xml:space="preserve">9.0944128036499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93939590454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14608573913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12024974822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83505821228027</t>
   </si>
   <si>
     <t xml:space="preserve">9.73171138763428</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90395355224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77477264404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53363227844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49918270111084</t>
+    <t xml:space="preserve">9.90395545959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77477359771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53363132476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49918365478516</t>
   </si>
   <si>
     <t xml:space="preserve">9.57669353485107</t>
@@ -854,22 +854,22 @@
     <t xml:space="preserve">9.54224491119385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17192363739014</t>
+    <t xml:space="preserve">9.17192268371582</t>
   </si>
   <si>
     <t xml:space="preserve">9.23220729827881</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55946922302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51640892028809</t>
+    <t xml:space="preserve">9.55947017669678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51640796661377</t>
   </si>
   <si>
     <t xml:space="preserve">9.86089324951172</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95661926269531</t>
+    <t xml:space="preserve">8.95662021636963</t>
   </si>
   <si>
     <t xml:space="preserve">8.91355991363525</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">9.0427417755127</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99967956542969</t>
+    <t xml:space="preserve">8.999680519104</t>
   </si>
   <si>
     <t xml:space="preserve">8.82743740081787</t>
@@ -893,13 +893,13 @@
     <t xml:space="preserve">8.87049770355225</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7843770980835</t>
+    <t xml:space="preserve">8.78437805175781</t>
   </si>
   <si>
     <t xml:space="preserve">8.74131488800049</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61213302612305</t>
+    <t xml:space="preserve">8.61213397979736</t>
   </si>
   <si>
     <t xml:space="preserve">8.59490966796875</t>
@@ -914,7 +914,7 @@
     <t xml:space="preserve">9.06314468383789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10714149475098</t>
+    <t xml:space="preserve">9.10714054107666</t>
   </si>
   <si>
     <t xml:space="preserve">9.0191478729248</t>
@@ -923,10 +923,10 @@
     <t xml:space="preserve">8.97515296936035</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93115615844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88716316223145</t>
+    <t xml:space="preserve">8.93115711212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88716220855713</t>
   </si>
   <si>
     <t xml:space="preserve">8.84316444396973</t>
@@ -938,10 +938,10 @@
     <t xml:space="preserve">8.48239994049072</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71117687225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62318706512451</t>
+    <t xml:space="preserve">8.71117782592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62318801879883</t>
   </si>
   <si>
     <t xml:space="preserve">8.58798885345459</t>
@@ -950,7 +950,7 @@
     <t xml:space="preserve">8.65838241577148</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60558795928955</t>
+    <t xml:space="preserve">8.60558700561523</t>
   </si>
   <si>
     <t xml:space="preserve">8.7287769317627</t>
@@ -965,7 +965,7 @@
     <t xml:space="preserve">8.53519439697266</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44720268249512</t>
+    <t xml:space="preserve">8.44720363616943</t>
   </si>
   <si>
     <t xml:space="preserve">8.27122020721436</t>
@@ -977,58 +977,58 @@
     <t xml:space="preserve">8.28881740570068</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78157043457031</t>
+    <t xml:space="preserve">8.78157138824463</t>
   </si>
   <si>
     <t xml:space="preserve">8.64078330993652</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79916858673096</t>
+    <t xml:space="preserve">8.79916954040527</t>
   </si>
   <si>
     <t xml:space="preserve">8.67598152160645</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23912906646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37111663818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32711887359619</t>
+    <t xml:space="preserve">9.23912811279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37111473083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32712078094482</t>
   </si>
   <si>
     <t xml:space="preserve">9.1951322555542</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15113544464111</t>
+    <t xml:space="preserve">9.15113639831543</t>
   </si>
   <si>
     <t xml:space="preserve">8.46480083465576</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41200542449951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49999713897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34161376953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23602199554443</t>
+    <t xml:space="preserve">8.41200637817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49999904632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34161186218262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23602104187012</t>
   </si>
   <si>
     <t xml:space="preserve">8.30641555786133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13043212890625</t>
+    <t xml:space="preserve">8.13043117523193</t>
   </si>
   <si>
     <t xml:space="preserve">8.1832275390625</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16562938690186</t>
+    <t xml:space="preserve">8.16563034057617</t>
   </si>
   <si>
     <t xml:space="preserve">8.21842479705811</t>
@@ -1037,7 +1037,7 @@
     <t xml:space="preserve">8.25362110137939</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37681102752686</t>
+    <t xml:space="preserve">8.37681007385254</t>
   </si>
   <si>
     <t xml:space="preserve">8.51759624481201</t>
@@ -1049,7 +1049,7 @@
     <t xml:space="preserve">9.41511058807373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63508987426758</t>
+    <t xml:space="preserve">9.63509082794189</t>
   </si>
   <si>
     <t xml:space="preserve">9.59109401702881</t>
@@ -1058,37 +1058,37 @@
     <t xml:space="preserve">9.8990650177002</t>
   </si>
   <si>
-    <t xml:space="preserve">10.119044303894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1630411148071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2070369720459</t>
+    <t xml:space="preserve">10.1190452575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1630401611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2070379257202</t>
   </si>
   <si>
     <t xml:space="preserve">10.3390245437622</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2950286865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.383020401001</t>
+    <t xml:space="preserve">10.2950277328491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3830213546753</t>
   </si>
   <si>
     <t xml:space="preserve">10.2510318756104</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4270162582397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0750484466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5150079727173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6498165130615</t>
+    <t xml:space="preserve">10.4270143508911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.075047492981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5150089263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6498146057129</t>
   </si>
   <si>
     <t xml:space="preserve">10.4700708389282</t>
@@ -1097,19 +1097,19 @@
     <t xml:space="preserve">10.694751739502</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6048793792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3802013397217</t>
+    <t xml:space="preserve">10.6048803329468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3802003860474</t>
   </si>
   <si>
     <t xml:space="preserve">10.2453918457031</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0656471252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4251356124878</t>
+    <t xml:space="preserve">10.0656480789185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4251365661621</t>
   </si>
   <si>
     <t xml:space="preserve">10.3352642059326</t>
@@ -1118,22 +1118,22 @@
     <t xml:space="preserve">10.2903270721436</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2004566192627</t>
+    <t xml:space="preserve">10.200457572937</t>
   </si>
   <si>
     <t xml:space="preserve">9.97577667236328</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1105842590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93084144592285</t>
+    <t xml:space="preserve">10.1105833053589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93083953857422</t>
   </si>
   <si>
     <t xml:space="preserve">9.88590431213379</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1555213928223</t>
+    <t xml:space="preserve">10.1555204391479</t>
   </si>
   <si>
     <t xml:space="preserve">10.020712852478</t>
@@ -1142,10 +1142,10 @@
     <t xml:space="preserve">9.75109672546387</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70616149902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3466739654541</t>
+    <t xml:space="preserve">9.70616245269775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34667301177979</t>
   </si>
   <si>
     <t xml:space="preserve">9.30173778533936</t>
@@ -1160,31 +1160,31 @@
     <t xml:space="preserve">9.61628913879395</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52641677856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43654537200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12199306488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0321216583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16692924499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07705879211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25680160522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98718643188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57135391235352</t>
+    <t xml:space="preserve">9.52641868591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43654441833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12199401855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03212261199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16693019866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07705783843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25680065155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98718738555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57135200500488</t>
   </si>
   <si>
     <t xml:space="preserve">9.66122531890869</t>
@@ -1193,7 +1193,7 @@
     <t xml:space="preserve">9.79603290557861</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9643669128418</t>
+    <t xml:space="preserve">10.9643678665161</t>
   </si>
   <si>
     <t xml:space="preserve">11.4586629867554</t>
@@ -1202,7 +1202,7 @@
     <t xml:space="preserve">11.5035991668701</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2339820861816</t>
+    <t xml:space="preserve">11.2339811325073</t>
   </si>
   <si>
     <t xml:space="preserve">11.1441116333008</t>
@@ -1220,16 +1220,16 @@
     <t xml:space="preserve">11.2789192199707</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4137268066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5485334396362</t>
+    <t xml:space="preserve">11.413724899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5485343933105</t>
   </si>
   <si>
     <t xml:space="preserve">11.6833429336548</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7732133865356</t>
+    <t xml:space="preserve">11.77321434021</t>
   </si>
   <si>
     <t xml:space="preserve">11.9080209732056</t>
@@ -1241,19 +1241,19 @@
     <t xml:space="preserve">11.9978933334351</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8181505203247</t>
+    <t xml:space="preserve">11.8181495666504</t>
   </si>
   <si>
     <t xml:space="preserve">11.593469619751</t>
   </si>
   <si>
-    <t xml:space="preserve">12.312445640564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5820608139038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9415473937988</t>
+    <t xml:space="preserve">12.3124446868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5820617675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9415483474731</t>
   </si>
   <si>
     <t xml:space="preserve">12.8067407608032</t>
@@ -1262,19 +1262,19 @@
     <t xml:space="preserve">12.7618045806885</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0763559341431</t>
+    <t xml:space="preserve">13.0763568878174</t>
   </si>
   <si>
     <t xml:space="preserve">12.4472532272339</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5371246337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2675085067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4023170471191</t>
+    <t xml:space="preserve">12.5371236801147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2675094604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4023180007935</t>
   </si>
   <si>
     <t xml:space="preserve">12.6269969940186</t>
@@ -1289,7 +1289,7 @@
     <t xml:space="preserve">11.7282781600952</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7846231460571</t>
+    <t xml:space="preserve">10.7846240997314</t>
   </si>
   <si>
     <t xml:space="preserve">10.5599431991577</t>
@@ -1298,22 +1298,22 @@
     <t xml:space="preserve">8.89731407165527</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98062181472778</t>
+    <t xml:space="preserve">7.98062086105347</t>
   </si>
   <si>
     <t xml:space="preserve">7.81885194778442</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53126239776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89074897766113</t>
+    <t xml:space="preserve">7.53126192092896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89074802398682</t>
   </si>
   <si>
     <t xml:space="preserve">8.53782749176025</t>
   </si>
   <si>
-    <t xml:space="preserve">7.962646484375</t>
+    <t xml:space="preserve">7.96264743804932</t>
   </si>
   <si>
     <t xml:space="preserve">8.44795513153076</t>
@@ -1325,16 +1325,16 @@
     <t xml:space="preserve">8.66364669799805</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86136531829834</t>
+    <t xml:space="preserve">8.86136627197266</t>
   </si>
   <si>
     <t xml:space="preserve">9.21186637878418</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93848896026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80045509338379</t>
+    <t xml:space="preserve">9.93848991394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80045413970947</t>
   </si>
   <si>
     <t xml:space="preserve">9.89247894287109</t>
@@ -1349,34 +1349,34 @@
     <t xml:space="preserve">9.84646701812744</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1225357055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75444316864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3986053466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3065814971924</t>
+    <t xml:space="preserve">10.1225366592407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75444412231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3986043930054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3065824508667</t>
   </si>
   <si>
     <t xml:space="preserve">10.7206840515137</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5826511383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8587198257446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6746740341187</t>
+    <t xml:space="preserve">10.5826501846313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8587207794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.674674987793</t>
   </si>
   <si>
     <t xml:space="preserve">10.9967546463013</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6286630630493</t>
+    <t xml:space="preserve">10.628662109375</t>
   </si>
   <si>
     <t xml:space="preserve">10.7666969299316</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">11.3188352584839</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5028820037842</t>
+    <t xml:space="preserve">11.5028810501099</t>
   </si>
   <si>
     <t xml:space="preserve">11.1807994842529</t>
@@ -1406,19 +1406,19 @@
     <t xml:space="preserve">10.9507417678833</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0887775421143</t>
+    <t xml:space="preserve">11.0887765884399</t>
   </si>
   <si>
     <t xml:space="preserve">10.8127088546753</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9047317504883</t>
+    <t xml:space="preserve">10.904730796814</t>
   </si>
   <si>
     <t xml:space="preserve">11.4108591079712</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4568700790405</t>
+    <t xml:space="preserve">11.4568710327148</t>
   </si>
   <si>
     <t xml:space="preserve">11.2268123626709</t>
@@ -1430,7 +1430,7 @@
     <t xml:space="preserve">11.5488929748535</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5949039459229</t>
+    <t xml:space="preserve">11.5949058532715</t>
   </si>
   <si>
     <t xml:space="preserve">11.6869277954102</t>
@@ -1439,7 +1439,7 @@
     <t xml:space="preserve">11.9629974365234</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7789506912231</t>
+    <t xml:space="preserve">11.7789516448975</t>
   </si>
   <si>
     <t xml:space="preserve">12.0090084075928</t>
@@ -1457,7 +1457,7 @@
     <t xml:space="preserve">12.0550203323364</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8709735870361</t>
+    <t xml:space="preserve">11.8709726333618</t>
   </si>
   <si>
     <t xml:space="preserve">11.9169845581055</t>
@@ -1469,7 +1469,7 @@
     <t xml:space="preserve">12.1470422744751</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6991806030273</t>
+    <t xml:space="preserve">12.6991815567017</t>
   </si>
   <si>
     <t xml:space="preserve">12.7912034988403</t>
@@ -1487,7 +1487,7 @@
     <t xml:space="preserve">13.2053089141846</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2513189315796</t>
+    <t xml:space="preserve">13.2513198852539</t>
   </si>
   <si>
     <t xml:space="preserve">13.1132850646973</t>
@@ -1505,13 +1505,13 @@
     <t xml:space="preserve">12.9752511978149</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7114343643188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4353647232056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5151348114014</t>
+    <t xml:space="preserve">13.7114334106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4353666305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5151357650757</t>
   </si>
   <si>
     <t xml:space="preserve">12.3770999908447</t>
@@ -1523,31 +1523,31 @@
     <t xml:space="preserve">12.7451934814453</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6531686782837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3433437347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6194114685059</t>
+    <t xml:space="preserve">12.653169631958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3433427810669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6194124221802</t>
   </si>
   <si>
     <t xml:space="preserve">13.8494691848755</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9414930343628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1715497970581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3555965423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1255388259888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4936304092407</t>
+    <t xml:space="preserve">13.9414920806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1715488433838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3555955886841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1255378723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.493631362915</t>
   </si>
   <si>
     <t xml:space="preserve">14.7236881256104</t>
@@ -1556,7 +1556,7 @@
     <t xml:space="preserve">14.6776762008667</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8157119750977</t>
+    <t xml:space="preserve">14.8157110214233</t>
   </si>
   <si>
     <t xml:space="preserve">14.861722946167</t>
@@ -1568,25 +1568,25 @@
     <t xml:space="preserve">14.5396423339844</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6316652297974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4476194381714</t>
+    <t xml:space="preserve">14.6316661834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4476184844971</t>
   </si>
   <si>
     <t xml:space="preserve">14.2635726928711</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9875040054321</t>
+    <t xml:space="preserve">13.9875030517578</t>
   </si>
   <si>
     <t xml:space="preserve">14.3095855712891</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6654233932495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8034572601318</t>
+    <t xml:space="preserve">13.6654243469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8034582138062</t>
   </si>
   <si>
     <t xml:space="preserve">13.5734004974365</t>
@@ -1595,13 +1595,13 @@
     <t xml:space="preserve">13.7574453353882</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9537448883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0335140228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4269781112671</t>
+    <t xml:space="preserve">14.95374584198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0335149765015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4269771575928</t>
   </si>
   <si>
     <t xml:space="preserve">14.3801374435425</t>
@@ -1616,7 +1616,7 @@
     <t xml:space="preserve">14.8485460281372</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0359086990356</t>
+    <t xml:space="preserve">15.03590965271</t>
   </si>
   <si>
     <t xml:space="preserve">15.0827503204346</t>
@@ -1625,10 +1625,10 @@
     <t xml:space="preserve">14.8953857421875</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9422283172607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1764316558838</t>
+    <t xml:space="preserve">14.9422273635864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1764326095581</t>
   </si>
   <si>
     <t xml:space="preserve">15.1295900344849</t>
@@ -1637,10 +1637,10 @@
     <t xml:space="preserve">14.989068031311</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6611804962158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3169546127319</t>
+    <t xml:space="preserve">14.6611814498901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3169555664062</t>
   </si>
   <si>
     <t xml:space="preserve">14.7548637390137</t>
@@ -1649,7 +1649,7 @@
     <t xml:space="preserve">14.8017053604126</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2232713699341</t>
+    <t xml:space="preserve">15.2232723236084</t>
   </si>
   <si>
     <t xml:space="preserve">15.5043172836304</t>
@@ -1688,25 +1688,25 @@
     <t xml:space="preserve">17.1437454223633</t>
   </si>
   <si>
-    <t xml:space="preserve">16.581657409668</t>
+    <t xml:space="preserve">16.5816593170166</t>
   </si>
   <si>
     <t xml:space="preserve">16.2069282531738</t>
   </si>
   <si>
-    <t xml:space="preserve">17.284273147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7995185852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4716300964355</t>
+    <t xml:space="preserve">17.2842712402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7995204925537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4716320037842</t>
   </si>
   <si>
     <t xml:space="preserve">16.8158626556396</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6284980773926</t>
+    <t xml:space="preserve">16.6284961700439</t>
   </si>
   <si>
     <t xml:space="preserve">17.0969066619873</t>
@@ -1730,7 +1730,7 @@
     <t xml:space="preserve">18.923698425293</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7668342590332</t>
+    <t xml:space="preserve">19.7668361663818</t>
   </si>
   <si>
     <t xml:space="preserve">19.5794696807861</t>
@@ -1742,7 +1742,7 @@
     <t xml:space="preserve">19.1110610961914</t>
   </si>
   <si>
-    <t xml:space="preserve">19.673152923584</t>
+    <t xml:space="preserve">19.6731510162354</t>
   </si>
   <si>
     <t xml:space="preserve">19.2984256744385</t>
@@ -1751,7 +1751,7 @@
     <t xml:space="preserve">19.4857883453369</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8605155944824</t>
+    <t xml:space="preserve">19.8605175018311</t>
   </si>
   <si>
     <t xml:space="preserve">20.3289241790771</t>
@@ -1760,10 +1760,10 @@
     <t xml:space="preserve">20.9846954345703</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2657413482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0783748626709</t>
+    <t xml:space="preserve">21.265739440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0783767700195</t>
   </si>
   <si>
     <t xml:space="preserve">21.453104019165</t>
@@ -1775,13 +1775,13 @@
     <t xml:space="preserve">21.8278293609619</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1088752746582</t>
+    <t xml:space="preserve">22.1088771820068</t>
   </si>
   <si>
     <t xml:space="preserve">21.7341499328613</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0151920318604</t>
+    <t xml:space="preserve">22.015193939209</t>
   </si>
   <si>
     <t xml:space="preserve">22.296236038208</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">21.5467853546143</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2352428436279</t>
+    <t xml:space="preserve">20.2352409362793</t>
   </si>
   <si>
     <t xml:space="preserve">18.3147678375244</t>
@@ -1829,7 +1829,7 @@
     <t xml:space="preserve">20.5162868499756</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0478763580322</t>
+    <t xml:space="preserve">20.0478782653809</t>
   </si>
   <si>
     <t xml:space="preserve">22.6709671020508</t>
@@ -1838,7 +1838,7 @@
     <t xml:space="preserve">22.2025585174561</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3899211883545</t>
+    <t xml:space="preserve">22.3899192810059</t>
   </si>
   <si>
     <t xml:space="preserve">19.9541969299316</t>
@@ -1853,7 +1853,7 @@
     <t xml:space="preserve">19.3921070098877</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8300170898438</t>
+    <t xml:space="preserve">18.8300189971924</t>
   </si>
   <si>
     <t xml:space="preserve">18.361608505249</t>
@@ -1865,7 +1865,7 @@
     <t xml:space="preserve">17.6589946746826</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7526798248291</t>
+    <t xml:space="preserve">17.7526779174805</t>
   </si>
   <si>
     <t xml:space="preserve">17.377950668335</t>
@@ -1880,19 +1880,19 @@
     <t xml:space="preserve">18.2679271697998</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8768577575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6426544189453</t>
+    <t xml:space="preserve">18.8768558502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6426525115967</t>
   </si>
   <si>
     <t xml:space="preserve">18.3241367340088</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2117156982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2304534912109</t>
+    <t xml:space="preserve">18.2117176055908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2304553985596</t>
   </si>
   <si>
     <t xml:space="preserve">18.4552898406982</t>
@@ -1904,7 +1904,7 @@
     <t xml:space="preserve">18.1180362701416</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9705390930176</t>
+    <t xml:space="preserve">18.9705410003662</t>
   </si>
   <si>
     <t xml:space="preserve">20.2820835113525</t>
@@ -1913,7 +1913,7 @@
     <t xml:space="preserve">20.0947208404541</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1884002685547</t>
+    <t xml:space="preserve">20.1884021759033</t>
   </si>
   <si>
     <t xml:space="preserve">20.1415596008301</t>
@@ -1925,13 +1925,13 @@
     <t xml:space="preserve">17.5559463500977</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1999549865723</t>
+    <t xml:space="preserve">17.1999568939209</t>
   </si>
   <si>
     <t xml:space="preserve">16.8847980499268</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7634201049805</t>
+    <t xml:space="preserve">17.7634181976318</t>
   </si>
   <si>
     <t xml:space="preserve">18.0308246612549</t>
@@ -1943,7 +1943,7 @@
     <t xml:space="preserve">18.4319343566895</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6038379669189</t>
+    <t xml:space="preserve">18.6038398742676</t>
   </si>
   <si>
     <t xml:space="preserve">19.1004505157471</t>
@@ -1952,19 +1952,19 @@
     <t xml:space="preserve">18.9858474731445</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1482009887695</t>
+    <t xml:space="preserve">19.1481990814209</t>
   </si>
   <si>
     <t xml:space="preserve">18.90944480896</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9476470947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0077228546143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0554752349854</t>
+    <t xml:space="preserve">18.9476490020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0077247619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0554733276367</t>
   </si>
   <si>
     <t xml:space="preserve">20.5329856872559</t>
@@ -1973,16 +1973,16 @@
     <t xml:space="preserve">20.9149932861328</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1509742736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4374809265137</t>
+    <t xml:space="preserve">20.1509761810303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4374828338623</t>
   </si>
   <si>
     <t xml:space="preserve">21.0104961395264</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4880065917969</t>
+    <t xml:space="preserve">21.4880084991455</t>
   </si>
   <si>
     <t xml:space="preserve">19.5779628753662</t>
@@ -1997,13 +1997,13 @@
     <t xml:space="preserve">19.2914562225342</t>
   </si>
   <si>
-    <t xml:space="preserve">19.339204788208</t>
+    <t xml:space="preserve">19.3392066955566</t>
   </si>
   <si>
     <t xml:space="preserve">18.813943862915</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6993408203125</t>
+    <t xml:space="preserve">18.6993389129639</t>
   </si>
   <si>
     <t xml:space="preserve">19.3869571685791</t>
@@ -2018,7 +2018,7 @@
     <t xml:space="preserve">18.240930557251</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7757415771484</t>
+    <t xml:space="preserve">18.7757434844971</t>
   </si>
   <si>
     <t xml:space="preserve">19.9599704742432</t>
@@ -2036,13 +2036,13 @@
     <t xml:space="preserve">21.392505645752</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1537494659424</t>
+    <t xml:space="preserve">21.1537475585938</t>
   </si>
   <si>
     <t xml:space="preserve">21.7745132446289</t>
   </si>
   <si>
-    <t xml:space="preserve">21.679012298584</t>
+    <t xml:space="preserve">21.6790103912354</t>
   </si>
   <si>
     <t xml:space="preserve">21.9177684783936</t>
@@ -2057,7 +2057,7 @@
     <t xml:space="preserve">21.5835094451904</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5807323455811</t>
+    <t xml:space="preserve">20.5807342529297</t>
   </si>
   <si>
     <t xml:space="preserve">20.1032218933105</t>
@@ -2075,7 +2075,7 @@
     <t xml:space="preserve">22.9205417633057</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4430294036865</t>
+    <t xml:space="preserve">22.4430313110352</t>
   </si>
   <si>
     <t xml:space="preserve">22.1565227508545</t>
@@ -2087,16 +2087,16 @@
     <t xml:space="preserve">22.3475284576416</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0582447052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3897323608398</t>
+    <t xml:space="preserve">21.0582466125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3897304534912</t>
   </si>
   <si>
     <t xml:space="preserve">20.2942276000977</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1987266540527</t>
+    <t xml:space="preserve">20.1987247467041</t>
   </si>
   <si>
     <t xml:space="preserve">20.8194904327393</t>
@@ -2120,7 +2120,7 @@
     <t xml:space="preserve">19.8167171478271</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2464771270752</t>
+    <t xml:space="preserve">20.2464790344238</t>
   </si>
   <si>
     <t xml:space="preserve">20.6762371063232</t>
@@ -2129,7 +2129,7 @@
     <t xml:space="preserve">19.7689666748047</t>
   </si>
   <si>
-    <t xml:space="preserve">21.440258026123</t>
+    <t xml:space="preserve">21.4402561187744</t>
   </si>
   <si>
     <t xml:space="preserve">22.6340351104736</t>
@@ -2144,10 +2144,10 @@
     <t xml:space="preserve">22.5862808227539</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8727893829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5385303497314</t>
+    <t xml:space="preserve">22.8727912902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5385322570801</t>
   </si>
   <si>
     <t xml:space="preserve">22.6817855834961</t>
@@ -2156,7 +2156,7 @@
     <t xml:space="preserve">23.0160427093506</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3025512695312</t>
+    <t xml:space="preserve">23.3025493621826</t>
   </si>
   <si>
     <t xml:space="preserve">24.4485759735107</t>
@@ -2165,13 +2165,13 @@
     <t xml:space="preserve">23.7323112487793</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9710655212402</t>
+    <t xml:space="preserve">23.9710636138916</t>
   </si>
   <si>
     <t xml:space="preserve">24.2098217010498</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0665664672852</t>
+    <t xml:space="preserve">24.0665683746338</t>
   </si>
   <si>
     <t xml:space="preserve">24.1143188476562</t>
@@ -2186,19 +2186,19 @@
     <t xml:space="preserve">23.7800598144531</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9233131408691</t>
+    <t xml:space="preserve">23.9233150482178</t>
   </si>
   <si>
     <t xml:space="preserve">25.0693416595459</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5440788269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9260883331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3558483123779</t>
+    <t xml:space="preserve">24.5440807342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9260864257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3558464050293</t>
   </si>
   <si>
     <t xml:space="preserve">25.4035987854004</t>
@@ -2219,16 +2219,16 @@
     <t xml:space="preserve">24.5918292999268</t>
   </si>
   <si>
-    <t xml:space="preserve">24.830587387085</t>
+    <t xml:space="preserve">24.8305854797363</t>
   </si>
   <si>
     <t xml:space="preserve">25.260347366333</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7378597259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.785608291626</t>
+    <t xml:space="preserve">25.7378578186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7856101989746</t>
   </si>
   <si>
     <t xml:space="preserve">26.0721130371094</t>
@@ -2240,13 +2240,13 @@
     <t xml:space="preserve">25.4513492584229</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9288597106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5946044921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6901054382324</t>
+    <t xml:space="preserve">25.928861618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5946025848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6901073455811</t>
   </si>
   <si>
     <t xml:space="preserve">25.5468521118164</t>
@@ -2261,16 +2261,16 @@
     <t xml:space="preserve">27.0748901367188</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1703910827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6506748199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3219661712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8922023773193</t>
+    <t xml:space="preserve">27.1703929901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6506767272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.321964263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.892204284668</t>
   </si>
   <si>
     <t xml:space="preserve">29.9877071380615</t>
@@ -2279,7 +2279,7 @@
     <t xml:space="preserve">30.1309604644775</t>
   </si>
   <si>
-    <t xml:space="preserve">29.653450012207</t>
+    <t xml:space="preserve">29.6534481048584</t>
   </si>
   <si>
     <t xml:space="preserve">29.510196685791</t>
@@ -2297,7 +2297,7 @@
     <t xml:space="preserve">28.8416805267334</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2236919403076</t>
+    <t xml:space="preserve">29.223690032959</t>
   </si>
   <si>
     <t xml:space="preserve">29.1281871795654</t>
@@ -2318,10 +2318,10 @@
     <t xml:space="preserve">28.3641681671143</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8866577148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2714385986328</t>
+    <t xml:space="preserve">27.8866596221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2714405059814</t>
   </si>
   <si>
     <t xml:space="preserve">27.8389053344727</t>
@@ -2330,7 +2330,7 @@
     <t xml:space="preserve">27.6479034423828</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6029262542725</t>
+    <t xml:space="preserve">28.6029243469238</t>
   </si>
   <si>
     <t xml:space="preserve">28.4119205474854</t>
@@ -2339,7 +2339,7 @@
     <t xml:space="preserve">29.366943359375</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4146938323975</t>
+    <t xml:space="preserve">29.4146919250488</t>
   </si>
   <si>
     <t xml:space="preserve">30.0354595184326</t>
@@ -2357,13 +2357,13 @@
     <t xml:space="preserve">29.7012023925781</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5579490661621</t>
+    <t xml:space="preserve">29.5579471588135</t>
   </si>
   <si>
     <t xml:space="preserve">29.796703338623</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2209148406982</t>
+    <t xml:space="preserve">28.2209167480469</t>
   </si>
   <si>
     <t xml:space="preserve">28.3164176940918</t>
@@ -2375,10 +2375,10 @@
     <t xml:space="preserve">26.9480724334717</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5770225524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5930156707764</t>
+    <t xml:space="preserve">27.5770206451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.593017578125</t>
   </si>
   <si>
     <t xml:space="preserve">28.0124492645264</t>
@@ -2396,7 +2396,7 @@
     <t xml:space="preserve">28.0608291625977</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3994960784912</t>
+    <t xml:space="preserve">28.3994941711426</t>
   </si>
   <si>
     <t xml:space="preserve">28.7381591796875</t>
@@ -2405,7 +2405,7 @@
     <t xml:space="preserve">29.1252059936523</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9800643920898</t>
+    <t xml:space="preserve">28.9800624847412</t>
   </si>
   <si>
     <t xml:space="preserve">27.7705459594727</t>
@@ -2447,19 +2447,19 @@
     <t xml:space="preserve">29.2219676971436</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0284423828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2543525695801</t>
+    <t xml:space="preserve">29.0284442901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2543544769287</t>
   </si>
   <si>
     <t xml:space="preserve">29.705774307251</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0444393157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.996057510376</t>
+    <t xml:space="preserve">30.0444374084473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9960594177246</t>
   </si>
   <si>
     <t xml:space="preserve">28.8349208831787</t>
@@ -2474,7 +2474,7 @@
     <t xml:space="preserve">28.2059707641602</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4962558746338</t>
+    <t xml:space="preserve">28.4962577819824</t>
   </si>
   <si>
     <t xml:space="preserve">27.0932140350342</t>
@@ -2483,7 +2483,7 @@
     <t xml:space="preserve">26.8513107299805</t>
   </si>
   <si>
-    <t xml:space="preserve">26.077220916748</t>
+    <t xml:space="preserve">26.0772190093994</t>
   </si>
   <si>
     <t xml:space="preserve">26.8996906280518</t>
@@ -2507,22 +2507,22 @@
     <t xml:space="preserve">25.3031272888184</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2547473907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1579856872559</t>
+    <t xml:space="preserve">25.2547454833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1579837799072</t>
   </si>
   <si>
     <t xml:space="preserve">24.9160804748535</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4966487884521</t>
+    <t xml:space="preserve">25.4966506958008</t>
   </si>
   <si>
     <t xml:space="preserve">25.3515071868896</t>
   </si>
   <si>
-    <t xml:space="preserve">25.061222076416</t>
+    <t xml:space="preserve">25.0612239837646</t>
   </si>
   <si>
     <t xml:space="preserve">24.7225570678711</t>
@@ -2531,7 +2531,7 @@
     <t xml:space="preserve">24.4806537628174</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6098022460938</t>
+    <t xml:space="preserve">23.6098003387451</t>
   </si>
   <si>
     <t xml:space="preserve">23.0292301177979</t>
@@ -2540,7 +2540,7 @@
     <t xml:space="preserve">22.9324722290039</t>
   </si>
   <si>
-    <t xml:space="preserve">23.174373626709</t>
+    <t xml:space="preserve">23.1743755340576</t>
   </si>
   <si>
     <t xml:space="preserve">22.5938053131104</t>
@@ -2552,7 +2552,7 @@
     <t xml:space="preserve">21.6745719909668</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9164733886719</t>
+    <t xml:space="preserve">21.9164752960205</t>
   </si>
   <si>
     <t xml:space="preserve">21.5294284820557</t>
@@ -2564,16 +2564,16 @@
     <t xml:space="preserve">21.0940017700195</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4650535583496</t>
+    <t xml:space="preserve">20.465051651001</t>
   </si>
   <si>
     <t xml:space="preserve">20.2231483459473</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4166717529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9004802703857</t>
+    <t xml:space="preserve">20.4166736602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9004783630371</t>
   </si>
   <si>
     <t xml:space="preserve">20.8037185668945</t>
@@ -2582,22 +2582,22 @@
     <t xml:space="preserve">20.6101951599121</t>
   </si>
   <si>
-    <t xml:space="preserve">20.658576965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7069549560547</t>
+    <t xml:space="preserve">20.6585750579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7069568634033</t>
   </si>
   <si>
     <t xml:space="preserve">20.7553386688232</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3359050750732</t>
+    <t xml:space="preserve">21.3359069824219</t>
   </si>
   <si>
     <t xml:space="preserve">21.0456218719482</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4490566253662</t>
+    <t xml:space="preserve">19.4490585327148</t>
   </si>
   <si>
     <t xml:space="preserve">19.8361034393311</t>
@@ -2606,7 +2606,7 @@
     <t xml:space="preserve">19.2361812591553</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8878421783447</t>
+    <t xml:space="preserve">18.8878402709961</t>
   </si>
   <si>
     <t xml:space="preserve">18.6362609863281</t>
@@ -2630,13 +2630,13 @@
     <t xml:space="preserve">17.049373626709</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0300216674805</t>
+    <t xml:space="preserve">17.0300197601318</t>
   </si>
   <si>
     <t xml:space="preserve">16.8752021789551</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3266258239746</t>
+    <t xml:space="preserve">18.326623916626</t>
   </si>
   <si>
     <t xml:space="preserve">18.7717266082764</t>
@@ -2648,13 +2648,13 @@
     <t xml:space="preserve">18.5782051086426</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4233875274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1331005096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4974384307861</t>
+    <t xml:space="preserve">18.4233856201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1331024169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4974365234375</t>
   </si>
   <si>
     <t xml:space="preserve">20.1263866424561</t>
@@ -2663,7 +2663,7 @@
     <t xml:space="preserve">19.9328651428223</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3199119567871</t>
+    <t xml:space="preserve">20.3199100494385</t>
   </si>
   <si>
     <t xml:space="preserve">19.6425800323486</t>
@@ -2678,10 +2678,10 @@
     <t xml:space="preserve">19.1781253814697</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0233058929443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1974773406982</t>
+    <t xml:space="preserve">19.023307800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1974792480469</t>
   </si>
   <si>
     <t xml:space="preserve">18.9071941375732</t>
@@ -2690,7 +2690,7 @@
     <t xml:space="preserve">19.8844833374023</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4006767272949</t>
+    <t xml:space="preserve">19.4006748199463</t>
   </si>
   <si>
     <t xml:space="preserve">19.7877235412598</t>
@@ -2708,7 +2708,7 @@
     <t xml:space="preserve">22.0132369995117</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8357086181641</t>
+    <t xml:space="preserve">22.8357105255127</t>
   </si>
   <si>
     <t xml:space="preserve">22.1583786010742</t>
@@ -2720,19 +2720,19 @@
     <t xml:space="preserve">22.3519020080566</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7229537963867</t>
+    <t xml:space="preserve">21.7229518890381</t>
   </si>
   <si>
     <t xml:space="preserve">21.5778102874756</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4326686859131</t>
+    <t xml:space="preserve">21.4326667785645</t>
   </si>
   <si>
     <t xml:space="preserve">22.061616897583</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4970455169678</t>
+    <t xml:space="preserve">22.4970436096191</t>
   </si>
   <si>
     <t xml:space="preserve">22.2551403045654</t>
@@ -2744,7 +2744,7 @@
     <t xml:space="preserve">21.6261901855469</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7713317871094</t>
+    <t xml:space="preserve">21.771333694458</t>
   </si>
   <si>
     <t xml:space="preserve">22.3035202026367</t>
@@ -2753,10 +2753,10 @@
     <t xml:space="preserve">22.8840885162354</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7873287200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9648571014404</t>
+    <t xml:space="preserve">22.7873268127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9648551940918</t>
   </si>
   <si>
     <t xml:space="preserve">20.948860168457</t>
@@ -2771,7 +2771,7 @@
     <t xml:space="preserve">20.1747703552246</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5134334564209</t>
+    <t xml:space="preserve">20.5134353637695</t>
   </si>
   <si>
     <t xml:space="preserve">20.0296268463135</t>
@@ -2780,13 +2780,13 @@
     <t xml:space="preserve">22.9808521270752</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1259937286377</t>
+    <t xml:space="preserve">23.1259918212891</t>
   </si>
   <si>
     <t xml:space="preserve">21.3842868804932</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8520965576172</t>
+    <t xml:space="preserve">20.8520984649658</t>
   </si>
   <si>
     <t xml:space="preserve">20.5618133544922</t>
@@ -3342,6 +3342,9 @@
   </si>
   <si>
     <t xml:space="preserve">35.0999984741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.2000007629395</t>
   </si>
 </sst>
 </file>
@@ -68316,7 +68319,7 @@
     </row>
     <row r="2487">
       <c r="A2487" s="1" t="n">
-        <v>45940.6496412037</v>
+        <v>45940.2916666667</v>
       </c>
       <c r="B2487" t="n">
         <v>13738</v>
@@ -68337,6 +68340,32 @@
         <v>1109</v>
       </c>
       <c r="H2487" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2488">
+      <c r="A2488" s="1" t="n">
+        <v>45943.6493518519</v>
+      </c>
+      <c r="B2488" t="n">
+        <v>8172</v>
+      </c>
+      <c r="C2488" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="D2488" t="n">
+        <v>35.5499992370605</v>
+      </c>
+      <c r="E2488" t="n">
+        <v>35.5499992370605</v>
+      </c>
+      <c r="F2488" t="n">
+        <v>36.2000007629395</v>
+      </c>
+      <c r="G2488" t="s">
+        <v>1110</v>
+      </c>
+      <c r="H2488" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LUVE.MI.xlsx
+++ b/data/LUVE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1119" uniqueCount="1119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1120" uniqueCount="1120">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -56,34 +56,34 @@
     <t xml:space="preserve">8.19667816162109</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07632160186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15102577209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17177772521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03897094726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08462238311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06802082061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96841669082642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01821804046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99746656417847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91861343383789</t>
+    <t xml:space="preserve">8.07632350921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15102386474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17177677154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03896999359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08462142944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06802272796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96841764450073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01821994781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99746751785278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91861295700073</t>
   </si>
   <si>
     <t xml:space="preserve">7.91446399688721</t>
@@ -92,19 +92,19 @@
     <t xml:space="preserve">7.91031217575073</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88541126251221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87711143493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85221099853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.648850440979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71940326690674</t>
+    <t xml:space="preserve">7.88541221618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87711048126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.852210521698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64884996414185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7194037437439</t>
   </si>
   <si>
     <t xml:space="preserve">7.70280170440674</t>
@@ -113,58 +113,58 @@
     <t xml:space="preserve">7.69035053253174</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61979913711548</t>
+    <t xml:space="preserve">7.619797706604</t>
   </si>
   <si>
     <t xml:space="preserve">7.55754375457764</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55339431762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63639879226685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76920557022095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80240869522095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93521356582642</t>
+    <t xml:space="preserve">7.55339384078979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63639831542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76920413970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80240726470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93521499633789</t>
   </si>
   <si>
     <t xml:space="preserve">8.10122299194336</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05141830444336</t>
+    <t xml:space="preserve">8.05142021179199</t>
   </si>
   <si>
     <t xml:space="preserve">8.18422794342041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13442420959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00161838531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96011543273926</t>
+    <t xml:space="preserve">8.13442516326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00161743164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9601149559021</t>
   </si>
   <si>
     <t xml:space="preserve">8.21742820739746</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35853576660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3253345489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29213333129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20082855224609</t>
+    <t xml:space="preserve">8.35853672027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32533359527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29213237762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20082759857178</t>
   </si>
   <si>
     <t xml:space="preserve">8.15932655334473</t>
@@ -176,133 +176,133 @@
     <t xml:space="preserve">8.36267280578613</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43045520782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15085315704346</t>
+    <t xml:space="preserve">8.43045616149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15085411071777</t>
   </si>
   <si>
     <t xml:space="preserve">8.17627143859863</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20592784881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13390827178955</t>
+    <t xml:space="preserve">8.2059268951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13390731811523</t>
   </si>
   <si>
     <t xml:space="preserve">8.11696147918701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21863460540771</t>
+    <t xml:space="preserve">8.21863555908203</t>
   </si>
   <si>
     <t xml:space="preserve">8.21016216278076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21439933776855</t>
+    <t xml:space="preserve">8.21439838409424</t>
   </si>
   <si>
     <t xml:space="preserve">8.20168972015381</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26099967956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09154415130615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10848903656006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04917907714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96445083618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92208766937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.879723072052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8373589515686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12543392181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93479633331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75263023376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71026706695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93903207778931</t>
+    <t xml:space="preserve">8.26099872589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09154319763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10848808288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04918003082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96444988250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92208814620972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87972354888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83735752105713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12543487548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93479585647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75263071060181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71026611328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93903350830078</t>
   </si>
   <si>
     <t xml:space="preserve">7.81194067001343</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79499340057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62553930282593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66790294647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84583187103271</t>
+    <t xml:space="preserve">7.79499578475952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62553882598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66790199279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84583139419556</t>
   </si>
   <si>
     <t xml:space="preserve">8.19321727752686</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47281932830811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51518440246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52365970611572</t>
+    <t xml:space="preserve">8.47282123565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51518535614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52365779876709</t>
   </si>
   <si>
     <t xml:space="preserve">8.5999116897583</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78631401062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71853160858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50671005249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.540602684021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46858406066895</t>
+    <t xml:space="preserve">8.78631496429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71853351593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50671100616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54060363769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46858215332031</t>
   </si>
   <si>
     <t xml:space="preserve">8.46434688568115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55754947662354</t>
+    <t xml:space="preserve">8.5575475692749</t>
   </si>
   <si>
     <t xml:space="preserve">8.57449340820312</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81173229217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72700595855713</t>
+    <t xml:space="preserve">8.81173419952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7270040512085</t>
   </si>
   <si>
     <t xml:space="preserve">8.64227676391602</t>
@@ -311,7 +311,7 @@
     <t xml:space="preserve">8.89646053314209</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0235538482666</t>
+    <t xml:space="preserve">9.02355098724365</t>
   </si>
   <si>
     <t xml:space="preserve">9.09980869293213</t>
@@ -320,115 +320,115 @@
     <t xml:space="preserve">9.06591701507568</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10828399658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27773666381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19300937652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18453693389893</t>
+    <t xml:space="preserve">9.1082820892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27773761749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1930103302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18453788757324</t>
   </si>
   <si>
     <t xml:space="preserve">9.07439041137695</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09133625030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30315685272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32010173797607</t>
+    <t xml:space="preserve">9.09133529663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30315589904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32010269165039</t>
   </si>
   <si>
     <t xml:space="preserve">9.12522792816162</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60817909240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40483093261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4895601272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38788318634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53192329406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4810848236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44719409942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54039478302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5742883682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47261428833008</t>
+    <t xml:space="preserve">9.60818004608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4048318862915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48955917358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38788414001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53192234039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48108577728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44719314575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54039669036865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57428646087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47261333465576</t>
   </si>
   <si>
     <t xml:space="preserve">9.41330432891846</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42177581787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51497650146484</t>
+    <t xml:space="preserve">9.42177486419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51497554779053</t>
   </si>
   <si>
     <t xml:space="preserve">9.56581401824951</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74374389648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.065710067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2521114349365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1334924697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99792861938477</t>
+    <t xml:space="preserve">9.74374294281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0657110214233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2521133422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1334943771362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99792957305908</t>
   </si>
   <si>
     <t xml:space="preserve">9.95556354522705</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98098373413086</t>
+    <t xml:space="preserve">9.98098278045654</t>
   </si>
   <si>
     <t xml:space="preserve">9.88778114318848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91320037841797</t>
+    <t xml:space="preserve">9.91319942474365</t>
   </si>
   <si>
     <t xml:space="preserve">10.0148735046387</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1589117050171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0402927398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70137977600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73526954650879</t>
+    <t xml:space="preserve">10.1589097976685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0402908325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70137882232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73527050018311</t>
   </si>
   <si>
     <t xml:space="preserve">9.70985221862793</t>
@@ -437,13 +437,13 @@
     <t xml:space="preserve">10.0826559066772</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8623628616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1250200271606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2944784164429</t>
+    <t xml:space="preserve">9.86236381530762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.125020980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2944765090942</t>
   </si>
   <si>
     <t xml:space="preserve">10.4808788299561</t>
@@ -452,19 +452,19 @@
     <t xml:space="preserve">10.5317153930664</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5147695541382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8028450012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9129915237427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.862156867981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0146656036377</t>
+    <t xml:space="preserve">10.5147705078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.802845954895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9129934310913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8621559143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.014666557312</t>
   </si>
   <si>
     <t xml:space="preserve">11.0570306777954</t>
@@ -473,28 +473,28 @@
     <t xml:space="preserve">11.277325630188</t>
   </si>
   <si>
-    <t xml:space="preserve">11.438307762146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6586017608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5823459625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4806728363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5908193588257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7009649276733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7772207260132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.811110496521</t>
+    <t xml:space="preserve">11.4383068084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6586008071899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5823440551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4806709289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5908184051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.700963973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7772188186646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8111114501953</t>
   </si>
   <si>
     <t xml:space="preserve">11.8365297317505</t>
@@ -503,34 +503,34 @@
     <t xml:space="preserve">11.6670742034912</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5992908477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5230350494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.607762336731</t>
+    <t xml:space="preserve">11.5992918014526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5230379104614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6077632904053</t>
   </si>
   <si>
     <t xml:space="preserve">11.6263818740845</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7297258377075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6952772140503</t>
+    <t xml:space="preserve">11.7297267913818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6952781677246</t>
   </si>
   <si>
     <t xml:space="preserve">11.6780548095703</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7986240386963</t>
+    <t xml:space="preserve">11.798623085022</t>
   </si>
   <si>
     <t xml:space="preserve">11.8847465515137</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9105815887451</t>
+    <t xml:space="preserve">11.9105806350708</t>
   </si>
   <si>
     <t xml:space="preserve">12.0655994415283</t>
@@ -551,37 +551,37 @@
     <t xml:space="preserve">11.9967021942139</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8416833877563</t>
+    <t xml:space="preserve">11.8416843414307</t>
   </si>
   <si>
     <t xml:space="preserve">11.7555618286133</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7125015258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8502969741821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9191942214966</t>
+    <t xml:space="preserve">11.7125034332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8502979278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9191932678223</t>
   </si>
   <si>
     <t xml:space="preserve">11.962254524231</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0397644042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.048376083374</t>
+    <t xml:space="preserve">12.0397634506226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0483741760254</t>
   </si>
   <si>
     <t xml:space="preserve">11.7900104522705</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0311527252197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9450302124023</t>
+    <t xml:space="preserve">12.0311508178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9450283050537</t>
   </si>
   <si>
     <t xml:space="preserve">11.8158483505249</t>
@@ -593,16 +593,16 @@
     <t xml:space="preserve">11.8761320114136</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8244600296021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8675203323364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9019689559937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9278078079224</t>
+    <t xml:space="preserve">11.8244590759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8675212860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.901969909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9278059005737</t>
   </si>
   <si>
     <t xml:space="preserve">11.7211141586304</t>
@@ -614,73 +614,76 @@
     <t xml:space="preserve">11.6349945068359</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6091556549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.57470703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5316486358643</t>
+    <t xml:space="preserve">11.6091566085815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5747079849243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5316457748413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5230369567871</t>
   </si>
   <si>
     <t xml:space="preserve">11.3680171966553</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3594045639038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2818965911865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2302236557007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1957731246948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1871633529663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1096525192261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0579814910889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1785497665405</t>
+    <t xml:space="preserve">11.3594036102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2818956375122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2302217483521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1957740783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1871614456177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1096515655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0579805374146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1785488128662</t>
   </si>
   <si>
     <t xml:space="preserve">11.1268768310547</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9374103546143</t>
+    <t xml:space="preserve">10.9374094009399</t>
   </si>
   <si>
     <t xml:space="preserve">11.066593170166</t>
   </si>
   <si>
-    <t xml:space="preserve">11.023530960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.083815574646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1354894638062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2043857574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3163433074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.454137802124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5402603149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.411078453064</t>
+    <t xml:space="preserve">11.0235319137573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0838165283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1354904174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2043867111206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3163442611694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4541397094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5402593612671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4110774993896</t>
   </si>
   <si>
     <t xml:space="preserve">11.2905073165894</t>
@@ -689,43 +692,43 @@
     <t xml:space="preserve">11.1613254547119</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2646722793579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1527147293091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0407571792603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4196891784668</t>
+    <t xml:space="preserve">11.2646703720093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1527128219604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0407562255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4196920394897</t>
   </si>
   <si>
     <t xml:space="preserve">11.2216100692749</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2388353347778</t>
+    <t xml:space="preserve">11.2388362884521</t>
   </si>
   <si>
     <t xml:space="preserve">11.3421802520752</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9546337127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.96324634552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0063076019287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0924282073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74032402038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01690578460693</t>
+    <t xml:space="preserve">10.9546346664429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9632453918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0063066482544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0924301147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74032306671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01690483093262</t>
   </si>
   <si>
     <t xml:space="preserve">9.2149829864502</t>
@@ -746,43 +749,43 @@
     <t xml:space="preserve">9.60252857208252</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6886510848999</t>
+    <t xml:space="preserve">9.68865013122559</t>
   </si>
   <si>
     <t xml:space="preserve">9.56808185577393</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39583778381348</t>
+    <t xml:space="preserve">9.39583873748779</t>
   </si>
   <si>
     <t xml:space="preserve">9.34416484832764</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2580451965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30110454559326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41306304931641</t>
+    <t xml:space="preserve">9.25804328918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30110549926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41306209564209</t>
   </si>
   <si>
     <t xml:space="preserve">9.28388023376465</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24081993103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12886333465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02551460266113</t>
+    <t xml:space="preserve">9.24081897735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12886238098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02551555633545</t>
   </si>
   <si>
     <t xml:space="preserve">9.20637130737305</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26665687561035</t>
+    <t xml:space="preserve">9.26665592193604</t>
   </si>
   <si>
     <t xml:space="preserve">9.69726276397705</t>
@@ -794,55 +797,55 @@
     <t xml:space="preserve">9.66281509399414</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64559078216553</t>
+    <t xml:space="preserve">9.64558982849121</t>
   </si>
   <si>
     <t xml:space="preserve">9.67142581939697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75754833221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71448612213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09441471099854</t>
+    <t xml:space="preserve">9.75754737854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71448802947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0944128036499</t>
   </si>
   <si>
     <t xml:space="preserve">8.9393949508667</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14608478546143</t>
+    <t xml:space="preserve">9.14608573913574</t>
   </si>
   <si>
     <t xml:space="preserve">9.12024974822998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83505630493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73171138763428</t>
+    <t xml:space="preserve">9.83505916595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73171234130859</t>
   </si>
   <si>
     <t xml:space="preserve">9.90395450592041</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77477359771729</t>
+    <t xml:space="preserve">9.77477169036865</t>
   </si>
   <si>
     <t xml:space="preserve">9.53363227844238</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49918270111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57669353485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58530426025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47334766387939</t>
+    <t xml:space="preserve">9.49918365478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57669258117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58530521392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47334671020508</t>
   </si>
   <si>
     <t xml:space="preserve">9.43028545379639</t>
@@ -851,19 +854,19 @@
     <t xml:space="preserve">9.54224395751953</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17192268371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23220729827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55946922302246</t>
+    <t xml:space="preserve">9.1719217300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23220825195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55946826934814</t>
   </si>
   <si>
     <t xml:space="preserve">9.51640796661377</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86089420318604</t>
+    <t xml:space="preserve">9.8608922958374</t>
   </si>
   <si>
     <t xml:space="preserve">8.95661926269531</t>
@@ -872,43 +875,43 @@
     <t xml:space="preserve">8.91355895996094</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08580303192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04274082183838</t>
+    <t xml:space="preserve">9.08580207824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04273986816406</t>
   </si>
   <si>
     <t xml:space="preserve">8.99967956542969</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82743740081787</t>
+    <t xml:space="preserve">8.82743644714355</t>
   </si>
   <si>
     <t xml:space="preserve">8.69825649261475</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87049865722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78437614440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7413158416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61213302612305</t>
+    <t xml:space="preserve">8.87049770355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7843770980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74131679534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61213397979736</t>
   </si>
   <si>
     <t xml:space="preserve">8.59490966796875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65519523620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45711612701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06314563751221</t>
+    <t xml:space="preserve">8.65519332885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45711517333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06314373016357</t>
   </si>
   <si>
     <t xml:space="preserve">9.10714054107666</t>
@@ -917,7 +920,7 @@
     <t xml:space="preserve">9.0191478729248</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97515201568604</t>
+    <t xml:space="preserve">8.97515296936035</t>
   </si>
   <si>
     <t xml:space="preserve">8.93115711212158</t>
@@ -929,7 +932,7 @@
     <t xml:space="preserve">8.84316539764404</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76397323608398</t>
+    <t xml:space="preserve">8.76397228240967</t>
   </si>
   <si>
     <t xml:space="preserve">8.48240089416504</t>
@@ -947,19 +950,19 @@
     <t xml:space="preserve">8.6583833694458</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60558700561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7287769317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69357967376709</t>
+    <t xml:space="preserve">8.60558795928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72877597808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69357776641846</t>
   </si>
   <si>
     <t xml:space="preserve">8.74637413024902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53519344329834</t>
+    <t xml:space="preserve">8.53519535064697</t>
   </si>
   <si>
     <t xml:space="preserve">8.44720458984375</t>
@@ -968,31 +971,31 @@
     <t xml:space="preserve">8.27121925354004</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32401466369629</t>
+    <t xml:space="preserve">8.32401371002197</t>
   </si>
   <si>
     <t xml:space="preserve">8.28881740570068</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78157138824463</t>
+    <t xml:space="preserve">8.78157043457031</t>
   </si>
   <si>
     <t xml:space="preserve">8.64078426361084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79916858673096</t>
+    <t xml:space="preserve">8.79916954040527</t>
   </si>
   <si>
     <t xml:space="preserve">8.67598056793213</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23912811279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37111568450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32712078094482</t>
+    <t xml:space="preserve">9.23912715911865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37111473083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32711887359619</t>
   </si>
   <si>
     <t xml:space="preserve">9.1951322555542</t>
@@ -1001,13 +1004,13 @@
     <t xml:space="preserve">9.15113544464111</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46480083465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41200542449951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49999713897705</t>
+    <t xml:space="preserve">8.46480178833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41200637817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49999809265137</t>
   </si>
   <si>
     <t xml:space="preserve">8.34161281585693</t>
@@ -1019,34 +1022,34 @@
     <t xml:space="preserve">8.30641555786133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13043022155762</t>
+    <t xml:space="preserve">8.13043212890625</t>
   </si>
   <si>
     <t xml:space="preserve">8.1832275390625</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16563034057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21842479705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25362110137939</t>
+    <t xml:space="preserve">8.16562938690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21842384338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25362014770508</t>
   </si>
   <si>
     <t xml:space="preserve">8.37681007385254</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51759624481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28312492370605</t>
+    <t xml:space="preserve">8.5175952911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28312397003174</t>
   </si>
   <si>
     <t xml:space="preserve">9.41511154174805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63508892059326</t>
+    <t xml:space="preserve">9.63508987426758</t>
   </si>
   <si>
     <t xml:space="preserve">9.59109401702881</t>
@@ -1061,13 +1064,13 @@
     <t xml:space="preserve">10.1630411148071</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2070379257202</t>
+    <t xml:space="preserve">10.2070369720459</t>
   </si>
   <si>
     <t xml:space="preserve">10.3390245437622</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2950286865234</t>
+    <t xml:space="preserve">10.2950277328491</t>
   </si>
   <si>
     <t xml:space="preserve">10.383020401001</t>
@@ -1076,43 +1079,40 @@
     <t xml:space="preserve">10.2510318756104</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4270162582397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0750494003296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5150079727173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6498165130615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4700727462769</t>
+    <t xml:space="preserve">10.4270153045654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0750484466553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.515007019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6498155593872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4700717926025</t>
   </si>
   <si>
     <t xml:space="preserve">10.694751739502</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6048803329468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3802003860474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2453908920288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0656480789185</t>
+    <t xml:space="preserve">10.6048793792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3802013397217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2453918457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0656490325928</t>
   </si>
   <si>
     <t xml:space="preserve">10.4251356124878</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5150089263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3352651596069</t>
+    <t xml:space="preserve">10.3352642059326</t>
   </si>
   <si>
     <t xml:space="preserve">10.2903270721436</t>
@@ -1121,37 +1121,37 @@
     <t xml:space="preserve">10.2004556655884</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97577571868896</t>
+    <t xml:space="preserve">9.97577667236328</t>
   </si>
   <si>
     <t xml:space="preserve">10.1105842590332</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93084049224854</t>
+    <t xml:space="preserve">9.93084144592285</t>
   </si>
   <si>
     <t xml:space="preserve">9.88590431213379</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1555213928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.020712852478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75109672546387</t>
+    <t xml:space="preserve">10.1555204391479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0207109451294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7510986328125</t>
   </si>
   <si>
     <t xml:space="preserve">9.70616149902344</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34667301177979</t>
+    <t xml:space="preserve">9.34667491912842</t>
   </si>
   <si>
     <t xml:space="preserve">9.30173778533936</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39161014556885</t>
+    <t xml:space="preserve">9.39160823822021</t>
   </si>
   <si>
     <t xml:space="preserve">9.48148155212402</t>
@@ -1160,34 +1160,34 @@
     <t xml:space="preserve">9.61628913879395</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5264196395874</t>
+    <t xml:space="preserve">9.52641868591309</t>
   </si>
   <si>
     <t xml:space="preserve">9.43654537200928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12199306488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0321216583252</t>
+    <t xml:space="preserve">9.12199401855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03212261199951</t>
   </si>
   <si>
     <t xml:space="preserve">9.16693019866943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07705879211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25680065155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98718547821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5713529586792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66122531890869</t>
+    <t xml:space="preserve">9.07705783843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25680160522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98718643188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57135200500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66122436523438</t>
   </si>
   <si>
     <t xml:space="preserve">9.7960319519043</t>
@@ -1196,28 +1196,28 @@
     <t xml:space="preserve">10.9643669128418</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4586629867554</t>
+    <t xml:space="preserve">11.4586610794067</t>
   </si>
   <si>
     <t xml:space="preserve">11.5035991668701</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2339811325073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1441106796265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9194297790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8744945526123</t>
+    <t xml:space="preserve">11.233983039856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1441097259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9194307327271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8744955062866</t>
   </si>
   <si>
     <t xml:space="preserve">11.0093030929565</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2789192199707</t>
+    <t xml:space="preserve">11.2789182662964</t>
   </si>
   <si>
     <t xml:space="preserve">11.4137268066406</t>
@@ -1226,7 +1226,7 @@
     <t xml:space="preserve">11.5485343933105</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6833410263062</t>
+    <t xml:space="preserve">11.6833419799805</t>
   </si>
   <si>
     <t xml:space="preserve">11.77321434021</t>
@@ -1235,28 +1235,28 @@
     <t xml:space="preserve">11.9080219268799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1327018737793</t>
+    <t xml:space="preserve">12.132700920105</t>
   </si>
   <si>
     <t xml:space="preserve">11.9978942871094</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8181495666504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5934705734253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3124446868896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5820617675781</t>
+    <t xml:space="preserve">11.8181505203247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.593469619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3124437332153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5820608139038</t>
   </si>
   <si>
     <t xml:space="preserve">12.9415483474731</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8067398071289</t>
+    <t xml:space="preserve">12.8067407608032</t>
   </si>
   <si>
     <t xml:space="preserve">12.7618036270142</t>
@@ -1265,13 +1265,13 @@
     <t xml:space="preserve">13.0763559341431</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4472532272339</t>
+    <t xml:space="preserve">12.4472541809082</t>
   </si>
   <si>
     <t xml:space="preserve">12.5371246337891</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2675085067749</t>
+    <t xml:space="preserve">12.2675094604492</t>
   </si>
   <si>
     <t xml:space="preserve">12.4023170471191</t>
@@ -1286,34 +1286,34 @@
     <t xml:space="preserve">12.8966121673584</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7282781600952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7846231460571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5599431991577</t>
+    <t xml:space="preserve">11.7282772064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7846240997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.559944152832</t>
   </si>
   <si>
     <t xml:space="preserve">8.89731407165527</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98062181472778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81885147094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53126239776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89074945449829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53782653808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.962646484375</t>
+    <t xml:space="preserve">7.98062086105347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81885099411011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53126192092896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89074802398682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53782558441162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96264743804932</t>
   </si>
   <si>
     <t xml:space="preserve">8.44795513153076</t>
@@ -1331,40 +1331,40 @@
     <t xml:space="preserve">9.21186542510986</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93848896026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80045509338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89247894287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66242027282715</t>
+    <t xml:space="preserve">9.93848991394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80045413970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89247798919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66242122650146</t>
   </si>
   <si>
     <t xml:space="preserve">9.7084321975708</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84646701812744</t>
+    <t xml:space="preserve">9.84646606445312</t>
   </si>
   <si>
     <t xml:space="preserve">10.1225357055664</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75444507598877</t>
+    <t xml:space="preserve">9.75444412231445</t>
   </si>
   <si>
     <t xml:space="preserve">10.3986053466797</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3065814971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7206859588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5826511383057</t>
+    <t xml:space="preserve">10.3065824508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.720685005188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5826501846313</t>
   </si>
   <si>
     <t xml:space="preserve">10.8587207794189</t>
@@ -1376,52 +1376,52 @@
     <t xml:space="preserve">10.9967546463013</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6286630630493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.766697883606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4906272888184</t>
+    <t xml:space="preserve">10.6286640167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7666959762573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4906282424927</t>
   </si>
   <si>
     <t xml:space="preserve">11.1347894668579</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3188362121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5028800964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1807994842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0427656173706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2728233337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9507427215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0887784957886</t>
+    <t xml:space="preserve">11.3188352584839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5028810501099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1808004379272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0427665710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2728242874146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9507436752319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0887765884399</t>
   </si>
   <si>
     <t xml:space="preserve">10.8127088546753</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9047317504883</t>
+    <t xml:space="preserve">10.904730796814</t>
   </si>
   <si>
     <t xml:space="preserve">11.4108581542969</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4568691253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2268114089966</t>
+    <t xml:space="preserve">11.4568710327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2268123626709</t>
   </si>
   <si>
     <t xml:space="preserve">11.3648471832275</t>
@@ -1448,16 +1448,16 @@
     <t xml:space="preserve">12.1010313034058</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7329397201538</t>
+    <t xml:space="preserve">11.7329378128052</t>
   </si>
   <si>
     <t xml:space="preserve">11.8249626159668</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0550203323364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8709735870361</t>
+    <t xml:space="preserve">12.0550193786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8709726333618</t>
   </si>
   <si>
     <t xml:space="preserve">11.9169855117798</t>
@@ -1466,19 +1466,19 @@
     <t xml:space="preserve">11.6409158706665</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1470413208008</t>
+    <t xml:space="preserve">12.1470432281494</t>
   </si>
   <si>
     <t xml:space="preserve">12.6991815567017</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7912044525146</t>
+    <t xml:space="preserve">12.7912034988403</t>
   </si>
   <si>
     <t xml:space="preserve">13.0672731399536</t>
   </si>
   <si>
-    <t xml:space="preserve">12.883228302002</t>
+    <t xml:space="preserve">12.8832273483276</t>
   </si>
   <si>
     <t xml:space="preserve">12.9292392730713</t>
@@ -1487,10 +1487,10 @@
     <t xml:space="preserve">13.2053079605103</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2513198852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1132841110229</t>
+    <t xml:space="preserve">13.2513189315796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1132850646973</t>
   </si>
   <si>
     <t xml:space="preserve">13.1592960357666</t>
@@ -1508,10 +1508,10 @@
     <t xml:space="preserve">13.7114334106445</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4353656768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5151348114014</t>
+    <t xml:space="preserve">13.4353666305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5151357650757</t>
   </si>
   <si>
     <t xml:space="preserve">12.3770999908447</t>
@@ -1520,22 +1520,22 @@
     <t xml:space="preserve">12.837215423584</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7451934814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6531705856323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3433427810669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6194124221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8494701385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9414920806885</t>
+    <t xml:space="preserve">12.7451944351196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6531686782837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3433418273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6194114685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8494691848755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9414911270142</t>
   </si>
   <si>
     <t xml:space="preserve">14.1715488433838</t>
@@ -1544,37 +1544,37 @@
     <t xml:space="preserve">14.3555965423584</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1255388259888</t>
+    <t xml:space="preserve">14.1255378723145</t>
   </si>
   <si>
     <t xml:space="preserve">14.4936304092407</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7236881256104</t>
+    <t xml:space="preserve">14.7236890792847</t>
   </si>
   <si>
     <t xml:space="preserve">14.6776762008667</t>
   </si>
   <si>
-    <t xml:space="preserve">14.815712928772</t>
+    <t xml:space="preserve">14.8157110214233</t>
   </si>
   <si>
     <t xml:space="preserve">14.861722946167</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0457696914673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5396413803101</t>
+    <t xml:space="preserve">15.0457706451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5396423339844</t>
   </si>
   <si>
     <t xml:space="preserve">14.6316652297974</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4476184844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2635736465454</t>
+    <t xml:space="preserve">14.4476175308228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2635726928711</t>
   </si>
   <si>
     <t xml:space="preserve">13.9875040054321</t>
@@ -1583,94 +1583,94 @@
     <t xml:space="preserve">14.3095846176147</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6654243469238</t>
+    <t xml:space="preserve">13.6654233932495</t>
   </si>
   <si>
     <t xml:space="preserve">13.8034582138062</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5733995437622</t>
+    <t xml:space="preserve">13.5734004974365</t>
   </si>
   <si>
     <t xml:space="preserve">13.7574462890625</t>
   </si>
   <si>
-    <t xml:space="preserve">14.95374584198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0335149765015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4269771575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3801374435425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4738187789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7080240249634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8485460281372</t>
+    <t xml:space="preserve">14.9537467956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0335159301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4269781112671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3801383972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.473819732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7080230712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8485469818115</t>
   </si>
   <si>
     <t xml:space="preserve">15.03590965271</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0827503204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8953857421875</t>
+    <t xml:space="preserve">15.0827493667603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8953866958618</t>
   </si>
   <si>
     <t xml:space="preserve">14.9422273635864</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1764335632324</t>
+    <t xml:space="preserve">15.1764326095581</t>
   </si>
   <si>
     <t xml:space="preserve">15.1295900344849</t>
   </si>
   <si>
-    <t xml:space="preserve">14.989068031311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6611814498901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3169555664062</t>
+    <t xml:space="preserve">14.9890689849854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6611824035645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3169536590576</t>
   </si>
   <si>
     <t xml:space="preserve">14.7548637390137</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8017053604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2232723236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5043172836304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0664081573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6916790008545</t>
+    <t xml:space="preserve">14.8017044067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2232713699341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5043163299561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.06640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6916799545288</t>
   </si>
   <si>
     <t xml:space="preserve">15.7385215759277</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9727230072021</t>
+    <t xml:space="preserve">15.9727239608765</t>
   </si>
   <si>
     <t xml:space="preserve">15.9258861541748</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7853622436523</t>
+    <t xml:space="preserve">15.7853651046753</t>
   </si>
   <si>
     <t xml:space="preserve">16.1132488250732</t>
@@ -1682,13 +1682,13 @@
     <t xml:space="preserve">16.5348167419434</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8627033233643</t>
+    <t xml:space="preserve">16.8627014160156</t>
   </si>
   <si>
     <t xml:space="preserve">17.1437454223633</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5816593170166</t>
+    <t xml:space="preserve">16.5816555023193</t>
   </si>
   <si>
     <t xml:space="preserve">16.2069282531738</t>
@@ -1697,22 +1697,22 @@
     <t xml:space="preserve">17.2842712402344</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7995204925537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4716320037842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8158626556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6284961700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0969066619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5184764862061</t>
+    <t xml:space="preserve">17.7995185852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4716339111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.815860748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6284980773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0969047546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5184726715088</t>
   </si>
   <si>
     <t xml:space="preserve">17.612154006958</t>
@@ -1730,7 +1730,7 @@
     <t xml:space="preserve">18.9237003326416</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7668361663818</t>
+    <t xml:space="preserve">19.7668342590332</t>
   </si>
   <si>
     <t xml:space="preserve">19.5794696807861</t>
@@ -1751,10 +1751,10 @@
     <t xml:space="preserve">19.4857883453369</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8605155944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3289241790771</t>
+    <t xml:space="preserve">19.8605175018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3289222717285</t>
   </si>
   <si>
     <t xml:space="preserve">20.9846954345703</t>
@@ -1763,19 +1763,19 @@
     <t xml:space="preserve">21.265739440918</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0783767700195</t>
+    <t xml:space="preserve">21.0783786773682</t>
   </si>
   <si>
     <t xml:space="preserve">21.453104019165</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7973327636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8278293609619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1088771820068</t>
+    <t xml:space="preserve">20.7973346710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8278312683105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1088790893555</t>
   </si>
   <si>
     <t xml:space="preserve">21.7341499328613</t>
@@ -1787,16 +1787,16 @@
     <t xml:space="preserve">22.2962379455566</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4836006164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6404685974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5467834472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2352428436279</t>
+    <t xml:space="preserve">22.4836025238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6404666900635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5467853546143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2352447509766</t>
   </si>
   <si>
     <t xml:space="preserve">18.3147678375244</t>
@@ -1820,7 +1820,7 @@
     <t xml:space="preserve">21.172061920166</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7036514282227</t>
+    <t xml:space="preserve">20.703649520874</t>
   </si>
   <si>
     <t xml:space="preserve">21.3594207763672</t>
@@ -1841,13 +1841,13 @@
     <t xml:space="preserve">22.3899192810059</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9541969299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4226036071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8910140991211</t>
+    <t xml:space="preserve">19.954195022583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4226055145264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8910121917725</t>
   </si>
   <si>
     <t xml:space="preserve">19.3921070098877</t>
@@ -1862,13 +1862,13 @@
     <t xml:space="preserve">16.9563846588135</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6589965820312</t>
+    <t xml:space="preserve">17.6589984893799</t>
   </si>
   <si>
     <t xml:space="preserve">17.7526779174805</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3779525756836</t>
+    <t xml:space="preserve">17.377950668335</t>
   </si>
   <si>
     <t xml:space="preserve">17.8931999206543</t>
@@ -1880,10 +1880,10 @@
     <t xml:space="preserve">18.2679271697998</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8768558502197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6426544189453</t>
+    <t xml:space="preserve">18.8768577575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6426525115967</t>
   </si>
   <si>
     <t xml:space="preserve">18.3241348266602</t>
@@ -1892,19 +1892,19 @@
     <t xml:space="preserve">18.2117195129395</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2304534912109</t>
+    <t xml:space="preserve">18.2304553985596</t>
   </si>
   <si>
     <t xml:space="preserve">18.4552898406982</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9494094848633</t>
+    <t xml:space="preserve">17.9494113922119</t>
   </si>
   <si>
     <t xml:space="preserve">18.1180362701416</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9705410003662</t>
+    <t xml:space="preserve">18.9705390930176</t>
   </si>
   <si>
     <t xml:space="preserve">20.2820816040039</t>
@@ -1913,19 +1913,19 @@
     <t xml:space="preserve">20.0947189331055</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1884021759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1415596008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4927635192871</t>
+    <t xml:space="preserve">20.1884002685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1415615081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4927616119385</t>
   </si>
   <si>
     <t xml:space="preserve">17.5559463500977</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1999549865723</t>
+    <t xml:space="preserve">17.1999588012695</t>
   </si>
   <si>
     <t xml:space="preserve">16.8847980499268</t>
@@ -1937,13 +1937,13 @@
     <t xml:space="preserve">18.0308246612549</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9285469055176</t>
+    <t xml:space="preserve">18.9285449981689</t>
   </si>
   <si>
     <t xml:space="preserve">18.4319343566895</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6038398742676</t>
+    <t xml:space="preserve">18.6038379669189</t>
   </si>
   <si>
     <t xml:space="preserve">19.1004505157471</t>
@@ -1952,19 +1952,19 @@
     <t xml:space="preserve">18.9858474731445</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1481990814209</t>
+    <t xml:space="preserve">19.1482009887695</t>
   </si>
   <si>
     <t xml:space="preserve">18.90944480896</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9476490020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0077247619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0554733276367</t>
+    <t xml:space="preserve">18.9476470947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0077228546143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0554714202881</t>
   </si>
   <si>
     <t xml:space="preserve">20.5329856872559</t>
@@ -1979,7 +1979,7 @@
     <t xml:space="preserve">20.4374828338623</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0104961395264</t>
+    <t xml:space="preserve">21.0104942321777</t>
   </si>
   <si>
     <t xml:space="preserve">21.4880084991455</t>
@@ -2003,7 +2003,7 @@
     <t xml:space="preserve">18.813943862915</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6993389129639</t>
+    <t xml:space="preserve">18.6993408203125</t>
   </si>
   <si>
     <t xml:space="preserve">19.3869571685791</t>
@@ -2018,13 +2018,13 @@
     <t xml:space="preserve">18.240930557251</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7757434844971</t>
+    <t xml:space="preserve">18.7757415771484</t>
   </si>
   <si>
     <t xml:space="preserve">19.9599704742432</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4852352142334</t>
+    <t xml:space="preserve">20.4852333068848</t>
   </si>
   <si>
     <t xml:space="preserve">21.1059970855713</t>
@@ -2033,13 +2033,13 @@
     <t xml:space="preserve">21.8700160980225</t>
   </si>
   <si>
-    <t xml:space="preserve">21.392505645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1537475585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7745132446289</t>
+    <t xml:space="preserve">21.3925037384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1537494659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7745113372803</t>
   </si>
   <si>
     <t xml:space="preserve">21.6790103912354</t>
@@ -2048,22 +2048,22 @@
     <t xml:space="preserve">21.9177684783936</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2970027923584</t>
+    <t xml:space="preserve">21.2970008850098</t>
   </si>
   <si>
     <t xml:space="preserve">21.7267627716064</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5835094451904</t>
+    <t xml:space="preserve">21.5835113525391</t>
   </si>
   <si>
     <t xml:space="preserve">20.5807342529297</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1032218933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.62571144104</t>
+    <t xml:space="preserve">20.1032238006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6257133483887</t>
   </si>
   <si>
     <t xml:space="preserve">19.8644676208496</t>
@@ -2075,7 +2075,7 @@
     <t xml:space="preserve">22.9205417633057</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4430313110352</t>
+    <t xml:space="preserve">22.4430294036865</t>
   </si>
   <si>
     <t xml:space="preserve">22.1565227508545</t>
@@ -2084,7 +2084,7 @@
     <t xml:space="preserve">22.0610198974609</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3475284576416</t>
+    <t xml:space="preserve">22.347526550293</t>
   </si>
   <si>
     <t xml:space="preserve">21.0582466125488</t>
@@ -2093,7 +2093,7 @@
     <t xml:space="preserve">20.3897304534912</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2942276000977</t>
+    <t xml:space="preserve">20.2942295074463</t>
   </si>
   <si>
     <t xml:space="preserve">20.1987247467041</t>
@@ -2105,7 +2105,7 @@
     <t xml:space="preserve">20.8672428131104</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0499267578125</t>
+    <t xml:space="preserve">18.0499248504639</t>
   </si>
   <si>
     <t xml:space="preserve">18.833044052124</t>
@@ -2141,16 +2141,16 @@
     <t xml:space="preserve">22.7295341491699</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5862808227539</t>
+    <t xml:space="preserve">22.5862827301025</t>
   </si>
   <si>
     <t xml:space="preserve">22.8727912902832</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5385322570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6817855834961</t>
+    <t xml:space="preserve">22.5385341644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6817836761475</t>
   </si>
   <si>
     <t xml:space="preserve">23.0160427093506</t>
@@ -2159,13 +2159,13 @@
     <t xml:space="preserve">23.3025493621826</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4485759735107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7323112487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9710636138916</t>
+    <t xml:space="preserve">24.4485778808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7323093414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9710655212402</t>
   </si>
   <si>
     <t xml:space="preserve">24.2098217010498</t>
@@ -2174,19 +2174,19 @@
     <t xml:space="preserve">24.0665683746338</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1143188476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4008255004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3080978393555</t>
+    <t xml:space="preserve">24.1143207550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4008235931396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3080959320068</t>
   </si>
   <si>
     <t xml:space="preserve">23.7800598144531</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9233150482178</t>
+    <t xml:space="preserve">23.9233131408691</t>
   </si>
   <si>
     <t xml:space="preserve">25.0693416595459</t>
@@ -2201,13 +2201,13 @@
     <t xml:space="preserve">25.3558464050293</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4035987854004</t>
+    <t xml:space="preserve">25.403600692749</t>
   </si>
   <si>
     <t xml:space="preserve">25.8333587646484</t>
   </si>
   <si>
-    <t xml:space="preserve">26.883882522583</t>
+    <t xml:space="preserve">26.8838844299316</t>
   </si>
   <si>
     <t xml:space="preserve">26.7883815765381</t>
@@ -2222,19 +2222,19 @@
     <t xml:space="preserve">24.8305854797363</t>
   </si>
   <si>
-    <t xml:space="preserve">25.260347366333</t>
+    <t xml:space="preserve">25.2603454589844</t>
   </si>
   <si>
     <t xml:space="preserve">25.7378578186035</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7856101989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0721130371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2631206512451</t>
+    <t xml:space="preserve">25.785608291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.072114944458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2631187438965</t>
   </si>
   <si>
     <t xml:space="preserve">25.4513492584229</t>
@@ -2252,7 +2252,7 @@
     <t xml:space="preserve">25.5468521118164</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4541244506836</t>
+    <t xml:space="preserve">26.4541263580322</t>
   </si>
   <si>
     <t xml:space="preserve">26.7406311035156</t>
@@ -2261,7 +2261,7 @@
     <t xml:space="preserve">27.0748901367188</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1703929901123</t>
+    <t xml:space="preserve">27.1703910827637</t>
   </si>
   <si>
     <t xml:space="preserve">28.6506767272949</t>
@@ -2288,7 +2288,7 @@
     <t xml:space="preserve">28.5074214935303</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3191909790039</t>
+    <t xml:space="preserve">29.3191928863525</t>
   </si>
   <si>
     <t xml:space="preserve">28.9371814727783</t>
@@ -2300,28 +2300,28 @@
     <t xml:space="preserve">29.223690032959</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1281871795654</t>
+    <t xml:space="preserve">29.1281852722168</t>
   </si>
   <si>
     <t xml:space="preserve">29.1759376525879</t>
   </si>
   <si>
-    <t xml:space="preserve">29.080436706543</t>
+    <t xml:space="preserve">29.0804386138916</t>
   </si>
   <si>
     <t xml:space="preserve">28.6984272003174</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9849338531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3641681671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8866596221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2714405059814</t>
+    <t xml:space="preserve">28.984935760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3641700744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8866577148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2714385986328</t>
   </si>
   <si>
     <t xml:space="preserve">27.8389053344727</t>
@@ -2339,19 +2339,19 @@
     <t xml:space="preserve">29.366943359375</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4146919250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0354595184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7489490509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7039737701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2742137908936</t>
+    <t xml:space="preserve">29.4146938323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0354614257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.748950958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7039756774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2742156982422</t>
   </si>
   <si>
     <t xml:space="preserve">29.7012023925781</t>
@@ -2360,10 +2360,10 @@
     <t xml:space="preserve">29.5579471588135</t>
   </si>
   <si>
-    <t xml:space="preserve">29.796703338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2209167480469</t>
+    <t xml:space="preserve">29.7967014312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2209148406982</t>
   </si>
   <si>
     <t xml:space="preserve">28.3164176940918</t>
@@ -2375,10 +2375,10 @@
     <t xml:space="preserve">26.9480724334717</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5770206451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.593017578125</t>
+    <t xml:space="preserve">27.5770225524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5930156707764</t>
   </si>
   <si>
     <t xml:space="preserve">28.0124492645264</t>
@@ -2396,7 +2396,7 @@
     <t xml:space="preserve">28.0608291625977</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3994941711426</t>
+    <t xml:space="preserve">28.3994960784912</t>
   </si>
   <si>
     <t xml:space="preserve">28.7381591796875</t>
@@ -2405,7 +2405,7 @@
     <t xml:space="preserve">29.1252059936523</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9800624847412</t>
+    <t xml:space="preserve">28.9800643920898</t>
   </si>
   <si>
     <t xml:space="preserve">27.7705459594727</t>
@@ -2447,19 +2447,19 @@
     <t xml:space="preserve">29.2219676971436</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0284442901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2543544769287</t>
+    <t xml:space="preserve">29.0284423828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2543525695801</t>
   </si>
   <si>
     <t xml:space="preserve">29.705774307251</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0444374084473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9960594177246</t>
+    <t xml:space="preserve">30.0444393157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.996057510376</t>
   </si>
   <si>
     <t xml:space="preserve">28.8349208831787</t>
@@ -2474,7 +2474,7 @@
     <t xml:space="preserve">28.2059707641602</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4962577819824</t>
+    <t xml:space="preserve">28.4962558746338</t>
   </si>
   <si>
     <t xml:space="preserve">27.0932140350342</t>
@@ -2483,7 +2483,7 @@
     <t xml:space="preserve">26.8513107299805</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0772190093994</t>
+    <t xml:space="preserve">26.077220916748</t>
   </si>
   <si>
     <t xml:space="preserve">26.8996906280518</t>
@@ -2507,22 +2507,22 @@
     <t xml:space="preserve">25.3031272888184</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2547454833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1579837799072</t>
+    <t xml:space="preserve">25.2547473907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1579856872559</t>
   </si>
   <si>
     <t xml:space="preserve">24.9160804748535</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4966506958008</t>
+    <t xml:space="preserve">25.4966487884521</t>
   </si>
   <si>
     <t xml:space="preserve">25.3515071868896</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0612239837646</t>
+    <t xml:space="preserve">25.061222076416</t>
   </si>
   <si>
     <t xml:space="preserve">24.7225570678711</t>
@@ -2531,7 +2531,7 @@
     <t xml:space="preserve">24.4806537628174</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6098003387451</t>
+    <t xml:space="preserve">23.6098022460938</t>
   </si>
   <si>
     <t xml:space="preserve">23.0292301177979</t>
@@ -2540,7 +2540,7 @@
     <t xml:space="preserve">22.9324722290039</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1743755340576</t>
+    <t xml:space="preserve">23.174373626709</t>
   </si>
   <si>
     <t xml:space="preserve">22.5938053131104</t>
@@ -2552,7 +2552,7 @@
     <t xml:space="preserve">21.6745719909668</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9164752960205</t>
+    <t xml:space="preserve">21.9164733886719</t>
   </si>
   <si>
     <t xml:space="preserve">21.5294284820557</t>
@@ -2564,16 +2564,16 @@
     <t xml:space="preserve">21.0940017700195</t>
   </si>
   <si>
-    <t xml:space="preserve">20.465051651001</t>
+    <t xml:space="preserve">20.4650535583496</t>
   </si>
   <si>
     <t xml:space="preserve">20.2231483459473</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4166736602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9004783630371</t>
+    <t xml:space="preserve">20.4166717529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9004802703857</t>
   </si>
   <si>
     <t xml:space="preserve">20.8037185668945</t>
@@ -2582,22 +2582,22 @@
     <t xml:space="preserve">20.6101951599121</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6585750579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7069568634033</t>
+    <t xml:space="preserve">20.658576965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7069549560547</t>
   </si>
   <si>
     <t xml:space="preserve">20.7553386688232</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3359069824219</t>
+    <t xml:space="preserve">21.3359050750732</t>
   </si>
   <si>
     <t xml:space="preserve">21.0456218719482</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4490585327148</t>
+    <t xml:space="preserve">19.4490566253662</t>
   </si>
   <si>
     <t xml:space="preserve">19.8361034393311</t>
@@ -2606,7 +2606,7 @@
     <t xml:space="preserve">19.2361812591553</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8878402709961</t>
+    <t xml:space="preserve">18.8878421783447</t>
   </si>
   <si>
     <t xml:space="preserve">18.6362609863281</t>
@@ -2630,13 +2630,13 @@
     <t xml:space="preserve">17.049373626709</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0300197601318</t>
+    <t xml:space="preserve">17.0300216674805</t>
   </si>
   <si>
     <t xml:space="preserve">16.8752021789551</t>
   </si>
   <si>
-    <t xml:space="preserve">18.326623916626</t>
+    <t xml:space="preserve">18.3266258239746</t>
   </si>
   <si>
     <t xml:space="preserve">18.7717266082764</t>
@@ -2648,13 +2648,13 @@
     <t xml:space="preserve">18.5782051086426</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4233856201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1331024169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4974365234375</t>
+    <t xml:space="preserve">18.4233875274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1331005096436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4974384307861</t>
   </si>
   <si>
     <t xml:space="preserve">20.1263866424561</t>
@@ -2663,7 +2663,7 @@
     <t xml:space="preserve">19.9328651428223</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3199100494385</t>
+    <t xml:space="preserve">20.3199119567871</t>
   </si>
   <si>
     <t xml:space="preserve">19.6425800323486</t>
@@ -2678,10 +2678,10 @@
     <t xml:space="preserve">19.1781253814697</t>
   </si>
   <si>
-    <t xml:space="preserve">19.023307800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1974792480469</t>
+    <t xml:space="preserve">19.0233058929443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1974773406982</t>
   </si>
   <si>
     <t xml:space="preserve">18.9071941375732</t>
@@ -2690,7 +2690,7 @@
     <t xml:space="preserve">19.8844833374023</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4006748199463</t>
+    <t xml:space="preserve">19.4006767272949</t>
   </si>
   <si>
     <t xml:space="preserve">19.7877235412598</t>
@@ -2708,7 +2708,7 @@
     <t xml:space="preserve">22.0132369995117</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8357105255127</t>
+    <t xml:space="preserve">22.8357086181641</t>
   </si>
   <si>
     <t xml:space="preserve">22.1583786010742</t>
@@ -2720,19 +2720,19 @@
     <t xml:space="preserve">22.3519020080566</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7229518890381</t>
+    <t xml:space="preserve">21.7229537963867</t>
   </si>
   <si>
     <t xml:space="preserve">21.5778102874756</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4326667785645</t>
+    <t xml:space="preserve">21.4326686859131</t>
   </si>
   <si>
     <t xml:space="preserve">22.061616897583</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4970436096191</t>
+    <t xml:space="preserve">22.4970455169678</t>
   </si>
   <si>
     <t xml:space="preserve">22.2551403045654</t>
@@ -2744,7 +2744,7 @@
     <t xml:space="preserve">21.6261901855469</t>
   </si>
   <si>
-    <t xml:space="preserve">21.771333694458</t>
+    <t xml:space="preserve">21.7713317871094</t>
   </si>
   <si>
     <t xml:space="preserve">22.3035202026367</t>
@@ -2753,10 +2753,10 @@
     <t xml:space="preserve">22.8840885162354</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7873268127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9648551940918</t>
+    <t xml:space="preserve">22.7873287200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9648571014404</t>
   </si>
   <si>
     <t xml:space="preserve">20.948860168457</t>
@@ -2771,7 +2771,7 @@
     <t xml:space="preserve">20.1747703552246</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5134353637695</t>
+    <t xml:space="preserve">20.5134334564209</t>
   </si>
   <si>
     <t xml:space="preserve">20.0296268463135</t>
@@ -2780,13 +2780,13 @@
     <t xml:space="preserve">22.9808521270752</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1259918212891</t>
+    <t xml:space="preserve">23.1259937286377</t>
   </si>
   <si>
     <t xml:space="preserve">21.3842868804932</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8520984649658</t>
+    <t xml:space="preserve">20.8520965576172</t>
   </si>
   <si>
     <t xml:space="preserve">20.5618133544922</t>
@@ -3369,6 +3369,9 @@
   </si>
   <si>
     <t xml:space="preserve">36.75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6500015258789</t>
   </si>
 </sst>
 </file>
@@ -13891,7 +13894,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G392" t="s">
-        <v>164</v>
+        <v>203</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -13917,7 +13920,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G393" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -13943,7 +13946,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G394" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -13969,7 +13972,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G395" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -13995,7 +13998,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G396" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -14021,7 +14024,7 @@
         <v>13</v>
       </c>
       <c r="G397" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -14047,7 +14050,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G398" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -14073,7 +14076,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G399" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -14099,7 +14102,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G400" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -14125,7 +14128,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G401" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -14151,7 +14154,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G402" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -14177,7 +14180,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G403" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -14203,7 +14206,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G404" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -14229,7 +14232,7 @@
         <v>13</v>
       </c>
       <c r="G405" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -14255,7 +14258,7 @@
         <v>13</v>
       </c>
       <c r="G406" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -14281,7 +14284,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G407" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -14307,7 +14310,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G408" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -14333,7 +14336,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G409" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -14359,7 +14362,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G410" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -14385,7 +14388,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G411" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -14411,7 +14414,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G412" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -14437,7 +14440,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G413" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -14463,7 +14466,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G414" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -14489,7 +14492,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G415" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -14515,7 +14518,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G416" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -14541,7 +14544,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G417" t="s">
-        <v>164</v>
+        <v>203</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -14567,7 +14570,7 @@
         <v>13.25</v>
       </c>
       <c r="G418" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -14593,7 +14596,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G419" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -14619,7 +14622,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G420" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -14645,7 +14648,7 @@
         <v>13</v>
       </c>
       <c r="G421" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -14671,7 +14674,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G422" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -14697,7 +14700,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G423" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -14723,7 +14726,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G424" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -14749,7 +14752,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G425" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -14775,7 +14778,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G426" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -14801,7 +14804,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G427" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -14827,7 +14830,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G428" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -14853,7 +14856,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G429" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -14879,7 +14882,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G430" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -14905,7 +14908,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G431" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -14931,7 +14934,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G432" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -14957,7 +14960,7 @@
         <v>13.1700000762939</v>
       </c>
       <c r="G433" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -14983,7 +14986,7 @@
         <v>13</v>
       </c>
       <c r="G434" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -15009,7 +15012,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G435" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -15035,7 +15038,7 @@
         <v>12.7299995422363</v>
       </c>
       <c r="G436" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -15061,7 +15064,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G437" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -15087,7 +15090,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G438" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -15113,7 +15116,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G439" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -15139,7 +15142,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G440" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -15165,7 +15168,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G441" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -15191,7 +15194,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G442" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -15217,7 +15220,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G443" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -15243,7 +15246,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G444" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -15269,7 +15272,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G445" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -15295,7 +15298,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G446" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -15321,7 +15324,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G447" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -15347,7 +15350,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G448" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -15373,7 +15376,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G449" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -15399,7 +15402,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G450" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -15425,7 +15428,7 @@
         <v>11.25</v>
       </c>
       <c r="G451" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -15451,7 +15454,7 @@
         <v>11.1099996566772</v>
       </c>
       <c r="G452" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -15477,7 +15480,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G453" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -15503,7 +15506,7 @@
         <v>11.25</v>
       </c>
       <c r="G454" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -15529,7 +15532,7 @@
         <v>10.9099998474121</v>
       </c>
       <c r="G455" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -15555,7 +15558,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G456" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -15581,7 +15584,7 @@
         <v>10.75</v>
       </c>
       <c r="G457" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -15607,7 +15610,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G458" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -15633,7 +15636,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G459" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -15659,7 +15662,7 @@
         <v>10.9300003051758</v>
       </c>
       <c r="G460" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -15685,7 +15688,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G461" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -15711,7 +15714,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G462" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -15737,7 +15740,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G463" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -15763,7 +15766,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G464" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -15789,7 +15792,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G465" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -15815,7 +15818,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G466" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -15841,7 +15844,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G467" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -15867,7 +15870,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G468" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -15893,7 +15896,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G469" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -15919,7 +15922,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G470" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -15945,7 +15948,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G471" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -15971,7 +15974,7 @@
         <v>11.2299995422363</v>
       </c>
       <c r="G472" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -15997,7 +16000,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G473" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -16023,7 +16026,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G474" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -16049,7 +16052,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G475" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -16075,7 +16078,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G476" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -16101,7 +16104,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G477" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -16127,7 +16130,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G478" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -16153,7 +16156,7 @@
         <v>10.75</v>
       </c>
       <c r="G479" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -16179,7 +16182,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G480" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -16205,7 +16208,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G481" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -16231,7 +16234,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G482" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -16257,7 +16260,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G483" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -16283,7 +16286,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G484" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -16309,7 +16312,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G485" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -16335,7 +16338,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G486" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -16361,7 +16364,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G487" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -16387,7 +16390,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G488" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -16413,7 +16416,7 @@
         <v>11.5</v>
       </c>
       <c r="G489" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -16439,7 +16442,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G490" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -16465,7 +16468,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G491" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -16491,7 +16494,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G492" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -16517,7 +16520,7 @@
         <v>11.0699996948242</v>
       </c>
       <c r="G493" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -16543,7 +16546,7 @@
         <v>11.2299995422363</v>
       </c>
       <c r="G494" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -16569,7 +16572,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G495" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -16595,7 +16598,7 @@
         <v>10.9300003051758</v>
       </c>
       <c r="G496" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -16621,7 +16624,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G497" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -16647,7 +16650,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G498" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -16673,7 +16676,7 @@
         <v>11.25</v>
       </c>
       <c r="G499" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -16699,7 +16702,7 @@
         <v>11.1300001144409</v>
       </c>
       <c r="G500" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -16725,7 +16728,7 @@
         <v>11</v>
       </c>
       <c r="G501" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -16751,7 +16754,7 @@
         <v>11.0699996948242</v>
       </c>
       <c r="G502" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -16777,7 +16780,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G503" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -16803,7 +16806,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G504" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -16829,7 +16832,7 @@
         <v>11</v>
       </c>
       <c r="G505" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -16855,7 +16858,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G506" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -16881,7 +16884,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G507" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -16907,7 +16910,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G508" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -16933,7 +16936,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G509" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -16959,7 +16962,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G510" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -16985,7 +16988,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G511" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -17011,7 +17014,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G512" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -17037,7 +17040,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G513" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -17063,7 +17066,7 @@
         <v>10.75</v>
       </c>
       <c r="G514" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -17089,7 +17092,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G515" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -17115,7 +17118,7 @@
         <v>10.75</v>
       </c>
       <c r="G516" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -17141,7 +17144,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G517" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -17167,7 +17170,7 @@
         <v>11</v>
       </c>
       <c r="G518" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -17193,7 +17196,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G519" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -17219,7 +17222,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G520" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -17245,7 +17248,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G521" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -17271,7 +17274,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G522" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -17297,7 +17300,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G523" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -17323,7 +17326,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G524" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -17349,7 +17352,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G525" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -17375,7 +17378,7 @@
         <v>11.25</v>
       </c>
       <c r="G526" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -17401,7 +17404,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G527" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -17427,7 +17430,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G528" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -17453,7 +17456,7 @@
         <v>11.25</v>
       </c>
       <c r="G529" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -17479,7 +17482,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G530" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -17505,7 +17508,7 @@
         <v>11.5</v>
       </c>
       <c r="G531" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -17531,7 +17534,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G532" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -17557,7 +17560,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G533" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -17583,7 +17586,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G534" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -17609,7 +17612,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G535" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -17635,7 +17638,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G536" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -17661,7 +17664,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G537" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -17687,7 +17690,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G538" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -17713,7 +17716,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G539" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -17739,7 +17742,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G540" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -17765,7 +17768,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G541" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -17791,7 +17794,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G542" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -17817,7 +17820,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G543" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -17843,7 +17846,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G544" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -17869,7 +17872,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G545" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -17895,7 +17898,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G546" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -17921,7 +17924,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G547" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -17947,7 +17950,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G548" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -17973,7 +17976,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G549" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -17999,7 +18002,7 @@
         <v>10.5</v>
       </c>
       <c r="G550" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -18025,7 +18028,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G551" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -18051,7 +18054,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G552" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -18077,7 +18080,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G553" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -18103,7 +18106,7 @@
         <v>10.25</v>
       </c>
       <c r="G554" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -18129,7 +18132,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G555" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -18155,7 +18158,7 @@
         <v>10.25</v>
       </c>
       <c r="G556" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -18181,7 +18184,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G557" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -18207,7 +18210,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G558" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -18233,7 +18236,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G559" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -18259,7 +18262,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G560" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -18285,7 +18288,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G561" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -18311,7 +18314,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G562" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -18337,7 +18340,7 @@
         <v>10.5</v>
       </c>
       <c r="G563" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -18363,7 +18366,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G564" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -18389,7 +18392,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G565" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -18415,7 +18418,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G566" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -18441,7 +18444,7 @@
         <v>10.25</v>
       </c>
       <c r="G567" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -18467,7 +18470,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G568" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -18493,7 +18496,7 @@
         <v>10.25</v>
       </c>
       <c r="G569" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -18519,7 +18522,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G570" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -18545,7 +18548,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G571" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -18571,7 +18574,7 @@
         <v>10</v>
       </c>
       <c r="G572" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -18597,7 +18600,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G573" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -18623,7 +18626,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G574" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -18649,7 +18652,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G575" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -18675,7 +18678,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G576" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -18701,7 +18704,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G577" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -18727,7 +18730,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G578" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -18753,7 +18756,7 @@
         <v>10</v>
       </c>
       <c r="G579" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -18779,7 +18782,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G580" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -18805,7 +18808,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G581" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -18831,7 +18834,7 @@
         <v>10.25</v>
       </c>
       <c r="G582" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -18857,7 +18860,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G583" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -18883,7 +18886,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G584" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -18909,7 +18912,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G585" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -18935,7 +18938,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G586" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -18961,7 +18964,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G587" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -18987,7 +18990,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G588" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -19013,7 +19016,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G589" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -19039,7 +19042,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G590" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -19065,7 +19068,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G591" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -19091,7 +19094,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G592" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -19117,7 +19120,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G593" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -19143,7 +19146,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G594" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -19169,7 +19172,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G595" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -19195,7 +19198,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G596" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -19221,7 +19224,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G597" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -19247,7 +19250,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G598" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -19273,7 +19276,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G599" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -19299,7 +19302,7 @@
         <v>10.25</v>
       </c>
       <c r="G600" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -19325,7 +19328,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G601" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -19351,7 +19354,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G602" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -19377,7 +19380,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G603" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -19403,7 +19406,7 @@
         <v>10.25</v>
       </c>
       <c r="G604" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -19429,7 +19432,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G605" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -19455,7 +19458,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G606" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -19481,7 +19484,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G607" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -19507,7 +19510,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G608" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19533,7 +19536,7 @@
         <v>10.25</v>
       </c>
       <c r="G609" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19559,7 +19562,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G610" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19585,7 +19588,7 @@
         <v>10.25</v>
       </c>
       <c r="G611" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19611,7 +19614,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G612" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19637,7 +19640,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G613" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19663,7 +19666,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G614" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19689,7 +19692,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G615" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19715,7 +19718,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G616" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19741,7 +19744,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G617" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19767,7 +19770,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G618" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19793,7 +19796,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G619" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19819,7 +19822,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G620" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19845,7 +19848,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G621" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19871,7 +19874,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G622" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19897,7 +19900,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G623" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19923,7 +19926,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G624" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19949,7 +19952,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G625" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19975,7 +19978,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G626" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -20001,7 +20004,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G627" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -20027,7 +20030,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G628" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -20053,7 +20056,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G629" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -20079,7 +20082,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G630" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -20105,7 +20108,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G631" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -20131,7 +20134,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G632" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -20157,7 +20160,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G633" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -20183,7 +20186,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G634" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -20209,7 +20212,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G635" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -20235,7 +20238,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G636" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -20261,7 +20264,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G637" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -20287,7 +20290,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G638" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -20313,7 +20316,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G639" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -20339,7 +20342,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G640" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -20365,7 +20368,7 @@
         <v>10</v>
       </c>
       <c r="G641" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -20391,7 +20394,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G642" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -20417,7 +20420,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G643" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -20443,7 +20446,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G644" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -20469,7 +20472,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G645" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -20495,7 +20498,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G646" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -20521,7 +20524,7 @@
         <v>10</v>
       </c>
       <c r="G647" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -20547,7 +20550,7 @@
         <v>10</v>
       </c>
       <c r="G648" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -20573,7 +20576,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G649" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -20599,7 +20602,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G650" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -20625,7 +20628,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G651" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -20651,7 +20654,7 @@
         <v>10</v>
       </c>
       <c r="G652" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -20677,7 +20680,7 @@
         <v>10</v>
       </c>
       <c r="G653" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -20703,7 +20706,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G654" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -20729,7 +20732,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G655" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -20755,7 +20758,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G656" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -20781,7 +20784,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G657" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -20807,7 +20810,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G658" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -20833,7 +20836,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G659" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -20859,7 +20862,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G660" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -20885,7 +20888,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G661" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -20911,7 +20914,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G662" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -20937,7 +20940,7 @@
         <v>10</v>
       </c>
       <c r="G663" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -20963,7 +20966,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G664" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -20989,7 +20992,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G665" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -21015,7 +21018,7 @@
         <v>10.25</v>
       </c>
       <c r="G666" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -21041,7 +21044,7 @@
         <v>10</v>
       </c>
       <c r="G667" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -21067,7 +21070,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G668" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -21093,7 +21096,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G669" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -21119,7 +21122,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G670" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -21145,7 +21148,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G671" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -21171,7 +21174,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G672" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -21197,7 +21200,7 @@
         <v>10</v>
       </c>
       <c r="G673" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -21223,7 +21226,7 @@
         <v>10</v>
       </c>
       <c r="G674" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -21249,7 +21252,7 @@
         <v>10</v>
       </c>
       <c r="G675" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -21275,7 +21278,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G676" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -21301,7 +21304,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G677" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -21327,7 +21330,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G678" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -21353,7 +21356,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G679" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -21379,7 +21382,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G680" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -21405,7 +21408,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G681" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -21431,7 +21434,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G682" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -21457,7 +21460,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G683" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -21483,7 +21486,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G684" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -21509,7 +21512,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G685" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -21535,7 +21538,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G686" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -21561,7 +21564,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G687" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -21587,7 +21590,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G688" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -21613,7 +21616,7 @@
         <v>10</v>
       </c>
       <c r="G689" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -21639,7 +21642,7 @@
         <v>10</v>
       </c>
       <c r="G690" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -21665,7 +21668,7 @@
         <v>10</v>
       </c>
       <c r="G691" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -21691,7 +21694,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G692" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -21717,7 +21720,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G693" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -21743,7 +21746,7 @@
         <v>10</v>
       </c>
       <c r="G694" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -21769,7 +21772,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G695" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -21795,7 +21798,7 @@
         <v>10</v>
       </c>
       <c r="G696" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -21821,7 +21824,7 @@
         <v>10</v>
       </c>
       <c r="G697" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -21847,7 +21850,7 @@
         <v>10.5</v>
       </c>
       <c r="G698" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -21873,7 +21876,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G699" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -21899,7 +21902,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G700" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -21925,7 +21928,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G701" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -21951,7 +21954,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G702" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -21977,7 +21980,7 @@
         <v>10.25</v>
       </c>
       <c r="G703" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -22003,7 +22006,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G704" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -22029,7 +22032,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G705" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -22055,7 +22058,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G706" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -22081,7 +22084,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G707" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -22107,7 +22110,7 @@
         <v>10</v>
       </c>
       <c r="G708" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -22133,7 +22136,7 @@
         <v>10</v>
       </c>
       <c r="G709" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -22159,7 +22162,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G710" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -22185,7 +22188,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G711" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -22211,7 +22214,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G712" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -22237,7 +22240,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G713" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -22263,7 +22266,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G714" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -22289,7 +22292,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G715" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -22315,7 +22318,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G716" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -22341,7 +22344,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G717" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -22367,7 +22370,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G718" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -22393,7 +22396,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G719" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -22419,7 +22422,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G720" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -22445,7 +22448,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G721" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -22471,7 +22474,7 @@
         <v>10</v>
       </c>
       <c r="G722" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -22497,7 +22500,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G723" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -22523,7 +22526,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G724" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -22549,7 +22552,7 @@
         <v>10</v>
       </c>
       <c r="G725" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -22575,7 +22578,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G726" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -22601,7 +22604,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G727" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -22627,7 +22630,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G728" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -22653,7 +22656,7 @@
         <v>10</v>
       </c>
       <c r="G729" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -22679,7 +22682,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G730" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -22705,7 +22708,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G731" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -22731,7 +22734,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G732" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -22757,7 +22760,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G733" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -22783,7 +22786,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G734" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -22809,7 +22812,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G735" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -22835,7 +22838,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G736" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -22861,7 +22864,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G737" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -22887,7 +22890,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G738" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -22913,7 +22916,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G739" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -22939,7 +22942,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G740" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -22965,7 +22968,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G741" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -22991,7 +22994,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G742" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -23017,7 +23020,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G743" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -23043,7 +23046,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G744" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -23069,7 +23072,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G745" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -23095,7 +23098,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G746" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -23121,7 +23124,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G747" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -23147,7 +23150,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G748" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -23173,7 +23176,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G749" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -23199,7 +23202,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G750" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -23225,7 +23228,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G751" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -23251,7 +23254,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G752" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -23277,7 +23280,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G753" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -23303,7 +23306,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G754" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -23329,7 +23332,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G755" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -23355,7 +23358,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G756" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -23381,7 +23384,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G757" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -23407,7 +23410,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G758" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -23433,7 +23436,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G759" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -23459,7 +23462,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G760" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -23485,7 +23488,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G761" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -23511,7 +23514,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G762" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -23537,7 +23540,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G763" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -23563,7 +23566,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G764" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -23589,7 +23592,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G765" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -23615,7 +23618,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G766" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -23641,7 +23644,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G767" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -23667,7 +23670,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G768" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -23693,7 +23696,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G769" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -23719,7 +23722,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G770" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -23745,7 +23748,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G771" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -23771,7 +23774,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G772" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -23797,7 +23800,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G773" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -23823,7 +23826,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G774" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -23849,7 +23852,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G775" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -23875,7 +23878,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G776" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -23901,7 +23904,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G777" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -23927,7 +23930,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G778" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -23953,7 +23956,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G779" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -23979,7 +23982,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G780" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -24005,7 +24008,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G781" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -24031,7 +24034,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G782" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -24057,7 +24060,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G783" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -24083,7 +24086,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G784" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -24109,7 +24112,7 @@
         <v>10</v>
       </c>
       <c r="G785" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -24135,7 +24138,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G786" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -24161,7 +24164,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G787" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -24187,7 +24190,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G788" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -24213,7 +24216,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G789" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -24239,7 +24242,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G790" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -24265,7 +24268,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G791" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -24291,7 +24294,7 @@
         <v>10</v>
       </c>
       <c r="G792" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -24317,7 +24320,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G793" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -24343,7 +24346,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G794" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -24369,7 +24372,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G795" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -24395,7 +24398,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G796" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -24421,7 +24424,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G797" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -24447,7 +24450,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G798" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -24473,7 +24476,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G799" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -24499,7 +24502,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G800" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -24525,7 +24528,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G801" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -24551,7 +24554,7 @@
         <v>10.25</v>
       </c>
       <c r="G802" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -24577,7 +24580,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G803" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -24603,7 +24606,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G804" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -24629,7 +24632,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G805" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -24655,7 +24658,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G806" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -24681,7 +24684,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G807" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -24707,7 +24710,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G808" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -24733,7 +24736,7 @@
         <v>10.5</v>
       </c>
       <c r="G809" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -24759,7 +24762,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G810" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -24785,7 +24788,7 @@
         <v>10</v>
       </c>
       <c r="G811" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -24811,7 +24814,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G812" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -24837,7 +24840,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G813" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -24863,7 +24866,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G814" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -24889,7 +24892,7 @@
         <v>10.5</v>
       </c>
       <c r="G815" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -24915,7 +24918,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G816" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -24941,7 +24944,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G817" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -24967,7 +24970,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G818" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -24993,7 +24996,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G819" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -25019,7 +25022,7 @@
         <v>11.25</v>
       </c>
       <c r="G820" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -25045,7 +25048,7 @@
         <v>11.5</v>
       </c>
       <c r="G821" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -25071,7 +25074,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G822" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -25097,7 +25100,7 @@
         <v>11.5</v>
       </c>
       <c r="G823" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -25123,7 +25126,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G824" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -25149,7 +25152,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G825" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -25175,7 +25178,7 @@
         <v>11.75</v>
       </c>
       <c r="G826" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -25201,7 +25204,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G827" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -25227,7 +25230,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G828" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -25253,7 +25256,7 @@
         <v>11.75</v>
       </c>
       <c r="G829" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -25279,7 +25282,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G830" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -25305,7 +25308,7 @@
         <v>11.75</v>
       </c>
       <c r="G831" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -25331,7 +25334,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G832" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -25357,7 +25360,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G833" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -25383,7 +25386,7 @@
         <v>11.75</v>
       </c>
       <c r="G834" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -25409,7 +25412,7 @@
         <v>11.75</v>
       </c>
       <c r="G835" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -25435,7 +25438,7 @@
         <v>11.75</v>
       </c>
       <c r="G836" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -25461,7 +25464,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G837" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -25487,7 +25490,7 @@
         <v>11.75</v>
       </c>
       <c r="G838" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -25513,7 +25516,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G839" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -25539,7 +25542,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G840" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -25565,7 +25568,7 @@
         <v>11.25</v>
       </c>
       <c r="G841" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -25591,7 +25594,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G842" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -25617,7 +25620,7 @@
         <v>11.5</v>
       </c>
       <c r="G843" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -25643,7 +25646,7 @@
         <v>11.5</v>
       </c>
       <c r="G844" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -25669,7 +25672,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G845" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -25695,7 +25698,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G846" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -25721,7 +25724,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G847" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -25747,7 +25750,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G848" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -25773,7 +25776,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G849" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -25799,7 +25802,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G850" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -25825,7 +25828,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G851" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -25851,7 +25854,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G852" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -25877,7 +25880,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G853" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -25903,7 +25906,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G854" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -25929,7 +25932,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G855" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -25955,7 +25958,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G856" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -25981,7 +25984,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G857" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -26007,7 +26010,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G858" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -26033,7 +26036,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G859" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -26059,7 +26062,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G860" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -26085,7 +26088,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G861" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -26111,7 +26114,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G862" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -26137,7 +26140,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G863" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -26163,7 +26166,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G864" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -26189,7 +26192,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G865" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -26215,7 +26218,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G866" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -26241,7 +26244,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G867" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -26267,7 +26270,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G868" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -26293,7 +26296,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G869" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -26319,7 +26322,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G870" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -26553,7 +26556,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G879" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -26657,7 +26660,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G883" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -26709,7 +26712,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G885" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -26839,7 +26842,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G890" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -26943,7 +26946,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G894" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -26995,7 +26998,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G896" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -27021,7 +27024,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G897" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -27281,7 +27284,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G907" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -27359,7 +27362,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G910" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -27385,7 +27388,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G911" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -27411,7 +27414,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G912" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -27515,7 +27518,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G916" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -27567,7 +27570,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G918" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -29413,7 +29416,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G989" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -29491,7 +29494,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G992" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -31363,7 +31366,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1064" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -32221,7 +32224,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1097" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -32273,7 +32276,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G1099" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -68603,7 +68606,7 @@
     </row>
     <row r="2497">
       <c r="A2497" s="1" t="n">
-        <v>45954.6494097222</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B2497" t="n">
         <v>6770</v>
@@ -68624,6 +68627,32 @@
         <v>1118</v>
       </c>
       <c r="H2497" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2498">
+      <c r="A2498" s="1" t="n">
+        <v>45957.6912152778</v>
+      </c>
+      <c r="B2498" t="n">
+        <v>4715</v>
+      </c>
+      <c r="C2498" t="n">
+        <v>37.0999984741211</v>
+      </c>
+      <c r="D2498" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="E2498" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="F2498" t="n">
+        <v>36.6500015258789</v>
+      </c>
+      <c r="G2498" t="s">
+        <v>1119</v>
+      </c>
+      <c r="H2498" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LUVE.MI.xlsx
+++ b/data/LUVE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1120" uniqueCount="1120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1121" uniqueCount="1121">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30043315887451</t>
+    <t xml:space="preserve">8.30043411254883</t>
   </si>
   <si>
     <t xml:space="preserve">LUVE.MI</t>
@@ -50,88 +50,88 @@
     <t xml:space="preserve">8.2838306427002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09292221069336</t>
+    <t xml:space="preserve">8.09292125701904</t>
   </si>
   <si>
     <t xml:space="preserve">8.19667816162109</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07632350921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15102386474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17177677154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03896999359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08462142944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06802272796631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96841764450073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01821994781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99746751785278</t>
+    <t xml:space="preserve">8.07632064819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15102481842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17177581787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03897190093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08462238311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06802082061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96841669082642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01821804046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99746656417847</t>
   </si>
   <si>
     <t xml:space="preserve">7.91861295700073</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91446399688721</t>
+    <t xml:space="preserve">7.91446256637573</t>
   </si>
   <si>
     <t xml:space="preserve">7.91031217575073</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88541221618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87711048126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.852210521698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64884996414185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7194037437439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70280170440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69035053253174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.619797706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55754375457764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55339384078979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63639831542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76920413970947</t>
+    <t xml:space="preserve">7.88541173934937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87711143493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85220909118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64884901046753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71940279006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70280313491821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69035243988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61979913711548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55754470825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55339479446411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63639783859253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76920461654663</t>
   </si>
   <si>
     <t xml:space="preserve">7.80240726470947</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93521499633789</t>
+    <t xml:space="preserve">7.93521451950073</t>
   </si>
   <si>
     <t xml:space="preserve">8.10122299194336</t>
@@ -143,16 +143,16 @@
     <t xml:space="preserve">8.18422794342041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13442516326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00161743164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9601149559021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21742820739746</t>
+    <t xml:space="preserve">8.13442420959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00161838531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96011590957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21742725372314</t>
   </si>
   <si>
     <t xml:space="preserve">8.35853672027588</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">8.32533359527588</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29213237762451</t>
+    <t xml:space="preserve">8.2921314239502</t>
   </si>
   <si>
     <t xml:space="preserve">8.20082759857178</t>
@@ -173,73 +173,73 @@
     <t xml:space="preserve">8.30336380004883</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36267280578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43045616149902</t>
+    <t xml:space="preserve">8.36267471313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43045520782471</t>
   </si>
   <si>
     <t xml:space="preserve">8.15085411071777</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17627143859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2059268951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13390731811523</t>
+    <t xml:space="preserve">8.17627048492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20592784881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13390827178955</t>
   </si>
   <si>
     <t xml:space="preserve">8.11696147918701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21863555908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21016216278076</t>
+    <t xml:space="preserve">8.21863460540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21016311645508</t>
   </si>
   <si>
     <t xml:space="preserve">8.21439838409424</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20168972015381</t>
+    <t xml:space="preserve">8.20168876647949</t>
   </si>
   <si>
     <t xml:space="preserve">8.26099872589111</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09154319763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10848808288574</t>
+    <t xml:space="preserve">8.09154415130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10848903656006</t>
   </si>
   <si>
     <t xml:space="preserve">8.04918003082275</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96444988250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92208814620972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87972354888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83735752105713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12543487548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93479585647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75263071060181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71026611328125</t>
+    <t xml:space="preserve">7.96445083618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92208671569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.879723072052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83735942840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12543392181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93479633331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75262928009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71026659011841</t>
   </si>
   <si>
     <t xml:space="preserve">7.93903350830078</t>
@@ -248,16 +248,16 @@
     <t xml:space="preserve">7.81194067001343</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79499578475952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62553882598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66790199279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84583139419556</t>
+    <t xml:space="preserve">7.79499387741089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62553834915161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66790294647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84583282470703</t>
   </si>
   <si>
     <t xml:space="preserve">8.19321727752686</t>
@@ -266,16 +266,16 @@
     <t xml:space="preserve">8.47282123565674</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51518535614014</t>
+    <t xml:space="preserve">8.51518440246582</t>
   </si>
   <si>
     <t xml:space="preserve">8.52365779876709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5999116897583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78631496429443</t>
+    <t xml:space="preserve">8.59991359710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78631401062012</t>
   </si>
   <si>
     <t xml:space="preserve">8.71853351593018</t>
@@ -284,16 +284,16 @@
     <t xml:space="preserve">8.50671100616455</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54060363769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46858215332031</t>
+    <t xml:space="preserve">8.540602684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46858406066895</t>
   </si>
   <si>
     <t xml:space="preserve">8.46434688568115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5575475692749</t>
+    <t xml:space="preserve">8.55754852294922</t>
   </si>
   <si>
     <t xml:space="preserve">8.57449340820312</t>
@@ -302,58 +302,58 @@
     <t xml:space="preserve">8.81173419952393</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7270040512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64227676391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89646053314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02355098724365</t>
+    <t xml:space="preserve">8.72700500488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6422758102417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89646148681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02355289459229</t>
   </si>
   <si>
     <t xml:space="preserve">9.09980869293213</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06591701507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1082820892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27773761749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1930103302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18453788757324</t>
+    <t xml:space="preserve">9.06591796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10828304290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27773857116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19300937652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18453884124756</t>
   </si>
   <si>
     <t xml:space="preserve">9.07439041137695</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09133529663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30315589904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32010269165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12522792816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60818004608154</t>
+    <t xml:space="preserve">9.09133625030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30315685272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32010364532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12522888183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60817813873291</t>
   </si>
   <si>
     <t xml:space="preserve">9.4048318862915</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48955917358398</t>
+    <t xml:space="preserve">9.48955726623535</t>
   </si>
   <si>
     <t xml:space="preserve">9.38788414001465</t>
@@ -365,49 +365,49 @@
     <t xml:space="preserve">9.48108577728271</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44719314575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54039669036865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57428646087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47261333465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41330432891846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42177486419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51497554779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56581401824951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74374294281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0657110214233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2521133422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1334943771362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99792957305908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95556354522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98098278045654</t>
+    <t xml:space="preserve">9.44719505310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54039573669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5742883682251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47261238098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41330242156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42177581787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51497650146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5658130645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74374389648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0657119750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2521123886108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1334915161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99792861938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95556259155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98098087310791</t>
   </si>
   <si>
     <t xml:space="preserve">9.88778114318848</t>
@@ -419,79 +419,79 @@
     <t xml:space="preserve">10.0148735046387</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1589097976685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0402908325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70137882232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73527050018311</t>
+    <t xml:space="preserve">10.1589107513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0402927398682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70137786865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73526954650879</t>
   </si>
   <si>
     <t xml:space="preserve">9.70985221862793</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0826559066772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86236381530762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.125020980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2944765090942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4808788299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5317153930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5147705078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.802845954895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9129934310913</t>
+    <t xml:space="preserve">10.0826568603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86236190795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1250190734863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2944755554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4808778762817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5317163467407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5147695541382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8028450012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.912992477417</t>
   </si>
   <si>
     <t xml:space="preserve">10.8621559143066</t>
   </si>
   <si>
-    <t xml:space="preserve">11.014666557312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0570306777954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.277325630188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4383068084717</t>
+    <t xml:space="preserve">11.0146656036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0570297241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2773246765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.438307762146</t>
   </si>
   <si>
     <t xml:space="preserve">11.6586008071899</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5823440551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4806709289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5908184051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.700963973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7772188186646</t>
+    <t xml:space="preserve">11.5823450088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4806718826294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5908193588257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7009649276733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7772207260132</t>
   </si>
   <si>
     <t xml:space="preserve">11.8111114501953</t>
@@ -500,43 +500,43 @@
     <t xml:space="preserve">11.8365297317505</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6670742034912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5992918014526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5230379104614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6077632904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6263818740845</t>
+    <t xml:space="preserve">11.6670751571655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.599289894104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5230350494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6077651977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6263809204102</t>
   </si>
   <si>
     <t xml:space="preserve">11.7297267913818</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6952781677246</t>
+    <t xml:space="preserve">11.6952772140503</t>
   </si>
   <si>
     <t xml:space="preserve">11.6780548095703</t>
   </si>
   <si>
-    <t xml:space="preserve">11.798623085022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8847465515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9105806350708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0655994415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3153514862061</t>
+    <t xml:space="preserve">11.7986240386963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.884744644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9105815887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0656003952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3153524398804</t>
   </si>
   <si>
     <t xml:space="preserve">12.3584127426147</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">12.1431093215942</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9967021942139</t>
+    <t xml:space="preserve">11.9967031478882</t>
   </si>
   <si>
     <t xml:space="preserve">11.8416843414307</t>
@@ -557,10 +557,10 @@
     <t xml:space="preserve">11.7555618286133</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7125034332275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8502979278564</t>
+    <t xml:space="preserve">11.7125024795532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8502960205078</t>
   </si>
   <si>
     <t xml:space="preserve">11.9191932678223</t>
@@ -572,34 +572,34 @@
     <t xml:space="preserve">12.0397634506226</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0483741760254</t>
+    <t xml:space="preserve">12.048376083374</t>
   </si>
   <si>
     <t xml:space="preserve">11.7900104522705</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0311508178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9450283050537</t>
+    <t xml:space="preserve">12.0311517715454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.945029258728</t>
   </si>
   <si>
     <t xml:space="preserve">11.8158483505249</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8933572769165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8761320114136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8244590759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8675212860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.901969909668</t>
+    <t xml:space="preserve">11.8933582305908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8761339187622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8244600296021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8675203323364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9019689559937</t>
   </si>
   <si>
     <t xml:space="preserve">11.9278059005737</t>
@@ -611,7 +611,7 @@
     <t xml:space="preserve">11.6694421768188</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6349945068359</t>
+    <t xml:space="preserve">11.6349925994873</t>
   </si>
   <si>
     <t xml:space="preserve">11.6091566085815</t>
@@ -620,43 +620,40 @@
     <t xml:space="preserve">11.5747079849243</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5316457748413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5230369567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3680171966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3594036102295</t>
+    <t xml:space="preserve">11.5316476821899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.368016242981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3594045639038</t>
   </si>
   <si>
     <t xml:space="preserve">11.2818956375122</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2302217483521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1957740783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1871614456177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1096515655518</t>
+    <t xml:space="preserve">11.230224609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1957731246948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.187162399292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1096534729004</t>
   </si>
   <si>
     <t xml:space="preserve">11.0579805374146</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1785488128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1268768310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9374094009399</t>
+    <t xml:space="preserve">11.1785497665405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.126877784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9374113082886</t>
   </si>
   <si>
     <t xml:space="preserve">11.066593170166</t>
@@ -665,13 +662,13 @@
     <t xml:space="preserve">11.0235319137573</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0838165283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1354904174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2043867111206</t>
+    <t xml:space="preserve">11.083815574646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1354894638062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2043857574463</t>
   </si>
   <si>
     <t xml:space="preserve">11.3163442611694</t>
@@ -680,7 +677,7 @@
     <t xml:space="preserve">11.4541397094727</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5402593612671</t>
+    <t xml:space="preserve">11.5402603149414</t>
   </si>
   <si>
     <t xml:space="preserve">11.4110774993896</t>
@@ -692,28 +689,28 @@
     <t xml:space="preserve">11.1613254547119</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2646703720093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1527128219604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0407562255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4196920394897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2216100692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2388362884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3421802520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9546346664429</t>
+    <t xml:space="preserve">11.2646722793579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1527137756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0407552719116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4196901321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2216110229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2388334274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3421821594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9546356201172</t>
   </si>
   <si>
     <t xml:space="preserve">10.9632453918457</t>
@@ -722,7 +719,7 @@
     <t xml:space="preserve">11.0063066482544</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0924301147461</t>
+    <t xml:space="preserve">11.0924291610718</t>
   </si>
   <si>
     <t xml:space="preserve">9.74032306671143</t>
@@ -731,67 +728,67 @@
     <t xml:space="preserve">9.01690483093262</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2149829864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37861347198486</t>
+    <t xml:space="preserve">9.21498394012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37861442565918</t>
   </si>
   <si>
     <t xml:space="preserve">9.49057197570801</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50779628753662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59391784667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60252857208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68865013122559</t>
+    <t xml:space="preserve">9.50779724121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.593918800354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60253047943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68865203857422</t>
   </si>
   <si>
     <t xml:space="preserve">9.56808185577393</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39583873748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34416484832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25804328918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30110549926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41306209564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28388023376465</t>
+    <t xml:space="preserve">9.39583778381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34416580200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25804424285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30110454559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41306400299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28388118743896</t>
   </si>
   <si>
     <t xml:space="preserve">9.24081897735596</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12886238098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02551555633545</t>
+    <t xml:space="preserve">9.12886142730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02551651000977</t>
   </si>
   <si>
     <t xml:space="preserve">9.20637130737305</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26665592193604</t>
+    <t xml:space="preserve">9.26665687561035</t>
   </si>
   <si>
     <t xml:space="preserve">9.69726276397705</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65420246124268</t>
+    <t xml:space="preserve">9.65420150756836</t>
   </si>
   <si>
     <t xml:space="preserve">9.66281509399414</t>
@@ -800,16 +797,16 @@
     <t xml:space="preserve">9.64558982849121</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67142581939697</t>
+    <t xml:space="preserve">9.67142677307129</t>
   </si>
   <si>
     <t xml:space="preserve">9.75754737854004</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71448802947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0944128036499</t>
+    <t xml:space="preserve">9.71448612213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09441375732422</t>
   </si>
   <si>
     <t xml:space="preserve">8.9393949508667</t>
@@ -818,34 +815,34 @@
     <t xml:space="preserve">9.14608573913574</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12024974822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83505916595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73171234130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90395450592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77477169036865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53363227844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49918365478516</t>
+    <t xml:space="preserve">9.1202507019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83505821228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73171329498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90395355224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77477264404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5336332321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49918460845947</t>
   </si>
   <si>
     <t xml:space="preserve">9.57669258117676</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58530521392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47334671020508</t>
+    <t xml:space="preserve">9.58530426025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47334766387939</t>
   </si>
   <si>
     <t xml:space="preserve">9.43028545379639</t>
@@ -854,37 +851,37 @@
     <t xml:space="preserve">9.54224395751953</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1719217300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23220825195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55946826934814</t>
+    <t xml:space="preserve">9.17192363739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23220920562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55946922302246</t>
   </si>
   <si>
     <t xml:space="preserve">9.51640796661377</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8608922958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95661926269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91355895996094</t>
+    <t xml:space="preserve">9.86089324951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95662021636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91355800628662</t>
   </si>
   <si>
     <t xml:space="preserve">9.08580207824707</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04273986816406</t>
+    <t xml:space="preserve">9.0427417755127</t>
   </si>
   <si>
     <t xml:space="preserve">8.99967956542969</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82743644714355</t>
+    <t xml:space="preserve">8.82743740081787</t>
   </si>
   <si>
     <t xml:space="preserve">8.69825649261475</t>
@@ -893,10 +890,10 @@
     <t xml:space="preserve">8.87049770355225</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7843770980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74131679534912</t>
+    <t xml:space="preserve">8.78437614440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7413158416748</t>
   </si>
   <si>
     <t xml:space="preserve">8.61213397979736</t>
@@ -905,22 +902,22 @@
     <t xml:space="preserve">8.59490966796875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65519332885742</t>
+    <t xml:space="preserve">8.65519618988037</t>
   </si>
   <si>
     <t xml:space="preserve">8.45711517333984</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06314373016357</t>
+    <t xml:space="preserve">9.06314468383789</t>
   </si>
   <si>
     <t xml:space="preserve">9.10714054107666</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0191478729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97515296936035</t>
+    <t xml:space="preserve">9.01914882659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97515201568604</t>
   </si>
   <si>
     <t xml:space="preserve">8.93115711212158</t>
@@ -929,10 +926,10 @@
     <t xml:space="preserve">8.88716220855713</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84316539764404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76397228240967</t>
+    <t xml:space="preserve">8.84316635131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76397323608398</t>
   </si>
   <si>
     <t xml:space="preserve">8.48240089416504</t>
@@ -944,106 +941,106 @@
     <t xml:space="preserve">8.62318706512451</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58798980712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6583833694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60558795928955</t>
+    <t xml:space="preserve">8.58799076080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65838241577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60558700561523</t>
   </si>
   <si>
     <t xml:space="preserve">8.72877597808838</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69357776641846</t>
+    <t xml:space="preserve">8.69357872009277</t>
   </si>
   <si>
     <t xml:space="preserve">8.74637413024902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53519535064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44720458984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27121925354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32401371002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28881740570068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78157043457031</t>
+    <t xml:space="preserve">8.53519344329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44720268249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27121829986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32401466369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.288818359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78157138824463</t>
   </si>
   <si>
     <t xml:space="preserve">8.64078426361084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79916954040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67598056793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23912715911865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37111473083496</t>
+    <t xml:space="preserve">8.79916858673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67598152160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23912906646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37111568450928</t>
   </si>
   <si>
     <t xml:space="preserve">9.32711887359619</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1951322555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15113544464111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46480178833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41200637817383</t>
+    <t xml:space="preserve">9.19513130187988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15113639831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46480083465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41200542449951</t>
   </si>
   <si>
     <t xml:space="preserve">8.49999809265137</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34161281585693</t>
+    <t xml:space="preserve">8.34161376953125</t>
   </si>
   <si>
     <t xml:space="preserve">8.23602199554443</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30641555786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13043212890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1832275390625</t>
+    <t xml:space="preserve">8.30641651153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13043117523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18322849273682</t>
   </si>
   <si>
     <t xml:space="preserve">8.16562938690186</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21842384338379</t>
+    <t xml:space="preserve">8.21842479705811</t>
   </si>
   <si>
     <t xml:space="preserve">8.25362014770508</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37681007385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5175952911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28312397003174</t>
+    <t xml:space="preserve">8.37680912017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51759719848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28312492370605</t>
   </si>
   <si>
     <t xml:space="preserve">9.41511154174805</t>
@@ -1052,34 +1049,34 @@
     <t xml:space="preserve">9.63508987426758</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59109401702881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8990650177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1190452575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1630411148071</t>
+    <t xml:space="preserve">9.59109497070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89906692504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.119044303894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1630401611328</t>
   </si>
   <si>
     <t xml:space="preserve">10.2070369720459</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3390245437622</t>
+    <t xml:space="preserve">10.3390254974365</t>
   </si>
   <si>
     <t xml:space="preserve">10.2950277328491</t>
   </si>
   <si>
-    <t xml:space="preserve">10.383020401001</t>
+    <t xml:space="preserve">10.3830194473267</t>
   </si>
   <si>
     <t xml:space="preserve">10.2510318756104</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4270153045654</t>
+    <t xml:space="preserve">10.4270162582397</t>
   </si>
   <si>
     <t xml:space="preserve">10.0750484466553</t>
@@ -1094,28 +1091,31 @@
     <t xml:space="preserve">10.4700717926025</t>
   </si>
   <si>
-    <t xml:space="preserve">10.694751739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6048793792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3802013397217</t>
+    <t xml:space="preserve">10.6947507858276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6048803329468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3802003860474</t>
   </si>
   <si>
     <t xml:space="preserve">10.2453918457031</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0656490325928</t>
+    <t xml:space="preserve">10.0656480789185</t>
   </si>
   <si>
     <t xml:space="preserve">10.4251356124878</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3352642059326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2903270721436</t>
+    <t xml:space="preserve">10.5150079727173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3352632522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2903280258179</t>
   </si>
   <si>
     <t xml:space="preserve">10.2004556655884</t>
@@ -1130,37 +1130,37 @@
     <t xml:space="preserve">9.93084144592285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88590431213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1555204391479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0207109451294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7510986328125</t>
+    <t xml:space="preserve">9.88590526580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1555213928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.020712852478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75109672546387</t>
   </si>
   <si>
     <t xml:space="preserve">9.70616149902344</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34667491912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30173778533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39160823822021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48148155212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61628913879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52641868591309</t>
+    <t xml:space="preserve">9.3466739654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30173683166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39160919189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48148250579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61629009246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52641677856445</t>
   </si>
   <si>
     <t xml:space="preserve">9.43654537200928</t>
@@ -1175,19 +1175,19 @@
     <t xml:space="preserve">9.16693019866943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07705783843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25680160522461</t>
+    <t xml:space="preserve">9.07705879211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25680065155029</t>
   </si>
   <si>
     <t xml:space="preserve">8.98718643188477</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57135200500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66122436523438</t>
+    <t xml:space="preserve">9.5713529586792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66122531890869</t>
   </si>
   <si>
     <t xml:space="preserve">9.7960319519043</t>
@@ -1196,25 +1196,25 @@
     <t xml:space="preserve">10.9643669128418</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4586610794067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5035991668701</t>
+    <t xml:space="preserve">11.4586629867554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5035982131958</t>
   </si>
   <si>
     <t xml:space="preserve">11.233983039856</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1441097259521</t>
+    <t xml:space="preserve">11.1441116333008</t>
   </si>
   <si>
     <t xml:space="preserve">10.9194307327271</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8744955062866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0093030929565</t>
+    <t xml:space="preserve">10.8744945526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0093021392822</t>
   </si>
   <si>
     <t xml:space="preserve">11.2789182662964</t>
@@ -1226,22 +1226,22 @@
     <t xml:space="preserve">11.5485343933105</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6833419799805</t>
+    <t xml:space="preserve">11.6833429336548</t>
   </si>
   <si>
     <t xml:space="preserve">11.77321434021</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9080219268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.132700920105</t>
+    <t xml:space="preserve">11.9080228805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1327018737793</t>
   </si>
   <si>
     <t xml:space="preserve">11.9978942871094</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8181505203247</t>
+    <t xml:space="preserve">11.8181495666504</t>
   </si>
   <si>
     <t xml:space="preserve">11.593469619751</t>
@@ -1250,10 +1250,10 @@
     <t xml:space="preserve">12.3124437332153</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5820608139038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9415483474731</t>
+    <t xml:space="preserve">12.5820617675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9415473937988</t>
   </si>
   <si>
     <t xml:space="preserve">12.8067407608032</t>
@@ -1265,16 +1265,16 @@
     <t xml:space="preserve">13.0763559341431</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4472541809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5371246337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2675094604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4023170471191</t>
+    <t xml:space="preserve">12.4472532272339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5371236801147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2675085067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4023160934448</t>
   </si>
   <si>
     <t xml:space="preserve">12.6269969940186</t>
@@ -1283,13 +1283,13 @@
     <t xml:space="preserve">12.671932220459</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8966121673584</t>
+    <t xml:space="preserve">12.8966131210327</t>
   </si>
   <si>
     <t xml:space="preserve">11.7282772064209</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7846240997314</t>
+    <t xml:space="preserve">10.7846231460571</t>
   </si>
   <si>
     <t xml:space="preserve">10.559944152832</t>
@@ -1298,25 +1298,25 @@
     <t xml:space="preserve">8.89731407165527</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98062086105347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81885099411011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53126192092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89074802398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53782558441162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96264743804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44795513153076</t>
+    <t xml:space="preserve">7.98062133789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81885194778442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5312614440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89074897766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53782844543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.962646484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44795417785645</t>
   </si>
   <si>
     <t xml:space="preserve">8.6097240447998</t>
@@ -1325,40 +1325,40 @@
     <t xml:space="preserve">8.66364860534668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86136531829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21186542510986</t>
+    <t xml:space="preserve">8.86136436462402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21186637878418</t>
   </si>
   <si>
     <t xml:space="preserve">9.93848991394043</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80045413970947</t>
+    <t xml:space="preserve">9.80045509338379</t>
   </si>
   <si>
     <t xml:space="preserve">9.89247798919678</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66242122650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7084321975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84646606445312</t>
+    <t xml:space="preserve">9.66242027282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70843315124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84646701812744</t>
   </si>
   <si>
     <t xml:space="preserve">10.1225357055664</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75444412231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3986053466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3065824508667</t>
+    <t xml:space="preserve">9.75444316864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.398606300354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3065814971924</t>
   </si>
   <si>
     <t xml:space="preserve">10.720685005188</t>
@@ -1373,52 +1373,52 @@
     <t xml:space="preserve">10.6746740341187</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9967546463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6286640167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7666959762573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4906282424927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1347894668579</t>
+    <t xml:space="preserve">10.996753692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6286630630493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7666969299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4906272888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1347885131836</t>
   </si>
   <si>
     <t xml:space="preserve">11.3188352584839</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5028810501099</t>
+    <t xml:space="preserve">11.5028820037842</t>
   </si>
   <si>
     <t xml:space="preserve">11.1808004379272</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0427665710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2728242874146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9507436752319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0887765884399</t>
+    <t xml:space="preserve">11.0427656173706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2728233337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9507427215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0887775421143</t>
   </si>
   <si>
     <t xml:space="preserve">10.8127088546753</t>
   </si>
   <si>
-    <t xml:space="preserve">10.904730796814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4108581542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4568710327148</t>
+    <t xml:space="preserve">10.9047317504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4108591079712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4568691253662</t>
   </si>
   <si>
     <t xml:space="preserve">11.2268123626709</t>
@@ -1430,61 +1430,61 @@
     <t xml:space="preserve">11.5488929748535</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5949048995972</t>
+    <t xml:space="preserve">11.5949039459229</t>
   </si>
   <si>
     <t xml:space="preserve">11.6869277954102</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9629964828491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7789516448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0090084075928</t>
+    <t xml:space="preserve">11.9629974365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7789506912231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0090074539185</t>
   </si>
   <si>
     <t xml:space="preserve">12.1010313034058</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7329378128052</t>
+    <t xml:space="preserve">11.7329397201538</t>
   </si>
   <si>
     <t xml:space="preserve">11.8249626159668</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0550193786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8709726333618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9169855117798</t>
+    <t xml:space="preserve">12.0550203323364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8709735870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9169845581055</t>
   </si>
   <si>
     <t xml:space="preserve">11.6409158706665</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1470432281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6991815567017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7912034988403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0672731399536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8832273483276</t>
+    <t xml:space="preserve">12.1470413208008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6991806030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7912044525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0672721862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.883228302002</t>
   </si>
   <si>
     <t xml:space="preserve">12.9292392730713</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2053079605103</t>
+    <t xml:space="preserve">13.2053089141846</t>
   </si>
   <si>
     <t xml:space="preserve">13.2513189315796</t>
@@ -1505,28 +1505,28 @@
     <t xml:space="preserve">12.9752502441406</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7114334106445</t>
+    <t xml:space="preserve">13.7114343643188</t>
   </si>
   <si>
     <t xml:space="preserve">13.4353666305542</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5151357650757</t>
+    <t xml:space="preserve">12.51513671875</t>
   </si>
   <si>
     <t xml:space="preserve">12.3770999908447</t>
   </si>
   <si>
-    <t xml:space="preserve">12.837215423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7451944351196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6531686782837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3433418273926</t>
+    <t xml:space="preserve">12.8372144699097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7451934814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6531705856323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3433427810669</t>
   </si>
   <si>
     <t xml:space="preserve">13.6194114685059</t>
@@ -1535,7 +1535,7 @@
     <t xml:space="preserve">13.8494691848755</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9414911270142</t>
+    <t xml:space="preserve">13.9414920806885</t>
   </si>
   <si>
     <t xml:space="preserve">14.1715488433838</t>
@@ -1544,22 +1544,22 @@
     <t xml:space="preserve">14.3555965423584</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1255378723145</t>
+    <t xml:space="preserve">14.1255388259888</t>
   </si>
   <si>
     <t xml:space="preserve">14.4936304092407</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7236890792847</t>
+    <t xml:space="preserve">14.7236881256104</t>
   </si>
   <si>
     <t xml:space="preserve">14.6776762008667</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8157110214233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.861722946167</t>
+    <t xml:space="preserve">14.8157119750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8617219924927</t>
   </si>
   <si>
     <t xml:space="preserve">15.0457706451416</t>
@@ -1568,109 +1568,109 @@
     <t xml:space="preserve">14.5396423339844</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6316652297974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4476175308228</t>
+    <t xml:space="preserve">14.631664276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4476194381714</t>
   </si>
   <si>
     <t xml:space="preserve">14.2635726928711</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9875040054321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3095846176147</t>
+    <t xml:space="preserve">13.9875030517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3095855712891</t>
   </si>
   <si>
     <t xml:space="preserve">13.6654233932495</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8034582138062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5734004974365</t>
+    <t xml:space="preserve">13.8034572601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5733995437622</t>
   </si>
   <si>
     <t xml:space="preserve">13.7574462890625</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9537467956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0335159301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4269781112671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3801383972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.473819732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7080230712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8485469818115</t>
+    <t xml:space="preserve">14.95374584198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0335149765015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4269771575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3801374435425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4738187789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7080240249634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8485460281372</t>
   </si>
   <si>
     <t xml:space="preserve">15.03590965271</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0827493667603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8953866958618</t>
+    <t xml:space="preserve">15.0827503204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8953857421875</t>
   </si>
   <si>
     <t xml:space="preserve">14.9422273635864</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1764326095581</t>
+    <t xml:space="preserve">15.1764335632324</t>
   </si>
   <si>
     <t xml:space="preserve">15.1295900344849</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9890689849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6611824035645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3169536590576</t>
+    <t xml:space="preserve">14.989068031311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6611814498901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3169555664062</t>
   </si>
   <si>
     <t xml:space="preserve">14.7548637390137</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8017044067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2232713699341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5043163299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.06640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6916799545288</t>
+    <t xml:space="preserve">14.8017053604126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2232723236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5043172836304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0664081573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6916790008545</t>
   </si>
   <si>
     <t xml:space="preserve">15.7385215759277</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9727239608765</t>
+    <t xml:space="preserve">15.9727230072021</t>
   </si>
   <si>
     <t xml:space="preserve">15.9258861541748</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7853651046753</t>
+    <t xml:space="preserve">15.7853622436523</t>
   </si>
   <si>
     <t xml:space="preserve">16.1132488250732</t>
@@ -1682,13 +1682,13 @@
     <t xml:space="preserve">16.5348167419434</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8627014160156</t>
+    <t xml:space="preserve">16.8627033233643</t>
   </si>
   <si>
     <t xml:space="preserve">17.1437454223633</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5816555023193</t>
+    <t xml:space="preserve">16.5816593170166</t>
   </si>
   <si>
     <t xml:space="preserve">16.2069282531738</t>
@@ -1697,22 +1697,22 @@
     <t xml:space="preserve">17.2842712402344</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7995185852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4716339111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.815860748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6284980773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0969047546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5184726715088</t>
+    <t xml:space="preserve">17.7995204925537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4716320037842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8158626556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6284961700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0969066619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5184764862061</t>
   </si>
   <si>
     <t xml:space="preserve">17.612154006958</t>
@@ -1730,7 +1730,7 @@
     <t xml:space="preserve">18.9237003326416</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7668342590332</t>
+    <t xml:space="preserve">19.7668361663818</t>
   </si>
   <si>
     <t xml:space="preserve">19.5794696807861</t>
@@ -1751,10 +1751,10 @@
     <t xml:space="preserve">19.4857883453369</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8605175018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3289222717285</t>
+    <t xml:space="preserve">19.8605155944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3289241790771</t>
   </si>
   <si>
     <t xml:space="preserve">20.9846954345703</t>
@@ -1763,19 +1763,19 @@
     <t xml:space="preserve">21.265739440918</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0783786773682</t>
+    <t xml:space="preserve">21.0783767700195</t>
   </si>
   <si>
     <t xml:space="preserve">21.453104019165</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7973346710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8278312683105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1088790893555</t>
+    <t xml:space="preserve">20.7973327636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8278293609619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1088771820068</t>
   </si>
   <si>
     <t xml:space="preserve">21.7341499328613</t>
@@ -1787,16 +1787,16 @@
     <t xml:space="preserve">22.2962379455566</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4836025238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6404666900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5467853546143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2352447509766</t>
+    <t xml:space="preserve">22.4836006164551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6404685974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5467834472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2352428436279</t>
   </si>
   <si>
     <t xml:space="preserve">18.3147678375244</t>
@@ -1820,7 +1820,7 @@
     <t xml:space="preserve">21.172061920166</t>
   </si>
   <si>
-    <t xml:space="preserve">20.703649520874</t>
+    <t xml:space="preserve">20.7036514282227</t>
   </si>
   <si>
     <t xml:space="preserve">21.3594207763672</t>
@@ -1841,13 +1841,13 @@
     <t xml:space="preserve">22.3899192810059</t>
   </si>
   <si>
-    <t xml:space="preserve">19.954195022583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4226055145264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8910121917725</t>
+    <t xml:space="preserve">19.9541969299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4226036071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8910140991211</t>
   </si>
   <si>
     <t xml:space="preserve">19.3921070098877</t>
@@ -1862,13 +1862,13 @@
     <t xml:space="preserve">16.9563846588135</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6589984893799</t>
+    <t xml:space="preserve">17.6589965820312</t>
   </si>
   <si>
     <t xml:space="preserve">17.7526779174805</t>
   </si>
   <si>
-    <t xml:space="preserve">17.377950668335</t>
+    <t xml:space="preserve">17.3779525756836</t>
   </si>
   <si>
     <t xml:space="preserve">17.8931999206543</t>
@@ -1880,10 +1880,10 @@
     <t xml:space="preserve">18.2679271697998</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8768577575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6426525115967</t>
+    <t xml:space="preserve">18.8768558502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6426544189453</t>
   </si>
   <si>
     <t xml:space="preserve">18.3241348266602</t>
@@ -1892,19 +1892,19 @@
     <t xml:space="preserve">18.2117195129395</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2304553985596</t>
+    <t xml:space="preserve">18.2304534912109</t>
   </si>
   <si>
     <t xml:space="preserve">18.4552898406982</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9494113922119</t>
+    <t xml:space="preserve">17.9494094848633</t>
   </si>
   <si>
     <t xml:space="preserve">18.1180362701416</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9705390930176</t>
+    <t xml:space="preserve">18.9705410003662</t>
   </si>
   <si>
     <t xml:space="preserve">20.2820816040039</t>
@@ -1913,19 +1913,19 @@
     <t xml:space="preserve">20.0947189331055</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1884002685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1415615081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4927616119385</t>
+    <t xml:space="preserve">20.1884021759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1415596008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4927635192871</t>
   </si>
   <si>
     <t xml:space="preserve">17.5559463500977</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1999588012695</t>
+    <t xml:space="preserve">17.1999549865723</t>
   </si>
   <si>
     <t xml:space="preserve">16.8847980499268</t>
@@ -1937,13 +1937,13 @@
     <t xml:space="preserve">18.0308246612549</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9285449981689</t>
+    <t xml:space="preserve">18.9285469055176</t>
   </si>
   <si>
     <t xml:space="preserve">18.4319343566895</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6038379669189</t>
+    <t xml:space="preserve">18.6038398742676</t>
   </si>
   <si>
     <t xml:space="preserve">19.1004505157471</t>
@@ -1952,19 +1952,19 @@
     <t xml:space="preserve">18.9858474731445</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1482009887695</t>
+    <t xml:space="preserve">19.1481990814209</t>
   </si>
   <si>
     <t xml:space="preserve">18.90944480896</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9476470947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0077228546143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0554714202881</t>
+    <t xml:space="preserve">18.9476490020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0077247619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0554733276367</t>
   </si>
   <si>
     <t xml:space="preserve">20.5329856872559</t>
@@ -1979,7 +1979,7 @@
     <t xml:space="preserve">20.4374828338623</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0104942321777</t>
+    <t xml:space="preserve">21.0104961395264</t>
   </si>
   <si>
     <t xml:space="preserve">21.4880084991455</t>
@@ -2003,7 +2003,7 @@
     <t xml:space="preserve">18.813943862915</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6993408203125</t>
+    <t xml:space="preserve">18.6993389129639</t>
   </si>
   <si>
     <t xml:space="preserve">19.3869571685791</t>
@@ -2018,13 +2018,13 @@
     <t xml:space="preserve">18.240930557251</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7757415771484</t>
+    <t xml:space="preserve">18.7757434844971</t>
   </si>
   <si>
     <t xml:space="preserve">19.9599704742432</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4852333068848</t>
+    <t xml:space="preserve">20.4852352142334</t>
   </si>
   <si>
     <t xml:space="preserve">21.1059970855713</t>
@@ -2033,13 +2033,13 @@
     <t xml:space="preserve">21.8700160980225</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3925037384033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1537494659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7745113372803</t>
+    <t xml:space="preserve">21.392505645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1537475585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7745132446289</t>
   </si>
   <si>
     <t xml:space="preserve">21.6790103912354</t>
@@ -2048,22 +2048,22 @@
     <t xml:space="preserve">21.9177684783936</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2970008850098</t>
+    <t xml:space="preserve">21.2970027923584</t>
   </si>
   <si>
     <t xml:space="preserve">21.7267627716064</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5835113525391</t>
+    <t xml:space="preserve">21.5835094451904</t>
   </si>
   <si>
     <t xml:space="preserve">20.5807342529297</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1032238006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6257133483887</t>
+    <t xml:space="preserve">20.1032218933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.62571144104</t>
   </si>
   <si>
     <t xml:space="preserve">19.8644676208496</t>
@@ -2075,7 +2075,7 @@
     <t xml:space="preserve">22.9205417633057</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4430294036865</t>
+    <t xml:space="preserve">22.4430313110352</t>
   </si>
   <si>
     <t xml:space="preserve">22.1565227508545</t>
@@ -2084,7 +2084,7 @@
     <t xml:space="preserve">22.0610198974609</t>
   </si>
   <si>
-    <t xml:space="preserve">22.347526550293</t>
+    <t xml:space="preserve">22.3475284576416</t>
   </si>
   <si>
     <t xml:space="preserve">21.0582466125488</t>
@@ -2093,7 +2093,7 @@
     <t xml:space="preserve">20.3897304534912</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2942295074463</t>
+    <t xml:space="preserve">20.2942276000977</t>
   </si>
   <si>
     <t xml:space="preserve">20.1987247467041</t>
@@ -2105,7 +2105,7 @@
     <t xml:space="preserve">20.8672428131104</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0499248504639</t>
+    <t xml:space="preserve">18.0499267578125</t>
   </si>
   <si>
     <t xml:space="preserve">18.833044052124</t>
@@ -2141,16 +2141,16 @@
     <t xml:space="preserve">22.7295341491699</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5862827301025</t>
+    <t xml:space="preserve">22.5862808227539</t>
   </si>
   <si>
     <t xml:space="preserve">22.8727912902832</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5385341644287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6817836761475</t>
+    <t xml:space="preserve">22.5385322570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6817855834961</t>
   </si>
   <si>
     <t xml:space="preserve">23.0160427093506</t>
@@ -2159,13 +2159,13 @@
     <t xml:space="preserve">23.3025493621826</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4485778808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7323093414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9710655212402</t>
+    <t xml:space="preserve">24.4485759735107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7323112487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9710636138916</t>
   </si>
   <si>
     <t xml:space="preserve">24.2098217010498</t>
@@ -2174,19 +2174,19 @@
     <t xml:space="preserve">24.0665683746338</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1143207550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4008235931396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3080959320068</t>
+    <t xml:space="preserve">24.1143188476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4008255004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3080978393555</t>
   </si>
   <si>
     <t xml:space="preserve">23.7800598144531</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9233131408691</t>
+    <t xml:space="preserve">23.9233150482178</t>
   </si>
   <si>
     <t xml:space="preserve">25.0693416595459</t>
@@ -2201,13 +2201,13 @@
     <t xml:space="preserve">25.3558464050293</t>
   </si>
   <si>
-    <t xml:space="preserve">25.403600692749</t>
+    <t xml:space="preserve">25.4035987854004</t>
   </si>
   <si>
     <t xml:space="preserve">25.8333587646484</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8838844299316</t>
+    <t xml:space="preserve">26.883882522583</t>
   </si>
   <si>
     <t xml:space="preserve">26.7883815765381</t>
@@ -2222,19 +2222,19 @@
     <t xml:space="preserve">24.8305854797363</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2603454589844</t>
+    <t xml:space="preserve">25.260347366333</t>
   </si>
   <si>
     <t xml:space="preserve">25.7378578186035</t>
   </si>
   <si>
-    <t xml:space="preserve">25.785608291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.072114944458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2631187438965</t>
+    <t xml:space="preserve">25.7856101989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0721130371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2631206512451</t>
   </si>
   <si>
     <t xml:space="preserve">25.4513492584229</t>
@@ -2252,7 +2252,7 @@
     <t xml:space="preserve">25.5468521118164</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4541263580322</t>
+    <t xml:space="preserve">26.4541244506836</t>
   </si>
   <si>
     <t xml:space="preserve">26.7406311035156</t>
@@ -2261,7 +2261,7 @@
     <t xml:space="preserve">27.0748901367188</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1703910827637</t>
+    <t xml:space="preserve">27.1703929901123</t>
   </si>
   <si>
     <t xml:space="preserve">28.6506767272949</t>
@@ -2288,7 +2288,7 @@
     <t xml:space="preserve">28.5074214935303</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3191928863525</t>
+    <t xml:space="preserve">29.3191909790039</t>
   </si>
   <si>
     <t xml:space="preserve">28.9371814727783</t>
@@ -2300,28 +2300,28 @@
     <t xml:space="preserve">29.223690032959</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1281852722168</t>
+    <t xml:space="preserve">29.1281871795654</t>
   </si>
   <si>
     <t xml:space="preserve">29.1759376525879</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0804386138916</t>
+    <t xml:space="preserve">29.080436706543</t>
   </si>
   <si>
     <t xml:space="preserve">28.6984272003174</t>
   </si>
   <si>
-    <t xml:space="preserve">28.984935760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3641700744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8866577148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2714385986328</t>
+    <t xml:space="preserve">28.9849338531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3641681671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8866596221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2714405059814</t>
   </si>
   <si>
     <t xml:space="preserve">27.8389053344727</t>
@@ -2339,19 +2339,19 @@
     <t xml:space="preserve">29.366943359375</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4146938323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0354614257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.748950958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7039756774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2742156982422</t>
+    <t xml:space="preserve">29.4146919250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0354595184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7489490509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7039737701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2742137908936</t>
   </si>
   <si>
     <t xml:space="preserve">29.7012023925781</t>
@@ -2360,10 +2360,10 @@
     <t xml:space="preserve">29.5579471588135</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7967014312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2209148406982</t>
+    <t xml:space="preserve">29.796703338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2209167480469</t>
   </si>
   <si>
     <t xml:space="preserve">28.3164176940918</t>
@@ -2375,10 +2375,10 @@
     <t xml:space="preserve">26.9480724334717</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5770225524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5930156707764</t>
+    <t xml:space="preserve">27.5770206451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.593017578125</t>
   </si>
   <si>
     <t xml:space="preserve">28.0124492645264</t>
@@ -2396,7 +2396,7 @@
     <t xml:space="preserve">28.0608291625977</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3994960784912</t>
+    <t xml:space="preserve">28.3994941711426</t>
   </si>
   <si>
     <t xml:space="preserve">28.7381591796875</t>
@@ -2405,7 +2405,7 @@
     <t xml:space="preserve">29.1252059936523</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9800643920898</t>
+    <t xml:space="preserve">28.9800624847412</t>
   </si>
   <si>
     <t xml:space="preserve">27.7705459594727</t>
@@ -2447,19 +2447,19 @@
     <t xml:space="preserve">29.2219676971436</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0284423828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2543525695801</t>
+    <t xml:space="preserve">29.0284442901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2543544769287</t>
   </si>
   <si>
     <t xml:space="preserve">29.705774307251</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0444393157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.996057510376</t>
+    <t xml:space="preserve">30.0444374084473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9960594177246</t>
   </si>
   <si>
     <t xml:space="preserve">28.8349208831787</t>
@@ -2474,7 +2474,7 @@
     <t xml:space="preserve">28.2059707641602</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4962558746338</t>
+    <t xml:space="preserve">28.4962577819824</t>
   </si>
   <si>
     <t xml:space="preserve">27.0932140350342</t>
@@ -2483,7 +2483,7 @@
     <t xml:space="preserve">26.8513107299805</t>
   </si>
   <si>
-    <t xml:space="preserve">26.077220916748</t>
+    <t xml:space="preserve">26.0772190093994</t>
   </si>
   <si>
     <t xml:space="preserve">26.8996906280518</t>
@@ -2507,22 +2507,22 @@
     <t xml:space="preserve">25.3031272888184</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2547473907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1579856872559</t>
+    <t xml:space="preserve">25.2547454833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1579837799072</t>
   </si>
   <si>
     <t xml:space="preserve">24.9160804748535</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4966487884521</t>
+    <t xml:space="preserve">25.4966506958008</t>
   </si>
   <si>
     <t xml:space="preserve">25.3515071868896</t>
   </si>
   <si>
-    <t xml:space="preserve">25.061222076416</t>
+    <t xml:space="preserve">25.0612239837646</t>
   </si>
   <si>
     <t xml:space="preserve">24.7225570678711</t>
@@ -2531,7 +2531,7 @@
     <t xml:space="preserve">24.4806537628174</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6098022460938</t>
+    <t xml:space="preserve">23.6098003387451</t>
   </si>
   <si>
     <t xml:space="preserve">23.0292301177979</t>
@@ -2540,7 +2540,7 @@
     <t xml:space="preserve">22.9324722290039</t>
   </si>
   <si>
-    <t xml:space="preserve">23.174373626709</t>
+    <t xml:space="preserve">23.1743755340576</t>
   </si>
   <si>
     <t xml:space="preserve">22.5938053131104</t>
@@ -2552,7 +2552,7 @@
     <t xml:space="preserve">21.6745719909668</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9164733886719</t>
+    <t xml:space="preserve">21.9164752960205</t>
   </si>
   <si>
     <t xml:space="preserve">21.5294284820557</t>
@@ -2564,16 +2564,16 @@
     <t xml:space="preserve">21.0940017700195</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4650535583496</t>
+    <t xml:space="preserve">20.465051651001</t>
   </si>
   <si>
     <t xml:space="preserve">20.2231483459473</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4166717529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9004802703857</t>
+    <t xml:space="preserve">20.4166736602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9004783630371</t>
   </si>
   <si>
     <t xml:space="preserve">20.8037185668945</t>
@@ -2582,22 +2582,22 @@
     <t xml:space="preserve">20.6101951599121</t>
   </si>
   <si>
-    <t xml:space="preserve">20.658576965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7069549560547</t>
+    <t xml:space="preserve">20.6585750579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7069568634033</t>
   </si>
   <si>
     <t xml:space="preserve">20.7553386688232</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3359050750732</t>
+    <t xml:space="preserve">21.3359069824219</t>
   </si>
   <si>
     <t xml:space="preserve">21.0456218719482</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4490566253662</t>
+    <t xml:space="preserve">19.4490585327148</t>
   </si>
   <si>
     <t xml:space="preserve">19.8361034393311</t>
@@ -2606,7 +2606,7 @@
     <t xml:space="preserve">19.2361812591553</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8878421783447</t>
+    <t xml:space="preserve">18.8878402709961</t>
   </si>
   <si>
     <t xml:space="preserve">18.6362609863281</t>
@@ -2630,13 +2630,13 @@
     <t xml:space="preserve">17.049373626709</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0300216674805</t>
+    <t xml:space="preserve">17.0300197601318</t>
   </si>
   <si>
     <t xml:space="preserve">16.8752021789551</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3266258239746</t>
+    <t xml:space="preserve">18.326623916626</t>
   </si>
   <si>
     <t xml:space="preserve">18.7717266082764</t>
@@ -2648,13 +2648,13 @@
     <t xml:space="preserve">18.5782051086426</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4233875274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1331005096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4974384307861</t>
+    <t xml:space="preserve">18.4233856201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1331024169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4974365234375</t>
   </si>
   <si>
     <t xml:space="preserve">20.1263866424561</t>
@@ -2663,7 +2663,7 @@
     <t xml:space="preserve">19.9328651428223</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3199119567871</t>
+    <t xml:space="preserve">20.3199100494385</t>
   </si>
   <si>
     <t xml:space="preserve">19.6425800323486</t>
@@ -2678,10 +2678,10 @@
     <t xml:space="preserve">19.1781253814697</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0233058929443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1974773406982</t>
+    <t xml:space="preserve">19.023307800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1974792480469</t>
   </si>
   <si>
     <t xml:space="preserve">18.9071941375732</t>
@@ -2690,7 +2690,7 @@
     <t xml:space="preserve">19.8844833374023</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4006767272949</t>
+    <t xml:space="preserve">19.4006748199463</t>
   </si>
   <si>
     <t xml:space="preserve">19.7877235412598</t>
@@ -2708,7 +2708,7 @@
     <t xml:space="preserve">22.0132369995117</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8357086181641</t>
+    <t xml:space="preserve">22.8357105255127</t>
   </si>
   <si>
     <t xml:space="preserve">22.1583786010742</t>
@@ -2720,19 +2720,19 @@
     <t xml:space="preserve">22.3519020080566</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7229537963867</t>
+    <t xml:space="preserve">21.7229518890381</t>
   </si>
   <si>
     <t xml:space="preserve">21.5778102874756</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4326686859131</t>
+    <t xml:space="preserve">21.4326667785645</t>
   </si>
   <si>
     <t xml:space="preserve">22.061616897583</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4970455169678</t>
+    <t xml:space="preserve">22.4970436096191</t>
   </si>
   <si>
     <t xml:space="preserve">22.2551403045654</t>
@@ -2744,7 +2744,7 @@
     <t xml:space="preserve">21.6261901855469</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7713317871094</t>
+    <t xml:space="preserve">21.771333694458</t>
   </si>
   <si>
     <t xml:space="preserve">22.3035202026367</t>
@@ -2753,10 +2753,10 @@
     <t xml:space="preserve">22.8840885162354</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7873287200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9648571014404</t>
+    <t xml:space="preserve">22.7873268127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9648551940918</t>
   </si>
   <si>
     <t xml:space="preserve">20.948860168457</t>
@@ -2771,7 +2771,7 @@
     <t xml:space="preserve">20.1747703552246</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5134334564209</t>
+    <t xml:space="preserve">20.5134353637695</t>
   </si>
   <si>
     <t xml:space="preserve">20.0296268463135</t>
@@ -2780,13 +2780,13 @@
     <t xml:space="preserve">22.9808521270752</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1259937286377</t>
+    <t xml:space="preserve">23.1259918212891</t>
   </si>
   <si>
     <t xml:space="preserve">21.3842868804932</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8520965576172</t>
+    <t xml:space="preserve">20.8520984649658</t>
   </si>
   <si>
     <t xml:space="preserve">20.5618133544922</t>
@@ -3372,6 +3372,9 @@
   </si>
   <si>
     <t xml:space="preserve">36.6500015258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.25</t>
   </si>
 </sst>
 </file>
@@ -13894,7 +13897,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G392" t="s">
-        <v>203</v>
+        <v>164</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -13920,7 +13923,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G393" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -13946,7 +13949,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G394" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -13972,7 +13975,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G395" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -13998,7 +14001,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G396" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -14024,7 +14027,7 @@
         <v>13</v>
       </c>
       <c r="G397" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -14050,7 +14053,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G398" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -14076,7 +14079,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G399" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -14102,7 +14105,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G400" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -14128,7 +14131,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G401" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -14154,7 +14157,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G402" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -14180,7 +14183,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G403" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -14206,7 +14209,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G404" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -14232,7 +14235,7 @@
         <v>13</v>
       </c>
       <c r="G405" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -14258,7 +14261,7 @@
         <v>13</v>
       </c>
       <c r="G406" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -14284,7 +14287,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G407" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -14310,7 +14313,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G408" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -14336,7 +14339,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G409" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -14362,7 +14365,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G410" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -14388,7 +14391,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G411" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -14414,7 +14417,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G412" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -14440,7 +14443,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G413" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -14466,7 +14469,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G414" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -14492,7 +14495,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G415" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -14518,7 +14521,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G416" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -14544,7 +14547,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G417" t="s">
-        <v>203</v>
+        <v>164</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -14570,7 +14573,7 @@
         <v>13.25</v>
       </c>
       <c r="G418" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -14596,7 +14599,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G419" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -14622,7 +14625,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G420" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -14648,7 +14651,7 @@
         <v>13</v>
       </c>
       <c r="G421" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -14674,7 +14677,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G422" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -14700,7 +14703,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G423" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -14726,7 +14729,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G424" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -14752,7 +14755,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G425" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -14778,7 +14781,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G426" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -14804,7 +14807,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G427" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -14830,7 +14833,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G428" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -14856,7 +14859,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G429" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -14882,7 +14885,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G430" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -14908,7 +14911,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G431" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -14934,7 +14937,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G432" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -14960,7 +14963,7 @@
         <v>13.1700000762939</v>
       </c>
       <c r="G433" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -14986,7 +14989,7 @@
         <v>13</v>
       </c>
       <c r="G434" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -15012,7 +15015,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G435" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -15038,7 +15041,7 @@
         <v>12.7299995422363</v>
       </c>
       <c r="G436" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -15064,7 +15067,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G437" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -15090,7 +15093,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G438" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -15116,7 +15119,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G439" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -15142,7 +15145,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G440" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -15168,7 +15171,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G441" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -15194,7 +15197,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G442" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -15220,7 +15223,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G443" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -15246,7 +15249,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G444" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -15272,7 +15275,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G445" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -15298,7 +15301,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G446" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -15324,7 +15327,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G447" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -15350,7 +15353,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G448" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -15376,7 +15379,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G449" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -15402,7 +15405,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G450" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -15428,7 +15431,7 @@
         <v>11.25</v>
       </c>
       <c r="G451" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -15454,7 +15457,7 @@
         <v>11.1099996566772</v>
       </c>
       <c r="G452" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -15480,7 +15483,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G453" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -15506,7 +15509,7 @@
         <v>11.25</v>
       </c>
       <c r="G454" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -15532,7 +15535,7 @@
         <v>10.9099998474121</v>
       </c>
       <c r="G455" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -15558,7 +15561,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G456" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -15584,7 +15587,7 @@
         <v>10.75</v>
       </c>
       <c r="G457" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -15610,7 +15613,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G458" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -15636,7 +15639,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G459" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -15662,7 +15665,7 @@
         <v>10.9300003051758</v>
       </c>
       <c r="G460" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -15688,7 +15691,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G461" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -15714,7 +15717,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G462" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -15740,7 +15743,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G463" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -15766,7 +15769,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G464" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -15792,7 +15795,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G465" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -15818,7 +15821,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G466" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -15844,7 +15847,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G467" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -15870,7 +15873,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G468" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -15896,7 +15899,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G469" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -15922,7 +15925,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G470" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -15948,7 +15951,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G471" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -15974,7 +15977,7 @@
         <v>11.2299995422363</v>
       </c>
       <c r="G472" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -16000,7 +16003,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G473" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -16026,7 +16029,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G474" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -16052,7 +16055,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G475" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -16078,7 +16081,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G476" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -16104,7 +16107,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G477" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -16130,7 +16133,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G478" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -16156,7 +16159,7 @@
         <v>10.75</v>
       </c>
       <c r="G479" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -16182,7 +16185,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G480" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -16208,7 +16211,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G481" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -16234,7 +16237,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G482" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -16260,7 +16263,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G483" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -16286,7 +16289,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G484" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -16312,7 +16315,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G485" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -16338,7 +16341,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G486" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -16364,7 +16367,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G487" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -16390,7 +16393,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G488" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -16416,7 +16419,7 @@
         <v>11.5</v>
       </c>
       <c r="G489" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -16442,7 +16445,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G490" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -16468,7 +16471,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G491" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -16494,7 +16497,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G492" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -16520,7 +16523,7 @@
         <v>11.0699996948242</v>
       </c>
       <c r="G493" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -16546,7 +16549,7 @@
         <v>11.2299995422363</v>
       </c>
       <c r="G494" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -16572,7 +16575,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G495" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -16598,7 +16601,7 @@
         <v>10.9300003051758</v>
       </c>
       <c r="G496" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -16624,7 +16627,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G497" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -16650,7 +16653,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G498" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -16676,7 +16679,7 @@
         <v>11.25</v>
       </c>
       <c r="G499" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -16702,7 +16705,7 @@
         <v>11.1300001144409</v>
       </c>
       <c r="G500" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -16728,7 +16731,7 @@
         <v>11</v>
       </c>
       <c r="G501" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -16754,7 +16757,7 @@
         <v>11.0699996948242</v>
       </c>
       <c r="G502" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -16780,7 +16783,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G503" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -16806,7 +16809,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G504" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -16832,7 +16835,7 @@
         <v>11</v>
       </c>
       <c r="G505" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -16858,7 +16861,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G506" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -16884,7 +16887,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G507" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -16910,7 +16913,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G508" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -16936,7 +16939,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G509" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -16962,7 +16965,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G510" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -16988,7 +16991,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G511" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -17014,7 +17017,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G512" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -17040,7 +17043,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G513" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -17066,7 +17069,7 @@
         <v>10.75</v>
       </c>
       <c r="G514" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -17092,7 +17095,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G515" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -17118,7 +17121,7 @@
         <v>10.75</v>
       </c>
       <c r="G516" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -17144,7 +17147,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G517" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -17170,7 +17173,7 @@
         <v>11</v>
       </c>
       <c r="G518" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -17196,7 +17199,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G519" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -17222,7 +17225,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G520" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -17248,7 +17251,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G521" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -17274,7 +17277,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G522" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -17300,7 +17303,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G523" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -17326,7 +17329,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G524" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -17352,7 +17355,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G525" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -17378,7 +17381,7 @@
         <v>11.25</v>
       </c>
       <c r="G526" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -17404,7 +17407,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G527" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -17430,7 +17433,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G528" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -17456,7 +17459,7 @@
         <v>11.25</v>
       </c>
       <c r="G529" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -17482,7 +17485,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G530" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -17508,7 +17511,7 @@
         <v>11.5</v>
       </c>
       <c r="G531" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -17534,7 +17537,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G532" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -17560,7 +17563,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G533" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -17586,7 +17589,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G534" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -17612,7 +17615,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G535" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -17638,7 +17641,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G536" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -17664,7 +17667,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G537" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -17690,7 +17693,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G538" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -17716,7 +17719,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G539" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -17742,7 +17745,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G540" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -17768,7 +17771,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G541" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -17794,7 +17797,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G542" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -17820,7 +17823,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G543" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -17846,7 +17849,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G544" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -17872,7 +17875,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G545" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -17898,7 +17901,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G546" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -17924,7 +17927,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G547" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -17950,7 +17953,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G548" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -17976,7 +17979,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G549" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -18002,7 +18005,7 @@
         <v>10.5</v>
       </c>
       <c r="G550" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -18028,7 +18031,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G551" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -18054,7 +18057,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G552" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -18080,7 +18083,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G553" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -18106,7 +18109,7 @@
         <v>10.25</v>
       </c>
       <c r="G554" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -18132,7 +18135,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G555" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -18158,7 +18161,7 @@
         <v>10.25</v>
       </c>
       <c r="G556" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -18184,7 +18187,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G557" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -18210,7 +18213,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G558" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -18236,7 +18239,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G559" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -18262,7 +18265,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G560" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -18288,7 +18291,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G561" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -18314,7 +18317,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G562" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -18340,7 +18343,7 @@
         <v>10.5</v>
       </c>
       <c r="G563" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -18366,7 +18369,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G564" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -18392,7 +18395,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G565" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -18418,7 +18421,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G566" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -18444,7 +18447,7 @@
         <v>10.25</v>
       </c>
       <c r="G567" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -18470,7 +18473,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G568" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -18496,7 +18499,7 @@
         <v>10.25</v>
       </c>
       <c r="G569" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -18522,7 +18525,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G570" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -18548,7 +18551,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G571" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -18574,7 +18577,7 @@
         <v>10</v>
       </c>
       <c r="G572" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -18600,7 +18603,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G573" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -18626,7 +18629,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G574" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -18652,7 +18655,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G575" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -18678,7 +18681,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G576" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -18704,7 +18707,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G577" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -18730,7 +18733,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G578" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -18756,7 +18759,7 @@
         <v>10</v>
       </c>
       <c r="G579" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -18782,7 +18785,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G580" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -18808,7 +18811,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G581" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -18834,7 +18837,7 @@
         <v>10.25</v>
       </c>
       <c r="G582" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -18860,7 +18863,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G583" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -18886,7 +18889,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G584" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -18912,7 +18915,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G585" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -18938,7 +18941,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G586" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -18964,7 +18967,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G587" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -18990,7 +18993,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G588" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -19016,7 +19019,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G589" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -19042,7 +19045,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G590" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -19068,7 +19071,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G591" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -19094,7 +19097,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G592" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -19120,7 +19123,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G593" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -19146,7 +19149,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G594" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -19172,7 +19175,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G595" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -19198,7 +19201,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G596" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -19224,7 +19227,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G597" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -19250,7 +19253,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G598" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -19276,7 +19279,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G599" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -19302,7 +19305,7 @@
         <v>10.25</v>
       </c>
       <c r="G600" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -19328,7 +19331,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G601" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -19354,7 +19357,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G602" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -19380,7 +19383,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G603" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -19406,7 +19409,7 @@
         <v>10.25</v>
       </c>
       <c r="G604" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -19432,7 +19435,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G605" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -19458,7 +19461,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G606" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -19484,7 +19487,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G607" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -19510,7 +19513,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G608" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19536,7 +19539,7 @@
         <v>10.25</v>
       </c>
       <c r="G609" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19562,7 +19565,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G610" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19588,7 +19591,7 @@
         <v>10.25</v>
       </c>
       <c r="G611" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19614,7 +19617,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G612" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19640,7 +19643,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G613" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19666,7 +19669,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G614" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19692,7 +19695,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G615" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19718,7 +19721,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G616" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19744,7 +19747,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G617" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19770,7 +19773,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G618" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19796,7 +19799,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G619" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19822,7 +19825,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G620" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19848,7 +19851,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G621" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19874,7 +19877,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G622" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19900,7 +19903,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G623" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19926,7 +19929,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G624" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19952,7 +19955,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G625" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19978,7 +19981,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G626" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -20004,7 +20007,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G627" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -20030,7 +20033,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G628" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -20056,7 +20059,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G629" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -20082,7 +20085,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G630" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -20108,7 +20111,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G631" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -20134,7 +20137,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G632" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -20160,7 +20163,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G633" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -20186,7 +20189,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G634" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -20212,7 +20215,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G635" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -20238,7 +20241,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G636" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -20264,7 +20267,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G637" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -20290,7 +20293,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G638" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -20316,7 +20319,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G639" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -20342,7 +20345,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G640" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -20368,7 +20371,7 @@
         <v>10</v>
       </c>
       <c r="G641" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -20394,7 +20397,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G642" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -20420,7 +20423,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G643" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -20446,7 +20449,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G644" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -20472,7 +20475,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G645" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -20498,7 +20501,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G646" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -20524,7 +20527,7 @@
         <v>10</v>
       </c>
       <c r="G647" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -20550,7 +20553,7 @@
         <v>10</v>
       </c>
       <c r="G648" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -20576,7 +20579,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G649" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -20602,7 +20605,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G650" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -20628,7 +20631,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G651" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -20654,7 +20657,7 @@
         <v>10</v>
       </c>
       <c r="G652" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -20680,7 +20683,7 @@
         <v>10</v>
       </c>
       <c r="G653" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -20706,7 +20709,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G654" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -20732,7 +20735,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G655" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -20758,7 +20761,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G656" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -20784,7 +20787,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G657" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -20810,7 +20813,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G658" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -20836,7 +20839,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G659" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -20862,7 +20865,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G660" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -20888,7 +20891,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G661" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -20914,7 +20917,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G662" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -20940,7 +20943,7 @@
         <v>10</v>
       </c>
       <c r="G663" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -20966,7 +20969,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G664" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -20992,7 +20995,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G665" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -21018,7 +21021,7 @@
         <v>10.25</v>
       </c>
       <c r="G666" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -21044,7 +21047,7 @@
         <v>10</v>
       </c>
       <c r="G667" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -21070,7 +21073,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G668" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -21096,7 +21099,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G669" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -21122,7 +21125,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G670" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -21148,7 +21151,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G671" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -21174,7 +21177,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G672" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -21200,7 +21203,7 @@
         <v>10</v>
       </c>
       <c r="G673" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -21226,7 +21229,7 @@
         <v>10</v>
       </c>
       <c r="G674" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -21252,7 +21255,7 @@
         <v>10</v>
       </c>
       <c r="G675" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -21278,7 +21281,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G676" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -21304,7 +21307,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G677" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -21330,7 +21333,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G678" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -21356,7 +21359,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G679" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -21382,7 +21385,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G680" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -21408,7 +21411,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G681" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -21434,7 +21437,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G682" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -21460,7 +21463,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G683" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -21486,7 +21489,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G684" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -21512,7 +21515,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G685" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -21538,7 +21541,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G686" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -21564,7 +21567,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G687" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -21590,7 +21593,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G688" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -21616,7 +21619,7 @@
         <v>10</v>
       </c>
       <c r="G689" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -21642,7 +21645,7 @@
         <v>10</v>
       </c>
       <c r="G690" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -21668,7 +21671,7 @@
         <v>10</v>
       </c>
       <c r="G691" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -21694,7 +21697,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G692" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -21720,7 +21723,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G693" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -21746,7 +21749,7 @@
         <v>10</v>
       </c>
       <c r="G694" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -21772,7 +21775,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G695" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -21798,7 +21801,7 @@
         <v>10</v>
       </c>
       <c r="G696" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -21824,7 +21827,7 @@
         <v>10</v>
       </c>
       <c r="G697" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -21850,7 +21853,7 @@
         <v>10.5</v>
       </c>
       <c r="G698" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -21876,7 +21879,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G699" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -21902,7 +21905,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G700" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -21928,7 +21931,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G701" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -21954,7 +21957,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G702" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -21980,7 +21983,7 @@
         <v>10.25</v>
       </c>
       <c r="G703" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -22006,7 +22009,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G704" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -22032,7 +22035,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G705" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -22058,7 +22061,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G706" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -22084,7 +22087,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G707" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -22110,7 +22113,7 @@
         <v>10</v>
       </c>
       <c r="G708" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -22136,7 +22139,7 @@
         <v>10</v>
       </c>
       <c r="G709" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -22162,7 +22165,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G710" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -22188,7 +22191,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G711" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -22214,7 +22217,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G712" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -22240,7 +22243,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G713" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -22266,7 +22269,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G714" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -22292,7 +22295,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G715" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -22318,7 +22321,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G716" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -22344,7 +22347,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G717" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -22370,7 +22373,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G718" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -22396,7 +22399,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G719" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -22422,7 +22425,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G720" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -22448,7 +22451,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G721" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -22474,7 +22477,7 @@
         <v>10</v>
       </c>
       <c r="G722" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -22500,7 +22503,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G723" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -22526,7 +22529,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G724" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -22552,7 +22555,7 @@
         <v>10</v>
       </c>
       <c r="G725" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -22578,7 +22581,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G726" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -22604,7 +22607,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G727" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -22630,7 +22633,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G728" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -22656,7 +22659,7 @@
         <v>10</v>
       </c>
       <c r="G729" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -22682,7 +22685,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G730" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -22708,7 +22711,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G731" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -22734,7 +22737,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G732" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -22760,7 +22763,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G733" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -22786,7 +22789,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G734" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -22812,7 +22815,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G735" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -22838,7 +22841,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G736" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -22864,7 +22867,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G737" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -22890,7 +22893,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G738" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -22916,7 +22919,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G739" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -22942,7 +22945,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G740" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -22968,7 +22971,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G741" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -22994,7 +22997,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G742" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -23020,7 +23023,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G743" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -23046,7 +23049,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G744" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -23072,7 +23075,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G745" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -23098,7 +23101,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G746" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -23124,7 +23127,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G747" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -23150,7 +23153,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G748" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -23176,7 +23179,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G749" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -23202,7 +23205,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G750" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -23228,7 +23231,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G751" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -23254,7 +23257,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G752" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -23280,7 +23283,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G753" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -23306,7 +23309,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G754" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -23332,7 +23335,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G755" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -23358,7 +23361,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G756" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -23384,7 +23387,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G757" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -23410,7 +23413,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G758" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -23436,7 +23439,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G759" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -23462,7 +23465,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G760" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -23488,7 +23491,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G761" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -23514,7 +23517,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G762" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -23540,7 +23543,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G763" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -23566,7 +23569,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G764" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -23592,7 +23595,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G765" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -23618,7 +23621,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G766" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -23644,7 +23647,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G767" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -23670,7 +23673,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G768" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -23696,7 +23699,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G769" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -23722,7 +23725,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G770" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -23748,7 +23751,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G771" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -23774,7 +23777,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G772" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -23800,7 +23803,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G773" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -23826,7 +23829,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G774" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -23852,7 +23855,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G775" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -23878,7 +23881,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G776" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -23904,7 +23907,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G777" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -23930,7 +23933,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G778" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -23956,7 +23959,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G779" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -23982,7 +23985,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G780" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -24008,7 +24011,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G781" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -24034,7 +24037,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G782" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -24060,7 +24063,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G783" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -24086,7 +24089,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G784" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -24112,7 +24115,7 @@
         <v>10</v>
       </c>
       <c r="G785" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -24138,7 +24141,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G786" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -24164,7 +24167,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G787" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -24190,7 +24193,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G788" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -24216,7 +24219,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G789" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -24242,7 +24245,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G790" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -24268,7 +24271,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G791" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -24294,7 +24297,7 @@
         <v>10</v>
       </c>
       <c r="G792" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -24320,7 +24323,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G793" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -24346,7 +24349,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G794" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -24372,7 +24375,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G795" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -24398,7 +24401,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G796" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -24424,7 +24427,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G797" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -24450,7 +24453,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G798" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -24476,7 +24479,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G799" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -24502,7 +24505,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G800" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -24528,7 +24531,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G801" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -24554,7 +24557,7 @@
         <v>10.25</v>
       </c>
       <c r="G802" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -24580,7 +24583,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G803" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -24606,7 +24609,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G804" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -24632,7 +24635,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G805" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -24658,7 +24661,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G806" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -24684,7 +24687,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G807" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -24710,7 +24713,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G808" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -24736,7 +24739,7 @@
         <v>10.5</v>
       </c>
       <c r="G809" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -24762,7 +24765,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G810" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -24788,7 +24791,7 @@
         <v>10</v>
       </c>
       <c r="G811" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -24814,7 +24817,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G812" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -24840,7 +24843,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G813" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -24866,7 +24869,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G814" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -24892,7 +24895,7 @@
         <v>10.5</v>
       </c>
       <c r="G815" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -24918,7 +24921,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G816" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -24944,7 +24947,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G817" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -24970,7 +24973,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G818" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -24996,7 +24999,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G819" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -25022,7 +25025,7 @@
         <v>11.25</v>
       </c>
       <c r="G820" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -25048,7 +25051,7 @@
         <v>11.5</v>
       </c>
       <c r="G821" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -25074,7 +25077,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G822" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -25100,7 +25103,7 @@
         <v>11.5</v>
       </c>
       <c r="G823" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -25126,7 +25129,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G824" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -25152,7 +25155,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G825" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -25178,7 +25181,7 @@
         <v>11.75</v>
       </c>
       <c r="G826" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -25204,7 +25207,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G827" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -25230,7 +25233,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G828" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -25256,7 +25259,7 @@
         <v>11.75</v>
       </c>
       <c r="G829" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -25282,7 +25285,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G830" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -25308,7 +25311,7 @@
         <v>11.75</v>
       </c>
       <c r="G831" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -25334,7 +25337,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G832" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -25360,7 +25363,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G833" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -25386,7 +25389,7 @@
         <v>11.75</v>
       </c>
       <c r="G834" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -25412,7 +25415,7 @@
         <v>11.75</v>
       </c>
       <c r="G835" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -25438,7 +25441,7 @@
         <v>11.75</v>
       </c>
       <c r="G836" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -25464,7 +25467,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G837" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -25490,7 +25493,7 @@
         <v>11.75</v>
       </c>
       <c r="G838" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -25516,7 +25519,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G839" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -25542,7 +25545,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G840" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -25568,7 +25571,7 @@
         <v>11.25</v>
       </c>
       <c r="G841" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -25594,7 +25597,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G842" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -25620,7 +25623,7 @@
         <v>11.5</v>
       </c>
       <c r="G843" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -25646,7 +25649,7 @@
         <v>11.5</v>
       </c>
       <c r="G844" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -25672,7 +25675,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G845" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -25698,7 +25701,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G846" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -25724,7 +25727,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G847" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -25750,7 +25753,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G848" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -25776,7 +25779,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G849" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -25802,7 +25805,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G850" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -25828,7 +25831,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G851" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -25854,7 +25857,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G852" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -25880,7 +25883,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G853" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -25906,7 +25909,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G854" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -25932,7 +25935,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G855" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -25958,7 +25961,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G856" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -25984,7 +25987,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G857" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -26010,7 +26013,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G858" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -26036,7 +26039,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G859" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -26062,7 +26065,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G860" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -26088,7 +26091,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G861" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -26114,7 +26117,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G862" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -26140,7 +26143,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G863" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -26166,7 +26169,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G864" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -26192,7 +26195,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G865" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -26218,7 +26221,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G866" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -26244,7 +26247,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G867" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -26270,7 +26273,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G868" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -26296,7 +26299,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G869" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -26322,7 +26325,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G870" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -26556,7 +26559,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G879" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -26660,7 +26663,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G883" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -26712,7 +26715,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G885" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -26842,7 +26845,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G890" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -26946,7 +26949,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G894" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -26998,7 +27001,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G896" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -27024,7 +27027,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G897" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -27284,7 +27287,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G907" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -27362,7 +27365,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G910" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -27388,7 +27391,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G911" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -27414,7 +27417,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G912" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -27518,7 +27521,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G916" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -27570,7 +27573,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G918" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -29416,7 +29419,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G989" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -29494,7 +29497,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G992" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -31366,7 +31369,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1064" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -32224,7 +32227,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1097" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -32276,7 +32279,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G1099" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -68632,7 +68635,7 @@
     </row>
     <row r="2498">
       <c r="A2498" s="1" t="n">
-        <v>45957.6912152778</v>
+        <v>45957.3333333333</v>
       </c>
       <c r="B2498" t="n">
         <v>4715</v>
@@ -68653,6 +68656,32 @@
         <v>1119</v>
       </c>
       <c r="H2498" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2499">
+      <c r="A2499" s="1" t="n">
+        <v>45958.6912384259</v>
+      </c>
+      <c r="B2499" t="n">
+        <v>7574</v>
+      </c>
+      <c r="C2499" t="n">
+        <v>37.4000015258789</v>
+      </c>
+      <c r="D2499" t="n">
+        <v>36.2000007629395</v>
+      </c>
+      <c r="E2499" t="n">
+        <v>36.2999992370605</v>
+      </c>
+      <c r="F2499" t="n">
+        <v>37.25</v>
+      </c>
+      <c r="G2499" t="s">
+        <v>1120</v>
+      </c>
+      <c r="H2499" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LUVE.MI.xlsx
+++ b/data/LUVE.MI.xlsx
@@ -47,28 +47,28 @@
     <t xml:space="preserve">8.3170337677002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2838306427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09292125701904</t>
+    <t xml:space="preserve">8.28383159637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09292316436768</t>
   </si>
   <si>
     <t xml:space="preserve">8.19667816162109</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07632064819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15102481842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17177581787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03897190093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08462238311768</t>
+    <t xml:space="preserve">8.07631969451904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15102577209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17177677154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03896999359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08462142944336</t>
   </si>
   <si>
     <t xml:space="preserve">8.06802082061768</t>
@@ -77,73 +77,73 @@
     <t xml:space="preserve">7.96841669082642</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01821804046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99746656417847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91861295700073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91446256637573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91031217575073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88541173934937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87711143493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85220909118652</t>
+    <t xml:space="preserve">8.01821899414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99746942520142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91861391067505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91446399688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91031312942505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88541269302368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87711095809937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85220956802368</t>
   </si>
   <si>
     <t xml:space="preserve">7.64884901046753</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71940279006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70280313491821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69035243988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61979913711548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55754470825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55339479446411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63639783859253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76920461654663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80240726470947</t>
+    <t xml:space="preserve">7.7194037437439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70280265808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69035196304321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61979961395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55754375457764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55339527130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63639831542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76920557022095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80240774154663</t>
   </si>
   <si>
     <t xml:space="preserve">7.93521451950073</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10122299194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05142021179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18422794342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13442420959473</t>
+    <t xml:space="preserve">8.10122394561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05141925811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18422698974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13442516326904</t>
   </si>
   <si>
     <t xml:space="preserve">8.00161838531494</t>
@@ -152,46 +152,46 @@
     <t xml:space="preserve">7.96011590957642</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21742725372314</t>
+    <t xml:space="preserve">8.21742820739746</t>
   </si>
   <si>
     <t xml:space="preserve">8.35853672027588</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32533359527588</t>
+    <t xml:space="preserve">8.32533550262451</t>
   </si>
   <si>
     <t xml:space="preserve">8.2921314239502</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20082759857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15932655334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30336380004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36267471313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43045520782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15085411071777</t>
+    <t xml:space="preserve">8.20082855224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15932559967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30336475372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36267375946045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43045616149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15085315704346</t>
   </si>
   <si>
     <t xml:space="preserve">8.17627048492432</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20592784881592</t>
+    <t xml:space="preserve">8.2059268951416</t>
   </si>
   <si>
     <t xml:space="preserve">8.13390827178955</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11696147918701</t>
+    <t xml:space="preserve">8.11696338653564</t>
   </si>
   <si>
     <t xml:space="preserve">8.21863460540771</t>
@@ -200,64 +200,64 @@
     <t xml:space="preserve">8.21016311645508</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21439838409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20168876647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26099872589111</t>
+    <t xml:space="preserve">8.21439933776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20168972015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26099967956543</t>
   </si>
   <si>
     <t xml:space="preserve">8.09154415130615</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10848903656006</t>
+    <t xml:space="preserve">8.10848808288574</t>
   </si>
   <si>
     <t xml:space="preserve">8.04918003082275</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96445083618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92208671569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.879723072052</t>
+    <t xml:space="preserve">7.9644513130188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92208814620972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87972354888916</t>
   </si>
   <si>
     <t xml:space="preserve">7.83735942840576</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12543392181396</t>
+    <t xml:space="preserve">8.12543487548828</t>
   </si>
   <si>
     <t xml:space="preserve">7.93479633331299</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75262928009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71026659011841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93903350830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81194067001343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79499387741089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62553834915161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66790294647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84583282470703</t>
+    <t xml:space="preserve">7.75262975692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71026706695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93903303146362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81194019317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79499435424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62553882598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66790199279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84583377838135</t>
   </si>
   <si>
     <t xml:space="preserve">8.19321727752686</t>
@@ -266,49 +266,49 @@
     <t xml:space="preserve">8.47282123565674</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51518440246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52365779876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59991359710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78631401062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71853351593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50671100616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.540602684021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46858406066895</t>
+    <t xml:space="preserve">8.51518535614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52365875244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5999116897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78631496429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71853256225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50671195983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54060363769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46858310699463</t>
   </si>
   <si>
     <t xml:space="preserve">8.46434688568115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55754852294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57449340820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81173419952393</t>
+    <t xml:space="preserve">8.5575475692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57449245452881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81173324584961</t>
   </si>
   <si>
     <t xml:space="preserve">8.72700500488281</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6422758102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89646148681641</t>
+    <t xml:space="preserve">8.64227676391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89646053314209</t>
   </si>
   <si>
     <t xml:space="preserve">9.02355289459229</t>
@@ -320,19 +320,19 @@
     <t xml:space="preserve">9.06591796875</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10828304290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27773857116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19300937652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18453884124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07439041137695</t>
+    <t xml:space="preserve">9.1082820892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27773761749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1930103302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18453693389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07439136505127</t>
   </si>
   <si>
     <t xml:space="preserve">9.09133625030518</t>
@@ -341,76 +341,76 @@
     <t xml:space="preserve">9.30315685272217</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32010364532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12522888183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60817813873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4048318862915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48955726623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38788414001465</t>
+    <t xml:space="preserve">9.32010173797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12522983551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60817909240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40483093261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48955917358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38788509368896</t>
   </si>
   <si>
     <t xml:space="preserve">9.53192234039307</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48108577728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44719505310059</t>
+    <t xml:space="preserve">9.48108386993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44719409942627</t>
   </si>
   <si>
     <t xml:space="preserve">9.54039573669434</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5742883682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47261238098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41330242156982</t>
+    <t xml:space="preserve">9.57428741455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47261428833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41330337524414</t>
   </si>
   <si>
     <t xml:space="preserve">9.42177581787109</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51497650146484</t>
+    <t xml:space="preserve">9.51497554779053</t>
   </si>
   <si>
     <t xml:space="preserve">9.5658130645752</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74374389648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0657119750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2521123886108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1334915161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99792861938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95556259155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98098087310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88778114318848</t>
+    <t xml:space="preserve">9.74374198913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.065710067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2521142959595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1334924697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99792766571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95556449890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98098373413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88778018951416</t>
   </si>
   <si>
     <t xml:space="preserve">9.91319942474365</t>
@@ -419,40 +419,40 @@
     <t xml:space="preserve">10.0148735046387</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1589107513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0402927398682</t>
+    <t xml:space="preserve">10.1589117050171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0402908325195</t>
   </si>
   <si>
     <t xml:space="preserve">9.70137786865234</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73526954650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70985221862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0826568603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86236190795898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1250190734863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2944755554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4808778762817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5317163467407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5147695541382</t>
+    <t xml:space="preserve">9.73527050018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70985126495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0826559066772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8623628616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1250200271606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2944774627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4808788299561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5317153930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5147686004639</t>
   </si>
   <si>
     <t xml:space="preserve">10.8028450012207</t>
@@ -467,25 +467,25 @@
     <t xml:space="preserve">11.0146656036377</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0570297241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2773246765137</t>
+    <t xml:space="preserve">11.0570316314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.277325630188</t>
   </si>
   <si>
     <t xml:space="preserve">11.438307762146</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6586008071899</t>
+    <t xml:space="preserve">11.6585998535156</t>
   </si>
   <si>
     <t xml:space="preserve">11.5823450088501</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4806718826294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5908193588257</t>
+    <t xml:space="preserve">11.4806728363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5908174514771</t>
   </si>
   <si>
     <t xml:space="preserve">11.7009649276733</t>
@@ -494,22 +494,22 @@
     <t xml:space="preserve">11.7772207260132</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8111114501953</t>
+    <t xml:space="preserve">11.8111095428467</t>
   </si>
   <si>
     <t xml:space="preserve">11.8365297317505</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6670751571655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.599289894104</t>
+    <t xml:space="preserve">11.6670732498169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5992918014526</t>
   </si>
   <si>
     <t xml:space="preserve">11.5230350494385</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6077651977539</t>
+    <t xml:space="preserve">11.6077632904053</t>
   </si>
   <si>
     <t xml:space="preserve">11.6263809204102</t>
@@ -518,13 +518,13 @@
     <t xml:space="preserve">11.7297267913818</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6952772140503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6780548095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7986240386963</t>
+    <t xml:space="preserve">11.6952781677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6780529022217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7986221313477</t>
   </si>
   <si>
     <t xml:space="preserve">11.884744644165</t>
@@ -533,37 +533,37 @@
     <t xml:space="preserve">11.9105815887451</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0656003952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3153524398804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3584127426147</t>
+    <t xml:space="preserve">12.065598487854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3153514862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3584146499634</t>
   </si>
   <si>
     <t xml:space="preserve">12.0569887161255</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1431093215942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9967031478882</t>
+    <t xml:space="preserve">12.1431083679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9967041015625</t>
   </si>
   <si>
     <t xml:space="preserve">11.8416843414307</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7555618286133</t>
+    <t xml:space="preserve">11.7555627822876</t>
   </si>
   <si>
     <t xml:space="preserve">11.7125024795532</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8502960205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9191932678223</t>
+    <t xml:space="preserve">11.8502969741821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9191942214966</t>
   </si>
   <si>
     <t xml:space="preserve">11.962254524231</t>
@@ -572,25 +572,25 @@
     <t xml:space="preserve">12.0397634506226</t>
   </si>
   <si>
-    <t xml:space="preserve">12.048376083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7900104522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0311517715454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.945029258728</t>
+    <t xml:space="preserve">12.0483770370483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7900114059448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0311527252197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9450283050537</t>
   </si>
   <si>
     <t xml:space="preserve">11.8158483505249</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8933582305908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8761339187622</t>
+    <t xml:space="preserve">11.8933572769165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8761348724365</t>
   </si>
   <si>
     <t xml:space="preserve">11.8244600296021</t>
@@ -599,10 +599,10 @@
     <t xml:space="preserve">11.8675203323364</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9019689559937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9278059005737</t>
+    <t xml:space="preserve">11.901969909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.927806854248</t>
   </si>
   <si>
     <t xml:space="preserve">11.7211141586304</t>
@@ -611,13 +611,13 @@
     <t xml:space="preserve">11.6694421768188</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6349925994873</t>
+    <t xml:space="preserve">11.6349945068359</t>
   </si>
   <si>
     <t xml:space="preserve">11.6091566085815</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5747079849243</t>
+    <t xml:space="preserve">11.5747089385986</t>
   </si>
   <si>
     <t xml:space="preserve">11.5316476821899</t>
@@ -626,22 +626,22 @@
     <t xml:space="preserve">11.368016242981</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3594045639038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2818956375122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.230224609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1957731246948</t>
+    <t xml:space="preserve">11.3594055175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2818975448608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2302217483521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1957750320435</t>
   </si>
   <si>
     <t xml:space="preserve">11.187162399292</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1096534729004</t>
+    <t xml:space="preserve">11.1096525192261</t>
   </si>
   <si>
     <t xml:space="preserve">11.0579805374146</t>
@@ -659,7 +659,7 @@
     <t xml:space="preserve">11.066593170166</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0235319137573</t>
+    <t xml:space="preserve">11.023530960083</t>
   </si>
   <si>
     <t xml:space="preserve">11.083815574646</t>
@@ -671,16 +671,16 @@
     <t xml:space="preserve">11.2043857574463</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3163442611694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4541397094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5402603149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4110774993896</t>
+    <t xml:space="preserve">11.3163433074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4541387557983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5402593612671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.411078453064</t>
   </si>
   <si>
     <t xml:space="preserve">11.2905073165894</t>
@@ -689,22 +689,22 @@
     <t xml:space="preserve">11.1613254547119</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2646722793579</t>
+    <t xml:space="preserve">11.2646713256836</t>
   </si>
   <si>
     <t xml:space="preserve">11.1527137756348</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0407552719116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4196901321411</t>
+    <t xml:space="preserve">11.0407571792603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4196920394897</t>
   </si>
   <si>
     <t xml:space="preserve">11.2216110229492</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2388334274292</t>
+    <t xml:space="preserve">11.2388353347778</t>
   </si>
   <si>
     <t xml:space="preserve">11.3421821594238</t>
@@ -713,58 +713,58 @@
     <t xml:space="preserve">10.9546356201172</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9632453918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0063066482544</t>
+    <t xml:space="preserve">10.96324634552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0063076019287</t>
   </si>
   <si>
     <t xml:space="preserve">11.0924291610718</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74032306671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01690483093262</t>
+    <t xml:space="preserve">9.74032402038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0169038772583</t>
   </si>
   <si>
     <t xml:space="preserve">9.21498394012451</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37861442565918</t>
+    <t xml:space="preserve">9.37861347198486</t>
   </si>
   <si>
     <t xml:space="preserve">9.49057197570801</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50779724121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.593918800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60253047943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68865203857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56808185577393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39583778381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34416580200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25804424285889</t>
+    <t xml:space="preserve">9.5077953338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59391689300537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60252952575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68865013122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56808090209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39583873748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34416675567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2580451965332</t>
   </si>
   <si>
     <t xml:space="preserve">9.30110454559326</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41306400299072</t>
+    <t xml:space="preserve">9.41306209564209</t>
   </si>
   <si>
     <t xml:space="preserve">9.28388118743896</t>
@@ -776,7 +776,7 @@
     <t xml:space="preserve">9.12886142730713</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02551651000977</t>
+    <t xml:space="preserve">9.02551555633545</t>
   </si>
   <si>
     <t xml:space="preserve">9.20637130737305</t>
@@ -785,16 +785,16 @@
     <t xml:space="preserve">9.26665687561035</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69726276397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65420150756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66281509399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64558982849121</t>
+    <t xml:space="preserve">9.69726371765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65420341491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66281414031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64559173583984</t>
   </si>
   <si>
     <t xml:space="preserve">9.67142677307129</t>
@@ -803,79 +803,79 @@
     <t xml:space="preserve">9.75754737854004</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71448612213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09441375732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9393949508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14608573913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1202507019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83505821228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73171329498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90395355224609</t>
+    <t xml:space="preserve">9.71448802947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0944128036499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93939590454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14608669281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12024974822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83505630493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73171234130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90395450592041</t>
   </si>
   <si>
     <t xml:space="preserve">9.77477264404297</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5336332321167</t>
+    <t xml:space="preserve">9.53363037109375</t>
   </si>
   <si>
     <t xml:space="preserve">9.49918460845947</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57669258117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58530426025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47334766387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43028545379639</t>
+    <t xml:space="preserve">9.57669448852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58530521392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47334671020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4302864074707</t>
   </si>
   <si>
     <t xml:space="preserve">9.54224395751953</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17192363739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23220920562744</t>
+    <t xml:space="preserve">9.1719217300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23220825195312</t>
   </si>
   <si>
     <t xml:space="preserve">9.55946922302246</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51640796661377</t>
+    <t xml:space="preserve">9.51640701293945</t>
   </si>
   <si>
     <t xml:space="preserve">9.86089324951172</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95662021636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91355800628662</t>
+    <t xml:space="preserve">8.95661926269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91355895996094</t>
   </si>
   <si>
     <t xml:space="preserve">9.08580207824707</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0427417755127</t>
+    <t xml:space="preserve">9.04274082183838</t>
   </si>
   <si>
     <t xml:space="preserve">8.99967956542969</t>
@@ -887,28 +887,28 @@
     <t xml:space="preserve">8.69825649261475</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87049770355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78437614440918</t>
+    <t xml:space="preserve">8.87049961090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7843770980835</t>
   </si>
   <si>
     <t xml:space="preserve">8.7413158416748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61213397979736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59490966796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65519618988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45711517333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06314468383789</t>
+    <t xml:space="preserve">8.61213302612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59490871429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65519523620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45711421966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06314563751221</t>
   </si>
   <si>
     <t xml:space="preserve">9.10714054107666</t>
@@ -917,7 +917,7 @@
     <t xml:space="preserve">9.01914882659912</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97515201568604</t>
+    <t xml:space="preserve">8.97515296936035</t>
   </si>
   <si>
     <t xml:space="preserve">8.93115711212158</t>
@@ -926,10 +926,10 @@
     <t xml:space="preserve">8.88716220855713</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84316635131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76397323608398</t>
+    <t xml:space="preserve">8.84316539764404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76397132873535</t>
   </si>
   <si>
     <t xml:space="preserve">8.48240089416504</t>
@@ -938,58 +938,58 @@
     <t xml:space="preserve">8.71117782592773</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62318706512451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58799076080322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65838241577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60558700561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72877597808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69357872009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74637413024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53519344329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44720268249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27121829986572</t>
+    <t xml:space="preserve">8.6231861114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58798980712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6583833694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60558795928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7287769317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69357967376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74637508392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53519439697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44720363616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27121925354004</t>
   </si>
   <si>
     <t xml:space="preserve">8.32401466369629</t>
   </si>
   <si>
-    <t xml:space="preserve">8.288818359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78157138824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64078426361084</t>
+    <t xml:space="preserve">8.28881645202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78157043457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64078330993652</t>
   </si>
   <si>
     <t xml:space="preserve">8.79916858673096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67598152160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23912906646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37111568450928</t>
+    <t xml:space="preserve">8.67598056793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23912811279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37111473083496</t>
   </si>
   <si>
     <t xml:space="preserve">9.32711887359619</t>
@@ -1010,37 +1010,37 @@
     <t xml:space="preserve">8.49999809265137</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34161376953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23602199554443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30641651153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13043117523193</t>
+    <t xml:space="preserve">8.34161186218262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23602294921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30641555786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13043212890625</t>
   </si>
   <si>
     <t xml:space="preserve">8.18322849273682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16562938690186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21842479705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25362014770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37680912017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51759719848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28312492370605</t>
+    <t xml:space="preserve">8.16562843322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21842384338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25362110137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37681007385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51759624481201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28312397003174</t>
   </si>
   <si>
     <t xml:space="preserve">9.41511154174805</t>
@@ -1052,28 +1052,28 @@
     <t xml:space="preserve">9.59109497070312</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89906692504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.119044303894</t>
+    <t xml:space="preserve">9.8990650177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1190452575684</t>
   </si>
   <si>
     <t xml:space="preserve">10.1630401611328</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2070369720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3390254974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2950277328491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3830194473267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2510318756104</t>
+    <t xml:space="preserve">10.2070360183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3390245437622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2950286865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.383020401001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2510328292847</t>
   </si>
   <si>
     <t xml:space="preserve">10.4270162582397</t>
@@ -1097,13 +1097,13 @@
     <t xml:space="preserve">10.6048803329468</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3802003860474</t>
+    <t xml:space="preserve">10.380199432373</t>
   </si>
   <si>
     <t xml:space="preserve">10.2453918457031</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0656480789185</t>
+    <t xml:space="preserve">10.0656499862671</t>
   </si>
   <si>
     <t xml:space="preserve">10.4251356124878</t>
@@ -1112,25 +1112,25 @@
     <t xml:space="preserve">10.5150079727173</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3352632522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2903280258179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2004556655884</t>
+    <t xml:space="preserve">10.3352642059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2903270721436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2004566192627</t>
   </si>
   <si>
     <t xml:space="preserve">9.97577667236328</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1105842590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93084144592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88590526580811</t>
+    <t xml:space="preserve">10.1105833053589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93083953857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88590431213379</t>
   </si>
   <si>
     <t xml:space="preserve">10.1555213928223</t>
@@ -1139,7 +1139,7 @@
     <t xml:space="preserve">10.020712852478</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75109672546387</t>
+    <t xml:space="preserve">9.75109767913818</t>
   </si>
   <si>
     <t xml:space="preserve">9.70616149902344</t>
@@ -1148,16 +1148,16 @@
     <t xml:space="preserve">9.3466739654541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30173683166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39160919189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48148250579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61629009246826</t>
+    <t xml:space="preserve">9.30173778533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39160823822021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48148155212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61628913879395</t>
   </si>
   <si>
     <t xml:space="preserve">9.52641677856445</t>
@@ -1169,7 +1169,7 @@
     <t xml:space="preserve">9.12199401855469</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03212261199951</t>
+    <t xml:space="preserve">9.0321216583252</t>
   </si>
   <si>
     <t xml:space="preserve">9.16693019866943</t>
@@ -1178,22 +1178,22 @@
     <t xml:space="preserve">9.07705879211426</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25680065155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98718643188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5713529586792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66122531890869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7960319519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9643669128418</t>
+    <t xml:space="preserve">9.25680255889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98718547821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57135200500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66122627258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79603290557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9643678665161</t>
   </si>
   <si>
     <t xml:space="preserve">11.4586629867554</t>
@@ -1202,22 +1202,22 @@
     <t xml:space="preserve">11.5035982131958</t>
   </si>
   <si>
-    <t xml:space="preserve">11.233983039856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1441116333008</t>
+    <t xml:space="preserve">11.2339820861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1441106796265</t>
   </si>
   <si>
     <t xml:space="preserve">10.9194307327271</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8744945526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0093021392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2789182662964</t>
+    <t xml:space="preserve">10.8744964599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0093030929565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2789192199707</t>
   </si>
   <si>
     <t xml:space="preserve">11.4137268066406</t>
@@ -1229,19 +1229,19 @@
     <t xml:space="preserve">11.6833429336548</t>
   </si>
   <si>
-    <t xml:space="preserve">11.77321434021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9080228805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1327018737793</t>
+    <t xml:space="preserve">11.7732152938843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9080219268799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.132700920105</t>
   </si>
   <si>
     <t xml:space="preserve">11.9978942871094</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8181495666504</t>
+    <t xml:space="preserve">11.8181486129761</t>
   </si>
   <si>
     <t xml:space="preserve">11.593469619751</t>
@@ -1268,25 +1268,25 @@
     <t xml:space="preserve">12.4472532272339</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5371236801147</t>
+    <t xml:space="preserve">12.5371246337891</t>
   </si>
   <si>
     <t xml:space="preserve">12.2675085067749</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4023160934448</t>
+    <t xml:space="preserve">12.4023170471191</t>
   </si>
   <si>
     <t xml:space="preserve">12.6269969940186</t>
   </si>
   <si>
-    <t xml:space="preserve">12.671932220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8966131210327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7282772064209</t>
+    <t xml:space="preserve">12.6719312667847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.896614074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7282781600952</t>
   </si>
   <si>
     <t xml:space="preserve">10.7846231460571</t>
@@ -1298,25 +1298,25 @@
     <t xml:space="preserve">8.89731407165527</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98062133789062</t>
+    <t xml:space="preserve">7.98062181472778</t>
   </si>
   <si>
     <t xml:space="preserve">7.81885194778442</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5312614440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89074897766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53782844543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.962646484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44795417785645</t>
+    <t xml:space="preserve">7.53126192092896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89074850082397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53782653808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96264696121216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44795513153076</t>
   </si>
   <si>
     <t xml:space="preserve">8.6097240447998</t>
@@ -1325,16 +1325,16 @@
     <t xml:space="preserve">8.66364860534668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86136436462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21186637878418</t>
+    <t xml:space="preserve">8.86136531829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21186542510986</t>
   </si>
   <si>
     <t xml:space="preserve">9.93848991394043</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80045509338379</t>
+    <t xml:space="preserve">9.80045318603516</t>
   </si>
   <si>
     <t xml:space="preserve">9.89247798919678</t>
@@ -1343,7 +1343,7 @@
     <t xml:space="preserve">9.66242027282715</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70843315124512</t>
+    <t xml:space="preserve">9.7084321975708</t>
   </si>
   <si>
     <t xml:space="preserve">9.84646701812744</t>
@@ -1352,19 +1352,19 @@
     <t xml:space="preserve">10.1225357055664</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75444316864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.398606300354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3065814971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.720685005188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5826501846313</t>
+    <t xml:space="preserve">9.75444412231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3986043930054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3065824508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7206840515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5826511383057</t>
   </si>
   <si>
     <t xml:space="preserve">10.8587207794189</t>
@@ -1373,10 +1373,10 @@
     <t xml:space="preserve">10.6746740341187</t>
   </si>
   <si>
-    <t xml:space="preserve">10.996753692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6286630630493</t>
+    <t xml:space="preserve">10.9967546463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.628662109375</t>
   </si>
   <si>
     <t xml:space="preserve">10.7666969299316</t>
@@ -1385,40 +1385,40 @@
     <t xml:space="preserve">10.4906272888184</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1347885131836</t>
+    <t xml:space="preserve">11.1347894668579</t>
   </si>
   <si>
     <t xml:space="preserve">11.3188352584839</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5028820037842</t>
+    <t xml:space="preserve">11.5028810501099</t>
   </si>
   <si>
     <t xml:space="preserve">11.1808004379272</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0427656173706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2728233337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9507427215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0887775421143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8127088546753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9047317504883</t>
+    <t xml:space="preserve">11.0427665710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2728242874146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9507417678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0887765884399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8127098083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9047327041626</t>
   </si>
   <si>
     <t xml:space="preserve">11.4108591079712</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4568691253662</t>
+    <t xml:space="preserve">11.4568700790405</t>
   </si>
   <si>
     <t xml:space="preserve">11.2268123626709</t>
@@ -1427,10 +1427,10 @@
     <t xml:space="preserve">11.3648471832275</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5488929748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5949039459229</t>
+    <t xml:space="preserve">11.5488920211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5949048995972</t>
   </si>
   <si>
     <t xml:space="preserve">11.6869277954102</t>
@@ -1442,10 +1442,10 @@
     <t xml:space="preserve">11.7789506912231</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0090074539185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1010313034058</t>
+    <t xml:space="preserve">12.0090084075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1010303497314</t>
   </si>
   <si>
     <t xml:space="preserve">11.7329397201538</t>
@@ -1466,22 +1466,22 @@
     <t xml:space="preserve">11.6409158706665</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1470413208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6991806030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7912044525146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0672721862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.883228302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9292392730713</t>
+    <t xml:space="preserve">12.1470432281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6991815567017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7912034988403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0672731399536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8832273483276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9292402267456</t>
   </si>
   <si>
     <t xml:space="preserve">13.2053089141846</t>
@@ -1490,115 +1490,115 @@
     <t xml:space="preserve">13.2513189315796</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1132850646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1592960357666</t>
+    <t xml:space="preserve">13.1132860183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1592969894409</t>
   </si>
   <si>
     <t xml:space="preserve">13.3893537521362</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2973308563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9752502441406</t>
+    <t xml:space="preserve">13.2973299026489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9752492904663</t>
   </si>
   <si>
     <t xml:space="preserve">13.7114343643188</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4353666305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.51513671875</t>
+    <t xml:space="preserve">13.4353656768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5151348114014</t>
   </si>
   <si>
     <t xml:space="preserve">12.3770999908447</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8372144699097</t>
+    <t xml:space="preserve">12.837215423584</t>
   </si>
   <si>
     <t xml:space="preserve">12.7451934814453</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6531705856323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3433427810669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6194114685059</t>
+    <t xml:space="preserve">12.653169631958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3433418273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6194124221802</t>
   </si>
   <si>
     <t xml:space="preserve">13.8494691848755</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9414920806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1715488433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3555965423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1255388259888</t>
+    <t xml:space="preserve">13.9414911270142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1715497970581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3555955886841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1255378723145</t>
   </si>
   <si>
     <t xml:space="preserve">14.4936304092407</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7236881256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6776762008667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8157119750977</t>
+    <t xml:space="preserve">14.723687171936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.677677154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.815710067749</t>
   </si>
   <si>
     <t xml:space="preserve">14.8617219924927</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0457706451416</t>
+    <t xml:space="preserve">15.0457696914673</t>
   </si>
   <si>
     <t xml:space="preserve">14.5396423339844</t>
   </si>
   <si>
-    <t xml:space="preserve">14.631664276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4476194381714</t>
+    <t xml:space="preserve">14.6316652297974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4476184844971</t>
   </si>
   <si>
     <t xml:space="preserve">14.2635726928711</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9875030517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3095855712891</t>
+    <t xml:space="preserve">13.9875049591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3095846176147</t>
   </si>
   <si>
     <t xml:space="preserve">13.6654233932495</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8034572601318</t>
+    <t xml:space="preserve">13.8034582138062</t>
   </si>
   <si>
     <t xml:space="preserve">13.5733995437622</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7574462890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.95374584198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0335149765015</t>
+    <t xml:space="preserve">13.7574453353882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9537467956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0335159301758</t>
   </si>
   <si>
     <t xml:space="preserve">14.4269771575928</t>
@@ -1607,7 +1607,7 @@
     <t xml:space="preserve">14.3801374435425</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4738187789917</t>
+    <t xml:space="preserve">14.473819732666</t>
   </si>
   <si>
     <t xml:space="preserve">14.7080240249634</t>
@@ -1616,7 +1616,7 @@
     <t xml:space="preserve">14.8485460281372</t>
   </si>
   <si>
-    <t xml:space="preserve">15.03590965271</t>
+    <t xml:space="preserve">15.0359086990356</t>
   </si>
   <si>
     <t xml:space="preserve">15.0827503204346</t>
@@ -1628,10 +1628,10 @@
     <t xml:space="preserve">14.9422273635864</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1764335632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1295900344849</t>
+    <t xml:space="preserve">15.1764316558838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1295909881592</t>
   </si>
   <si>
     <t xml:space="preserve">14.989068031311</t>
@@ -1640,7 +1640,7 @@
     <t xml:space="preserve">14.6611814498901</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3169555664062</t>
+    <t xml:space="preserve">15.3169546127319</t>
   </si>
   <si>
     <t xml:space="preserve">14.7548637390137</t>
@@ -1649,7 +1649,7 @@
     <t xml:space="preserve">14.8017053604126</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2232723236084</t>
+    <t xml:space="preserve">15.2232713699341</t>
   </si>
   <si>
     <t xml:space="preserve">15.5043172836304</t>
@@ -1658,7 +1658,7 @@
     <t xml:space="preserve">16.0664081573486</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6916790008545</t>
+    <t xml:space="preserve">15.6916799545288</t>
   </si>
   <si>
     <t xml:space="preserve">15.7385215759277</t>
@@ -1682,22 +1682,22 @@
     <t xml:space="preserve">16.5348167419434</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8627033233643</t>
+    <t xml:space="preserve">16.8627014160156</t>
   </si>
   <si>
     <t xml:space="preserve">17.1437454223633</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5816593170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2069282531738</t>
+    <t xml:space="preserve">16.581657409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2069301605225</t>
   </si>
   <si>
     <t xml:space="preserve">17.2842712402344</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7995204925537</t>
+    <t xml:space="preserve">17.7995185852051</t>
   </si>
   <si>
     <t xml:space="preserve">17.4716320037842</t>
@@ -1706,16 +1706,16 @@
     <t xml:space="preserve">16.8158626556396</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6284961700439</t>
+    <t xml:space="preserve">16.6284980773926</t>
   </si>
   <si>
     <t xml:space="preserve">17.0969066619873</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5184764862061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.612154006958</t>
+    <t xml:space="preserve">17.5184745788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6121559143066</t>
   </si>
   <si>
     <t xml:space="preserve">18.0337219238281</t>
@@ -1727,31 +1727,31 @@
     <t xml:space="preserve">18.7363357543945</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9237003326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7668361663818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5794696807861</t>
+    <t xml:space="preserve">18.923698425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7668342590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5794677734375</t>
   </si>
   <si>
     <t xml:space="preserve">19.2047443389893</t>
   </si>
   <si>
-    <t xml:space="preserve">19.11106300354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6731510162354</t>
+    <t xml:space="preserve">19.1110610961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.673152923584</t>
   </si>
   <si>
     <t xml:space="preserve">19.2984237670898</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4857883453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8605155944824</t>
+    <t xml:space="preserve">19.4857864379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8605175018311</t>
   </si>
   <si>
     <t xml:space="preserve">20.3289241790771</t>
@@ -1760,7 +1760,7 @@
     <t xml:space="preserve">20.9846954345703</t>
   </si>
   <si>
-    <t xml:space="preserve">21.265739440918</t>
+    <t xml:space="preserve">21.2657413482666</t>
   </si>
   <si>
     <t xml:space="preserve">21.0783767700195</t>
@@ -1778,16 +1778,16 @@
     <t xml:space="preserve">22.1088771820068</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7341499328613</t>
+    <t xml:space="preserve">21.7341480255127</t>
   </si>
   <si>
     <t xml:space="preserve">22.015193939209</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2962379455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4836006164551</t>
+    <t xml:space="preserve">22.2962398529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4836025238037</t>
   </si>
   <si>
     <t xml:space="preserve">21.6404685974121</t>
@@ -1808,7 +1808,7 @@
     <t xml:space="preserve">20.6099681854248</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9215126037598</t>
+    <t xml:space="preserve">21.9215106964111</t>
   </si>
   <si>
     <t xml:space="preserve">22.7646465301514</t>
@@ -1817,10 +1817,10 @@
     <t xml:space="preserve">22.5772838592529</t>
   </si>
   <si>
-    <t xml:space="preserve">21.172061920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7036514282227</t>
+    <t xml:space="preserve">21.1720600128174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.703649520874</t>
   </si>
   <si>
     <t xml:space="preserve">21.3594207763672</t>
@@ -1829,28 +1829,28 @@
     <t xml:space="preserve">20.5162868499756</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0478801727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6709651947021</t>
+    <t xml:space="preserve">20.0478782653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6709671020508</t>
   </si>
   <si>
     <t xml:space="preserve">22.2025585174561</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3899192810059</t>
+    <t xml:space="preserve">22.3899211883545</t>
   </si>
   <si>
     <t xml:space="preserve">19.9541969299316</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4226036071777</t>
+    <t xml:space="preserve">20.4226055145264</t>
   </si>
   <si>
     <t xml:space="preserve">20.8910140991211</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3921070098877</t>
+    <t xml:space="preserve">19.3921089172363</t>
   </si>
   <si>
     <t xml:space="preserve">18.8300170898438</t>
@@ -1868,31 +1868,31 @@
     <t xml:space="preserve">17.7526779174805</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3779525756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8931999206543</t>
+    <t xml:space="preserve">17.3779487609863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8932018280029</t>
   </si>
   <si>
     <t xml:space="preserve">17.9400405883789</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2679271697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8768558502197</t>
+    <t xml:space="preserve">18.2679252624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8768577575684</t>
   </si>
   <si>
     <t xml:space="preserve">18.6426544189453</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3241348266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2117195129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2304534912109</t>
+    <t xml:space="preserve">18.3241367340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2117176055908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2304515838623</t>
   </si>
   <si>
     <t xml:space="preserve">18.4552898406982</t>
@@ -1904,22 +1904,22 @@
     <t xml:space="preserve">18.1180362701416</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9705410003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2820816040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0947189331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1884021759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1415596008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4927635192871</t>
+    <t xml:space="preserve">18.9705390930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2820835113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0947208404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1883983612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1415615081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4927616119385</t>
   </si>
   <si>
     <t xml:space="preserve">17.5559463500977</t>
@@ -1937,13 +1937,13 @@
     <t xml:space="preserve">18.0308246612549</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9285469055176</t>
+    <t xml:space="preserve">18.9285449981689</t>
   </si>
   <si>
     <t xml:space="preserve">18.4319343566895</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6038398742676</t>
+    <t xml:space="preserve">18.6038379669189</t>
   </si>
   <si>
     <t xml:space="preserve">19.1004505157471</t>
@@ -1952,16 +1952,16 @@
     <t xml:space="preserve">18.9858474731445</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1481990814209</t>
+    <t xml:space="preserve">19.1482009887695</t>
   </si>
   <si>
     <t xml:space="preserve">18.90944480896</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9476490020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0077247619629</t>
+    <t xml:space="preserve">18.9476470947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0077228546143</t>
   </si>
   <si>
     <t xml:space="preserve">20.0554733276367</t>
@@ -1970,19 +1970,19 @@
     <t xml:space="preserve">20.5329856872559</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9149932861328</t>
+    <t xml:space="preserve">20.9149913787842</t>
   </si>
   <si>
     <t xml:space="preserve">20.1509761810303</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4374828338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0104961395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4880084991455</t>
+    <t xml:space="preserve">20.4374809265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0104942321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4880065917969</t>
   </si>
   <si>
     <t xml:space="preserve">19.5779628753662</t>
@@ -1997,13 +1997,13 @@
     <t xml:space="preserve">19.2914562225342</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3392066955566</t>
+    <t xml:space="preserve">19.339204788208</t>
   </si>
   <si>
     <t xml:space="preserve">18.813943862915</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6993389129639</t>
+    <t xml:space="preserve">18.6993408203125</t>
   </si>
   <si>
     <t xml:space="preserve">19.3869571685791</t>
@@ -2012,31 +2012,31 @@
     <t xml:space="preserve">18.852144241333</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0813503265381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.240930557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7757434844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9599704742432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4852352142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1059970855713</t>
+    <t xml:space="preserve">19.0813484191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2409324645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7757415771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9599685668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4852333068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1059989929199</t>
   </si>
   <si>
     <t xml:space="preserve">21.8700160980225</t>
   </si>
   <si>
-    <t xml:space="preserve">21.392505645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1537475585938</t>
+    <t xml:space="preserve">21.3925037384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1537494659424</t>
   </si>
   <si>
     <t xml:space="preserve">21.7745132446289</t>
@@ -2054,16 +2054,16 @@
     <t xml:space="preserve">21.7267627716064</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5835094451904</t>
+    <t xml:space="preserve">21.5835113525391</t>
   </si>
   <si>
     <t xml:space="preserve">20.5807342529297</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1032218933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.62571144104</t>
+    <t xml:space="preserve">20.1032238006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6257133483887</t>
   </si>
   <si>
     <t xml:space="preserve">19.8644676208496</t>
@@ -2072,16 +2072,16 @@
     <t xml:space="preserve">21.2492504119873</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9205417633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4430313110352</t>
+    <t xml:space="preserve">22.920539855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4430294036865</t>
   </si>
   <si>
     <t xml:space="preserve">22.1565227508545</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0610198974609</t>
+    <t xml:space="preserve">22.0610218048096</t>
   </si>
   <si>
     <t xml:space="preserve">22.3475284576416</t>
@@ -2090,7 +2090,7 @@
     <t xml:space="preserve">21.0582466125488</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3897304534912</t>
+    <t xml:space="preserve">20.3897323608398</t>
   </si>
   <si>
     <t xml:space="preserve">20.2942276000977</t>
@@ -2105,7 +2105,7 @@
     <t xml:space="preserve">20.8672428131104</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0499267578125</t>
+    <t xml:space="preserve">18.0499248504639</t>
   </si>
   <si>
     <t xml:space="preserve">18.833044052124</t>
@@ -2120,7 +2120,7 @@
     <t xml:space="preserve">19.8167171478271</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2464790344238</t>
+    <t xml:space="preserve">20.2464771270752</t>
   </si>
   <si>
     <t xml:space="preserve">20.6762371063232</t>
@@ -2141,10 +2141,10 @@
     <t xml:space="preserve">22.7295341491699</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5862808227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8727912902832</t>
+    <t xml:space="preserve">22.5862827301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8727893829346</t>
   </si>
   <si>
     <t xml:space="preserve">22.5385322570801</t>
@@ -2156,58 +2156,58 @@
     <t xml:space="preserve">23.0160427093506</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3025493621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4485759735107</t>
+    <t xml:space="preserve">23.3025512695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4485778808594</t>
   </si>
   <si>
     <t xml:space="preserve">23.7323112487793</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9710636138916</t>
+    <t xml:space="preserve">23.9710655212402</t>
   </si>
   <si>
     <t xml:space="preserve">24.2098217010498</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0665683746338</t>
+    <t xml:space="preserve">24.0665664672852</t>
   </si>
   <si>
     <t xml:space="preserve">24.1143188476562</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4008255004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3080978393555</t>
+    <t xml:space="preserve">24.4008235931396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3080959320068</t>
   </si>
   <si>
     <t xml:space="preserve">23.7800598144531</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9233150482178</t>
+    <t xml:space="preserve">23.9233131408691</t>
   </si>
   <si>
     <t xml:space="preserve">25.0693416595459</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5440807342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9260864257812</t>
+    <t xml:space="preserve">24.5440788269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9260883331299</t>
   </si>
   <si>
     <t xml:space="preserve">25.3558464050293</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4035987854004</t>
+    <t xml:space="preserve">25.403600692749</t>
   </si>
   <si>
     <t xml:space="preserve">25.8333587646484</t>
   </si>
   <si>
-    <t xml:space="preserve">26.883882522583</t>
+    <t xml:space="preserve">26.8838844299316</t>
   </si>
   <si>
     <t xml:space="preserve">26.7883815765381</t>
@@ -2222,19 +2222,19 @@
     <t xml:space="preserve">24.8305854797363</t>
   </si>
   <si>
-    <t xml:space="preserve">25.260347366333</t>
+    <t xml:space="preserve">25.2603454589844</t>
   </si>
   <si>
     <t xml:space="preserve">25.7378578186035</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7856101989746</t>
+    <t xml:space="preserve">25.7856063842773</t>
   </si>
   <si>
     <t xml:space="preserve">26.0721130371094</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2631206512451</t>
+    <t xml:space="preserve">26.2631187438965</t>
   </si>
   <si>
     <t xml:space="preserve">25.4513492584229</t>
@@ -2243,7 +2243,7 @@
     <t xml:space="preserve">25.928861618042</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5946025848389</t>
+    <t xml:space="preserve">25.5946044921875</t>
   </si>
   <si>
     <t xml:space="preserve">25.6901073455811</t>
@@ -2252,10 +2252,10 @@
     <t xml:space="preserve">25.5468521118164</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4541244506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7406311035156</t>
+    <t xml:space="preserve">26.4541263580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.740629196167</t>
   </si>
   <si>
     <t xml:space="preserve">27.0748901367188</t>
@@ -2264,13 +2264,13 @@
     <t xml:space="preserve">27.1703929901123</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6506767272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.321964263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.892204284668</t>
+    <t xml:space="preserve">28.6506748199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3219661712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8922023773193</t>
   </si>
   <si>
     <t xml:space="preserve">29.9877071380615</t>
@@ -2288,7 +2288,7 @@
     <t xml:space="preserve">28.5074214935303</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3191909790039</t>
+    <t xml:space="preserve">29.3191928863525</t>
   </si>
   <si>
     <t xml:space="preserve">28.9371814727783</t>
@@ -2300,70 +2300,70 @@
     <t xml:space="preserve">29.223690032959</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1281871795654</t>
+    <t xml:space="preserve">29.1281852722168</t>
   </si>
   <si>
     <t xml:space="preserve">29.1759376525879</t>
   </si>
   <si>
-    <t xml:space="preserve">29.080436706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6984272003174</t>
+    <t xml:space="preserve">29.0804386138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6984252929688</t>
   </si>
   <si>
     <t xml:space="preserve">28.9849338531494</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3641681671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8866596221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2714405059814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8389053344727</t>
+    <t xml:space="preserve">28.3641700744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8866577148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2714385986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8389072418213</t>
   </si>
   <si>
     <t xml:space="preserve">27.6479034423828</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6029243469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4119205474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.366943359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4146919250488</t>
+    <t xml:space="preserve">28.6029262542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4119186401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3669414520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4146938323975</t>
   </si>
   <si>
     <t xml:space="preserve">30.0354595184326</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7489490509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7039737701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2742137908936</t>
+    <t xml:space="preserve">29.748950958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7039756774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2742156982422</t>
   </si>
   <si>
     <t xml:space="preserve">29.7012023925781</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5579471588135</t>
+    <t xml:space="preserve">29.5579490661621</t>
   </si>
   <si>
     <t xml:space="preserve">29.796703338623</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2209167480469</t>
+    <t xml:space="preserve">28.2209148406982</t>
   </si>
   <si>
     <t xml:space="preserve">28.3164176940918</t>
@@ -2375,10 +2375,10 @@
     <t xml:space="preserve">26.9480724334717</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5770206451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.593017578125</t>
+    <t xml:space="preserve">27.5770225524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5930156707764</t>
   </si>
   <si>
     <t xml:space="preserve">28.0124492645264</t>
@@ -2396,7 +2396,7 @@
     <t xml:space="preserve">28.0608291625977</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3994941711426</t>
+    <t xml:space="preserve">28.3994960784912</t>
   </si>
   <si>
     <t xml:space="preserve">28.7381591796875</t>
@@ -2405,7 +2405,7 @@
     <t xml:space="preserve">29.1252059936523</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9800624847412</t>
+    <t xml:space="preserve">28.9800643920898</t>
   </si>
   <si>
     <t xml:space="preserve">27.7705459594727</t>
@@ -2447,19 +2447,19 @@
     <t xml:space="preserve">29.2219676971436</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0284442901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2543544769287</t>
+    <t xml:space="preserve">29.0284423828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2543525695801</t>
   </si>
   <si>
     <t xml:space="preserve">29.705774307251</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0444374084473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9960594177246</t>
+    <t xml:space="preserve">30.0444393157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.996057510376</t>
   </si>
   <si>
     <t xml:space="preserve">28.8349208831787</t>
@@ -2474,7 +2474,7 @@
     <t xml:space="preserve">28.2059707641602</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4962577819824</t>
+    <t xml:space="preserve">28.4962558746338</t>
   </si>
   <si>
     <t xml:space="preserve">27.0932140350342</t>
@@ -2483,7 +2483,7 @@
     <t xml:space="preserve">26.8513107299805</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0772190093994</t>
+    <t xml:space="preserve">26.077220916748</t>
   </si>
   <si>
     <t xml:space="preserve">26.8996906280518</t>
@@ -2507,22 +2507,22 @@
     <t xml:space="preserve">25.3031272888184</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2547454833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1579837799072</t>
+    <t xml:space="preserve">25.2547473907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1579856872559</t>
   </si>
   <si>
     <t xml:space="preserve">24.9160804748535</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4966506958008</t>
+    <t xml:space="preserve">25.4966487884521</t>
   </si>
   <si>
     <t xml:space="preserve">25.3515071868896</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0612239837646</t>
+    <t xml:space="preserve">25.061222076416</t>
   </si>
   <si>
     <t xml:space="preserve">24.7225570678711</t>
@@ -2531,7 +2531,7 @@
     <t xml:space="preserve">24.4806537628174</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6098003387451</t>
+    <t xml:space="preserve">23.6098022460938</t>
   </si>
   <si>
     <t xml:space="preserve">23.0292301177979</t>
@@ -2540,7 +2540,7 @@
     <t xml:space="preserve">22.9324722290039</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1743755340576</t>
+    <t xml:space="preserve">23.174373626709</t>
   </si>
   <si>
     <t xml:space="preserve">22.5938053131104</t>
@@ -2552,7 +2552,7 @@
     <t xml:space="preserve">21.6745719909668</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9164752960205</t>
+    <t xml:space="preserve">21.9164733886719</t>
   </si>
   <si>
     <t xml:space="preserve">21.5294284820557</t>
@@ -2564,16 +2564,16 @@
     <t xml:space="preserve">21.0940017700195</t>
   </si>
   <si>
-    <t xml:space="preserve">20.465051651001</t>
+    <t xml:space="preserve">20.4650535583496</t>
   </si>
   <si>
     <t xml:space="preserve">20.2231483459473</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4166736602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9004783630371</t>
+    <t xml:space="preserve">20.4166717529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9004802703857</t>
   </si>
   <si>
     <t xml:space="preserve">20.8037185668945</t>
@@ -2582,22 +2582,22 @@
     <t xml:space="preserve">20.6101951599121</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6585750579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7069568634033</t>
+    <t xml:space="preserve">20.658576965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7069549560547</t>
   </si>
   <si>
     <t xml:space="preserve">20.7553386688232</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3359069824219</t>
+    <t xml:space="preserve">21.3359050750732</t>
   </si>
   <si>
     <t xml:space="preserve">21.0456218719482</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4490585327148</t>
+    <t xml:space="preserve">19.4490566253662</t>
   </si>
   <si>
     <t xml:space="preserve">19.8361034393311</t>
@@ -2606,7 +2606,7 @@
     <t xml:space="preserve">19.2361812591553</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8878402709961</t>
+    <t xml:space="preserve">18.8878421783447</t>
   </si>
   <si>
     <t xml:space="preserve">18.6362609863281</t>
@@ -2630,13 +2630,13 @@
     <t xml:space="preserve">17.049373626709</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0300197601318</t>
+    <t xml:space="preserve">17.0300216674805</t>
   </si>
   <si>
     <t xml:space="preserve">16.8752021789551</t>
   </si>
   <si>
-    <t xml:space="preserve">18.326623916626</t>
+    <t xml:space="preserve">18.3266258239746</t>
   </si>
   <si>
     <t xml:space="preserve">18.7717266082764</t>
@@ -2648,13 +2648,13 @@
     <t xml:space="preserve">18.5782051086426</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4233856201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1331024169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4974365234375</t>
+    <t xml:space="preserve">18.4233875274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1331005096436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4974384307861</t>
   </si>
   <si>
     <t xml:space="preserve">20.1263866424561</t>
@@ -2663,7 +2663,7 @@
     <t xml:space="preserve">19.9328651428223</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3199100494385</t>
+    <t xml:space="preserve">20.3199119567871</t>
   </si>
   <si>
     <t xml:space="preserve">19.6425800323486</t>
@@ -2678,10 +2678,10 @@
     <t xml:space="preserve">19.1781253814697</t>
   </si>
   <si>
-    <t xml:space="preserve">19.023307800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1974792480469</t>
+    <t xml:space="preserve">19.0233058929443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1974773406982</t>
   </si>
   <si>
     <t xml:space="preserve">18.9071941375732</t>
@@ -2690,7 +2690,7 @@
     <t xml:space="preserve">19.8844833374023</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4006748199463</t>
+    <t xml:space="preserve">19.4006767272949</t>
   </si>
   <si>
     <t xml:space="preserve">19.7877235412598</t>
@@ -2708,7 +2708,7 @@
     <t xml:space="preserve">22.0132369995117</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8357105255127</t>
+    <t xml:space="preserve">22.8357086181641</t>
   </si>
   <si>
     <t xml:space="preserve">22.1583786010742</t>
@@ -2720,19 +2720,19 @@
     <t xml:space="preserve">22.3519020080566</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7229518890381</t>
+    <t xml:space="preserve">21.7229537963867</t>
   </si>
   <si>
     <t xml:space="preserve">21.5778102874756</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4326667785645</t>
+    <t xml:space="preserve">21.4326686859131</t>
   </si>
   <si>
     <t xml:space="preserve">22.061616897583</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4970436096191</t>
+    <t xml:space="preserve">22.4970455169678</t>
   </si>
   <si>
     <t xml:space="preserve">22.2551403045654</t>
@@ -2744,7 +2744,7 @@
     <t xml:space="preserve">21.6261901855469</t>
   </si>
   <si>
-    <t xml:space="preserve">21.771333694458</t>
+    <t xml:space="preserve">21.7713317871094</t>
   </si>
   <si>
     <t xml:space="preserve">22.3035202026367</t>
@@ -2753,10 +2753,10 @@
     <t xml:space="preserve">22.8840885162354</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7873268127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9648551940918</t>
+    <t xml:space="preserve">22.7873287200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9648571014404</t>
   </si>
   <si>
     <t xml:space="preserve">20.948860168457</t>
@@ -2771,7 +2771,7 @@
     <t xml:space="preserve">20.1747703552246</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5134353637695</t>
+    <t xml:space="preserve">20.5134334564209</t>
   </si>
   <si>
     <t xml:space="preserve">20.0296268463135</t>
@@ -2780,13 +2780,13 @@
     <t xml:space="preserve">22.9808521270752</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1259918212891</t>
+    <t xml:space="preserve">23.1259937286377</t>
   </si>
   <si>
     <t xml:space="preserve">21.3842868804932</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8520984649658</t>
+    <t xml:space="preserve">20.8520965576172</t>
   </si>
   <si>
     <t xml:space="preserve">20.5618133544922</t>
@@ -68661,7 +68661,7 @@
     </row>
     <row r="2499">
       <c r="A2499" s="1" t="n">
-        <v>45958.6912384259</v>
+        <v>45958.3333333333</v>
       </c>
       <c r="B2499" t="n">
         <v>7574</v>
@@ -68682,6 +68682,32 @@
         <v>1120</v>
       </c>
       <c r="H2499" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2500">
+      <c r="A2500" s="1" t="n">
+        <v>45959.6911689815</v>
+      </c>
+      <c r="B2500" t="n">
+        <v>13315</v>
+      </c>
+      <c r="C2500" t="n">
+        <v>37.4000015258789</v>
+      </c>
+      <c r="D2500" t="n">
+        <v>36.4500007629395</v>
+      </c>
+      <c r="E2500" t="n">
+        <v>37.4000015258789</v>
+      </c>
+      <c r="F2500" t="n">
+        <v>36.6500015258789</v>
+      </c>
+      <c r="G2500" t="s">
+        <v>1119</v>
+      </c>
+      <c r="H2500" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LUVE.MI.xlsx
+++ b/data/LUVE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1121" uniqueCount="1121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="1122">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30043411254883</t>
+    <t xml:space="preserve">8.30043506622314</t>
   </si>
   <si>
     <t xml:space="preserve">LUVE.MI</t>
@@ -47,88 +47,88 @@
     <t xml:space="preserve">8.3170337677002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28383159637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09292316436768</t>
+    <t xml:space="preserve">8.28383255004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09292221069336</t>
   </si>
   <si>
     <t xml:space="preserve">8.19667816162109</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07631969451904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15102577209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17177677154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03896999359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08462142944336</t>
+    <t xml:space="preserve">8.07632160186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15102672576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17177772521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03897190093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08462238311768</t>
   </si>
   <si>
     <t xml:space="preserve">8.06802082061768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96841669082642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01821899414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99746942520142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91861391067505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91446399688721</t>
+    <t xml:space="preserve">7.96841621398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01821708679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99746704101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91861295700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91446447372437</t>
   </si>
   <si>
     <t xml:space="preserve">7.91031312942505</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88541269302368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87711095809937</t>
+    <t xml:space="preserve">7.88541078567505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87711000442505</t>
   </si>
   <si>
     <t xml:space="preserve">7.85220956802368</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64884901046753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7194037437439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70280265808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69035196304321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61979961395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55754375457764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55339527130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63639831542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76920557022095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80240774154663</t>
+    <t xml:space="preserve">7.64884996414185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71940231323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70280122756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69035243988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.619797706604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55754280090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55339431762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63639879226685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76920652389526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80240821838379</t>
   </si>
   <si>
     <t xml:space="preserve">7.93521451950073</t>
@@ -137,16 +137,16 @@
     <t xml:space="preserve">8.10122394561768</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05141925811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18422698974609</t>
+    <t xml:space="preserve">8.05142021179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18422794342041</t>
   </si>
   <si>
     <t xml:space="preserve">8.13442516326904</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00161838531494</t>
+    <t xml:space="preserve">8.00161743164062</t>
   </si>
   <si>
     <t xml:space="preserve">7.96011590957642</t>
@@ -155,25 +155,25 @@
     <t xml:space="preserve">8.21742820739746</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35853672027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32533550262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2921314239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20082855224609</t>
+    <t xml:space="preserve">8.35853576660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3253345489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29213237762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20082664489746</t>
   </si>
   <si>
     <t xml:space="preserve">8.15932559967041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30336475372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36267375946045</t>
+    <t xml:space="preserve">8.30336380004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36267280578613</t>
   </si>
   <si>
     <t xml:space="preserve">8.43045616149902</t>
@@ -182,25 +182,25 @@
     <t xml:space="preserve">8.15085315704346</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17627048492432</t>
+    <t xml:space="preserve">8.17627143859863</t>
   </si>
   <si>
     <t xml:space="preserve">8.2059268951416</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13390827178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11696338653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21863460540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21016311645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21439933776855</t>
+    <t xml:space="preserve">8.13390731811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11696243286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21863651275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21016216278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21440029144287</t>
   </si>
   <si>
     <t xml:space="preserve">8.20168972015381</t>
@@ -212,7 +212,7 @@
     <t xml:space="preserve">8.09154415130615</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10848808288574</t>
+    <t xml:space="preserve">8.10848712921143</t>
   </si>
   <si>
     <t xml:space="preserve">8.04918003082275</t>
@@ -221,10 +221,10 @@
     <t xml:space="preserve">7.9644513130188</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92208814620972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87972354888916</t>
+    <t xml:space="preserve">7.92208671569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87972259521484</t>
   </si>
   <si>
     <t xml:space="preserve">7.83735942840576</t>
@@ -236,46 +236,46 @@
     <t xml:space="preserve">7.93479633331299</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75262975692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71026706695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93903303146362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81194019317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79499435424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62553882598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66790199279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84583377838135</t>
+    <t xml:space="preserve">7.75263118743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71026611328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93903350830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81194067001343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79499483108521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62553834915161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66790294647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84583139419556</t>
   </si>
   <si>
     <t xml:space="preserve">8.19321727752686</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47282123565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51518535614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52365875244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5999116897583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78631496429443</t>
+    <t xml:space="preserve">8.47281932830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51518440246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52365779876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59991455078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78631401062012</t>
   </si>
   <si>
     <t xml:space="preserve">8.71853256225586</t>
@@ -287,25 +287,25 @@
     <t xml:space="preserve">8.54060363769531</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46858310699463</t>
+    <t xml:space="preserve">8.46858215332031</t>
   </si>
   <si>
     <t xml:space="preserve">8.46434688568115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5575475692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57449245452881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81173324584961</t>
+    <t xml:space="preserve">8.55754947662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57449340820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81173419952393</t>
   </si>
   <si>
     <t xml:space="preserve">8.72700500488281</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64227676391602</t>
+    <t xml:space="preserve">8.6422758102417</t>
   </si>
   <si>
     <t xml:space="preserve">8.89646053314209</t>
@@ -314,43 +314,43 @@
     <t xml:space="preserve">9.02355289459229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09980869293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06591796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1082820892334</t>
+    <t xml:space="preserve">9.09980964660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06591892242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10828304290771</t>
   </si>
   <si>
     <t xml:space="preserve">9.27773761749268</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1930103302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18453693389893</t>
+    <t xml:space="preserve">9.19300937652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18453788757324</t>
   </si>
   <si>
     <t xml:space="preserve">9.07439136505127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09133625030518</t>
+    <t xml:space="preserve">9.09133434295654</t>
   </si>
   <si>
     <t xml:space="preserve">9.30315685272217</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32010173797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12522983551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60817909240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40483093261719</t>
+    <t xml:space="preserve">9.32010269165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12522888183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60817813873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40482997894287</t>
   </si>
   <si>
     <t xml:space="preserve">9.48955917358398</t>
@@ -359,43 +359,43 @@
     <t xml:space="preserve">9.38788509368896</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53192234039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48108386993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44719409942627</t>
+    <t xml:space="preserve">9.5319242477417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4810848236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44719505310059</t>
   </si>
   <si>
     <t xml:space="preserve">9.54039573669434</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57428741455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47261428833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41330337524414</t>
+    <t xml:space="preserve">9.57428646087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47261238098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41330146789551</t>
   </si>
   <si>
     <t xml:space="preserve">9.42177581787109</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51497554779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5658130645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74374198913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.065710067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2521142959595</t>
+    <t xml:space="preserve">9.51497650146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56581497192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74374389648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0657110214233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2521133422852</t>
   </si>
   <si>
     <t xml:space="preserve">10.1334924697876</t>
@@ -404,16 +404,16 @@
     <t xml:space="preserve">9.99792766571045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95556449890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98098373413086</t>
+    <t xml:space="preserve">9.95556354522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98098182678223</t>
   </si>
   <si>
     <t xml:space="preserve">9.88778018951416</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91319942474365</t>
+    <t xml:space="preserve">9.91320037841797</t>
   </si>
   <si>
     <t xml:space="preserve">10.0148735046387</t>
@@ -422,94 +422,94 @@
     <t xml:space="preserve">10.1589117050171</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0402908325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70137786865234</t>
+    <t xml:space="preserve">10.0402927398682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70137882232666</t>
   </si>
   <si>
     <t xml:space="preserve">9.73527050018311</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70985126495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0826559066772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8623628616333</t>
+    <t xml:space="preserve">9.70985221862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0826549530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86236381530762</t>
   </si>
   <si>
     <t xml:space="preserve">10.1250200271606</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2944774627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4808788299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5317153930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5147686004639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8028450012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.912992477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8621559143066</t>
+    <t xml:space="preserve">10.2944765090942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4808778762817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5317163467407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5147695541382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.802845954895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9129934310913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8621549606323</t>
   </si>
   <si>
     <t xml:space="preserve">11.0146656036377</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0570316314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.277325630188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.438307762146</t>
+    <t xml:space="preserve">11.0570306777954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2773237228394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4383087158203</t>
   </si>
   <si>
     <t xml:space="preserve">11.6585998535156</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5823450088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4806728363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5908174514771</t>
+    <t xml:space="preserve">11.5823459625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4806709289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5908184051514</t>
   </si>
   <si>
     <t xml:space="preserve">11.7009649276733</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7772207260132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8111095428467</t>
+    <t xml:space="preserve">11.7772197723389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8111114501953</t>
   </si>
   <si>
     <t xml:space="preserve">11.8365297317505</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6670732498169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5992918014526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5230350494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6077632904053</t>
+    <t xml:space="preserve">11.6670751571655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.599289894104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5230360031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.607762336731</t>
   </si>
   <si>
     <t xml:space="preserve">11.6263809204102</t>
@@ -518,37 +518,37 @@
     <t xml:space="preserve">11.7297267913818</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6952781677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6780529022217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7986221313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.884744644165</t>
+    <t xml:space="preserve">11.6952791213989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6780557632446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.798623085022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8847455978394</t>
   </si>
   <si>
     <t xml:space="preserve">11.9105815887451</t>
   </si>
   <si>
-    <t xml:space="preserve">12.065598487854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3153514862061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3584146499634</t>
+    <t xml:space="preserve">12.0655994415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3153524398804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3584127426147</t>
   </si>
   <si>
     <t xml:space="preserve">12.0569887161255</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1431083679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9967041015625</t>
+    <t xml:space="preserve">12.1431093215942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9967031478882</t>
   </si>
   <si>
     <t xml:space="preserve">11.8416843414307</t>
@@ -557,94 +557,94 @@
     <t xml:space="preserve">11.7555627822876</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7125024795532</t>
+    <t xml:space="preserve">11.7125015258789</t>
   </si>
   <si>
     <t xml:space="preserve">11.8502969741821</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9191942214966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.962254524231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0397634506226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0483770370483</t>
+    <t xml:space="preserve">11.9191923141479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9622554779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0397624969482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0483741760254</t>
   </si>
   <si>
     <t xml:space="preserve">11.7900114059448</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0311527252197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9450283050537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8158483505249</t>
+    <t xml:space="preserve">12.0311517715454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.945029258728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8158493041992</t>
   </si>
   <si>
     <t xml:space="preserve">11.8933572769165</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8761348724365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8244600296021</t>
+    <t xml:space="preserve">11.8761329650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8244590759277</t>
   </si>
   <si>
     <t xml:space="preserve">11.8675203323364</t>
   </si>
   <si>
-    <t xml:space="preserve">11.901969909668</t>
+    <t xml:space="preserve">11.9019708633423</t>
   </si>
   <si>
     <t xml:space="preserve">11.927806854248</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7211141586304</t>
+    <t xml:space="preserve">11.7211151123047</t>
   </si>
   <si>
     <t xml:space="preserve">11.6694421768188</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6349945068359</t>
+    <t xml:space="preserve">11.6349925994873</t>
   </si>
   <si>
     <t xml:space="preserve">11.6091566085815</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5747089385986</t>
+    <t xml:space="preserve">11.5747079849243</t>
   </si>
   <si>
     <t xml:space="preserve">11.5316476821899</t>
   </si>
   <si>
-    <t xml:space="preserve">11.368016242981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3594055175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2818975448608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2302217483521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1957750320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.187162399292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1096525192261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0579805374146</t>
+    <t xml:space="preserve">11.3680171966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3594045639038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2818965911865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2302236557007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1957731246948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1871614456177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1096534729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0579814910889</t>
   </si>
   <si>
     <t xml:space="preserve">11.1785497665405</t>
@@ -653,85 +653,85 @@
     <t xml:space="preserve">11.126877784729</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9374113082886</t>
+    <t xml:space="preserve">10.9374094009399</t>
   </si>
   <si>
     <t xml:space="preserve">11.066593170166</t>
   </si>
   <si>
-    <t xml:space="preserve">11.023530960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.083815574646</t>
+    <t xml:space="preserve">11.0235319137573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0838174819946</t>
   </si>
   <si>
     <t xml:space="preserve">11.1354894638062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2043857574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3163433074951</t>
+    <t xml:space="preserve">11.2043876647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3163442611694</t>
   </si>
   <si>
     <t xml:space="preserve">11.4541387557983</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5402593612671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.411078453064</t>
+    <t xml:space="preserve">11.5402603149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4110774993896</t>
   </si>
   <si>
     <t xml:space="preserve">11.2905073165894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1613254547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2646713256836</t>
+    <t xml:space="preserve">11.1613245010376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2646722793579</t>
   </si>
   <si>
     <t xml:space="preserve">11.1527137756348</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0407571792603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4196920394897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2216110229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2388353347778</t>
+    <t xml:space="preserve">11.0407552719116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4196910858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2216100692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2388343811035</t>
   </si>
   <si>
     <t xml:space="preserve">11.3421821594238</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9546356201172</t>
+    <t xml:space="preserve">10.9546337127686</t>
   </si>
   <si>
     <t xml:space="preserve">10.96324634552</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0063076019287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0924291610718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74032402038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0169038772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21498394012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37861347198486</t>
+    <t xml:space="preserve">11.0063066482544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0924282073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74032497406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01690483093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2149829864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37861442565918</t>
   </si>
   <si>
     <t xml:space="preserve">9.49057197570801</t>
@@ -740,64 +740,64 @@
     <t xml:space="preserve">9.5077953338623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59391689300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60252952575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68865013122559</t>
+    <t xml:space="preserve">9.59391784667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60253143310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6886510848999</t>
   </si>
   <si>
     <t xml:space="preserve">9.56808090209961</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39583873748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34416675567627</t>
+    <t xml:space="preserve">9.39583778381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34416580200195</t>
   </si>
   <si>
     <t xml:space="preserve">9.2580451965332</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30110454559326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41306209564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28388118743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24081897735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12886142730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02551555633545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20637130737305</t>
+    <t xml:space="preserve">9.30110359191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41306304931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28388023376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24081993103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12886333465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02551651000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20637226104736</t>
   </si>
   <si>
     <t xml:space="preserve">9.26665687561035</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69726371765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65420341491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66281414031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64559173583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67142677307129</t>
+    <t xml:space="preserve">9.69726276397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65420246124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66281509399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64558887481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67142581939697</t>
   </si>
   <si>
     <t xml:space="preserve">9.75754737854004</t>
@@ -806,7 +806,7 @@
     <t xml:space="preserve">9.71448802947998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0944128036499</t>
+    <t xml:space="preserve">9.09441375732422</t>
   </si>
   <si>
     <t xml:space="preserve">8.93939590454102</t>
@@ -818,40 +818,40 @@
     <t xml:space="preserve">9.12024974822998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83505630493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73171234130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90395450592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77477264404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53363037109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49918460845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57669448852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58530521392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47334671020508</t>
+    <t xml:space="preserve">9.83505821228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73171138763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90395355224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77477169036865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53363227844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49918365478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57669353485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58530426025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47334766387939</t>
   </si>
   <si>
     <t xml:space="preserve">9.4302864074707</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54224395751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1719217300415</t>
+    <t xml:space="preserve">9.54224491119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17192268371582</t>
   </si>
   <si>
     <t xml:space="preserve">9.23220825195312</t>
@@ -860,16 +860,16 @@
     <t xml:space="preserve">9.55946922302246</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51640701293945</t>
+    <t xml:space="preserve">9.51640796661377</t>
   </si>
   <si>
     <t xml:space="preserve">9.86089324951172</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95661926269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91355895996094</t>
+    <t xml:space="preserve">8.95662021636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91355800628662</t>
   </si>
   <si>
     <t xml:space="preserve">9.08580207824707</t>
@@ -878,13 +878,13 @@
     <t xml:space="preserve">9.04274082183838</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99967956542969</t>
+    <t xml:space="preserve">8.999680519104</t>
   </si>
   <si>
     <t xml:space="preserve">8.82743740081787</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69825649261475</t>
+    <t xml:space="preserve">8.69825553894043</t>
   </si>
   <si>
     <t xml:space="preserve">8.87049961090088</t>
@@ -893,22 +893,22 @@
     <t xml:space="preserve">8.7843770980835</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7413158416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61213302612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59490871429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65519523620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45711421966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06314563751221</t>
+    <t xml:space="preserve">8.74131679534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61213493347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59490966796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65519428253174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45711517333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06314468383789</t>
   </si>
   <si>
     <t xml:space="preserve">9.10714054107666</t>
@@ -920,22 +920,22 @@
     <t xml:space="preserve">8.97515296936035</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93115711212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88716220855713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84316539764404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76397132873535</t>
+    <t xml:space="preserve">8.93115615844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88716125488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84316730499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76397323608398</t>
   </si>
   <si>
     <t xml:space="preserve">8.48240089416504</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71117782592773</t>
+    <t xml:space="preserve">8.71117877960205</t>
   </si>
   <si>
     <t xml:space="preserve">8.6231861114502</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">8.58798980712891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6583833694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60558795928955</t>
+    <t xml:space="preserve">8.65838241577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60558891296387</t>
   </si>
   <si>
     <t xml:space="preserve">8.7287769317627</t>
@@ -956,13 +956,13 @@
     <t xml:space="preserve">8.69357967376709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74637508392334</t>
+    <t xml:space="preserve">8.74637413024902</t>
   </si>
   <si>
     <t xml:space="preserve">8.53519439697266</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44720363616943</t>
+    <t xml:space="preserve">8.4472017288208</t>
   </si>
   <si>
     <t xml:space="preserve">8.27121925354004</t>
@@ -971,64 +971,64 @@
     <t xml:space="preserve">8.32401466369629</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28881645202637</t>
+    <t xml:space="preserve">8.288818359375</t>
   </si>
   <si>
     <t xml:space="preserve">8.78157043457031</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64078330993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79916858673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67598056793213</t>
+    <t xml:space="preserve">8.64078426361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79917049407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67598152160645</t>
   </si>
   <si>
     <t xml:space="preserve">9.23912811279297</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37111473083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32711887359619</t>
+    <t xml:space="preserve">9.37111568450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32712078094482</t>
   </si>
   <si>
     <t xml:space="preserve">9.19513130187988</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15113639831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46480083465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41200542449951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49999809265137</t>
+    <t xml:space="preserve">9.15113544464111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46480178833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41200637817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49999713897705</t>
   </si>
   <si>
     <t xml:space="preserve">8.34161186218262</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23602294921875</t>
+    <t xml:space="preserve">8.23602199554443</t>
   </si>
   <si>
     <t xml:space="preserve">8.30641555786133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13043212890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18322849273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16562843322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21842384338379</t>
+    <t xml:space="preserve">8.13043117523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1832275390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16562938690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21842479705811</t>
   </si>
   <si>
     <t xml:space="preserve">8.25362110137939</t>
@@ -1046,28 +1046,28 @@
     <t xml:space="preserve">9.41511154174805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63508987426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59109497070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8990650177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1190452575684</t>
+    <t xml:space="preserve">9.63509082794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59109401702881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89906597137451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1190462112427</t>
   </si>
   <si>
     <t xml:space="preserve">10.1630401611328</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2070360183716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3390245437622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2950286865234</t>
+    <t xml:space="preserve">10.2070369720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3390235900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2950296401978</t>
   </si>
   <si>
     <t xml:space="preserve">10.383020401001</t>
@@ -1079,10 +1079,10 @@
     <t xml:space="preserve">10.4270162582397</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0750484466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.515007019043</t>
+    <t xml:space="preserve">10.0750494003296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5150060653687</t>
   </si>
   <si>
     <t xml:space="preserve">10.6498155593872</t>
@@ -1103,19 +1103,19 @@
     <t xml:space="preserve">10.2453918457031</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0656499862671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4251356124878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5150079727173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3352642059326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2903270721436</t>
+    <t xml:space="preserve">10.0656471252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4251365661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5150089263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3352651596069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2903280258179</t>
   </si>
   <si>
     <t xml:space="preserve">10.2004566192627</t>
@@ -1124,28 +1124,28 @@
     <t xml:space="preserve">9.97577667236328</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1105833053589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93083953857422</t>
+    <t xml:space="preserve">10.1105842590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93084049224854</t>
   </si>
   <si>
     <t xml:space="preserve">9.88590431213379</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1555213928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.020712852478</t>
+    <t xml:space="preserve">10.1555204391479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0207138061523</t>
   </si>
   <si>
     <t xml:space="preserve">9.75109767913818</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70616149902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3466739654541</t>
+    <t xml:space="preserve">9.70616054534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34667301177979</t>
   </si>
   <si>
     <t xml:space="preserve">9.30173778533936</t>
@@ -1160,100 +1160,100 @@
     <t xml:space="preserve">9.61628913879395</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52641677856445</t>
+    <t xml:space="preserve">9.52641868591309</t>
   </si>
   <si>
     <t xml:space="preserve">9.43654537200928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12199401855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0321216583252</t>
+    <t xml:space="preserve">9.12199306488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03212356567383</t>
   </si>
   <si>
     <t xml:space="preserve">9.16693019866943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07705879211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25680255889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98718547821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57135200500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66122627258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79603290557861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9643678665161</t>
+    <t xml:space="preserve">9.07705783843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25680160522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98718738555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5713529586792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66122531890869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7960319519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9643669128418</t>
   </si>
   <si>
     <t xml:space="preserve">11.4586629867554</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5035982131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2339820861816</t>
+    <t xml:space="preserve">11.5035991668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2339811325073</t>
   </si>
   <si>
     <t xml:space="preserve">11.1441106796265</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9194307327271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8744964599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0093030929565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2789192199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4137268066406</t>
+    <t xml:space="preserve">10.9194316864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8744955062866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0093040466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2789182662964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4137258529663</t>
   </si>
   <si>
     <t xml:space="preserve">11.5485343933105</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6833429336548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7732152938843</t>
+    <t xml:space="preserve">11.6833410263062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.77321434021</t>
   </si>
   <si>
     <t xml:space="preserve">11.9080219268799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.132700920105</t>
+    <t xml:space="preserve">12.1327018737793</t>
   </si>
   <si>
     <t xml:space="preserve">11.9978942871094</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8181486129761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.593469619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3124437332153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5820617675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9415473937988</t>
+    <t xml:space="preserve">11.8181495666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5934705734253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3124446868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5820598602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9415493011475</t>
   </si>
   <si>
     <t xml:space="preserve">12.8067407608032</t>
@@ -1265,10 +1265,10 @@
     <t xml:space="preserve">13.0763559341431</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4472532272339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5371246337891</t>
+    <t xml:space="preserve">12.4472541809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5371236801147</t>
   </si>
   <si>
     <t xml:space="preserve">12.2675085067749</t>
@@ -1277,64 +1277,64 @@
     <t xml:space="preserve">12.4023170471191</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6269969940186</t>
+    <t xml:space="preserve">12.6269979476929</t>
   </si>
   <si>
     <t xml:space="preserve">12.6719312667847</t>
   </si>
   <si>
-    <t xml:space="preserve">12.896614074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7282781600952</t>
+    <t xml:space="preserve">12.8966131210327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7282772064209</t>
   </si>
   <si>
     <t xml:space="preserve">10.7846231460571</t>
   </si>
   <si>
-    <t xml:space="preserve">10.559944152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89731407165527</t>
+    <t xml:space="preserve">10.5599431991577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89731502532959</t>
   </si>
   <si>
     <t xml:space="preserve">7.98062181472778</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81885194778442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53126192092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89074850082397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53782653808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96264696121216</t>
+    <t xml:space="preserve">7.81885147094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53126239776611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89074897766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53782749176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96264553070068</t>
   </si>
   <si>
     <t xml:space="preserve">8.44795513153076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6097240447998</t>
+    <t xml:space="preserve">8.60972499847412</t>
   </si>
   <si>
     <t xml:space="preserve">8.66364860534668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86136531829834</t>
+    <t xml:space="preserve">8.86136627197266</t>
   </si>
   <si>
     <t xml:space="preserve">9.21186542510986</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93848991394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80045318603516</t>
+    <t xml:space="preserve">9.9384880065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80045509338379</t>
   </si>
   <si>
     <t xml:space="preserve">9.89247798919678</t>
@@ -1343,28 +1343,28 @@
     <t xml:space="preserve">9.66242027282715</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7084321975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84646701812744</t>
+    <t xml:space="preserve">9.70843315124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84646606445312</t>
   </si>
   <si>
     <t xml:space="preserve">10.1225357055664</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75444412231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3986043930054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3065824508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7206840515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5826511383057</t>
+    <t xml:space="preserve">9.75444507598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3986053466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3065814971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.720685005188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5826501846313</t>
   </si>
   <si>
     <t xml:space="preserve">10.8587207794189</t>
@@ -1373,25 +1373,25 @@
     <t xml:space="preserve">10.6746740341187</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9967546463013</t>
+    <t xml:space="preserve">10.996753692627</t>
   </si>
   <si>
     <t xml:space="preserve">10.628662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7666969299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4906272888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1347894668579</t>
+    <t xml:space="preserve">10.766697883606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4906282424927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1347904205322</t>
   </si>
   <si>
     <t xml:space="preserve">11.3188352584839</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5028810501099</t>
+    <t xml:space="preserve">11.5028800964355</t>
   </si>
   <si>
     <t xml:space="preserve">11.1808004379272</t>
@@ -1406,19 +1406,19 @@
     <t xml:space="preserve">10.9507417678833</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0887765884399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8127098083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9047327041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4108591079712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4568700790405</t>
+    <t xml:space="preserve">11.0887784957886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8127088546753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9047317504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4108581542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4568691253662</t>
   </si>
   <si>
     <t xml:space="preserve">11.2268123626709</t>
@@ -1436,16 +1436,16 @@
     <t xml:space="preserve">11.6869277954102</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9629974365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7789506912231</t>
+    <t xml:space="preserve">11.9629964828491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7789516448975</t>
   </si>
   <si>
     <t xml:space="preserve">12.0090084075928</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1010303497314</t>
+    <t xml:space="preserve">12.1010313034058</t>
   </si>
   <si>
     <t xml:space="preserve">11.7329397201538</t>
@@ -1454,22 +1454,22 @@
     <t xml:space="preserve">11.8249626159668</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0550203323364</t>
+    <t xml:space="preserve">12.0550193786621</t>
   </si>
   <si>
     <t xml:space="preserve">11.8709735870361</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9169845581055</t>
+    <t xml:space="preserve">11.9169855117798</t>
   </si>
   <si>
     <t xml:space="preserve">11.6409158706665</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1470432281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6991815567017</t>
+    <t xml:space="preserve">12.1470422744751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.699182510376</t>
   </si>
   <si>
     <t xml:space="preserve">12.7912034988403</t>
@@ -1478,19 +1478,19 @@
     <t xml:space="preserve">13.0672731399536</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8832273483276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9292402267456</t>
+    <t xml:space="preserve">12.8832263946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9292392730713</t>
   </si>
   <si>
     <t xml:space="preserve">13.2053089141846</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2513189315796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1132860183716</t>
+    <t xml:space="preserve">13.2513198852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1132841110229</t>
   </si>
   <si>
     <t xml:space="preserve">13.1592969894409</t>
@@ -1499,43 +1499,43 @@
     <t xml:space="preserve">13.3893537521362</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2973299026489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9752492904663</t>
+    <t xml:space="preserve">13.2973318099976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9752502441406</t>
   </si>
   <si>
     <t xml:space="preserve">13.7114343643188</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4353656768799</t>
+    <t xml:space="preserve">13.4353666305542</t>
   </si>
   <si>
     <t xml:space="preserve">12.5151348114014</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3770999908447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.837215423584</t>
+    <t xml:space="preserve">12.377100944519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8372144699097</t>
   </si>
   <si>
     <t xml:space="preserve">12.7451934814453</t>
   </si>
   <si>
-    <t xml:space="preserve">12.653169631958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3433418273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6194124221802</t>
+    <t xml:space="preserve">12.6531705856323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3433427810669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6194114685059</t>
   </si>
   <si>
     <t xml:space="preserve">13.8494691848755</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9414911270142</t>
+    <t xml:space="preserve">13.9414920806885</t>
   </si>
   <si>
     <t xml:space="preserve">14.1715497970581</t>
@@ -1544,22 +1544,22 @@
     <t xml:space="preserve">14.3555955886841</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1255378723145</t>
+    <t xml:space="preserve">14.1255388259888</t>
   </si>
   <si>
     <t xml:space="preserve">14.4936304092407</t>
   </si>
   <si>
-    <t xml:space="preserve">14.723687171936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.677677154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.815710067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8617219924927</t>
+    <t xml:space="preserve">14.7236881256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6776762008667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8157119750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.861722946167</t>
   </si>
   <si>
     <t xml:space="preserve">15.0457696914673</t>
@@ -1574,10 +1574,10 @@
     <t xml:space="preserve">14.4476184844971</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2635726928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9875049591064</t>
+    <t xml:space="preserve">14.2635736465454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9875040054321</t>
   </si>
   <si>
     <t xml:space="preserve">14.3095846176147</t>
@@ -1586,19 +1586,19 @@
     <t xml:space="preserve">13.6654233932495</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8034582138062</t>
+    <t xml:space="preserve">13.8034572601318</t>
   </si>
   <si>
     <t xml:space="preserve">13.5733995437622</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7574453353882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9537467956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0335159301758</t>
+    <t xml:space="preserve">13.7574462890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.95374584198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0335149765015</t>
   </si>
   <si>
     <t xml:space="preserve">14.4269771575928</t>
@@ -1610,13 +1610,13 @@
     <t xml:space="preserve">14.473819732666</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7080240249634</t>
+    <t xml:space="preserve">14.7080230712891</t>
   </si>
   <si>
     <t xml:space="preserve">14.8485460281372</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0359086990356</t>
+    <t xml:space="preserve">15.03590965271</t>
   </si>
   <si>
     <t xml:space="preserve">15.0827503204346</t>
@@ -1628,10 +1628,10 @@
     <t xml:space="preserve">14.9422273635864</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1764316558838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1295909881592</t>
+    <t xml:space="preserve">15.1764326095581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1295900344849</t>
   </si>
   <si>
     <t xml:space="preserve">14.989068031311</t>
@@ -1640,7 +1640,7 @@
     <t xml:space="preserve">14.6611814498901</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3169546127319</t>
+    <t xml:space="preserve">15.3169555664062</t>
   </si>
   <si>
     <t xml:space="preserve">14.7548637390137</t>
@@ -1649,7 +1649,7 @@
     <t xml:space="preserve">14.8017053604126</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2232713699341</t>
+    <t xml:space="preserve">15.2232723236084</t>
   </si>
   <si>
     <t xml:space="preserve">15.5043172836304</t>
@@ -1658,28 +1658,28 @@
     <t xml:space="preserve">16.0664081573486</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6916799545288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7385215759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9727230072021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9258861541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7853622436523</t>
+    <t xml:space="preserve">15.6916809082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7385206222534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9727249145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9258842468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7853631973267</t>
   </si>
   <si>
     <t xml:space="preserve">16.1132488250732</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8322019577026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5348167419434</t>
+    <t xml:space="preserve">15.8322038650513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5348148345947</t>
   </si>
   <si>
     <t xml:space="preserve">16.8627014160156</t>
@@ -1688,16 +1688,16 @@
     <t xml:space="preserve">17.1437454223633</t>
   </si>
   <si>
-    <t xml:space="preserve">16.581657409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2069301605225</t>
+    <t xml:space="preserve">16.5816593170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2069282531738</t>
   </si>
   <si>
     <t xml:space="preserve">17.2842712402344</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7995185852051</t>
+    <t xml:space="preserve">17.7995204925537</t>
   </si>
   <si>
     <t xml:space="preserve">17.4716320037842</t>
@@ -1706,7 +1706,7 @@
     <t xml:space="preserve">16.8158626556396</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6284980773926</t>
+    <t xml:space="preserve">16.6284961700439</t>
   </si>
   <si>
     <t xml:space="preserve">17.0969066619873</t>
@@ -1718,22 +1718,22 @@
     <t xml:space="preserve">17.6121559143066</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0337219238281</t>
+    <t xml:space="preserve">18.0337238311768</t>
   </si>
   <si>
     <t xml:space="preserve">18.5489711761475</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7363357543945</t>
+    <t xml:space="preserve">18.7363376617432</t>
   </si>
   <si>
     <t xml:space="preserve">18.923698425293</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7668342590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5794677734375</t>
+    <t xml:space="preserve">19.7668361663818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5794696807861</t>
   </si>
   <si>
     <t xml:space="preserve">19.2047443389893</t>
@@ -1742,13 +1742,13 @@
     <t xml:space="preserve">19.1110610961914</t>
   </si>
   <si>
-    <t xml:space="preserve">19.673152923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2984237670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4857864379883</t>
+    <t xml:space="preserve">19.6731510162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2984256744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4857883453369</t>
   </si>
   <si>
     <t xml:space="preserve">19.8605175018311</t>
@@ -1760,7 +1760,7 @@
     <t xml:space="preserve">20.9846954345703</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2657413482666</t>
+    <t xml:space="preserve">21.265739440918</t>
   </si>
   <si>
     <t xml:space="preserve">21.0783767700195</t>
@@ -1778,13 +1778,13 @@
     <t xml:space="preserve">22.1088771820068</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7341480255127</t>
+    <t xml:space="preserve">21.7341499328613</t>
   </si>
   <si>
     <t xml:space="preserve">22.015193939209</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2962398529053</t>
+    <t xml:space="preserve">22.296236038208</t>
   </si>
   <si>
     <t xml:space="preserve">22.4836025238037</t>
@@ -1793,10 +1793,10 @@
     <t xml:space="preserve">21.6404685974121</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5467834472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2352428436279</t>
+    <t xml:space="preserve">21.5467853546143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2352409362793</t>
   </si>
   <si>
     <t xml:space="preserve">18.3147678375244</t>
@@ -1808,7 +1808,7 @@
     <t xml:space="preserve">20.6099681854248</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9215106964111</t>
+    <t xml:space="preserve">21.9215145111084</t>
   </si>
   <si>
     <t xml:space="preserve">22.7646465301514</t>
@@ -1820,7 +1820,7 @@
     <t xml:space="preserve">21.1720600128174</t>
   </si>
   <si>
-    <t xml:space="preserve">20.703649520874</t>
+    <t xml:space="preserve">20.7036514282227</t>
   </si>
   <si>
     <t xml:space="preserve">21.3594207763672</t>
@@ -1838,7 +1838,7 @@
     <t xml:space="preserve">22.2025585174561</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3899211883545</t>
+    <t xml:space="preserve">22.3899192810059</t>
   </si>
   <si>
     <t xml:space="preserve">19.9541969299316</t>
@@ -1847,43 +1847,43 @@
     <t xml:space="preserve">20.4226055145264</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8910140991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3921089172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8300170898438</t>
+    <t xml:space="preserve">20.8910160064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3921070098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8300189971924</t>
   </si>
   <si>
     <t xml:space="preserve">18.361608505249</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9563846588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6589965820312</t>
+    <t xml:space="preserve">16.9563827514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6589946746826</t>
   </si>
   <si>
     <t xml:space="preserve">17.7526779174805</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3779487609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8932018280029</t>
+    <t xml:space="preserve">17.377950668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8931999206543</t>
   </si>
   <si>
     <t xml:space="preserve">17.9400405883789</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2679252624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8768577575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6426544189453</t>
+    <t xml:space="preserve">18.2679271697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8768558502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6426525115967</t>
   </si>
   <si>
     <t xml:space="preserve">18.3241367340088</t>
@@ -1892,7 +1892,7 @@
     <t xml:space="preserve">18.2117176055908</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2304515838623</t>
+    <t xml:space="preserve">18.2304553985596</t>
   </si>
   <si>
     <t xml:space="preserve">18.4552898406982</t>
@@ -1904,7 +1904,7 @@
     <t xml:space="preserve">18.1180362701416</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9705390930176</t>
+    <t xml:space="preserve">18.9705410003662</t>
   </si>
   <si>
     <t xml:space="preserve">20.2820835113525</t>
@@ -1913,10 +1913,10 @@
     <t xml:space="preserve">20.0947208404541</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1883983612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1415615081787</t>
+    <t xml:space="preserve">20.1884021759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1415596008301</t>
   </si>
   <si>
     <t xml:space="preserve">18.4927616119385</t>
@@ -1925,7 +1925,7 @@
     <t xml:space="preserve">17.5559463500977</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1999549865723</t>
+    <t xml:space="preserve">17.1999568939209</t>
   </si>
   <si>
     <t xml:space="preserve">16.8847980499268</t>
@@ -1937,13 +1937,13 @@
     <t xml:space="preserve">18.0308246612549</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9285449981689</t>
+    <t xml:space="preserve">18.9285469055176</t>
   </si>
   <si>
     <t xml:space="preserve">18.4319343566895</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6038379669189</t>
+    <t xml:space="preserve">18.6038398742676</t>
   </si>
   <si>
     <t xml:space="preserve">19.1004505157471</t>
@@ -1952,16 +1952,16 @@
     <t xml:space="preserve">18.9858474731445</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1482009887695</t>
+    <t xml:space="preserve">19.1481990814209</t>
   </si>
   <si>
     <t xml:space="preserve">18.90944480896</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9476470947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0077228546143</t>
+    <t xml:space="preserve">18.9476490020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0077247619629</t>
   </si>
   <si>
     <t xml:space="preserve">20.0554733276367</t>
@@ -1970,19 +1970,19 @@
     <t xml:space="preserve">20.5329856872559</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9149913787842</t>
+    <t xml:space="preserve">20.9149932861328</t>
   </si>
   <si>
     <t xml:space="preserve">20.1509761810303</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4374809265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0104942321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4880065917969</t>
+    <t xml:space="preserve">20.4374828338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0104961395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4880084991455</t>
   </si>
   <si>
     <t xml:space="preserve">19.5779628753662</t>
@@ -1997,13 +1997,13 @@
     <t xml:space="preserve">19.2914562225342</t>
   </si>
   <si>
-    <t xml:space="preserve">19.339204788208</t>
+    <t xml:space="preserve">19.3392066955566</t>
   </si>
   <si>
     <t xml:space="preserve">18.813943862915</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6993408203125</t>
+    <t xml:space="preserve">18.6993389129639</t>
   </si>
   <si>
     <t xml:space="preserve">19.3869571685791</t>
@@ -2012,31 +2012,31 @@
     <t xml:space="preserve">18.852144241333</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0813484191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2409324645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7757415771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9599685668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4852333068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1059989929199</t>
+    <t xml:space="preserve">19.0813503265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.240930557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7757434844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9599704742432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4852352142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1059970855713</t>
   </si>
   <si>
     <t xml:space="preserve">21.8700160980225</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3925037384033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1537494659424</t>
+    <t xml:space="preserve">21.392505645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1537475585938</t>
   </si>
   <si>
     <t xml:space="preserve">21.7745132446289</t>
@@ -2054,16 +2054,16 @@
     <t xml:space="preserve">21.7267627716064</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5835113525391</t>
+    <t xml:space="preserve">21.5835094451904</t>
   </si>
   <si>
     <t xml:space="preserve">20.5807342529297</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1032238006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6257133483887</t>
+    <t xml:space="preserve">20.1032218933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.62571144104</t>
   </si>
   <si>
     <t xml:space="preserve">19.8644676208496</t>
@@ -2072,16 +2072,16 @@
     <t xml:space="preserve">21.2492504119873</t>
   </si>
   <si>
-    <t xml:space="preserve">22.920539855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4430294036865</t>
+    <t xml:space="preserve">22.9205417633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4430313110352</t>
   </si>
   <si>
     <t xml:space="preserve">22.1565227508545</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0610218048096</t>
+    <t xml:space="preserve">22.0610198974609</t>
   </si>
   <si>
     <t xml:space="preserve">22.3475284576416</t>
@@ -2090,7 +2090,7 @@
     <t xml:space="preserve">21.0582466125488</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3897323608398</t>
+    <t xml:space="preserve">20.3897304534912</t>
   </si>
   <si>
     <t xml:space="preserve">20.2942276000977</t>
@@ -2105,7 +2105,7 @@
     <t xml:space="preserve">20.8672428131104</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0499248504639</t>
+    <t xml:space="preserve">18.0499267578125</t>
   </si>
   <si>
     <t xml:space="preserve">18.833044052124</t>
@@ -2120,7 +2120,7 @@
     <t xml:space="preserve">19.8167171478271</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2464771270752</t>
+    <t xml:space="preserve">20.2464790344238</t>
   </si>
   <si>
     <t xml:space="preserve">20.6762371063232</t>
@@ -2141,10 +2141,10 @@
     <t xml:space="preserve">22.7295341491699</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5862827301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8727893829346</t>
+    <t xml:space="preserve">22.5862808227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8727912902832</t>
   </si>
   <si>
     <t xml:space="preserve">22.5385322570801</t>
@@ -2156,58 +2156,58 @@
     <t xml:space="preserve">23.0160427093506</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3025512695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4485778808594</t>
+    <t xml:space="preserve">23.3025493621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4485759735107</t>
   </si>
   <si>
     <t xml:space="preserve">23.7323112487793</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9710655212402</t>
+    <t xml:space="preserve">23.9710636138916</t>
   </si>
   <si>
     <t xml:space="preserve">24.2098217010498</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0665664672852</t>
+    <t xml:space="preserve">24.0665683746338</t>
   </si>
   <si>
     <t xml:space="preserve">24.1143188476562</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4008235931396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3080959320068</t>
+    <t xml:space="preserve">24.4008255004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3080978393555</t>
   </si>
   <si>
     <t xml:space="preserve">23.7800598144531</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9233131408691</t>
+    <t xml:space="preserve">23.9233150482178</t>
   </si>
   <si>
     <t xml:space="preserve">25.0693416595459</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5440788269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9260883331299</t>
+    <t xml:space="preserve">24.5440807342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9260864257812</t>
   </si>
   <si>
     <t xml:space="preserve">25.3558464050293</t>
   </si>
   <si>
-    <t xml:space="preserve">25.403600692749</t>
+    <t xml:space="preserve">25.4035987854004</t>
   </si>
   <si>
     <t xml:space="preserve">25.8333587646484</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8838844299316</t>
+    <t xml:space="preserve">26.883882522583</t>
   </si>
   <si>
     <t xml:space="preserve">26.7883815765381</t>
@@ -2222,19 +2222,19 @@
     <t xml:space="preserve">24.8305854797363</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2603454589844</t>
+    <t xml:space="preserve">25.260347366333</t>
   </si>
   <si>
     <t xml:space="preserve">25.7378578186035</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7856063842773</t>
+    <t xml:space="preserve">25.7856101989746</t>
   </si>
   <si>
     <t xml:space="preserve">26.0721130371094</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2631187438965</t>
+    <t xml:space="preserve">26.2631206512451</t>
   </si>
   <si>
     <t xml:space="preserve">25.4513492584229</t>
@@ -2243,7 +2243,7 @@
     <t xml:space="preserve">25.928861618042</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5946044921875</t>
+    <t xml:space="preserve">25.5946025848389</t>
   </si>
   <si>
     <t xml:space="preserve">25.6901073455811</t>
@@ -2252,10 +2252,10 @@
     <t xml:space="preserve">25.5468521118164</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4541263580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.740629196167</t>
+    <t xml:space="preserve">26.4541244506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7406311035156</t>
   </si>
   <si>
     <t xml:space="preserve">27.0748901367188</t>
@@ -2264,13 +2264,13 @@
     <t xml:space="preserve">27.1703929901123</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6506748199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3219661712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8922023773193</t>
+    <t xml:space="preserve">28.6506767272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.321964263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.892204284668</t>
   </si>
   <si>
     <t xml:space="preserve">29.9877071380615</t>
@@ -2288,7 +2288,7 @@
     <t xml:space="preserve">28.5074214935303</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3191928863525</t>
+    <t xml:space="preserve">29.3191909790039</t>
   </si>
   <si>
     <t xml:space="preserve">28.9371814727783</t>
@@ -2300,70 +2300,70 @@
     <t xml:space="preserve">29.223690032959</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1281852722168</t>
+    <t xml:space="preserve">29.1281871795654</t>
   </si>
   <si>
     <t xml:space="preserve">29.1759376525879</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0804386138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6984252929688</t>
+    <t xml:space="preserve">29.080436706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6984272003174</t>
   </si>
   <si>
     <t xml:space="preserve">28.9849338531494</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3641700744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8866577148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2714385986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8389072418213</t>
+    <t xml:space="preserve">28.3641681671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8866596221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2714405059814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8389053344727</t>
   </si>
   <si>
     <t xml:space="preserve">27.6479034423828</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6029262542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4119186401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3669414520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4146938323975</t>
+    <t xml:space="preserve">28.6029243469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4119205474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.366943359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4146919250488</t>
   </si>
   <si>
     <t xml:space="preserve">30.0354595184326</t>
   </si>
   <si>
-    <t xml:space="preserve">29.748950958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7039756774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2742156982422</t>
+    <t xml:space="preserve">29.7489490509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7039737701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2742137908936</t>
   </si>
   <si>
     <t xml:space="preserve">29.7012023925781</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5579490661621</t>
+    <t xml:space="preserve">29.5579471588135</t>
   </si>
   <si>
     <t xml:space="preserve">29.796703338623</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2209148406982</t>
+    <t xml:space="preserve">28.2209167480469</t>
   </si>
   <si>
     <t xml:space="preserve">28.3164176940918</t>
@@ -2375,10 +2375,10 @@
     <t xml:space="preserve">26.9480724334717</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5770225524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5930156707764</t>
+    <t xml:space="preserve">27.5770206451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.593017578125</t>
   </si>
   <si>
     <t xml:space="preserve">28.0124492645264</t>
@@ -2396,7 +2396,7 @@
     <t xml:space="preserve">28.0608291625977</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3994960784912</t>
+    <t xml:space="preserve">28.3994941711426</t>
   </si>
   <si>
     <t xml:space="preserve">28.7381591796875</t>
@@ -2405,7 +2405,7 @@
     <t xml:space="preserve">29.1252059936523</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9800643920898</t>
+    <t xml:space="preserve">28.9800624847412</t>
   </si>
   <si>
     <t xml:space="preserve">27.7705459594727</t>
@@ -2447,19 +2447,19 @@
     <t xml:space="preserve">29.2219676971436</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0284423828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2543525695801</t>
+    <t xml:space="preserve">29.0284442901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2543544769287</t>
   </si>
   <si>
     <t xml:space="preserve">29.705774307251</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0444393157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.996057510376</t>
+    <t xml:space="preserve">30.0444374084473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9960594177246</t>
   </si>
   <si>
     <t xml:space="preserve">28.8349208831787</t>
@@ -2474,7 +2474,7 @@
     <t xml:space="preserve">28.2059707641602</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4962558746338</t>
+    <t xml:space="preserve">28.4962577819824</t>
   </si>
   <si>
     <t xml:space="preserve">27.0932140350342</t>
@@ -2483,7 +2483,7 @@
     <t xml:space="preserve">26.8513107299805</t>
   </si>
   <si>
-    <t xml:space="preserve">26.077220916748</t>
+    <t xml:space="preserve">26.0772190093994</t>
   </si>
   <si>
     <t xml:space="preserve">26.8996906280518</t>
@@ -2507,22 +2507,22 @@
     <t xml:space="preserve">25.3031272888184</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2547473907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1579856872559</t>
+    <t xml:space="preserve">25.2547454833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1579837799072</t>
   </si>
   <si>
     <t xml:space="preserve">24.9160804748535</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4966487884521</t>
+    <t xml:space="preserve">25.4966506958008</t>
   </si>
   <si>
     <t xml:space="preserve">25.3515071868896</t>
   </si>
   <si>
-    <t xml:space="preserve">25.061222076416</t>
+    <t xml:space="preserve">25.0612239837646</t>
   </si>
   <si>
     <t xml:space="preserve">24.7225570678711</t>
@@ -2531,7 +2531,7 @@
     <t xml:space="preserve">24.4806537628174</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6098022460938</t>
+    <t xml:space="preserve">23.6098003387451</t>
   </si>
   <si>
     <t xml:space="preserve">23.0292301177979</t>
@@ -2540,7 +2540,7 @@
     <t xml:space="preserve">22.9324722290039</t>
   </si>
   <si>
-    <t xml:space="preserve">23.174373626709</t>
+    <t xml:space="preserve">23.1743755340576</t>
   </si>
   <si>
     <t xml:space="preserve">22.5938053131104</t>
@@ -2552,7 +2552,7 @@
     <t xml:space="preserve">21.6745719909668</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9164733886719</t>
+    <t xml:space="preserve">21.9164752960205</t>
   </si>
   <si>
     <t xml:space="preserve">21.5294284820557</t>
@@ -2564,16 +2564,16 @@
     <t xml:space="preserve">21.0940017700195</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4650535583496</t>
+    <t xml:space="preserve">20.465051651001</t>
   </si>
   <si>
     <t xml:space="preserve">20.2231483459473</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4166717529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9004802703857</t>
+    <t xml:space="preserve">20.4166736602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9004783630371</t>
   </si>
   <si>
     <t xml:space="preserve">20.8037185668945</t>
@@ -2582,22 +2582,22 @@
     <t xml:space="preserve">20.6101951599121</t>
   </si>
   <si>
-    <t xml:space="preserve">20.658576965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7069549560547</t>
+    <t xml:space="preserve">20.6585750579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7069568634033</t>
   </si>
   <si>
     <t xml:space="preserve">20.7553386688232</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3359050750732</t>
+    <t xml:space="preserve">21.3359069824219</t>
   </si>
   <si>
     <t xml:space="preserve">21.0456218719482</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4490566253662</t>
+    <t xml:space="preserve">19.4490585327148</t>
   </si>
   <si>
     <t xml:space="preserve">19.8361034393311</t>
@@ -2606,7 +2606,7 @@
     <t xml:space="preserve">19.2361812591553</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8878421783447</t>
+    <t xml:space="preserve">18.8878402709961</t>
   </si>
   <si>
     <t xml:space="preserve">18.6362609863281</t>
@@ -2630,13 +2630,13 @@
     <t xml:space="preserve">17.049373626709</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0300216674805</t>
+    <t xml:space="preserve">17.0300197601318</t>
   </si>
   <si>
     <t xml:space="preserve">16.8752021789551</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3266258239746</t>
+    <t xml:space="preserve">18.326623916626</t>
   </si>
   <si>
     <t xml:space="preserve">18.7717266082764</t>
@@ -2648,13 +2648,13 @@
     <t xml:space="preserve">18.5782051086426</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4233875274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1331005096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4974384307861</t>
+    <t xml:space="preserve">18.4233856201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1331024169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4974365234375</t>
   </si>
   <si>
     <t xml:space="preserve">20.1263866424561</t>
@@ -2663,7 +2663,7 @@
     <t xml:space="preserve">19.9328651428223</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3199119567871</t>
+    <t xml:space="preserve">20.3199100494385</t>
   </si>
   <si>
     <t xml:space="preserve">19.6425800323486</t>
@@ -2678,10 +2678,10 @@
     <t xml:space="preserve">19.1781253814697</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0233058929443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1974773406982</t>
+    <t xml:space="preserve">19.023307800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1974792480469</t>
   </si>
   <si>
     <t xml:space="preserve">18.9071941375732</t>
@@ -2690,7 +2690,7 @@
     <t xml:space="preserve">19.8844833374023</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4006767272949</t>
+    <t xml:space="preserve">19.4006748199463</t>
   </si>
   <si>
     <t xml:space="preserve">19.7877235412598</t>
@@ -2708,7 +2708,7 @@
     <t xml:space="preserve">22.0132369995117</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8357086181641</t>
+    <t xml:space="preserve">22.8357105255127</t>
   </si>
   <si>
     <t xml:space="preserve">22.1583786010742</t>
@@ -2720,19 +2720,19 @@
     <t xml:space="preserve">22.3519020080566</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7229537963867</t>
+    <t xml:space="preserve">21.7229518890381</t>
   </si>
   <si>
     <t xml:space="preserve">21.5778102874756</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4326686859131</t>
+    <t xml:space="preserve">21.4326667785645</t>
   </si>
   <si>
     <t xml:space="preserve">22.061616897583</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4970455169678</t>
+    <t xml:space="preserve">22.4970436096191</t>
   </si>
   <si>
     <t xml:space="preserve">22.2551403045654</t>
@@ -2744,7 +2744,7 @@
     <t xml:space="preserve">21.6261901855469</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7713317871094</t>
+    <t xml:space="preserve">21.771333694458</t>
   </si>
   <si>
     <t xml:space="preserve">22.3035202026367</t>
@@ -2753,10 +2753,10 @@
     <t xml:space="preserve">22.8840885162354</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7873287200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9648571014404</t>
+    <t xml:space="preserve">22.7873268127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9648551940918</t>
   </si>
   <si>
     <t xml:space="preserve">20.948860168457</t>
@@ -2771,7 +2771,7 @@
     <t xml:space="preserve">20.1747703552246</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5134334564209</t>
+    <t xml:space="preserve">20.5134353637695</t>
   </si>
   <si>
     <t xml:space="preserve">20.0296268463135</t>
@@ -2780,13 +2780,13 @@
     <t xml:space="preserve">22.9808521270752</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1259937286377</t>
+    <t xml:space="preserve">23.1259918212891</t>
   </si>
   <si>
     <t xml:space="preserve">21.3842868804932</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8520965576172</t>
+    <t xml:space="preserve">20.8520984649658</t>
   </si>
   <si>
     <t xml:space="preserve">20.5618133544922</t>
@@ -3375,6 +3375,9 @@
   </si>
   <si>
     <t xml:space="preserve">37.25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3499984741211</t>
   </si>
 </sst>
 </file>
@@ -68687,7 +68690,7 @@
     </row>
     <row r="2500">
       <c r="A2500" s="1" t="n">
-        <v>45959.6911689815</v>
+        <v>45959.3333333333</v>
       </c>
       <c r="B2500" t="n">
         <v>13315</v>
@@ -68708,6 +68711,32 @@
         <v>1119</v>
       </c>
       <c r="H2500" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2501">
+      <c r="A2501" s="1" t="n">
+        <v>45960.6909837963</v>
+      </c>
+      <c r="B2501" t="n">
+        <v>4971</v>
+      </c>
+      <c r="C2501" t="n">
+        <v>36.9000015258789</v>
+      </c>
+      <c r="D2501" t="n">
+        <v>36.25</v>
+      </c>
+      <c r="E2501" t="n">
+        <v>36.9000015258789</v>
+      </c>
+      <c r="F2501" t="n">
+        <v>36.3499984741211</v>
+      </c>
+      <c r="G2501" t="s">
+        <v>1121</v>
+      </c>
+      <c r="H2501" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LUVE.MI.xlsx
+++ b/data/LUVE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="1122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1123" uniqueCount="1123">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30043506622314</t>
+    <t xml:space="preserve">8.30043315887451</t>
   </si>
   <si>
     <t xml:space="preserve">LUVE.MI</t>
@@ -53,94 +53,94 @@
     <t xml:space="preserve">8.09292221069336</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19667816162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07632160186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15102672576904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17177772521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03897190093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08462238311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06802082061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96841621398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01821708679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99746704101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91861295700073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91446447372437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91031312942505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88541078567505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87711000442505</t>
+    <t xml:space="preserve">8.19667720794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07632064819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15102577209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17177677154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03896999359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08462142944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06802177429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96841669082642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01821899414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99746942520142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91861343383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91446113586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91031217575073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88541221618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87711191177368</t>
   </si>
   <si>
     <t xml:space="preserve">7.85220956802368</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64884996414185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71940231323242</t>
+    <t xml:space="preserve">7.64884948730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71940279006958</t>
   </si>
   <si>
     <t xml:space="preserve">7.70280122756958</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69035243988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.619797706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55754280090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55339431762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63639879226685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76920652389526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80240821838379</t>
+    <t xml:space="preserve">7.69035148620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61979818344116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55754375457764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55339574813843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63639783859253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76920413970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80240774154663</t>
   </si>
   <si>
     <t xml:space="preserve">7.93521451950073</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10122394561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05142021179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18422794342041</t>
+    <t xml:space="preserve">8.10122299194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05141925811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18422698974609</t>
   </si>
   <si>
     <t xml:space="preserve">8.13442516326904</t>
@@ -149,34 +149,34 @@
     <t xml:space="preserve">8.00161743164062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96011590957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21742820739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35853576660156</t>
+    <t xml:space="preserve">7.96011638641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21742725372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3585376739502</t>
   </si>
   <si>
     <t xml:space="preserve">8.3253345489502</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29213237762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20082664489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15932559967041</t>
+    <t xml:space="preserve">8.2921314239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20082855224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15932655334473</t>
   </si>
   <si>
     <t xml:space="preserve">8.30336380004883</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36267280578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43045616149902</t>
+    <t xml:space="preserve">8.36267375946045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43045520782471</t>
   </si>
   <si>
     <t xml:space="preserve">8.15085315704346</t>
@@ -194,37 +194,37 @@
     <t xml:space="preserve">8.11696243286133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21863651275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21016216278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21440029144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20168972015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26099967956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09154415130615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10848712921143</t>
+    <t xml:space="preserve">8.21863460540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21016311645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21439933776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20169162750244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26099872589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09154319763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10848808288574</t>
   </si>
   <si>
     <t xml:space="preserve">8.04918003082275</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9644513130188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92208671569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87972259521484</t>
+    <t xml:space="preserve">7.96445083618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92208766937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87972402572632</t>
   </si>
   <si>
     <t xml:space="preserve">7.83735942840576</t>
@@ -233,31 +233,31 @@
     <t xml:space="preserve">8.12543487548828</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93479633331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75263118743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71026611328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93903350830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81194067001343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79499483108521</t>
+    <t xml:space="preserve">7.93479537963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75262975692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71026754379272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93903303146362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81194019317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79499387741089</t>
   </si>
   <si>
     <t xml:space="preserve">7.62553834915161</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66790294647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84583139419556</t>
+    <t xml:space="preserve">7.66790390014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84583044052124</t>
   </si>
   <si>
     <t xml:space="preserve">8.19321727752686</t>
@@ -269,88 +269,88 @@
     <t xml:space="preserve">8.51518440246582</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52365779876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59991455078125</t>
+    <t xml:space="preserve">8.52365875244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5999116897583</t>
   </si>
   <si>
     <t xml:space="preserve">8.78631401062012</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71853256225586</t>
+    <t xml:space="preserve">8.71853160858154</t>
   </si>
   <si>
     <t xml:space="preserve">8.50671195983887</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54060363769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46858215332031</t>
+    <t xml:space="preserve">8.540602684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46858406066895</t>
   </si>
   <si>
     <t xml:space="preserve">8.46434688568115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55754947662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57449340820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81173419952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72700500488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6422758102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89646053314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02355289459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09980964660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06591892242432</t>
+    <t xml:space="preserve">8.55754852294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57449436187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81173229217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7270040512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64227676391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89645957946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02355194091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09980869293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06591701507568</t>
   </si>
   <si>
     <t xml:space="preserve">9.10828304290771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27773761749268</t>
+    <t xml:space="preserve">9.27773857116699</t>
   </si>
   <si>
     <t xml:space="preserve">9.19300937652588</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18453788757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07439136505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09133434295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30315685272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32010269165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12522888183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60817813873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40482997894287</t>
+    <t xml:space="preserve">9.18453693389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07439041137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09133625030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30315589904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32010364532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1252269744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60817909240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4048318862915</t>
   </si>
   <si>
     <t xml:space="preserve">9.48955917358398</t>
@@ -368,31 +368,31 @@
     <t xml:space="preserve">9.44719505310059</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54039573669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57428646087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47261238098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41330146789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42177581787109</t>
+    <t xml:space="preserve">9.5403938293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5742883682251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47261333465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41330337524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42177486419678</t>
   </si>
   <si>
     <t xml:space="preserve">9.51497650146484</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56581497192383</t>
+    <t xml:space="preserve">9.56581401824951</t>
   </si>
   <si>
     <t xml:space="preserve">9.74374389648438</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0657110214233</t>
+    <t xml:space="preserve">10.065710067749</t>
   </si>
   <si>
     <t xml:space="preserve">10.2521133422852</t>
@@ -413,16 +413,16 @@
     <t xml:space="preserve">9.88778018951416</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91320037841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0148735046387</t>
+    <t xml:space="preserve">9.91319942474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0148725509644</t>
   </si>
   <si>
     <t xml:space="preserve">10.1589117050171</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0402927398682</t>
+    <t xml:space="preserve">10.0402917861938</t>
   </si>
   <si>
     <t xml:space="preserve">9.70137882232666</t>
@@ -434,7 +434,7 @@
     <t xml:space="preserve">9.70985221862793</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0826549530029</t>
+    <t xml:space="preserve">10.0826559066772</t>
   </si>
   <si>
     <t xml:space="preserve">9.86236381530762</t>
@@ -443,25 +443,25 @@
     <t xml:space="preserve">10.1250200271606</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2944765090942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4808778762817</t>
+    <t xml:space="preserve">10.2944755554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4808788299561</t>
   </si>
   <si>
     <t xml:space="preserve">10.5317163467407</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5147695541382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.802845954895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9129934310913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8621549606323</t>
+    <t xml:space="preserve">10.5147705078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8028450012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.912992477417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.862156867981</t>
   </si>
   <si>
     <t xml:space="preserve">11.0146656036377</t>
@@ -473,19 +473,19 @@
     <t xml:space="preserve">11.2773237228394</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4383087158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6585998535156</t>
+    <t xml:space="preserve">11.438307762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6586008071899</t>
   </si>
   <si>
     <t xml:space="preserve">11.5823459625244</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4806709289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5908184051514</t>
+    <t xml:space="preserve">11.4806718826294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5908193588257</t>
   </si>
   <si>
     <t xml:space="preserve">11.7009649276733</t>
@@ -500,16 +500,16 @@
     <t xml:space="preserve">11.8365297317505</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6670751571655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.599289894104</t>
+    <t xml:space="preserve">11.6670742034912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5992908477783</t>
   </si>
   <si>
     <t xml:space="preserve">11.5230360031128</t>
   </si>
   <si>
-    <t xml:space="preserve">11.607762336731</t>
+    <t xml:space="preserve">11.6077632904053</t>
   </si>
   <si>
     <t xml:space="preserve">11.6263809204102</t>
@@ -518,16 +518,16 @@
     <t xml:space="preserve">11.7297267913818</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6952791213989</t>
+    <t xml:space="preserve">11.6952772140503</t>
   </si>
   <si>
     <t xml:space="preserve">11.6780557632446</t>
   </si>
   <si>
-    <t xml:space="preserve">11.798623085022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8847455978394</t>
+    <t xml:space="preserve">11.7986240386963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.884744644165</t>
   </si>
   <si>
     <t xml:space="preserve">11.9105815887451</t>
@@ -536,19 +536,19 @@
     <t xml:space="preserve">12.0655994415283</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3153524398804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3584127426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0569887161255</t>
+    <t xml:space="preserve">12.3153505325317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3584117889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0569877624512</t>
   </si>
   <si>
     <t xml:space="preserve">12.1431093215942</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9967031478882</t>
+    <t xml:space="preserve">11.9967041015625</t>
   </si>
   <si>
     <t xml:space="preserve">11.8416843414307</t>
@@ -557,22 +557,22 @@
     <t xml:space="preserve">11.7555627822876</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7125015258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8502969741821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9191923141479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9622554779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0397624969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0483741760254</t>
+    <t xml:space="preserve">11.7125024795532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8502960205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9191942214966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.962254524231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0397634506226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0483751296997</t>
   </si>
   <si>
     <t xml:space="preserve">11.7900114059448</t>
@@ -584,7 +584,7 @@
     <t xml:space="preserve">11.945029258728</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8158493041992</t>
+    <t xml:space="preserve">11.8158473968506</t>
   </si>
   <si>
     <t xml:space="preserve">11.8933572769165</t>
@@ -599,31 +599,31 @@
     <t xml:space="preserve">11.8675203323364</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9019708633423</t>
+    <t xml:space="preserve">11.9019689559937</t>
   </si>
   <si>
     <t xml:space="preserve">11.927806854248</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7211151123047</t>
+    <t xml:space="preserve">11.7211141586304</t>
   </si>
   <si>
     <t xml:space="preserve">11.6694421768188</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6349925994873</t>
+    <t xml:space="preserve">11.6349945068359</t>
   </si>
   <si>
     <t xml:space="preserve">11.6091566085815</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5747079849243</t>
+    <t xml:space="preserve">11.57470703125</t>
   </si>
   <si>
     <t xml:space="preserve">11.5316476821899</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3680171966553</t>
+    <t xml:space="preserve">11.3680181503296</t>
   </si>
   <si>
     <t xml:space="preserve">11.3594045639038</t>
@@ -632,25 +632,25 @@
     <t xml:space="preserve">11.2818965911865</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2302236557007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1957731246948</t>
+    <t xml:space="preserve">11.2302227020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1957740783691</t>
   </si>
   <si>
     <t xml:space="preserve">11.1871614456177</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1096534729004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0579814910889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1785497665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.126877784729</t>
+    <t xml:space="preserve">11.1096515655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0579805374146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1785507202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1268768310547</t>
   </si>
   <si>
     <t xml:space="preserve">10.9374094009399</t>
@@ -659,25 +659,25 @@
     <t xml:space="preserve">11.066593170166</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0235319137573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0838174819946</t>
+    <t xml:space="preserve">11.023530960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0838165283203</t>
   </si>
   <si>
     <t xml:space="preserve">11.1354894638062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2043876647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3163442611694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4541387557983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5402603149414</t>
+    <t xml:space="preserve">11.2043867111206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3163433074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.454137802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5402593612671</t>
   </si>
   <si>
     <t xml:space="preserve">11.4110774993896</t>
@@ -686,55 +686,55 @@
     <t xml:space="preserve">11.2905073165894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1613245010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2646722793579</t>
+    <t xml:space="preserve">11.1613264083862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2646713256836</t>
   </si>
   <si>
     <t xml:space="preserve">11.1527137756348</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0407552719116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4196910858154</t>
+    <t xml:space="preserve">11.0407562255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4196901321411</t>
   </si>
   <si>
     <t xml:space="preserve">11.2216100692749</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2388343811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3421821594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9546337127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.96324634552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0063066482544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0924282073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74032497406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01690483093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2149829864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37861442565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49057197570801</t>
+    <t xml:space="preserve">11.2388353347778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3421792984009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9546346664429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9632453918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0063056945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0924272537231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74032402038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0169038772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21498394012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3786153793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49057102203369</t>
   </si>
   <si>
     <t xml:space="preserve">9.5077953338623</t>
@@ -743,73 +743,73 @@
     <t xml:space="preserve">9.59391784667969</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60253143310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6886510848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56808090209961</t>
+    <t xml:space="preserve">9.60252952575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68865203857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56808185577393</t>
   </si>
   <si>
     <t xml:space="preserve">9.39583778381348</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34416580200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2580451965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30110359191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41306304931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28388023376465</t>
+    <t xml:space="preserve">9.34416484832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25804424285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30110454559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41306209564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28388214111328</t>
   </si>
   <si>
     <t xml:space="preserve">9.24081993103027</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12886333465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02551651000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20637226104736</t>
+    <t xml:space="preserve">9.12886238098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02551555633545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20637130737305</t>
   </si>
   <si>
     <t xml:space="preserve">9.26665687561035</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69726276397705</t>
+    <t xml:space="preserve">9.69726371765137</t>
   </si>
   <si>
     <t xml:space="preserve">9.65420246124268</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66281509399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64558887481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67142581939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75754737854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71448802947998</t>
+    <t xml:space="preserve">9.66281604766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64559078216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67142677307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75754928588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71448707580566</t>
   </si>
   <si>
     <t xml:space="preserve">9.09441375732422</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93939590454102</t>
+    <t xml:space="preserve">8.9393949508667</t>
   </si>
   <si>
     <t xml:space="preserve">9.14608669281006</t>
@@ -818,22 +818,22 @@
     <t xml:space="preserve">9.12024974822998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83505821228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73171138763428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90395355224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77477169036865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53363227844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49918365478516</t>
+    <t xml:space="preserve">9.83505630493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73171234130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90395450592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77477264404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5336332321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49918270111084</t>
   </si>
   <si>
     <t xml:space="preserve">9.57669353485107</t>
@@ -848,28 +848,28 @@
     <t xml:space="preserve">9.4302864074707</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54224491119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17192268371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23220825195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55946922302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51640796661377</t>
+    <t xml:space="preserve">9.54224586486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17192363739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23220729827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55947017669678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51640701293945</t>
   </si>
   <si>
     <t xml:space="preserve">9.86089324951172</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95662021636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91355800628662</t>
+    <t xml:space="preserve">8.95661926269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91355895996094</t>
   </si>
   <si>
     <t xml:space="preserve">9.08580207824707</t>
@@ -887,16 +887,16 @@
     <t xml:space="preserve">8.69825553894043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87049961090088</t>
+    <t xml:space="preserve">8.87049865722656</t>
   </si>
   <si>
     <t xml:space="preserve">8.7843770980835</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74131679534912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61213493347168</t>
+    <t xml:space="preserve">8.7413158416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61213302612305</t>
   </si>
   <si>
     <t xml:space="preserve">8.59490966796875</t>
@@ -908,61 +908,61 @@
     <t xml:space="preserve">8.45711517333984</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06314468383789</t>
+    <t xml:space="preserve">9.06314563751221</t>
   </si>
   <si>
     <t xml:space="preserve">9.10714054107666</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01914882659912</t>
+    <t xml:space="preserve">9.0191478729248</t>
   </si>
   <si>
     <t xml:space="preserve">8.97515296936035</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93115615844727</t>
+    <t xml:space="preserve">8.9311580657959</t>
   </si>
   <si>
     <t xml:space="preserve">8.88716125488281</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84316730499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76397323608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48240089416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71117877960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6231861114502</t>
+    <t xml:space="preserve">8.84316539764404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76397228240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48239994049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71117687225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62318801879883</t>
   </si>
   <si>
     <t xml:space="preserve">8.58798980712891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65838241577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60558891296387</t>
+    <t xml:space="preserve">8.6583833694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60558700561523</t>
   </si>
   <si>
     <t xml:space="preserve">8.7287769317627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69357967376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74637413024902</t>
+    <t xml:space="preserve">8.69358062744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74637317657471</t>
   </si>
   <si>
     <t xml:space="preserve">8.53519439697266</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4472017288208</t>
+    <t xml:space="preserve">8.44720458984375</t>
   </si>
   <si>
     <t xml:space="preserve">8.27121925354004</t>
@@ -974,22 +974,22 @@
     <t xml:space="preserve">8.288818359375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78157043457031</t>
+    <t xml:space="preserve">8.78157138824463</t>
   </si>
   <si>
     <t xml:space="preserve">8.64078426361084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79917049407959</t>
+    <t xml:space="preserve">8.79916858673096</t>
   </si>
   <si>
     <t xml:space="preserve">8.67598152160645</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23912811279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37111568450928</t>
+    <t xml:space="preserve">9.23912906646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37111473083496</t>
   </si>
   <si>
     <t xml:space="preserve">9.32712078094482</t>
@@ -998,28 +998,28 @@
     <t xml:space="preserve">9.19513130187988</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15113544464111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46480178833008</t>
+    <t xml:space="preserve">9.15113639831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46479988098145</t>
   </si>
   <si>
     <t xml:space="preserve">8.41200637817383</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49999713897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34161186218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23602199554443</t>
+    <t xml:space="preserve">8.49999809265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34161281585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23602104187012</t>
   </si>
   <si>
     <t xml:space="preserve">8.30641555786133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13043117523193</t>
+    <t xml:space="preserve">8.13043212890625</t>
   </si>
   <si>
     <t xml:space="preserve">8.1832275390625</t>
@@ -1028,7 +1028,7 @@
     <t xml:space="preserve">8.16562938690186</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21842479705811</t>
+    <t xml:space="preserve">8.21842575073242</t>
   </si>
   <si>
     <t xml:space="preserve">8.25362110137939</t>
@@ -1046,28 +1046,28 @@
     <t xml:space="preserve">9.41511154174805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63509082794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59109401702881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89906597137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1190462112427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1630401611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2070369720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3390235900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2950296401978</t>
+    <t xml:space="preserve">9.63508987426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59109497070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8990650177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1190433502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1630420684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2070379257202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3390245437622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2950286865234</t>
   </si>
   <si>
     <t xml:space="preserve">10.383020401001</t>
@@ -1079,10 +1079,10 @@
     <t xml:space="preserve">10.4270162582397</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0750494003296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5150060653687</t>
+    <t xml:space="preserve">10.0750484466553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5150079727173</t>
   </si>
   <si>
     <t xml:space="preserve">10.6498155593872</t>
@@ -1091,34 +1091,34 @@
     <t xml:space="preserve">10.4700717926025</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6947507858276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6048803329468</t>
+    <t xml:space="preserve">10.694751739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6048784255981</t>
   </si>
   <si>
     <t xml:space="preserve">10.380199432373</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2453918457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0656471252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4251365661621</t>
+    <t xml:space="preserve">10.2453908920288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0656480789185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4251356124878</t>
   </si>
   <si>
     <t xml:space="preserve">10.5150089263916</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3352651596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2903280258179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2004566192627</t>
+    <t xml:space="preserve">10.3352632522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2903270721436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.200457572937</t>
   </si>
   <si>
     <t xml:space="preserve">9.97577667236328</t>
@@ -1133,16 +1133,16 @@
     <t xml:space="preserve">9.88590431213379</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1555204391479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0207138061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75109767913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70616054534912</t>
+    <t xml:space="preserve">10.1555213928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.020712852478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75109672546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70616149902344</t>
   </si>
   <si>
     <t xml:space="preserve">9.34667301177979</t>
@@ -1151,7 +1151,7 @@
     <t xml:space="preserve">9.30173778533936</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39160823822021</t>
+    <t xml:space="preserve">9.39160919189453</t>
   </si>
   <si>
     <t xml:space="preserve">9.48148155212402</t>
@@ -1166,13 +1166,13 @@
     <t xml:space="preserve">9.43654537200928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12199306488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03212356567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16693019866943</t>
+    <t xml:space="preserve">9.12199401855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03212261199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1669282913208</t>
   </si>
   <si>
     <t xml:space="preserve">9.07705783843994</t>
@@ -1181,16 +1181,16 @@
     <t xml:space="preserve">9.25680160522461</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98718738555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5713529586792</t>
+    <t xml:space="preserve">8.98718643188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57135200500488</t>
   </si>
   <si>
     <t xml:space="preserve">9.66122531890869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7960319519043</t>
+    <t xml:space="preserve">9.79603290557861</t>
   </si>
   <si>
     <t xml:space="preserve">10.9643669128418</t>
@@ -1202,40 +1202,40 @@
     <t xml:space="preserve">11.5035991668701</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2339811325073</t>
+    <t xml:space="preserve">11.2339820861816</t>
   </si>
   <si>
     <t xml:space="preserve">11.1441106796265</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9194316864014</t>
+    <t xml:space="preserve">10.9194297790527</t>
   </si>
   <si>
     <t xml:space="preserve">10.8744955062866</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0093040466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2789182662964</t>
+    <t xml:space="preserve">11.0093021392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2789192199707</t>
   </si>
   <si>
     <t xml:space="preserve">11.4137258529663</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5485343933105</t>
+    <t xml:space="preserve">11.5485334396362</t>
   </si>
   <si>
     <t xml:space="preserve">11.6833410263062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.77321434021</t>
+    <t xml:space="preserve">11.7732152938843</t>
   </si>
   <si>
     <t xml:space="preserve">11.9080219268799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1327018737793</t>
+    <t xml:space="preserve">12.132700920105</t>
   </si>
   <si>
     <t xml:space="preserve">11.9978942871094</t>
@@ -1244,7 +1244,7 @@
     <t xml:space="preserve">11.8181495666504</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5934705734253</t>
+    <t xml:space="preserve">11.593469619751</t>
   </si>
   <si>
     <t xml:space="preserve">12.3124446868896</t>
@@ -1253,10 +1253,10 @@
     <t xml:space="preserve">12.5820598602295</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9415493011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8067407608032</t>
+    <t xml:space="preserve">12.9415483474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8067398071289</t>
   </si>
   <si>
     <t xml:space="preserve">12.7618036270142</t>
@@ -1265,94 +1265,94 @@
     <t xml:space="preserve">13.0763559341431</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4472541809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5371236801147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2675085067749</t>
+    <t xml:space="preserve">12.4472522735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5371246337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2675094604492</t>
   </si>
   <si>
     <t xml:space="preserve">12.4023170471191</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6269979476929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6719312667847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8966131210327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7282772064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7846231460571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5599431991577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89731502532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98062181472778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81885147094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53126239776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89074897766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53782749176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96264553070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44795513153076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60972499847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66364860534668</t>
+    <t xml:space="preserve">12.6269969940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6719331741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8966121673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7282781600952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7846240997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.559944152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89731407165527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98062086105347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81885194778442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53126192092896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89074945449829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53782653808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.962646484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44795417785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6097240447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66364765167236</t>
   </si>
   <si>
     <t xml:space="preserve">8.86136627197266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21186542510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9384880065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80045509338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89247798919678</t>
+    <t xml:space="preserve">9.21186637878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93848896026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80045413970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89247894287109</t>
   </si>
   <si>
     <t xml:space="preserve">9.66242027282715</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70843315124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84646606445312</t>
+    <t xml:space="preserve">9.7084321975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84646701812744</t>
   </si>
   <si>
     <t xml:space="preserve">10.1225357055664</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75444507598877</t>
+    <t xml:space="preserve">9.75444412231445</t>
   </si>
   <si>
     <t xml:space="preserve">10.3986053466797</t>
@@ -1364,10 +1364,10 @@
     <t xml:space="preserve">10.720685005188</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5826501846313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8587207794189</t>
+    <t xml:space="preserve">10.582649230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8587198257446</t>
   </si>
   <si>
     <t xml:space="preserve">10.6746740341187</t>
@@ -1382,7 +1382,7 @@
     <t xml:space="preserve">10.766697883606</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4906282424927</t>
+    <t xml:space="preserve">10.4906272888184</t>
   </si>
   <si>
     <t xml:space="preserve">11.1347904205322</t>
@@ -1391,49 +1391,49 @@
     <t xml:space="preserve">11.3188352584839</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5028800964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1808004379272</t>
+    <t xml:space="preserve">11.5028810501099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1807994842529</t>
   </si>
   <si>
     <t xml:space="preserve">11.0427665710449</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2728242874146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9507417678833</t>
+    <t xml:space="preserve">11.2728223800659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9507427215576</t>
   </si>
   <si>
     <t xml:space="preserve">11.0887784957886</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8127088546753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9047317504883</t>
+    <t xml:space="preserve">10.8127098083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.904730796814</t>
   </si>
   <si>
     <t xml:space="preserve">11.4108581542969</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4568691253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2268123626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3648471832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5488920211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5949048995972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6869277954102</t>
+    <t xml:space="preserve">11.4568710327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2268114089966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3648481369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5488929748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5949039459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6869268417358</t>
   </si>
   <si>
     <t xml:space="preserve">11.9629964828491</t>
@@ -1451,13 +1451,13 @@
     <t xml:space="preserve">11.7329397201538</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8249626159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0550193786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8709735870361</t>
+    <t xml:space="preserve">11.8249616622925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0550212860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8709726333618</t>
   </si>
   <si>
     <t xml:space="preserve">11.9169855117798</t>
@@ -1469,10 +1469,10 @@
     <t xml:space="preserve">12.1470422744751</t>
   </si>
   <si>
-    <t xml:space="preserve">12.699182510376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7912034988403</t>
+    <t xml:space="preserve">12.6991815567017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.791202545166</t>
   </si>
   <si>
     <t xml:space="preserve">13.0672731399536</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">12.9292392730713</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2053089141846</t>
+    <t xml:space="preserve">13.2053079605103</t>
   </si>
   <si>
     <t xml:space="preserve">13.2513198852539</t>
@@ -1493,49 +1493,49 @@
     <t xml:space="preserve">13.1132841110229</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1592969894409</t>
+    <t xml:space="preserve">13.1592960357666</t>
   </si>
   <si>
     <t xml:space="preserve">13.3893537521362</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2973318099976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9752502441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7114343643188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4353666305542</t>
+    <t xml:space="preserve">13.2973308563232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9752511978149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7114334106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4353647232056</t>
   </si>
   <si>
     <t xml:space="preserve">12.5151348114014</t>
   </si>
   <si>
-    <t xml:space="preserve">12.377100944519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8372144699097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7451934814453</t>
+    <t xml:space="preserve">12.3770999908447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.837215423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.745192527771</t>
   </si>
   <si>
     <t xml:space="preserve">12.6531705856323</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3433427810669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6194114685059</t>
+    <t xml:space="preserve">13.3433437347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6194124221802</t>
   </si>
   <si>
     <t xml:space="preserve">13.8494691848755</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9414920806885</t>
+    <t xml:space="preserve">13.9414930343628</t>
   </si>
   <si>
     <t xml:space="preserve">14.1715497970581</t>
@@ -1553,25 +1553,25 @@
     <t xml:space="preserve">14.7236881256104</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6776762008667</t>
+    <t xml:space="preserve">14.6776752471924</t>
   </si>
   <si>
     <t xml:space="preserve">14.8157119750977</t>
   </si>
   <si>
-    <t xml:space="preserve">14.861722946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0457696914673</t>
+    <t xml:space="preserve">14.8617238998413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0457677841187</t>
   </si>
   <si>
     <t xml:space="preserve">14.5396423339844</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6316652297974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4476184844971</t>
+    <t xml:space="preserve">14.631664276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4476194381714</t>
   </si>
   <si>
     <t xml:space="preserve">14.2635736465454</t>
@@ -1583,7 +1583,7 @@
     <t xml:space="preserve">14.3095846176147</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6654233932495</t>
+    <t xml:space="preserve">13.6654253005981</t>
   </si>
   <si>
     <t xml:space="preserve">13.8034572601318</t>
@@ -1604,16 +1604,16 @@
     <t xml:space="preserve">14.4269771575928</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3801374435425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.473819732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7080230712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8485460281372</t>
+    <t xml:space="preserve">14.3801383972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4738187789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7080240249634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8485450744629</t>
   </si>
   <si>
     <t xml:space="preserve">15.03590965271</t>
@@ -1628,10 +1628,10 @@
     <t xml:space="preserve">14.9422273635864</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1764326095581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1295900344849</t>
+    <t xml:space="preserve">15.1764316558838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1295909881592</t>
   </si>
   <si>
     <t xml:space="preserve">14.989068031311</t>
@@ -1640,7 +1640,7 @@
     <t xml:space="preserve">14.6611814498901</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3169555664062</t>
+    <t xml:space="preserve">15.3169536590576</t>
   </si>
   <si>
     <t xml:space="preserve">14.7548637390137</t>
@@ -1652,13 +1652,13 @@
     <t xml:space="preserve">15.2232723236084</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5043172836304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0664081573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6916809082031</t>
+    <t xml:space="preserve">15.5043153762817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0664100646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6916818618774</t>
   </si>
   <si>
     <t xml:space="preserve">15.7385206222534</t>
@@ -1667,7 +1667,7 @@
     <t xml:space="preserve">15.9727249145508</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9258842468262</t>
+    <t xml:space="preserve">15.9258861541748</t>
   </si>
   <si>
     <t xml:space="preserve">15.7853631973267</t>
@@ -1676,7 +1676,7 @@
     <t xml:space="preserve">16.1132488250732</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8322038650513</t>
+    <t xml:space="preserve">15.8322019577026</t>
   </si>
   <si>
     <t xml:space="preserve">16.5348148345947</t>
@@ -1691,13 +1691,13 @@
     <t xml:space="preserve">16.5816593170166</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2069282531738</t>
+    <t xml:space="preserve">16.2069301605225</t>
   </si>
   <si>
     <t xml:space="preserve">17.2842712402344</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7995204925537</t>
+    <t xml:space="preserve">17.7995185852051</t>
   </si>
   <si>
     <t xml:space="preserve">17.4716320037842</t>
@@ -1706,16 +1706,16 @@
     <t xml:space="preserve">16.8158626556396</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6284961700439</t>
+    <t xml:space="preserve">16.6284980773926</t>
   </si>
   <si>
     <t xml:space="preserve">17.0969066619873</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5184745788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6121559143066</t>
+    <t xml:space="preserve">17.5184764862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.612154006958</t>
   </si>
   <si>
     <t xml:space="preserve">18.0337238311768</t>
@@ -1724,13 +1724,13 @@
     <t xml:space="preserve">18.5489711761475</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7363376617432</t>
+    <t xml:space="preserve">18.7363357543945</t>
   </si>
   <si>
     <t xml:space="preserve">18.923698425293</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7668361663818</t>
+    <t xml:space="preserve">19.7668342590332</t>
   </si>
   <si>
     <t xml:space="preserve">19.5794696807861</t>
@@ -1739,10 +1739,10 @@
     <t xml:space="preserve">19.2047443389893</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1110610961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6731510162354</t>
+    <t xml:space="preserve">19.1110591888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.673152923584</t>
   </si>
   <si>
     <t xml:space="preserve">19.2984256744385</t>
@@ -1751,7 +1751,7 @@
     <t xml:space="preserve">19.4857883453369</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8605175018311</t>
+    <t xml:space="preserve">19.8605155944824</t>
   </si>
   <si>
     <t xml:space="preserve">20.3289241790771</t>
@@ -1760,7 +1760,7 @@
     <t xml:space="preserve">20.9846954345703</t>
   </si>
   <si>
-    <t xml:space="preserve">21.265739440918</t>
+    <t xml:space="preserve">21.2657432556152</t>
   </si>
   <si>
     <t xml:space="preserve">21.0783767700195</t>
@@ -1778,13 +1778,13 @@
     <t xml:space="preserve">22.1088771820068</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7341499328613</t>
+    <t xml:space="preserve">21.7341480255127</t>
   </si>
   <si>
     <t xml:space="preserve">22.015193939209</t>
   </si>
   <si>
-    <t xml:space="preserve">22.296236038208</t>
+    <t xml:space="preserve">22.2962379455566</t>
   </si>
   <si>
     <t xml:space="preserve">22.4836025238037</t>
@@ -1793,16 +1793,16 @@
     <t xml:space="preserve">21.6404685974121</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5467853546143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2352409362793</t>
+    <t xml:space="preserve">21.5467834472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2352428436279</t>
   </si>
   <si>
     <t xml:space="preserve">18.3147678375244</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0173797607422</t>
+    <t xml:space="preserve">19.0173816680908</t>
   </si>
   <si>
     <t xml:space="preserve">20.6099681854248</t>
@@ -1820,10 +1820,10 @@
     <t xml:space="preserve">21.1720600128174</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7036514282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3594207763672</t>
+    <t xml:space="preserve">20.703649520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3594188690186</t>
   </si>
   <si>
     <t xml:space="preserve">20.5162868499756</t>
@@ -1835,10 +1835,10 @@
     <t xml:space="preserve">22.6709671020508</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2025585174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3899192810059</t>
+    <t xml:space="preserve">22.2025566101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3899211883545</t>
   </si>
   <si>
     <t xml:space="preserve">19.9541969299316</t>
@@ -1847,7 +1847,7 @@
     <t xml:space="preserve">20.4226055145264</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8910160064697</t>
+    <t xml:space="preserve">20.8910140991211</t>
   </si>
   <si>
     <t xml:space="preserve">19.3921070098877</t>
@@ -1880,7 +1880,7 @@
     <t xml:space="preserve">18.2679271697998</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8768558502197</t>
+    <t xml:space="preserve">18.8768577575684</t>
   </si>
   <si>
     <t xml:space="preserve">18.6426525115967</t>
@@ -1892,10 +1892,10 @@
     <t xml:space="preserve">18.2117176055908</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2304553985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4552898406982</t>
+    <t xml:space="preserve">18.2304534912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4552879333496</t>
   </si>
   <si>
     <t xml:space="preserve">17.9494094848633</t>
@@ -1910,7 +1910,7 @@
     <t xml:space="preserve">20.2820835113525</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0947208404541</t>
+    <t xml:space="preserve">20.0947189331055</t>
   </si>
   <si>
     <t xml:space="preserve">20.1884021759033</t>
@@ -1919,19 +1919,19 @@
     <t xml:space="preserve">20.1415596008301</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4927616119385</t>
+    <t xml:space="preserve">18.4927635192871</t>
   </si>
   <si>
     <t xml:space="preserve">17.5559463500977</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1999568939209</t>
+    <t xml:space="preserve">17.1999549865723</t>
   </si>
   <si>
     <t xml:space="preserve">16.8847980499268</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7634181976318</t>
+    <t xml:space="preserve">17.7634201049805</t>
   </si>
   <si>
     <t xml:space="preserve">18.0308246612549</t>
@@ -1943,7 +1943,7 @@
     <t xml:space="preserve">18.4319343566895</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6038398742676</t>
+    <t xml:space="preserve">18.6038379669189</t>
   </si>
   <si>
     <t xml:space="preserve">19.1004505157471</t>
@@ -1952,19 +1952,19 @@
     <t xml:space="preserve">18.9858474731445</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1481990814209</t>
+    <t xml:space="preserve">19.1482009887695</t>
   </si>
   <si>
     <t xml:space="preserve">18.90944480896</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9476490020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0077247619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0554733276367</t>
+    <t xml:space="preserve">18.9476470947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0077228546143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0554752349854</t>
   </si>
   <si>
     <t xml:space="preserve">20.5329856872559</t>
@@ -1973,16 +1973,16 @@
     <t xml:space="preserve">20.9149932861328</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1509761810303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4374828338623</t>
+    <t xml:space="preserve">20.1509742736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4374809265137</t>
   </si>
   <si>
     <t xml:space="preserve">21.0104961395264</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4880084991455</t>
+    <t xml:space="preserve">21.4880065917969</t>
   </si>
   <si>
     <t xml:space="preserve">19.5779628753662</t>
@@ -1997,13 +1997,13 @@
     <t xml:space="preserve">19.2914562225342</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3392066955566</t>
+    <t xml:space="preserve">19.339204788208</t>
   </si>
   <si>
     <t xml:space="preserve">18.813943862915</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6993389129639</t>
+    <t xml:space="preserve">18.6993408203125</t>
   </si>
   <si>
     <t xml:space="preserve">19.3869571685791</t>
@@ -2018,7 +2018,7 @@
     <t xml:space="preserve">18.240930557251</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7757434844971</t>
+    <t xml:space="preserve">18.7757415771484</t>
   </si>
   <si>
     <t xml:space="preserve">19.9599704742432</t>
@@ -2036,13 +2036,13 @@
     <t xml:space="preserve">21.392505645752</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1537475585938</t>
+    <t xml:space="preserve">21.1537494659424</t>
   </si>
   <si>
     <t xml:space="preserve">21.7745132446289</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6790103912354</t>
+    <t xml:space="preserve">21.679012298584</t>
   </si>
   <si>
     <t xml:space="preserve">21.9177684783936</t>
@@ -2057,7 +2057,7 @@
     <t xml:space="preserve">21.5835094451904</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5807342529297</t>
+    <t xml:space="preserve">20.5807323455811</t>
   </si>
   <si>
     <t xml:space="preserve">20.1032218933105</t>
@@ -2075,7 +2075,7 @@
     <t xml:space="preserve">22.9205417633057</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4430313110352</t>
+    <t xml:space="preserve">22.4430294036865</t>
   </si>
   <si>
     <t xml:space="preserve">22.1565227508545</t>
@@ -2087,16 +2087,16 @@
     <t xml:space="preserve">22.3475284576416</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0582466125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3897304534912</t>
+    <t xml:space="preserve">21.0582447052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3897323608398</t>
   </si>
   <si>
     <t xml:space="preserve">20.2942276000977</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1987247467041</t>
+    <t xml:space="preserve">20.1987266540527</t>
   </si>
   <si>
     <t xml:space="preserve">20.8194904327393</t>
@@ -2120,7 +2120,7 @@
     <t xml:space="preserve">19.8167171478271</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2464790344238</t>
+    <t xml:space="preserve">20.2464771270752</t>
   </si>
   <si>
     <t xml:space="preserve">20.6762371063232</t>
@@ -2129,7 +2129,7 @@
     <t xml:space="preserve">19.7689666748047</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4402561187744</t>
+    <t xml:space="preserve">21.440258026123</t>
   </si>
   <si>
     <t xml:space="preserve">22.6340351104736</t>
@@ -2144,10 +2144,10 @@
     <t xml:space="preserve">22.5862808227539</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8727912902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5385322570801</t>
+    <t xml:space="preserve">22.8727893829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5385303497314</t>
   </si>
   <si>
     <t xml:space="preserve">22.6817855834961</t>
@@ -2156,7 +2156,7 @@
     <t xml:space="preserve">23.0160427093506</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3025493621826</t>
+    <t xml:space="preserve">23.3025512695312</t>
   </si>
   <si>
     <t xml:space="preserve">24.4485759735107</t>
@@ -2165,13 +2165,13 @@
     <t xml:space="preserve">23.7323112487793</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9710636138916</t>
+    <t xml:space="preserve">23.9710655212402</t>
   </si>
   <si>
     <t xml:space="preserve">24.2098217010498</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0665683746338</t>
+    <t xml:space="preserve">24.0665664672852</t>
   </si>
   <si>
     <t xml:space="preserve">24.1143188476562</t>
@@ -2186,19 +2186,19 @@
     <t xml:space="preserve">23.7800598144531</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9233150482178</t>
+    <t xml:space="preserve">23.9233131408691</t>
   </si>
   <si>
     <t xml:space="preserve">25.0693416595459</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5440807342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9260864257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3558464050293</t>
+    <t xml:space="preserve">24.5440788269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9260883331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3558483123779</t>
   </si>
   <si>
     <t xml:space="preserve">25.4035987854004</t>
@@ -2219,16 +2219,16 @@
     <t xml:space="preserve">24.5918292999268</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8305854797363</t>
+    <t xml:space="preserve">24.830587387085</t>
   </si>
   <si>
     <t xml:space="preserve">25.260347366333</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7378578186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7856101989746</t>
+    <t xml:space="preserve">25.7378597259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.785608291626</t>
   </si>
   <si>
     <t xml:space="preserve">26.0721130371094</t>
@@ -2240,13 +2240,13 @@
     <t xml:space="preserve">25.4513492584229</t>
   </si>
   <si>
-    <t xml:space="preserve">25.928861618042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5946025848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6901073455811</t>
+    <t xml:space="preserve">25.9288597106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5946044921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6901054382324</t>
   </si>
   <si>
     <t xml:space="preserve">25.5468521118164</t>
@@ -2261,16 +2261,16 @@
     <t xml:space="preserve">27.0748901367188</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1703929901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6506767272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.321964263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.892204284668</t>
+    <t xml:space="preserve">27.1703910827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6506748199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3219661712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8922023773193</t>
   </si>
   <si>
     <t xml:space="preserve">29.9877071380615</t>
@@ -2279,7 +2279,7 @@
     <t xml:space="preserve">30.1309604644775</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6534481048584</t>
+    <t xml:space="preserve">29.653450012207</t>
   </si>
   <si>
     <t xml:space="preserve">29.510196685791</t>
@@ -2297,7 +2297,7 @@
     <t xml:space="preserve">28.8416805267334</t>
   </si>
   <si>
-    <t xml:space="preserve">29.223690032959</t>
+    <t xml:space="preserve">29.2236919403076</t>
   </si>
   <si>
     <t xml:space="preserve">29.1281871795654</t>
@@ -2318,10 +2318,10 @@
     <t xml:space="preserve">28.3641681671143</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8866596221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2714405059814</t>
+    <t xml:space="preserve">27.8866577148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2714385986328</t>
   </si>
   <si>
     <t xml:space="preserve">27.8389053344727</t>
@@ -2330,7 +2330,7 @@
     <t xml:space="preserve">27.6479034423828</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6029243469238</t>
+    <t xml:space="preserve">28.6029262542725</t>
   </si>
   <si>
     <t xml:space="preserve">28.4119205474854</t>
@@ -2339,7 +2339,7 @@
     <t xml:space="preserve">29.366943359375</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4146919250488</t>
+    <t xml:space="preserve">29.4146938323975</t>
   </si>
   <si>
     <t xml:space="preserve">30.0354595184326</t>
@@ -2357,13 +2357,13 @@
     <t xml:space="preserve">29.7012023925781</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5579471588135</t>
+    <t xml:space="preserve">29.5579490661621</t>
   </si>
   <si>
     <t xml:space="preserve">29.796703338623</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2209167480469</t>
+    <t xml:space="preserve">28.2209148406982</t>
   </si>
   <si>
     <t xml:space="preserve">28.3164176940918</t>
@@ -2375,10 +2375,10 @@
     <t xml:space="preserve">26.9480724334717</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5770206451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.593017578125</t>
+    <t xml:space="preserve">27.5770225524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5930156707764</t>
   </si>
   <si>
     <t xml:space="preserve">28.0124492645264</t>
@@ -2396,7 +2396,7 @@
     <t xml:space="preserve">28.0608291625977</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3994941711426</t>
+    <t xml:space="preserve">28.3994960784912</t>
   </si>
   <si>
     <t xml:space="preserve">28.7381591796875</t>
@@ -2405,7 +2405,7 @@
     <t xml:space="preserve">29.1252059936523</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9800624847412</t>
+    <t xml:space="preserve">28.9800643920898</t>
   </si>
   <si>
     <t xml:space="preserve">27.7705459594727</t>
@@ -2447,19 +2447,19 @@
     <t xml:space="preserve">29.2219676971436</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0284442901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2543544769287</t>
+    <t xml:space="preserve">29.0284423828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2543525695801</t>
   </si>
   <si>
     <t xml:space="preserve">29.705774307251</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0444374084473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9960594177246</t>
+    <t xml:space="preserve">30.0444393157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.996057510376</t>
   </si>
   <si>
     <t xml:space="preserve">28.8349208831787</t>
@@ -2474,7 +2474,7 @@
     <t xml:space="preserve">28.2059707641602</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4962577819824</t>
+    <t xml:space="preserve">28.4962558746338</t>
   </si>
   <si>
     <t xml:space="preserve">27.0932140350342</t>
@@ -2483,7 +2483,7 @@
     <t xml:space="preserve">26.8513107299805</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0772190093994</t>
+    <t xml:space="preserve">26.077220916748</t>
   </si>
   <si>
     <t xml:space="preserve">26.8996906280518</t>
@@ -2507,22 +2507,22 @@
     <t xml:space="preserve">25.3031272888184</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2547454833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1579837799072</t>
+    <t xml:space="preserve">25.2547473907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1579856872559</t>
   </si>
   <si>
     <t xml:space="preserve">24.9160804748535</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4966506958008</t>
+    <t xml:space="preserve">25.4966487884521</t>
   </si>
   <si>
     <t xml:space="preserve">25.3515071868896</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0612239837646</t>
+    <t xml:space="preserve">25.061222076416</t>
   </si>
   <si>
     <t xml:space="preserve">24.7225570678711</t>
@@ -2531,7 +2531,7 @@
     <t xml:space="preserve">24.4806537628174</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6098003387451</t>
+    <t xml:space="preserve">23.6098022460938</t>
   </si>
   <si>
     <t xml:space="preserve">23.0292301177979</t>
@@ -2540,7 +2540,7 @@
     <t xml:space="preserve">22.9324722290039</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1743755340576</t>
+    <t xml:space="preserve">23.174373626709</t>
   </si>
   <si>
     <t xml:space="preserve">22.5938053131104</t>
@@ -2552,7 +2552,7 @@
     <t xml:space="preserve">21.6745719909668</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9164752960205</t>
+    <t xml:space="preserve">21.9164733886719</t>
   </si>
   <si>
     <t xml:space="preserve">21.5294284820557</t>
@@ -2564,16 +2564,16 @@
     <t xml:space="preserve">21.0940017700195</t>
   </si>
   <si>
-    <t xml:space="preserve">20.465051651001</t>
+    <t xml:space="preserve">20.4650535583496</t>
   </si>
   <si>
     <t xml:space="preserve">20.2231483459473</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4166736602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9004783630371</t>
+    <t xml:space="preserve">20.4166717529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9004802703857</t>
   </si>
   <si>
     <t xml:space="preserve">20.8037185668945</t>
@@ -2582,22 +2582,22 @@
     <t xml:space="preserve">20.6101951599121</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6585750579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7069568634033</t>
+    <t xml:space="preserve">20.658576965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7069549560547</t>
   </si>
   <si>
     <t xml:space="preserve">20.7553386688232</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3359069824219</t>
+    <t xml:space="preserve">21.3359050750732</t>
   </si>
   <si>
     <t xml:space="preserve">21.0456218719482</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4490585327148</t>
+    <t xml:space="preserve">19.4490566253662</t>
   </si>
   <si>
     <t xml:space="preserve">19.8361034393311</t>
@@ -2606,7 +2606,7 @@
     <t xml:space="preserve">19.2361812591553</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8878402709961</t>
+    <t xml:space="preserve">18.8878421783447</t>
   </si>
   <si>
     <t xml:space="preserve">18.6362609863281</t>
@@ -2630,13 +2630,13 @@
     <t xml:space="preserve">17.049373626709</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0300197601318</t>
+    <t xml:space="preserve">17.0300216674805</t>
   </si>
   <si>
     <t xml:space="preserve">16.8752021789551</t>
   </si>
   <si>
-    <t xml:space="preserve">18.326623916626</t>
+    <t xml:space="preserve">18.3266258239746</t>
   </si>
   <si>
     <t xml:space="preserve">18.7717266082764</t>
@@ -2648,13 +2648,13 @@
     <t xml:space="preserve">18.5782051086426</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4233856201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1331024169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4974365234375</t>
+    <t xml:space="preserve">18.4233875274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1331005096436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4974384307861</t>
   </si>
   <si>
     <t xml:space="preserve">20.1263866424561</t>
@@ -2663,7 +2663,7 @@
     <t xml:space="preserve">19.9328651428223</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3199100494385</t>
+    <t xml:space="preserve">20.3199119567871</t>
   </si>
   <si>
     <t xml:space="preserve">19.6425800323486</t>
@@ -2678,10 +2678,10 @@
     <t xml:space="preserve">19.1781253814697</t>
   </si>
   <si>
-    <t xml:space="preserve">19.023307800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1974792480469</t>
+    <t xml:space="preserve">19.0233058929443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1974773406982</t>
   </si>
   <si>
     <t xml:space="preserve">18.9071941375732</t>
@@ -2690,7 +2690,7 @@
     <t xml:space="preserve">19.8844833374023</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4006748199463</t>
+    <t xml:space="preserve">19.4006767272949</t>
   </si>
   <si>
     <t xml:space="preserve">19.7877235412598</t>
@@ -2708,7 +2708,7 @@
     <t xml:space="preserve">22.0132369995117</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8357105255127</t>
+    <t xml:space="preserve">22.8357086181641</t>
   </si>
   <si>
     <t xml:space="preserve">22.1583786010742</t>
@@ -2720,19 +2720,19 @@
     <t xml:space="preserve">22.3519020080566</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7229518890381</t>
+    <t xml:space="preserve">21.7229537963867</t>
   </si>
   <si>
     <t xml:space="preserve">21.5778102874756</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4326667785645</t>
+    <t xml:space="preserve">21.4326686859131</t>
   </si>
   <si>
     <t xml:space="preserve">22.061616897583</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4970436096191</t>
+    <t xml:space="preserve">22.4970455169678</t>
   </si>
   <si>
     <t xml:space="preserve">22.2551403045654</t>
@@ -2744,7 +2744,7 @@
     <t xml:space="preserve">21.6261901855469</t>
   </si>
   <si>
-    <t xml:space="preserve">21.771333694458</t>
+    <t xml:space="preserve">21.7713317871094</t>
   </si>
   <si>
     <t xml:space="preserve">22.3035202026367</t>
@@ -2753,10 +2753,10 @@
     <t xml:space="preserve">22.8840885162354</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7873268127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9648551940918</t>
+    <t xml:space="preserve">22.7873287200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9648571014404</t>
   </si>
   <si>
     <t xml:space="preserve">20.948860168457</t>
@@ -2771,7 +2771,7 @@
     <t xml:space="preserve">20.1747703552246</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5134353637695</t>
+    <t xml:space="preserve">20.5134334564209</t>
   </si>
   <si>
     <t xml:space="preserve">20.0296268463135</t>
@@ -2780,13 +2780,13 @@
     <t xml:space="preserve">22.9808521270752</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1259918212891</t>
+    <t xml:space="preserve">23.1259937286377</t>
   </si>
   <si>
     <t xml:space="preserve">21.3842868804932</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8520984649658</t>
+    <t xml:space="preserve">20.8520965576172</t>
   </si>
   <si>
     <t xml:space="preserve">20.5618133544922</t>
@@ -3378,6 +3378,9 @@
   </si>
   <si>
     <t xml:space="preserve">36.3499984741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.0999984741211</t>
   </si>
 </sst>
 </file>
@@ -68716,7 +68719,7 @@
     </row>
     <row r="2501">
       <c r="A2501" s="1" t="n">
-        <v>45960.6909837963</v>
+        <v>45960.3333333333</v>
       </c>
       <c r="B2501" t="n">
         <v>4971</v>
@@ -68737,6 +68740,32 @@
         <v>1121</v>
       </c>
       <c r="H2501" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2502">
+      <c r="A2502" s="1" t="n">
+        <v>45961.6909953704</v>
+      </c>
+      <c r="B2502" t="n">
+        <v>3897</v>
+      </c>
+      <c r="C2502" t="n">
+        <v>36.5999984741211</v>
+      </c>
+      <c r="D2502" t="n">
+        <v>36.0499992370605</v>
+      </c>
+      <c r="E2502" t="n">
+        <v>36.5999984741211</v>
+      </c>
+      <c r="F2502" t="n">
+        <v>36.0999984741211</v>
+      </c>
+      <c r="G2502" t="s">
+        <v>1122</v>
+      </c>
+      <c r="H2502" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LUVE.MI.xlsx
+++ b/data/LUVE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1123" uniqueCount="1123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="1124">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,28 +38,28 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30043315887451</t>
+    <t xml:space="preserve">8.3004322052002</t>
   </si>
   <si>
     <t xml:space="preserve">LUVE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3170337677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28383255004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09292221069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19667720794678</t>
+    <t xml:space="preserve">8.31703472137451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28383159637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09292316436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19667625427246</t>
   </si>
   <si>
     <t xml:space="preserve">8.07632064819336</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15102577209473</t>
+    <t xml:space="preserve">8.15102481842041</t>
   </si>
   <si>
     <t xml:space="preserve">8.17177677154541</t>
@@ -68,76 +68,76 @@
     <t xml:space="preserve">8.03896999359131</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08462142944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06802177429199</t>
+    <t xml:space="preserve">8.08462047576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06802082061768</t>
   </si>
   <si>
     <t xml:space="preserve">7.96841669082642</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01821899414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99746942520142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91861343383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91446113586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91031217575073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88541221618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87711191177368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85220956802368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64884948730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71940279006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70280122756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69035148620605</t>
+    <t xml:space="preserve">8.01821613311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99746799468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91861295700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91446352005005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91031408309937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88541173934937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87711048126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85221004486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64884996414185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71940326690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70280170440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69035196304321</t>
   </si>
   <si>
     <t xml:space="preserve">7.61979818344116</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55754375457764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55339574813843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63639783859253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76920413970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80240774154663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93521451950073</t>
+    <t xml:space="preserve">7.55754518508911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55339336395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63639831542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76920461654663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80240869522095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93521356582642</t>
   </si>
   <si>
     <t xml:space="preserve">8.10122299194336</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05141925811768</t>
+    <t xml:space="preserve">8.05142021179199</t>
   </si>
   <si>
     <t xml:space="preserve">8.18422698974609</t>
@@ -146,28 +146,28 @@
     <t xml:space="preserve">8.13442516326904</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00161743164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96011638641357</t>
+    <t xml:space="preserve">8.00161838531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96011590957642</t>
   </si>
   <si>
     <t xml:space="preserve">8.21742725372314</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3585376739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3253345489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2921314239502</t>
+    <t xml:space="preserve">8.35853576660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32533359527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29213333129883</t>
   </si>
   <si>
     <t xml:space="preserve">8.20082855224609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15932655334473</t>
+    <t xml:space="preserve">8.15932464599609</t>
   </si>
   <si>
     <t xml:space="preserve">8.30336380004883</t>
@@ -176,13 +176,13 @@
     <t xml:space="preserve">8.36267375946045</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43045520782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15085315704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17627143859863</t>
+    <t xml:space="preserve">8.43045616149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15085220336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17626953125</t>
   </si>
   <si>
     <t xml:space="preserve">8.2059268951416</t>
@@ -197,34 +197,34 @@
     <t xml:space="preserve">8.21863460540771</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21016311645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21439933776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20169162750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26099872589111</t>
+    <t xml:space="preserve">8.21016120910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21439838409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20169067382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26100063323975</t>
   </si>
   <si>
     <t xml:space="preserve">8.09154319763184</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10848808288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04918003082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96445083618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92208766937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87972402572632</t>
+    <t xml:space="preserve">8.10848903656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04917907714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96445178985596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92208671569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87972211837769</t>
   </si>
   <si>
     <t xml:space="preserve">7.83735942840576</t>
@@ -236,28 +236,28 @@
     <t xml:space="preserve">7.93479537963867</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75262975692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71026754379272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93903303146362</t>
+    <t xml:space="preserve">7.75263023376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71026611328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93903160095215</t>
   </si>
   <si>
     <t xml:space="preserve">7.81194019317627</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79499387741089</t>
+    <t xml:space="preserve">7.79499435424805</t>
   </si>
   <si>
     <t xml:space="preserve">7.62553834915161</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66790390014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84583044052124</t>
+    <t xml:space="preserve">7.66790246963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84583187103271</t>
   </si>
   <si>
     <t xml:space="preserve">8.19321727752686</t>
@@ -269,13 +269,13 @@
     <t xml:space="preserve">8.51518440246582</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52365875244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5999116897583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78631401062012</t>
+    <t xml:space="preserve">8.52365779876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59991264343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78631496429443</t>
   </si>
   <si>
     <t xml:space="preserve">8.71853160858154</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">8.540602684021</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46858406066895</t>
+    <t xml:space="preserve">8.46858501434326</t>
   </si>
   <si>
     <t xml:space="preserve">8.46434688568115</t>
@@ -296,22 +296,22 @@
     <t xml:space="preserve">8.55754852294922</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57449436187744</t>
+    <t xml:space="preserve">8.57449340820312</t>
   </si>
   <si>
     <t xml:space="preserve">8.81173229217529</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7270040512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64227676391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89645957946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02355194091797</t>
+    <t xml:space="preserve">8.72700595855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6422758102417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89646053314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0235538482666</t>
   </si>
   <si>
     <t xml:space="preserve">9.09980869293213</t>
@@ -344,13 +344,13 @@
     <t xml:space="preserve">9.32010364532471</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1252269744873</t>
+    <t xml:space="preserve">9.12522888183594</t>
   </si>
   <si>
     <t xml:space="preserve">9.60817909240723</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4048318862915</t>
+    <t xml:space="preserve">9.40483093261719</t>
   </si>
   <si>
     <t xml:space="preserve">9.48955917358398</t>
@@ -359,28 +359,28 @@
     <t xml:space="preserve">9.38788509368896</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5319242477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4810848236084</t>
+    <t xml:space="preserve">9.53192329406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48108768463135</t>
   </si>
   <si>
     <t xml:space="preserve">9.44719505310059</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5403938293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5742883682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47261333465576</t>
+    <t xml:space="preserve">9.54039669036865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57428741455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47261428833008</t>
   </si>
   <si>
     <t xml:space="preserve">9.41330337524414</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42177486419678</t>
+    <t xml:space="preserve">9.42177581787109</t>
   </si>
   <si>
     <t xml:space="preserve">9.51497650146484</t>
@@ -392,16 +392,16 @@
     <t xml:space="preserve">9.74374389648438</t>
   </si>
   <si>
-    <t xml:space="preserve">10.065710067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2521133422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1334924697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99792766571045</t>
+    <t xml:space="preserve">10.0657119750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2521123886108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1334934234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99792957305908</t>
   </si>
   <si>
     <t xml:space="preserve">9.95556354522705</t>
@@ -416,55 +416,55 @@
     <t xml:space="preserve">9.91319942474365</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0148725509644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1589117050171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0402917861938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70137882232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73527050018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70985221862793</t>
+    <t xml:space="preserve">10.0148735046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1589107513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0402936935425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70137977600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73526859283447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70985317230225</t>
   </si>
   <si>
     <t xml:space="preserve">10.0826559066772</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86236381530762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1250200271606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2944755554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4808788299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5317163467407</t>
+    <t xml:space="preserve">9.8623628616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.125020980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2944774627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4808778762817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5317153930664</t>
   </si>
   <si>
     <t xml:space="preserve">10.5147705078125</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8028450012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.912992477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.862156867981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0146656036377</t>
+    <t xml:space="preserve">10.8028469085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9129915237427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8621559143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0146675109863</t>
   </si>
   <si>
     <t xml:space="preserve">11.0570306777954</t>
@@ -473,19 +473,19 @@
     <t xml:space="preserve">11.2773237228394</t>
   </si>
   <si>
-    <t xml:space="preserve">11.438307762146</t>
+    <t xml:space="preserve">11.4383068084717</t>
   </si>
   <si>
     <t xml:space="preserve">11.6586008071899</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5823459625244</t>
+    <t xml:space="preserve">11.5823450088501</t>
   </si>
   <si>
     <t xml:space="preserve">11.4806718826294</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5908193588257</t>
+    <t xml:space="preserve">11.5908174514771</t>
   </si>
   <si>
     <t xml:space="preserve">11.7009649276733</t>
@@ -494,25 +494,25 @@
     <t xml:space="preserve">11.7772197723389</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8111114501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8365297317505</t>
+    <t xml:space="preserve">11.811110496521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8365306854248</t>
   </si>
   <si>
     <t xml:space="preserve">11.6670742034912</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5992908477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5230360031128</t>
+    <t xml:space="preserve">11.599289894104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5230369567871</t>
   </si>
   <si>
     <t xml:space="preserve">11.6077632904053</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6263809204102</t>
+    <t xml:space="preserve">11.6263799667358</t>
   </si>
   <si>
     <t xml:space="preserve">11.7297267913818</t>
@@ -521,16 +521,16 @@
     <t xml:space="preserve">11.6952772140503</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6780557632446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7986240386963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.884744644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9105815887451</t>
+    <t xml:space="preserve">11.678053855896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.798623085022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8847455978394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9105806350708</t>
   </si>
   <si>
     <t xml:space="preserve">12.0655994415283</t>
@@ -539,25 +539,25 @@
     <t xml:space="preserve">12.3153505325317</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3584117889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0569877624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1431093215942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9967041015625</t>
+    <t xml:space="preserve">12.3584127426147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0569887161255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1431074142456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9967031478882</t>
   </si>
   <si>
     <t xml:space="preserve">11.8416843414307</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7555627822876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7125024795532</t>
+    <t xml:space="preserve">11.7555618286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7125034332275</t>
   </si>
   <si>
     <t xml:space="preserve">11.8502960205078</t>
@@ -566,13 +566,13 @@
     <t xml:space="preserve">11.9191942214966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.962254524231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0397634506226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0483751296997</t>
+    <t xml:space="preserve">11.9622535705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0397624969482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.048376083374</t>
   </si>
   <si>
     <t xml:space="preserve">11.7900114059448</t>
@@ -581,28 +581,28 @@
     <t xml:space="preserve">12.0311517715454</t>
   </si>
   <si>
-    <t xml:space="preserve">11.945029258728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8158473968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8933572769165</t>
+    <t xml:space="preserve">11.9450302124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8158464431763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8933582305908</t>
   </si>
   <si>
     <t xml:space="preserve">11.8761329650879</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8244590759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8675203323364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9019689559937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.927806854248</t>
+    <t xml:space="preserve">11.8244600296021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8675212860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9019680023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9278059005737</t>
   </si>
   <si>
     <t xml:space="preserve">11.7211141586304</t>
@@ -611,10 +611,10 @@
     <t xml:space="preserve">11.6694421768188</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6349945068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6091566085815</t>
+    <t xml:space="preserve">11.6349935531616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6091556549072</t>
   </si>
   <si>
     <t xml:space="preserve">11.57470703125</t>
@@ -623,31 +623,34 @@
     <t xml:space="preserve">11.5316476821899</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3680181503296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3594045639038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2818965911865</t>
+    <t xml:space="preserve">11.5230350494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.368016242981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3594055175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2818946838379</t>
   </si>
   <si>
     <t xml:space="preserve">11.2302227020264</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1957740783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1871614456177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1096515655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0579805374146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1785507202148</t>
+    <t xml:space="preserve">11.1957750320435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1871633529663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1096534729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0579814910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1785488128662</t>
   </si>
   <si>
     <t xml:space="preserve">11.1268768310547</t>
@@ -662,16 +665,16 @@
     <t xml:space="preserve">11.023530960083</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0838165283203</t>
+    <t xml:space="preserve">11.083815574646</t>
   </si>
   <si>
     <t xml:space="preserve">11.1354894638062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2043867111206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3163433074951</t>
+    <t xml:space="preserve">11.2043857574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3163442611694</t>
   </si>
   <si>
     <t xml:space="preserve">11.454137802124</t>
@@ -686,10 +689,10 @@
     <t xml:space="preserve">11.2905073165894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1613264083862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2646713256836</t>
+    <t xml:space="preserve">11.1613254547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2646722793579</t>
   </si>
   <si>
     <t xml:space="preserve">11.1527137756348</t>
@@ -698,76 +701,76 @@
     <t xml:space="preserve">11.0407562255859</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4196901321411</t>
+    <t xml:space="preserve">11.4196910858154</t>
   </si>
   <si>
     <t xml:space="preserve">11.2216100692749</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2388353347778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3421792984009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9546346664429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9632453918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0063056945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0924272537231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74032402038574</t>
+    <t xml:space="preserve">11.2388343811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3421821594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9546356201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.96324634552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0063076019287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0924282073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74032306671143</t>
   </si>
   <si>
     <t xml:space="preserve">9.0169038772583</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21498394012451</t>
+    <t xml:space="preserve">9.2149829864502</t>
   </si>
   <si>
     <t xml:space="preserve">9.3786153793335</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49057102203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5077953338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59391784667969</t>
+    <t xml:space="preserve">9.49057292938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50779724121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59391689300537</t>
   </si>
   <si>
     <t xml:space="preserve">9.60252952575684</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68865203857422</t>
+    <t xml:space="preserve">9.6886510848999</t>
   </si>
   <si>
     <t xml:space="preserve">9.56808185577393</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39583778381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34416484832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25804424285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30110454559326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41306209564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28388214111328</t>
+    <t xml:space="preserve">9.39583873748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34416580200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2580451965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30110549926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41306304931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28388023376465</t>
   </si>
   <si>
     <t xml:space="preserve">9.24081993103027</t>
@@ -776,7 +779,7 @@
     <t xml:space="preserve">9.12886238098145</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02551555633545</t>
+    <t xml:space="preserve">9.02551746368408</t>
   </si>
   <si>
     <t xml:space="preserve">9.20637130737305</t>
@@ -791,70 +794,70 @@
     <t xml:space="preserve">9.65420246124268</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66281604766846</t>
+    <t xml:space="preserve">9.66281509399414</t>
   </si>
   <si>
     <t xml:space="preserve">9.64559078216553</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67142677307129</t>
+    <t xml:space="preserve">9.67142581939697</t>
   </si>
   <si>
     <t xml:space="preserve">9.75754928588867</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71448707580566</t>
+    <t xml:space="preserve">9.71448802947998</t>
   </si>
   <si>
     <t xml:space="preserve">9.09441375732422</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9393949508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14608669281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12024974822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83505630493164</t>
+    <t xml:space="preserve">8.93939590454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14608764648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1202507019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83505821228027</t>
   </si>
   <si>
     <t xml:space="preserve">9.73171234130859</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90395450592041</t>
+    <t xml:space="preserve">9.90395355224609</t>
   </si>
   <si>
     <t xml:space="preserve">9.77477264404297</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5336332321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49918270111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57669353485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58530426025391</t>
+    <t xml:space="preserve">9.53363227844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49918365478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57669162750244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58530616760254</t>
   </si>
   <si>
     <t xml:space="preserve">9.47334766387939</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4302864074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54224586486816</t>
+    <t xml:space="preserve">9.43028736114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54224491119385</t>
   </si>
   <si>
     <t xml:space="preserve">9.17192363739014</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23220729827881</t>
+    <t xml:space="preserve">9.23220920562744</t>
   </si>
   <si>
     <t xml:space="preserve">9.55947017669678</t>
@@ -875,10 +878,10 @@
     <t xml:space="preserve">9.08580207824707</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04274082183838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.999680519104</t>
+    <t xml:space="preserve">9.04273986816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99968147277832</t>
   </si>
   <si>
     <t xml:space="preserve">8.82743740081787</t>
@@ -890,16 +893,16 @@
     <t xml:space="preserve">8.87049865722656</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7843770980835</t>
+    <t xml:space="preserve">8.78437614440918</t>
   </si>
   <si>
     <t xml:space="preserve">8.7413158416748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61213302612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59490966796875</t>
+    <t xml:space="preserve">8.61213397979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59490871429443</t>
   </si>
   <si>
     <t xml:space="preserve">8.65519428253174</t>
@@ -911,34 +914,34 @@
     <t xml:space="preserve">9.06314563751221</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10714054107666</t>
+    <t xml:space="preserve">9.10714149475098</t>
   </si>
   <si>
     <t xml:space="preserve">9.0191478729248</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97515296936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9311580657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88716125488281</t>
+    <t xml:space="preserve">8.97515201568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93115615844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88716220855713</t>
   </si>
   <si>
     <t xml:space="preserve">8.84316539764404</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76397228240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48239994049072</t>
+    <t xml:space="preserve">8.76397323608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48240089416504</t>
   </si>
   <si>
     <t xml:space="preserve">8.71117687225342</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62318801879883</t>
+    <t xml:space="preserve">8.62318706512451</t>
   </si>
   <si>
     <t xml:space="preserve">8.58798980712891</t>
@@ -947,37 +950,37 @@
     <t xml:space="preserve">8.6583833694458</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60558700561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7287769317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69358062744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74637317657471</t>
+    <t xml:space="preserve">8.60558795928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72877597808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69357872009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74637413024902</t>
   </si>
   <si>
     <t xml:space="preserve">8.53519439697266</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44720458984375</t>
+    <t xml:space="preserve">8.44720268249512</t>
   </si>
   <si>
     <t xml:space="preserve">8.27121925354004</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32401466369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.288818359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78157138824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64078426361084</t>
+    <t xml:space="preserve">8.32401275634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28881740570068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78157043457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64078521728516</t>
   </si>
   <si>
     <t xml:space="preserve">8.79916858673096</t>
@@ -986,43 +989,43 @@
     <t xml:space="preserve">8.67598152160645</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23912906646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37111473083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32712078094482</t>
+    <t xml:space="preserve">9.23912811279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37111568450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32711887359619</t>
   </si>
   <si>
     <t xml:space="preserve">9.19513130187988</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15113639831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46479988098145</t>
+    <t xml:space="preserve">9.15113735198975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46480083465576</t>
   </si>
   <si>
     <t xml:space="preserve">8.41200637817383</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49999809265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34161281585693</t>
+    <t xml:space="preserve">8.49999713897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34161376953125</t>
   </si>
   <si>
     <t xml:space="preserve">8.23602104187012</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30641555786133</t>
+    <t xml:space="preserve">8.30641651153564</t>
   </si>
   <si>
     <t xml:space="preserve">8.13043212890625</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1832275390625</t>
+    <t xml:space="preserve">8.18322849273682</t>
   </si>
   <si>
     <t xml:space="preserve">8.16562938690186</t>
@@ -1031,7 +1034,7 @@
     <t xml:space="preserve">8.21842575073242</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25362110137939</t>
+    <t xml:space="preserve">8.25362014770508</t>
   </si>
   <si>
     <t xml:space="preserve">8.37681007385254</t>
@@ -1040,64 +1043,64 @@
     <t xml:space="preserve">8.51759624481201</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28312397003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41511154174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63508987426758</t>
+    <t xml:space="preserve">9.28312492370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41511058807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63509082794189</t>
   </si>
   <si>
     <t xml:space="preserve">9.59109497070312</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8990650177002</t>
+    <t xml:space="preserve">9.89906597137451</t>
   </si>
   <si>
     <t xml:space="preserve">10.1190433502197</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1630420684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2070379257202</t>
+    <t xml:space="preserve">10.1630411148071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2070360183716</t>
   </si>
   <si>
     <t xml:space="preserve">10.3390245437622</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2950286865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.383020401001</t>
+    <t xml:space="preserve">10.2950277328491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3830184936523</t>
   </si>
   <si>
     <t xml:space="preserve">10.2510328292847</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4270162582397</t>
+    <t xml:space="preserve">10.4270172119141</t>
   </si>
   <si>
     <t xml:space="preserve">10.0750484466553</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5150079727173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6498155593872</t>
+    <t xml:space="preserve">10.5150089263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6498146057129</t>
   </si>
   <si>
     <t xml:space="preserve">10.4700717926025</t>
   </si>
   <si>
-    <t xml:space="preserve">10.694751739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6048784255981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.380199432373</t>
+    <t xml:space="preserve">10.6947507858276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6048803329468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3802003860474</t>
   </si>
   <si>
     <t xml:space="preserve">10.2453908920288</t>
@@ -1106,16 +1109,13 @@
     <t xml:space="preserve">10.0656480789185</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4251356124878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5150089263916</t>
+    <t xml:space="preserve">10.4251346588135</t>
   </si>
   <si>
     <t xml:space="preserve">10.3352632522583</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2903270721436</t>
+    <t xml:space="preserve">10.2903280258179</t>
   </si>
   <si>
     <t xml:space="preserve">10.200457572937</t>
@@ -1130,10 +1130,10 @@
     <t xml:space="preserve">9.93084049224854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88590431213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1555213928223</t>
+    <t xml:space="preserve">9.88590526580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1555204391479</t>
   </si>
   <si>
     <t xml:space="preserve">10.020712852478</t>
@@ -1145,10 +1145,10 @@
     <t xml:space="preserve">9.70616149902344</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34667301177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30173778533936</t>
+    <t xml:space="preserve">9.3466739654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30173683166504</t>
   </si>
   <si>
     <t xml:space="preserve">9.39160919189453</t>
@@ -1160,16 +1160,16 @@
     <t xml:space="preserve">9.61628913879395</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52641868591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43654537200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12199401855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03212261199951</t>
+    <t xml:space="preserve">9.52641677856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43654632568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.121994972229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03212356567383</t>
   </si>
   <si>
     <t xml:space="preserve">9.1669282913208</t>
@@ -1184,7 +1184,7 @@
     <t xml:space="preserve">8.98718643188477</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57135200500488</t>
+    <t xml:space="preserve">9.5713529586792</t>
   </si>
   <si>
     <t xml:space="preserve">9.66122531890869</t>
@@ -1193,22 +1193,22 @@
     <t xml:space="preserve">9.79603290557861</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9643669128418</t>
+    <t xml:space="preserve">10.9643659591675</t>
   </si>
   <si>
     <t xml:space="preserve">11.4586629867554</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5035991668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2339820861816</t>
+    <t xml:space="preserve">11.5035972595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.233983039856</t>
   </si>
   <si>
     <t xml:space="preserve">11.1441106796265</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9194297790527</t>
+    <t xml:space="preserve">10.9194307327271</t>
   </si>
   <si>
     <t xml:space="preserve">10.8744955062866</t>
@@ -1217,16 +1217,16 @@
     <t xml:space="preserve">11.0093021392822</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2789192199707</t>
+    <t xml:space="preserve">11.2789182662964</t>
   </si>
   <si>
     <t xml:space="preserve">11.4137258529663</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5485334396362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6833410263062</t>
+    <t xml:space="preserve">11.5485343933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6833429336548</t>
   </si>
   <si>
     <t xml:space="preserve">11.7732152938843</t>
@@ -1238,25 +1238,25 @@
     <t xml:space="preserve">12.132700920105</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9978942871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8181495666504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.593469619751</t>
+    <t xml:space="preserve">11.9978952407837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8181486129761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5934686660767</t>
   </si>
   <si>
     <t xml:space="preserve">12.3124446868896</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5820598602295</t>
+    <t xml:space="preserve">12.5820608139038</t>
   </si>
   <si>
     <t xml:space="preserve">12.9415483474731</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8067398071289</t>
+    <t xml:space="preserve">12.8067407608032</t>
   </si>
   <si>
     <t xml:space="preserve">12.7618036270142</t>
@@ -1274,19 +1274,19 @@
     <t xml:space="preserve">12.2675094604492</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4023170471191</t>
+    <t xml:space="preserve">12.4023160934448</t>
   </si>
   <si>
     <t xml:space="preserve">12.6269969940186</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6719331741333</t>
+    <t xml:space="preserve">12.671932220459</t>
   </si>
   <si>
     <t xml:space="preserve">12.8966121673584</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7282781600952</t>
+    <t xml:space="preserve">11.7282772064209</t>
   </si>
   <si>
     <t xml:space="preserve">10.7846240997314</t>
@@ -1298,7 +1298,7 @@
     <t xml:space="preserve">8.89731407165527</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98062086105347</t>
+    <t xml:space="preserve">7.98062133789062</t>
   </si>
   <si>
     <t xml:space="preserve">7.81885194778442</t>
@@ -1307,10 +1307,10 @@
     <t xml:space="preserve">7.53126192092896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89074945449829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53782653808594</t>
+    <t xml:space="preserve">7.89074897766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53782749176025</t>
   </si>
   <si>
     <t xml:space="preserve">7.962646484375</t>
@@ -1325,34 +1325,34 @@
     <t xml:space="preserve">8.66364765167236</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86136627197266</t>
+    <t xml:space="preserve">8.86136436462402</t>
   </si>
   <si>
     <t xml:space="preserve">9.21186637878418</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93848896026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80045413970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89247894287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66242027282715</t>
+    <t xml:space="preserve">9.93848991394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80045509338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89247798919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66242122650146</t>
   </si>
   <si>
     <t xml:space="preserve">9.7084321975708</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84646701812744</t>
+    <t xml:space="preserve">9.84646606445312</t>
   </si>
   <si>
     <t xml:space="preserve">10.1225357055664</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75444412231445</t>
+    <t xml:space="preserve">9.75444316864014</t>
   </si>
   <si>
     <t xml:space="preserve">10.3986053466797</t>
@@ -1364,52 +1364,52 @@
     <t xml:space="preserve">10.720685005188</t>
   </si>
   <si>
-    <t xml:space="preserve">10.582649230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8587198257446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6746740341187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.996753692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.628662109375</t>
+    <t xml:space="preserve">10.5826501846313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8587207794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6746730804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9967546463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6286630630493</t>
   </si>
   <si>
     <t xml:space="preserve">10.766697883606</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4906272888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1347904205322</t>
+    <t xml:space="preserve">10.490626335144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1347894668579</t>
   </si>
   <si>
     <t xml:space="preserve">11.3188352584839</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5028810501099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1807994842529</t>
+    <t xml:space="preserve">11.5028820037842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1808004379272</t>
   </si>
   <si>
     <t xml:space="preserve">11.0427665710449</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2728223800659</t>
+    <t xml:space="preserve">11.2728233337402</t>
   </si>
   <si>
     <t xml:space="preserve">10.9507427215576</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0887784957886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8127098083496</t>
+    <t xml:space="preserve">11.0887775421143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8127088546753</t>
   </si>
   <si>
     <t xml:space="preserve">10.904730796814</t>
@@ -1418,13 +1418,13 @@
     <t xml:space="preserve">11.4108581542969</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4568710327148</t>
+    <t xml:space="preserve">11.4568700790405</t>
   </si>
   <si>
     <t xml:space="preserve">11.2268114089966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3648481369019</t>
+    <t xml:space="preserve">11.3648471832275</t>
   </si>
   <si>
     <t xml:space="preserve">11.5488929748535</t>
@@ -1436,22 +1436,22 @@
     <t xml:space="preserve">11.6869268417358</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9629964828491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7789516448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0090084075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1010313034058</t>
+    <t xml:space="preserve">11.9629974365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7789497375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0090074539185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1010303497314</t>
   </si>
   <si>
     <t xml:space="preserve">11.7329397201538</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8249616622925</t>
+    <t xml:space="preserve">11.8249626159668</t>
   </si>
   <si>
     <t xml:space="preserve">12.0550212860107</t>
@@ -1460,7 +1460,7 @@
     <t xml:space="preserve">11.8709726333618</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9169855117798</t>
+    <t xml:space="preserve">11.9169845581055</t>
   </si>
   <si>
     <t xml:space="preserve">11.6409158706665</t>
@@ -1469,16 +1469,16 @@
     <t xml:space="preserve">12.1470422744751</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6991815567017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.791202545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0672731399536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8832263946533</t>
+    <t xml:space="preserve">12.6991806030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7912034988403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0672721862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8832273483276</t>
   </si>
   <si>
     <t xml:space="preserve">12.9292392730713</t>
@@ -1490,31 +1490,31 @@
     <t xml:space="preserve">13.2513198852539</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1132841110229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1592960357666</t>
+    <t xml:space="preserve">13.1132850646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1592969894409</t>
   </si>
   <si>
     <t xml:space="preserve">13.3893537521362</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2973308563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9752511978149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7114334106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4353647232056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5151348114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3770999908447</t>
+    <t xml:space="preserve">13.2973299026489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9752502441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7114343643188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4353656768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5151357650757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3770990371704</t>
   </si>
   <si>
     <t xml:space="preserve">12.837215423584</t>
@@ -1526,25 +1526,25 @@
     <t xml:space="preserve">12.6531705856323</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3433437347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6194124221802</t>
+    <t xml:space="preserve">13.3433427810669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6194114685059</t>
   </si>
   <si>
     <t xml:space="preserve">13.8494691848755</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9414930343628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1715497970581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3555955886841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1255388259888</t>
+    <t xml:space="preserve">13.9414920806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1715488433838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3555965423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1255397796631</t>
   </si>
   <si>
     <t xml:space="preserve">14.4936304092407</t>
@@ -1553,16 +1553,16 @@
     <t xml:space="preserve">14.7236881256104</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6776752471924</t>
+    <t xml:space="preserve">14.6776762008667</t>
   </si>
   <si>
     <t xml:space="preserve">14.8157119750977</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8617238998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0457677841187</t>
+    <t xml:space="preserve">14.861722946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.045768737793</t>
   </si>
   <si>
     <t xml:space="preserve">14.5396423339844</t>
@@ -1574,16 +1574,16 @@
     <t xml:space="preserve">14.4476194381714</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2635736465454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9875040054321</t>
+    <t xml:space="preserve">14.2635726928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9875030517578</t>
   </si>
   <si>
     <t xml:space="preserve">14.3095846176147</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6654253005981</t>
+    <t xml:space="preserve">13.6654243469238</t>
   </si>
   <si>
     <t xml:space="preserve">13.8034572601318</t>
@@ -3381,6 +3381,9 @@
   </si>
   <si>
     <t xml:space="preserve">36.0999984741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.0499992370605</t>
   </si>
 </sst>
 </file>
@@ -13903,7 +13906,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G392" t="s">
-        <v>164</v>
+        <v>203</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -13929,7 +13932,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G393" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -13955,7 +13958,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G394" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -13981,7 +13984,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G395" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -14007,7 +14010,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G396" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -14033,7 +14036,7 @@
         <v>13</v>
       </c>
       <c r="G397" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -14059,7 +14062,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G398" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -14085,7 +14088,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G399" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -14111,7 +14114,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G400" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -14137,7 +14140,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G401" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -14163,7 +14166,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G402" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -14189,7 +14192,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G403" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -14215,7 +14218,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G404" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -14241,7 +14244,7 @@
         <v>13</v>
       </c>
       <c r="G405" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -14267,7 +14270,7 @@
         <v>13</v>
       </c>
       <c r="G406" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -14293,7 +14296,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G407" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -14319,7 +14322,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G408" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -14345,7 +14348,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G409" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -14371,7 +14374,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G410" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -14397,7 +14400,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G411" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -14423,7 +14426,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G412" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -14449,7 +14452,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G413" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -14475,7 +14478,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G414" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -14501,7 +14504,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G415" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -14527,7 +14530,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G416" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -14553,7 +14556,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G417" t="s">
-        <v>164</v>
+        <v>203</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -14579,7 +14582,7 @@
         <v>13.25</v>
       </c>
       <c r="G418" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -14605,7 +14608,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G419" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -14631,7 +14634,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G420" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -14657,7 +14660,7 @@
         <v>13</v>
       </c>
       <c r="G421" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -14683,7 +14686,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G422" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -14709,7 +14712,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G423" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -14735,7 +14738,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G424" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -14761,7 +14764,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G425" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -14787,7 +14790,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G426" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -14813,7 +14816,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G427" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -14839,7 +14842,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G428" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -14865,7 +14868,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G429" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -14891,7 +14894,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G430" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -14917,7 +14920,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G431" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -14943,7 +14946,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G432" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -14969,7 +14972,7 @@
         <v>13.1700000762939</v>
       </c>
       <c r="G433" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -14995,7 +14998,7 @@
         <v>13</v>
       </c>
       <c r="G434" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -15021,7 +15024,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G435" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -15047,7 +15050,7 @@
         <v>12.7299995422363</v>
       </c>
       <c r="G436" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -15073,7 +15076,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G437" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -15099,7 +15102,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G438" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -15125,7 +15128,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G439" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -15151,7 +15154,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G440" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -15177,7 +15180,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G441" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -15203,7 +15206,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G442" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -15229,7 +15232,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G443" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -15255,7 +15258,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G444" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -15281,7 +15284,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G445" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -15307,7 +15310,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G446" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -15333,7 +15336,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G447" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -15359,7 +15362,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G448" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -15385,7 +15388,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G449" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -15411,7 +15414,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G450" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -15437,7 +15440,7 @@
         <v>11.25</v>
       </c>
       <c r="G451" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -15463,7 +15466,7 @@
         <v>11.1099996566772</v>
       </c>
       <c r="G452" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -15489,7 +15492,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G453" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -15515,7 +15518,7 @@
         <v>11.25</v>
       </c>
       <c r="G454" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -15541,7 +15544,7 @@
         <v>10.9099998474121</v>
       </c>
       <c r="G455" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -15567,7 +15570,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G456" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -15593,7 +15596,7 @@
         <v>10.75</v>
       </c>
       <c r="G457" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -15619,7 +15622,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G458" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -15645,7 +15648,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G459" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -15671,7 +15674,7 @@
         <v>10.9300003051758</v>
       </c>
       <c r="G460" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -15697,7 +15700,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G461" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -15723,7 +15726,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G462" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -15749,7 +15752,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G463" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -15775,7 +15778,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G464" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -15801,7 +15804,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G465" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -15827,7 +15830,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G466" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -15853,7 +15856,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G467" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -15879,7 +15882,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G468" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -15905,7 +15908,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G469" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -15931,7 +15934,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G470" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -15957,7 +15960,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G471" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -15983,7 +15986,7 @@
         <v>11.2299995422363</v>
       </c>
       <c r="G472" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -16009,7 +16012,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G473" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -16035,7 +16038,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G474" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -16061,7 +16064,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G475" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -16087,7 +16090,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G476" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -16113,7 +16116,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G477" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -16139,7 +16142,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G478" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -16165,7 +16168,7 @@
         <v>10.75</v>
       </c>
       <c r="G479" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -16191,7 +16194,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G480" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -16217,7 +16220,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G481" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -16243,7 +16246,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G482" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -16269,7 +16272,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G483" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -16295,7 +16298,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G484" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -16321,7 +16324,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G485" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -16347,7 +16350,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G486" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -16373,7 +16376,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G487" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -16399,7 +16402,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G488" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -16425,7 +16428,7 @@
         <v>11.5</v>
       </c>
       <c r="G489" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -16451,7 +16454,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G490" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -16477,7 +16480,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G491" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -16503,7 +16506,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G492" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -16529,7 +16532,7 @@
         <v>11.0699996948242</v>
       </c>
       <c r="G493" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -16555,7 +16558,7 @@
         <v>11.2299995422363</v>
       </c>
       <c r="G494" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -16581,7 +16584,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G495" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -16607,7 +16610,7 @@
         <v>10.9300003051758</v>
       </c>
       <c r="G496" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -16633,7 +16636,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G497" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -16659,7 +16662,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G498" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -16685,7 +16688,7 @@
         <v>11.25</v>
       </c>
       <c r="G499" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -16711,7 +16714,7 @@
         <v>11.1300001144409</v>
       </c>
       <c r="G500" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -16737,7 +16740,7 @@
         <v>11</v>
       </c>
       <c r="G501" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -16763,7 +16766,7 @@
         <v>11.0699996948242</v>
       </c>
       <c r="G502" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -16789,7 +16792,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G503" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -16815,7 +16818,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G504" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -16841,7 +16844,7 @@
         <v>11</v>
       </c>
       <c r="G505" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -16867,7 +16870,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G506" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -16893,7 +16896,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G507" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -16919,7 +16922,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G508" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -16945,7 +16948,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G509" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -16971,7 +16974,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G510" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -16997,7 +17000,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G511" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -17023,7 +17026,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G512" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -17049,7 +17052,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G513" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -17075,7 +17078,7 @@
         <v>10.75</v>
       </c>
       <c r="G514" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -17101,7 +17104,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G515" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -17127,7 +17130,7 @@
         <v>10.75</v>
       </c>
       <c r="G516" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -17153,7 +17156,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G517" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -17179,7 +17182,7 @@
         <v>11</v>
       </c>
       <c r="G518" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -17205,7 +17208,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G519" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -17231,7 +17234,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G520" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -17257,7 +17260,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G521" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -17283,7 +17286,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G522" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -17309,7 +17312,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G523" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -17335,7 +17338,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G524" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -17361,7 +17364,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G525" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -17387,7 +17390,7 @@
         <v>11.25</v>
       </c>
       <c r="G526" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -17413,7 +17416,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G527" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -17439,7 +17442,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G528" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -17465,7 +17468,7 @@
         <v>11.25</v>
       </c>
       <c r="G529" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -17491,7 +17494,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G530" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -17517,7 +17520,7 @@
         <v>11.5</v>
       </c>
       <c r="G531" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -17543,7 +17546,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G532" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -17569,7 +17572,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G533" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -17595,7 +17598,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G534" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -17621,7 +17624,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G535" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -17647,7 +17650,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G536" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -17673,7 +17676,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G537" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -17699,7 +17702,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G538" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -17725,7 +17728,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G539" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -17751,7 +17754,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G540" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -17777,7 +17780,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G541" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -17803,7 +17806,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G542" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -17829,7 +17832,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G543" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -17855,7 +17858,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G544" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -17881,7 +17884,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G545" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -17907,7 +17910,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G546" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -17933,7 +17936,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G547" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -17959,7 +17962,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G548" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -17985,7 +17988,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G549" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -18011,7 +18014,7 @@
         <v>10.5</v>
       </c>
       <c r="G550" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -18037,7 +18040,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G551" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -18063,7 +18066,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G552" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -18089,7 +18092,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G553" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -18115,7 +18118,7 @@
         <v>10.25</v>
       </c>
       <c r="G554" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -18141,7 +18144,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G555" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -18167,7 +18170,7 @@
         <v>10.25</v>
       </c>
       <c r="G556" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -18193,7 +18196,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G557" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -18219,7 +18222,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G558" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -18245,7 +18248,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G559" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -18271,7 +18274,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G560" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -18297,7 +18300,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G561" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -18323,7 +18326,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G562" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -18349,7 +18352,7 @@
         <v>10.5</v>
       </c>
       <c r="G563" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -18375,7 +18378,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G564" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -18401,7 +18404,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G565" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -18427,7 +18430,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G566" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -18453,7 +18456,7 @@
         <v>10.25</v>
       </c>
       <c r="G567" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -18479,7 +18482,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G568" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -18505,7 +18508,7 @@
         <v>10.25</v>
       </c>
       <c r="G569" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -18531,7 +18534,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G570" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -18557,7 +18560,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G571" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -18583,7 +18586,7 @@
         <v>10</v>
       </c>
       <c r="G572" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -18609,7 +18612,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G573" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -18635,7 +18638,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G574" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -18661,7 +18664,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G575" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -18687,7 +18690,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G576" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -18713,7 +18716,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G577" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -18739,7 +18742,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G578" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -18765,7 +18768,7 @@
         <v>10</v>
       </c>
       <c r="G579" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -18791,7 +18794,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G580" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -18817,7 +18820,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G581" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -18843,7 +18846,7 @@
         <v>10.25</v>
       </c>
       <c r="G582" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -18869,7 +18872,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G583" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -18895,7 +18898,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G584" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -18921,7 +18924,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G585" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -18947,7 +18950,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G586" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -18973,7 +18976,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G587" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -18999,7 +19002,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G588" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -19025,7 +19028,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G589" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -19051,7 +19054,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G590" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -19077,7 +19080,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G591" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -19103,7 +19106,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G592" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -19129,7 +19132,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G593" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -19155,7 +19158,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G594" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -19181,7 +19184,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G595" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -19207,7 +19210,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G596" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -19233,7 +19236,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G597" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -19259,7 +19262,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G598" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -19285,7 +19288,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G599" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -19311,7 +19314,7 @@
         <v>10.25</v>
       </c>
       <c r="G600" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -19337,7 +19340,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G601" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -19363,7 +19366,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G602" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -19389,7 +19392,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G603" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -19415,7 +19418,7 @@
         <v>10.25</v>
       </c>
       <c r="G604" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -19441,7 +19444,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G605" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -19467,7 +19470,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G606" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -19493,7 +19496,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G607" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -19519,7 +19522,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G608" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19545,7 +19548,7 @@
         <v>10.25</v>
       </c>
       <c r="G609" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19571,7 +19574,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G610" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19597,7 +19600,7 @@
         <v>10.25</v>
       </c>
       <c r="G611" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19623,7 +19626,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G612" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19649,7 +19652,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G613" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19675,7 +19678,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G614" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19701,7 +19704,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G615" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19727,7 +19730,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G616" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19753,7 +19756,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G617" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19779,7 +19782,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G618" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19805,7 +19808,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G619" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19831,7 +19834,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G620" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19857,7 +19860,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G621" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19883,7 +19886,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G622" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19909,7 +19912,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G623" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19935,7 +19938,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G624" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19961,7 +19964,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G625" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19987,7 +19990,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G626" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -20013,7 +20016,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G627" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -20039,7 +20042,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G628" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -20065,7 +20068,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G629" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -20091,7 +20094,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G630" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -20117,7 +20120,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G631" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -20143,7 +20146,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G632" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -20169,7 +20172,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G633" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -20195,7 +20198,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G634" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -20221,7 +20224,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G635" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -20247,7 +20250,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G636" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -20273,7 +20276,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G637" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -20299,7 +20302,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G638" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -20325,7 +20328,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G639" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -20351,7 +20354,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G640" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -20377,7 +20380,7 @@
         <v>10</v>
       </c>
       <c r="G641" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -20403,7 +20406,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G642" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -20429,7 +20432,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G643" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -20455,7 +20458,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G644" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -20481,7 +20484,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G645" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -20507,7 +20510,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G646" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -20533,7 +20536,7 @@
         <v>10</v>
       </c>
       <c r="G647" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -20559,7 +20562,7 @@
         <v>10</v>
       </c>
       <c r="G648" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -20585,7 +20588,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G649" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -20611,7 +20614,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G650" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -20637,7 +20640,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G651" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -20663,7 +20666,7 @@
         <v>10</v>
       </c>
       <c r="G652" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -20689,7 +20692,7 @@
         <v>10</v>
       </c>
       <c r="G653" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -20715,7 +20718,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G654" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -20741,7 +20744,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G655" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -20767,7 +20770,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G656" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -20793,7 +20796,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G657" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -20819,7 +20822,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G658" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -20845,7 +20848,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G659" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -20871,7 +20874,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G660" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -20897,7 +20900,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G661" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -20923,7 +20926,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G662" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -20949,7 +20952,7 @@
         <v>10</v>
       </c>
       <c r="G663" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -20975,7 +20978,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G664" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -21001,7 +21004,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G665" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -21027,7 +21030,7 @@
         <v>10.25</v>
       </c>
       <c r="G666" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -21053,7 +21056,7 @@
         <v>10</v>
       </c>
       <c r="G667" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -21079,7 +21082,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G668" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -21105,7 +21108,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G669" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -21131,7 +21134,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G670" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -21157,7 +21160,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G671" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -21183,7 +21186,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G672" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -21209,7 +21212,7 @@
         <v>10</v>
       </c>
       <c r="G673" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -21235,7 +21238,7 @@
         <v>10</v>
       </c>
       <c r="G674" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -21261,7 +21264,7 @@
         <v>10</v>
       </c>
       <c r="G675" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -21287,7 +21290,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G676" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -21313,7 +21316,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G677" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -21339,7 +21342,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G678" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -21365,7 +21368,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G679" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -21391,7 +21394,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G680" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -21417,7 +21420,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G681" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -21443,7 +21446,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G682" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -21469,7 +21472,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G683" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -21495,7 +21498,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G684" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -21521,7 +21524,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G685" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -21547,7 +21550,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G686" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -21573,7 +21576,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G687" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -21599,7 +21602,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G688" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -21625,7 +21628,7 @@
         <v>10</v>
       </c>
       <c r="G689" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -21651,7 +21654,7 @@
         <v>10</v>
       </c>
       <c r="G690" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -21677,7 +21680,7 @@
         <v>10</v>
       </c>
       <c r="G691" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -21703,7 +21706,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G692" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -21729,7 +21732,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G693" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -21755,7 +21758,7 @@
         <v>10</v>
       </c>
       <c r="G694" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -21781,7 +21784,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G695" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -21807,7 +21810,7 @@
         <v>10</v>
       </c>
       <c r="G696" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -21833,7 +21836,7 @@
         <v>10</v>
       </c>
       <c r="G697" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -21859,7 +21862,7 @@
         <v>10.5</v>
       </c>
       <c r="G698" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -21885,7 +21888,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G699" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -21911,7 +21914,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G700" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -21937,7 +21940,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G701" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -21963,7 +21966,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G702" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -21989,7 +21992,7 @@
         <v>10.25</v>
       </c>
       <c r="G703" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -22015,7 +22018,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G704" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -22041,7 +22044,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G705" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -22067,7 +22070,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G706" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -22093,7 +22096,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G707" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -22119,7 +22122,7 @@
         <v>10</v>
       </c>
       <c r="G708" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -22145,7 +22148,7 @@
         <v>10</v>
       </c>
       <c r="G709" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -22171,7 +22174,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G710" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -22197,7 +22200,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G711" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -22223,7 +22226,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G712" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -22249,7 +22252,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G713" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -22275,7 +22278,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G714" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -22301,7 +22304,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G715" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -22327,7 +22330,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G716" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -22353,7 +22356,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G717" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -22379,7 +22382,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G718" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -22405,7 +22408,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G719" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -22431,7 +22434,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G720" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -22457,7 +22460,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G721" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -22483,7 +22486,7 @@
         <v>10</v>
       </c>
       <c r="G722" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -22509,7 +22512,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G723" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -22535,7 +22538,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G724" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -22561,7 +22564,7 @@
         <v>10</v>
       </c>
       <c r="G725" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -22587,7 +22590,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G726" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -22613,7 +22616,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G727" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -22639,7 +22642,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G728" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -22665,7 +22668,7 @@
         <v>10</v>
       </c>
       <c r="G729" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -22691,7 +22694,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G730" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -22717,7 +22720,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G731" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -22743,7 +22746,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G732" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -22769,7 +22772,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G733" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -22795,7 +22798,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G734" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -22821,7 +22824,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G735" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -22847,7 +22850,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G736" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -22873,7 +22876,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G737" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -22899,7 +22902,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G738" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -22925,7 +22928,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G739" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -22951,7 +22954,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G740" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -22977,7 +22980,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G741" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -23003,7 +23006,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G742" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -23029,7 +23032,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G743" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -23055,7 +23058,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G744" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -23081,7 +23084,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G745" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -23107,7 +23110,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G746" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -23133,7 +23136,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G747" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -23159,7 +23162,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G748" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -23185,7 +23188,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G749" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -23211,7 +23214,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G750" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -23237,7 +23240,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G751" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -23263,7 +23266,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G752" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -23289,7 +23292,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G753" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -23315,7 +23318,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G754" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -23341,7 +23344,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G755" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -23367,7 +23370,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G756" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -23393,7 +23396,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G757" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -23419,7 +23422,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G758" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -23445,7 +23448,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G759" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -23471,7 +23474,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G760" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -23497,7 +23500,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G761" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -23523,7 +23526,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G762" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -23549,7 +23552,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G763" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -23575,7 +23578,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G764" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -23601,7 +23604,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G765" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -23627,7 +23630,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G766" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -23653,7 +23656,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G767" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -23679,7 +23682,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G768" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -23705,7 +23708,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G769" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -23731,7 +23734,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G770" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -23757,7 +23760,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G771" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -23783,7 +23786,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G772" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -23809,7 +23812,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G773" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -23835,7 +23838,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G774" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -23861,7 +23864,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G775" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -23887,7 +23890,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G776" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -23913,7 +23916,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G777" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -23939,7 +23942,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G778" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -23965,7 +23968,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G779" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -23991,7 +23994,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G780" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -24017,7 +24020,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G781" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -24043,7 +24046,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G782" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -24069,7 +24072,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G783" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -24095,7 +24098,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G784" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -24121,7 +24124,7 @@
         <v>10</v>
       </c>
       <c r="G785" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -24147,7 +24150,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G786" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -24173,7 +24176,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G787" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -24199,7 +24202,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G788" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -24225,7 +24228,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G789" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -24251,7 +24254,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G790" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -24277,7 +24280,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G791" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -24303,7 +24306,7 @@
         <v>10</v>
       </c>
       <c r="G792" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -24329,7 +24332,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G793" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -24355,7 +24358,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G794" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -24381,7 +24384,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G795" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -24407,7 +24410,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G796" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -24433,7 +24436,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G797" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -24459,7 +24462,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G798" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -24485,7 +24488,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G799" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -24511,7 +24514,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G800" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -24537,7 +24540,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G801" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -24563,7 +24566,7 @@
         <v>10.25</v>
       </c>
       <c r="G802" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -24589,7 +24592,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G803" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -24615,7 +24618,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G804" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -24641,7 +24644,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G805" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -24667,7 +24670,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G806" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -24693,7 +24696,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G807" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -24719,7 +24722,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G808" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -24745,7 +24748,7 @@
         <v>10.5</v>
       </c>
       <c r="G809" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -24771,7 +24774,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G810" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -24797,7 +24800,7 @@
         <v>10</v>
       </c>
       <c r="G811" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -24823,7 +24826,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G812" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -24849,7 +24852,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G813" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -24875,7 +24878,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G814" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -24901,7 +24904,7 @@
         <v>10.5</v>
       </c>
       <c r="G815" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -24927,7 +24930,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G816" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -24953,7 +24956,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G817" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -24979,7 +24982,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G818" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -25005,7 +25008,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G819" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -25031,7 +25034,7 @@
         <v>11.25</v>
       </c>
       <c r="G820" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -25057,7 +25060,7 @@
         <v>11.5</v>
       </c>
       <c r="G821" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -25083,7 +25086,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G822" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -25109,7 +25112,7 @@
         <v>11.5</v>
       </c>
       <c r="G823" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -25135,7 +25138,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G824" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -25161,7 +25164,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G825" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -25187,7 +25190,7 @@
         <v>11.75</v>
       </c>
       <c r="G826" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -25213,7 +25216,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G827" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -25239,7 +25242,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G828" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -25265,7 +25268,7 @@
         <v>11.75</v>
       </c>
       <c r="G829" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -25291,7 +25294,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G830" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -25317,7 +25320,7 @@
         <v>11.75</v>
       </c>
       <c r="G831" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -25343,7 +25346,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G832" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -25369,7 +25372,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G833" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -25395,7 +25398,7 @@
         <v>11.75</v>
       </c>
       <c r="G834" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -25421,7 +25424,7 @@
         <v>11.75</v>
       </c>
       <c r="G835" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -25447,7 +25450,7 @@
         <v>11.75</v>
       </c>
       <c r="G836" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -25473,7 +25476,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G837" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -25499,7 +25502,7 @@
         <v>11.75</v>
       </c>
       <c r="G838" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -25525,7 +25528,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G839" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -25551,7 +25554,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G840" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -25577,7 +25580,7 @@
         <v>11.25</v>
       </c>
       <c r="G841" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -25603,7 +25606,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G842" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -25629,7 +25632,7 @@
         <v>11.5</v>
       </c>
       <c r="G843" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -25655,7 +25658,7 @@
         <v>11.5</v>
       </c>
       <c r="G844" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -25681,7 +25684,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G845" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -25707,7 +25710,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G846" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -25733,7 +25736,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G847" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -25759,7 +25762,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G848" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -25785,7 +25788,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G849" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -25811,7 +25814,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G850" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -25837,7 +25840,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G851" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -25863,7 +25866,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G852" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -25889,7 +25892,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G853" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -25915,7 +25918,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G854" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -25941,7 +25944,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G855" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -25967,7 +25970,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G856" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -25993,7 +25996,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G857" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -26019,7 +26022,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G858" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -26045,7 +26048,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G859" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -26071,7 +26074,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G860" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -26097,7 +26100,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G861" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -26123,7 +26126,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G862" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -26149,7 +26152,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G863" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -26175,7 +26178,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G864" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -26201,7 +26204,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G865" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -26227,7 +26230,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G866" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -26253,7 +26256,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G867" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -26279,7 +26282,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G868" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -26305,7 +26308,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G869" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -26331,7 +26334,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G870" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -26565,7 +26568,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G879" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -26669,7 +26672,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G883" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -26721,7 +26724,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G885" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -26851,7 +26854,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G890" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -26955,7 +26958,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G894" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -27007,7 +27010,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G896" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -27033,7 +27036,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G897" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -27293,7 +27296,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G907" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -27371,7 +27374,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G910" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -27397,7 +27400,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G911" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -27423,7 +27426,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G912" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -27527,7 +27530,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G916" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -27579,7 +27582,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G918" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -29425,7 +29428,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G989" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -29503,7 +29506,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G992" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -31375,7 +31378,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1064" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -32233,7 +32236,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1097" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -32285,7 +32288,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G1099" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -68745,7 +68748,7 @@
     </row>
     <row r="2502">
       <c r="A2502" s="1" t="n">
-        <v>45961.6909953704</v>
+        <v>45961.3333333333</v>
       </c>
       <c r="B2502" t="n">
         <v>3897</v>
@@ -68766,6 +68769,32 @@
         <v>1122</v>
       </c>
       <c r="H2502" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2503">
+      <c r="A2503" s="1" t="n">
+        <v>45964.6910763889</v>
+      </c>
+      <c r="B2503" t="n">
+        <v>5900</v>
+      </c>
+      <c r="C2503" t="n">
+        <v>36.4500007629395</v>
+      </c>
+      <c r="D2503" t="n">
+        <v>35.9000015258789</v>
+      </c>
+      <c r="E2503" t="n">
+        <v>36.0999984741211</v>
+      </c>
+      <c r="F2503" t="n">
+        <v>36.0499992370605</v>
+      </c>
+      <c r="G2503" t="s">
+        <v>1123</v>
+      </c>
+      <c r="H2503" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LUVE.MI.xlsx
+++ b/data/LUVE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="1124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1125" uniqueCount="1125">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30043411254883</t>
+    <t xml:space="preserve">8.3004322052002</t>
   </si>
   <si>
     <t xml:space="preserve">LUVE.MI</t>
@@ -47,85 +47,85 @@
     <t xml:space="preserve">8.31703472137451</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28383159637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09292221069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19667816162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07632064819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15102672576904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17177867889404</t>
+    <t xml:space="preserve">8.28383255004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09292411804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19667720794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07631969451904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15102577209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17177677154541</t>
   </si>
   <si>
     <t xml:space="preserve">8.03897094726562</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08462333679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06802177429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9684157371521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01821994781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9974684715271</t>
+    <t xml:space="preserve">8.08462238311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06802082061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96841669082642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01821899414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99746656417847</t>
   </si>
   <si>
     <t xml:space="preserve">7.91861248016357</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91446304321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91031217575073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88541173934937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87710952758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.852210521698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64884901046753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71940326690674</t>
+    <t xml:space="preserve">7.91446208953857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91031312942505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88541126251221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87711000442505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85220909118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64884948730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7194037437439</t>
   </si>
   <si>
     <t xml:space="preserve">7.7028021812439</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69035196304321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61979866027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55754423141479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55339574813843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63639879226685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76920604705811</t>
+    <t xml:space="preserve">7.69035148620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.619797706604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55754518508911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55339527130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63639831542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76920461654663</t>
   </si>
   <si>
     <t xml:space="preserve">7.80240774154663</t>
@@ -140,19 +140,19 @@
     <t xml:space="preserve">8.05142021179199</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18422698974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13442420959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00161933898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96011447906494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21742916107178</t>
+    <t xml:space="preserve">8.18422794342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13442516326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00161743164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96011638641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21742820739746</t>
   </si>
   <si>
     <t xml:space="preserve">8.35853672027588</t>
@@ -161,16 +161,16 @@
     <t xml:space="preserve">8.32533550262451</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2921314239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20082759857178</t>
+    <t xml:space="preserve">8.29213333129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20082855224609</t>
   </si>
   <si>
     <t xml:space="preserve">8.15932655334473</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3033618927002</t>
+    <t xml:space="preserve">8.30336380004883</t>
   </si>
   <si>
     <t xml:space="preserve">8.36267375946045</t>
@@ -194,28 +194,28 @@
     <t xml:space="preserve">8.11696243286133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21863460540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21016311645508</t>
+    <t xml:space="preserve">8.21863555908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21016216278076</t>
   </si>
   <si>
     <t xml:space="preserve">8.21439838409424</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20169067382812</t>
+    <t xml:space="preserve">8.20168972015381</t>
   </si>
   <si>
     <t xml:space="preserve">8.26099967956543</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09154415130615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10848999023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04918003082275</t>
+    <t xml:space="preserve">8.09154319763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10848903656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04917907714844</t>
   </si>
   <si>
     <t xml:space="preserve">7.96445083618164</t>
@@ -224,124 +224,124 @@
     <t xml:space="preserve">7.92208766937256</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87972354888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83735799789429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12543392181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93479633331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75262928009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71026754379272</t>
+    <t xml:space="preserve">7.87972211837769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83735847473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12543487548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93479442596436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75263118743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71026706695557</t>
   </si>
   <si>
     <t xml:space="preserve">7.93903303146362</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81194067001343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79499387741089</t>
+    <t xml:space="preserve">7.81194019317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79499578475952</t>
   </si>
   <si>
     <t xml:space="preserve">7.62553834915161</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66790246963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84583234786987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19321632385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47282218933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5151834487915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52365875244141</t>
+    <t xml:space="preserve">7.66790199279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84583044052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19321727752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47281932830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51518535614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52365779876709</t>
   </si>
   <si>
     <t xml:space="preserve">8.59991264343262</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78631496429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71853256225586</t>
+    <t xml:space="preserve">8.78631401062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71853160858154</t>
   </si>
   <si>
     <t xml:space="preserve">8.50671100616455</t>
   </si>
   <si>
-    <t xml:space="preserve">8.540602684021</t>
+    <t xml:space="preserve">8.54060363769531</t>
   </si>
   <si>
     <t xml:space="preserve">8.46858406066895</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46434688568115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5575475692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57449531555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81173419952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7270040512085</t>
+    <t xml:space="preserve">8.46434783935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55755043029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57449436187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81173324584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72700500488281</t>
   </si>
   <si>
     <t xml:space="preserve">8.64227676391602</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89646053314209</t>
+    <t xml:space="preserve">8.89646148681641</t>
   </si>
   <si>
     <t xml:space="preserve">9.02355289459229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09980964660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06591796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1082820892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27773761749268</t>
+    <t xml:space="preserve">9.09980773925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06591701507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10828304290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27773857116699</t>
   </si>
   <si>
     <t xml:space="preserve">9.1930103302002</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18453693389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07438945770264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09133529663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30315589904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32010269165039</t>
+    <t xml:space="preserve">9.18453598022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07439136505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09133625030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30315494537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32010364532471</t>
   </si>
   <si>
     <t xml:space="preserve">9.1252269744873</t>
@@ -353,22 +353,22 @@
     <t xml:space="preserve">9.40483093261719</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48955726623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38788604736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5319242477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48108577728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44719505310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54039478302002</t>
+    <t xml:space="preserve">9.48955821990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38788509368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53192329406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4810848236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44719409942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54039573669434</t>
   </si>
   <si>
     <t xml:space="preserve">9.57428741455078</t>
@@ -377,19 +377,19 @@
     <t xml:space="preserve">9.47261428833008</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41330242156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42177581787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51497554779053</t>
+    <t xml:space="preserve">9.41330337524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42177486419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51497745513916</t>
   </si>
   <si>
     <t xml:space="preserve">9.56581401824951</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74374389648438</t>
+    <t xml:space="preserve">9.74374294281006</t>
   </si>
   <si>
     <t xml:space="preserve">10.065710067749</t>
@@ -401,55 +401,55 @@
     <t xml:space="preserve">10.1334915161133</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99792861938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95556354522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98098182678223</t>
+    <t xml:space="preserve">9.99792766571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95556259155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98098087310791</t>
   </si>
   <si>
     <t xml:space="preserve">9.88778209686279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91319942474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0148735046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1589117050171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0402927398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70137882232666</t>
+    <t xml:space="preserve">9.91319847106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0148725509644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1589107513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0402936935425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70137977600098</t>
   </si>
   <si>
     <t xml:space="preserve">9.73527050018311</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70985317230225</t>
+    <t xml:space="preserve">9.70985221862793</t>
   </si>
   <si>
     <t xml:space="preserve">10.0826559066772</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86236381530762</t>
+    <t xml:space="preserve">9.8623628616333</t>
   </si>
   <si>
     <t xml:space="preserve">10.1250200271606</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2944765090942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4808778762817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5317153930664</t>
+    <t xml:space="preserve">10.2944755554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4808769226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5317163467407</t>
   </si>
   <si>
     <t xml:space="preserve">10.5147695541382</t>
@@ -458,7 +458,7 @@
     <t xml:space="preserve">10.802845954895</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9129915237427</t>
+    <t xml:space="preserve">10.9129934310913</t>
   </si>
   <si>
     <t xml:space="preserve">10.8621559143066</t>
@@ -467,37 +467,37 @@
     <t xml:space="preserve">11.014666557312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0570306777954</t>
+    <t xml:space="preserve">11.0570297241211</t>
   </si>
   <si>
     <t xml:space="preserve">11.2773237228394</t>
   </si>
   <si>
-    <t xml:space="preserve">11.438307762146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6586017608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5823459625244</t>
+    <t xml:space="preserve">11.4383058547974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6586008071899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5823450088501</t>
   </si>
   <si>
     <t xml:space="preserve">11.4806718826294</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5908174514771</t>
+    <t xml:space="preserve">11.5908184051514</t>
   </si>
   <si>
     <t xml:space="preserve">11.7009649276733</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7772207260132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8111114501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8365297317505</t>
+    <t xml:space="preserve">11.7772197723389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.811110496521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8365306854248</t>
   </si>
   <si>
     <t xml:space="preserve">11.6670732498169</t>
@@ -509,7 +509,7 @@
     <t xml:space="preserve">11.5230360031128</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6077642440796</t>
+    <t xml:space="preserve">11.6077632904053</t>
   </si>
   <si>
     <t xml:space="preserve">11.6263799667358</t>
@@ -518,25 +518,25 @@
     <t xml:space="preserve">11.7297267913818</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6952772140503</t>
+    <t xml:space="preserve">11.6952781677246</t>
   </si>
   <si>
     <t xml:space="preserve">11.6780548095703</t>
   </si>
   <si>
-    <t xml:space="preserve">11.798623085022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8847465515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9105815887451</t>
+    <t xml:space="preserve">11.7986240386963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8847455978394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9105825424194</t>
   </si>
   <si>
     <t xml:space="preserve">12.0655994415283</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3153524398804</t>
+    <t xml:space="preserve">12.3153505325317</t>
   </si>
   <si>
     <t xml:space="preserve">12.3584127426147</t>
@@ -545,112 +545,112 @@
     <t xml:space="preserve">12.0569887161255</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1431093215942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9967012405396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8416833877563</t>
+    <t xml:space="preserve">12.1431112289429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9967031478882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8416843414307</t>
   </si>
   <si>
     <t xml:space="preserve">11.7555637359619</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7125034332275</t>
+    <t xml:space="preserve">11.7125024795532</t>
   </si>
   <si>
     <t xml:space="preserve">11.8502960205078</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9191951751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.962254524231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0397634506226</t>
+    <t xml:space="preserve">11.9191942214966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9622554779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0397624969482</t>
   </si>
   <si>
     <t xml:space="preserve">12.048376083374</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7900104522705</t>
+    <t xml:space="preserve">11.7900114059448</t>
   </si>
   <si>
     <t xml:space="preserve">12.0311527252197</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9450302124023</t>
+    <t xml:space="preserve">11.945029258728</t>
   </si>
   <si>
     <t xml:space="preserve">11.8158473968506</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8933582305908</t>
+    <t xml:space="preserve">11.8933572769165</t>
   </si>
   <si>
     <t xml:space="preserve">11.8761339187622</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8244590759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8675203323364</t>
+    <t xml:space="preserve">11.8244581222534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8675212860107</t>
   </si>
   <si>
     <t xml:space="preserve">11.901969909668</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9278059005737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7211151123047</t>
+    <t xml:space="preserve">11.927806854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.721116065979</t>
   </si>
   <si>
     <t xml:space="preserve">11.6694421768188</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6349935531616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6091556549072</t>
+    <t xml:space="preserve">11.6349945068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6091566085815</t>
   </si>
   <si>
     <t xml:space="preserve">11.5747079849243</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5316476821899</t>
+    <t xml:space="preserve">11.5316486358643</t>
   </si>
   <si>
     <t xml:space="preserve">11.3680181503296</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3594036102295</t>
+    <t xml:space="preserve">11.3594045639038</t>
   </si>
   <si>
     <t xml:space="preserve">11.2818965911865</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2302227020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1957750320435</t>
+    <t xml:space="preserve">11.2302217483521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1957740783691</t>
   </si>
   <si>
     <t xml:space="preserve">11.1871633529663</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1096534729004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0579805374146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1785497665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1268768310547</t>
+    <t xml:space="preserve">11.1096515655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0579814910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1785507202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.126877784729</t>
   </si>
   <si>
     <t xml:space="preserve">10.9374103546143</t>
@@ -659,28 +659,28 @@
     <t xml:space="preserve">11.066593170166</t>
   </si>
   <si>
-    <t xml:space="preserve">11.023530960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0838165283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1354894638062</t>
+    <t xml:space="preserve">11.0235319137573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.083815574646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1354904174805</t>
   </si>
   <si>
     <t xml:space="preserve">11.2043857574463</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3163442611694</t>
+    <t xml:space="preserve">11.3163433074951</t>
   </si>
   <si>
     <t xml:space="preserve">11.454137802124</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5402603149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.411078453064</t>
+    <t xml:space="preserve">11.5402612686157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4110774993896</t>
   </si>
   <si>
     <t xml:space="preserve">11.2905073165894</t>
@@ -689,7 +689,7 @@
     <t xml:space="preserve">11.1613264083862</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2646722793579</t>
+    <t xml:space="preserve">11.2646703720093</t>
   </si>
   <si>
     <t xml:space="preserve">11.1527137756348</t>
@@ -701,40 +701,40 @@
     <t xml:space="preserve">11.4196901321411</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2216100692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2388353347778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3421812057495</t>
+    <t xml:space="preserve">11.2216110229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2388343811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3421802520752</t>
   </si>
   <si>
     <t xml:space="preserve">10.9546346664429</t>
   </si>
   <si>
-    <t xml:space="preserve">10.96324634552</t>
+    <t xml:space="preserve">10.9632453918457</t>
   </si>
   <si>
     <t xml:space="preserve">11.0063076019287</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0924282073975</t>
+    <t xml:space="preserve">11.0924291610718</t>
   </si>
   <si>
     <t xml:space="preserve">9.74032402038574</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01690578460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21498394012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37861442565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49057197570801</t>
+    <t xml:space="preserve">9.01690483093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2149829864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3786153793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49057102203369</t>
   </si>
   <si>
     <t xml:space="preserve">9.5077953338623</t>
@@ -749,7 +749,7 @@
     <t xml:space="preserve">9.6886510848999</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56808185577393</t>
+    <t xml:space="preserve">9.56808090209961</t>
   </si>
   <si>
     <t xml:space="preserve">9.39583778381348</t>
@@ -761,34 +761,34 @@
     <t xml:space="preserve">9.2580451965332</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30110549926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41306400299072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28388023376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24081897735596</t>
+    <t xml:space="preserve">9.30110454559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41306304931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28388118743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24081993103027</t>
   </si>
   <si>
     <t xml:space="preserve">9.12886142730713</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02551555633545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20637130737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26665592193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69726467132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65420341491699</t>
+    <t xml:space="preserve">9.02551651000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20637226104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26665687561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69726371765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65420246124268</t>
   </si>
   <si>
     <t xml:space="preserve">9.66281509399414</t>
@@ -797,13 +797,13 @@
     <t xml:space="preserve">9.64558982849121</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67142581939697</t>
+    <t xml:space="preserve">9.67142677307129</t>
   </si>
   <si>
     <t xml:space="preserve">9.75754833221436</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71448707580566</t>
+    <t xml:space="preserve">9.71448612213135</t>
   </si>
   <si>
     <t xml:space="preserve">9.09441375732422</t>
@@ -821,7 +821,7 @@
     <t xml:space="preserve">9.83505630493164</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73171043395996</t>
+    <t xml:space="preserve">9.73171138763428</t>
   </si>
   <si>
     <t xml:space="preserve">9.90395355224609</t>
@@ -833,16 +833,16 @@
     <t xml:space="preserve">9.53363227844238</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49918270111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57669353485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58530521392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47334671020508</t>
+    <t xml:space="preserve">9.49918365478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57669258117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58530616760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47334861755371</t>
   </si>
   <si>
     <t xml:space="preserve">9.43028736114502</t>
@@ -857,7 +857,7 @@
     <t xml:space="preserve">9.23220825195312</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55947017669678</t>
+    <t xml:space="preserve">9.55946922302246</t>
   </si>
   <si>
     <t xml:space="preserve">9.51640796661377</t>
@@ -866,7 +866,7 @@
     <t xml:space="preserve">9.86089324951172</t>
   </si>
   <si>
-    <t xml:space="preserve">8.956618309021</t>
+    <t xml:space="preserve">8.95662021636963</t>
   </si>
   <si>
     <t xml:space="preserve">8.91355895996094</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">8.99967956542969</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82743740081787</t>
+    <t xml:space="preserve">8.82743644714355</t>
   </si>
   <si>
     <t xml:space="preserve">8.69825744628906</t>
@@ -890,34 +890,34 @@
     <t xml:space="preserve">8.87049865722656</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7843770980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74131488800049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61213397979736</t>
+    <t xml:space="preserve">8.78437614440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7413158416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61213302612305</t>
   </si>
   <si>
     <t xml:space="preserve">8.59490966796875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65519428253174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45711421966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06314373016357</t>
+    <t xml:space="preserve">8.65519523620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45711612701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06314468383789</t>
   </si>
   <si>
     <t xml:space="preserve">9.10714054107666</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01914882659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97515296936035</t>
+    <t xml:space="preserve">9.0191478729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97515201568604</t>
   </si>
   <si>
     <t xml:space="preserve">8.93115711212158</t>
@@ -926,22 +926,22 @@
     <t xml:space="preserve">8.88716220855713</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84316444396973</t>
+    <t xml:space="preserve">8.84316539764404</t>
   </si>
   <si>
     <t xml:space="preserve">8.76397323608398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48239994049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71117782592773</t>
+    <t xml:space="preserve">8.48240089416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71117687225342</t>
   </si>
   <si>
     <t xml:space="preserve">8.62318706512451</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58798980712891</t>
+    <t xml:space="preserve">8.58798885345459</t>
   </si>
   <si>
     <t xml:space="preserve">8.6583833694458</t>
@@ -956,31 +956,31 @@
     <t xml:space="preserve">8.69357872009277</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74637508392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53519344329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44720363616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27121925354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32401466369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28881645202637</t>
+    <t xml:space="preserve">8.74637413024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53519439697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44720268249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27122020721436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32401371002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28881740570068</t>
   </si>
   <si>
     <t xml:space="preserve">8.78157043457031</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64078330993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79916954040527</t>
+    <t xml:space="preserve">8.64078426361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79916858673096</t>
   </si>
   <si>
     <t xml:space="preserve">8.67598152160645</t>
@@ -989,7 +989,7 @@
     <t xml:space="preserve">9.23912811279297</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37111473083496</t>
+    <t xml:space="preserve">9.37111568450928</t>
   </si>
   <si>
     <t xml:space="preserve">9.32711982727051</t>
@@ -998,13 +998,13 @@
     <t xml:space="preserve">9.1951322555542</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15113544464111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46480083465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41200542449951</t>
+    <t xml:space="preserve">9.15113639831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46479988098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41200637817383</t>
   </si>
   <si>
     <t xml:space="preserve">8.49999809265137</t>
@@ -1013,22 +1013,22 @@
     <t xml:space="preserve">8.34161281585693</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23602294921875</t>
+    <t xml:space="preserve">8.23602199554443</t>
   </si>
   <si>
     <t xml:space="preserve">8.30641555786133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13043117523193</t>
+    <t xml:space="preserve">8.13043212890625</t>
   </si>
   <si>
     <t xml:space="preserve">8.1832275390625</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16562843322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21842384338379</t>
+    <t xml:space="preserve">8.16562938690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21842479705811</t>
   </si>
   <si>
     <t xml:space="preserve">8.25362110137939</t>
@@ -1040,13 +1040,13 @@
     <t xml:space="preserve">8.51759624481201</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28312397003174</t>
+    <t xml:space="preserve">9.28312301635742</t>
   </si>
   <si>
     <t xml:space="preserve">9.41511249542236</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63508987426758</t>
+    <t xml:space="preserve">9.63509082794189</t>
   </si>
   <si>
     <t xml:space="preserve">9.59109401702881</t>
@@ -1055,25 +1055,25 @@
     <t xml:space="preserve">9.8990650177002</t>
   </si>
   <si>
-    <t xml:space="preserve">10.119044303894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1630411148071</t>
+    <t xml:space="preserve">10.1190433502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1630420684814</t>
   </si>
   <si>
     <t xml:space="preserve">10.2070369720459</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3390245437622</t>
+    <t xml:space="preserve">10.3390235900879</t>
   </si>
   <si>
     <t xml:space="preserve">10.2950277328491</t>
   </si>
   <si>
-    <t xml:space="preserve">10.383020401001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2510318756104</t>
+    <t xml:space="preserve">10.3830194473267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2510328292847</t>
   </si>
   <si>
     <t xml:space="preserve">10.4270162582397</t>
@@ -1082,25 +1082,25 @@
     <t xml:space="preserve">10.0750484466553</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5150079727173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6498165130615</t>
+    <t xml:space="preserve">10.5150089263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6498155593872</t>
   </si>
   <si>
     <t xml:space="preserve">10.4700708389282</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6947507858276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6048803329468</t>
+    <t xml:space="preserve">10.694751739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6048793792725</t>
   </si>
   <si>
     <t xml:space="preserve">10.380199432373</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2453918457031</t>
+    <t xml:space="preserve">10.2453908920288</t>
   </si>
   <si>
     <t xml:space="preserve">10.0656480789185</t>
@@ -1109,7 +1109,7 @@
     <t xml:space="preserve">10.4251356124878</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3352642059326</t>
+    <t xml:space="preserve">10.3352632522583</t>
   </si>
   <si>
     <t xml:space="preserve">10.2903280258179</t>
@@ -1121,7 +1121,7 @@
     <t xml:space="preserve">9.97577667236328</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1105833053589</t>
+    <t xml:space="preserve">10.1105842590332</t>
   </si>
   <si>
     <t xml:space="preserve">9.93084049224854</t>
@@ -1130,7 +1130,7 @@
     <t xml:space="preserve">9.88590431213379</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1555194854736</t>
+    <t xml:space="preserve">10.1555204391479</t>
   </si>
   <si>
     <t xml:space="preserve">10.020712852478</t>
@@ -1142,13 +1142,13 @@
     <t xml:space="preserve">9.70616149902344</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3466739654541</t>
+    <t xml:space="preserve">9.34667301177979</t>
   </si>
   <si>
     <t xml:space="preserve">9.30173778533936</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39160823822021</t>
+    <t xml:space="preserve">9.39160919189453</t>
   </si>
   <si>
     <t xml:space="preserve">9.48148250579834</t>
@@ -1163,13 +1163,13 @@
     <t xml:space="preserve">9.43654537200928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12199306488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0321216583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16693019866943</t>
+    <t xml:space="preserve">9.12199401855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03212261199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1669282913208</t>
   </si>
   <si>
     <t xml:space="preserve">9.07705783843994</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">9.66122531890869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79603290557861</t>
+    <t xml:space="preserve">9.79603385925293</t>
   </si>
   <si>
     <t xml:space="preserve">10.9643669128418</t>
@@ -1199,10 +1199,10 @@
     <t xml:space="preserve">11.5035982131958</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2339820861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1441116333008</t>
+    <t xml:space="preserve">11.233983039856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1441106796265</t>
   </si>
   <si>
     <t xml:space="preserve">10.9194307327271</t>
@@ -1217,13 +1217,13 @@
     <t xml:space="preserve">11.2789192199707</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4137258529663</t>
+    <t xml:space="preserve">11.413724899292</t>
   </si>
   <si>
     <t xml:space="preserve">11.5485343933105</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6833419799805</t>
+    <t xml:space="preserve">11.6833410263062</t>
   </si>
   <si>
     <t xml:space="preserve">11.77321434021</t>
@@ -1232,7 +1232,7 @@
     <t xml:space="preserve">11.9080219268799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.132700920105</t>
+    <t xml:space="preserve">12.1327018737793</t>
   </si>
   <si>
     <t xml:space="preserve">11.9978942871094</t>
@@ -1247,22 +1247,22 @@
     <t xml:space="preserve">12.312445640564</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5820617675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9415473937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8067407608032</t>
+    <t xml:space="preserve">12.5820608139038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9415483474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8067398071289</t>
   </si>
   <si>
     <t xml:space="preserve">12.7618036270142</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0763549804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4472541809082</t>
+    <t xml:space="preserve">13.0763559341431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4472532272339</t>
   </si>
   <si>
     <t xml:space="preserve">12.5371246337891</t>
@@ -1274,16 +1274,16 @@
     <t xml:space="preserve">12.4023170471191</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6269979476929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6719312667847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8966131210327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7282781600952</t>
+    <t xml:space="preserve">12.6269969940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.671932220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8966121673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7282772064209</t>
   </si>
   <si>
     <t xml:space="preserve">10.7846240997314</t>
@@ -1292,13 +1292,13 @@
     <t xml:space="preserve">10.559944152832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89731407165527</t>
+    <t xml:space="preserve">8.89731311798096</t>
   </si>
   <si>
     <t xml:space="preserve">7.98062086105347</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81885051727295</t>
+    <t xml:space="preserve">7.81885147094727</t>
   </si>
   <si>
     <t xml:space="preserve">7.53126192092896</t>
@@ -1352,7 +1352,7 @@
     <t xml:space="preserve">9.75444412231445</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3986043930054</t>
+    <t xml:space="preserve">10.3986053466797</t>
   </si>
   <si>
     <t xml:space="preserve">10.3065814971924</t>
@@ -1361,25 +1361,25 @@
     <t xml:space="preserve">10.720685005188</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5826501846313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8587207794189</t>
+    <t xml:space="preserve">10.582649230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8587198257446</t>
   </si>
   <si>
     <t xml:space="preserve">10.6746740341187</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9967546463013</t>
+    <t xml:space="preserve">10.996753692627</t>
   </si>
   <si>
     <t xml:space="preserve">10.628662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7666969299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4906282424927</t>
+    <t xml:space="preserve">10.766697883606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4906272888184</t>
   </si>
   <si>
     <t xml:space="preserve">11.1347904205322</t>
@@ -1388,7 +1388,7 @@
     <t xml:space="preserve">11.3188352584839</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5028800964355</t>
+    <t xml:space="preserve">11.5028810501099</t>
   </si>
   <si>
     <t xml:space="preserve">11.1807994842529</t>
@@ -1397,22 +1397,22 @@
     <t xml:space="preserve">11.0427665710449</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2728233337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9507417678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0887775421143</t>
+    <t xml:space="preserve">11.2728223800659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9507427215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0887784957886</t>
   </si>
   <si>
     <t xml:space="preserve">10.8127098083496</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9047317504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4108591079712</t>
+    <t xml:space="preserve">10.904730796814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4108581542969</t>
   </si>
   <si>
     <t xml:space="preserve">11.4568710327148</t>
@@ -1421,25 +1421,25 @@
     <t xml:space="preserve">11.2268114089966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3648471832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5488920211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5949048995972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6869277954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9629974365234</t>
+    <t xml:space="preserve">11.3648481369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5488929748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5949039459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6869268417358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9629964828491</t>
   </si>
   <si>
     <t xml:space="preserve">11.7789516448975</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0090093612671</t>
+    <t xml:space="preserve">12.0090084075928</t>
   </si>
   <si>
     <t xml:space="preserve">12.1010313034058</t>
@@ -1457,7 +1457,7 @@
     <t xml:space="preserve">11.8709726333618</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9169845581055</t>
+    <t xml:space="preserve">11.9169855117798</t>
   </si>
   <si>
     <t xml:space="preserve">11.6409158706665</t>
@@ -1475,55 +1475,55 @@
     <t xml:space="preserve">13.0672731399536</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8832273483276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9292402267456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2053089141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2513189315796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1132850646973</t>
+    <t xml:space="preserve">12.8832263946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9292392730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2053079605103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2513198852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1132841110229</t>
   </si>
   <si>
     <t xml:space="preserve">13.1592960357666</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3893527984619</t>
+    <t xml:space="preserve">13.3893537521362</t>
   </si>
   <si>
     <t xml:space="preserve">13.2973308563232</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9752502441406</t>
+    <t xml:space="preserve">12.9752511978149</t>
   </si>
   <si>
     <t xml:space="preserve">13.7114334106445</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4353656768799</t>
+    <t xml:space="preserve">13.4353647232056</t>
   </si>
   <si>
     <t xml:space="preserve">12.5151348114014</t>
   </si>
   <si>
-    <t xml:space="preserve">12.377100944519</t>
+    <t xml:space="preserve">12.3770999908447</t>
   </si>
   <si>
     <t xml:space="preserve">12.837215423584</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7451934814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.653169631958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3433427810669</t>
+    <t xml:space="preserve">12.745192527771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6531705856323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3433437347412</t>
   </si>
   <si>
     <t xml:space="preserve">13.6194124221802</t>
@@ -1532,7 +1532,7 @@
     <t xml:space="preserve">13.8494691848755</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9414920806885</t>
+    <t xml:space="preserve">13.9414930343628</t>
   </si>
   <si>
     <t xml:space="preserve">14.1715497970581</t>
@@ -1541,55 +1541,55 @@
     <t xml:space="preserve">14.3555955886841</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1255378723145</t>
+    <t xml:space="preserve">14.1255388259888</t>
   </si>
   <si>
     <t xml:space="preserve">14.4936304092407</t>
   </si>
   <si>
-    <t xml:space="preserve">14.723687171936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6776762008667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8157110214233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.861722946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0457696914673</t>
+    <t xml:space="preserve">14.7236881256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6776752471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8157119750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8617238998413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0457677841187</t>
   </si>
   <si>
     <t xml:space="preserve">14.5396423339844</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6316652297974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4476175308228</t>
+    <t xml:space="preserve">14.631664276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4476194381714</t>
   </si>
   <si>
     <t xml:space="preserve">14.2635736465454</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9875049591064</t>
+    <t xml:space="preserve">13.9875040054321</t>
   </si>
   <si>
     <t xml:space="preserve">14.3095846176147</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6654243469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8034582138062</t>
+    <t xml:space="preserve">13.6654253005981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8034572601318</t>
   </si>
   <si>
     <t xml:space="preserve">13.5733995437622</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7574453353882</t>
+    <t xml:space="preserve">13.7574462890625</t>
   </si>
   <si>
     <t xml:space="preserve">14.95374584198</t>
@@ -1601,19 +1601,19 @@
     <t xml:space="preserve">14.4269771575928</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3801374435425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.473819732666</t>
+    <t xml:space="preserve">14.3801383972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4738187789917</t>
   </si>
   <si>
     <t xml:space="preserve">14.7080240249634</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8485460281372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0359086990356</t>
+    <t xml:space="preserve">14.8485450744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.03590965271</t>
   </si>
   <si>
     <t xml:space="preserve">15.0827503204346</t>
@@ -1622,13 +1622,13 @@
     <t xml:space="preserve">14.8953857421875</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9422283172607</t>
+    <t xml:space="preserve">14.9422273635864</t>
   </si>
   <si>
     <t xml:space="preserve">15.1764316558838</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1295900344849</t>
+    <t xml:space="preserve">15.1295909881592</t>
   </si>
   <si>
     <t xml:space="preserve">14.989068031311</t>
@@ -1637,7 +1637,7 @@
     <t xml:space="preserve">14.6611814498901</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3169546127319</t>
+    <t xml:space="preserve">15.3169536590576</t>
   </si>
   <si>
     <t xml:space="preserve">14.7548637390137</t>
@@ -1646,22 +1646,22 @@
     <t xml:space="preserve">14.8017053604126</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2232713699341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5043163299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0664081573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6916799545288</t>
+    <t xml:space="preserve">15.2232723236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5043153762817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0664100646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6916818618774</t>
   </si>
   <si>
     <t xml:space="preserve">15.7385206222534</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9727230072021</t>
+    <t xml:space="preserve">15.9727249145508</t>
   </si>
   <si>
     <t xml:space="preserve">15.9258861541748</t>
@@ -1676,16 +1676,16 @@
     <t xml:space="preserve">15.8322019577026</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5348167419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8627033233643</t>
+    <t xml:space="preserve">16.5348148345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8627014160156</t>
   </si>
   <si>
     <t xml:space="preserve">17.1437454223633</t>
   </si>
   <si>
-    <t xml:space="preserve">16.581657409668</t>
+    <t xml:space="preserve">16.5816593170166</t>
   </si>
   <si>
     <t xml:space="preserve">16.2069301605225</t>
@@ -1697,7 +1697,7 @@
     <t xml:space="preserve">17.7995185852051</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4716300964355</t>
+    <t xml:space="preserve">17.4716320037842</t>
   </si>
   <si>
     <t xml:space="preserve">16.8158626556396</t>
@@ -1712,7 +1712,7 @@
     <t xml:space="preserve">17.5184764862061</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6121559143066</t>
+    <t xml:space="preserve">17.612154006958</t>
   </si>
   <si>
     <t xml:space="preserve">18.0337238311768</t>
@@ -1730,13 +1730,13 @@
     <t xml:space="preserve">19.7668342590332</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5794677734375</t>
+    <t xml:space="preserve">19.5794696807861</t>
   </si>
   <si>
     <t xml:space="preserve">19.2047443389893</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1110610961914</t>
+    <t xml:space="preserve">19.1110591888428</t>
   </si>
   <si>
     <t xml:space="preserve">19.673152923584</t>
@@ -1757,10 +1757,10 @@
     <t xml:space="preserve">20.9846954345703</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2657413482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0783748626709</t>
+    <t xml:space="preserve">21.2657432556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0783767700195</t>
   </si>
   <si>
     <t xml:space="preserve">21.453104019165</t>
@@ -1769,7 +1769,7 @@
     <t xml:space="preserve">20.7973327636719</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8278274536133</t>
+    <t xml:space="preserve">21.8278293609619</t>
   </si>
   <si>
     <t xml:space="preserve">22.1088771820068</t>
@@ -1796,16 +1796,16 @@
     <t xml:space="preserve">20.2352428436279</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3147659301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0173797607422</t>
+    <t xml:space="preserve">18.3147678375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0173816680908</t>
   </si>
   <si>
     <t xml:space="preserve">20.6099681854248</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9215126037598</t>
+    <t xml:space="preserve">21.9215145111084</t>
   </si>
   <si>
     <t xml:space="preserve">22.7646465301514</t>
@@ -1817,10 +1817,10 @@
     <t xml:space="preserve">21.1720600128174</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7036514282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3594207763672</t>
+    <t xml:space="preserve">20.703649520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3594188690186</t>
   </si>
   <si>
     <t xml:space="preserve">20.5162868499756</t>
@@ -1832,13 +1832,13 @@
     <t xml:space="preserve">22.6709671020508</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2025585174561</t>
+    <t xml:space="preserve">22.2025566101074</t>
   </si>
   <si>
     <t xml:space="preserve">22.3899211883545</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9541988372803</t>
+    <t xml:space="preserve">19.9541969299316</t>
   </si>
   <si>
     <t xml:space="preserve">20.4226055145264</t>
@@ -1850,7 +1850,7 @@
     <t xml:space="preserve">19.3921070098877</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8300170898438</t>
+    <t xml:space="preserve">18.8300189971924</t>
   </si>
   <si>
     <t xml:space="preserve">18.361608505249</t>
@@ -1862,16 +1862,16 @@
     <t xml:space="preserve">17.6589946746826</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7526798248291</t>
+    <t xml:space="preserve">17.7526779174805</t>
   </si>
   <si>
     <t xml:space="preserve">17.377950668335</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8932018280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9400386810303</t>
+    <t xml:space="preserve">17.8931999206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9400405883789</t>
   </si>
   <si>
     <t xml:space="preserve">18.2679271697998</t>
@@ -1892,7 +1892,7 @@
     <t xml:space="preserve">18.2304534912109</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4552898406982</t>
+    <t xml:space="preserve">18.4552879333496</t>
   </si>
   <si>
     <t xml:space="preserve">17.9494094848633</t>
@@ -1910,10 +1910,10 @@
     <t xml:space="preserve">20.0947189331055</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1884002685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1415615081787</t>
+    <t xml:space="preserve">20.1884021759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1415596008301</t>
   </si>
   <si>
     <t xml:space="preserve">18.4927635192871</t>
@@ -3384,6 +3384,9 @@
   </si>
   <si>
     <t xml:space="preserve">35.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.25</t>
   </si>
 </sst>
 </file>
@@ -68800,7 +68803,7 @@
     </row>
     <row r="2504">
       <c r="A2504" s="1" t="n">
-        <v>45965.6910300926</v>
+        <v>45965.3333333333</v>
       </c>
       <c r="B2504" t="n">
         <v>6351</v>
@@ -68821,6 +68824,32 @@
         <v>1123</v>
       </c>
       <c r="H2504" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2505">
+      <c r="A2505" s="1" t="n">
+        <v>45966.6912615741</v>
+      </c>
+      <c r="B2505" t="n">
+        <v>16173</v>
+      </c>
+      <c r="C2505" t="n">
+        <v>37.4500007629395</v>
+      </c>
+      <c r="D2505" t="n">
+        <v>35.5999984741211</v>
+      </c>
+      <c r="E2505" t="n">
+        <v>36.0999984741211</v>
+      </c>
+      <c r="F2505" t="n">
+        <v>36.25</v>
+      </c>
+      <c r="G2505" t="s">
+        <v>1124</v>
+      </c>
+      <c r="H2505" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LUVE.MI.xlsx
+++ b/data/LUVE.MI.xlsx
@@ -44,103 +44,103 @@
     <t xml:space="preserve">LUVE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31703472137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28383255004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09292221069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19667720794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07632064819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15102577209473</t>
+    <t xml:space="preserve">8.31703567504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28383159637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09292316436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19667816162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07632160186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15102672576904</t>
   </si>
   <si>
     <t xml:space="preserve">8.17177677154541</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03896999359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08462142944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06802177429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9684157371521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01821708679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99746751785278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91861343383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91446304321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91031217575073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88541078567505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87711048126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85221004486084</t>
+    <t xml:space="preserve">8.03896903991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08462238311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06802082061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96841621398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01821804046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9974684715271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91861295700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91446399688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91031265258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88541173934937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87711238861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85221099853516</t>
   </si>
   <si>
     <t xml:space="preserve">7.64884996414185</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71940422058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7028021812439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69035339355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.619797706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55754613876343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55339431762695</t>
+    <t xml:space="preserve">7.71940326690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70280075073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69035196304321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61979818344116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55754470825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55339622497559</t>
   </si>
   <si>
     <t xml:space="preserve">7.636399269104</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76920509338379</t>
+    <t xml:space="preserve">7.76920652389526</t>
   </si>
   <si>
     <t xml:space="preserve">7.80240678787231</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93521404266357</t>
+    <t xml:space="preserve">7.93521356582642</t>
   </si>
   <si>
     <t xml:space="preserve">8.10122299194336</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05142021179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18422794342041</t>
+    <t xml:space="preserve">8.05141925811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18422698974609</t>
   </si>
   <si>
     <t xml:space="preserve">8.13442516326904</t>
@@ -149,43 +149,43 @@
     <t xml:space="preserve">8.00161743164062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9601149559021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21742820739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35853481292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32533550262451</t>
+    <t xml:space="preserve">7.96011543273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21742916107178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35853576660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32533359527588</t>
   </si>
   <si>
     <t xml:space="preserve">8.29213333129883</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20083045959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15932655334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30336475372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36267471313477</t>
+    <t xml:space="preserve">8.20082855224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15932559967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30336380004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36267375946045</t>
   </si>
   <si>
     <t xml:space="preserve">8.43045711517334</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15085411071777</t>
+    <t xml:space="preserve">8.15085315704346</t>
   </si>
   <si>
     <t xml:space="preserve">8.17627048492432</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2059268951416</t>
+    <t xml:space="preserve">8.20592784881592</t>
   </si>
   <si>
     <t xml:space="preserve">8.13390827178955</t>
@@ -194,13 +194,13 @@
     <t xml:space="preserve">8.11696147918701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21863460540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21016407012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21439838409424</t>
+    <t xml:space="preserve">8.21863555908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21016120910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21440029144287</t>
   </si>
   <si>
     <t xml:space="preserve">8.20169067382812</t>
@@ -209,61 +209,61 @@
     <t xml:space="preserve">8.26099967956543</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09154319763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10848808288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04918098449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96445035934448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92208671569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87972402572632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8373589515686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1254358291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93479442596436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75263071060181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71026611328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93903350830078</t>
+    <t xml:space="preserve">8.09154224395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10848903656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04917907714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96445083618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92208766937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87972259521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83736038208008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12543487548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93479633331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75262975692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71026849746704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93903207778931</t>
   </si>
   <si>
     <t xml:space="preserve">7.81194067001343</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79499387741089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62553739547729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66790294647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84583234786987</t>
+    <t xml:space="preserve">7.79499483108521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62553882598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66790342330933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84583139419556</t>
   </si>
   <si>
     <t xml:space="preserve">8.19321727752686</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47281932830811</t>
+    <t xml:space="preserve">8.47282123565674</t>
   </si>
   <si>
     <t xml:space="preserve">8.51518535614014</t>
@@ -281,121 +281,121 @@
     <t xml:space="preserve">8.71853256225586</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50671195983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54060173034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46858501434326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46434783935547</t>
+    <t xml:space="preserve">8.50671100616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54060363769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46858310699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46434688568115</t>
   </si>
   <si>
     <t xml:space="preserve">8.55754852294922</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57449436187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81173133850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72700500488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64227771759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89646148681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0235538482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09980964660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06591892242432</t>
+    <t xml:space="preserve">8.57449340820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81173324584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7270040512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64227676391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89646053314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02355289459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09980773925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06591606140137</t>
   </si>
   <si>
     <t xml:space="preserve">9.10828113555908</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27773761749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1930103302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18453693389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07439041137695</t>
+    <t xml:space="preserve">9.27773857116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19300937652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18453598022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07439231872559</t>
   </si>
   <si>
     <t xml:space="preserve">9.09133625030518</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30315589904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32010269165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12522792816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60817718505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40483093261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4895601272583</t>
+    <t xml:space="preserve">9.30315494537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32010173797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1252269744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60817813873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4048318862915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48955821990967</t>
   </si>
   <si>
     <t xml:space="preserve">9.38788509368896</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53192234039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48108673095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44719314575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54039669036865</t>
+    <t xml:space="preserve">9.53192329406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48108577728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44719505310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54039573669434</t>
   </si>
   <si>
     <t xml:space="preserve">9.57428646087646</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47261428833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41330432891846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42177581787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51497554779053</t>
+    <t xml:space="preserve">9.47261333465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41330337524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42177486419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51497745513916</t>
   </si>
   <si>
     <t xml:space="preserve">9.56581401824951</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74374389648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0657119750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2521142959595</t>
+    <t xml:space="preserve">9.74374294281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.065710067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2521133422852</t>
   </si>
   <si>
     <t xml:space="preserve">10.1334934234619</t>
@@ -404,37 +404,37 @@
     <t xml:space="preserve">9.99792766571045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95556449890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98098182678223</t>
+    <t xml:space="preserve">9.95556354522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98098278045654</t>
   </si>
   <si>
     <t xml:space="preserve">9.88778114318848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91319942474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.01487159729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1589117050171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0402927398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70137786865234</t>
+    <t xml:space="preserve">9.91319751739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0148735046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1589107513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0402936935425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70137882232666</t>
   </si>
   <si>
     <t xml:space="preserve">9.73527050018311</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70985126495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0826549530029</t>
+    <t xml:space="preserve">9.7098503112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0826568603516</t>
   </si>
   <si>
     <t xml:space="preserve">9.8623628616333</t>
@@ -443,82 +443,82 @@
     <t xml:space="preserve">10.1250200271606</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2944755554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4808788299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5317153930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5147705078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8028469085693</t>
+    <t xml:space="preserve">10.2944765090942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4808778762817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.531717300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5147695541382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8028450012207</t>
   </si>
   <si>
     <t xml:space="preserve">10.912992477417</t>
   </si>
   <si>
-    <t xml:space="preserve">10.862156867981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0146675109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0570297241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2773246765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.438307762146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6586008071899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5823450088501</t>
+    <t xml:space="preserve">10.8621549606323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.014666557312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0570316314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.277322769165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4383068084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6586027145386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5823459625244</t>
   </si>
   <si>
     <t xml:space="preserve">11.4806709289551</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5908193588257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7009649276733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7772197723389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.811110496521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8365316390991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6670751571655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5992908477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5230369567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6077642440796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6263799667358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7297258377075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6952781677246</t>
+    <t xml:space="preserve">11.5908174514771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7009658813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7772207260132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8111124038696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8365306854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6670742034912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.599289894104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5230340957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6077632904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6263809204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7297267913818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6952772140503</t>
   </si>
   <si>
     <t xml:space="preserve">11.6780548095703</t>
@@ -527,10 +527,10 @@
     <t xml:space="preserve">11.798623085022</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8847465515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9105796813965</t>
+    <t xml:space="preserve">11.8847455978394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9105825424194</t>
   </si>
   <si>
     <t xml:space="preserve">12.0656003952026</t>
@@ -539,7 +539,7 @@
     <t xml:space="preserve">12.3153524398804</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3584136962891</t>
+    <t xml:space="preserve">12.3584127426147</t>
   </si>
   <si>
     <t xml:space="preserve">12.0569877624512</t>
@@ -548,31 +548,31 @@
     <t xml:space="preserve">12.1431093215942</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9967041015625</t>
+    <t xml:space="preserve">11.9967031478882</t>
   </si>
   <si>
     <t xml:space="preserve">11.8416843414307</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7555637359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7125024795532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8502969741821</t>
+    <t xml:space="preserve">11.7555618286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7125015258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8502979278564</t>
   </si>
   <si>
     <t xml:space="preserve">11.9191942214966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9622554779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0397634506226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.048376083374</t>
+    <t xml:space="preserve">11.962254524231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0397644042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0483751296997</t>
   </si>
   <si>
     <t xml:space="preserve">11.7900104522705</t>
@@ -581,22 +581,22 @@
     <t xml:space="preserve">12.0311517715454</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9450283050537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8158493041992</t>
+    <t xml:space="preserve">11.9450302124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8158483505249</t>
   </si>
   <si>
     <t xml:space="preserve">11.8933582305908</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8761329650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8244609832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8675212860107</t>
+    <t xml:space="preserve">11.8761320114136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8244600296021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8675203323364</t>
   </si>
   <si>
     <t xml:space="preserve">11.901969909668</t>
@@ -605,24 +605,27 @@
     <t xml:space="preserve">11.9278059005737</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7211132049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6694421768188</t>
+    <t xml:space="preserve">11.7211151123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6694412231445</t>
   </si>
   <si>
     <t xml:space="preserve">11.6349935531616</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6091556549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5747079849243</t>
+    <t xml:space="preserve">11.6091575622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.57470703125</t>
   </si>
   <si>
     <t xml:space="preserve">11.5316476821899</t>
   </si>
   <si>
+    <t xml:space="preserve">11.5230350494385</t>
+  </si>
+  <si>
     <t xml:space="preserve">11.368016242981</t>
   </si>
   <si>
@@ -632,37 +635,37 @@
     <t xml:space="preserve">11.2818956375122</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2302236557007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1957759857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1871633529663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1096544265747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0579805374146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1785507202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.126877784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9374113082886</t>
+    <t xml:space="preserve">11.2302227020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1957740783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1871614456177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1096515655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0579786300659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1785497665405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1268768310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9374084472656</t>
   </si>
   <si>
     <t xml:space="preserve">11.0665922164917</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0235319137573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0838165283203</t>
+    <t xml:space="preserve">11.0235328674316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0838174819946</t>
   </si>
   <si>
     <t xml:space="preserve">11.1354894638062</t>
@@ -674,34 +677,34 @@
     <t xml:space="preserve">11.3163452148438</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4541368484497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5402603149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.411078453064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.290506362915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1613264083862</t>
+    <t xml:space="preserve">11.4541387557983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5402584075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4110765457153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2905082702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1613254547119</t>
   </si>
   <si>
     <t xml:space="preserve">11.2646713256836</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1527128219604</t>
+    <t xml:space="preserve">11.1527137756348</t>
   </si>
   <si>
     <t xml:space="preserve">11.0407562255859</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4196901321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2216110229492</t>
+    <t xml:space="preserve">11.4196910858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2216091156006</t>
   </si>
   <si>
     <t xml:space="preserve">11.2388353347778</t>
@@ -719,28 +722,28 @@
     <t xml:space="preserve">11.0063076019287</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0924291610718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74032402038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01690483093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21498394012451</t>
+    <t xml:space="preserve">11.0924282073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74032497406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01690578460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21498203277588</t>
   </si>
   <si>
     <t xml:space="preserve">9.37861442565918</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49057292938232</t>
+    <t xml:space="preserve">9.49057102203369</t>
   </si>
   <si>
     <t xml:space="preserve">9.5077953338623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59391689300537</t>
+    <t xml:space="preserve">9.593918800354</t>
   </si>
   <si>
     <t xml:space="preserve">9.60252952575684</t>
@@ -749,43 +752,43 @@
     <t xml:space="preserve">9.6886510848999</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56808090209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39583778381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34416484832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2580451965332</t>
+    <t xml:space="preserve">9.56808185577393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39583873748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34416389465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25804424285889</t>
   </si>
   <si>
     <t xml:space="preserve">9.30110454559326</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41306209564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28388023376465</t>
+    <t xml:space="preserve">9.41306304931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28387928009033</t>
   </si>
   <si>
     <t xml:space="preserve">9.24081993103027</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12886333465576</t>
+    <t xml:space="preserve">9.12886238098145</t>
   </si>
   <si>
     <t xml:space="preserve">9.02551651000977</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20637130737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26665592193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69726181030273</t>
+    <t xml:space="preserve">9.20637035369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26665782928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69726371765137</t>
   </si>
   <si>
     <t xml:space="preserve">9.65420246124268</t>
@@ -794,10 +797,10 @@
     <t xml:space="preserve">9.66281509399414</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64559078216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67142581939697</t>
+    <t xml:space="preserve">9.64558887481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67142677307129</t>
   </si>
   <si>
     <t xml:space="preserve">9.75754833221436</t>
@@ -806,13 +809,13 @@
     <t xml:space="preserve">9.71448802947998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09441375732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93939399719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14608669281006</t>
+    <t xml:space="preserve">9.09441566467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93939590454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14608764648438</t>
   </si>
   <si>
     <t xml:space="preserve">9.12024974822998</t>
@@ -824,16 +827,16 @@
     <t xml:space="preserve">9.73171138763428</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90395450592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77477264404297</t>
+    <t xml:space="preserve">9.90395355224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77477169036865</t>
   </si>
   <si>
     <t xml:space="preserve">9.5336332321167</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49918556213379</t>
+    <t xml:space="preserve">9.49918270111084</t>
   </si>
   <si>
     <t xml:space="preserve">9.57669258117676</t>
@@ -851,10 +854,10 @@
     <t xml:space="preserve">9.54224586486816</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17192268371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23220634460449</t>
+    <t xml:space="preserve">9.1719217300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23220825195312</t>
   </si>
   <si>
     <t xml:space="preserve">9.55947017669678</t>
@@ -863,67 +866,67 @@
     <t xml:space="preserve">9.51640796661377</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86089420318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.956618309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91355991363525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08580207824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04274082183838</t>
+    <t xml:space="preserve">9.86089324951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95662021636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91355800628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08580112457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04273986816406</t>
   </si>
   <si>
     <t xml:space="preserve">8.999680519104</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82743644714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69825458526611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87049865722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7843770980835</t>
+    <t xml:space="preserve">8.82743740081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69825553894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87049674987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78437614440918</t>
   </si>
   <si>
     <t xml:space="preserve">8.7413158416748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61213493347168</t>
+    <t xml:space="preserve">8.61213397979736</t>
   </si>
   <si>
     <t xml:space="preserve">8.59490871429443</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65519428253174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45711421966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06314468383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10714149475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0191478729248</t>
+    <t xml:space="preserve">8.65519523620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45711612701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06314373016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10714054107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01914882659912</t>
   </si>
   <si>
     <t xml:space="preserve">8.97515296936035</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93115615844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88716125488281</t>
+    <t xml:space="preserve">8.93115711212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88716220855713</t>
   </si>
   <si>
     <t xml:space="preserve">8.84316539764404</t>
@@ -932,64 +935,64 @@
     <t xml:space="preserve">8.76397323608398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48239898681641</t>
+    <t xml:space="preserve">8.48239994049072</t>
   </si>
   <si>
     <t xml:space="preserve">8.71117782592773</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62318801879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58798980712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65838241577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60558891296387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72877597808838</t>
+    <t xml:space="preserve">8.62318706512451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58798885345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6583833694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60558795928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7287769317627</t>
   </si>
   <si>
     <t xml:space="preserve">8.69357967376709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74637317657471</t>
+    <t xml:space="preserve">8.74637413024902</t>
   </si>
   <si>
     <t xml:space="preserve">8.53519535064697</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44720458984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27121829986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32401466369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28881740570068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78157043457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64078330993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79917049407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67598056793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23912906646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37111568450928</t>
+    <t xml:space="preserve">8.44720363616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27121925354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32401371002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.288818359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78157138824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64078426361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79916858673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67598152160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23912811279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37111473083496</t>
   </si>
   <si>
     <t xml:space="preserve">9.32711982727051</t>
@@ -998,28 +1001,28 @@
     <t xml:space="preserve">9.19513320922852</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15113544464111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46480178833008</t>
+    <t xml:space="preserve">9.15113639831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46480083465576</t>
   </si>
   <si>
     <t xml:space="preserve">8.41200637817383</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49999713897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34161186218262</t>
+    <t xml:space="preserve">8.49999809265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34161281585693</t>
   </si>
   <si>
     <t xml:space="preserve">8.23602294921875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30641555786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13043212890625</t>
+    <t xml:space="preserve">8.30641460418701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13043308258057</t>
   </si>
   <si>
     <t xml:space="preserve">8.18322849273682</t>
@@ -1028,37 +1031,37 @@
     <t xml:space="preserve">8.16562843322754</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21842575073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25362014770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37681007385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51759624481201</t>
+    <t xml:space="preserve">8.21842479705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25362110137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37681102752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51759719848633</t>
   </si>
   <si>
     <t xml:space="preserve">9.28312397003174</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41511154174805</t>
+    <t xml:space="preserve">9.41511058807373</t>
   </si>
   <si>
     <t xml:space="preserve">9.63509082794189</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59109401702881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8990650177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1190462112427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1630401611328</t>
+    <t xml:space="preserve">9.59109497070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89906692504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.119044303894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1630420684814</t>
   </si>
   <si>
     <t xml:space="preserve">10.2070379257202</t>
@@ -1067,7 +1070,7 @@
     <t xml:space="preserve">10.3390245437622</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2950267791748</t>
+    <t xml:space="preserve">10.2950277328491</t>
   </si>
   <si>
     <t xml:space="preserve">10.383020401001</t>
@@ -1076,43 +1079,40 @@
     <t xml:space="preserve">10.2510318756104</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4270172119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0750484466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.515007019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6498165130615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4700708389282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6947507858276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6048803329468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.380199432373</t>
+    <t xml:space="preserve">10.4270153045654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0750494003296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5150079727173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6498155593872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4700717926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.694751739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6048793792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3802013397217</t>
   </si>
   <si>
     <t xml:space="preserve">10.2453927993774</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0656490325928</t>
+    <t xml:space="preserve">10.0656471252441</t>
   </si>
   <si>
     <t xml:space="preserve">10.4251365661621</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5150060653687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3352642059326</t>
+    <t xml:space="preserve">10.3352632522583</t>
   </si>
   <si>
     <t xml:space="preserve">10.2903280258179</t>
@@ -1121,58 +1121,58 @@
     <t xml:space="preserve">10.2004566192627</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9757776260376</t>
+    <t xml:space="preserve">9.97577667236328</t>
   </si>
   <si>
     <t xml:space="preserve">10.1105842590332</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93084144592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88590431213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1555194854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.020712852478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7510986328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70616149902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34667301177979</t>
+    <t xml:space="preserve">9.93084049224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88590526580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1555204391479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0207118988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75109672546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70616245269775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3466739654541</t>
   </si>
   <si>
     <t xml:space="preserve">9.30173778533936</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39161109924316</t>
+    <t xml:space="preserve">9.39161014556885</t>
   </si>
   <si>
     <t xml:space="preserve">9.48148155212402</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61628818511963</t>
+    <t xml:space="preserve">9.61628913879395</t>
   </si>
   <si>
     <t xml:space="preserve">9.52641773223877</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43654632568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12199306488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03212261199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16693019866943</t>
+    <t xml:space="preserve">9.43654537200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12199401855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0321216583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16692924499512</t>
   </si>
   <si>
     <t xml:space="preserve">9.07705783843994</t>
@@ -1184,16 +1184,16 @@
     <t xml:space="preserve">8.98718547821045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5713529586792</t>
+    <t xml:space="preserve">9.57135200500488</t>
   </si>
   <si>
     <t xml:space="preserve">9.66122531890869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79603099822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9643659591675</t>
+    <t xml:space="preserve">9.79603290557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9643669128418</t>
   </si>
   <si>
     <t xml:space="preserve">11.4586629867554</t>
@@ -1208,31 +1208,31 @@
     <t xml:space="preserve">11.1441106796265</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9194307327271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8744964599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0093030929565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2789182662964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4137268066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5485343933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6833429336548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.77321434021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9080219268799</t>
+    <t xml:space="preserve">10.9194316864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8744945526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0093021392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2789192199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4137258529663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5485353469849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6833419799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7732133865356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9080200195312</t>
   </si>
   <si>
     <t xml:space="preserve">12.132700920105</t>
@@ -1241,7 +1241,7 @@
     <t xml:space="preserve">11.9978942871094</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8181486129761</t>
+    <t xml:space="preserve">11.8181505203247</t>
   </si>
   <si>
     <t xml:space="preserve">11.593469619751</t>
@@ -1253,7 +1253,7 @@
     <t xml:space="preserve">12.5820608139038</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9415483474731</t>
+    <t xml:space="preserve">12.9415464401245</t>
   </si>
   <si>
     <t xml:space="preserve">12.8067398071289</t>
@@ -1265,31 +1265,31 @@
     <t xml:space="preserve">13.0763559341431</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4472522735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5371236801147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2675104141235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4023170471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6269960403442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.671932220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8966131210327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7282791137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7846231460571</t>
+    <t xml:space="preserve">12.4472532272339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5371246337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2675085067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4023160934448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6269969940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6719312667847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.896614074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7282781600952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7846240997314</t>
   </si>
   <si>
     <t xml:space="preserve">10.559944152832</t>
@@ -1298,31 +1298,31 @@
     <t xml:space="preserve">8.89731407165527</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98062133789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81885051727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53126192092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89074945449829</t>
+    <t xml:space="preserve">7.98062086105347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81885147094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53126287460327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89074993133545</t>
   </si>
   <si>
     <t xml:space="preserve">8.53782653808594</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96264600753784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44795322418213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60972309112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66364860534668</t>
+    <t xml:space="preserve">7.962646484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44795513153076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6097240447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66364765167236</t>
   </si>
   <si>
     <t xml:space="preserve">8.86136531829834</t>
@@ -1331,16 +1331,16 @@
     <t xml:space="preserve">9.21186637878418</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93848991394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80045509338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89247894287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66242122650146</t>
+    <t xml:space="preserve">9.93849086761475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80045413970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89247798919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66242027282715</t>
   </si>
   <si>
     <t xml:space="preserve">9.7084321975708</t>
@@ -1349,19 +1349,19 @@
     <t xml:space="preserve">9.84646606445312</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1225357055664</t>
+    <t xml:space="preserve">10.1225347518921</t>
   </si>
   <si>
     <t xml:space="preserve">9.75444412231445</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3986053466797</t>
+    <t xml:space="preserve">10.3986043930054</t>
   </si>
   <si>
     <t xml:space="preserve">10.3065814971924</t>
   </si>
   <si>
-    <t xml:space="preserve">10.720685005188</t>
+    <t xml:space="preserve">10.7206859588623</t>
   </si>
   <si>
     <t xml:space="preserve">10.5826501846313</t>
@@ -1370,19 +1370,19 @@
     <t xml:space="preserve">10.8587207794189</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6746730804443</t>
+    <t xml:space="preserve">10.6746740341187</t>
   </si>
   <si>
     <t xml:space="preserve">10.9967546463013</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6286630630493</t>
+    <t xml:space="preserve">10.6286611557007</t>
   </si>
   <si>
     <t xml:space="preserve">10.7666959762573</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4906272888184</t>
+    <t xml:space="preserve">10.4906282424927</t>
   </si>
   <si>
     <t xml:space="preserve">11.1347894668579</t>
@@ -1394,16 +1394,16 @@
     <t xml:space="preserve">11.5028820037842</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1808004379272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0427665710449</t>
+    <t xml:space="preserve">11.1807994842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0427675247192</t>
   </si>
   <si>
     <t xml:space="preserve">11.2728242874146</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9507436752319</t>
+    <t xml:space="preserve">10.9507427215576</t>
   </si>
   <si>
     <t xml:space="preserve">11.0887775421143</t>
@@ -1418,43 +1418,43 @@
     <t xml:space="preserve">11.4108581542969</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4568691253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2268123626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3648462295532</t>
+    <t xml:space="preserve">11.4568700790405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2268114089966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3648471832275</t>
   </si>
   <si>
     <t xml:space="preserve">11.5488929748535</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5949039459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6869258880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9629983901978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7789497375488</t>
+    <t xml:space="preserve">11.5949048995972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6869268417358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9629974365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7789506912231</t>
   </si>
   <si>
     <t xml:space="preserve">12.0090084075928</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1010313034058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7329397201538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8249626159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0550212860107</t>
+    <t xml:space="preserve">12.1010303497314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7329387664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8249635696411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0550193786621</t>
   </si>
   <si>
     <t xml:space="preserve">11.8709726333618</t>
@@ -1466,55 +1466,55 @@
     <t xml:space="preserve">11.6409158706665</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1470432281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6991806030273</t>
+    <t xml:space="preserve">12.1470422744751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6991815567017</t>
   </si>
   <si>
     <t xml:space="preserve">12.7912034988403</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0672731399536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8832263946533</t>
+    <t xml:space="preserve">13.0672740936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8832273483276</t>
   </si>
   <si>
     <t xml:space="preserve">12.929238319397</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2053089141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2513198852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1132850646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1592969894409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3893537521362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2973299026489</t>
+    <t xml:space="preserve">13.2053079605103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2513189315796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1132831573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1592960357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3893547058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2973308563232</t>
   </si>
   <si>
     <t xml:space="preserve">12.9752502441406</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7114343643188</t>
+    <t xml:space="preserve">13.7114334106445</t>
   </si>
   <si>
     <t xml:space="preserve">13.4353656768799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5151357650757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3770999908447</t>
+    <t xml:space="preserve">12.51513671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.377100944519</t>
   </si>
   <si>
     <t xml:space="preserve">12.837215423584</t>
@@ -1523,25 +1523,25 @@
     <t xml:space="preserve">12.7451934814453</t>
   </si>
   <si>
-    <t xml:space="preserve">12.653169631958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3433437347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6194114685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8494691848755</t>
+    <t xml:space="preserve">12.6531686782837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3433427810669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6194124221802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8494701385498</t>
   </si>
   <si>
     <t xml:space="preserve">13.9414920806885</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1715488433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3555974960327</t>
+    <t xml:space="preserve">14.1715507507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3555965423584</t>
   </si>
   <si>
     <t xml:space="preserve">14.1255388259888</t>
@@ -1550,67 +1550,67 @@
     <t xml:space="preserve">14.4936304092407</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7236881256104</t>
+    <t xml:space="preserve">14.7236890792847</t>
   </si>
   <si>
     <t xml:space="preserve">14.6776762008667</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8157119750977</t>
+    <t xml:space="preserve">14.8157110214233</t>
   </si>
   <si>
     <t xml:space="preserve">14.861722946167</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0457696914673</t>
+    <t xml:space="preserve">15.045768737793</t>
   </si>
   <si>
     <t xml:space="preserve">14.5396423339844</t>
   </si>
   <si>
-    <t xml:space="preserve">14.631664276123</t>
+    <t xml:space="preserve">14.6316652297974</t>
   </si>
   <si>
     <t xml:space="preserve">14.4476194381714</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2635736465454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9875030517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3095846176147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6654243469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8034572601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5734004974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7574453353882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9537448883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0335149765015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4269771575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3801374435425</t>
+    <t xml:space="preserve">14.2635726928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9875040054321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3095855712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6654224395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8034582138062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5733995437622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7574462890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.95374584198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0335140228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4269781112671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3801383972168</t>
   </si>
   <si>
     <t xml:space="preserve">14.473819732666</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7080240249634</t>
+    <t xml:space="preserve">14.7080230712891</t>
   </si>
   <si>
     <t xml:space="preserve">14.8485460281372</t>
@@ -1619,16 +1619,16 @@
     <t xml:space="preserve">15.0359086990356</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0827503204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8953857421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9422273635864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1764316558838</t>
+    <t xml:space="preserve">15.0827493667603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8953866958618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9422264099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1764326095581</t>
   </si>
   <si>
     <t xml:space="preserve">15.1295909881592</t>
@@ -1640,40 +1640,40 @@
     <t xml:space="preserve">14.6611814498901</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3169546127319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7548637390137</t>
+    <t xml:space="preserve">15.3169555664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7548627853394</t>
   </si>
   <si>
     <t xml:space="preserve">14.8017053604126</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2232713699341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5043172836304</t>
+    <t xml:space="preserve">15.2232723236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5043153762817</t>
   </si>
   <si>
     <t xml:space="preserve">16.0664081573486</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6916799545288</t>
+    <t xml:space="preserve">15.6916818618774</t>
   </si>
   <si>
     <t xml:space="preserve">15.7385215759277</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9727230072021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9258861541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7853622436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1132488250732</t>
+    <t xml:space="preserve">15.9727249145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9258852005005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.785364151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1132469177246</t>
   </si>
   <si>
     <t xml:space="preserve">15.8322019577026</t>
@@ -1682,7 +1682,7 @@
     <t xml:space="preserve">16.5348167419434</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8627014160156</t>
+    <t xml:space="preserve">16.8627033233643</t>
   </si>
   <si>
     <t xml:space="preserve">17.1437454223633</t>
@@ -1691,49 +1691,49 @@
     <t xml:space="preserve">16.581657409668</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2069301605225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2842712402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7995185852051</t>
+    <t xml:space="preserve">16.2069282531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2842693328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7995166778564</t>
   </si>
   <si>
     <t xml:space="preserve">17.4716320037842</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8158626556396</t>
+    <t xml:space="preserve">16.815860748291</t>
   </si>
   <si>
     <t xml:space="preserve">16.6284980773926</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0969066619873</t>
+    <t xml:space="preserve">17.0969047546387</t>
   </si>
   <si>
     <t xml:space="preserve">17.5184745788574</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6121559143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0337219238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5489711761475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7363357543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.923698425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7668342590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5794677734375</t>
+    <t xml:space="preserve">17.612154006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0337238311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5489730834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7363338470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9237003326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7668323516846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5794696807861</t>
   </si>
   <si>
     <t xml:space="preserve">19.2047443389893</t>
@@ -1742,13 +1742,13 @@
     <t xml:space="preserve">19.1110610961914</t>
   </si>
   <si>
-    <t xml:space="preserve">19.673152923584</t>
+    <t xml:space="preserve">19.6731510162354</t>
   </si>
   <si>
     <t xml:space="preserve">19.2984237670898</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4857864379883</t>
+    <t xml:space="preserve">19.4857883453369</t>
   </si>
   <si>
     <t xml:space="preserve">19.8605175018311</t>
@@ -1757,49 +1757,49 @@
     <t xml:space="preserve">20.3289241790771</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9846954345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2657413482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0783767700195</t>
+    <t xml:space="preserve">20.9846935272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.265739440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0783748626709</t>
   </si>
   <si>
     <t xml:space="preserve">21.453104019165</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7973327636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8278293609619</t>
+    <t xml:space="preserve">20.7973346710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8278312683105</t>
   </si>
   <si>
     <t xml:space="preserve">22.1088771820068</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7341480255127</t>
+    <t xml:space="preserve">21.7341499328613</t>
   </si>
   <si>
     <t xml:space="preserve">22.015193939209</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2962398529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4836025238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6404685974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5467834472656</t>
+    <t xml:space="preserve">22.2962379455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4836044311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6404666900635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5467853546143</t>
   </si>
   <si>
     <t xml:space="preserve">20.2352428436279</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3147678375244</t>
+    <t xml:space="preserve">18.314769744873</t>
   </si>
   <si>
     <t xml:space="preserve">19.0173797607422</t>
@@ -1820,19 +1820,19 @@
     <t xml:space="preserve">21.1720600128174</t>
   </si>
   <si>
-    <t xml:space="preserve">20.703649520874</t>
+    <t xml:space="preserve">20.7036514282227</t>
   </si>
   <si>
     <t xml:space="preserve">21.3594207763672</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5162868499756</t>
+    <t xml:space="preserve">20.5162887573242</t>
   </si>
   <si>
     <t xml:space="preserve">20.0478782653809</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6709671020508</t>
+    <t xml:space="preserve">22.6709651947021</t>
   </si>
   <si>
     <t xml:space="preserve">22.2025585174561</t>
@@ -1841,19 +1841,19 @@
     <t xml:space="preserve">22.3899211883545</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9541969299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4226055145264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8910140991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3921089172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8300170898438</t>
+    <t xml:space="preserve">19.954195022583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4226036071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8910121917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3921070098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8300189971924</t>
   </si>
   <si>
     <t xml:space="preserve">18.361608505249</t>
@@ -1862,22 +1862,22 @@
     <t xml:space="preserve">16.9563846588135</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6589965820312</t>
+    <t xml:space="preserve">17.6589984893799</t>
   </si>
   <si>
     <t xml:space="preserve">17.7526779174805</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3779487609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8932018280029</t>
+    <t xml:space="preserve">17.3779525756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8931999206543</t>
   </si>
   <si>
     <t xml:space="preserve">17.9400405883789</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2679252624512</t>
+    <t xml:space="preserve">18.2679271697998</t>
   </si>
   <si>
     <t xml:space="preserve">18.8768577575684</t>
@@ -1886,13 +1886,13 @@
     <t xml:space="preserve">18.6426544189453</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3241367340088</t>
+    <t xml:space="preserve">18.3241348266602</t>
   </si>
   <si>
     <t xml:space="preserve">18.2117176055908</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2304515838623</t>
+    <t xml:space="preserve">18.2304534912109</t>
   </si>
   <si>
     <t xml:space="preserve">18.4552898406982</t>
@@ -1904,31 +1904,31 @@
     <t xml:space="preserve">18.1180362701416</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9705390930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2820835113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0947208404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1883983612061</t>
+    <t xml:space="preserve">18.9705410003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2820816040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0947189331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1884002685547</t>
   </si>
   <si>
     <t xml:space="preserve">20.1415615081787</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4927616119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5559463500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1999549865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8847980499268</t>
+    <t xml:space="preserve">18.4927635192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.555944442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1999568939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8847961425781</t>
   </si>
   <si>
     <t xml:space="preserve">17.7634181976318</t>
@@ -1940,13 +1940,13 @@
     <t xml:space="preserve">18.9285449981689</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4319343566895</t>
+    <t xml:space="preserve">18.4319324493408</t>
   </si>
   <si>
     <t xml:space="preserve">18.6038379669189</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1004505157471</t>
+    <t xml:space="preserve">19.1004486083984</t>
   </si>
   <si>
     <t xml:space="preserve">18.9858474731445</t>
@@ -1955,7 +1955,7 @@
     <t xml:space="preserve">19.1482009887695</t>
   </si>
   <si>
-    <t xml:space="preserve">18.90944480896</t>
+    <t xml:space="preserve">18.9094467163086</t>
   </si>
   <si>
     <t xml:space="preserve">18.9476470947266</t>
@@ -1964,16 +1964,16 @@
     <t xml:space="preserve">20.0077228546143</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0554733276367</t>
+    <t xml:space="preserve">20.0554714202881</t>
   </si>
   <si>
     <t xml:space="preserve">20.5329856872559</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9149913787842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1509761810303</t>
+    <t xml:space="preserve">20.9149932861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1509742736816</t>
   </si>
   <si>
     <t xml:space="preserve">20.4374809265137</t>
@@ -1997,7 +1997,7 @@
     <t xml:space="preserve">19.2914562225342</t>
   </si>
   <si>
-    <t xml:space="preserve">19.339204788208</t>
+    <t xml:space="preserve">19.3392086029053</t>
   </si>
   <si>
     <t xml:space="preserve">18.813943862915</t>
@@ -2006,28 +2006,28 @@
     <t xml:space="preserve">18.6993408203125</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3869571685791</t>
+    <t xml:space="preserve">19.3869552612305</t>
   </si>
   <si>
     <t xml:space="preserve">18.852144241333</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0813484191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2409324645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7757415771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9599685668945</t>
+    <t xml:space="preserve">19.0813503265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.240930557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7757434844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9599704742432</t>
   </si>
   <si>
     <t xml:space="preserve">20.4852333068848</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1059989929199</t>
+    <t xml:space="preserve">21.1059970855713</t>
   </si>
   <si>
     <t xml:space="preserve">21.8700160980225</t>
@@ -2039,16 +2039,16 @@
     <t xml:space="preserve">21.1537494659424</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7745132446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6790103912354</t>
+    <t xml:space="preserve">21.7745113372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.679012298584</t>
   </si>
   <si>
     <t xml:space="preserve">21.9177684783936</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2970027923584</t>
+    <t xml:space="preserve">21.2970008850098</t>
   </si>
   <si>
     <t xml:space="preserve">21.7267627716064</t>
@@ -2063,16 +2063,16 @@
     <t xml:space="preserve">20.1032238006592</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6257133483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8644676208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2492504119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.920539855957</t>
+    <t xml:space="preserve">19.62571144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8644695281982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2492523193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9205417633057</t>
   </si>
   <si>
     <t xml:space="preserve">22.4430294036865</t>
@@ -2081,22 +2081,22 @@
     <t xml:space="preserve">22.1565227508545</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0610218048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3475284576416</t>
+    <t xml:space="preserve">22.0610198974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.347526550293</t>
   </si>
   <si>
     <t xml:space="preserve">21.0582466125488</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3897323608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2942276000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1987247467041</t>
+    <t xml:space="preserve">20.3897304534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2942295074463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1987266540527</t>
   </si>
   <si>
     <t xml:space="preserve">20.8194904327393</t>
@@ -2111,7 +2111,7 @@
     <t xml:space="preserve">18.833044052124</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4824600219727</t>
+    <t xml:space="preserve">19.482458114624</t>
   </si>
   <si>
     <t xml:space="preserve">19.7212142944336</t>
@@ -2120,7 +2120,7 @@
     <t xml:space="preserve">19.8167171478271</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2464771270752</t>
+    <t xml:space="preserve">20.2464790344238</t>
   </si>
   <si>
     <t xml:space="preserve">20.6762371063232</t>
@@ -2132,10 +2132,10 @@
     <t xml:space="preserve">21.4402561187744</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6340351104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2070465087891</t>
+    <t xml:space="preserve">22.634033203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2070484161377</t>
   </si>
   <si>
     <t xml:space="preserve">22.7295341491699</t>
@@ -2144,10 +2144,10 @@
     <t xml:space="preserve">22.5862827301025</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8727893829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5385322570801</t>
+    <t xml:space="preserve">22.8727912902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5385341644287</t>
   </si>
   <si>
     <t xml:space="preserve">22.6817855834961</t>
@@ -2156,10 +2156,10 @@
     <t xml:space="preserve">23.0160427093506</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3025512695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4485778808594</t>
+    <t xml:space="preserve">23.3025493621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4485759735107</t>
   </si>
   <si>
     <t xml:space="preserve">23.7323112487793</t>
@@ -2171,13 +2171,13 @@
     <t xml:space="preserve">24.2098217010498</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0665664672852</t>
+    <t xml:space="preserve">24.0665683746338</t>
   </si>
   <si>
     <t xml:space="preserve">24.1143188476562</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4008235931396</t>
+    <t xml:space="preserve">24.4008255004883</t>
   </si>
   <si>
     <t xml:space="preserve">25.3080959320068</t>
@@ -2192,22 +2192,22 @@
     <t xml:space="preserve">25.0693416595459</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5440788269043</t>
+    <t xml:space="preserve">24.5440807342529</t>
   </si>
   <si>
     <t xml:space="preserve">24.9260883331299</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3558464050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.403600692749</t>
+    <t xml:space="preserve">25.3558483123779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4035987854004</t>
   </si>
   <si>
     <t xml:space="preserve">25.8333587646484</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8838844299316</t>
+    <t xml:space="preserve">26.883882522583</t>
   </si>
   <si>
     <t xml:space="preserve">26.7883815765381</t>
@@ -2219,7 +2219,7 @@
     <t xml:space="preserve">24.5918292999268</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8305854797363</t>
+    <t xml:space="preserve">24.830587387085</t>
   </si>
   <si>
     <t xml:space="preserve">25.2603454589844</t>
@@ -2228,55 +2228,55 @@
     <t xml:space="preserve">25.7378578186035</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7856063842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0721130371094</t>
+    <t xml:space="preserve">25.785608291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.072114944458</t>
   </si>
   <si>
     <t xml:space="preserve">26.2631187438965</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4513492584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.928861618042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5946044921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6901073455811</t>
+    <t xml:space="preserve">25.4513511657715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9288597106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5946025848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6901054382324</t>
   </si>
   <si>
     <t xml:space="preserve">25.5468521118164</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4541263580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.740629196167</t>
+    <t xml:space="preserve">26.4541244506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7406311035156</t>
   </si>
   <si>
     <t xml:space="preserve">27.0748901367188</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1703929901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6506748199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3219661712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8922023773193</t>
+    <t xml:space="preserve">27.1703910827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6506767272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.321964263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.892204284668</t>
   </si>
   <si>
     <t xml:space="preserve">29.9877071380615</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1309604644775</t>
+    <t xml:space="preserve">30.1309585571289</t>
   </si>
   <si>
     <t xml:space="preserve">29.6534481048584</t>
@@ -2309,7 +2309,7 @@
     <t xml:space="preserve">29.0804386138916</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6984252929688</t>
+    <t xml:space="preserve">28.6984272003174</t>
   </si>
   <si>
     <t xml:space="preserve">28.9849338531494</t>
@@ -2318,49 +2318,49 @@
     <t xml:space="preserve">28.3641700744629</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8866577148438</t>
+    <t xml:space="preserve">27.8866596221924</t>
   </si>
   <si>
     <t xml:space="preserve">29.2714385986328</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8389072418213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6479034423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6029262542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4119186401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3669414520264</t>
+    <t xml:space="preserve">27.8389053344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6479015350342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6029243469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4119205474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.366943359375</t>
   </si>
   <si>
     <t xml:space="preserve">29.4146938323975</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0354595184326</t>
+    <t xml:space="preserve">30.0354614257812</t>
   </si>
   <si>
     <t xml:space="preserve">29.748950958252</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7039756774902</t>
+    <t xml:space="preserve">30.7039775848389</t>
   </si>
   <si>
     <t xml:space="preserve">30.2742156982422</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7012023925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5579490661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.796703338623</t>
+    <t xml:space="preserve">29.7012004852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5579471588135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7967014312744</t>
   </si>
   <si>
     <t xml:space="preserve">28.2209148406982</t>
@@ -2375,10 +2375,10 @@
     <t xml:space="preserve">26.9480724334717</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5770225524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5930156707764</t>
+    <t xml:space="preserve">27.5770206451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.593017578125</t>
   </si>
   <si>
     <t xml:space="preserve">28.0124492645264</t>
@@ -2396,7 +2396,7 @@
     <t xml:space="preserve">28.0608291625977</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3994960784912</t>
+    <t xml:space="preserve">28.3994941711426</t>
   </si>
   <si>
     <t xml:space="preserve">28.7381591796875</t>
@@ -2405,7 +2405,7 @@
     <t xml:space="preserve">29.1252059936523</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9800643920898</t>
+    <t xml:space="preserve">28.9800624847412</t>
   </si>
   <si>
     <t xml:space="preserve">27.7705459594727</t>
@@ -2447,19 +2447,19 @@
     <t xml:space="preserve">29.2219676971436</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0284423828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2543525695801</t>
+    <t xml:space="preserve">29.0284442901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2543544769287</t>
   </si>
   <si>
     <t xml:space="preserve">29.705774307251</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0444393157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.996057510376</t>
+    <t xml:space="preserve">30.0444374084473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9960594177246</t>
   </si>
   <si>
     <t xml:space="preserve">28.8349208831787</t>
@@ -2474,7 +2474,7 @@
     <t xml:space="preserve">28.2059707641602</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4962558746338</t>
+    <t xml:space="preserve">28.4962577819824</t>
   </si>
   <si>
     <t xml:space="preserve">27.0932140350342</t>
@@ -2483,7 +2483,7 @@
     <t xml:space="preserve">26.8513107299805</t>
   </si>
   <si>
-    <t xml:space="preserve">26.077220916748</t>
+    <t xml:space="preserve">26.0772190093994</t>
   </si>
   <si>
     <t xml:space="preserve">26.8996906280518</t>
@@ -2507,22 +2507,22 @@
     <t xml:space="preserve">25.3031272888184</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2547473907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1579856872559</t>
+    <t xml:space="preserve">25.2547454833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1579837799072</t>
   </si>
   <si>
     <t xml:space="preserve">24.9160804748535</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4966487884521</t>
+    <t xml:space="preserve">25.4966506958008</t>
   </si>
   <si>
     <t xml:space="preserve">25.3515071868896</t>
   </si>
   <si>
-    <t xml:space="preserve">25.061222076416</t>
+    <t xml:space="preserve">25.0612239837646</t>
   </si>
   <si>
     <t xml:space="preserve">24.7225570678711</t>
@@ -2531,7 +2531,7 @@
     <t xml:space="preserve">24.4806537628174</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6098022460938</t>
+    <t xml:space="preserve">23.6098003387451</t>
   </si>
   <si>
     <t xml:space="preserve">23.0292301177979</t>
@@ -2540,7 +2540,7 @@
     <t xml:space="preserve">22.9324722290039</t>
   </si>
   <si>
-    <t xml:space="preserve">23.174373626709</t>
+    <t xml:space="preserve">23.1743755340576</t>
   </si>
   <si>
     <t xml:space="preserve">22.5938053131104</t>
@@ -2552,7 +2552,7 @@
     <t xml:space="preserve">21.6745719909668</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9164733886719</t>
+    <t xml:space="preserve">21.9164752960205</t>
   </si>
   <si>
     <t xml:space="preserve">21.5294284820557</t>
@@ -2564,16 +2564,16 @@
     <t xml:space="preserve">21.0940017700195</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4650535583496</t>
+    <t xml:space="preserve">20.465051651001</t>
   </si>
   <si>
     <t xml:space="preserve">20.2231483459473</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4166717529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9004802703857</t>
+    <t xml:space="preserve">20.4166736602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9004783630371</t>
   </si>
   <si>
     <t xml:space="preserve">20.8037185668945</t>
@@ -2582,22 +2582,22 @@
     <t xml:space="preserve">20.6101951599121</t>
   </si>
   <si>
-    <t xml:space="preserve">20.658576965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7069549560547</t>
+    <t xml:space="preserve">20.6585750579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7069568634033</t>
   </si>
   <si>
     <t xml:space="preserve">20.7553386688232</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3359050750732</t>
+    <t xml:space="preserve">21.3359069824219</t>
   </si>
   <si>
     <t xml:space="preserve">21.0456218719482</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4490566253662</t>
+    <t xml:space="preserve">19.4490585327148</t>
   </si>
   <si>
     <t xml:space="preserve">19.8361034393311</t>
@@ -2606,7 +2606,7 @@
     <t xml:space="preserve">19.2361812591553</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8878421783447</t>
+    <t xml:space="preserve">18.8878402709961</t>
   </si>
   <si>
     <t xml:space="preserve">18.6362609863281</t>
@@ -2630,13 +2630,13 @@
     <t xml:space="preserve">17.049373626709</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0300216674805</t>
+    <t xml:space="preserve">17.0300197601318</t>
   </si>
   <si>
     <t xml:space="preserve">16.8752021789551</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3266258239746</t>
+    <t xml:space="preserve">18.326623916626</t>
   </si>
   <si>
     <t xml:space="preserve">18.7717266082764</t>
@@ -2648,13 +2648,13 @@
     <t xml:space="preserve">18.5782051086426</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4233875274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1331005096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4974384307861</t>
+    <t xml:space="preserve">18.4233856201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1331024169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4974365234375</t>
   </si>
   <si>
     <t xml:space="preserve">20.1263866424561</t>
@@ -2663,7 +2663,7 @@
     <t xml:space="preserve">19.9328651428223</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3199119567871</t>
+    <t xml:space="preserve">20.3199100494385</t>
   </si>
   <si>
     <t xml:space="preserve">19.6425800323486</t>
@@ -2678,10 +2678,10 @@
     <t xml:space="preserve">19.1781253814697</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0233058929443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1974773406982</t>
+    <t xml:space="preserve">19.023307800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1974792480469</t>
   </si>
   <si>
     <t xml:space="preserve">18.9071941375732</t>
@@ -2690,7 +2690,7 @@
     <t xml:space="preserve">19.8844833374023</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4006767272949</t>
+    <t xml:space="preserve">19.4006748199463</t>
   </si>
   <si>
     <t xml:space="preserve">19.7877235412598</t>
@@ -2708,7 +2708,7 @@
     <t xml:space="preserve">22.0132369995117</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8357086181641</t>
+    <t xml:space="preserve">22.8357105255127</t>
   </si>
   <si>
     <t xml:space="preserve">22.1583786010742</t>
@@ -2720,19 +2720,19 @@
     <t xml:space="preserve">22.3519020080566</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7229537963867</t>
+    <t xml:space="preserve">21.7229518890381</t>
   </si>
   <si>
     <t xml:space="preserve">21.5778102874756</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4326686859131</t>
+    <t xml:space="preserve">21.4326667785645</t>
   </si>
   <si>
     <t xml:space="preserve">22.061616897583</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4970455169678</t>
+    <t xml:space="preserve">22.4970436096191</t>
   </si>
   <si>
     <t xml:space="preserve">22.2551403045654</t>
@@ -2744,7 +2744,7 @@
     <t xml:space="preserve">21.6261901855469</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7713317871094</t>
+    <t xml:space="preserve">21.771333694458</t>
   </si>
   <si>
     <t xml:space="preserve">22.3035202026367</t>
@@ -2753,10 +2753,10 @@
     <t xml:space="preserve">22.8840885162354</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7873287200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9648571014404</t>
+    <t xml:space="preserve">22.7873268127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9648551940918</t>
   </si>
   <si>
     <t xml:space="preserve">20.948860168457</t>
@@ -2771,7 +2771,7 @@
     <t xml:space="preserve">20.1747703552246</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5134334564209</t>
+    <t xml:space="preserve">20.5134353637695</t>
   </si>
   <si>
     <t xml:space="preserve">20.0296268463135</t>
@@ -2780,13 +2780,13 @@
     <t xml:space="preserve">22.9808521270752</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1259937286377</t>
+    <t xml:space="preserve">23.1259918212891</t>
   </si>
   <si>
     <t xml:space="preserve">21.3842868804932</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8520965576172</t>
+    <t xml:space="preserve">20.8520984649658</t>
   </si>
   <si>
     <t xml:space="preserve">20.5618133544922</t>
@@ -13921,7 +13921,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G392" t="s">
-        <v>164</v>
+        <v>203</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -13947,7 +13947,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G393" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -13973,7 +13973,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G394" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -13999,7 +13999,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G395" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -14025,7 +14025,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G396" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -14051,7 +14051,7 @@
         <v>13</v>
       </c>
       <c r="G397" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -14077,7 +14077,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G398" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -14103,7 +14103,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G399" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -14129,7 +14129,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G400" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -14155,7 +14155,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G401" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -14181,7 +14181,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G402" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -14207,7 +14207,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G403" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -14233,7 +14233,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G404" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -14259,7 +14259,7 @@
         <v>13</v>
       </c>
       <c r="G405" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -14285,7 +14285,7 @@
         <v>13</v>
       </c>
       <c r="G406" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -14311,7 +14311,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G407" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -14337,7 +14337,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G408" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -14363,7 +14363,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G409" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -14389,7 +14389,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G410" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -14415,7 +14415,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G411" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -14441,7 +14441,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G412" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -14467,7 +14467,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G413" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -14493,7 +14493,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G414" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -14519,7 +14519,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G415" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -14545,7 +14545,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G416" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -14571,7 +14571,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G417" t="s">
-        <v>164</v>
+        <v>203</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -14597,7 +14597,7 @@
         <v>13.25</v>
       </c>
       <c r="G418" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -14623,7 +14623,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G419" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -14649,7 +14649,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G420" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -14675,7 +14675,7 @@
         <v>13</v>
       </c>
       <c r="G421" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -14701,7 +14701,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G422" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -14727,7 +14727,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G423" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -14753,7 +14753,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G424" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -14779,7 +14779,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G425" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -14805,7 +14805,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G426" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -14831,7 +14831,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G427" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -14857,7 +14857,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G428" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -14883,7 +14883,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G429" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -14909,7 +14909,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G430" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -14935,7 +14935,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G431" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -14961,7 +14961,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G432" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -14987,7 +14987,7 @@
         <v>13.1700000762939</v>
       </c>
       <c r="G433" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -15013,7 +15013,7 @@
         <v>13</v>
       </c>
       <c r="G434" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -15039,7 +15039,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G435" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -15065,7 +15065,7 @@
         <v>12.7299995422363</v>
       </c>
       <c r="G436" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -15091,7 +15091,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G437" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -15117,7 +15117,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G438" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -15143,7 +15143,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G439" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -15169,7 +15169,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G440" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -15195,7 +15195,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G441" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -15221,7 +15221,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G442" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -15247,7 +15247,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G443" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -15273,7 +15273,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G444" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -15299,7 +15299,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G445" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -15325,7 +15325,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G446" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -15351,7 +15351,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G447" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -15377,7 +15377,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G448" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -15403,7 +15403,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G449" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -15429,7 +15429,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G450" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -15455,7 +15455,7 @@
         <v>11.25</v>
       </c>
       <c r="G451" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -15481,7 +15481,7 @@
         <v>11.1099996566772</v>
       </c>
       <c r="G452" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -15507,7 +15507,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G453" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -15533,7 +15533,7 @@
         <v>11.25</v>
       </c>
       <c r="G454" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -15559,7 +15559,7 @@
         <v>10.9099998474121</v>
       </c>
       <c r="G455" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -15585,7 +15585,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G456" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -15611,7 +15611,7 @@
         <v>10.75</v>
       </c>
       <c r="G457" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -15637,7 +15637,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G458" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -15663,7 +15663,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G459" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -15689,7 +15689,7 @@
         <v>10.9300003051758</v>
       </c>
       <c r="G460" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -15715,7 +15715,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G461" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -15741,7 +15741,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G462" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -15767,7 +15767,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G463" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -15793,7 +15793,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G464" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -15819,7 +15819,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G465" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -15845,7 +15845,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G466" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -15871,7 +15871,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G467" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -15897,7 +15897,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G468" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -15923,7 +15923,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G469" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -15949,7 +15949,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G470" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -15975,7 +15975,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G471" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -16001,7 +16001,7 @@
         <v>11.2299995422363</v>
       </c>
       <c r="G472" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -16027,7 +16027,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G473" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -16053,7 +16053,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G474" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -16079,7 +16079,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G475" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -16105,7 +16105,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G476" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -16131,7 +16131,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G477" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -16157,7 +16157,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G478" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -16183,7 +16183,7 @@
         <v>10.75</v>
       </c>
       <c r="G479" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -16209,7 +16209,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G480" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -16235,7 +16235,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G481" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -16261,7 +16261,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G482" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -16287,7 +16287,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G483" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -16313,7 +16313,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G484" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -16339,7 +16339,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G485" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -16365,7 +16365,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G486" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -16391,7 +16391,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G487" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -16417,7 +16417,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G488" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -16443,7 +16443,7 @@
         <v>11.5</v>
       </c>
       <c r="G489" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -16469,7 +16469,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G490" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -16495,7 +16495,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G491" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -16521,7 +16521,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G492" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -16547,7 +16547,7 @@
         <v>11.0699996948242</v>
       </c>
       <c r="G493" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -16573,7 +16573,7 @@
         <v>11.2299995422363</v>
       </c>
       <c r="G494" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -16599,7 +16599,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G495" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -16625,7 +16625,7 @@
         <v>10.9300003051758</v>
       </c>
       <c r="G496" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -16651,7 +16651,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G497" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -16677,7 +16677,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G498" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -16703,7 +16703,7 @@
         <v>11.25</v>
       </c>
       <c r="G499" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -16729,7 +16729,7 @@
         <v>11.1300001144409</v>
       </c>
       <c r="G500" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -16755,7 +16755,7 @@
         <v>11</v>
       </c>
       <c r="G501" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -16781,7 +16781,7 @@
         <v>11.0699996948242</v>
       </c>
       <c r="G502" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -16807,7 +16807,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G503" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -16833,7 +16833,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G504" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -16859,7 +16859,7 @@
         <v>11</v>
       </c>
       <c r="G505" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -16885,7 +16885,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G506" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -16911,7 +16911,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G507" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -16937,7 +16937,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G508" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -16963,7 +16963,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G509" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -16989,7 +16989,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G510" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -17015,7 +17015,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G511" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -17041,7 +17041,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G512" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -17067,7 +17067,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G513" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -17093,7 +17093,7 @@
         <v>10.75</v>
       </c>
       <c r="G514" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -17119,7 +17119,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G515" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -17145,7 +17145,7 @@
         <v>10.75</v>
       </c>
       <c r="G516" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -17171,7 +17171,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G517" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -17197,7 +17197,7 @@
         <v>11</v>
       </c>
       <c r="G518" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -17223,7 +17223,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G519" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -17249,7 +17249,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G520" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -17275,7 +17275,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G521" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -17301,7 +17301,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G522" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -17327,7 +17327,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G523" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -17353,7 +17353,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G524" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -17379,7 +17379,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G525" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -17405,7 +17405,7 @@
         <v>11.25</v>
       </c>
       <c r="G526" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -17431,7 +17431,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G527" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -17457,7 +17457,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G528" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -17483,7 +17483,7 @@
         <v>11.25</v>
       </c>
       <c r="G529" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -17509,7 +17509,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G530" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -17535,7 +17535,7 @@
         <v>11.5</v>
       </c>
       <c r="G531" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -17561,7 +17561,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G532" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -17587,7 +17587,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G533" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -17613,7 +17613,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G534" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -17639,7 +17639,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G535" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -17665,7 +17665,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G536" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -17691,7 +17691,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G537" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -17717,7 +17717,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G538" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -17743,7 +17743,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G539" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -17769,7 +17769,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G540" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -17795,7 +17795,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G541" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -17821,7 +17821,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G542" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -17847,7 +17847,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G543" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -17873,7 +17873,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G544" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -17899,7 +17899,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G545" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -17925,7 +17925,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G546" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -17951,7 +17951,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G547" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -17977,7 +17977,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G548" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -18003,7 +18003,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G549" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -18029,7 +18029,7 @@
         <v>10.5</v>
       </c>
       <c r="G550" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -18055,7 +18055,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G551" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -18081,7 +18081,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G552" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -18107,7 +18107,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G553" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -18133,7 +18133,7 @@
         <v>10.25</v>
       </c>
       <c r="G554" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -18159,7 +18159,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G555" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -18185,7 +18185,7 @@
         <v>10.25</v>
       </c>
       <c r="G556" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -18211,7 +18211,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G557" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -18237,7 +18237,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G558" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -18263,7 +18263,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G559" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -18289,7 +18289,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G560" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -18315,7 +18315,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G561" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -18341,7 +18341,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G562" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -18367,7 +18367,7 @@
         <v>10.5</v>
       </c>
       <c r="G563" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -18393,7 +18393,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G564" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -18419,7 +18419,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G565" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -18445,7 +18445,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G566" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -18471,7 +18471,7 @@
         <v>10.25</v>
       </c>
       <c r="G567" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -18497,7 +18497,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G568" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -18523,7 +18523,7 @@
         <v>10.25</v>
       </c>
       <c r="G569" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -18549,7 +18549,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G570" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -18575,7 +18575,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G571" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -18601,7 +18601,7 @@
         <v>10</v>
       </c>
       <c r="G572" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -18627,7 +18627,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G573" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -18653,7 +18653,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G574" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -18679,7 +18679,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G575" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -18705,7 +18705,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G576" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -18731,7 +18731,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G577" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -18757,7 +18757,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G578" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -18783,7 +18783,7 @@
         <v>10</v>
       </c>
       <c r="G579" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -18809,7 +18809,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G580" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -18835,7 +18835,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G581" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -18861,7 +18861,7 @@
         <v>10.25</v>
       </c>
       <c r="G582" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -18887,7 +18887,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G583" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -18913,7 +18913,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G584" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -18939,7 +18939,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G585" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -18965,7 +18965,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G586" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -18991,7 +18991,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G587" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -19017,7 +19017,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G588" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -19043,7 +19043,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G589" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -19069,7 +19069,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G590" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -19095,7 +19095,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G591" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -19121,7 +19121,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G592" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -19147,7 +19147,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G593" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -19173,7 +19173,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G594" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -19199,7 +19199,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G595" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -19225,7 +19225,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G596" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -19251,7 +19251,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G597" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -19277,7 +19277,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G598" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -19303,7 +19303,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G599" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -19329,7 +19329,7 @@
         <v>10.25</v>
       </c>
       <c r="G600" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -19355,7 +19355,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G601" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -19381,7 +19381,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G602" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -19407,7 +19407,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G603" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -19433,7 +19433,7 @@
         <v>10.25</v>
       </c>
       <c r="G604" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -19459,7 +19459,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G605" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -19485,7 +19485,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G606" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -19511,7 +19511,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G607" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -19537,7 +19537,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G608" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19563,7 +19563,7 @@
         <v>10.25</v>
       </c>
       <c r="G609" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19589,7 +19589,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G610" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19615,7 +19615,7 @@
         <v>10.25</v>
       </c>
       <c r="G611" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19641,7 +19641,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G612" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19667,7 +19667,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G613" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19693,7 +19693,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G614" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19719,7 +19719,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G615" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19745,7 +19745,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G616" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19771,7 +19771,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G617" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19797,7 +19797,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G618" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19823,7 +19823,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G619" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19849,7 +19849,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G620" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19875,7 +19875,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G621" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19901,7 +19901,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G622" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19927,7 +19927,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G623" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19953,7 +19953,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G624" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19979,7 +19979,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G625" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -20005,7 +20005,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G626" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -20031,7 +20031,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G627" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -20057,7 +20057,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G628" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -20083,7 +20083,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G629" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -20109,7 +20109,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G630" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -20135,7 +20135,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G631" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -20161,7 +20161,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G632" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -20187,7 +20187,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G633" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -20213,7 +20213,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G634" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -20239,7 +20239,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G635" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -20265,7 +20265,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G636" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -20291,7 +20291,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G637" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -20317,7 +20317,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G638" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -20343,7 +20343,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G639" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -20369,7 +20369,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G640" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -20395,7 +20395,7 @@
         <v>10</v>
       </c>
       <c r="G641" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -20421,7 +20421,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G642" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -20447,7 +20447,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G643" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -20473,7 +20473,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G644" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -20499,7 +20499,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G645" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -20525,7 +20525,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G646" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -20551,7 +20551,7 @@
         <v>10</v>
       </c>
       <c r="G647" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -20577,7 +20577,7 @@
         <v>10</v>
       </c>
       <c r="G648" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -20603,7 +20603,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G649" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -20629,7 +20629,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G650" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -20655,7 +20655,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G651" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -20681,7 +20681,7 @@
         <v>10</v>
       </c>
       <c r="G652" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -20707,7 +20707,7 @@
         <v>10</v>
       </c>
       <c r="G653" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -20733,7 +20733,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G654" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -20759,7 +20759,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G655" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -20785,7 +20785,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G656" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -20811,7 +20811,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G657" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -20837,7 +20837,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G658" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -20863,7 +20863,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G659" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -20889,7 +20889,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G660" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -20915,7 +20915,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G661" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -20941,7 +20941,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G662" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -20967,7 +20967,7 @@
         <v>10</v>
       </c>
       <c r="G663" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -20993,7 +20993,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G664" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -21019,7 +21019,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G665" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -21045,7 +21045,7 @@
         <v>10.25</v>
       </c>
       <c r="G666" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -21071,7 +21071,7 @@
         <v>10</v>
       </c>
       <c r="G667" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -21097,7 +21097,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G668" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -21123,7 +21123,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G669" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -21149,7 +21149,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G670" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -21175,7 +21175,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G671" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -21201,7 +21201,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G672" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -21227,7 +21227,7 @@
         <v>10</v>
       </c>
       <c r="G673" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -21253,7 +21253,7 @@
         <v>10</v>
       </c>
       <c r="G674" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -21279,7 +21279,7 @@
         <v>10</v>
       </c>
       <c r="G675" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -21305,7 +21305,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G676" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -21331,7 +21331,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G677" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -21357,7 +21357,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G678" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -21383,7 +21383,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G679" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -21409,7 +21409,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G680" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -21435,7 +21435,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G681" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -21461,7 +21461,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G682" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -21487,7 +21487,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G683" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -21513,7 +21513,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G684" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -21539,7 +21539,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G685" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -21565,7 +21565,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G686" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -21591,7 +21591,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G687" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -21617,7 +21617,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G688" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -21643,7 +21643,7 @@
         <v>10</v>
       </c>
       <c r="G689" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -21669,7 +21669,7 @@
         <v>10</v>
       </c>
       <c r="G690" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -21695,7 +21695,7 @@
         <v>10</v>
       </c>
       <c r="G691" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -21721,7 +21721,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G692" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -21747,7 +21747,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G693" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -21773,7 +21773,7 @@
         <v>10</v>
       </c>
       <c r="G694" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -21799,7 +21799,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G695" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -21825,7 +21825,7 @@
         <v>10</v>
       </c>
       <c r="G696" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -21851,7 +21851,7 @@
         <v>10</v>
       </c>
       <c r="G697" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -21877,7 +21877,7 @@
         <v>10.5</v>
       </c>
       <c r="G698" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -21903,7 +21903,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G699" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -21929,7 +21929,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G700" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -21955,7 +21955,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G701" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -21981,7 +21981,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G702" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -22007,7 +22007,7 @@
         <v>10.25</v>
       </c>
       <c r="G703" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -22033,7 +22033,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G704" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -22059,7 +22059,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G705" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -22085,7 +22085,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G706" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -22111,7 +22111,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G707" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -22137,7 +22137,7 @@
         <v>10</v>
       </c>
       <c r="G708" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -22163,7 +22163,7 @@
         <v>10</v>
       </c>
       <c r="G709" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -22189,7 +22189,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G710" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -22215,7 +22215,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G711" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -22241,7 +22241,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G712" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -22267,7 +22267,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G713" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -22293,7 +22293,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G714" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -22319,7 +22319,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G715" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -22345,7 +22345,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G716" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -22371,7 +22371,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G717" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -22397,7 +22397,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G718" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -22423,7 +22423,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G719" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -22449,7 +22449,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G720" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -22475,7 +22475,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G721" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -22501,7 +22501,7 @@
         <v>10</v>
       </c>
       <c r="G722" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -22527,7 +22527,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G723" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -22553,7 +22553,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G724" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -22579,7 +22579,7 @@
         <v>10</v>
       </c>
       <c r="G725" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -22605,7 +22605,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G726" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -22631,7 +22631,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G727" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -22657,7 +22657,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G728" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -22683,7 +22683,7 @@
         <v>10</v>
       </c>
       <c r="G729" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -22709,7 +22709,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G730" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -22735,7 +22735,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G731" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -22761,7 +22761,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G732" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -22787,7 +22787,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G733" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -22813,7 +22813,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G734" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -22839,7 +22839,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G735" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -22865,7 +22865,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G736" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -22891,7 +22891,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G737" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -22917,7 +22917,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G738" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -22943,7 +22943,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G739" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -22969,7 +22969,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G740" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -22995,7 +22995,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G741" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -23021,7 +23021,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G742" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -23047,7 +23047,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G743" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -23073,7 +23073,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G744" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -23099,7 +23099,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G745" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -23125,7 +23125,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G746" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -23151,7 +23151,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G747" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -23177,7 +23177,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G748" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -23203,7 +23203,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G749" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -23229,7 +23229,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G750" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -23255,7 +23255,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G751" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -23281,7 +23281,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G752" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -23307,7 +23307,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G753" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -23333,7 +23333,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G754" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -23359,7 +23359,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G755" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -23385,7 +23385,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G756" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -23411,7 +23411,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G757" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -23437,7 +23437,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G758" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -23463,7 +23463,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G759" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -23489,7 +23489,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G760" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -23515,7 +23515,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G761" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -23541,7 +23541,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G762" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -23567,7 +23567,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G763" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -23593,7 +23593,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G764" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -23619,7 +23619,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G765" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -23645,7 +23645,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G766" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -23671,7 +23671,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G767" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -23697,7 +23697,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G768" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -23723,7 +23723,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G769" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -23749,7 +23749,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G770" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -23775,7 +23775,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G771" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -23801,7 +23801,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G772" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -23827,7 +23827,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G773" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -23853,7 +23853,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G774" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -23879,7 +23879,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G775" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -23905,7 +23905,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G776" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -23931,7 +23931,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G777" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -23957,7 +23957,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G778" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -23983,7 +23983,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G779" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -24009,7 +24009,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G780" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -24035,7 +24035,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G781" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -24061,7 +24061,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G782" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -24087,7 +24087,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G783" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -24113,7 +24113,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G784" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -24139,7 +24139,7 @@
         <v>10</v>
       </c>
       <c r="G785" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -24165,7 +24165,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G786" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -24191,7 +24191,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G787" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -24217,7 +24217,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G788" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -24243,7 +24243,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G789" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -24269,7 +24269,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G790" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -24295,7 +24295,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G791" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -24321,7 +24321,7 @@
         <v>10</v>
       </c>
       <c r="G792" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -24347,7 +24347,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G793" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -24373,7 +24373,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G794" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -24399,7 +24399,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G795" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -24425,7 +24425,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G796" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -24451,7 +24451,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G797" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -24477,7 +24477,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G798" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -24503,7 +24503,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G799" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -24529,7 +24529,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G800" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -24555,7 +24555,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G801" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -24581,7 +24581,7 @@
         <v>10.25</v>
       </c>
       <c r="G802" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -24607,7 +24607,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G803" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -24633,7 +24633,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G804" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -24659,7 +24659,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G805" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -24685,7 +24685,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G806" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -24711,7 +24711,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G807" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -24737,7 +24737,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G808" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -24763,7 +24763,7 @@
         <v>10.5</v>
       </c>
       <c r="G809" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -24789,7 +24789,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G810" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -24815,7 +24815,7 @@
         <v>10</v>
       </c>
       <c r="G811" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -24841,7 +24841,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G812" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -24867,7 +24867,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G813" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -24893,7 +24893,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G814" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -24919,7 +24919,7 @@
         <v>10.5</v>
       </c>
       <c r="G815" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -24945,7 +24945,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G816" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -24971,7 +24971,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G817" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -24997,7 +24997,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G818" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -25023,7 +25023,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G819" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -25049,7 +25049,7 @@
         <v>11.25</v>
       </c>
       <c r="G820" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -25075,7 +25075,7 @@
         <v>11.5</v>
       </c>
       <c r="G821" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -25101,7 +25101,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G822" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -25127,7 +25127,7 @@
         <v>11.5</v>
       </c>
       <c r="G823" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -25153,7 +25153,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G824" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -25179,7 +25179,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G825" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -25205,7 +25205,7 @@
         <v>11.75</v>
       </c>
       <c r="G826" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -25231,7 +25231,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G827" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -25257,7 +25257,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G828" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -25283,7 +25283,7 @@
         <v>11.75</v>
       </c>
       <c r="G829" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -25309,7 +25309,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G830" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -25335,7 +25335,7 @@
         <v>11.75</v>
       </c>
       <c r="G831" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -25361,7 +25361,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G832" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -25387,7 +25387,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G833" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -25413,7 +25413,7 @@
         <v>11.75</v>
       </c>
       <c r="G834" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -25439,7 +25439,7 @@
         <v>11.75</v>
       </c>
       <c r="G835" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -25465,7 +25465,7 @@
         <v>11.75</v>
       </c>
       <c r="G836" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -25491,7 +25491,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G837" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -25517,7 +25517,7 @@
         <v>11.75</v>
       </c>
       <c r="G838" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -25543,7 +25543,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G839" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -25569,7 +25569,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G840" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -25595,7 +25595,7 @@
         <v>11.25</v>
       </c>
       <c r="G841" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -25621,7 +25621,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G842" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -25647,7 +25647,7 @@
         <v>11.5</v>
       </c>
       <c r="G843" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -25673,7 +25673,7 @@
         <v>11.5</v>
       </c>
       <c r="G844" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -25699,7 +25699,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G845" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -25725,7 +25725,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G846" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -25751,7 +25751,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G847" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -25777,7 +25777,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G848" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -25803,7 +25803,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G849" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -25829,7 +25829,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G850" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -25855,7 +25855,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G851" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -25881,7 +25881,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G852" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -25907,7 +25907,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G853" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -25933,7 +25933,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G854" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -25959,7 +25959,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G855" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -25985,7 +25985,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G856" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -26011,7 +26011,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G857" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -26037,7 +26037,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G858" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -26063,7 +26063,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G859" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -26089,7 +26089,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G860" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -26115,7 +26115,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G861" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -26141,7 +26141,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G862" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -26167,7 +26167,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G863" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -26193,7 +26193,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G864" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -26219,7 +26219,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G865" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -26245,7 +26245,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G866" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -26271,7 +26271,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G867" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -26297,7 +26297,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G868" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -26323,7 +26323,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G869" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -26349,7 +26349,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G870" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -26583,7 +26583,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G879" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -26687,7 +26687,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G883" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -26739,7 +26739,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G885" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -26869,7 +26869,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G890" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -26973,7 +26973,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G894" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -27025,7 +27025,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G896" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -27051,7 +27051,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G897" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -27311,7 +27311,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G907" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -27389,7 +27389,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G910" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -27415,7 +27415,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G911" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -27441,7 +27441,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G912" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -27545,7 +27545,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G916" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -27597,7 +27597,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G918" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -29443,7 +29443,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G989" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -29521,7 +29521,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G992" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -31393,7 +31393,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1064" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -32251,7 +32251,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1097" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -32303,7 +32303,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G1099" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -69049,7 +69049,7 @@
     </row>
     <row r="2513">
       <c r="A2513" s="1" t="n">
-        <v>45978.6909722222</v>
+        <v>45978.3333333333</v>
       </c>
       <c r="B2513" t="n">
         <v>7128</v>
@@ -69070,6 +69070,32 @@
         <v>1128</v>
       </c>
       <c r="H2513" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2514">
+      <c r="A2514" s="1" t="n">
+        <v>45979.6911805556</v>
+      </c>
+      <c r="B2514" t="n">
+        <v>9199</v>
+      </c>
+      <c r="C2514" t="n">
+        <v>37.2000007629395</v>
+      </c>
+      <c r="D2514" t="n">
+        <v>36.0999984741211</v>
+      </c>
+      <c r="E2514" t="n">
+        <v>36.25</v>
+      </c>
+      <c r="F2514" t="n">
+        <v>36.6500015258789</v>
+      </c>
+      <c r="G2514" t="s">
+        <v>1119</v>
+      </c>
+      <c r="H2514" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LUVE.MI.xlsx
+++ b/data/LUVE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1129" uniqueCount="1129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1130" uniqueCount="1130">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30043315887451</t>
+    <t xml:space="preserve">8.30043411254883</t>
   </si>
   <si>
     <t xml:space="preserve">LUVE.MI</t>
@@ -47,34 +47,34 @@
     <t xml:space="preserve">8.31703567504883</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28383159637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09292316436768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19667816162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07632160186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15102672576904</t>
+    <t xml:space="preserve">8.2838306427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09292221069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19667720794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07632064819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15102481842041</t>
   </si>
   <si>
     <t xml:space="preserve">8.17177677154541</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03896903991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08462238311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06802082061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96841621398926</t>
+    <t xml:space="preserve">8.03896999359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08462142944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06802177429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96841669082642</t>
   </si>
   <si>
     <t xml:space="preserve">8.01821804046631</t>
@@ -83,61 +83,61 @@
     <t xml:space="preserve">7.9974684715271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91861295700073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91446399688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91031265258789</t>
+    <t xml:space="preserve">7.91861343383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91446304321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91031122207642</t>
   </si>
   <si>
     <t xml:space="preserve">7.88541173934937</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87711238861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85221099853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64884996414185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71940326690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70280075073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69035196304321</t>
+    <t xml:space="preserve">7.87711143493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.852210521698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64884948730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71940279006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70280170440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69035291671753</t>
   </si>
   <si>
     <t xml:space="preserve">7.61979818344116</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55754470825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55339622497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.636399269104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76920652389526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80240678787231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93521356582642</t>
+    <t xml:space="preserve">7.55754423141479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55339479446411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63639831542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76920509338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80240774154663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93521499633789</t>
   </si>
   <si>
     <t xml:space="preserve">8.10122299194336</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05141925811768</t>
+    <t xml:space="preserve">8.05142021179199</t>
   </si>
   <si>
     <t xml:space="preserve">8.18422698974609</t>
@@ -149,19 +149,19 @@
     <t xml:space="preserve">8.00161743164062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96011543273926</t>
+    <t xml:space="preserve">7.96011590957642</t>
   </si>
   <si>
     <t xml:space="preserve">8.21742916107178</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35853576660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32533359527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29213333129883</t>
+    <t xml:space="preserve">8.35853672027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3253345489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29213237762451</t>
   </si>
   <si>
     <t xml:space="preserve">8.20082855224609</t>
@@ -176,16 +176,16 @@
     <t xml:space="preserve">8.36267375946045</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43045711517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15085315704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17627048492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20592784881592</t>
+    <t xml:space="preserve">8.43045616149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15085220336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17627143859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2059268951416</t>
   </si>
   <si>
     <t xml:space="preserve">8.13390827178955</t>
@@ -194,22 +194,22 @@
     <t xml:space="preserve">8.11696147918701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21863555908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21016120910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21440029144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20169067382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26099967956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09154224395752</t>
+    <t xml:space="preserve">8.21863460540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21016407012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21439838409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20169162750244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26100063323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09154415130615</t>
   </si>
   <si>
     <t xml:space="preserve">8.10848903656006</t>
@@ -218,64 +218,64 @@
     <t xml:space="preserve">8.04917907714844</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96445083618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92208766937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87972259521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83736038208008</t>
+    <t xml:space="preserve">7.9644513130188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92208671569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87972354888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83735847473145</t>
   </si>
   <si>
     <t xml:space="preserve">8.12543487548828</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93479633331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75262975692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71026849746704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93903207778931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81194067001343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79499483108521</t>
+    <t xml:space="preserve">7.9347972869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75263023376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71026706695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93903160095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81194114685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79499435424805</t>
   </si>
   <si>
     <t xml:space="preserve">7.62553882598877</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66790342330933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84583139419556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19321727752686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47282123565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51518535614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52365779876709</t>
+    <t xml:space="preserve">7.66790246963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84583234786987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19321823120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47281932830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51518440246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52365684509277</t>
   </si>
   <si>
     <t xml:space="preserve">8.59991264343262</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78631401062012</t>
+    <t xml:space="preserve">8.78631496429443</t>
   </si>
   <si>
     <t xml:space="preserve">8.71853256225586</t>
@@ -284,25 +284,25 @@
     <t xml:space="preserve">8.50671100616455</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54060363769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46858310699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46434688568115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55754852294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57449340820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81173324584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7270040512085</t>
+    <t xml:space="preserve">8.540602684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46858406066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46434783935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55754947662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57449531555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81173229217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72700595855713</t>
   </si>
   <si>
     <t xml:space="preserve">8.64227676391602</t>
@@ -311,31 +311,31 @@
     <t xml:space="preserve">8.89646053314209</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02355289459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09980773925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06591606140137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10828113555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27773857116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19300937652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18453598022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07439231872559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09133625030518</t>
+    <t xml:space="preserve">9.0235538482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09980964660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06591701507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10828304290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27773952484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1930103302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18453788757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07439041137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09133720397949</t>
   </si>
   <si>
     <t xml:space="preserve">9.30315494537354</t>
@@ -344,34 +344,34 @@
     <t xml:space="preserve">9.32010173797607</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1252269744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60817813873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4048318862915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48955821990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38788509368896</t>
+    <t xml:space="preserve">9.12522792816162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60817909240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40482997894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48955726623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38788414001465</t>
   </si>
   <si>
     <t xml:space="preserve">9.53192329406738</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48108577728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44719505310059</t>
+    <t xml:space="preserve">9.4810848236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44719314575195</t>
   </si>
   <si>
     <t xml:space="preserve">9.54039573669434</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57428646087646</t>
+    <t xml:space="preserve">9.57428741455078</t>
   </si>
   <si>
     <t xml:space="preserve">9.47261333465576</t>
@@ -380,28 +380,28 @@
     <t xml:space="preserve">9.41330337524414</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42177486419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51497745513916</t>
+    <t xml:space="preserve">9.42177677154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51497650146484</t>
   </si>
   <si>
     <t xml:space="preserve">9.56581401824951</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74374294281006</t>
+    <t xml:space="preserve">9.74374485015869</t>
   </si>
   <si>
     <t xml:space="preserve">10.065710067749</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2521133422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1334934234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99792766571045</t>
+    <t xml:space="preserve">10.2521123886108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1334943771362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99792861938477</t>
   </si>
   <si>
     <t xml:space="preserve">9.95556354522705</t>
@@ -410,82 +410,82 @@
     <t xml:space="preserve">9.98098278045654</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88778114318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91319751739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0148735046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1589107513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0402936935425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70137882232666</t>
+    <t xml:space="preserve">9.88778018951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91320037841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0148725509644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1589117050171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0402927398682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70137786865234</t>
   </si>
   <si>
     <t xml:space="preserve">9.73527050018311</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7098503112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0826568603516</t>
+    <t xml:space="preserve">9.70985126495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0826549530029</t>
   </si>
   <si>
     <t xml:space="preserve">9.8623628616333</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1250200271606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2944765090942</t>
+    <t xml:space="preserve">10.1250219345093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2944755554199</t>
   </si>
   <si>
     <t xml:space="preserve">10.4808778762817</t>
   </si>
   <si>
-    <t xml:space="preserve">10.531717300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5147695541382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8028450012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.912992477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8621549606323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.014666557312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0570316314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.277322769165</t>
+    <t xml:space="preserve">10.5317163467407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5147705078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.802845954895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9129915237427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8621559143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0146675109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0570306777954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.277325630188</t>
   </si>
   <si>
     <t xml:space="preserve">11.4383068084717</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6586027145386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5823459625244</t>
+    <t xml:space="preserve">11.6586008071899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5823450088501</t>
   </si>
   <si>
     <t xml:space="preserve">11.4806709289551</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5908174514771</t>
+    <t xml:space="preserve">11.5908193588257</t>
   </si>
   <si>
     <t xml:space="preserve">11.7009658813477</t>
@@ -494,7 +494,7 @@
     <t xml:space="preserve">11.7772207260132</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8111124038696</t>
+    <t xml:space="preserve">11.811110496521</t>
   </si>
   <si>
     <t xml:space="preserve">11.8365306854248</t>
@@ -503,16 +503,16 @@
     <t xml:space="preserve">11.6670742034912</t>
   </si>
   <si>
-    <t xml:space="preserve">11.599289894104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5230340957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6077632904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6263809204102</t>
+    <t xml:space="preserve">11.5992918014526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5230360031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6077651977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6263818740845</t>
   </si>
   <si>
     <t xml:space="preserve">11.7297267913818</t>
@@ -521,28 +521,28 @@
     <t xml:space="preserve">11.6952772140503</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6780548095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.798623085022</t>
+    <t xml:space="preserve">11.678053855896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7986240386963</t>
   </si>
   <si>
     <t xml:space="preserve">11.8847455978394</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9105825424194</t>
+    <t xml:space="preserve">11.9105806350708</t>
   </si>
   <si>
     <t xml:space="preserve">12.0656003952026</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3153524398804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3584127426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0569877624512</t>
+    <t xml:space="preserve">12.3153514862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3584136962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0569868087769</t>
   </si>
   <si>
     <t xml:space="preserve">12.1431093215942</t>
@@ -554,43 +554,43 @@
     <t xml:space="preserve">11.8416843414307</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7555618286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7125015258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8502979278564</t>
+    <t xml:space="preserve">11.7555627822876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7125034332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8502969741821</t>
   </si>
   <si>
     <t xml:space="preserve">11.9191942214966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.962254524231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0397644042969</t>
+    <t xml:space="preserve">11.9622554779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0397634506226</t>
   </si>
   <si>
     <t xml:space="preserve">12.0483751296997</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7900104522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0311517715454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9450302124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8158483505249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8933582305908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8761320114136</t>
+    <t xml:space="preserve">11.7900114059448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0311527252197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9450311660767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8158493041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8933572769165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8761329650879</t>
   </si>
   <si>
     <t xml:space="preserve">11.8244600296021</t>
@@ -599,22 +599,22 @@
     <t xml:space="preserve">11.8675203323364</t>
   </si>
   <si>
-    <t xml:space="preserve">11.901969909668</t>
+    <t xml:space="preserve">11.9019680023193</t>
   </si>
   <si>
     <t xml:space="preserve">11.9278059005737</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7211151123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6694412231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6349935531616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6091575622559</t>
+    <t xml:space="preserve">11.7211141586304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6694421768188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6349945068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6091566085815</t>
   </si>
   <si>
     <t xml:space="preserve">11.57470703125</t>
@@ -629,46 +629,46 @@
     <t xml:space="preserve">11.368016242981</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3594045639038</t>
+    <t xml:space="preserve">11.3594036102295</t>
   </si>
   <si>
     <t xml:space="preserve">11.2818956375122</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2302227020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1957740783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1871614456177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1096515655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0579786300659</t>
+    <t xml:space="preserve">11.2302236557007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1957750320435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.187162399292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1096534729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0579795837402</t>
   </si>
   <si>
     <t xml:space="preserve">11.1785497665405</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1268768310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9374084472656</t>
+    <t xml:space="preserve">11.126877784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9374103546143</t>
   </si>
   <si>
     <t xml:space="preserve">11.0665922164917</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0235328674316</t>
+    <t xml:space="preserve">11.023530960083</t>
   </si>
   <si>
     <t xml:space="preserve">11.0838174819946</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1354894638062</t>
+    <t xml:space="preserve">11.1354885101318</t>
   </si>
   <si>
     <t xml:space="preserve">11.2043867111206</t>
@@ -683,13 +683,13 @@
     <t xml:space="preserve">11.5402584075928</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4110765457153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2905082702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1613254547119</t>
+    <t xml:space="preserve">11.411078453064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2905073165894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1613264083862</t>
   </si>
   <si>
     <t xml:space="preserve">11.2646713256836</t>
@@ -704,46 +704,46 @@
     <t xml:space="preserve">11.4196910858154</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2216091156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2388353347778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3421802520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9546346664429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.96324634552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0063076019287</t>
+    <t xml:space="preserve">11.2216100692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2388343811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3421821594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9546337127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9632472991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.006308555603</t>
   </si>
   <si>
     <t xml:space="preserve">11.0924282073975</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74032497406006</t>
+    <t xml:space="preserve">9.74032402038574</t>
   </si>
   <si>
     <t xml:space="preserve">9.01690578460693</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21498203277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37861442565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49057102203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5077953338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.593918800354</t>
+    <t xml:space="preserve">9.2149829864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37861347198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49057197570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50779628753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59391689300537</t>
   </si>
   <si>
     <t xml:space="preserve">9.60252952575684</t>
@@ -752,61 +752,61 @@
     <t xml:space="preserve">9.6886510848999</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56808185577393</t>
+    <t xml:space="preserve">9.56808090209961</t>
   </si>
   <si>
     <t xml:space="preserve">9.39583873748779</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34416389465332</t>
+    <t xml:space="preserve">9.34416484832764</t>
   </si>
   <si>
     <t xml:space="preserve">9.25804424285889</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30110454559326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41306304931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28387928009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24081993103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12886238098145</t>
+    <t xml:space="preserve">9.30110549926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41306209564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28388118743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24082088470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12886333465576</t>
   </si>
   <si>
     <t xml:space="preserve">9.02551651000977</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20637035369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26665782928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69726371765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65420246124268</t>
+    <t xml:space="preserve">9.20637130737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26665496826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69726276397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65420341491699</t>
   </si>
   <si>
     <t xml:space="preserve">9.66281509399414</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64558887481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67142677307129</t>
+    <t xml:space="preserve">9.64558982849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67142581939697</t>
   </si>
   <si>
     <t xml:space="preserve">9.75754833221436</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71448802947998</t>
+    <t xml:space="preserve">9.71448707580566</t>
   </si>
   <si>
     <t xml:space="preserve">9.09441566467285</t>
@@ -815,52 +815,52 @@
     <t xml:space="preserve">8.93939590454102</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14608764648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12024974822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83505725860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73171138763428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90395355224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77477169036865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5336332321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49918270111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57669258117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58530426025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47334671020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4302864074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54224586486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1719217300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23220825195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55947017669678</t>
+    <t xml:space="preserve">9.14608573913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12024879455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83505821228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73171234130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90395450592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77477264404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53363227844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49918460845947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57669353485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58530521392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47334766387939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43028736114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54224491119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17192268371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23220729827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55946826934814</t>
   </si>
   <si>
     <t xml:space="preserve">9.51640796661377</t>
@@ -869,37 +869,37 @@
     <t xml:space="preserve">9.86089324951172</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95662021636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91355800628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08580112457275</t>
+    <t xml:space="preserve">8.95661926269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91355895996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08580303192139</t>
   </si>
   <si>
     <t xml:space="preserve">9.04273986816406</t>
   </si>
   <si>
-    <t xml:space="preserve">8.999680519104</t>
+    <t xml:space="preserve">8.99967956542969</t>
   </si>
   <si>
     <t xml:space="preserve">8.82743740081787</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69825553894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87049674987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78437614440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7413158416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61213397979736</t>
+    <t xml:space="preserve">8.69825649261475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87049961090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7843770980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74131488800049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61213493347168</t>
   </si>
   <si>
     <t xml:space="preserve">8.59490871429443</t>
@@ -911,10 +911,10 @@
     <t xml:space="preserve">8.45711612701416</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06314373016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10714054107666</t>
+    <t xml:space="preserve">9.06314468383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10714244842529</t>
   </si>
   <si>
     <t xml:space="preserve">9.01914882659912</t>
@@ -923,13 +923,13 @@
     <t xml:space="preserve">8.97515296936035</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93115711212158</t>
+    <t xml:space="preserve">8.93115615844727</t>
   </si>
   <si>
     <t xml:space="preserve">8.88716220855713</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84316539764404</t>
+    <t xml:space="preserve">8.84316635131836</t>
   </si>
   <si>
     <t xml:space="preserve">8.76397323608398</t>
@@ -941,22 +941,22 @@
     <t xml:space="preserve">8.71117782592773</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62318706512451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58798885345459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6583833694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60558795928955</t>
+    <t xml:space="preserve">8.6231861114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58798980712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65838241577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60558700561523</t>
   </si>
   <si>
     <t xml:space="preserve">8.7287769317627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69357967376709</t>
+    <t xml:space="preserve">8.69357872009277</t>
   </si>
   <si>
     <t xml:space="preserve">8.74637413024902</t>
@@ -968,43 +968,43 @@
     <t xml:space="preserve">8.44720363616943</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27121925354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32401371002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.288818359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78157138824463</t>
+    <t xml:space="preserve">8.27122116088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32401561737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28881740570068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.781569480896</t>
   </si>
   <si>
     <t xml:space="preserve">8.64078426361084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79916858673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67598152160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23912811279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37111473083496</t>
+    <t xml:space="preserve">8.79916954040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67598056793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23912906646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37111568450928</t>
   </si>
   <si>
     <t xml:space="preserve">9.32711982727051</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19513320922852</t>
+    <t xml:space="preserve">9.19513130187988</t>
   </si>
   <si>
     <t xml:space="preserve">9.15113639831543</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46480083465576</t>
+    <t xml:space="preserve">8.46479988098145</t>
   </si>
   <si>
     <t xml:space="preserve">8.41200637817383</t>
@@ -1016,31 +1016,31 @@
     <t xml:space="preserve">8.34161281585693</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23602294921875</t>
+    <t xml:space="preserve">8.23602199554443</t>
   </si>
   <si>
     <t xml:space="preserve">8.30641460418701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13043308258057</t>
+    <t xml:space="preserve">8.13043212890625</t>
   </si>
   <si>
     <t xml:space="preserve">8.18322849273682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16562843322754</t>
+    <t xml:space="preserve">8.16562938690186</t>
   </si>
   <si>
     <t xml:space="preserve">8.21842479705811</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25362110137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37681102752686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51759719848633</t>
+    <t xml:space="preserve">8.25362014770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37681007385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5175952911377</t>
   </si>
   <si>
     <t xml:space="preserve">9.28312397003174</t>
@@ -1052,64 +1052,64 @@
     <t xml:space="preserve">9.63509082794189</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59109497070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89906692504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.119044303894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1630420684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2070379257202</t>
+    <t xml:space="preserve">9.59109401702881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8990650177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1190452575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1630401611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2070369720459</t>
   </si>
   <si>
     <t xml:space="preserve">10.3390245437622</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2950277328491</t>
+    <t xml:space="preserve">10.2950296401978</t>
   </si>
   <si>
     <t xml:space="preserve">10.383020401001</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2510318756104</t>
+    <t xml:space="preserve">10.2510328292847</t>
   </si>
   <si>
     <t xml:space="preserve">10.4270153045654</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0750494003296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5150079727173</t>
+    <t xml:space="preserve">10.0750484466553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.515007019043</t>
   </si>
   <si>
     <t xml:space="preserve">10.6498155593872</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4700717926025</t>
+    <t xml:space="preserve">10.4700708389282</t>
   </si>
   <si>
     <t xml:space="preserve">10.694751739502</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6048793792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3802013397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2453927993774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0656471252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4251365661621</t>
+    <t xml:space="preserve">10.6048812866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3802003860474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2453918457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0656490325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4251356124878</t>
   </si>
   <si>
     <t xml:space="preserve">10.3352632522583</t>
@@ -1124,52 +1124,52 @@
     <t xml:space="preserve">9.97577667236328</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1105842590332</t>
+    <t xml:space="preserve">10.1105833053589</t>
   </si>
   <si>
     <t xml:space="preserve">9.93084049224854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88590526580811</t>
+    <t xml:space="preserve">9.88590431213379</t>
   </si>
   <si>
     <t xml:space="preserve">10.1555204391479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0207118988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75109672546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70616245269775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3466739654541</t>
+    <t xml:space="preserve">10.020712852478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75109767913818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70616149902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34667205810547</t>
   </si>
   <si>
     <t xml:space="preserve">9.30173778533936</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39161014556885</t>
+    <t xml:space="preserve">9.39160823822021</t>
   </si>
   <si>
     <t xml:space="preserve">9.48148155212402</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61628913879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52641773223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43654537200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12199401855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0321216583252</t>
+    <t xml:space="preserve">9.61628818511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52641868591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43654632568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12199306488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03212261199951</t>
   </si>
   <si>
     <t xml:space="preserve">9.16692924499512</t>
@@ -1181,10 +1181,10 @@
     <t xml:space="preserve">9.25680160522461</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98718547821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57135200500488</t>
+    <t xml:space="preserve">8.98718643188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5713529586792</t>
   </si>
   <si>
     <t xml:space="preserve">9.66122531890869</t>
@@ -1196,64 +1196,64 @@
     <t xml:space="preserve">10.9643669128418</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4586629867554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5035982131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2339820861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1441106796265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9194316864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8744945526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0093021392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2789192199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4137258529663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5485353469849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6833419799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7732133865356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9080200195312</t>
+    <t xml:space="preserve">11.4586620330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5035972595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.233983039856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1441097259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9194307327271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8744964599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0093030929565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2789182662964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.413724899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5485343933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6833429336548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7732152938843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9080219268799</t>
   </si>
   <si>
     <t xml:space="preserve">12.132700920105</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9978942871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8181505203247</t>
+    <t xml:space="preserve">11.9978933334351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8181495666504</t>
   </si>
   <si>
     <t xml:space="preserve">11.593469619751</t>
   </si>
   <si>
-    <t xml:space="preserve">12.312445640564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5820608139038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9415464401245</t>
+    <t xml:space="preserve">12.3124446868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5820598602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9415493011475</t>
   </si>
   <si>
     <t xml:space="preserve">12.8067398071289</t>
@@ -1274,22 +1274,22 @@
     <t xml:space="preserve">12.2675085067749</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4023160934448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6269969940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6719312667847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.896614074707</t>
+    <t xml:space="preserve">12.4023170471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6269960403442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.671932220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8966131210327</t>
   </si>
   <si>
     <t xml:space="preserve">11.7282781600952</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7846240997314</t>
+    <t xml:space="preserve">10.7846231460571</t>
   </si>
   <si>
     <t xml:space="preserve">10.559944152832</t>
@@ -1298,22 +1298,22 @@
     <t xml:space="preserve">8.89731407165527</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98062086105347</t>
+    <t xml:space="preserve">7.98062133789062</t>
   </si>
   <si>
     <t xml:space="preserve">7.81885147094727</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53126287460327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89074993133545</t>
+    <t xml:space="preserve">7.53126239776611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89074850082397</t>
   </si>
   <si>
     <t xml:space="preserve">8.53782653808594</t>
   </si>
   <si>
-    <t xml:space="preserve">7.962646484375</t>
+    <t xml:space="preserve">7.96264600753784</t>
   </si>
   <si>
     <t xml:space="preserve">8.44795513153076</t>
@@ -1322,7 +1322,7 @@
     <t xml:space="preserve">8.6097240447998</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66364765167236</t>
+    <t xml:space="preserve">8.66364860534668</t>
   </si>
   <si>
     <t xml:space="preserve">8.86136531829834</t>
@@ -1331,16 +1331,16 @@
     <t xml:space="preserve">9.21186637878418</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93849086761475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80045413970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89247798919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66242027282715</t>
+    <t xml:space="preserve">9.93848991394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80045509338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89247894287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66242122650146</t>
   </si>
   <si>
     <t xml:space="preserve">9.7084321975708</t>
@@ -1349,19 +1349,19 @@
     <t xml:space="preserve">9.84646606445312</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1225347518921</t>
+    <t xml:space="preserve">10.1225357055664</t>
   </si>
   <si>
     <t xml:space="preserve">9.75444412231445</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3986043930054</t>
+    <t xml:space="preserve">10.3986053466797</t>
   </si>
   <si>
     <t xml:space="preserve">10.3065814971924</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7206859588623</t>
+    <t xml:space="preserve">10.720685005188</t>
   </si>
   <si>
     <t xml:space="preserve">10.5826501846313</t>
@@ -1370,19 +1370,19 @@
     <t xml:space="preserve">10.8587207794189</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6746740341187</t>
+    <t xml:space="preserve">10.6746730804443</t>
   </si>
   <si>
     <t xml:space="preserve">10.9967546463013</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6286611557007</t>
+    <t xml:space="preserve">10.6286630630493</t>
   </si>
   <si>
     <t xml:space="preserve">10.7666959762573</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4906282424927</t>
+    <t xml:space="preserve">10.4906272888184</t>
   </si>
   <si>
     <t xml:space="preserve">11.1347894668579</t>
@@ -1394,16 +1394,16 @@
     <t xml:space="preserve">11.5028820037842</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1807994842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0427675247192</t>
+    <t xml:space="preserve">11.1808004379272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0427665710449</t>
   </si>
   <si>
     <t xml:space="preserve">11.2728242874146</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9507427215576</t>
+    <t xml:space="preserve">10.9507436752319</t>
   </si>
   <si>
     <t xml:space="preserve">11.0887775421143</t>
@@ -1418,43 +1418,43 @@
     <t xml:space="preserve">11.4108581542969</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4568700790405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2268114089966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3648471832275</t>
+    <t xml:space="preserve">11.4568691253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2268123626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3648462295532</t>
   </si>
   <si>
     <t xml:space="preserve">11.5488929748535</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5949048995972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6869268417358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9629974365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7789506912231</t>
+    <t xml:space="preserve">11.5949039459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6869258880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9629983901978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7789497375488</t>
   </si>
   <si>
     <t xml:space="preserve">12.0090084075928</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1010303497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7329387664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8249635696411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0550193786621</t>
+    <t xml:space="preserve">12.1010313034058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7329397201538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8249626159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0550212860107</t>
   </si>
   <si>
     <t xml:space="preserve">11.8709726333618</t>
@@ -1466,55 +1466,55 @@
     <t xml:space="preserve">11.6409158706665</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1470422744751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6991815567017</t>
+    <t xml:space="preserve">12.1470432281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6991806030273</t>
   </si>
   <si>
     <t xml:space="preserve">12.7912034988403</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0672740936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8832273483276</t>
+    <t xml:space="preserve">13.0672731399536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8832263946533</t>
   </si>
   <si>
     <t xml:space="preserve">12.929238319397</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2053079605103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2513189315796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1132831573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1592960357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3893547058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2973308563232</t>
+    <t xml:space="preserve">13.2053089141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2513198852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1132850646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1592969894409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3893537521362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2973299026489</t>
   </si>
   <si>
     <t xml:space="preserve">12.9752502441406</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7114334106445</t>
+    <t xml:space="preserve">13.7114343643188</t>
   </si>
   <si>
     <t xml:space="preserve">13.4353656768799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.51513671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.377100944519</t>
+    <t xml:space="preserve">12.5151357650757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3770999908447</t>
   </si>
   <si>
     <t xml:space="preserve">12.837215423584</t>
@@ -1523,25 +1523,25 @@
     <t xml:space="preserve">12.7451934814453</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6531686782837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3433427810669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6194124221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8494701385498</t>
+    <t xml:space="preserve">12.653169631958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3433437347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6194114685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8494691848755</t>
   </si>
   <si>
     <t xml:space="preserve">13.9414920806885</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1715507507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3555965423584</t>
+    <t xml:space="preserve">14.1715488433838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3555974960327</t>
   </si>
   <si>
     <t xml:space="preserve">14.1255388259888</t>
@@ -1550,67 +1550,67 @@
     <t xml:space="preserve">14.4936304092407</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7236890792847</t>
+    <t xml:space="preserve">14.7236881256104</t>
   </si>
   <si>
     <t xml:space="preserve">14.6776762008667</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8157110214233</t>
+    <t xml:space="preserve">14.8157119750977</t>
   </si>
   <si>
     <t xml:space="preserve">14.861722946167</t>
   </si>
   <si>
-    <t xml:space="preserve">15.045768737793</t>
+    <t xml:space="preserve">15.0457696914673</t>
   </si>
   <si>
     <t xml:space="preserve">14.5396423339844</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6316652297974</t>
+    <t xml:space="preserve">14.631664276123</t>
   </si>
   <si>
     <t xml:space="preserve">14.4476194381714</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2635726928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9875040054321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3095855712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6654224395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8034582138062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5733995437622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7574462890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.95374584198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0335140228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4269781112671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3801383972168</t>
+    <t xml:space="preserve">14.2635736465454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9875030517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3095846176147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6654243469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8034572601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5734004974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7574453353882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9537448883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0335149765015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4269771575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3801374435425</t>
   </si>
   <si>
     <t xml:space="preserve">14.473819732666</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7080230712891</t>
+    <t xml:space="preserve">14.7080240249634</t>
   </si>
   <si>
     <t xml:space="preserve">14.8485460281372</t>
@@ -1619,16 +1619,16 @@
     <t xml:space="preserve">15.0359086990356</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0827493667603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8953866958618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9422264099121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1764326095581</t>
+    <t xml:space="preserve">15.0827503204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8953857421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9422273635864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1764316558838</t>
   </si>
   <si>
     <t xml:space="preserve">15.1295909881592</t>
@@ -1640,40 +1640,40 @@
     <t xml:space="preserve">14.6611814498901</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3169555664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7548627853394</t>
+    <t xml:space="preserve">15.3169546127319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7548637390137</t>
   </si>
   <si>
     <t xml:space="preserve">14.8017053604126</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2232723236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5043153762817</t>
+    <t xml:space="preserve">15.2232713699341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5043172836304</t>
   </si>
   <si>
     <t xml:space="preserve">16.0664081573486</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6916818618774</t>
+    <t xml:space="preserve">15.6916799545288</t>
   </si>
   <si>
     <t xml:space="preserve">15.7385215759277</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9727249145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9258852005005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.785364151001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1132469177246</t>
+    <t xml:space="preserve">15.9727230072021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9258861541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7853622436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1132488250732</t>
   </si>
   <si>
     <t xml:space="preserve">15.8322019577026</t>
@@ -1682,7 +1682,7 @@
     <t xml:space="preserve">16.5348167419434</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8627033233643</t>
+    <t xml:space="preserve">16.8627014160156</t>
   </si>
   <si>
     <t xml:space="preserve">17.1437454223633</t>
@@ -1691,49 +1691,49 @@
     <t xml:space="preserve">16.581657409668</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2069282531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2842693328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7995166778564</t>
+    <t xml:space="preserve">16.2069301605225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2842712402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7995185852051</t>
   </si>
   <si>
     <t xml:space="preserve">17.4716320037842</t>
   </si>
   <si>
-    <t xml:space="preserve">16.815860748291</t>
+    <t xml:space="preserve">16.8158626556396</t>
   </si>
   <si>
     <t xml:space="preserve">16.6284980773926</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0969047546387</t>
+    <t xml:space="preserve">17.0969066619873</t>
   </si>
   <si>
     <t xml:space="preserve">17.5184745788574</t>
   </si>
   <si>
-    <t xml:space="preserve">17.612154006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0337238311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5489730834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7363338470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9237003326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7668323516846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5794696807861</t>
+    <t xml:space="preserve">17.6121559143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0337219238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5489711761475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7363357543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.923698425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7668342590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5794677734375</t>
   </si>
   <si>
     <t xml:space="preserve">19.2047443389893</t>
@@ -1742,13 +1742,13 @@
     <t xml:space="preserve">19.1110610961914</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6731510162354</t>
+    <t xml:space="preserve">19.673152923584</t>
   </si>
   <si>
     <t xml:space="preserve">19.2984237670898</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4857883453369</t>
+    <t xml:space="preserve">19.4857864379883</t>
   </si>
   <si>
     <t xml:space="preserve">19.8605175018311</t>
@@ -1757,49 +1757,49 @@
     <t xml:space="preserve">20.3289241790771</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9846935272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.265739440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0783748626709</t>
+    <t xml:space="preserve">20.9846954345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2657413482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0783767700195</t>
   </si>
   <si>
     <t xml:space="preserve">21.453104019165</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7973346710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8278312683105</t>
+    <t xml:space="preserve">20.7973327636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8278293609619</t>
   </si>
   <si>
     <t xml:space="preserve">22.1088771820068</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7341499328613</t>
+    <t xml:space="preserve">21.7341480255127</t>
   </si>
   <si>
     <t xml:space="preserve">22.015193939209</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2962379455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4836044311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6404666900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5467853546143</t>
+    <t xml:space="preserve">22.2962398529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4836025238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6404685974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5467834472656</t>
   </si>
   <si>
     <t xml:space="preserve">20.2352428436279</t>
   </si>
   <si>
-    <t xml:space="preserve">18.314769744873</t>
+    <t xml:space="preserve">18.3147678375244</t>
   </si>
   <si>
     <t xml:space="preserve">19.0173797607422</t>
@@ -1820,19 +1820,19 @@
     <t xml:space="preserve">21.1720600128174</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7036514282227</t>
+    <t xml:space="preserve">20.703649520874</t>
   </si>
   <si>
     <t xml:space="preserve">21.3594207763672</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5162887573242</t>
+    <t xml:space="preserve">20.5162868499756</t>
   </si>
   <si>
     <t xml:space="preserve">20.0478782653809</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6709651947021</t>
+    <t xml:space="preserve">22.6709671020508</t>
   </si>
   <si>
     <t xml:space="preserve">22.2025585174561</t>
@@ -1841,19 +1841,19 @@
     <t xml:space="preserve">22.3899211883545</t>
   </si>
   <si>
-    <t xml:space="preserve">19.954195022583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4226036071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8910121917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3921070098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8300189971924</t>
+    <t xml:space="preserve">19.9541969299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4226055145264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8910140991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3921089172363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8300170898438</t>
   </si>
   <si>
     <t xml:space="preserve">18.361608505249</t>
@@ -1862,22 +1862,22 @@
     <t xml:space="preserve">16.9563846588135</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6589984893799</t>
+    <t xml:space="preserve">17.6589965820312</t>
   </si>
   <si>
     <t xml:space="preserve">17.7526779174805</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3779525756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8931999206543</t>
+    <t xml:space="preserve">17.3779487609863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8932018280029</t>
   </si>
   <si>
     <t xml:space="preserve">17.9400405883789</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2679271697998</t>
+    <t xml:space="preserve">18.2679252624512</t>
   </si>
   <si>
     <t xml:space="preserve">18.8768577575684</t>
@@ -1886,13 +1886,13 @@
     <t xml:space="preserve">18.6426544189453</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3241348266602</t>
+    <t xml:space="preserve">18.3241367340088</t>
   </si>
   <si>
     <t xml:space="preserve">18.2117176055908</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2304534912109</t>
+    <t xml:space="preserve">18.2304515838623</t>
   </si>
   <si>
     <t xml:space="preserve">18.4552898406982</t>
@@ -1904,31 +1904,31 @@
     <t xml:space="preserve">18.1180362701416</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9705410003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2820816040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0947189331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1884002685547</t>
+    <t xml:space="preserve">18.9705390930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2820835113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0947208404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1883983612061</t>
   </si>
   <si>
     <t xml:space="preserve">20.1415615081787</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4927635192871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.555944442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1999568939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8847961425781</t>
+    <t xml:space="preserve">18.4927616119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5559463500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1999549865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8847980499268</t>
   </si>
   <si>
     <t xml:space="preserve">17.7634181976318</t>
@@ -1940,13 +1940,13 @@
     <t xml:space="preserve">18.9285449981689</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4319324493408</t>
+    <t xml:space="preserve">18.4319343566895</t>
   </si>
   <si>
     <t xml:space="preserve">18.6038379669189</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1004486083984</t>
+    <t xml:space="preserve">19.1004505157471</t>
   </si>
   <si>
     <t xml:space="preserve">18.9858474731445</t>
@@ -1955,7 +1955,7 @@
     <t xml:space="preserve">19.1482009887695</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9094467163086</t>
+    <t xml:space="preserve">18.90944480896</t>
   </si>
   <si>
     <t xml:space="preserve">18.9476470947266</t>
@@ -1964,16 +1964,16 @@
     <t xml:space="preserve">20.0077228546143</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0554714202881</t>
+    <t xml:space="preserve">20.0554733276367</t>
   </si>
   <si>
     <t xml:space="preserve">20.5329856872559</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9149932861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1509742736816</t>
+    <t xml:space="preserve">20.9149913787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1509761810303</t>
   </si>
   <si>
     <t xml:space="preserve">20.4374809265137</t>
@@ -1997,7 +1997,7 @@
     <t xml:space="preserve">19.2914562225342</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3392086029053</t>
+    <t xml:space="preserve">19.339204788208</t>
   </si>
   <si>
     <t xml:space="preserve">18.813943862915</t>
@@ -2006,28 +2006,28 @@
     <t xml:space="preserve">18.6993408203125</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3869552612305</t>
+    <t xml:space="preserve">19.3869571685791</t>
   </si>
   <si>
     <t xml:space="preserve">18.852144241333</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0813503265381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.240930557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7757434844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9599704742432</t>
+    <t xml:space="preserve">19.0813484191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2409324645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7757415771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9599685668945</t>
   </si>
   <si>
     <t xml:space="preserve">20.4852333068848</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1059970855713</t>
+    <t xml:space="preserve">21.1059989929199</t>
   </si>
   <si>
     <t xml:space="preserve">21.8700160980225</t>
@@ -2039,16 +2039,16 @@
     <t xml:space="preserve">21.1537494659424</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7745113372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.679012298584</t>
+    <t xml:space="preserve">21.7745132446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6790103912354</t>
   </si>
   <si>
     <t xml:space="preserve">21.9177684783936</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2970008850098</t>
+    <t xml:space="preserve">21.2970027923584</t>
   </si>
   <si>
     <t xml:space="preserve">21.7267627716064</t>
@@ -2063,16 +2063,16 @@
     <t xml:space="preserve">20.1032238006592</t>
   </si>
   <si>
-    <t xml:space="preserve">19.62571144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8644695281982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2492523193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9205417633057</t>
+    <t xml:space="preserve">19.6257133483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8644676208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2492504119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.920539855957</t>
   </si>
   <si>
     <t xml:space="preserve">22.4430294036865</t>
@@ -2081,22 +2081,22 @@
     <t xml:space="preserve">22.1565227508545</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0610198974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.347526550293</t>
+    <t xml:space="preserve">22.0610218048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3475284576416</t>
   </si>
   <si>
     <t xml:space="preserve">21.0582466125488</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3897304534912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2942295074463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1987266540527</t>
+    <t xml:space="preserve">20.3897323608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2942276000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1987247467041</t>
   </si>
   <si>
     <t xml:space="preserve">20.8194904327393</t>
@@ -2111,7 +2111,7 @@
     <t xml:space="preserve">18.833044052124</t>
   </si>
   <si>
-    <t xml:space="preserve">19.482458114624</t>
+    <t xml:space="preserve">19.4824600219727</t>
   </si>
   <si>
     <t xml:space="preserve">19.7212142944336</t>
@@ -2120,7 +2120,7 @@
     <t xml:space="preserve">19.8167171478271</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2464790344238</t>
+    <t xml:space="preserve">20.2464771270752</t>
   </si>
   <si>
     <t xml:space="preserve">20.6762371063232</t>
@@ -2132,10 +2132,10 @@
     <t xml:space="preserve">21.4402561187744</t>
   </si>
   <si>
-    <t xml:space="preserve">22.634033203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2070484161377</t>
+    <t xml:space="preserve">22.6340351104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2070465087891</t>
   </si>
   <si>
     <t xml:space="preserve">22.7295341491699</t>
@@ -2144,10 +2144,10 @@
     <t xml:space="preserve">22.5862827301025</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8727912902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5385341644287</t>
+    <t xml:space="preserve">22.8727893829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5385322570801</t>
   </si>
   <si>
     <t xml:space="preserve">22.6817855834961</t>
@@ -2156,10 +2156,10 @@
     <t xml:space="preserve">23.0160427093506</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3025493621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4485759735107</t>
+    <t xml:space="preserve">23.3025512695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4485778808594</t>
   </si>
   <si>
     <t xml:space="preserve">23.7323112487793</t>
@@ -2171,13 +2171,13 @@
     <t xml:space="preserve">24.2098217010498</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0665683746338</t>
+    <t xml:space="preserve">24.0665664672852</t>
   </si>
   <si>
     <t xml:space="preserve">24.1143188476562</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4008255004883</t>
+    <t xml:space="preserve">24.4008235931396</t>
   </si>
   <si>
     <t xml:space="preserve">25.3080959320068</t>
@@ -2192,22 +2192,22 @@
     <t xml:space="preserve">25.0693416595459</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5440807342529</t>
+    <t xml:space="preserve">24.5440788269043</t>
   </si>
   <si>
     <t xml:space="preserve">24.9260883331299</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3558483123779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4035987854004</t>
+    <t xml:space="preserve">25.3558464050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.403600692749</t>
   </si>
   <si>
     <t xml:space="preserve">25.8333587646484</t>
   </si>
   <si>
-    <t xml:space="preserve">26.883882522583</t>
+    <t xml:space="preserve">26.8838844299316</t>
   </si>
   <si>
     <t xml:space="preserve">26.7883815765381</t>
@@ -2219,7 +2219,7 @@
     <t xml:space="preserve">24.5918292999268</t>
   </si>
   <si>
-    <t xml:space="preserve">24.830587387085</t>
+    <t xml:space="preserve">24.8305854797363</t>
   </si>
   <si>
     <t xml:space="preserve">25.2603454589844</t>
@@ -2228,55 +2228,55 @@
     <t xml:space="preserve">25.7378578186035</t>
   </si>
   <si>
-    <t xml:space="preserve">25.785608291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.072114944458</t>
+    <t xml:space="preserve">25.7856063842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0721130371094</t>
   </si>
   <si>
     <t xml:space="preserve">26.2631187438965</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4513511657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9288597106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5946025848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6901054382324</t>
+    <t xml:space="preserve">25.4513492584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.928861618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5946044921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6901073455811</t>
   </si>
   <si>
     <t xml:space="preserve">25.5468521118164</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4541244506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7406311035156</t>
+    <t xml:space="preserve">26.4541263580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.740629196167</t>
   </si>
   <si>
     <t xml:space="preserve">27.0748901367188</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1703910827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6506767272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.321964263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.892204284668</t>
+    <t xml:space="preserve">27.1703929901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6506748199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3219661712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8922023773193</t>
   </si>
   <si>
     <t xml:space="preserve">29.9877071380615</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1309585571289</t>
+    <t xml:space="preserve">30.1309604644775</t>
   </si>
   <si>
     <t xml:space="preserve">29.6534481048584</t>
@@ -2309,7 +2309,7 @@
     <t xml:space="preserve">29.0804386138916</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6984272003174</t>
+    <t xml:space="preserve">28.6984252929688</t>
   </si>
   <si>
     <t xml:space="preserve">28.9849338531494</t>
@@ -2318,49 +2318,49 @@
     <t xml:space="preserve">28.3641700744629</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8866596221924</t>
+    <t xml:space="preserve">27.8866577148438</t>
   </si>
   <si>
     <t xml:space="preserve">29.2714385986328</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8389053344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6479015350342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6029243469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4119205474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.366943359375</t>
+    <t xml:space="preserve">27.8389072418213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6479034423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6029262542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4119186401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3669414520264</t>
   </si>
   <si>
     <t xml:space="preserve">29.4146938323975</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0354614257812</t>
+    <t xml:space="preserve">30.0354595184326</t>
   </si>
   <si>
     <t xml:space="preserve">29.748950958252</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7039775848389</t>
+    <t xml:space="preserve">30.7039756774902</t>
   </si>
   <si>
     <t xml:space="preserve">30.2742156982422</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7012004852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5579471588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7967014312744</t>
+    <t xml:space="preserve">29.7012023925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5579490661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.796703338623</t>
   </si>
   <si>
     <t xml:space="preserve">28.2209148406982</t>
@@ -2375,10 +2375,10 @@
     <t xml:space="preserve">26.9480724334717</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5770206451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.593017578125</t>
+    <t xml:space="preserve">27.5770225524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5930156707764</t>
   </si>
   <si>
     <t xml:space="preserve">28.0124492645264</t>
@@ -2396,7 +2396,7 @@
     <t xml:space="preserve">28.0608291625977</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3994941711426</t>
+    <t xml:space="preserve">28.3994960784912</t>
   </si>
   <si>
     <t xml:space="preserve">28.7381591796875</t>
@@ -2405,7 +2405,7 @@
     <t xml:space="preserve">29.1252059936523</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9800624847412</t>
+    <t xml:space="preserve">28.9800643920898</t>
   </si>
   <si>
     <t xml:space="preserve">27.7705459594727</t>
@@ -2447,19 +2447,19 @@
     <t xml:space="preserve">29.2219676971436</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0284442901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2543544769287</t>
+    <t xml:space="preserve">29.0284423828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2543525695801</t>
   </si>
   <si>
     <t xml:space="preserve">29.705774307251</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0444374084473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9960594177246</t>
+    <t xml:space="preserve">30.0444393157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.996057510376</t>
   </si>
   <si>
     <t xml:space="preserve">28.8349208831787</t>
@@ -2474,7 +2474,7 @@
     <t xml:space="preserve">28.2059707641602</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4962577819824</t>
+    <t xml:space="preserve">28.4962558746338</t>
   </si>
   <si>
     <t xml:space="preserve">27.0932140350342</t>
@@ -2483,7 +2483,7 @@
     <t xml:space="preserve">26.8513107299805</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0772190093994</t>
+    <t xml:space="preserve">26.077220916748</t>
   </si>
   <si>
     <t xml:space="preserve">26.8996906280518</t>
@@ -2507,22 +2507,22 @@
     <t xml:space="preserve">25.3031272888184</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2547454833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1579837799072</t>
+    <t xml:space="preserve">25.2547473907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1579856872559</t>
   </si>
   <si>
     <t xml:space="preserve">24.9160804748535</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4966506958008</t>
+    <t xml:space="preserve">25.4966487884521</t>
   </si>
   <si>
     <t xml:space="preserve">25.3515071868896</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0612239837646</t>
+    <t xml:space="preserve">25.061222076416</t>
   </si>
   <si>
     <t xml:space="preserve">24.7225570678711</t>
@@ -2531,7 +2531,7 @@
     <t xml:space="preserve">24.4806537628174</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6098003387451</t>
+    <t xml:space="preserve">23.6098022460938</t>
   </si>
   <si>
     <t xml:space="preserve">23.0292301177979</t>
@@ -2540,7 +2540,7 @@
     <t xml:space="preserve">22.9324722290039</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1743755340576</t>
+    <t xml:space="preserve">23.174373626709</t>
   </si>
   <si>
     <t xml:space="preserve">22.5938053131104</t>
@@ -2552,7 +2552,7 @@
     <t xml:space="preserve">21.6745719909668</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9164752960205</t>
+    <t xml:space="preserve">21.9164733886719</t>
   </si>
   <si>
     <t xml:space="preserve">21.5294284820557</t>
@@ -2564,16 +2564,16 @@
     <t xml:space="preserve">21.0940017700195</t>
   </si>
   <si>
-    <t xml:space="preserve">20.465051651001</t>
+    <t xml:space="preserve">20.4650535583496</t>
   </si>
   <si>
     <t xml:space="preserve">20.2231483459473</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4166736602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9004783630371</t>
+    <t xml:space="preserve">20.4166717529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9004802703857</t>
   </si>
   <si>
     <t xml:space="preserve">20.8037185668945</t>
@@ -2582,22 +2582,22 @@
     <t xml:space="preserve">20.6101951599121</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6585750579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7069568634033</t>
+    <t xml:space="preserve">20.658576965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7069549560547</t>
   </si>
   <si>
     <t xml:space="preserve">20.7553386688232</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3359069824219</t>
+    <t xml:space="preserve">21.3359050750732</t>
   </si>
   <si>
     <t xml:space="preserve">21.0456218719482</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4490585327148</t>
+    <t xml:space="preserve">19.4490566253662</t>
   </si>
   <si>
     <t xml:space="preserve">19.8361034393311</t>
@@ -2606,7 +2606,7 @@
     <t xml:space="preserve">19.2361812591553</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8878402709961</t>
+    <t xml:space="preserve">18.8878421783447</t>
   </si>
   <si>
     <t xml:space="preserve">18.6362609863281</t>
@@ -2630,13 +2630,13 @@
     <t xml:space="preserve">17.049373626709</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0300197601318</t>
+    <t xml:space="preserve">17.0300216674805</t>
   </si>
   <si>
     <t xml:space="preserve">16.8752021789551</t>
   </si>
   <si>
-    <t xml:space="preserve">18.326623916626</t>
+    <t xml:space="preserve">18.3266258239746</t>
   </si>
   <si>
     <t xml:space="preserve">18.7717266082764</t>
@@ -2648,13 +2648,13 @@
     <t xml:space="preserve">18.5782051086426</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4233856201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1331024169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4974365234375</t>
+    <t xml:space="preserve">18.4233875274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1331005096436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4974384307861</t>
   </si>
   <si>
     <t xml:space="preserve">20.1263866424561</t>
@@ -2663,7 +2663,7 @@
     <t xml:space="preserve">19.9328651428223</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3199100494385</t>
+    <t xml:space="preserve">20.3199119567871</t>
   </si>
   <si>
     <t xml:space="preserve">19.6425800323486</t>
@@ -2678,10 +2678,10 @@
     <t xml:space="preserve">19.1781253814697</t>
   </si>
   <si>
-    <t xml:space="preserve">19.023307800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1974792480469</t>
+    <t xml:space="preserve">19.0233058929443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1974773406982</t>
   </si>
   <si>
     <t xml:space="preserve">18.9071941375732</t>
@@ -2690,7 +2690,7 @@
     <t xml:space="preserve">19.8844833374023</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4006748199463</t>
+    <t xml:space="preserve">19.4006767272949</t>
   </si>
   <si>
     <t xml:space="preserve">19.7877235412598</t>
@@ -2708,7 +2708,7 @@
     <t xml:space="preserve">22.0132369995117</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8357105255127</t>
+    <t xml:space="preserve">22.8357086181641</t>
   </si>
   <si>
     <t xml:space="preserve">22.1583786010742</t>
@@ -2720,19 +2720,19 @@
     <t xml:space="preserve">22.3519020080566</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7229518890381</t>
+    <t xml:space="preserve">21.7229537963867</t>
   </si>
   <si>
     <t xml:space="preserve">21.5778102874756</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4326667785645</t>
+    <t xml:space="preserve">21.4326686859131</t>
   </si>
   <si>
     <t xml:space="preserve">22.061616897583</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4970436096191</t>
+    <t xml:space="preserve">22.4970455169678</t>
   </si>
   <si>
     <t xml:space="preserve">22.2551403045654</t>
@@ -2744,7 +2744,7 @@
     <t xml:space="preserve">21.6261901855469</t>
   </si>
   <si>
-    <t xml:space="preserve">21.771333694458</t>
+    <t xml:space="preserve">21.7713317871094</t>
   </si>
   <si>
     <t xml:space="preserve">22.3035202026367</t>
@@ -2753,10 +2753,10 @@
     <t xml:space="preserve">22.8840885162354</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7873268127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9648551940918</t>
+    <t xml:space="preserve">22.7873287200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9648571014404</t>
   </si>
   <si>
     <t xml:space="preserve">20.948860168457</t>
@@ -2771,7 +2771,7 @@
     <t xml:space="preserve">20.1747703552246</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5134353637695</t>
+    <t xml:space="preserve">20.5134334564209</t>
   </si>
   <si>
     <t xml:space="preserve">20.0296268463135</t>
@@ -2780,13 +2780,13 @@
     <t xml:space="preserve">22.9808521270752</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1259918212891</t>
+    <t xml:space="preserve">23.1259937286377</t>
   </si>
   <si>
     <t xml:space="preserve">21.3842868804932</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8520984649658</t>
+    <t xml:space="preserve">20.8520965576172</t>
   </si>
   <si>
     <t xml:space="preserve">20.5618133544922</t>
@@ -3399,6 +3399,9 @@
   </si>
   <si>
     <t xml:space="preserve">36.5499992370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.4000015258789</t>
   </si>
 </sst>
 </file>
@@ -69075,7 +69078,7 @@
     </row>
     <row r="2514">
       <c r="A2514" s="1" t="n">
-        <v>45979.6911805556</v>
+        <v>45979.3333333333</v>
       </c>
       <c r="B2514" t="n">
         <v>9199</v>
@@ -69096,6 +69099,32 @@
         <v>1119</v>
       </c>
       <c r="H2514" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2515">
+      <c r="A2515" s="1" t="n">
+        <v>45980.6912268518</v>
+      </c>
+      <c r="B2515" t="n">
+        <v>15175</v>
+      </c>
+      <c r="C2515" t="n">
+        <v>37.7000007629395</v>
+      </c>
+      <c r="D2515" t="n">
+        <v>36.2999992370605</v>
+      </c>
+      <c r="E2515" t="n">
+        <v>37.5499992370605</v>
+      </c>
+      <c r="F2515" t="n">
+        <v>37.4000015258789</v>
+      </c>
+      <c r="G2515" t="s">
+        <v>1129</v>
+      </c>
+      <c r="H2515" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LUVE.MI.xlsx
+++ b/data/LUVE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1131" uniqueCount="1131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1132" uniqueCount="1132">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30043411254883</t>
+    <t xml:space="preserve">8.3004322052002</t>
   </si>
   <si>
     <t xml:space="preserve">LUVE.MI</t>
@@ -47,10 +47,10 @@
     <t xml:space="preserve">8.31703472137451</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2838306427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09292411804199</t>
+    <t xml:space="preserve">8.28383255004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09292125701904</t>
   </si>
   <si>
     <t xml:space="preserve">8.19667720794678</t>
@@ -59,43 +59,43 @@
     <t xml:space="preserve">8.07632064819336</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15102481842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17177772521973</t>
+    <t xml:space="preserve">8.15102577209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17177677154541</t>
   </si>
   <si>
     <t xml:space="preserve">8.03896903991699</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08462429046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06802082061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96841621398926</t>
+    <t xml:space="preserve">8.08462333679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06802177429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96841764450073</t>
   </si>
   <si>
     <t xml:space="preserve">8.01821899414062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99746942520142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91861391067505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91446495056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91031360626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88541173934937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.877112865448</t>
+    <t xml:space="preserve">7.99746751785278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91861343383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91446208953857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91031312942505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88541221618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87711095809937</t>
   </si>
   <si>
     <t xml:space="preserve">7.85221004486084</t>
@@ -107,82 +107,82 @@
     <t xml:space="preserve">7.71940326690674</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7028021812439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69035243988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61979818344116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55754375457764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55339431762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63639783859253</t>
+    <t xml:space="preserve">7.70280170440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6903510093689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.619797706604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55754470825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55339574813843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63639736175537</t>
   </si>
   <si>
     <t xml:space="preserve">7.76920557022095</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80240678787231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93521451950073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10122299194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05142021179199</t>
+    <t xml:space="preserve">7.80240869522095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93521547317505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10122203826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05141925811768</t>
   </si>
   <si>
     <t xml:space="preserve">8.18422794342041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13442420959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00161838531494</t>
+    <t xml:space="preserve">8.13442516326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00161933898926</t>
   </si>
   <si>
     <t xml:space="preserve">7.96011638641357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21743011474609</t>
+    <t xml:space="preserve">8.21742820739746</t>
   </si>
   <si>
     <t xml:space="preserve">8.35853672027588</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32533359527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29213333129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20082664489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15932464599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30336475372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36267375946045</t>
+    <t xml:space="preserve">8.3253345489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29213428497314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20082855224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15932559967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30336380004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36267185211182</t>
   </si>
   <si>
     <t xml:space="preserve">8.43045616149902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15085315704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17626953125</t>
+    <t xml:space="preserve">8.15085220336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17627143859863</t>
   </si>
   <si>
     <t xml:space="preserve">8.2059268951416</t>
@@ -191,43 +191,43 @@
     <t xml:space="preserve">8.13390827178955</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1169605255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21863555908203</t>
+    <t xml:space="preserve">8.11696243286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21863460540771</t>
   </si>
   <si>
     <t xml:space="preserve">8.21016216278076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21440029144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20168972015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26099967956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09154510498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10848903656006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04917907714844</t>
+    <t xml:space="preserve">8.21439838409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20169067382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26099872589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09154415130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10848999023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04918003082275</t>
   </si>
   <si>
     <t xml:space="preserve">7.96445178985596</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92208766937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87972211837769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83735799789429</t>
+    <t xml:space="preserve">7.92208671569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.879723072052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83735847473145</t>
   </si>
   <si>
     <t xml:space="preserve">8.12543487548828</t>
@@ -239,151 +239,151 @@
     <t xml:space="preserve">7.75263166427612</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71026659011841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93903303146362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81194067001343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79499483108521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62553834915161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66790151596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84583330154419</t>
+    <t xml:space="preserve">7.71026802062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93903207778931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81194019317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79499387741089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62553930282593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66790294647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84583187103271</t>
   </si>
   <si>
     <t xml:space="preserve">8.19321823120117</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47282028198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5151834487915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52365779876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5999116897583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78631496429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71853256225586</t>
+    <t xml:space="preserve">8.47281932830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51518630981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52365875244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59991359710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78631401062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71853160858154</t>
   </si>
   <si>
     <t xml:space="preserve">8.50671100616455</t>
   </si>
   <si>
-    <t xml:space="preserve">8.540602684021</t>
+    <t xml:space="preserve">8.54060363769531</t>
   </si>
   <si>
     <t xml:space="preserve">8.46858406066895</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46434783935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55754852294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57449245452881</t>
+    <t xml:space="preserve">8.46434879302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55754947662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57449436187744</t>
   </si>
   <si>
     <t xml:space="preserve">8.81173324584961</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72700500488281</t>
+    <t xml:space="preserve">8.7270040512085</t>
   </si>
   <si>
     <t xml:space="preserve">8.64227771759033</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89646053314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02355289459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09980964660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06591606140137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10828113555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27773952484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1930103302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18453788757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07439231872559</t>
+    <t xml:space="preserve">8.89645957946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0235538482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09980869293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06591796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10828018188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27773857116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19300937652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18453598022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07438945770264</t>
   </si>
   <si>
     <t xml:space="preserve">9.09133625030518</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30315494537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32010269165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12522792816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60817909240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40482997894287</t>
+    <t xml:space="preserve">9.30315589904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32010173797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1252269744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60817718505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40483093261719</t>
   </si>
   <si>
     <t xml:space="preserve">9.48955917358398</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38788414001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53192234039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4810848236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44719409942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54039573669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57428741455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47261238098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41330337524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42177677154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51497840881348</t>
+    <t xml:space="preserve">9.38788509368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53192329406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48108577728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44719505310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5403938293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57428646087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47261428833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41330432891846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42177581787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51497745513916</t>
   </si>
   <si>
     <t xml:space="preserve">9.56581401824951</t>
@@ -392,40 +392,40 @@
     <t xml:space="preserve">9.74374294281006</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0657110214233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2521133422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1334934234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99792766571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95556259155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98098087310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88778209686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91319942474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.014874458313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1589107513428</t>
+    <t xml:space="preserve">10.0657091140747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2521114349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1334924697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99792671203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95556354522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98098182678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88778114318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91320037841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0148735046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1589117050171</t>
   </si>
   <si>
     <t xml:space="preserve">10.0402917861938</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70137786865234</t>
+    <t xml:space="preserve">9.70138072967529</t>
   </si>
   <si>
     <t xml:space="preserve">9.73527145385742</t>
@@ -434,7 +434,7 @@
     <t xml:space="preserve">9.70985221862793</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0826549530029</t>
+    <t xml:space="preserve">10.0826559066772</t>
   </si>
   <si>
     <t xml:space="preserve">9.8623628616333</t>
@@ -443,19 +443,19 @@
     <t xml:space="preserve">10.1250200271606</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2944774627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4808788299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5317163467407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5147705078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8028450012207</t>
+    <t xml:space="preserve">10.2944765090942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4808778762817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5317153930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5147695541382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.802845954895</t>
   </si>
   <si>
     <t xml:space="preserve">10.9129934310913</t>
@@ -464,7 +464,7 @@
     <t xml:space="preserve">10.8621559143066</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0146675109863</t>
+    <t xml:space="preserve">11.0146656036377</t>
   </si>
   <si>
     <t xml:space="preserve">11.0570306777954</t>
@@ -476,19 +476,19 @@
     <t xml:space="preserve">11.4383068084717</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6586008071899</t>
+    <t xml:space="preserve">11.6586017608643</t>
   </si>
   <si>
     <t xml:space="preserve">11.5823459625244</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4806728363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5908203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7009658813477</t>
+    <t xml:space="preserve">11.4806718826294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5908193588257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7009649276733</t>
   </si>
   <si>
     <t xml:space="preserve">11.7772197723389</t>
@@ -503,133 +503,133 @@
     <t xml:space="preserve">11.6670742034912</t>
   </si>
   <si>
-    <t xml:space="preserve">11.599289894104</t>
+    <t xml:space="preserve">11.5992908477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5230360031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6077642440796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6263809204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7297258377075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6952772140503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6780548095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7986249923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8847465515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9105825424194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0656003952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3153514862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3584146499634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0569877624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1431093215942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9967031478882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8416843414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7555618286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7125024795532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8502969741821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9191942214966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9622535705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0397624969482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0483751296997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7900114059448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0311527252197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9450302124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8158483505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8933572769165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8761329650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8244590759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8675222396851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9019689559937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.927806854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7211141586304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6694421768188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6349935531616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6091556549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.57470703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5316476821899</t>
   </si>
   <si>
     <t xml:space="preserve">11.5230350494385</t>
   </si>
   <si>
-    <t xml:space="preserve">11.607762336731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6263799667358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7297267913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6952772140503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.678053855896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7986240386963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8847455978394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9105815887451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0656003952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3153533935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3584127426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0569887161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1431093215942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9967031478882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.841685295105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7555627822876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7125034332275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8502969741821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9191932678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9622554779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0397624969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.048376083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7900114059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0311517715454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9450311660767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8158483505249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8933582305908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8761329650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8244590759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8675193786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.901969909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9278059005737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7211141586304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6694421768188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6349945068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6091566085815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.57470703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5316467285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5230340957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3680152893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3594026565552</t>
+    <t xml:space="preserve">11.3680171966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3594045639038</t>
   </si>
   <si>
     <t xml:space="preserve">11.2818965911865</t>
@@ -638,70 +638,70 @@
     <t xml:space="preserve">11.2302227020264</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1957750320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.187162399292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1096515655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0579795837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1785507202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.126877784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9374094009399</t>
+    <t xml:space="preserve">11.1957731246948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1871633529663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1096525192261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0579805374146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1785497665405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1268768310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9374103546143</t>
   </si>
   <si>
     <t xml:space="preserve">11.066593170166</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0235328674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0838165283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1354913711548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2043867111206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3163452148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.454137802124</t>
+    <t xml:space="preserve">11.0235319137573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.083815574646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1354885101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2043857574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3163433074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4541387557983</t>
   </si>
   <si>
     <t xml:space="preserve">11.5402593612671</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4110765457153</t>
+    <t xml:space="preserve">11.411078453064</t>
   </si>
   <si>
     <t xml:space="preserve">11.2905082702637</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1613254547119</t>
+    <t xml:space="preserve">11.1613264083862</t>
   </si>
   <si>
     <t xml:space="preserve">11.2646713256836</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1527147293091</t>
+    <t xml:space="preserve">11.1527137756348</t>
   </si>
   <si>
     <t xml:space="preserve">11.0407562255859</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4196891784668</t>
+    <t xml:space="preserve">11.4196910858154</t>
   </si>
   <si>
     <t xml:space="preserve">11.2216110229492</t>
@@ -710,19 +710,19 @@
     <t xml:space="preserve">11.2388353347778</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3421812057495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9546337127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9632472991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0063076019287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0924301147461</t>
+    <t xml:space="preserve">11.3421802520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9546346664429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.96324634552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.006308555603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0924291610718</t>
   </si>
   <si>
     <t xml:space="preserve">9.74032402038574</t>
@@ -731,7 +731,7 @@
     <t xml:space="preserve">9.01690483093262</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21498203277588</t>
+    <t xml:space="preserve">9.21498394012451</t>
   </si>
   <si>
     <t xml:space="preserve">9.37861442565918</t>
@@ -746,25 +746,25 @@
     <t xml:space="preserve">9.593918800354</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60252857208252</t>
+    <t xml:space="preserve">9.60252952575684</t>
   </si>
   <si>
     <t xml:space="preserve">9.6886510848999</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56808090209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39583778381348</t>
+    <t xml:space="preserve">9.56808185577393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39583873748779</t>
   </si>
   <si>
     <t xml:space="preserve">9.34416484832764</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25804424285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30110645294189</t>
+    <t xml:space="preserve">9.25804233551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30110454559326</t>
   </si>
   <si>
     <t xml:space="preserve">9.41306304931641</t>
@@ -773,58 +773,58 @@
     <t xml:space="preserve">9.28388023376465</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24081897735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12886333465576</t>
+    <t xml:space="preserve">9.24081993103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12886238098145</t>
   </si>
   <si>
     <t xml:space="preserve">9.02551651000977</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20637035369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26665592193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69726371765137</t>
+    <t xml:space="preserve">9.20637130737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26665687561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69726181030273</t>
   </si>
   <si>
     <t xml:space="preserve">9.65420246124268</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66281414031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64558982849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67142772674561</t>
+    <t xml:space="preserve">9.66281509399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64559078216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67142677307129</t>
   </si>
   <si>
     <t xml:space="preserve">9.75754737854004</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71448802947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09441566467285</t>
+    <t xml:space="preserve">9.71448707580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09441471099854</t>
   </si>
   <si>
     <t xml:space="preserve">8.9393949508667</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14608669281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1202507019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83505821228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73171138763428</t>
+    <t xml:space="preserve">9.14608764648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12024974822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83505535125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73171043395996</t>
   </si>
   <si>
     <t xml:space="preserve">9.90395355224609</t>
@@ -833,40 +833,40 @@
     <t xml:space="preserve">9.77477264404297</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53363227844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49918270111084</t>
+    <t xml:space="preserve">9.5336332321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49918365478516</t>
   </si>
   <si>
     <t xml:space="preserve">9.57669353485107</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58530521392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47334766387939</t>
+    <t xml:space="preserve">9.58530426025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47334671020508</t>
   </si>
   <si>
     <t xml:space="preserve">9.43028736114502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54224395751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1719217300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23220729827881</t>
+    <t xml:space="preserve">9.54224491119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17192363739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23220825195312</t>
   </si>
   <si>
     <t xml:space="preserve">9.55946922302246</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51640701293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86089324951172</t>
+    <t xml:space="preserve">9.51640796661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86089420318604</t>
   </si>
   <si>
     <t xml:space="preserve">8.95662021636963</t>
@@ -875,16 +875,16 @@
     <t xml:space="preserve">8.91355895996094</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08580112457275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04274082183838</t>
+    <t xml:space="preserve">9.08580207824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04273986816406</t>
   </si>
   <si>
     <t xml:space="preserve">8.99967956542969</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82743740081787</t>
+    <t xml:space="preserve">8.82743644714355</t>
   </si>
   <si>
     <t xml:space="preserve">8.69825649261475</t>
@@ -893,49 +893,49 @@
     <t xml:space="preserve">8.87049770355225</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78437805175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7413158416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61213397979736</t>
+    <t xml:space="preserve">8.7843770980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74131679534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61213207244873</t>
   </si>
   <si>
     <t xml:space="preserve">8.59490966796875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65519523620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45711421966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06314373016357</t>
+    <t xml:space="preserve">8.65519618988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45711612701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06314468383789</t>
   </si>
   <si>
     <t xml:space="preserve">9.10714054107666</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0191478729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97515392303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93115711212158</t>
+    <t xml:space="preserve">9.01914691925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97515296936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9311580657959</t>
   </si>
   <si>
     <t xml:space="preserve">8.88716220855713</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84316539764404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76397323608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48239994049072</t>
+    <t xml:space="preserve">8.84316635131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76397228240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48240089416504</t>
   </si>
   <si>
     <t xml:space="preserve">8.71117782592773</t>
@@ -947,10 +947,10 @@
     <t xml:space="preserve">8.58798885345459</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6583833694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60558700561523</t>
+    <t xml:space="preserve">8.65838241577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60558795928955</t>
   </si>
   <si>
     <t xml:space="preserve">8.72877597808838</t>
@@ -962,7 +962,7 @@
     <t xml:space="preserve">8.74637413024902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53519439697266</t>
+    <t xml:space="preserve">8.53519344329834</t>
   </si>
   <si>
     <t xml:space="preserve">8.44720363616943</t>
@@ -980,58 +980,58 @@
     <t xml:space="preserve">8.78157138824463</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64078330993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79916954040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67598247528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23912811279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37111473083496</t>
+    <t xml:space="preserve">8.64078426361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79916763305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67598152160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23912715911865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37111663818359</t>
   </si>
   <si>
     <t xml:space="preserve">9.32711982727051</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19513130187988</t>
+    <t xml:space="preserve">9.1951322555542</t>
   </si>
   <si>
     <t xml:space="preserve">9.15113639831543</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46480178833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41200637817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49999904632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34161186218262</t>
+    <t xml:space="preserve">8.46479988098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41200733184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49999809265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34161376953125</t>
   </si>
   <si>
     <t xml:space="preserve">8.23602199554443</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30641460418701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13043212890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18322849273682</t>
+    <t xml:space="preserve">8.30641555786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13043117523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1832275390625</t>
   </si>
   <si>
     <t xml:space="preserve">8.16562938690186</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21842384338379</t>
+    <t xml:space="preserve">8.21842479705811</t>
   </si>
   <si>
     <t xml:space="preserve">8.25362110137939</t>
@@ -1040,13 +1040,13 @@
     <t xml:space="preserve">8.37681007385254</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51759719848633</t>
+    <t xml:space="preserve">8.51759624481201</t>
   </si>
   <si>
     <t xml:space="preserve">9.28312397003174</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41511058807373</t>
+    <t xml:space="preserve">9.41511249542236</t>
   </si>
   <si>
     <t xml:space="preserve">9.63509082794189</t>
@@ -1055,43 +1055,43 @@
     <t xml:space="preserve">9.59109401702881</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89906597137451</t>
+    <t xml:space="preserve">9.8990650177002</t>
   </si>
   <si>
     <t xml:space="preserve">10.119044303894</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1630420684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2070388793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3390235900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2950277328491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.383020401001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.251030921936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4270153045654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0750484466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5150079727173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6498155593872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4700708389282</t>
+    <t xml:space="preserve">10.1630411148071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2070379257202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3390245437622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2950296401978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3830184936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2510328292847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4270162582397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0750494003296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5150089263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6498165130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4700717926025</t>
   </si>
   <si>
     <t xml:space="preserve">10.6947507858276</t>
@@ -1100,22 +1100,22 @@
     <t xml:space="preserve">10.6048793792725</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3802013397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2453927993774</t>
+    <t xml:space="preserve">10.380199432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2453918457031</t>
   </si>
   <si>
     <t xml:space="preserve">10.0656480789185</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4251375198364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3352632522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2903270721436</t>
+    <t xml:space="preserve">10.4251356124878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3352642059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2903280258179</t>
   </si>
   <si>
     <t xml:space="preserve">10.2004566192627</t>
@@ -1124,28 +1124,28 @@
     <t xml:space="preserve">9.97577667236328</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1105833053589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93083953857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88590526580811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1555204391479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0207118988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75109672546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70616245269775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3466739654541</t>
+    <t xml:space="preserve">10.1105842590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93084049224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88590431213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1555213928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0207138061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75109767913818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70616149902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34667205810547</t>
   </si>
   <si>
     <t xml:space="preserve">9.30173778533936</t>
@@ -1160,43 +1160,43 @@
     <t xml:space="preserve">9.61628913879395</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52641773223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43654537200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12199401855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0321216583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16693115234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07705783843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25680065155029</t>
+    <t xml:space="preserve">9.52641868591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43654441833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12199306488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03212261199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16692924499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07705879211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25680160522461</t>
   </si>
   <si>
     <t xml:space="preserve">8.98718643188477</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57135200500488</t>
+    <t xml:space="preserve">9.57135391235352</t>
   </si>
   <si>
     <t xml:space="preserve">9.66122531890869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7960319519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9643678665161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4586620330811</t>
+    <t xml:space="preserve">9.79603290557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9643669128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4586629867554</t>
   </si>
   <si>
     <t xml:space="preserve">11.5035991668701</t>
@@ -1208,7 +1208,7 @@
     <t xml:space="preserve">11.1441116333008</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9194316864014</t>
+    <t xml:space="preserve">10.9194297790527</t>
   </si>
   <si>
     <t xml:space="preserve">10.8744945526123</t>
@@ -1217,25 +1217,25 @@
     <t xml:space="preserve">11.0093030929565</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2789192199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4137258529663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5485353469849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6833429336548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.77321434021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9080209732056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1326999664307</t>
+    <t xml:space="preserve">11.2789182662964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4137268066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5485343933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6833410263062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7732133865356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9080219268799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1327018737793</t>
   </si>
   <si>
     <t xml:space="preserve">11.9978933334351</t>
@@ -1244,22 +1244,22 @@
     <t xml:space="preserve">11.8181495666504</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5934686660767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.312445640564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5820617675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9415473937988</t>
+    <t xml:space="preserve">11.5934705734253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3124437332153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5820608139038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9415483474731</t>
   </si>
   <si>
     <t xml:space="preserve">12.8067398071289</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7618045806885</t>
+    <t xml:space="preserve">12.7618036270142</t>
   </si>
   <si>
     <t xml:space="preserve">13.0763559341431</t>
@@ -1268,19 +1268,19 @@
     <t xml:space="preserve">12.4472532272339</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5371236801147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2675085067749</t>
+    <t xml:space="preserve">12.5371246337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2675075531006</t>
   </si>
   <si>
     <t xml:space="preserve">12.4023170471191</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6269969940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6719312667847</t>
+    <t xml:space="preserve">12.6269979476929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6719331741333</t>
   </si>
   <si>
     <t xml:space="preserve">12.8966131210327</t>
@@ -1289,7 +1289,7 @@
     <t xml:space="preserve">11.7282781600952</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7846240997314</t>
+    <t xml:space="preserve">10.7846231460571</t>
   </si>
   <si>
     <t xml:space="preserve">10.5599431991577</t>
@@ -1307,58 +1307,58 @@
     <t xml:space="preserve">7.53126192092896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89074897766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53782653808594</t>
+    <t xml:space="preserve">7.89074850082397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53782749176025</t>
   </si>
   <si>
     <t xml:space="preserve">7.962646484375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44795608520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60972309112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66364765167236</t>
+    <t xml:space="preserve">8.44795513153076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60972499847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66364860534668</t>
   </si>
   <si>
     <t xml:space="preserve">8.86136627197266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21186542510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93849086761475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80045413970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89247798919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66242027282715</t>
+    <t xml:space="preserve">9.21186637878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93848896026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80045604705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89247894287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66241931915283</t>
   </si>
   <si>
     <t xml:space="preserve">9.7084321975708</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84646606445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1225366592407</t>
+    <t xml:space="preserve">9.84646701812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1225357055664</t>
   </si>
   <si>
     <t xml:space="preserve">9.75444412231445</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3986034393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3065824508667</t>
+    <t xml:space="preserve">10.3986053466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3065814971924</t>
   </si>
   <si>
     <t xml:space="preserve">10.720685005188</t>
@@ -1370,16 +1370,16 @@
     <t xml:space="preserve">10.8587207794189</t>
   </si>
   <si>
-    <t xml:space="preserve">10.674674987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9967546463013</t>
+    <t xml:space="preserve">10.6746740341187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.996753692627</t>
   </si>
   <si>
     <t xml:space="preserve">10.628662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7666959762573</t>
+    <t xml:space="preserve">10.766697883606</t>
   </si>
   <si>
     <t xml:space="preserve">10.4906282424927</t>
@@ -1388,7 +1388,7 @@
     <t xml:space="preserve">11.1347894668579</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3188343048096</t>
+    <t xml:space="preserve">11.3188362121582</t>
   </si>
   <si>
     <t xml:space="preserve">11.5028810501099</t>
@@ -1397,13 +1397,13 @@
     <t xml:space="preserve">11.1807994842529</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0427675247192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2728242874146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9507427215576</t>
+    <t xml:space="preserve">11.0427656173706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2728233337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9507417678833</t>
   </si>
   <si>
     <t xml:space="preserve">11.0887775421143</t>
@@ -1415,28 +1415,28 @@
     <t xml:space="preserve">10.9047317504883</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4108581542969</t>
+    <t xml:space="preserve">11.4108591079712</t>
   </si>
   <si>
     <t xml:space="preserve">11.4568700790405</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2268123626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3648471832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5488929748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5949058532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6869268417358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9629974365234</t>
+    <t xml:space="preserve">11.2268114089966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3648481369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5488920211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5949048995972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6869277954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9629964828491</t>
   </si>
   <si>
     <t xml:space="preserve">11.7789516448975</t>
@@ -1445,19 +1445,19 @@
     <t xml:space="preserve">12.0090084075928</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1010303497314</t>
+    <t xml:space="preserve">12.1010313034058</t>
   </si>
   <si>
     <t xml:space="preserve">11.7329397201538</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8249635696411</t>
+    <t xml:space="preserve">11.8249626159668</t>
   </si>
   <si>
     <t xml:space="preserve">12.0550193786621</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8709726333618</t>
+    <t xml:space="preserve">11.8709735870361</t>
   </si>
   <si>
     <t xml:space="preserve">11.9169855117798</t>
@@ -1466,25 +1466,25 @@
     <t xml:space="preserve">11.6409158706665</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1470432281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.699182510376</t>
+    <t xml:space="preserve">12.1470422744751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6991815567017</t>
   </si>
   <si>
     <t xml:space="preserve">12.7912034988403</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0672740936279</t>
+    <t xml:space="preserve">13.0672731399536</t>
   </si>
   <si>
     <t xml:space="preserve">12.8832273483276</t>
   </si>
   <si>
-    <t xml:space="preserve">12.929238319397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2053079605103</t>
+    <t xml:space="preserve">12.9292402267456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2053089141846</t>
   </si>
   <si>
     <t xml:space="preserve">13.2513198852539</t>
@@ -1493,25 +1493,25 @@
     <t xml:space="preserve">13.1132841110229</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1592960357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3893547058105</t>
+    <t xml:space="preserve">13.1592969894409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3893537521362</t>
   </si>
   <si>
     <t xml:space="preserve">13.2973308563232</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9752492904663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7114334106445</t>
+    <t xml:space="preserve">12.9752511978149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7114343643188</t>
   </si>
   <si>
     <t xml:space="preserve">13.4353666305542</t>
   </si>
   <si>
-    <t xml:space="preserve">12.51513671875</t>
+    <t xml:space="preserve">12.5151348114014</t>
   </si>
   <si>
     <t xml:space="preserve">12.377100944519</t>
@@ -1526,10 +1526,10 @@
     <t xml:space="preserve">12.653169631958</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3433418273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6194124221802</t>
+    <t xml:space="preserve">13.3433427810669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6194114685059</t>
   </si>
   <si>
     <t xml:space="preserve">13.8494691848755</t>
@@ -1538,16 +1538,16 @@
     <t xml:space="preserve">13.9414920806885</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1715497970581</t>
+    <t xml:space="preserve">14.1715488433838</t>
   </si>
   <si>
     <t xml:space="preserve">14.3555965423584</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1255388259888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4936304092407</t>
+    <t xml:space="preserve">14.1255378723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.493631362915</t>
   </si>
   <si>
     <t xml:space="preserve">14.7236881256104</t>
@@ -1556,13 +1556,13 @@
     <t xml:space="preserve">14.6776762008667</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8157110214233</t>
+    <t xml:space="preserve">14.8157119750977</t>
   </si>
   <si>
     <t xml:space="preserve">14.861722946167</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0457706451416</t>
+    <t xml:space="preserve">15.0457696914673</t>
   </si>
   <si>
     <t xml:space="preserve">14.5396423339844</t>
@@ -1571,25 +1571,25 @@
     <t xml:space="preserve">14.6316652297974</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4476184844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2635726928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9875030517578</t>
+    <t xml:space="preserve">14.4476194381714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2635736465454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9875040054321</t>
   </si>
   <si>
     <t xml:space="preserve">14.3095855712891</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6654224395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8034582138062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5734004974365</t>
+    <t xml:space="preserve">13.6654233932495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8034572601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5733995437622</t>
   </si>
   <si>
     <t xml:space="preserve">13.7574462890625</t>
@@ -1598,13 +1598,13 @@
     <t xml:space="preserve">14.95374584198</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0335149765015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4269781112671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3801383972168</t>
+    <t xml:space="preserve">14.0335140228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4269771575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3801374435425</t>
   </si>
   <si>
     <t xml:space="preserve">14.473819732666</t>
@@ -1613,16 +1613,16 @@
     <t xml:space="preserve">14.7080230712891</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8485450744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0359086990356</t>
+    <t xml:space="preserve">14.8485460281372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.03590965271</t>
   </si>
   <si>
     <t xml:space="preserve">15.0827503204346</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8953866958618</t>
+    <t xml:space="preserve">14.8953857421875</t>
   </si>
   <si>
     <t xml:space="preserve">14.9422273635864</t>
@@ -1631,7 +1631,7 @@
     <t xml:space="preserve">15.1764326095581</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1295909881592</t>
+    <t xml:space="preserve">15.1295900344849</t>
   </si>
   <si>
     <t xml:space="preserve">14.989068031311</t>
@@ -1643,112 +1643,112 @@
     <t xml:space="preserve">15.3169555664062</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7548627853394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8017044067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2232732772827</t>
+    <t xml:space="preserve">14.7548637390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8017053604126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2232723236084</t>
   </si>
   <si>
     <t xml:space="preserve">15.5043172836304</t>
   </si>
   <si>
-    <t xml:space="preserve">16.06640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6916799545288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7385215759277</t>
+    <t xml:space="preserve">16.0664081573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6916809082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7385206222534</t>
   </si>
   <si>
     <t xml:space="preserve">15.9727249145508</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9258852005005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7853622436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1132469177246</t>
+    <t xml:space="preserve">15.9258842468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7853631973267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1132488250732</t>
   </si>
   <si>
     <t xml:space="preserve">15.8322038650513</t>
   </si>
   <si>
-    <t xml:space="preserve">16.534818649292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8627033233643</t>
+    <t xml:space="preserve">16.5348148345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8627014160156</t>
   </si>
   <si>
     <t xml:space="preserve">17.1437454223633</t>
   </si>
   <si>
-    <t xml:space="preserve">16.581657409668</t>
+    <t xml:space="preserve">16.5816593170166</t>
   </si>
   <si>
     <t xml:space="preserve">16.2069282531738</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2842693328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7995185852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4716339111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.815860748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6284980773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0969047546387</t>
+    <t xml:space="preserve">17.2842712402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7995204925537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4716320037842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8158626556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6284961700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0969066619873</t>
   </si>
   <si>
     <t xml:space="preserve">17.5184745788574</t>
   </si>
   <si>
-    <t xml:space="preserve">17.612154006958</t>
+    <t xml:space="preserve">17.6121559143066</t>
   </si>
   <si>
     <t xml:space="preserve">18.0337238311768</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5489730834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7363357543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9237003326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7668342590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5794677734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2047424316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.11106300354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.673152923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2984237670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4857864379883</t>
+    <t xml:space="preserve">18.5489711761475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7363376617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.923698425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7668361663818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5794696807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2047443389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1110610961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6731510162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2984256744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4857883453369</t>
   </si>
   <si>
     <t xml:space="preserve">19.8605175018311</t>
@@ -1766,10 +1766,10 @@
     <t xml:space="preserve">21.0783767700195</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4531021118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7973346710205</t>
+    <t xml:space="preserve">21.453104019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7973327636719</t>
   </si>
   <si>
     <t xml:space="preserve">21.8278293609619</t>
@@ -1781,37 +1781,37 @@
     <t xml:space="preserve">21.7341499328613</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0151958465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2962379455566</t>
+    <t xml:space="preserve">22.015193939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.296236038208</t>
   </si>
   <si>
     <t xml:space="preserve">22.4836025238037</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6404666900635</t>
+    <t xml:space="preserve">21.6404685974121</t>
   </si>
   <si>
     <t xml:space="preserve">21.5467853546143</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2352428436279</t>
+    <t xml:space="preserve">20.2352409362793</t>
   </si>
   <si>
     <t xml:space="preserve">18.3147678375244</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0173816680908</t>
+    <t xml:space="preserve">19.0173797607422</t>
   </si>
   <si>
     <t xml:space="preserve">20.6099681854248</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9215126037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7646446228027</t>
+    <t xml:space="preserve">21.9215145111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7646465301514</t>
   </si>
   <si>
     <t xml:space="preserve">22.5772838592529</t>
@@ -1829,25 +1829,25 @@
     <t xml:space="preserve">20.5162868499756</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0478801727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6709651947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2025604248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3899211883545</t>
+    <t xml:space="preserve">20.0478782653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6709671020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2025585174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3899192810059</t>
   </si>
   <si>
     <t xml:space="preserve">19.9541969299316</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4226036071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8910140991211</t>
+    <t xml:space="preserve">20.4226055145264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8910160064697</t>
   </si>
   <si>
     <t xml:space="preserve">19.3921070098877</t>
@@ -1859,10 +1859,10 @@
     <t xml:space="preserve">18.361608505249</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9563846588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6589965820312</t>
+    <t xml:space="preserve">16.9563827514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6589946746826</t>
   </si>
   <si>
     <t xml:space="preserve">17.7526779174805</t>
@@ -1877,49 +1877,49 @@
     <t xml:space="preserve">17.9400405883789</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2679252624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8768577575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6426544189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3241348266602</t>
+    <t xml:space="preserve">18.2679271697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8768558502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6426525115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3241367340088</t>
   </si>
   <si>
     <t xml:space="preserve">18.2117176055908</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2304534912109</t>
+    <t xml:space="preserve">18.2304553985596</t>
   </si>
   <si>
     <t xml:space="preserve">18.4552898406982</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9494075775146</t>
+    <t xml:space="preserve">17.9494094848633</t>
   </si>
   <si>
     <t xml:space="preserve">18.1180362701416</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9705390930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2820816040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0947189331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1884002685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1415615081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4927635192871</t>
+    <t xml:space="preserve">18.9705410003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2820835113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0947208404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1884021759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1415596008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4927616119385</t>
   </si>
   <si>
     <t xml:space="preserve">17.5559463500977</t>
@@ -1931,7 +1931,7 @@
     <t xml:space="preserve">16.8847980499268</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7634201049805</t>
+    <t xml:space="preserve">17.7634181976318</t>
   </si>
   <si>
     <t xml:space="preserve">18.0308246612549</t>
@@ -1943,7 +1943,7 @@
     <t xml:space="preserve">18.4319343566895</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6038379669189</t>
+    <t xml:space="preserve">18.6038398742676</t>
   </si>
   <si>
     <t xml:space="preserve">19.1004505157471</t>
@@ -1952,16 +1952,16 @@
     <t xml:space="preserve">18.9858474731445</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1482009887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9094467163086</t>
+    <t xml:space="preserve">19.1481990814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.90944480896</t>
   </si>
   <si>
     <t xml:space="preserve">18.9476490020752</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0077228546143</t>
+    <t xml:space="preserve">20.0077247619629</t>
   </si>
   <si>
     <t xml:space="preserve">20.0554733276367</t>
@@ -1970,7 +1970,7 @@
     <t xml:space="preserve">20.5329856872559</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9149913787842</t>
+    <t xml:space="preserve">20.9149932861328</t>
   </si>
   <si>
     <t xml:space="preserve">20.1509761810303</t>
@@ -1979,16 +1979,16 @@
     <t xml:space="preserve">20.4374828338623</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0104942321777</t>
+    <t xml:space="preserve">21.0104961395264</t>
   </si>
   <si>
     <t xml:space="preserve">21.4880084991455</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5779609680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5274353027344</t>
+    <t xml:space="preserve">19.5779628753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.527437210083</t>
   </si>
   <si>
     <t xml:space="preserve">18.7184410095215</t>
@@ -2021,16 +2021,16 @@
     <t xml:space="preserve">18.7757434844971</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9599685668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4852333068848</t>
+    <t xml:space="preserve">19.9599704742432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4852352142334</t>
   </si>
   <si>
     <t xml:space="preserve">21.1059970855713</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8700141906738</t>
+    <t xml:space="preserve">21.8700160980225</t>
   </si>
   <si>
     <t xml:space="preserve">21.392505645752</t>
@@ -2039,10 +2039,10 @@
     <t xml:space="preserve">21.1537475585938</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7745113372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.679012298584</t>
+    <t xml:space="preserve">21.7745132446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6790103912354</t>
   </si>
   <si>
     <t xml:space="preserve">21.9177684783936</t>
@@ -2054,13 +2054,13 @@
     <t xml:space="preserve">21.7267627716064</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5835113525391</t>
+    <t xml:space="preserve">21.5835094451904</t>
   </si>
   <si>
     <t xml:space="preserve">20.5807342529297</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1032238006592</t>
+    <t xml:space="preserve">20.1032218933105</t>
   </si>
   <si>
     <t xml:space="preserve">19.62571144104</t>
@@ -2069,10 +2069,10 @@
     <t xml:space="preserve">19.8644676208496</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2492523193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.920539855957</t>
+    <t xml:space="preserve">21.2492504119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9205417633057</t>
   </si>
   <si>
     <t xml:space="preserve">22.4430313110352</t>
@@ -2093,10 +2093,10 @@
     <t xml:space="preserve">20.3897304534912</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2942295074463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1987266540527</t>
+    <t xml:space="preserve">20.2942276000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1987247467041</t>
   </si>
   <si>
     <t xml:space="preserve">20.8194904327393</t>
@@ -2108,7 +2108,7 @@
     <t xml:space="preserve">18.0499267578125</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8330421447754</t>
+    <t xml:space="preserve">18.833044052124</t>
   </si>
   <si>
     <t xml:space="preserve">19.4824600219727</t>
@@ -2141,13 +2141,13 @@
     <t xml:space="preserve">22.7295341491699</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5862827301025</t>
+    <t xml:space="preserve">22.5862808227539</t>
   </si>
   <si>
     <t xml:space="preserve">22.8727912902832</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5385341644287</t>
+    <t xml:space="preserve">22.5385322570801</t>
   </si>
   <si>
     <t xml:space="preserve">22.6817855834961</t>
@@ -2165,7 +2165,7 @@
     <t xml:space="preserve">23.7323112487793</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9710655212402</t>
+    <t xml:space="preserve">23.9710636138916</t>
   </si>
   <si>
     <t xml:space="preserve">24.2098217010498</t>
@@ -2177,25 +2177,25 @@
     <t xml:space="preserve">24.1143188476562</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4008235931396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3080959320068</t>
+    <t xml:space="preserve">24.4008255004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3080978393555</t>
   </si>
   <si>
     <t xml:space="preserve">23.7800598144531</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9233131408691</t>
+    <t xml:space="preserve">23.9233150482178</t>
   </si>
   <si>
     <t xml:space="preserve">25.0693416595459</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5440788269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9260883331299</t>
+    <t xml:space="preserve">24.5440807342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9260864257812</t>
   </si>
   <si>
     <t xml:space="preserve">25.3558464050293</t>
@@ -2207,10 +2207,10 @@
     <t xml:space="preserve">25.8333587646484</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8838844299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7883796691895</t>
+    <t xml:space="preserve">26.883882522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7883815765381</t>
   </si>
   <si>
     <t xml:space="preserve">25.1170921325684</t>
@@ -2225,16 +2225,16 @@
     <t xml:space="preserve">25.260347366333</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7378559112549</t>
+    <t xml:space="preserve">25.7378578186035</t>
   </si>
   <si>
     <t xml:space="preserve">25.7856101989746</t>
   </si>
   <si>
-    <t xml:space="preserve">26.072114944458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2631187438965</t>
+    <t xml:space="preserve">26.0721130371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2631206512451</t>
   </si>
   <si>
     <t xml:space="preserve">25.4513492584229</t>
@@ -2246,7 +2246,7 @@
     <t xml:space="preserve">25.5946025848389</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6901054382324</t>
+    <t xml:space="preserve">25.6901073455811</t>
   </si>
   <si>
     <t xml:space="preserve">25.5468521118164</t>
@@ -2267,7 +2267,7 @@
     <t xml:space="preserve">28.6506767272949</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3219661712646</t>
+    <t xml:space="preserve">30.321964263916</t>
   </si>
   <si>
     <t xml:space="preserve">29.892204284668</t>
@@ -2276,7 +2276,7 @@
     <t xml:space="preserve">29.9877071380615</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1309585571289</t>
+    <t xml:space="preserve">30.1309604644775</t>
   </si>
   <si>
     <t xml:space="preserve">29.6534481048584</t>
@@ -2288,7 +2288,7 @@
     <t xml:space="preserve">28.5074214935303</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3191928863525</t>
+    <t xml:space="preserve">29.3191909790039</t>
   </si>
   <si>
     <t xml:space="preserve">28.9371814727783</t>
@@ -2300,22 +2300,22 @@
     <t xml:space="preserve">29.223690032959</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1281852722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1759395599365</t>
+    <t xml:space="preserve">29.1281871795654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1759376525879</t>
   </si>
   <si>
     <t xml:space="preserve">29.080436706543</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6984252929688</t>
+    <t xml:space="preserve">28.6984272003174</t>
   </si>
   <si>
     <t xml:space="preserve">28.9849338531494</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3641700744629</t>
+    <t xml:space="preserve">28.3641681671143</t>
   </si>
   <si>
     <t xml:space="preserve">27.8866596221924</t>
@@ -2327,7 +2327,7 @@
     <t xml:space="preserve">27.8389053344727</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6479015350342</t>
+    <t xml:space="preserve">27.6479034423828</t>
   </si>
   <si>
     <t xml:space="preserve">28.6029243469238</t>
@@ -2339,22 +2339,22 @@
     <t xml:space="preserve">29.366943359375</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4146938323975</t>
+    <t xml:space="preserve">29.4146919250488</t>
   </si>
   <si>
     <t xml:space="preserve">30.0354595184326</t>
   </si>
   <si>
-    <t xml:space="preserve">29.748950958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7039756774902</t>
+    <t xml:space="preserve">29.7489490509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7039737701416</t>
   </si>
   <si>
     <t xml:space="preserve">30.2742137908936</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7012004852295</t>
+    <t xml:space="preserve">29.7012023925781</t>
   </si>
   <si>
     <t xml:space="preserve">29.5579471588135</t>
@@ -2366,10 +2366,10 @@
     <t xml:space="preserve">28.2209167480469</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3164196014404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0326824188232</t>
+    <t xml:space="preserve">28.3164176940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0326843261719</t>
   </si>
   <si>
     <t xml:space="preserve">26.9480724334717</t>
@@ -3405,6 +3405,9 @@
   </si>
   <si>
     <t xml:space="preserve">36.7999992370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1500015258789</t>
   </si>
 </sst>
 </file>
@@ -69159,7 +69162,7 @@
     </row>
     <row r="2517">
       <c r="A2517" s="1" t="n">
-        <v>45982.6912384259</v>
+        <v>45982.3333333333</v>
       </c>
       <c r="B2517" t="n">
         <v>11172</v>
@@ -69180,6 +69183,32 @@
         <v>1117</v>
       </c>
       <c r="H2517" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2518">
+      <c r="A2518" s="1" t="n">
+        <v>45985.6912847222</v>
+      </c>
+      <c r="B2518" t="n">
+        <v>15693</v>
+      </c>
+      <c r="C2518" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="D2518" t="n">
+        <v>37.3499984741211</v>
+      </c>
+      <c r="E2518" t="n">
+        <v>37.4000015258789</v>
+      </c>
+      <c r="F2518" t="n">
+        <v>38.1500015258789</v>
+      </c>
+      <c r="G2518" t="s">
+        <v>1131</v>
+      </c>
+      <c r="H2518" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LUVE.MI.xlsx
+++ b/data/LUVE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1135" uniqueCount="1135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1136" uniqueCount="1136">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,67 +38,67 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30043506622314</t>
+    <t xml:space="preserve">8.30043411254883</t>
   </si>
   <si>
     <t xml:space="preserve">LUVE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31703567504883</t>
+    <t xml:space="preserve">8.3170337677002</t>
   </si>
   <si>
     <t xml:space="preserve">8.28383159637451</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09292316436768</t>
+    <t xml:space="preserve">8.09292221069336</t>
   </si>
   <si>
     <t xml:space="preserve">8.19667911529541</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07632160186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15102481842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17177677154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03896999359131</t>
+    <t xml:space="preserve">8.07632064819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15102672576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17177963256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03896903991699</t>
   </si>
   <si>
     <t xml:space="preserve">8.08462238311768</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06802177429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96841764450073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01821899414062</t>
+    <t xml:space="preserve">8.06802272796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96841669082642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01821804046631</t>
   </si>
   <si>
     <t xml:space="preserve">7.99746751785278</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91861343383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91446352005005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91031360626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.885413646698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87711191177368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.852210521698</t>
+    <t xml:space="preserve">7.91861534118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91446304321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91031217575073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88541126251221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87711048126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85220956802368</t>
   </si>
   <si>
     <t xml:space="preserve">7.64884996414185</t>
@@ -107,55 +107,55 @@
     <t xml:space="preserve">7.71940326690674</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70280122756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69035148620605</t>
+    <t xml:space="preserve">7.7028021812439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69035291671753</t>
   </si>
   <si>
     <t xml:space="preserve">7.61979866027832</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55754375457764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55339479446411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63639831542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76920461654663</t>
+    <t xml:space="preserve">7.55754470825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55339384078979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.636399269104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76920509338379</t>
   </si>
   <si>
     <t xml:space="preserve">7.80240678787231</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93521404266357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10122394561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05141925811768</t>
+    <t xml:space="preserve">7.93521451950073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10122299194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05142021179199</t>
   </si>
   <si>
     <t xml:space="preserve">8.18422698974609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13442420959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00161838531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9601149559021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21743011474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35853481292725</t>
+    <t xml:space="preserve">8.13442611694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00161743164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96011543273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21742725372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35853672027588</t>
   </si>
   <si>
     <t xml:space="preserve">8.32533550262451</t>
@@ -170,64 +170,64 @@
     <t xml:space="preserve">8.15932559967041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30336284637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36267375946045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43045616149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15085220336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17627048492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20592594146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13390827178955</t>
+    <t xml:space="preserve">8.30336380004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36267280578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43045520782471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15085315704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17627143859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2059268951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13390922546387</t>
   </si>
   <si>
     <t xml:space="preserve">8.11696147918701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21863460540771</t>
+    <t xml:space="preserve">8.21863555908203</t>
   </si>
   <si>
     <t xml:space="preserve">8.21016216278076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21439933776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20169067382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26099967956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09154319763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10848808288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04918098449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96445035934448</t>
+    <t xml:space="preserve">8.21439838409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20168972015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26100063323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09154415130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10848903656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04917907714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96444988250732</t>
   </si>
   <si>
     <t xml:space="preserve">7.92208766937256</t>
   </si>
   <si>
-    <t xml:space="preserve">7.879723072052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83735752105713</t>
+    <t xml:space="preserve">7.87972354888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83735847473145</t>
   </si>
   <si>
     <t xml:space="preserve">8.12543392181396</t>
@@ -236,19 +236,19 @@
     <t xml:space="preserve">7.93479633331299</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75262975692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71026659011841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93903255462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81193971633911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79499435424805</t>
+    <t xml:space="preserve">7.75262928009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71026611328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93903303146362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81194067001343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79499530792236</t>
   </si>
   <si>
     <t xml:space="preserve">7.62553834915161</t>
@@ -263,34 +263,34 @@
     <t xml:space="preserve">8.19321727752686</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47282123565674</t>
+    <t xml:space="preserve">8.47281932830811</t>
   </si>
   <si>
     <t xml:space="preserve">8.51518440246582</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52365779876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59991264343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78631687164307</t>
+    <t xml:space="preserve">8.52365875244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59991073608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78631496429443</t>
   </si>
   <si>
     <t xml:space="preserve">8.71853256225586</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50671195983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54060173034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46858406066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46434688568115</t>
+    <t xml:space="preserve">8.50671291351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.540602684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46858501434326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46434783935547</t>
   </si>
   <si>
     <t xml:space="preserve">8.55754852294922</t>
@@ -299,7 +299,7 @@
     <t xml:space="preserve">8.57449436187744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81173419952393</t>
+    <t xml:space="preserve">8.81173324584961</t>
   </si>
   <si>
     <t xml:space="preserve">8.7270040512085</t>
@@ -308,25 +308,25 @@
     <t xml:space="preserve">8.64227676391602</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89646244049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0235538482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09980964660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06591701507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1082820892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27773857116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1930103302002</t>
+    <t xml:space="preserve">8.89646148681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02355194091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09980869293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06591606140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10828018188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27773952484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19300842285156</t>
   </si>
   <si>
     <t xml:space="preserve">9.18453788757324</t>
@@ -335,19 +335,19 @@
     <t xml:space="preserve">9.07439041137695</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09133625030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30315780639648</t>
+    <t xml:space="preserve">9.09133529663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30315589904785</t>
   </si>
   <si>
     <t xml:space="preserve">9.32010173797607</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12522792816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60817909240723</t>
+    <t xml:space="preserve">9.12522888183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60817718505859</t>
   </si>
   <si>
     <t xml:space="preserve">9.40483093261719</t>
@@ -356,85 +356,85 @@
     <t xml:space="preserve">9.48955821990967</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38788414001465</t>
+    <t xml:space="preserve">9.38788509368896</t>
   </si>
   <si>
     <t xml:space="preserve">9.53192329406738</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4810848236084</t>
+    <t xml:space="preserve">9.48108386993408</t>
   </si>
   <si>
     <t xml:space="preserve">9.44719409942627</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54039764404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5742883682251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47261238098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41330337524414</t>
+    <t xml:space="preserve">9.54039573669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57428741455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47261333465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41330432891846</t>
   </si>
   <si>
     <t xml:space="preserve">9.42177581787109</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51497840881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56581497192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74374389648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0657119750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2521123886108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1334934234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99792861938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95556545257568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98098278045654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88778114318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91320037841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0148735046387</t>
+    <t xml:space="preserve">9.51497745513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56581401824951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74374294281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.065710067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2521133422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1334924697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99792766571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95556449890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98098087310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88778209686279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91319942474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.014874458313</t>
   </si>
   <si>
     <t xml:space="preserve">10.1589107513428</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0402927398682</t>
+    <t xml:space="preserve">10.0402936935425</t>
   </si>
   <si>
     <t xml:space="preserve">9.70137882232666</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73526954650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70985317230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0826549530029</t>
+    <t xml:space="preserve">9.73527050018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70985126495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0826559066772</t>
   </si>
   <si>
     <t xml:space="preserve">9.86236381530762</t>
@@ -443,85 +443,85 @@
     <t xml:space="preserve">10.1250200271606</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2944765090942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4808797836304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5317163467407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5147695541382</t>
+    <t xml:space="preserve">10.2944774627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4808778762817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.531717300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5147705078125</t>
   </si>
   <si>
     <t xml:space="preserve">10.802845954895</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9129915237427</t>
+    <t xml:space="preserve">10.9129934310913</t>
   </si>
   <si>
     <t xml:space="preserve">10.8621549606323</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0146646499634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0570306777954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2773237228394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.438307762146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6586008071899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5823459625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4806709289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5908193588257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7009649276733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7772207260132</t>
+    <t xml:space="preserve">11.0146656036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0570316314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2773246765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4383058547974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6586017608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5823440551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4806718826294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5908184051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7009658813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7772197723389</t>
   </si>
   <si>
     <t xml:space="preserve">11.8111114501953</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8365297317505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6670732498169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.599289894104</t>
+    <t xml:space="preserve">11.8365306854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6670722961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5992918014526</t>
   </si>
   <si>
     <t xml:space="preserve">11.5230369567871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6077642440796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6263818740845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7297258377075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6952781677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.678053855896</t>
+    <t xml:space="preserve">11.6077632904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6263799667358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7297248840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6952772140503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6780548095703</t>
   </si>
   <si>
     <t xml:space="preserve">11.7986240386963</t>
@@ -539,85 +539,85 @@
     <t xml:space="preserve">12.3153514862061</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3584136962891</t>
+    <t xml:space="preserve">12.3584127426147</t>
   </si>
   <si>
     <t xml:space="preserve">12.0569877624512</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1431083679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9967021942139</t>
+    <t xml:space="preserve">12.1431093215942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9967031478882</t>
   </si>
   <si>
     <t xml:space="preserve">11.8416843414307</t>
   </si>
   <si>
-    <t xml:space="preserve">11.755560874939</t>
+    <t xml:space="preserve">11.7555637359619</t>
   </si>
   <si>
     <t xml:space="preserve">11.7125034332275</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8502969741821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9191951751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.962254524231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0397624969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0483741760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7900104522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0311508178711</t>
+    <t xml:space="preserve">11.8502979278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9191932678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9622535705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0397644042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0483751296997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7900123596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0311527252197</t>
   </si>
   <si>
     <t xml:space="preserve">11.9450302124023</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8158493041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8933572769165</t>
+    <t xml:space="preserve">11.8158464431763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8933582305908</t>
   </si>
   <si>
     <t xml:space="preserve">11.8761320114136</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8244600296021</t>
+    <t xml:space="preserve">11.8244590759277</t>
   </si>
   <si>
     <t xml:space="preserve">11.8675203323364</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9019689559937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9278059005737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7211132049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6694412231445</t>
+    <t xml:space="preserve">11.901969909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.927806854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7211141586304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6694421768188</t>
   </si>
   <si>
     <t xml:space="preserve">11.6349935531616</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6091556549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5747089385986</t>
+    <t xml:space="preserve">11.6091566085815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5747079849243</t>
   </si>
   <si>
     <t xml:space="preserve">11.5316486358643</t>
@@ -629,49 +629,49 @@
     <t xml:space="preserve">11.3680171966553</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3594045639038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2818946838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2302236557007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1957731246948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.187162399292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1096525192261</t>
+    <t xml:space="preserve">11.3594036102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2818956375122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2302217483521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1957750320435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1871633529663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1096534729004</t>
   </si>
   <si>
     <t xml:space="preserve">11.0579805374146</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1785497665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1268768310547</t>
+    <t xml:space="preserve">11.1785507202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.126877784729</t>
   </si>
   <si>
     <t xml:space="preserve">10.9374103546143</t>
   </si>
   <si>
-    <t xml:space="preserve">11.066593170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0235328674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0838165283203</t>
+    <t xml:space="preserve">11.0665912628174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0235319137573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.083815574646</t>
   </si>
   <si>
     <t xml:space="preserve">11.1354894638062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2043876647949</t>
+    <t xml:space="preserve">11.2043867111206</t>
   </si>
   <si>
     <t xml:space="preserve">11.3163442611694</t>
@@ -683,25 +683,25 @@
     <t xml:space="preserve">11.5402593612671</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4110774993896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2905082702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1613245010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2646713256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1527137756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0407552719116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4196910858154</t>
+    <t xml:space="preserve">11.411078453064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2905073165894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1613264083862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2646732330322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1527128219604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0407562255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4196901321411</t>
   </si>
   <si>
     <t xml:space="preserve">11.2216100692749</t>
@@ -725,16 +725,16 @@
     <t xml:space="preserve">11.0924282073975</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74032402038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01690578460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2149829864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3786153793335</t>
+    <t xml:space="preserve">9.74032306671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0169038772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21498203277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37861442565918</t>
   </si>
   <si>
     <t xml:space="preserve">9.49057197570801</t>
@@ -743,25 +743,25 @@
     <t xml:space="preserve">9.50779438018799</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59391784667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60252952575684</t>
+    <t xml:space="preserve">9.59391689300537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60252857208252</t>
   </si>
   <si>
     <t xml:space="preserve">9.6886510848999</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56808090209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39583873748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34416580200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25804424285889</t>
+    <t xml:space="preserve">9.56808280944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39583778381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34416484832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25804328918457</t>
   </si>
   <si>
     <t xml:space="preserve">9.30110454559326</t>
@@ -773,34 +773,34 @@
     <t xml:space="preserve">9.28388023376465</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24081993103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12886238098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02551555633545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20637035369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26665496826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69726467132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65420055389404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66281509399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64558982849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67142772674561</t>
+    <t xml:space="preserve">9.24081897735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12886142730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02551460266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20637130737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26665592193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69726371765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65420150756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66281414031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64559173583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67142581939697</t>
   </si>
   <si>
     <t xml:space="preserve">9.75754833221436</t>
@@ -812,31 +812,31 @@
     <t xml:space="preserve">9.09441375732422</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93939590454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14608573913574</t>
+    <t xml:space="preserve">8.9393949508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14608764648438</t>
   </si>
   <si>
     <t xml:space="preserve">9.12024974822998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83505821228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73171329498291</t>
+    <t xml:space="preserve">9.83505725860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73171138763428</t>
   </si>
   <si>
     <t xml:space="preserve">9.90395450592041</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77477264404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5336332321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49918270111084</t>
+    <t xml:space="preserve">9.77477359771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53363037109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49918460845947</t>
   </si>
   <si>
     <t xml:space="preserve">9.57669258117676</t>
@@ -845,22 +845,22 @@
     <t xml:space="preserve">9.58530426025391</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47334671020508</t>
+    <t xml:space="preserve">9.47334766387939</t>
   </si>
   <si>
     <t xml:space="preserve">9.43028736114502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54224395751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17192268371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23220729827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55946922302246</t>
+    <t xml:space="preserve">9.54224586486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1719217300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23220825195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55947017669678</t>
   </si>
   <si>
     <t xml:space="preserve">9.51640796661377</t>
@@ -872,7 +872,7 @@
     <t xml:space="preserve">8.95662021636963</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91355895996094</t>
+    <t xml:space="preserve">8.91355991363525</t>
   </si>
   <si>
     <t xml:space="preserve">9.08580207824707</t>
@@ -884,7 +884,7 @@
     <t xml:space="preserve">8.999680519104</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82743740081787</t>
+    <t xml:space="preserve">8.8274393081665</t>
   </si>
   <si>
     <t xml:space="preserve">8.69825553894043</t>
@@ -893,13 +893,13 @@
     <t xml:space="preserve">8.87049770355225</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7843770980835</t>
+    <t xml:space="preserve">8.78437614440918</t>
   </si>
   <si>
     <t xml:space="preserve">8.7413158416748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61213493347168</t>
+    <t xml:space="preserve">8.61213397979736</t>
   </si>
   <si>
     <t xml:space="preserve">8.59490966796875</t>
@@ -908,19 +908,19 @@
     <t xml:space="preserve">8.65519523620605</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45711517333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06314468383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10714149475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0191478729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97515201568604</t>
+    <t xml:space="preserve">8.45711612701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06314373016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10714054107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01914882659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97515296936035</t>
   </si>
   <si>
     <t xml:space="preserve">8.93115711212158</t>
@@ -935,61 +935,61 @@
     <t xml:space="preserve">8.76397323608398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48239898681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71117877960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62318706512451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58798980712891</t>
+    <t xml:space="preserve">8.48240089416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71117687225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62318801879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58798885345459</t>
   </si>
   <si>
     <t xml:space="preserve">8.6583833694458</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60558795928955</t>
+    <t xml:space="preserve">8.60558700561523</t>
   </si>
   <si>
     <t xml:space="preserve">8.7287769317627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69357872009277</t>
+    <t xml:space="preserve">8.69357967376709</t>
   </si>
   <si>
     <t xml:space="preserve">8.74637413024902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53519344329834</t>
+    <t xml:space="preserve">8.53519439697266</t>
   </si>
   <si>
     <t xml:space="preserve">8.44720363616943</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27121829986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32401466369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.288818359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78157138824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64078426361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79917049407959</t>
+    <t xml:space="preserve">8.27121925354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32401561737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28881645202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78157043457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64078235626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79916858673096</t>
   </si>
   <si>
     <t xml:space="preserve">8.67598152160645</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23912811279297</t>
+    <t xml:space="preserve">9.23912906646729</t>
   </si>
   <si>
     <t xml:space="preserve">9.37111568450928</t>
@@ -1001,28 +1001,28 @@
     <t xml:space="preserve">9.1951322555542</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15113544464111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46479988098145</t>
+    <t xml:space="preserve">9.15113639831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46480178833008</t>
   </si>
   <si>
     <t xml:space="preserve">8.41200542449951</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49999713897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34161281585693</t>
+    <t xml:space="preserve">8.49999809265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34161186218262</t>
   </si>
   <si>
     <t xml:space="preserve">8.23602294921875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30641651153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13043212890625</t>
+    <t xml:space="preserve">8.30641555786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13043117523193</t>
   </si>
   <si>
     <t xml:space="preserve">8.1832275390625</t>
@@ -1031,10 +1031,10 @@
     <t xml:space="preserve">8.16562938690186</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21842384338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25362205505371</t>
+    <t xml:space="preserve">8.21842575073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25362014770508</t>
   </si>
   <si>
     <t xml:space="preserve">8.37680912017822</t>
@@ -1043,7 +1043,7 @@
     <t xml:space="preserve">8.5175952911377</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28312397003174</t>
+    <t xml:space="preserve">9.28312301635742</t>
   </si>
   <si>
     <t xml:space="preserve">9.41511154174805</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">9.63509082794189</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59109497070312</t>
+    <t xml:space="preserve">9.59109401702881</t>
   </si>
   <si>
     <t xml:space="preserve">9.89906597137451</t>
@@ -1061,16 +1061,16 @@
     <t xml:space="preserve">10.1190452575684</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1630401611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2070369720459</t>
+    <t xml:space="preserve">10.1630411148071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2070379257202</t>
   </si>
   <si>
     <t xml:space="preserve">10.3390245437622</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2950286865234</t>
+    <t xml:space="preserve">10.2950277328491</t>
   </si>
   <si>
     <t xml:space="preserve">10.383020401001</t>
@@ -1079,10 +1079,10 @@
     <t xml:space="preserve">10.2510318756104</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4270172119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0750494003296</t>
+    <t xml:space="preserve">10.4270162582397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0750484466553</t>
   </si>
   <si>
     <t xml:space="preserve">10.5150079727173</t>
@@ -1091,55 +1091,55 @@
     <t xml:space="preserve">10.6498165130615</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4700717926025</t>
+    <t xml:space="preserve">10.4700708389282</t>
   </si>
   <si>
     <t xml:space="preserve">10.694751739502</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6048803329468</t>
+    <t xml:space="preserve">10.6048793792725</t>
   </si>
   <si>
     <t xml:space="preserve">10.380199432373</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2453908920288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0656490325928</t>
+    <t xml:space="preserve">10.2453918457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0656480789185</t>
   </si>
   <si>
     <t xml:space="preserve">10.4251356124878</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3352642059326</t>
+    <t xml:space="preserve">10.3352651596069</t>
   </si>
   <si>
     <t xml:space="preserve">10.2903280258179</t>
   </si>
   <si>
-    <t xml:space="preserve">10.200457572937</t>
+    <t xml:space="preserve">10.2004566192627</t>
   </si>
   <si>
     <t xml:space="preserve">9.9757776260376</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1105852127075</t>
+    <t xml:space="preserve">10.1105842590332</t>
   </si>
   <si>
     <t xml:space="preserve">9.93084049224854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88590431213379</t>
+    <t xml:space="preserve">9.88590335845947</t>
   </si>
   <si>
     <t xml:space="preserve">10.1555204391479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0207118988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75109672546387</t>
+    <t xml:space="preserve">10.020712852478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75109767913818</t>
   </si>
   <si>
     <t xml:space="preserve">9.70616149902344</t>
@@ -1151,13 +1151,13 @@
     <t xml:space="preserve">9.30173778533936</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39160919189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48148155212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61629009246826</t>
+    <t xml:space="preserve">9.39161014556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48148059844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61628913879395</t>
   </si>
   <si>
     <t xml:space="preserve">9.52641773223877</t>
@@ -1172,13 +1172,13 @@
     <t xml:space="preserve">9.03212261199951</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16693019866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07705879211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25680160522461</t>
+    <t xml:space="preserve">9.16692924499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07705783843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25680065155029</t>
   </si>
   <si>
     <t xml:space="preserve">8.98718643188477</t>
@@ -1196,13 +1196,13 @@
     <t xml:space="preserve">10.9643669128418</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4586620330811</t>
+    <t xml:space="preserve">11.4586639404297</t>
   </si>
   <si>
     <t xml:space="preserve">11.5035991668701</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2339820861816</t>
+    <t xml:space="preserve">11.233983039856</t>
   </si>
   <si>
     <t xml:space="preserve">11.1441106796265</t>
@@ -1217,16 +1217,16 @@
     <t xml:space="preserve">11.0093030929565</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2789182662964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.413724899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5485343933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6833410263062</t>
+    <t xml:space="preserve">11.2789192199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4137258529663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5485334396362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6833429336548</t>
   </si>
   <si>
     <t xml:space="preserve">11.77321434021</t>
@@ -1241,52 +1241,52 @@
     <t xml:space="preserve">11.9978942871094</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8181486129761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5934705734253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3124437332153</t>
+    <t xml:space="preserve">11.8181505203247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.593469619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3124446868896</t>
   </si>
   <si>
     <t xml:space="preserve">12.5820608139038</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9415493011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8067407608032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7618036270142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0763568878174</t>
+    <t xml:space="preserve">12.9415483474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8067398071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7618045806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0763559341431</t>
   </si>
   <si>
     <t xml:space="preserve">12.4472532272339</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5371246337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2675085067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4023170471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6269960403442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6719331741333</t>
+    <t xml:space="preserve">12.5371236801147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2675094604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4023180007935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6269979476929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.671932220459</t>
   </si>
   <si>
     <t xml:space="preserve">12.8966121673584</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7282772064209</t>
+    <t xml:space="preserve">11.7282781600952</t>
   </si>
   <si>
     <t xml:space="preserve">10.7846231460571</t>
@@ -1295,7 +1295,7 @@
     <t xml:space="preserve">10.559944152832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89731502532959</t>
+    <t xml:space="preserve">8.89731407165527</t>
   </si>
   <si>
     <t xml:space="preserve">7.98062086105347</t>
@@ -1304,37 +1304,37 @@
     <t xml:space="preserve">7.81885194778442</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5312614440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89074802398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53782844543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96264743804932</t>
+    <t xml:space="preserve">7.53126192092896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89074993133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53782653808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.962646484375</t>
   </si>
   <si>
     <t xml:space="preserve">8.44795417785645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60972309112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66364669799805</t>
+    <t xml:space="preserve">8.60972499847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66364765167236</t>
   </si>
   <si>
     <t xml:space="preserve">8.86136531829834</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21186542510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93848896026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80045509338379</t>
+    <t xml:space="preserve">9.21186637878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93848991394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80045604705811</t>
   </si>
   <si>
     <t xml:space="preserve">9.89247894287109</t>
@@ -1343,22 +1343,22 @@
     <t xml:space="preserve">9.66242027282715</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7084321975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84646701812744</t>
+    <t xml:space="preserve">9.70843124389648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84646606445312</t>
   </si>
   <si>
     <t xml:space="preserve">10.1225357055664</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75444412231445</t>
+    <t xml:space="preserve">9.75444316864014</t>
   </si>
   <si>
     <t xml:space="preserve">10.3986053466797</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3065824508667</t>
+    <t xml:space="preserve">10.3065814971924</t>
   </si>
   <si>
     <t xml:space="preserve">10.720685005188</t>
@@ -1367,7 +1367,7 @@
     <t xml:space="preserve">10.5826501846313</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8587207794189</t>
+    <t xml:space="preserve">10.8587198257446</t>
   </si>
   <si>
     <t xml:space="preserve">10.6746740341187</t>
@@ -1382,19 +1382,19 @@
     <t xml:space="preserve">10.766697883606</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4906272888184</t>
+    <t xml:space="preserve">10.4906282424927</t>
   </si>
   <si>
     <t xml:space="preserve">11.1347894668579</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3188362121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5028810501099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1808004379272</t>
+    <t xml:space="preserve">11.3188352584839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5028820037842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1807994842529</t>
   </si>
   <si>
     <t xml:space="preserve">11.0427656173706</t>
@@ -1403,7 +1403,7 @@
     <t xml:space="preserve">11.2728233337402</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9507427215576</t>
+    <t xml:space="preserve">10.9507417678833</t>
   </si>
   <si>
     <t xml:space="preserve">11.0887775421143</t>
@@ -1415,46 +1415,46 @@
     <t xml:space="preserve">10.9047317504883</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4108591079712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4568691253662</t>
+    <t xml:space="preserve">11.4108581542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4568700790405</t>
   </si>
   <si>
     <t xml:space="preserve">11.2268123626709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3648471832275</t>
+    <t xml:space="preserve">11.3648481369019</t>
   </si>
   <si>
     <t xml:space="preserve">11.5488929748535</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5949048995972</t>
+    <t xml:space="preserve">11.5949039459229</t>
   </si>
   <si>
     <t xml:space="preserve">11.6869277954102</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9629964828491</t>
+    <t xml:space="preserve">11.9629974365234</t>
   </si>
   <si>
     <t xml:space="preserve">11.7789516448975</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0090084075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1010303497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7329387664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8249626159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0550203323364</t>
+    <t xml:space="preserve">12.0090093612671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1010313034058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7329397201538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8249616622925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0550193786621</t>
   </si>
   <si>
     <t xml:space="preserve">11.8709735870361</t>
@@ -1463,37 +1463,37 @@
     <t xml:space="preserve">11.9169845581055</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6409149169922</t>
+    <t xml:space="preserve">11.6409158706665</t>
   </si>
   <si>
     <t xml:space="preserve">12.1470422744751</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6991815567017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7912044525146</t>
+    <t xml:space="preserve">12.6991806030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7912034988403</t>
   </si>
   <si>
     <t xml:space="preserve">13.0672731399536</t>
   </si>
   <si>
-    <t xml:space="preserve">12.883228302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.929238319397</t>
+    <t xml:space="preserve">12.8832273483276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9292392730713</t>
   </si>
   <si>
     <t xml:space="preserve">13.2053089141846</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2513189315796</t>
+    <t xml:space="preserve">13.2513198852539</t>
   </si>
   <si>
     <t xml:space="preserve">13.1132850646973</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1592950820923</t>
+    <t xml:space="preserve">13.1592960357666</t>
   </si>
   <si>
     <t xml:space="preserve">13.3893537521362</t>
@@ -1502,16 +1502,16 @@
     <t xml:space="preserve">13.2973308563232</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9752511978149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7114334106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4353666305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5151357650757</t>
+    <t xml:space="preserve">12.9752521514893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7114343643188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4353656768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5151348114014</t>
   </si>
   <si>
     <t xml:space="preserve">12.3770999908447</t>
@@ -1529,7 +1529,7 @@
     <t xml:space="preserve">13.3433427810669</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6194105148315</t>
+    <t xml:space="preserve">13.6194114685059</t>
   </si>
   <si>
     <t xml:space="preserve">13.8494691848755</t>
@@ -1538,13 +1538,13 @@
     <t xml:space="preserve">13.9414920806885</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1715488433838</t>
+    <t xml:space="preserve">14.1715497970581</t>
   </si>
   <si>
     <t xml:space="preserve">14.3555965423584</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1255388259888</t>
+    <t xml:space="preserve">14.1255378723145</t>
   </si>
   <si>
     <t xml:space="preserve">14.493631362915</t>
@@ -1553,7 +1553,7 @@
     <t xml:space="preserve">14.7236881256104</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6776762008667</t>
+    <t xml:space="preserve">14.677677154541</t>
   </si>
   <si>
     <t xml:space="preserve">14.8157119750977</t>
@@ -1562,31 +1562,31 @@
     <t xml:space="preserve">14.861722946167</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0457706451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5396413803101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.631664276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4476184844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2635736465454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9875030517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3095846176147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6654243469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8034582138062</t>
+    <t xml:space="preserve">15.045768737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5396423339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6316652297974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4476194381714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2635726928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9875040054321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3095855712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6654233932495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8034563064575</t>
   </si>
   <si>
     <t xml:space="preserve">13.5734004974365</t>
@@ -1595,13 +1595,13 @@
     <t xml:space="preserve">13.7574462890625</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9537467956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0335159301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4269771575928</t>
+    <t xml:space="preserve">14.95374584198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0335140228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4269781112671</t>
   </si>
   <si>
     <t xml:space="preserve">14.3801374435425</t>
@@ -1616,7 +1616,7 @@
     <t xml:space="preserve">14.8485460281372</t>
   </si>
   <si>
-    <t xml:space="preserve">15.03590965271</t>
+    <t xml:space="preserve">15.0359086990356</t>
   </si>
   <si>
     <t xml:space="preserve">15.0827503204346</t>
@@ -1625,10 +1625,10 @@
     <t xml:space="preserve">14.8953857421875</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9422273635864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1764326095581</t>
+    <t xml:space="preserve">14.9422283172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1764316558838</t>
   </si>
   <si>
     <t xml:space="preserve">15.1295900344849</t>
@@ -1637,34 +1637,34 @@
     <t xml:space="preserve">14.989068031311</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6611824035645</t>
+    <t xml:space="preserve">14.6611804962158</t>
   </si>
   <si>
     <t xml:space="preserve">15.3169546127319</t>
   </si>
   <si>
-    <t xml:space="preserve">14.754864692688</t>
+    <t xml:space="preserve">14.7548637390137</t>
   </si>
   <si>
     <t xml:space="preserve">14.8017053604126</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2232723236084</t>
+    <t xml:space="preserve">15.2232713699341</t>
   </si>
   <si>
     <t xml:space="preserve">15.5043172836304</t>
   </si>
   <si>
-    <t xml:space="preserve">16.06640625</t>
+    <t xml:space="preserve">16.0664081573486</t>
   </si>
   <si>
     <t xml:space="preserve">15.6916809082031</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7385215759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9727239608765</t>
+    <t xml:space="preserve">15.7385206222534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9727249145508</t>
   </si>
   <si>
     <t xml:space="preserve">15.9258842468262</t>
@@ -1679,7 +1679,7 @@
     <t xml:space="preserve">15.8322038650513</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5348167419434</t>
+    <t xml:space="preserve">16.5348148345947</t>
   </si>
   <si>
     <t xml:space="preserve">16.8627014160156</t>
@@ -1694,25 +1694,25 @@
     <t xml:space="preserve">16.2069282531738</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2842712402344</t>
+    <t xml:space="preserve">17.284273147583</t>
   </si>
   <si>
     <t xml:space="preserve">17.7995185852051</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4716339111328</t>
+    <t xml:space="preserve">17.4716300964355</t>
   </si>
   <si>
     <t xml:space="preserve">16.8158626556396</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6284961700439</t>
+    <t xml:space="preserve">16.6284980773926</t>
   </si>
   <si>
     <t xml:space="preserve">17.0969066619873</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5184726715088</t>
+    <t xml:space="preserve">17.5184745788574</t>
   </si>
   <si>
     <t xml:space="preserve">17.6121559143066</t>
@@ -1724,10 +1724,10 @@
     <t xml:space="preserve">18.5489711761475</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7363357543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9237003326416</t>
+    <t xml:space="preserve">18.7363376617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.923698425293</t>
   </si>
   <si>
     <t xml:space="preserve">19.7668342590332</t>
@@ -1739,7 +1739,7 @@
     <t xml:space="preserve">19.2047443389893</t>
   </si>
   <si>
-    <t xml:space="preserve">19.11106300354</t>
+    <t xml:space="preserve">19.1110610961914</t>
   </si>
   <si>
     <t xml:space="preserve">19.673152923584</t>
@@ -1751,19 +1751,19 @@
     <t xml:space="preserve">19.4857883453369</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8605175018311</t>
+    <t xml:space="preserve">19.8605155944824</t>
   </si>
   <si>
     <t xml:space="preserve">20.3289241790771</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9846973419189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.265739440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0783786773682</t>
+    <t xml:space="preserve">20.9846954345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2657413482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0783748626709</t>
   </si>
   <si>
     <t xml:space="preserve">21.453104019165</t>
@@ -1775,37 +1775,37 @@
     <t xml:space="preserve">21.8278293609619</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1088771820068</t>
+    <t xml:space="preserve">22.1088752746582</t>
   </si>
   <si>
     <t xml:space="preserve">21.7341499328613</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0151958465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2962379455566</t>
+    <t xml:space="preserve">22.0151920318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.296236038208</t>
   </si>
   <si>
     <t xml:space="preserve">22.4836025238037</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6404666900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5467872619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2352409362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3147659301758</t>
+    <t xml:space="preserve">21.6404685974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5467853546143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2352428436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3147678375244</t>
   </si>
   <si>
     <t xml:space="preserve">19.0173797607422</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6099700927734</t>
+    <t xml:space="preserve">20.6099681854248</t>
   </si>
   <si>
     <t xml:space="preserve">21.9215145111084</t>
@@ -1820,25 +1820,25 @@
     <t xml:space="preserve">21.1720600128174</t>
   </si>
   <si>
-    <t xml:space="preserve">20.703649520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3594226837158</t>
+    <t xml:space="preserve">20.7036514282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3594207763672</t>
   </si>
   <si>
     <t xml:space="preserve">20.5162868499756</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0478801727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6709651947021</t>
+    <t xml:space="preserve">20.0478763580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6709671020508</t>
   </si>
   <si>
     <t xml:space="preserve">22.2025585174561</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3899192810059</t>
+    <t xml:space="preserve">22.3899211883545</t>
   </si>
   <si>
     <t xml:space="preserve">19.9541969299316</t>
@@ -1847,7 +1847,7 @@
     <t xml:space="preserve">20.4226055145264</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8910140991211</t>
+    <t xml:space="preserve">20.8910160064697</t>
   </si>
   <si>
     <t xml:space="preserve">19.3921070098877</t>
@@ -1862,10 +1862,10 @@
     <t xml:space="preserve">16.9563827514648</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6589965820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7526779174805</t>
+    <t xml:space="preserve">17.6589946746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7526798248291</t>
   </si>
   <si>
     <t xml:space="preserve">17.377950668335</t>
@@ -1877,22 +1877,22 @@
     <t xml:space="preserve">17.9400405883789</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2679252624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8768558502197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6426525115967</t>
+    <t xml:space="preserve">18.2679271697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8768577575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6426544189453</t>
   </si>
   <si>
     <t xml:space="preserve">18.3241367340088</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2117195129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2304553985596</t>
+    <t xml:space="preserve">18.2117156982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2304534912109</t>
   </si>
   <si>
     <t xml:space="preserve">18.4552898406982</t>
@@ -1907,7 +1907,7 @@
     <t xml:space="preserve">18.9705390930176</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2820816040039</t>
+    <t xml:space="preserve">20.2820835113525</t>
   </si>
   <si>
     <t xml:space="preserve">20.0947208404541</t>
@@ -1916,22 +1916,22 @@
     <t xml:space="preserve">20.1884002685547</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1415615081787</t>
+    <t xml:space="preserve">20.1415596008301</t>
   </si>
   <si>
     <t xml:space="preserve">18.4927616119385</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5559482574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1999588012695</t>
+    <t xml:space="preserve">17.5559463500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1999549865723</t>
   </si>
   <si>
     <t xml:space="preserve">16.8847980499268</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7634181976318</t>
+    <t xml:space="preserve">17.7634201049805</t>
   </si>
   <si>
     <t xml:space="preserve">18.0308246612549</t>
@@ -1943,7 +1943,7 @@
     <t xml:space="preserve">18.4319343566895</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6038398742676</t>
+    <t xml:space="preserve">18.6038379669189</t>
   </si>
   <si>
     <t xml:space="preserve">19.1004505157471</t>
@@ -1952,19 +1952,19 @@
     <t xml:space="preserve">18.9858474731445</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1481990814209</t>
+    <t xml:space="preserve">19.1482009887695</t>
   </si>
   <si>
     <t xml:space="preserve">18.90944480896</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9476490020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0077247619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0554733276367</t>
+    <t xml:space="preserve">18.9476470947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0077228546143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0554752349854</t>
   </si>
   <si>
     <t xml:space="preserve">20.5329856872559</t>
@@ -1973,16 +1973,16 @@
     <t xml:space="preserve">20.9149932861328</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1509761810303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4374828338623</t>
+    <t xml:space="preserve">20.1509742736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4374809265137</t>
   </si>
   <si>
     <t xml:space="preserve">21.0104961395264</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4880084991455</t>
+    <t xml:space="preserve">21.4880065917969</t>
   </si>
   <si>
     <t xml:space="preserve">19.5779628753662</t>
@@ -1997,13 +1997,13 @@
     <t xml:space="preserve">19.2914562225342</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3392066955566</t>
+    <t xml:space="preserve">19.339204788208</t>
   </si>
   <si>
     <t xml:space="preserve">18.813943862915</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6993389129639</t>
+    <t xml:space="preserve">18.6993408203125</t>
   </si>
   <si>
     <t xml:space="preserve">19.3869571685791</t>
@@ -2018,7 +2018,7 @@
     <t xml:space="preserve">18.240930557251</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7757434844971</t>
+    <t xml:space="preserve">18.7757415771484</t>
   </si>
   <si>
     <t xml:space="preserve">19.9599704742432</t>
@@ -2036,13 +2036,13 @@
     <t xml:space="preserve">21.392505645752</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1537475585938</t>
+    <t xml:space="preserve">21.1537494659424</t>
   </si>
   <si>
     <t xml:space="preserve">21.7745132446289</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6790103912354</t>
+    <t xml:space="preserve">21.679012298584</t>
   </si>
   <si>
     <t xml:space="preserve">21.9177684783936</t>
@@ -2057,7 +2057,7 @@
     <t xml:space="preserve">21.5835094451904</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5807342529297</t>
+    <t xml:space="preserve">20.5807323455811</t>
   </si>
   <si>
     <t xml:space="preserve">20.1032218933105</t>
@@ -2075,7 +2075,7 @@
     <t xml:space="preserve">22.9205417633057</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4430313110352</t>
+    <t xml:space="preserve">22.4430294036865</t>
   </si>
   <si>
     <t xml:space="preserve">22.1565227508545</t>
@@ -2087,16 +2087,16 @@
     <t xml:space="preserve">22.3475284576416</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0582466125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3897304534912</t>
+    <t xml:space="preserve">21.0582447052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3897323608398</t>
   </si>
   <si>
     <t xml:space="preserve">20.2942276000977</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1987247467041</t>
+    <t xml:space="preserve">20.1987266540527</t>
   </si>
   <si>
     <t xml:space="preserve">20.8194904327393</t>
@@ -2120,7 +2120,7 @@
     <t xml:space="preserve">19.8167171478271</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2464790344238</t>
+    <t xml:space="preserve">20.2464771270752</t>
   </si>
   <si>
     <t xml:space="preserve">20.6762371063232</t>
@@ -2129,7 +2129,7 @@
     <t xml:space="preserve">19.7689666748047</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4402561187744</t>
+    <t xml:space="preserve">21.440258026123</t>
   </si>
   <si>
     <t xml:space="preserve">22.6340351104736</t>
@@ -2144,10 +2144,10 @@
     <t xml:space="preserve">22.5862808227539</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8727912902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5385322570801</t>
+    <t xml:space="preserve">22.8727893829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5385303497314</t>
   </si>
   <si>
     <t xml:space="preserve">22.6817855834961</t>
@@ -2156,7 +2156,7 @@
     <t xml:space="preserve">23.0160427093506</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3025493621826</t>
+    <t xml:space="preserve">23.3025512695312</t>
   </si>
   <si>
     <t xml:space="preserve">24.4485759735107</t>
@@ -2165,13 +2165,13 @@
     <t xml:space="preserve">23.7323112487793</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9710636138916</t>
+    <t xml:space="preserve">23.9710655212402</t>
   </si>
   <si>
     <t xml:space="preserve">24.2098217010498</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0665683746338</t>
+    <t xml:space="preserve">24.0665664672852</t>
   </si>
   <si>
     <t xml:space="preserve">24.1143188476562</t>
@@ -2186,19 +2186,19 @@
     <t xml:space="preserve">23.7800598144531</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9233150482178</t>
+    <t xml:space="preserve">23.9233131408691</t>
   </si>
   <si>
     <t xml:space="preserve">25.0693416595459</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5440807342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9260864257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3558464050293</t>
+    <t xml:space="preserve">24.5440788269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9260883331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3558483123779</t>
   </si>
   <si>
     <t xml:space="preserve">25.4035987854004</t>
@@ -2219,16 +2219,16 @@
     <t xml:space="preserve">24.5918292999268</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8305854797363</t>
+    <t xml:space="preserve">24.830587387085</t>
   </si>
   <si>
     <t xml:space="preserve">25.260347366333</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7378578186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7856101989746</t>
+    <t xml:space="preserve">25.7378597259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.785608291626</t>
   </si>
   <si>
     <t xml:space="preserve">26.0721130371094</t>
@@ -2240,13 +2240,13 @@
     <t xml:space="preserve">25.4513492584229</t>
   </si>
   <si>
-    <t xml:space="preserve">25.928861618042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5946025848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6901073455811</t>
+    <t xml:space="preserve">25.9288597106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5946044921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6901054382324</t>
   </si>
   <si>
     <t xml:space="preserve">25.5468521118164</t>
@@ -2261,16 +2261,16 @@
     <t xml:space="preserve">27.0748901367188</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1703929901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6506767272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.321964263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.892204284668</t>
+    <t xml:space="preserve">27.1703910827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6506748199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3219661712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8922023773193</t>
   </si>
   <si>
     <t xml:space="preserve">29.9877071380615</t>
@@ -2279,7 +2279,7 @@
     <t xml:space="preserve">30.1309604644775</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6534481048584</t>
+    <t xml:space="preserve">29.653450012207</t>
   </si>
   <si>
     <t xml:space="preserve">29.510196685791</t>
@@ -2297,7 +2297,7 @@
     <t xml:space="preserve">28.8416805267334</t>
   </si>
   <si>
-    <t xml:space="preserve">29.223690032959</t>
+    <t xml:space="preserve">29.2236919403076</t>
   </si>
   <si>
     <t xml:space="preserve">29.1281871795654</t>
@@ -2318,10 +2318,10 @@
     <t xml:space="preserve">28.3641681671143</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8866596221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2714405059814</t>
+    <t xml:space="preserve">27.8866577148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2714385986328</t>
   </si>
   <si>
     <t xml:space="preserve">27.8389053344727</t>
@@ -2330,7 +2330,7 @@
     <t xml:space="preserve">27.6479034423828</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6029243469238</t>
+    <t xml:space="preserve">28.6029262542725</t>
   </si>
   <si>
     <t xml:space="preserve">28.4119205474854</t>
@@ -2339,7 +2339,7 @@
     <t xml:space="preserve">29.366943359375</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4146919250488</t>
+    <t xml:space="preserve">29.4146938323975</t>
   </si>
   <si>
     <t xml:space="preserve">30.0354595184326</t>
@@ -2357,13 +2357,13 @@
     <t xml:space="preserve">29.7012023925781</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5579471588135</t>
+    <t xml:space="preserve">29.5579490661621</t>
   </si>
   <si>
     <t xml:space="preserve">29.796703338623</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2209167480469</t>
+    <t xml:space="preserve">28.2209148406982</t>
   </si>
   <si>
     <t xml:space="preserve">28.3164176940918</t>
@@ -2375,10 +2375,10 @@
     <t xml:space="preserve">26.9480724334717</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5770206451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.593017578125</t>
+    <t xml:space="preserve">27.5770225524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5930156707764</t>
   </si>
   <si>
     <t xml:space="preserve">28.0124492645264</t>
@@ -2396,7 +2396,7 @@
     <t xml:space="preserve">28.0608291625977</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3994941711426</t>
+    <t xml:space="preserve">28.3994960784912</t>
   </si>
   <si>
     <t xml:space="preserve">28.7381591796875</t>
@@ -2405,7 +2405,7 @@
     <t xml:space="preserve">29.1252059936523</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9800624847412</t>
+    <t xml:space="preserve">28.9800643920898</t>
   </si>
   <si>
     <t xml:space="preserve">27.7705459594727</t>
@@ -2447,19 +2447,19 @@
     <t xml:space="preserve">29.2219676971436</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0284442901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2543544769287</t>
+    <t xml:space="preserve">29.0284423828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2543525695801</t>
   </si>
   <si>
     <t xml:space="preserve">29.705774307251</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0444374084473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9960594177246</t>
+    <t xml:space="preserve">30.0444393157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.996057510376</t>
   </si>
   <si>
     <t xml:space="preserve">28.8349208831787</t>
@@ -2474,7 +2474,7 @@
     <t xml:space="preserve">28.2059707641602</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4962577819824</t>
+    <t xml:space="preserve">28.4962558746338</t>
   </si>
   <si>
     <t xml:space="preserve">27.0932140350342</t>
@@ -2483,7 +2483,7 @@
     <t xml:space="preserve">26.8513107299805</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0772190093994</t>
+    <t xml:space="preserve">26.077220916748</t>
   </si>
   <si>
     <t xml:space="preserve">26.8996906280518</t>
@@ -2507,22 +2507,22 @@
     <t xml:space="preserve">25.3031272888184</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2547454833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1579837799072</t>
+    <t xml:space="preserve">25.2547473907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1579856872559</t>
   </si>
   <si>
     <t xml:space="preserve">24.9160804748535</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4966506958008</t>
+    <t xml:space="preserve">25.4966487884521</t>
   </si>
   <si>
     <t xml:space="preserve">25.3515071868896</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0612239837646</t>
+    <t xml:space="preserve">25.061222076416</t>
   </si>
   <si>
     <t xml:space="preserve">24.7225570678711</t>
@@ -2531,7 +2531,7 @@
     <t xml:space="preserve">24.4806537628174</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6098003387451</t>
+    <t xml:space="preserve">23.6098022460938</t>
   </si>
   <si>
     <t xml:space="preserve">23.0292301177979</t>
@@ -2540,7 +2540,7 @@
     <t xml:space="preserve">22.9324722290039</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1743755340576</t>
+    <t xml:space="preserve">23.174373626709</t>
   </si>
   <si>
     <t xml:space="preserve">22.5938053131104</t>
@@ -2552,7 +2552,7 @@
     <t xml:space="preserve">21.6745719909668</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9164752960205</t>
+    <t xml:space="preserve">21.9164733886719</t>
   </si>
   <si>
     <t xml:space="preserve">21.5294284820557</t>
@@ -2564,16 +2564,16 @@
     <t xml:space="preserve">21.0940017700195</t>
   </si>
   <si>
-    <t xml:space="preserve">20.465051651001</t>
+    <t xml:space="preserve">20.4650535583496</t>
   </si>
   <si>
     <t xml:space="preserve">20.2231483459473</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4166736602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9004783630371</t>
+    <t xml:space="preserve">20.4166717529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9004802703857</t>
   </si>
   <si>
     <t xml:space="preserve">20.8037185668945</t>
@@ -2582,22 +2582,22 @@
     <t xml:space="preserve">20.6101951599121</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6585750579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7069568634033</t>
+    <t xml:space="preserve">20.658576965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7069549560547</t>
   </si>
   <si>
     <t xml:space="preserve">20.7553386688232</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3359069824219</t>
+    <t xml:space="preserve">21.3359050750732</t>
   </si>
   <si>
     <t xml:space="preserve">21.0456218719482</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4490585327148</t>
+    <t xml:space="preserve">19.4490566253662</t>
   </si>
   <si>
     <t xml:space="preserve">19.8361034393311</t>
@@ -2606,7 +2606,7 @@
     <t xml:space="preserve">19.2361812591553</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8878402709961</t>
+    <t xml:space="preserve">18.8878421783447</t>
   </si>
   <si>
     <t xml:space="preserve">18.6362609863281</t>
@@ -2630,13 +2630,13 @@
     <t xml:space="preserve">17.049373626709</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0300197601318</t>
+    <t xml:space="preserve">17.0300216674805</t>
   </si>
   <si>
     <t xml:space="preserve">16.8752021789551</t>
   </si>
   <si>
-    <t xml:space="preserve">18.326623916626</t>
+    <t xml:space="preserve">18.3266258239746</t>
   </si>
   <si>
     <t xml:space="preserve">18.7717266082764</t>
@@ -2648,13 +2648,13 @@
     <t xml:space="preserve">18.5782051086426</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4233856201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1331024169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4974365234375</t>
+    <t xml:space="preserve">18.4233875274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1331005096436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4974384307861</t>
   </si>
   <si>
     <t xml:space="preserve">20.1263866424561</t>
@@ -2663,7 +2663,7 @@
     <t xml:space="preserve">19.9328651428223</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3199100494385</t>
+    <t xml:space="preserve">20.3199119567871</t>
   </si>
   <si>
     <t xml:space="preserve">19.6425800323486</t>
@@ -2678,10 +2678,10 @@
     <t xml:space="preserve">19.1781253814697</t>
   </si>
   <si>
-    <t xml:space="preserve">19.023307800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1974792480469</t>
+    <t xml:space="preserve">19.0233058929443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1974773406982</t>
   </si>
   <si>
     <t xml:space="preserve">18.9071941375732</t>
@@ -2690,7 +2690,7 @@
     <t xml:space="preserve">19.8844833374023</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4006748199463</t>
+    <t xml:space="preserve">19.4006767272949</t>
   </si>
   <si>
     <t xml:space="preserve">19.7877235412598</t>
@@ -2708,7 +2708,7 @@
     <t xml:space="preserve">22.0132369995117</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8357105255127</t>
+    <t xml:space="preserve">22.8357086181641</t>
   </si>
   <si>
     <t xml:space="preserve">22.1583786010742</t>
@@ -2720,19 +2720,19 @@
     <t xml:space="preserve">22.3519020080566</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7229518890381</t>
+    <t xml:space="preserve">21.7229537963867</t>
   </si>
   <si>
     <t xml:space="preserve">21.5778102874756</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4326667785645</t>
+    <t xml:space="preserve">21.4326686859131</t>
   </si>
   <si>
     <t xml:space="preserve">22.061616897583</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4970436096191</t>
+    <t xml:space="preserve">22.4970455169678</t>
   </si>
   <si>
     <t xml:space="preserve">22.2551403045654</t>
@@ -2744,7 +2744,7 @@
     <t xml:space="preserve">21.6261901855469</t>
   </si>
   <si>
-    <t xml:space="preserve">21.771333694458</t>
+    <t xml:space="preserve">21.7713317871094</t>
   </si>
   <si>
     <t xml:space="preserve">22.3035202026367</t>
@@ -2753,10 +2753,10 @@
     <t xml:space="preserve">22.8840885162354</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7873268127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9648551940918</t>
+    <t xml:space="preserve">22.7873287200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9648571014404</t>
   </si>
   <si>
     <t xml:space="preserve">20.948860168457</t>
@@ -2771,7 +2771,7 @@
     <t xml:space="preserve">20.1747703552246</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5134353637695</t>
+    <t xml:space="preserve">20.5134334564209</t>
   </si>
   <si>
     <t xml:space="preserve">20.0296268463135</t>
@@ -2780,13 +2780,13 @@
     <t xml:space="preserve">22.9808521270752</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1259918212891</t>
+    <t xml:space="preserve">23.1259937286377</t>
   </si>
   <si>
     <t xml:space="preserve">21.3842868804932</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8520984649658</t>
+    <t xml:space="preserve">20.8520965576172</t>
   </si>
   <si>
     <t xml:space="preserve">20.5618133544922</t>
@@ -3417,6 +3417,9 @@
   </si>
   <si>
     <t xml:space="preserve">38.7000007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.75</t>
   </si>
 </sst>
 </file>
@@ -69275,7 +69278,7 @@
     </row>
     <row r="2521">
       <c r="A2521" s="1" t="n">
-        <v>45988.6911342593</v>
+        <v>45988.3333333333</v>
       </c>
       <c r="B2521" t="n">
         <v>16742</v>
@@ -69296,6 +69299,32 @@
         <v>1134</v>
       </c>
       <c r="H2521" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2522">
+      <c r="A2522" s="1" t="n">
+        <v>45989.6912037037</v>
+      </c>
+      <c r="B2522" t="n">
+        <v>12290</v>
+      </c>
+      <c r="C2522" t="n">
+        <v>39.7999992370605</v>
+      </c>
+      <c r="D2522" t="n">
+        <v>38.8499984741211</v>
+      </c>
+      <c r="E2522" t="n">
+        <v>39</v>
+      </c>
+      <c r="F2522" t="n">
+        <v>39.75</v>
+      </c>
+      <c r="G2522" t="s">
+        <v>1135</v>
+      </c>
+      <c r="H2522" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LUVE.MI.xlsx
+++ b/data/LUVE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1136" uniqueCount="1136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1137" uniqueCount="1137">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,85 +44,85 @@
     <t xml:space="preserve">LUVE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3170337677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28383159637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09292221069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19667911529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07632064819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15102672576904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17177963256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03896903991699</t>
+    <t xml:space="preserve">8.31703472137451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28383255004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09292316436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19667816162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07631969451904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15102481842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17177677154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03896999359131</t>
   </si>
   <si>
     <t xml:space="preserve">8.08462238311768</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06802272796631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96841669082642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01821804046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99746751785278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91861534118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91446304321289</t>
+    <t xml:space="preserve">8.06802082061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96841621398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01821994781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99746704101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91861295700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91446495056152</t>
   </si>
   <si>
     <t xml:space="preserve">7.91031217575073</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88541126251221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87711048126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85220956802368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64884996414185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71940326690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7028021812439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69035291671753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61979866027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55754470825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55339384078979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.636399269104</t>
+    <t xml:space="preserve">7.88541030883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87711000442505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85221195220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64884948730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7194037437439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70280170440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69035196304321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61979722976685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55754375457764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55339431762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63639831542969</t>
   </si>
   <si>
     <t xml:space="preserve">7.76920509338379</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">7.80240678787231</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93521451950073</t>
+    <t xml:space="preserve">7.93521404266357</t>
   </si>
   <si>
     <t xml:space="preserve">8.10122299194336</t>
@@ -143,40 +143,40 @@
     <t xml:space="preserve">8.18422698974609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13442611694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00161743164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96011543273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21742725372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35853672027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32533550262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29213237762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20082855224609</t>
+    <t xml:space="preserve">8.13442516326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00161838531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96011686325073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21743011474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35853576660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3253345489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2921314239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20082759857178</t>
   </si>
   <si>
     <t xml:space="preserve">8.15932559967041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30336380004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36267280578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43045520782471</t>
+    <t xml:space="preserve">8.30336570739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36267471313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43045616149902</t>
   </si>
   <si>
     <t xml:space="preserve">8.15085315704346</t>
@@ -185,13 +185,13 @@
     <t xml:space="preserve">8.17627143859863</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2059268951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13390922546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11696147918701</t>
+    <t xml:space="preserve">8.20592594146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13390827178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1169605255127</t>
   </si>
   <si>
     <t xml:space="preserve">8.21863555908203</t>
@@ -200,70 +200,70 @@
     <t xml:space="preserve">8.21016216278076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21439838409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20168972015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26100063323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09154415130615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10848903656006</t>
+    <t xml:space="preserve">8.21439933776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20169067382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26099967956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09154319763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10848808288574</t>
   </si>
   <si>
     <t xml:space="preserve">8.04917907714844</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96444988250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92208766937256</t>
+    <t xml:space="preserve">7.9644513130188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9220871925354</t>
   </si>
   <si>
     <t xml:space="preserve">7.87972354888916</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83735847473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12543392181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93479633331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75262928009033</t>
+    <t xml:space="preserve">7.8373589515686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12543487548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93479537963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75263071060181</t>
   </si>
   <si>
     <t xml:space="preserve">7.71026611328125</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93903303146362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81194067001343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79499530792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62553834915161</t>
+    <t xml:space="preserve">7.93903350830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8119421005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79499435424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62553882598877</t>
   </si>
   <si>
     <t xml:space="preserve">7.66790294647217</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84583234786987</t>
+    <t xml:space="preserve">7.84583187103271</t>
   </si>
   <si>
     <t xml:space="preserve">8.19321727752686</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47281932830811</t>
+    <t xml:space="preserve">8.47282028198242</t>
   </si>
   <si>
     <t xml:space="preserve">8.51518440246582</t>
@@ -272,25 +272,25 @@
     <t xml:space="preserve">8.52365875244141</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59991073608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78631496429443</t>
+    <t xml:space="preserve">8.59991264343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78631591796875</t>
   </si>
   <si>
     <t xml:space="preserve">8.71853256225586</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50671291351318</t>
+    <t xml:space="preserve">8.50671100616455</t>
   </si>
   <si>
     <t xml:space="preserve">8.540602684021</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46858501434326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46434783935547</t>
+    <t xml:space="preserve">8.46858310699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46434879302979</t>
   </si>
   <si>
     <t xml:space="preserve">8.55754852294922</t>
@@ -299,16 +299,16 @@
     <t xml:space="preserve">8.57449436187744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81173324584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7270040512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64227676391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89646148681641</t>
+    <t xml:space="preserve">8.81173229217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72700500488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64227771759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89646244049072</t>
   </si>
   <si>
     <t xml:space="preserve">9.02355194091797</t>
@@ -317,22 +317,22 @@
     <t xml:space="preserve">9.09980869293213</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06591606140137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10828018188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27773952484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19300842285156</t>
+    <t xml:space="preserve">9.06591701507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1082820892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27773761749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1930103302002</t>
   </si>
   <si>
     <t xml:space="preserve">9.18453788757324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07439041137695</t>
+    <t xml:space="preserve">9.07439136505127</t>
   </si>
   <si>
     <t xml:space="preserve">9.09133529663086</t>
@@ -347,43 +347,43 @@
     <t xml:space="preserve">9.12522888183594</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60817718505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40483093261719</t>
+    <t xml:space="preserve">9.60817813873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4048318862915</t>
   </si>
   <si>
     <t xml:space="preserve">9.48955821990967</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38788509368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53192329406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48108386993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44719409942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54039573669434</t>
+    <t xml:space="preserve">9.38788414001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5319242477417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4810848236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4471960067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54039478302002</t>
   </si>
   <si>
     <t xml:space="preserve">9.57428741455078</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47261333465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41330432891846</t>
+    <t xml:space="preserve">9.47261428833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41330337524414</t>
   </si>
   <si>
     <t xml:space="preserve">9.42177581787109</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51497745513916</t>
+    <t xml:space="preserve">9.51497650146484</t>
   </si>
   <si>
     <t xml:space="preserve">9.56581401824951</t>
@@ -392,7 +392,7 @@
     <t xml:space="preserve">9.74374294281006</t>
   </si>
   <si>
-    <t xml:space="preserve">10.065710067749</t>
+    <t xml:space="preserve">10.0657091140747</t>
   </si>
   <si>
     <t xml:space="preserve">10.2521133422852</t>
@@ -401,7 +401,7 @@
     <t xml:space="preserve">10.1334924697876</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99792766571045</t>
+    <t xml:space="preserve">9.99792957305908</t>
   </si>
   <si>
     <t xml:space="preserve">9.95556449890137</t>
@@ -410,37 +410,37 @@
     <t xml:space="preserve">9.98098087310791</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88778209686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91319942474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.014874458313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1589107513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0402936935425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70137882232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73527050018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70985126495361</t>
+    <t xml:space="preserve">9.88778114318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91319751739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0148735046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1589117050171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0402927398682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70137786865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73526954650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70985221862793</t>
   </si>
   <si>
     <t xml:space="preserve">10.0826559066772</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86236381530762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1250200271606</t>
+    <t xml:space="preserve">9.8623628616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1250190734863</t>
   </si>
   <si>
     <t xml:space="preserve">10.2944774627686</t>
@@ -449,7 +449,7 @@
     <t xml:space="preserve">10.4808778762817</t>
   </si>
   <si>
-    <t xml:space="preserve">10.531717300415</t>
+    <t xml:space="preserve">10.5317153930664</t>
   </si>
   <si>
     <t xml:space="preserve">10.5147705078125</t>
@@ -458,25 +458,25 @@
     <t xml:space="preserve">10.802845954895</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9129934310913</t>
+    <t xml:space="preserve">10.912992477417</t>
   </si>
   <si>
     <t xml:space="preserve">10.8621549606323</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0146656036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0570316314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2773246765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4383058547974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6586017608643</t>
+    <t xml:space="preserve">11.014666557312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0570306777954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.277325630188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.438307762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6586008071899</t>
   </si>
   <si>
     <t xml:space="preserve">11.5823440551758</t>
@@ -488,40 +488,40 @@
     <t xml:space="preserve">11.5908184051514</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7009658813477</t>
+    <t xml:space="preserve">11.7009649276733</t>
   </si>
   <si>
     <t xml:space="preserve">11.7772197723389</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8111114501953</t>
+    <t xml:space="preserve">11.811110496521</t>
   </si>
   <si>
     <t xml:space="preserve">11.8365306854248</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6670722961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5992918014526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5230369567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6077632904053</t>
+    <t xml:space="preserve">11.6670742034912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.599289894104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5230350494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6077651977539</t>
   </si>
   <si>
     <t xml:space="preserve">11.6263799667358</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7297248840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6952772140503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6780548095703</t>
+    <t xml:space="preserve">11.7297258377075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6952781677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.678053855896</t>
   </si>
   <si>
     <t xml:space="preserve">11.7986240386963</t>
@@ -533,10 +533,10 @@
     <t xml:space="preserve">11.9105806350708</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0655994415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3153514862061</t>
+    <t xml:space="preserve">12.0656003952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3153533935547</t>
   </si>
   <si>
     <t xml:space="preserve">12.3584127426147</t>
@@ -545,55 +545,55 @@
     <t xml:space="preserve">12.0569877624512</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1431093215942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9967031478882</t>
+    <t xml:space="preserve">12.1431083679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9967041015625</t>
   </si>
   <si>
     <t xml:space="preserve">11.8416843414307</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7555637359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7125034332275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8502979278564</t>
+    <t xml:space="preserve">11.7555618286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7125015258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8502969741821</t>
   </si>
   <si>
     <t xml:space="preserve">11.9191932678223</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9622535705566</t>
+    <t xml:space="preserve">11.9622554779053</t>
   </si>
   <si>
     <t xml:space="preserve">12.0397644042969</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0483751296997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7900123596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0311527252197</t>
+    <t xml:space="preserve">12.048376083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7900094985962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0311508178711</t>
   </si>
   <si>
     <t xml:space="preserve">11.9450302124023</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8158464431763</t>
+    <t xml:space="preserve">11.8158483505249</t>
   </si>
   <si>
     <t xml:space="preserve">11.8933582305908</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8761320114136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8244590759277</t>
+    <t xml:space="preserve">11.8761339187622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8244600296021</t>
   </si>
   <si>
     <t xml:space="preserve">11.8675203323364</t>
@@ -620,7 +620,7 @@
     <t xml:space="preserve">11.5747079849243</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5316486358643</t>
+    <t xml:space="preserve">11.5316476821899</t>
   </si>
   <si>
     <t xml:space="preserve">11.5230360031128</t>
@@ -641,7 +641,7 @@
     <t xml:space="preserve">11.1957750320435</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1871633529663</t>
+    <t xml:space="preserve">11.187162399292</t>
   </si>
   <si>
     <t xml:space="preserve">11.1096534729004</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">11.0235319137573</t>
   </si>
   <si>
-    <t xml:space="preserve">11.083815574646</t>
+    <t xml:space="preserve">11.0838165283203</t>
   </si>
   <si>
     <t xml:space="preserve">11.1354894638062</t>
@@ -674,16 +674,16 @@
     <t xml:space="preserve">11.2043867111206</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3163442611694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4541387557983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5402593612671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.411078453064</t>
+    <t xml:space="preserve">11.3163461685181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.454137802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5402603149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4110774993896</t>
   </si>
   <si>
     <t xml:space="preserve">11.2905073165894</t>
@@ -692,88 +692,88 @@
     <t xml:space="preserve">11.1613264083862</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2646732330322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1527128219604</t>
+    <t xml:space="preserve">11.2646722793579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1527137756348</t>
   </si>
   <si>
     <t xml:space="preserve">11.0407562255859</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4196901321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2216100692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2388353347778</t>
+    <t xml:space="preserve">11.4196891784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2216110229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2388362884521</t>
   </si>
   <si>
     <t xml:space="preserve">11.3421812057495</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9546346664429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.96324634552</t>
+    <t xml:space="preserve">10.9546337127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9632453918457</t>
   </si>
   <si>
     <t xml:space="preserve">11.0063066482544</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0924282073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74032306671143</t>
+    <t xml:space="preserve">11.0924291610718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74032497406006</t>
   </si>
   <si>
     <t xml:space="preserve">9.0169038772583</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21498203277588</t>
+    <t xml:space="preserve">9.21498394012451</t>
   </si>
   <si>
     <t xml:space="preserve">9.37861442565918</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49057197570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50779438018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59391689300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60252857208252</t>
+    <t xml:space="preserve">9.49057292938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5077953338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59391784667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60253047943115</t>
   </si>
   <si>
     <t xml:space="preserve">9.6886510848999</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56808280944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39583778381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34416484832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25804328918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30110454559326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41306400299072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28388023376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24081897735596</t>
+    <t xml:space="preserve">9.56808090209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39583683013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34416675567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2580451965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30110549926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41306304931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28388118743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24081993103027</t>
   </si>
   <si>
     <t xml:space="preserve">9.12886142730713</t>
@@ -782,58 +782,58 @@
     <t xml:space="preserve">9.02551460266113</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20637130737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26665592193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69726371765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65420150756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66281414031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64559173583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67142581939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75754833221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71448707580566</t>
+    <t xml:space="preserve">9.20637226104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26665687561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69726276397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65420246124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66281604766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64559078216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67142677307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75754928588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71448802947998</t>
   </si>
   <si>
     <t xml:space="preserve">9.09441375732422</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9393949508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14608764648438</t>
+    <t xml:space="preserve">8.93939590454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14608669281006</t>
   </si>
   <si>
     <t xml:space="preserve">9.12024974822998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83505725860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73171138763428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90395450592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77477359771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53363037109375</t>
+    <t xml:space="preserve">9.83505630493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73171234130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90395355224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77477264404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53363227844238</t>
   </si>
   <si>
     <t xml:space="preserve">9.49918460845947</t>
@@ -842,13 +842,13 @@
     <t xml:space="preserve">9.57669258117676</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58530426025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47334766387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43028736114502</t>
+    <t xml:space="preserve">9.58530521392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47334671020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4302864074707</t>
   </si>
   <si>
     <t xml:space="preserve">9.54224586486816</t>
@@ -857,61 +857,61 @@
     <t xml:space="preserve">9.1719217300415</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23220825195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55947017669678</t>
+    <t xml:space="preserve">9.23220729827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55946922302246</t>
   </si>
   <si>
     <t xml:space="preserve">9.51640796661377</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86089324951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95662021636963</t>
+    <t xml:space="preserve">9.8608922958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95661926269531</t>
   </si>
   <si>
     <t xml:space="preserve">8.91355991363525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08580207824707</t>
+    <t xml:space="preserve">9.08580112457275</t>
   </si>
   <si>
     <t xml:space="preserve">9.0427417755127</t>
   </si>
   <si>
-    <t xml:space="preserve">8.999680519104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8274393081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69825553894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87049770355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78437614440918</t>
+    <t xml:space="preserve">8.99967956542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82743740081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69825458526611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87049865722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7843770980835</t>
   </si>
   <si>
     <t xml:space="preserve">8.7413158416748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61213397979736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59490966796875</t>
+    <t xml:space="preserve">8.61213493347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59490871429443</t>
   </si>
   <si>
     <t xml:space="preserve">8.65519523620605</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45711612701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06314373016357</t>
+    <t xml:space="preserve">8.45711517333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06314468383789</t>
   </si>
   <si>
     <t xml:space="preserve">9.10714054107666</t>
@@ -923,7 +923,7 @@
     <t xml:space="preserve">8.97515296936035</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93115711212158</t>
+    <t xml:space="preserve">8.93115615844727</t>
   </si>
   <si>
     <t xml:space="preserve">8.88716220855713</t>
@@ -932,28 +932,28 @@
     <t xml:space="preserve">8.84316539764404</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76397323608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48240089416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71117687225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62318801879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58798885345459</t>
+    <t xml:space="preserve">8.76397228240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48239994049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71117782592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62318706512451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58798980712891</t>
   </si>
   <si>
     <t xml:space="preserve">8.6583833694458</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60558700561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7287769317627</t>
+    <t xml:space="preserve">8.60558795928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72877597808838</t>
   </si>
   <si>
     <t xml:space="preserve">8.69357967376709</t>
@@ -965,31 +965,31 @@
     <t xml:space="preserve">8.53519439697266</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44720363616943</t>
+    <t xml:space="preserve">8.44720268249512</t>
   </si>
   <si>
     <t xml:space="preserve">8.27121925354004</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32401561737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28881645202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78157043457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64078235626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79916858673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67598152160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23912906646729</t>
+    <t xml:space="preserve">8.32401466369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.288818359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.781569480896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64078330993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79916954040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67597961425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23912811279297</t>
   </si>
   <si>
     <t xml:space="preserve">9.37111568450928</t>
@@ -998,31 +998,31 @@
     <t xml:space="preserve">9.32711982727051</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1951322555542</t>
+    <t xml:space="preserve">9.19513130187988</t>
   </si>
   <si>
     <t xml:space="preserve">9.15113639831543</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46480178833008</t>
+    <t xml:space="preserve">8.46480083465576</t>
   </si>
   <si>
     <t xml:space="preserve">8.41200542449951</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49999809265137</t>
+    <t xml:space="preserve">8.49999713897705</t>
   </si>
   <si>
     <t xml:space="preserve">8.34161186218262</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23602294921875</t>
+    <t xml:space="preserve">8.23602199554443</t>
   </si>
   <si>
     <t xml:space="preserve">8.30641555786133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13043117523193</t>
+    <t xml:space="preserve">8.13043212890625</t>
   </si>
   <si>
     <t xml:space="preserve">8.1832275390625</t>
@@ -1034,19 +1034,19 @@
     <t xml:space="preserve">8.21842575073242</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25362014770508</t>
+    <t xml:space="preserve">8.25362110137939</t>
   </si>
   <si>
     <t xml:space="preserve">8.37680912017822</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5175952911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28312301635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41511154174805</t>
+    <t xml:space="preserve">8.51759624481201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28312492370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41511058807373</t>
   </si>
   <si>
     <t xml:space="preserve">9.63509082794189</t>
@@ -1064,10 +1064,10 @@
     <t xml:space="preserve">10.1630411148071</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2070379257202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3390245437622</t>
+    <t xml:space="preserve">10.2070369720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3390235900879</t>
   </si>
   <si>
     <t xml:space="preserve">10.2950277328491</t>
@@ -1085,37 +1085,37 @@
     <t xml:space="preserve">10.0750484466553</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5150079727173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6498165130615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4700708389282</t>
+    <t xml:space="preserve">10.5150060653687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6498155593872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4700717926025</t>
   </si>
   <si>
     <t xml:space="preserve">10.694751739502</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6048793792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.380199432373</t>
+    <t xml:space="preserve">10.6048803329468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3802003860474</t>
   </si>
   <si>
     <t xml:space="preserve">10.2453918457031</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0656480789185</t>
+    <t xml:space="preserve">10.0656490325928</t>
   </si>
   <si>
     <t xml:space="preserve">10.4251356124878</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3352651596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2903280258179</t>
+    <t xml:space="preserve">10.3352632522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2903270721436</t>
   </si>
   <si>
     <t xml:space="preserve">10.2004566192627</t>
@@ -1130,10 +1130,10 @@
     <t xml:space="preserve">9.93084049224854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88590335845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1555204391479</t>
+    <t xml:space="preserve">9.88590526580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1555213928223</t>
   </si>
   <si>
     <t xml:space="preserve">10.020712852478</t>
@@ -1145,22 +1145,22 @@
     <t xml:space="preserve">9.70616149902344</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34667301177979</t>
+    <t xml:space="preserve">9.3466739654541</t>
   </si>
   <si>
     <t xml:space="preserve">9.30173778533936</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39161014556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48148059844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61628913879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52641773223877</t>
+    <t xml:space="preserve">9.39160919189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48148155212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61628818511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52641677856445</t>
   </si>
   <si>
     <t xml:space="preserve">9.43654537200928</t>
@@ -1169,16 +1169,16 @@
     <t xml:space="preserve">9.12199401855469</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03212261199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16692924499512</t>
+    <t xml:space="preserve">9.0321216583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16693019866943</t>
   </si>
   <si>
     <t xml:space="preserve">9.07705783843994</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25680065155029</t>
+    <t xml:space="preserve">9.25680255889893</t>
   </si>
   <si>
     <t xml:space="preserve">8.98718643188477</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">9.5713529586792</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66122531890869</t>
+    <t xml:space="preserve">9.66122627258301</t>
   </si>
   <si>
     <t xml:space="preserve">9.79603290557861</t>
@@ -1196,22 +1196,22 @@
     <t xml:space="preserve">10.9643669128418</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4586639404297</t>
+    <t xml:space="preserve">11.4586620330811</t>
   </si>
   <si>
     <t xml:space="preserve">11.5035991668701</t>
   </si>
   <si>
-    <t xml:space="preserve">11.233983039856</t>
+    <t xml:space="preserve">11.2339820861816</t>
   </si>
   <si>
     <t xml:space="preserve">11.1441106796265</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9194307327271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8744955062866</t>
+    <t xml:space="preserve">10.9194316864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8744964599609</t>
   </si>
   <si>
     <t xml:space="preserve">11.0093030929565</t>
@@ -1220,7 +1220,7 @@
     <t xml:space="preserve">11.2789192199707</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4137258529663</t>
+    <t xml:space="preserve">11.4137268066406</t>
   </si>
   <si>
     <t xml:space="preserve">11.5485334396362</t>
@@ -1235,25 +1235,25 @@
     <t xml:space="preserve">11.9080219268799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.132700920105</t>
+    <t xml:space="preserve">12.1326999664307</t>
   </si>
   <si>
     <t xml:space="preserve">11.9978942871094</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8181505203247</t>
+    <t xml:space="preserve">11.8181495666504</t>
   </si>
   <si>
     <t xml:space="preserve">11.593469619751</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3124446868896</t>
+    <t xml:space="preserve">12.312445640564</t>
   </si>
   <si>
     <t xml:space="preserve">12.5820608139038</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9415483474731</t>
+    <t xml:space="preserve">12.9415473937988</t>
   </si>
   <si>
     <t xml:space="preserve">12.8067398071289</t>
@@ -1262,31 +1262,31 @@
     <t xml:space="preserve">12.7618045806885</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0763559341431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4472532272339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5371236801147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2675094604492</t>
+    <t xml:space="preserve">13.0763549804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4472522735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5371246337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2675085067749</t>
   </si>
   <si>
     <t xml:space="preserve">12.4023180007935</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6269979476929</t>
+    <t xml:space="preserve">12.6269969940186</t>
   </si>
   <si>
     <t xml:space="preserve">12.671932220459</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8966121673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7282781600952</t>
+    <t xml:space="preserve">12.8966131210327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7282791137695</t>
   </si>
   <si>
     <t xml:space="preserve">10.7846231460571</t>
@@ -1298,28 +1298,28 @@
     <t xml:space="preserve">8.89731407165527</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98062086105347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81885194778442</t>
+    <t xml:space="preserve">7.98062181472778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81885147094727</t>
   </si>
   <si>
     <t xml:space="preserve">7.53126192092896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89074993133545</t>
+    <t xml:space="preserve">7.89074945449829</t>
   </si>
   <si>
     <t xml:space="preserve">8.53782653808594</t>
   </si>
   <si>
-    <t xml:space="preserve">7.962646484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44795417785645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60972499847412</t>
+    <t xml:space="preserve">7.96264600753784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44795513153076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6097240447998</t>
   </si>
   <si>
     <t xml:space="preserve">8.66364765167236</t>
@@ -1331,28 +1331,28 @@
     <t xml:space="preserve">9.21186637878418</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93848991394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80045604705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89247894287109</t>
+    <t xml:space="preserve">9.93848896026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80045509338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89247798919678</t>
   </si>
   <si>
     <t xml:space="preserve">9.66242027282715</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70843124389648</t>
+    <t xml:space="preserve">9.7084321975708</t>
   </si>
   <si>
     <t xml:space="preserve">9.84646606445312</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1225357055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75444316864014</t>
+    <t xml:space="preserve">10.1225347518921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75444412231445</t>
   </si>
   <si>
     <t xml:space="preserve">10.3986053466797</t>
@@ -1361,10 +1361,10 @@
     <t xml:space="preserve">10.3065814971924</t>
   </si>
   <si>
-    <t xml:space="preserve">10.720685005188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5826501846313</t>
+    <t xml:space="preserve">10.7206840515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5826511383057</t>
   </si>
   <si>
     <t xml:space="preserve">10.8587198257446</t>
@@ -1373,34 +1373,34 @@
     <t xml:space="preserve">10.6746740341187</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9967546463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.628662109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.766697883606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4906282424927</t>
+    <t xml:space="preserve">10.9967555999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6286630630493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7666959762573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4906272888184</t>
   </si>
   <si>
     <t xml:space="preserve">11.1347894668579</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3188352584839</t>
+    <t xml:space="preserve">11.3188343048096</t>
   </si>
   <si>
     <t xml:space="preserve">11.5028820037842</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1807994842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0427656173706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2728233337402</t>
+    <t xml:space="preserve">11.1808004379272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0427665710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2728242874146</t>
   </si>
   <si>
     <t xml:space="preserve">10.9507417678833</t>
@@ -1409,22 +1409,22 @@
     <t xml:space="preserve">11.0887775421143</t>
   </si>
   <si>
-    <t xml:space="preserve">10.812707901001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9047317504883</t>
+    <t xml:space="preserve">10.8127088546753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9047327041626</t>
   </si>
   <si>
     <t xml:space="preserve">11.4108581542969</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4568700790405</t>
+    <t xml:space="preserve">11.4568691253662</t>
   </si>
   <si>
     <t xml:space="preserve">11.2268123626709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3648481369019</t>
+    <t xml:space="preserve">11.3648471832275</t>
   </si>
   <si>
     <t xml:space="preserve">11.5488929748535</t>
@@ -1433,16 +1433,16 @@
     <t xml:space="preserve">11.5949039459229</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6869277954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9629974365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7789516448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0090093612671</t>
+    <t xml:space="preserve">11.6869268417358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9629964828491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7789497375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0090074539185</t>
   </si>
   <si>
     <t xml:space="preserve">12.1010313034058</t>
@@ -1451,7 +1451,7 @@
     <t xml:space="preserve">11.7329397201538</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8249616622925</t>
+    <t xml:space="preserve">11.8249626159668</t>
   </si>
   <si>
     <t xml:space="preserve">12.0550193786621</t>
@@ -1463,55 +1463,55 @@
     <t xml:space="preserve">11.9169845581055</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6409158706665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1470422744751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6991806030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7912034988403</t>
+    <t xml:space="preserve">11.6409168243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1470432281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6991815567017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7912044525146</t>
   </si>
   <si>
     <t xml:space="preserve">13.0672731399536</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8832273483276</t>
+    <t xml:space="preserve">12.883228302002</t>
   </si>
   <si>
     <t xml:space="preserve">12.9292392730713</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2053089141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2513198852539</t>
+    <t xml:space="preserve">13.2053079605103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2513189315796</t>
   </si>
   <si>
     <t xml:space="preserve">13.1132850646973</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1592960357666</t>
+    <t xml:space="preserve">13.1592969894409</t>
   </si>
   <si>
     <t xml:space="preserve">13.3893537521362</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2973308563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9752521514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7114343643188</t>
+    <t xml:space="preserve">13.2973299026489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9752511978149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7114353179932</t>
   </si>
   <si>
     <t xml:space="preserve">13.4353656768799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5151348114014</t>
+    <t xml:space="preserve">12.5151357650757</t>
   </si>
   <si>
     <t xml:space="preserve">12.3770999908447</t>
@@ -1520,16 +1520,16 @@
     <t xml:space="preserve">12.837215423584</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7451934814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.653169631958</t>
+    <t xml:space="preserve">12.745192527771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6531686782837</t>
   </si>
   <si>
     <t xml:space="preserve">13.3433427810669</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6194114685059</t>
+    <t xml:space="preserve">13.6194124221802</t>
   </si>
   <si>
     <t xml:space="preserve">13.8494691848755</t>
@@ -1538,19 +1538,19 @@
     <t xml:space="preserve">13.9414920806885</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1715497970581</t>
+    <t xml:space="preserve">14.1715507507324</t>
   </si>
   <si>
     <t xml:space="preserve">14.3555965423584</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1255378723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.493631362915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7236881256104</t>
+    <t xml:space="preserve">14.1255388259888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4936294555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.723687171936</t>
   </si>
   <si>
     <t xml:space="preserve">14.677677154541</t>
@@ -1562,13 +1562,13 @@
     <t xml:space="preserve">14.861722946167</t>
   </si>
   <si>
-    <t xml:space="preserve">15.045768737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5396423339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6316652297974</t>
+    <t xml:space="preserve">15.0457696914673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5396413803101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.631664276123</t>
   </si>
   <si>
     <t xml:space="preserve">14.4476194381714</t>
@@ -1580,37 +1580,37 @@
     <t xml:space="preserve">13.9875040054321</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3095855712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6654233932495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8034563064575</t>
+    <t xml:space="preserve">14.3095846176147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6654224395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8034572601318</t>
   </si>
   <si>
     <t xml:space="preserve">13.5734004974365</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7574462890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.95374584198</t>
+    <t xml:space="preserve">13.7574453353882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9537448883057</t>
   </si>
   <si>
     <t xml:space="preserve">14.0335140228271</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4269781112671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3801374435425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.473819732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7080230712891</t>
+    <t xml:space="preserve">14.4269771575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3801383972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4738187789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7080240249634</t>
   </si>
   <si>
     <t xml:space="preserve">14.8485460281372</t>
@@ -1625,7 +1625,7 @@
     <t xml:space="preserve">14.8953857421875</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9422283172607</t>
+    <t xml:space="preserve">14.9422273635864</t>
   </si>
   <si>
     <t xml:space="preserve">15.1764316558838</t>
@@ -1634,25 +1634,25 @@
     <t xml:space="preserve">15.1295900344849</t>
   </si>
   <si>
-    <t xml:space="preserve">14.989068031311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6611804962158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3169546127319</t>
+    <t xml:space="preserve">14.9890689849854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6611814498901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3169555664062</t>
   </si>
   <si>
     <t xml:space="preserve">14.7548637390137</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8017053604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2232713699341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5043172836304</t>
+    <t xml:space="preserve">14.8017044067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2232723236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5043182373047</t>
   </si>
   <si>
     <t xml:space="preserve">16.0664081573486</t>
@@ -1661,46 +1661,46 @@
     <t xml:space="preserve">15.6916809082031</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7385206222534</t>
+    <t xml:space="preserve">15.7385215759277</t>
   </si>
   <si>
     <t xml:space="preserve">15.9727249145508</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9258842468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7853631973267</t>
+    <t xml:space="preserve">15.9258861541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7853622436523</t>
   </si>
   <si>
     <t xml:space="preserve">16.1132488250732</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8322038650513</t>
+    <t xml:space="preserve">15.8322019577026</t>
   </si>
   <si>
     <t xml:space="preserve">16.5348148345947</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8627014160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1437454223633</t>
+    <t xml:space="preserve">16.8627033233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1437473297119</t>
   </si>
   <si>
     <t xml:space="preserve">16.581657409668</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2069282531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.284273147583</t>
+    <t xml:space="preserve">16.2069301605225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2842712402344</t>
   </si>
   <si>
     <t xml:space="preserve">17.7995185852051</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4716300964355</t>
+    <t xml:space="preserve">17.4716320037842</t>
   </si>
   <si>
     <t xml:space="preserve">16.8158626556396</t>
@@ -1724,7 +1724,7 @@
     <t xml:space="preserve">18.5489711761475</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7363376617432</t>
+    <t xml:space="preserve">18.7363357543945</t>
   </si>
   <si>
     <t xml:space="preserve">18.923698425293</t>
@@ -1733,7 +1733,7 @@
     <t xml:space="preserve">19.7668342590332</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5794696807861</t>
+    <t xml:space="preserve">19.5794677734375</t>
   </si>
   <si>
     <t xml:space="preserve">19.2047443389893</t>
@@ -1754,19 +1754,19 @@
     <t xml:space="preserve">19.8605155944824</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3289241790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9846954345703</t>
+    <t xml:space="preserve">20.3289222717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9846935272217</t>
   </si>
   <si>
     <t xml:space="preserve">21.2657413482666</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0783748626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.453104019165</t>
+    <t xml:space="preserve">21.0783767700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4531059265137</t>
   </si>
   <si>
     <t xml:space="preserve">20.7973327636719</t>
@@ -1775,16 +1775,16 @@
     <t xml:space="preserve">21.8278293609619</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1088752746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7341499328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0151920318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.296236038208</t>
+    <t xml:space="preserve">22.1088771820068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7341480255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.015193939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2962379455566</t>
   </si>
   <si>
     <t xml:space="preserve">22.4836025238037</t>
@@ -1793,7 +1793,7 @@
     <t xml:space="preserve">21.6404685974121</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5467853546143</t>
+    <t xml:space="preserve">21.5467834472656</t>
   </si>
   <si>
     <t xml:space="preserve">20.2352428436279</t>
@@ -1808,7 +1808,7 @@
     <t xml:space="preserve">20.6099681854248</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9215145111084</t>
+    <t xml:space="preserve">21.9215126037598</t>
   </si>
   <si>
     <t xml:space="preserve">22.7646465301514</t>
@@ -1823,19 +1823,19 @@
     <t xml:space="preserve">20.7036514282227</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3594207763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5162868499756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0478763580322</t>
+    <t xml:space="preserve">21.3594226837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.516284942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0478782653809</t>
   </si>
   <si>
     <t xml:space="preserve">22.6709671020508</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2025585174561</t>
+    <t xml:space="preserve">22.2025566101074</t>
   </si>
   <si>
     <t xml:space="preserve">22.3899211883545</t>
@@ -1847,13 +1847,13 @@
     <t xml:space="preserve">20.4226055145264</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8910160064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3921070098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8300170898438</t>
+    <t xml:space="preserve">20.8910140991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3921089172363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8300189971924</t>
   </si>
   <si>
     <t xml:space="preserve">18.361608505249</t>
@@ -1862,22 +1862,22 @@
     <t xml:space="preserve">16.9563827514648</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6589946746826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7526798248291</t>
+    <t xml:space="preserve">17.6589965820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7526779174805</t>
   </si>
   <si>
     <t xml:space="preserve">17.377950668335</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8931999206543</t>
+    <t xml:space="preserve">17.8932018280029</t>
   </si>
   <si>
     <t xml:space="preserve">17.9400405883789</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2679271697998</t>
+    <t xml:space="preserve">18.2679252624512</t>
   </si>
   <si>
     <t xml:space="preserve">18.8768577575684</t>
@@ -1889,10 +1889,10 @@
     <t xml:space="preserve">18.3241367340088</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2117156982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2304534912109</t>
+    <t xml:space="preserve">18.2117176055908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2304515838623</t>
   </si>
   <si>
     <t xml:space="preserve">18.4552898406982</t>
@@ -1904,10 +1904,10 @@
     <t xml:space="preserve">18.1180362701416</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9705390930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2820835113525</t>
+    <t xml:space="preserve">18.9705371856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2820816040039</t>
   </si>
   <si>
     <t xml:space="preserve">20.0947208404541</t>
@@ -1916,7 +1916,7 @@
     <t xml:space="preserve">20.1884002685547</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1415596008301</t>
+    <t xml:space="preserve">20.1415615081787</t>
   </si>
   <si>
     <t xml:space="preserve">18.4927616119385</t>
@@ -1931,13 +1931,13 @@
     <t xml:space="preserve">16.8847980499268</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7634201049805</t>
+    <t xml:space="preserve">17.7634181976318</t>
   </si>
   <si>
     <t xml:space="preserve">18.0308246612549</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9285469055176</t>
+    <t xml:space="preserve">18.9285449981689</t>
   </si>
   <si>
     <t xml:space="preserve">18.4319343566895</t>
@@ -1964,22 +1964,22 @@
     <t xml:space="preserve">20.0077228546143</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0554752349854</t>
+    <t xml:space="preserve">20.0554733276367</t>
   </si>
   <si>
     <t xml:space="preserve">20.5329856872559</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9149932861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1509742736816</t>
+    <t xml:space="preserve">20.9149913787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1509761810303</t>
   </si>
   <si>
     <t xml:space="preserve">20.4374809265137</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0104961395264</t>
+    <t xml:space="preserve">21.0104942321777</t>
   </si>
   <si>
     <t xml:space="preserve">21.4880065917969</t>
@@ -2012,28 +2012,28 @@
     <t xml:space="preserve">18.852144241333</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0813503265381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.240930557251</t>
+    <t xml:space="preserve">19.0813484191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2409324645996</t>
   </si>
   <si>
     <t xml:space="preserve">18.7757415771484</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9599704742432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4852352142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1059970855713</t>
+    <t xml:space="preserve">19.9599685668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4852333068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1059989929199</t>
   </si>
   <si>
     <t xml:space="preserve">21.8700160980225</t>
   </si>
   <si>
-    <t xml:space="preserve">21.392505645752</t>
+    <t xml:space="preserve">21.3925037384033</t>
   </si>
   <si>
     <t xml:space="preserve">21.1537494659424</t>
@@ -2042,7 +2042,7 @@
     <t xml:space="preserve">21.7745132446289</t>
   </si>
   <si>
-    <t xml:space="preserve">21.679012298584</t>
+    <t xml:space="preserve">21.6790103912354</t>
   </si>
   <si>
     <t xml:space="preserve">21.9177684783936</t>
@@ -2054,16 +2054,16 @@
     <t xml:space="preserve">21.7267627716064</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5835094451904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5807323455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1032218933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.62571144104</t>
+    <t xml:space="preserve">21.5835113525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5807342529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1032238006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6257133483887</t>
   </si>
   <si>
     <t xml:space="preserve">19.8644676208496</t>
@@ -2072,7 +2072,7 @@
     <t xml:space="preserve">21.2492504119873</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9205417633057</t>
+    <t xml:space="preserve">22.920539855957</t>
   </si>
   <si>
     <t xml:space="preserve">22.4430294036865</t>
@@ -2081,13 +2081,13 @@
     <t xml:space="preserve">22.1565227508545</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0610198974609</t>
+    <t xml:space="preserve">22.0610218048096</t>
   </si>
   <si>
     <t xml:space="preserve">22.3475284576416</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0582447052002</t>
+    <t xml:space="preserve">21.0582466125488</t>
   </si>
   <si>
     <t xml:space="preserve">20.3897323608398</t>
@@ -2096,7 +2096,7 @@
     <t xml:space="preserve">20.2942276000977</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1987266540527</t>
+    <t xml:space="preserve">20.1987247467041</t>
   </si>
   <si>
     <t xml:space="preserve">20.8194904327393</t>
@@ -2105,7 +2105,7 @@
     <t xml:space="preserve">20.8672428131104</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0499267578125</t>
+    <t xml:space="preserve">18.0499248504639</t>
   </si>
   <si>
     <t xml:space="preserve">18.833044052124</t>
@@ -2129,7 +2129,7 @@
     <t xml:space="preserve">19.7689666748047</t>
   </si>
   <si>
-    <t xml:space="preserve">21.440258026123</t>
+    <t xml:space="preserve">21.4402561187744</t>
   </si>
   <si>
     <t xml:space="preserve">22.6340351104736</t>
@@ -2141,13 +2141,13 @@
     <t xml:space="preserve">22.7295341491699</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5862808227539</t>
+    <t xml:space="preserve">22.5862827301025</t>
   </si>
   <si>
     <t xml:space="preserve">22.8727893829346</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5385303497314</t>
+    <t xml:space="preserve">22.5385322570801</t>
   </si>
   <si>
     <t xml:space="preserve">22.6817855834961</t>
@@ -2159,7 +2159,7 @@
     <t xml:space="preserve">23.3025512695312</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4485759735107</t>
+    <t xml:space="preserve">24.4485778808594</t>
   </si>
   <si>
     <t xml:space="preserve">23.7323112487793</t>
@@ -2177,10 +2177,10 @@
     <t xml:space="preserve">24.1143188476562</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4008255004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3080978393555</t>
+    <t xml:space="preserve">24.4008235931396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3080959320068</t>
   </si>
   <si>
     <t xml:space="preserve">23.7800598144531</t>
@@ -2198,16 +2198,16 @@
     <t xml:space="preserve">24.9260883331299</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3558483123779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4035987854004</t>
+    <t xml:space="preserve">25.3558464050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.403600692749</t>
   </si>
   <si>
     <t xml:space="preserve">25.8333587646484</t>
   </si>
   <si>
-    <t xml:space="preserve">26.883882522583</t>
+    <t xml:space="preserve">26.8838844299316</t>
   </si>
   <si>
     <t xml:space="preserve">26.7883815765381</t>
@@ -2219,49 +2219,49 @@
     <t xml:space="preserve">24.5918292999268</t>
   </si>
   <si>
-    <t xml:space="preserve">24.830587387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.260347366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7378597259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.785608291626</t>
+    <t xml:space="preserve">24.8305854797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2603454589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7378578186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7856063842773</t>
   </si>
   <si>
     <t xml:space="preserve">26.0721130371094</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2631206512451</t>
+    <t xml:space="preserve">26.2631187438965</t>
   </si>
   <si>
     <t xml:space="preserve">25.4513492584229</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9288597106934</t>
+    <t xml:space="preserve">25.928861618042</t>
   </si>
   <si>
     <t xml:space="preserve">25.5946044921875</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6901054382324</t>
+    <t xml:space="preserve">25.6901073455811</t>
   </si>
   <si>
     <t xml:space="preserve">25.5468521118164</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4541244506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7406311035156</t>
+    <t xml:space="preserve">26.4541263580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.740629196167</t>
   </si>
   <si>
     <t xml:space="preserve">27.0748901367188</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1703910827637</t>
+    <t xml:space="preserve">27.1703929901123</t>
   </si>
   <si>
     <t xml:space="preserve">28.6506748199463</t>
@@ -2279,7 +2279,7 @@
     <t xml:space="preserve">30.1309604644775</t>
   </si>
   <si>
-    <t xml:space="preserve">29.653450012207</t>
+    <t xml:space="preserve">29.6534481048584</t>
   </si>
   <si>
     <t xml:space="preserve">29.510196685791</t>
@@ -2288,7 +2288,7 @@
     <t xml:space="preserve">28.5074214935303</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3191909790039</t>
+    <t xml:space="preserve">29.3191928863525</t>
   </si>
   <si>
     <t xml:space="preserve">28.9371814727783</t>
@@ -2297,25 +2297,25 @@
     <t xml:space="preserve">28.8416805267334</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2236919403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1281871795654</t>
+    <t xml:space="preserve">29.223690032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1281852722168</t>
   </si>
   <si>
     <t xml:space="preserve">29.1759376525879</t>
   </si>
   <si>
-    <t xml:space="preserve">29.080436706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6984272003174</t>
+    <t xml:space="preserve">29.0804386138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6984252929688</t>
   </si>
   <si>
     <t xml:space="preserve">28.9849338531494</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3641681671143</t>
+    <t xml:space="preserve">28.3641700744629</t>
   </si>
   <si>
     <t xml:space="preserve">27.8866577148438</t>
@@ -2324,7 +2324,7 @@
     <t xml:space="preserve">29.2714385986328</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8389053344727</t>
+    <t xml:space="preserve">27.8389072418213</t>
   </si>
   <si>
     <t xml:space="preserve">27.6479034423828</t>
@@ -2333,10 +2333,10 @@
     <t xml:space="preserve">28.6029262542725</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4119205474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.366943359375</t>
+    <t xml:space="preserve">28.4119186401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3669414520264</t>
   </si>
   <si>
     <t xml:space="preserve">29.4146938323975</t>
@@ -2345,13 +2345,13 @@
     <t xml:space="preserve">30.0354595184326</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7489490509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7039737701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2742137908936</t>
+    <t xml:space="preserve">29.748950958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7039756774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2742156982422</t>
   </si>
   <si>
     <t xml:space="preserve">29.7012023925781</t>
@@ -3420,6 +3420,9 @@
   </si>
   <si>
     <t xml:space="preserve">39.75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.5</t>
   </si>
 </sst>
 </file>
@@ -69304,7 +69307,7 @@
     </row>
     <row r="2522">
       <c r="A2522" s="1" t="n">
-        <v>45989.6912037037</v>
+        <v>45989.3333333333</v>
       </c>
       <c r="B2522" t="n">
         <v>12290</v>
@@ -69325,6 +69328,32 @@
         <v>1135</v>
       </c>
       <c r="H2522" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2523">
+      <c r="A2523" s="1" t="n">
+        <v>45992.69125</v>
+      </c>
+      <c r="B2523" t="n">
+        <v>6574</v>
+      </c>
+      <c r="C2523" t="n">
+        <v>40.25</v>
+      </c>
+      <c r="D2523" t="n">
+        <v>39.0499992370605</v>
+      </c>
+      <c r="E2523" t="n">
+        <v>40.25</v>
+      </c>
+      <c r="F2523" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="G2523" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H2523" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LUVE.MI.xlsx
+++ b/data/LUVE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1137" uniqueCount="1137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1138" uniqueCount="1138">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30043411254883</t>
+    <t xml:space="preserve">8.30043315887451</t>
   </si>
   <si>
     <t xml:space="preserve">LUVE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31703472137451</t>
+    <t xml:space="preserve">8.31703567504883</t>
   </si>
   <si>
     <t xml:space="preserve">8.28383255004883</t>
@@ -56,91 +56,91 @@
     <t xml:space="preserve">8.19667816162109</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07631969451904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15102481842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17177677154541</t>
+    <t xml:space="preserve">8.07632064819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15102386474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17177772521973</t>
   </si>
   <si>
     <t xml:space="preserve">8.03896999359131</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08462238311768</t>
+    <t xml:space="preserve">8.08462142944336</t>
   </si>
   <si>
     <t xml:space="preserve">8.06802082061768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96841621398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01821994781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99746704101562</t>
+    <t xml:space="preserve">7.96841812133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01821708679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99746799468994</t>
   </si>
   <si>
     <t xml:space="preserve">7.91861295700073</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91446495056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91031217575073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88541030883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87711000442505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85221195220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64884948730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7194037437439</t>
+    <t xml:space="preserve">7.91446304321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91031312942505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88541221618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87711191177368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85220909118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.648850440979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71940326690674</t>
   </si>
   <si>
     <t xml:space="preserve">7.70280170440674</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69035196304321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61979722976685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55754375457764</t>
+    <t xml:space="preserve">7.69035243988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61979818344116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55754470825195</t>
   </si>
   <si>
     <t xml:space="preserve">7.55339431762695</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63639831542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76920509338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80240678787231</t>
+    <t xml:space="preserve">7.63639879226685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76920461654663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80240774154663</t>
   </si>
   <si>
     <t xml:space="preserve">7.93521404266357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10122299194336</t>
+    <t xml:space="preserve">8.10122394561768</t>
   </si>
   <si>
     <t xml:space="preserve">8.05142021179199</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18422698974609</t>
+    <t xml:space="preserve">8.18422794342041</t>
   </si>
   <si>
     <t xml:space="preserve">8.13442516326904</t>
@@ -149,37 +149,37 @@
     <t xml:space="preserve">8.00161838531494</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96011686325073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21743011474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35853576660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3253345489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2921314239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20082759857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15932559967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30336570739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36267471313477</t>
+    <t xml:space="preserve">7.9601149559021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21742916107178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35853481292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32533550262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29213237762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20082855224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15932464599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30336380004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36267375946045</t>
   </si>
   <si>
     <t xml:space="preserve">8.43045616149902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15085315704346</t>
+    <t xml:space="preserve">8.15085220336914</t>
   </si>
   <si>
     <t xml:space="preserve">8.17627143859863</t>
@@ -188,10 +188,10 @@
     <t xml:space="preserve">8.20592594146729</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13390827178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1169605255127</t>
+    <t xml:space="preserve">8.13390922546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11696243286133</t>
   </si>
   <si>
     <t xml:space="preserve">8.21863555908203</t>
@@ -200,16 +200,16 @@
     <t xml:space="preserve">8.21016216278076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21439933776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20169067382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26099967956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09154319763184</t>
+    <t xml:space="preserve">8.21439838409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20169162750244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26100158691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09154224395752</t>
   </si>
   <si>
     <t xml:space="preserve">8.10848808288574</t>
@@ -224,7 +224,7 @@
     <t xml:space="preserve">7.9220871925354</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87972354888916</t>
+    <t xml:space="preserve">7.87972259521484</t>
   </si>
   <si>
     <t xml:space="preserve">7.8373589515686</t>
@@ -233,55 +233,55 @@
     <t xml:space="preserve">8.12543487548828</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93479537963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75263071060181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71026611328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93903350830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8119421005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79499435424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62553882598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66790294647217</t>
+    <t xml:space="preserve">7.93479633331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75263023376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71026706695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93903160095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81194067001343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79499483108521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62553930282593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66790342330933</t>
   </si>
   <si>
     <t xml:space="preserve">7.84583187103271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19321727752686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47282028198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51518440246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52365875244141</t>
+    <t xml:space="preserve">8.19321823120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47281932830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5151834487915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52365779876709</t>
   </si>
   <si>
     <t xml:space="preserve">8.59991264343262</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78631591796875</t>
+    <t xml:space="preserve">8.78631496429443</t>
   </si>
   <si>
     <t xml:space="preserve">8.71853256225586</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50671100616455</t>
+    <t xml:space="preserve">8.50671195983887</t>
   </si>
   <si>
     <t xml:space="preserve">8.540602684021</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">8.46858310699463</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46434879302979</t>
+    <t xml:space="preserve">8.46434593200684</t>
   </si>
   <si>
     <t xml:space="preserve">8.55754852294922</t>
@@ -305,19 +305,19 @@
     <t xml:space="preserve">8.72700500488281</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64227771759033</t>
+    <t xml:space="preserve">8.6422758102417</t>
   </si>
   <si>
     <t xml:space="preserve">8.89646244049072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02355194091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09980869293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06591701507568</t>
+    <t xml:space="preserve">9.02355289459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09980773925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06591796875</t>
   </si>
   <si>
     <t xml:space="preserve">9.1082820892334</t>
@@ -326,76 +326,76 @@
     <t xml:space="preserve">9.27773761749268</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1930103302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18453788757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07439136505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09133529663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30315589904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32010173797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12522888183594</t>
+    <t xml:space="preserve">9.19300842285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18453693389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07439041137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09133434295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30315685272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32010269165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1252269744873</t>
   </si>
   <si>
     <t xml:space="preserve">9.60817813873291</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4048318862915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48955821990967</t>
+    <t xml:space="preserve">9.40483093261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48955917358398</t>
   </si>
   <si>
     <t xml:space="preserve">9.38788414001465</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5319242477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4810848236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4471960067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54039478302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57428741455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47261428833008</t>
+    <t xml:space="preserve">9.53192329406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48108577728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44719505310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54039573669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57428550720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47261333465576</t>
   </si>
   <si>
     <t xml:space="preserve">9.41330337524414</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42177581787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51497650146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56581401824951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74374294281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0657091140747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2521133422852</t>
+    <t xml:space="preserve">9.42177677154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51497745513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5658130645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74374389648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.065710067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2521123886108</t>
   </si>
   <si>
     <t xml:space="preserve">10.1334924697876</t>
@@ -404,73 +404,73 @@
     <t xml:space="preserve">9.99792957305908</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95556449890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98098087310791</t>
+    <t xml:space="preserve">9.95556354522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98098278045654</t>
   </si>
   <si>
     <t xml:space="preserve">9.88778114318848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91319751739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0148735046387</t>
+    <t xml:space="preserve">9.91320037841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0148725509644</t>
   </si>
   <si>
     <t xml:space="preserve">10.1589117050171</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0402927398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70137786865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73526954650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70985221862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0826559066772</t>
+    <t xml:space="preserve">10.0402936935425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70137977600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73526859283447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70985412597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0826568603516</t>
   </si>
   <si>
     <t xml:space="preserve">9.8623628616333</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1250190734863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2944774627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4808778762817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5317153930664</t>
+    <t xml:space="preserve">10.1250200271606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2944755554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4808769226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5317163467407</t>
   </si>
   <si>
     <t xml:space="preserve">10.5147705078125</t>
   </si>
   <si>
-    <t xml:space="preserve">10.802845954895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.912992477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8621549606323</t>
+    <t xml:space="preserve">10.8028469085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9129934310913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8621559143066</t>
   </si>
   <si>
     <t xml:space="preserve">11.014666557312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0570306777954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.277325630188</t>
+    <t xml:space="preserve">11.0570297241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2773246765137</t>
   </si>
   <si>
     <t xml:space="preserve">11.438307762146</t>
@@ -479,7 +479,7 @@
     <t xml:space="preserve">11.6586008071899</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5823440551758</t>
+    <t xml:space="preserve">11.5823450088501</t>
   </si>
   <si>
     <t xml:space="preserve">11.4806718826294</t>
@@ -488,10 +488,10 @@
     <t xml:space="preserve">11.5908184051514</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7009649276733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7772197723389</t>
+    <t xml:space="preserve">11.700963973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7772188186646</t>
   </si>
   <si>
     <t xml:space="preserve">11.811110496521</t>
@@ -506,34 +506,34 @@
     <t xml:space="preserve">11.599289894104</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5230350494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6077651977539</t>
+    <t xml:space="preserve">11.5230369567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6077642440796</t>
   </si>
   <si>
     <t xml:space="preserve">11.6263799667358</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7297258377075</t>
+    <t xml:space="preserve">11.7297267913818</t>
   </si>
   <si>
     <t xml:space="preserve">11.6952781677246</t>
   </si>
   <si>
-    <t xml:space="preserve">11.678053855896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7986240386963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8847455978394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9105806350708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0656003952026</t>
+    <t xml:space="preserve">11.6780548095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.798623085022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8847465515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9105815887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0655994415283</t>
   </si>
   <si>
     <t xml:space="preserve">12.3153533935547</t>
@@ -542,55 +542,55 @@
     <t xml:space="preserve">12.3584127426147</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0569877624512</t>
+    <t xml:space="preserve">12.0569887161255</t>
   </si>
   <si>
     <t xml:space="preserve">12.1431083679199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9967041015625</t>
+    <t xml:space="preserve">11.9967031478882</t>
   </si>
   <si>
     <t xml:space="preserve">11.8416843414307</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7555618286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7125015258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8502969741821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9191932678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9622554779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0397644042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.048376083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7900094985962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0311508178711</t>
+    <t xml:space="preserve">11.7555627822876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7125034332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8502960205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9191942214966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.962254524231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0397634506226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0483751296997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7900114059448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0311517715454</t>
   </si>
   <si>
     <t xml:space="preserve">11.9450302124023</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8158483505249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8933582305908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8761339187622</t>
+    <t xml:space="preserve">11.8158493041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8933572769165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8761329650879</t>
   </si>
   <si>
     <t xml:space="preserve">11.8244600296021</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">11.901969909668</t>
   </si>
   <si>
-    <t xml:space="preserve">11.927806854248</t>
+    <t xml:space="preserve">11.9278059005737</t>
   </si>
   <si>
     <t xml:space="preserve">11.7211141586304</t>
@@ -614,7 +614,7 @@
     <t xml:space="preserve">11.6349935531616</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6091566085815</t>
+    <t xml:space="preserve">11.6091556549072</t>
   </si>
   <si>
     <t xml:space="preserve">11.5747079849243</t>
@@ -629,16 +629,16 @@
     <t xml:space="preserve">11.3680171966553</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3594036102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2818956375122</t>
+    <t xml:space="preserve">11.3594045639038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2818965911865</t>
   </si>
   <si>
     <t xml:space="preserve">11.2302217483521</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1957750320435</t>
+    <t xml:space="preserve">11.1957740783691</t>
   </si>
   <si>
     <t xml:space="preserve">11.187162399292</t>
@@ -650,31 +650,31 @@
     <t xml:space="preserve">11.0579805374146</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1785507202148</t>
+    <t xml:space="preserve">11.1785488128662</t>
   </si>
   <si>
     <t xml:space="preserve">11.126877784729</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9374103546143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0665912628174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0235319137573</t>
+    <t xml:space="preserve">10.9374113082886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.066593170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.023530960083</t>
   </si>
   <si>
     <t xml:space="preserve">11.0838165283203</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1354894638062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2043867111206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3163461685181</t>
+    <t xml:space="preserve">11.1354904174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2043876647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3163452148438</t>
   </si>
   <si>
     <t xml:space="preserve">11.454137802124</t>
@@ -683,13 +683,13 @@
     <t xml:space="preserve">11.5402603149414</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4110774993896</t>
+    <t xml:space="preserve">11.4110765457153</t>
   </si>
   <si>
     <t xml:space="preserve">11.2905073165894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1613264083862</t>
+    <t xml:space="preserve">11.1613254547119</t>
   </si>
   <si>
     <t xml:space="preserve">11.2646722793579</t>
@@ -701,43 +701,43 @@
     <t xml:space="preserve">11.0407562255859</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4196891784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2216110229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2388362884521</t>
+    <t xml:space="preserve">11.4196901321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2216100692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2388343811035</t>
   </si>
   <si>
     <t xml:space="preserve">11.3421812057495</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9546337127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9632453918457</t>
+    <t xml:space="preserve">10.9546346664429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.96324634552</t>
   </si>
   <si>
     <t xml:space="preserve">11.0063066482544</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0924291610718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74032497406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0169038772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21498394012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37861442565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49057292938232</t>
+    <t xml:space="preserve">11.0924282073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74032306671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01690578460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2149829864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37861633300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49057197570801</t>
   </si>
   <si>
     <t xml:space="preserve">9.5077953338623</t>
@@ -746,55 +746,55 @@
     <t xml:space="preserve">9.59391784667969</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60253047943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6886510848999</t>
+    <t xml:space="preserve">9.60252952575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68865013122559</t>
   </si>
   <si>
     <t xml:space="preserve">9.56808090209961</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39583683013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34416675567627</t>
+    <t xml:space="preserve">9.39583778381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34416580200195</t>
   </si>
   <si>
     <t xml:space="preserve">9.2580451965332</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30110549926758</t>
+    <t xml:space="preserve">9.30110454559326</t>
   </si>
   <si>
     <t xml:space="preserve">9.41306304931641</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28388118743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24081993103027</t>
+    <t xml:space="preserve">9.28388023376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24081897735596</t>
   </si>
   <si>
     <t xml:space="preserve">9.12886142730713</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02551460266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20637226104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26665687561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69726276397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65420246124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66281604766846</t>
+    <t xml:space="preserve">9.02551651000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20637130737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26665782928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69726371765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65420341491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66281414031982</t>
   </si>
   <si>
     <t xml:space="preserve">9.64559078216553</t>
@@ -806,28 +806,28 @@
     <t xml:space="preserve">9.75754928588867</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71448802947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09441375732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93939590454102</t>
+    <t xml:space="preserve">9.71448612213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09441471099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93939685821533</t>
   </si>
   <si>
     <t xml:space="preserve">9.14608669281006</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12024974822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83505630493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73171234130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90395355224609</t>
+    <t xml:space="preserve">9.1202507019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83505821228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73171138763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90395545959473</t>
   </si>
   <si>
     <t xml:space="preserve">9.77477264404297</t>
@@ -839,106 +839,106 @@
     <t xml:space="preserve">9.49918460845947</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57669258117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58530521392822</t>
+    <t xml:space="preserve">9.57669353485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58530616760254</t>
   </si>
   <si>
     <t xml:space="preserve">9.47334671020508</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4302864074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54224586486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1719217300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23220729827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55946922302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51640796661377</t>
+    <t xml:space="preserve">9.43028736114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54224395751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17192268371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23220920562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55946826934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51640701293945</t>
   </si>
   <si>
     <t xml:space="preserve">9.8608922958374</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95661926269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91355991363525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08580112457275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0427417755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99967956542969</t>
+    <t xml:space="preserve">8.956618309021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91355800628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08580207824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04274082183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99968147277832</t>
   </si>
   <si>
     <t xml:space="preserve">8.82743740081787</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69825458526611</t>
+    <t xml:space="preserve">8.69825649261475</t>
   </si>
   <si>
     <t xml:space="preserve">8.87049865722656</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7843770980835</t>
+    <t xml:space="preserve">8.78437805175781</t>
   </si>
   <si>
     <t xml:space="preserve">8.7413158416748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61213493347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59490871429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65519523620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45711517333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06314468383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10714054107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01914882659912</t>
+    <t xml:space="preserve">8.61213397979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59490966796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65519428253174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45711421966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06314373016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10713958740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0191478729248</t>
   </si>
   <si>
     <t xml:space="preserve">8.97515296936035</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93115615844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88716220855713</t>
+    <t xml:space="preserve">8.93115711212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88716125488281</t>
   </si>
   <si>
     <t xml:space="preserve">8.84316539764404</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76397228240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48239994049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71117782592773</t>
+    <t xml:space="preserve">8.76397323608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48240089416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71117687225342</t>
   </si>
   <si>
     <t xml:space="preserve">8.62318706512451</t>
@@ -947,7 +947,7 @@
     <t xml:space="preserve">8.58798980712891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6583833694458</t>
+    <t xml:space="preserve">8.65838241577148</t>
   </si>
   <si>
     <t xml:space="preserve">8.60558795928955</t>
@@ -971,7 +971,7 @@
     <t xml:space="preserve">8.27121925354004</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32401466369629</t>
+    <t xml:space="preserve">8.32401371002197</t>
   </si>
   <si>
     <t xml:space="preserve">8.288818359375</t>
@@ -980,13 +980,13 @@
     <t xml:space="preserve">8.781569480896</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64078330993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79916954040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67597961425781</t>
+    <t xml:space="preserve">8.64078521728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79916763305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67598056793213</t>
   </si>
   <si>
     <t xml:space="preserve">9.23912811279297</t>
@@ -1007,22 +1007,22 @@
     <t xml:space="preserve">8.46480083465576</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41200542449951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49999713897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34161186218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23602199554443</t>
+    <t xml:space="preserve">8.41200637817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49999809265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34161281585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23602294921875</t>
   </si>
   <si>
     <t xml:space="preserve">8.30641555786133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13043212890625</t>
+    <t xml:space="preserve">8.13043117523193</t>
   </si>
   <si>
     <t xml:space="preserve">8.1832275390625</t>
@@ -1031,25 +1031,25 @@
     <t xml:space="preserve">8.16562938690186</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21842575073242</t>
+    <t xml:space="preserve">8.21842479705811</t>
   </si>
   <si>
     <t xml:space="preserve">8.25362110137939</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37680912017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51759624481201</t>
+    <t xml:space="preserve">8.37681007385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5175952911377</t>
   </si>
   <si>
     <t xml:space="preserve">9.28312492370605</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41511058807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63509082794189</t>
+    <t xml:space="preserve">9.41511249542236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63509178161621</t>
   </si>
   <si>
     <t xml:space="preserve">9.59109401702881</t>
@@ -1058,34 +1058,34 @@
     <t xml:space="preserve">9.89906597137451</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1190452575684</t>
+    <t xml:space="preserve">10.119044303894</t>
   </si>
   <si>
     <t xml:space="preserve">10.1630411148071</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2070369720459</t>
+    <t xml:space="preserve">10.2070360183716</t>
   </si>
   <si>
     <t xml:space="preserve">10.3390235900879</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2950277328491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.383020401001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2510318756104</t>
+    <t xml:space="preserve">10.2950286865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3830194473267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2510328292847</t>
   </si>
   <si>
     <t xml:space="preserve">10.4270162582397</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0750484466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5150060653687</t>
+    <t xml:space="preserve">10.0750494003296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5150079727173</t>
   </si>
   <si>
     <t xml:space="preserve">10.6498155593872</t>
@@ -1097,7 +1097,7 @@
     <t xml:space="preserve">10.694751739502</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6048803329468</t>
+    <t xml:space="preserve">10.6048793792725</t>
   </si>
   <si>
     <t xml:space="preserve">10.3802003860474</t>
@@ -1118,10 +1118,10 @@
     <t xml:space="preserve">10.2903270721436</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2004566192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9757776260376</t>
+    <t xml:space="preserve">10.200457572937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97577857971191</t>
   </si>
   <si>
     <t xml:space="preserve">10.1105842590332</t>
@@ -1130,13 +1130,13 @@
     <t xml:space="preserve">9.93084049224854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88590526580811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1555213928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.020712852478</t>
+    <t xml:space="preserve">9.88590431213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1555204391479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0207118988037</t>
   </si>
   <si>
     <t xml:space="preserve">9.75109767913818</t>
@@ -1145,7 +1145,7 @@
     <t xml:space="preserve">9.70616149902344</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3466739654541</t>
+    <t xml:space="preserve">9.34667205810547</t>
   </si>
   <si>
     <t xml:space="preserve">9.30173778533936</t>
@@ -1154,19 +1154,19 @@
     <t xml:space="preserve">9.39160919189453</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48148155212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61628818511963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52641677856445</t>
+    <t xml:space="preserve">9.48148059844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61628913879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52641773223877</t>
   </si>
   <si>
     <t xml:space="preserve">9.43654537200928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12199401855469</t>
+    <t xml:space="preserve">9.12199306488037</t>
   </si>
   <si>
     <t xml:space="preserve">9.0321216583252</t>
@@ -1175,10 +1175,10 @@
     <t xml:space="preserve">9.16693019866943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07705783843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25680255889893</t>
+    <t xml:space="preserve">9.07705879211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25680160522461</t>
   </si>
   <si>
     <t xml:space="preserve">8.98718643188477</t>
@@ -1190,7 +1190,7 @@
     <t xml:space="preserve">9.66122627258301</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79603290557861</t>
+    <t xml:space="preserve">9.7960319519043</t>
   </si>
   <si>
     <t xml:space="preserve">10.9643669128418</t>
@@ -1199,49 +1199,49 @@
     <t xml:space="preserve">11.4586620330811</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5035991668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2339820861816</t>
+    <t xml:space="preserve">11.5035982131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.233983039856</t>
   </si>
   <si>
     <t xml:space="preserve">11.1441106796265</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9194316864014</t>
+    <t xml:space="preserve">10.9194307327271</t>
   </si>
   <si>
     <t xml:space="preserve">10.8744964599609</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0093030929565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2789192199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4137268066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5485334396362</t>
+    <t xml:space="preserve">11.0093040466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.278920173645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4137258529663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5485343933105</t>
   </si>
   <si>
     <t xml:space="preserve">11.6833429336548</t>
   </si>
   <si>
-    <t xml:space="preserve">11.77321434021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9080219268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1326999664307</t>
+    <t xml:space="preserve">11.7732152938843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9080228805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.132700920105</t>
   </si>
   <si>
     <t xml:space="preserve">11.9978942871094</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8181495666504</t>
+    <t xml:space="preserve">11.8181505203247</t>
   </si>
   <si>
     <t xml:space="preserve">11.593469619751</t>
@@ -1253,19 +1253,19 @@
     <t xml:space="preserve">12.5820608139038</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9415473937988</t>
+    <t xml:space="preserve">12.9415483474731</t>
   </si>
   <si>
     <t xml:space="preserve">12.8067398071289</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7618045806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0763549804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4472522735596</t>
+    <t xml:space="preserve">12.7618036270142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0763559341431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4472532272339</t>
   </si>
   <si>
     <t xml:space="preserve">12.5371246337891</t>
@@ -1274,10 +1274,10 @@
     <t xml:space="preserve">12.2675085067749</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4023180007935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6269969940186</t>
+    <t xml:space="preserve">12.4023170471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6269960403442</t>
   </si>
   <si>
     <t xml:space="preserve">12.671932220459</t>
@@ -1286,13 +1286,13 @@
     <t xml:space="preserve">12.8966131210327</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7282791137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7846231460571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.559944152832</t>
+    <t xml:space="preserve">11.7282772064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7846240997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5599431991577</t>
   </si>
   <si>
     <t xml:space="preserve">8.89731407165527</t>
@@ -1301,10 +1301,10 @@
     <t xml:space="preserve">7.98062181472778</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81885147094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53126192092896</t>
+    <t xml:space="preserve">7.81885194778442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53126239776611</t>
   </si>
   <si>
     <t xml:space="preserve">7.89074945449829</t>
@@ -1322,34 +1322,34 @@
     <t xml:space="preserve">8.6097240447998</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66364765167236</t>
+    <t xml:space="preserve">8.66364860534668</t>
   </si>
   <si>
     <t xml:space="preserve">8.86136531829834</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21186637878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93848896026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80045509338379</t>
+    <t xml:space="preserve">9.21186542510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93848991394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80045413970947</t>
   </si>
   <si>
     <t xml:space="preserve">9.89247798919678</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66242027282715</t>
+    <t xml:space="preserve">9.66241931915283</t>
   </si>
   <si>
     <t xml:space="preserve">9.7084321975708</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84646606445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1225347518921</t>
+    <t xml:space="preserve">9.84646701812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1225357055664</t>
   </si>
   <si>
     <t xml:space="preserve">9.75444412231445</t>
@@ -1358,28 +1358,28 @@
     <t xml:space="preserve">10.3986053466797</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3065814971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7206840515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5826511383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8587198257446</t>
+    <t xml:space="preserve">10.3065805435181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.720685005188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5826501846313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8587207794189</t>
   </si>
   <si>
     <t xml:space="preserve">10.6746740341187</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9967555999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6286630630493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7666959762573</t>
+    <t xml:space="preserve">10.996753692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.628662109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7666969299316</t>
   </si>
   <si>
     <t xml:space="preserve">10.4906272888184</t>
@@ -1388,7 +1388,7 @@
     <t xml:space="preserve">11.1347894668579</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3188343048096</t>
+    <t xml:space="preserve">11.3188352584839</t>
   </si>
   <si>
     <t xml:space="preserve">11.5028820037842</t>
@@ -1397,10 +1397,10 @@
     <t xml:space="preserve">11.1808004379272</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0427665710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2728242874146</t>
+    <t xml:space="preserve">11.0427675247192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2728233337402</t>
   </si>
   <si>
     <t xml:space="preserve">10.9507417678833</t>
@@ -1412,34 +1412,34 @@
     <t xml:space="preserve">10.8127088546753</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9047327041626</t>
+    <t xml:space="preserve">10.9047317504883</t>
   </si>
   <si>
     <t xml:space="preserve">11.4108581542969</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4568691253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2268123626709</t>
+    <t xml:space="preserve">11.4568700790405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2268114089966</t>
   </si>
   <si>
     <t xml:space="preserve">11.3648471832275</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5488929748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5949039459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6869268417358</t>
+    <t xml:space="preserve">11.5488920211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5949048995972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6869258880615</t>
   </si>
   <si>
     <t xml:space="preserve">11.9629964828491</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7789497375488</t>
+    <t xml:space="preserve">11.7789506912231</t>
   </si>
   <si>
     <t xml:space="preserve">12.0090074539185</t>
@@ -1454,31 +1454,31 @@
     <t xml:space="preserve">11.8249626159668</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0550193786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8709735870361</t>
+    <t xml:space="preserve">12.0550203323364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8709745407104</t>
   </si>
   <si>
     <t xml:space="preserve">11.9169845581055</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6409168243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1470432281494</t>
+    <t xml:space="preserve">11.6409158706665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1470422744751</t>
   </si>
   <si>
     <t xml:space="preserve">12.6991815567017</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7912044525146</t>
+    <t xml:space="preserve">12.7912034988403</t>
   </si>
   <si>
     <t xml:space="preserve">13.0672731399536</t>
   </si>
   <si>
-    <t xml:space="preserve">12.883228302002</t>
+    <t xml:space="preserve">12.8832273483276</t>
   </si>
   <si>
     <t xml:space="preserve">12.9292392730713</t>
@@ -1496,22 +1496,22 @@
     <t xml:space="preserve">13.1592969894409</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3893537521362</t>
+    <t xml:space="preserve">13.3893556594849</t>
   </si>
   <si>
     <t xml:space="preserve">13.2973299026489</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9752511978149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7114353179932</t>
+    <t xml:space="preserve">12.9752502441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7114343643188</t>
   </si>
   <si>
     <t xml:space="preserve">13.4353656768799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5151357650757</t>
+    <t xml:space="preserve">12.5151348114014</t>
   </si>
   <si>
     <t xml:space="preserve">12.3770999908447</t>
@@ -1520,7 +1520,7 @@
     <t xml:space="preserve">12.837215423584</t>
   </si>
   <si>
-    <t xml:space="preserve">12.745192527771</t>
+    <t xml:space="preserve">12.7451934814453</t>
   </si>
   <si>
     <t xml:space="preserve">12.6531686782837</t>
@@ -1538,10 +1538,10 @@
     <t xml:space="preserve">13.9414920806885</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1715507507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3555965423584</t>
+    <t xml:space="preserve">14.1715497970581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3555955886841</t>
   </si>
   <si>
     <t xml:space="preserve">14.1255388259888</t>
@@ -1550,28 +1550,28 @@
     <t xml:space="preserve">14.4936294555664</t>
   </si>
   <si>
-    <t xml:space="preserve">14.723687171936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.677677154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8157119750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.861722946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0457696914673</t>
+    <t xml:space="preserve">14.7236890792847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6776762008667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.815710067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8617219924927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.045768737793</t>
   </si>
   <si>
     <t xml:space="preserve">14.5396413803101</t>
   </si>
   <si>
-    <t xml:space="preserve">14.631664276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4476194381714</t>
+    <t xml:space="preserve">14.6316652297974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4476203918457</t>
   </si>
   <si>
     <t xml:space="preserve">14.2635726928711</t>
@@ -1580,25 +1580,25 @@
     <t xml:space="preserve">13.9875040054321</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3095846176147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6654224395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8034572601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5734004974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7574453353882</t>
+    <t xml:space="preserve">14.3095855712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6654233932495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8034582138062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5733995437622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7574462890625</t>
   </si>
   <si>
     <t xml:space="preserve">14.9537448883057</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0335140228271</t>
+    <t xml:space="preserve">14.0335149765015</t>
   </si>
   <si>
     <t xml:space="preserve">14.4269771575928</t>
@@ -1619,16 +1619,16 @@
     <t xml:space="preserve">15.0359086990356</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0827503204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8953857421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9422273635864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1764316558838</t>
+    <t xml:space="preserve">15.0827493667603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8953866958618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9422264099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1764326095581</t>
   </si>
   <si>
     <t xml:space="preserve">15.1295900344849</t>
@@ -1637,13 +1637,13 @@
     <t xml:space="preserve">14.9890689849854</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6611814498901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3169555664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7548637390137</t>
+    <t xml:space="preserve">14.6611824035645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3169546127319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7548627853394</t>
   </si>
   <si>
     <t xml:space="preserve">14.8017044067383</t>
@@ -1652,7 +1652,7 @@
     <t xml:space="preserve">15.2232723236084</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5043182373047</t>
+    <t xml:space="preserve">15.5043163299561</t>
   </si>
   <si>
     <t xml:space="preserve">16.0664081573486</t>
@@ -1670,7 +1670,7 @@
     <t xml:space="preserve">15.9258861541748</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7853622436523</t>
+    <t xml:space="preserve">15.785364151001</t>
   </si>
   <si>
     <t xml:space="preserve">16.1132488250732</t>
@@ -1682,10 +1682,10 @@
     <t xml:space="preserve">16.5348148345947</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8627033233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1437473297119</t>
+    <t xml:space="preserve">16.8627014160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1437454223633</t>
   </si>
   <si>
     <t xml:space="preserve">16.581657409668</t>
@@ -1700,7 +1700,7 @@
     <t xml:space="preserve">17.7995185852051</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4716320037842</t>
+    <t xml:space="preserve">17.4716339111328</t>
   </si>
   <si>
     <t xml:space="preserve">16.8158626556396</t>
@@ -1709,16 +1709,16 @@
     <t xml:space="preserve">16.6284980773926</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0969066619873</t>
+    <t xml:space="preserve">17.0969047546387</t>
   </si>
   <si>
     <t xml:space="preserve">17.5184745788574</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6121559143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0337238311768</t>
+    <t xml:space="preserve">17.612154006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0337219238281</t>
   </si>
   <si>
     <t xml:space="preserve">18.5489711761475</t>
@@ -1733,7 +1733,7 @@
     <t xml:space="preserve">19.7668342590332</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5794677734375</t>
+    <t xml:space="preserve">19.5794696807861</t>
   </si>
   <si>
     <t xml:space="preserve">19.2047443389893</t>
@@ -1742,16 +1742,16 @@
     <t xml:space="preserve">19.1110610961914</t>
   </si>
   <si>
-    <t xml:space="preserve">19.673152923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2984256744385</t>
+    <t xml:space="preserve">19.6731510162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2984237670898</t>
   </si>
   <si>
     <t xml:space="preserve">19.4857883453369</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8605155944824</t>
+    <t xml:space="preserve">19.8605175018311</t>
   </si>
   <si>
     <t xml:space="preserve">20.3289222717285</t>
@@ -1763,19 +1763,19 @@
     <t xml:space="preserve">21.2657413482666</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0783767700195</t>
+    <t xml:space="preserve">21.0783786773682</t>
   </si>
   <si>
     <t xml:space="preserve">21.4531059265137</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7973327636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8278293609619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1088771820068</t>
+    <t xml:space="preserve">20.7973346710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8278312683105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1088790893555</t>
   </si>
   <si>
     <t xml:space="preserve">21.7341480255127</t>
@@ -1787,10 +1787,10 @@
     <t xml:space="preserve">22.2962379455566</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4836025238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6404685974121</t>
+    <t xml:space="preserve">22.4836044311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6404666900635</t>
   </si>
   <si>
     <t xml:space="preserve">21.5467834472656</t>
@@ -1808,7 +1808,7 @@
     <t xml:space="preserve">20.6099681854248</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9215126037598</t>
+    <t xml:space="preserve">21.9215106964111</t>
   </si>
   <si>
     <t xml:space="preserve">22.7646465301514</t>
@@ -1820,16 +1820,16 @@
     <t xml:space="preserve">21.1720600128174</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7036514282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3594226837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.516284942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0478782653809</t>
+    <t xml:space="preserve">20.703649520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3594207763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5162868499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0478801727295</t>
   </si>
   <si>
     <t xml:space="preserve">22.6709671020508</t>
@@ -1838,16 +1838,16 @@
     <t xml:space="preserve">22.2025566101074</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3899211883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9541969299316</t>
+    <t xml:space="preserve">22.3899192810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.954195022583</t>
   </si>
   <si>
     <t xml:space="preserve">20.4226055145264</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8910140991211</t>
+    <t xml:space="preserve">20.8910121917725</t>
   </si>
   <si>
     <t xml:space="preserve">19.3921089172363</t>
@@ -1859,19 +1859,19 @@
     <t xml:space="preserve">18.361608505249</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9563827514648</t>
+    <t xml:space="preserve">16.9563846588135</t>
   </si>
   <si>
     <t xml:space="preserve">17.6589965820312</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7526779174805</t>
+    <t xml:space="preserve">17.7526760101318</t>
   </si>
   <si>
     <t xml:space="preserve">17.377950668335</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8932018280029</t>
+    <t xml:space="preserve">17.8931999206543</t>
   </si>
   <si>
     <t xml:space="preserve">17.9400405883789</t>
@@ -1886,25 +1886,25 @@
     <t xml:space="preserve">18.6426544189453</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3241367340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2117176055908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2304515838623</t>
+    <t xml:space="preserve">18.3241348266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2117195129395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2304534912109</t>
   </si>
   <si>
     <t xml:space="preserve">18.4552898406982</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9494094848633</t>
+    <t xml:space="preserve">17.9494113922119</t>
   </si>
   <si>
     <t xml:space="preserve">18.1180362701416</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9705371856689</t>
+    <t xml:space="preserve">18.9705390930176</t>
   </si>
   <si>
     <t xml:space="preserve">20.2820816040039</t>
@@ -1925,7 +1925,7 @@
     <t xml:space="preserve">17.5559463500977</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1999549865723</t>
+    <t xml:space="preserve">17.1999568939209</t>
   </si>
   <si>
     <t xml:space="preserve">16.8847980499268</t>
@@ -1964,25 +1964,25 @@
     <t xml:space="preserve">20.0077228546143</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0554733276367</t>
+    <t xml:space="preserve">20.0554714202881</t>
   </si>
   <si>
     <t xml:space="preserve">20.5329856872559</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9149913787842</t>
+    <t xml:space="preserve">20.9149932861328</t>
   </si>
   <si>
     <t xml:space="preserve">20.1509761810303</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4374809265137</t>
+    <t xml:space="preserve">20.4374828338623</t>
   </si>
   <si>
     <t xml:space="preserve">21.0104942321777</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4880065917969</t>
+    <t xml:space="preserve">21.4880084991455</t>
   </si>
   <si>
     <t xml:space="preserve">19.5779628753662</t>
@@ -1997,7 +1997,7 @@
     <t xml:space="preserve">19.2914562225342</t>
   </si>
   <si>
-    <t xml:space="preserve">19.339204788208</t>
+    <t xml:space="preserve">19.3392066955566</t>
   </si>
   <si>
     <t xml:space="preserve">18.813943862915</t>
@@ -2012,22 +2012,22 @@
     <t xml:space="preserve">18.852144241333</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0813484191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2409324645996</t>
+    <t xml:space="preserve">19.0813503265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.240930557251</t>
   </si>
   <si>
     <t xml:space="preserve">18.7757415771484</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9599685668945</t>
+    <t xml:space="preserve">19.9599704742432</t>
   </si>
   <si>
     <t xml:space="preserve">20.4852333068848</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1059989929199</t>
+    <t xml:space="preserve">21.1059970855713</t>
   </si>
   <si>
     <t xml:space="preserve">21.8700160980225</t>
@@ -2039,7 +2039,7 @@
     <t xml:space="preserve">21.1537494659424</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7745132446289</t>
+    <t xml:space="preserve">21.7745113372803</t>
   </si>
   <si>
     <t xml:space="preserve">21.6790103912354</t>
@@ -2048,7 +2048,7 @@
     <t xml:space="preserve">21.9177684783936</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2970027923584</t>
+    <t xml:space="preserve">21.2970008850098</t>
   </si>
   <si>
     <t xml:space="preserve">21.7267627716064</t>
@@ -2072,7 +2072,7 @@
     <t xml:space="preserve">21.2492504119873</t>
   </si>
   <si>
-    <t xml:space="preserve">22.920539855957</t>
+    <t xml:space="preserve">22.9205417633057</t>
   </si>
   <si>
     <t xml:space="preserve">22.4430294036865</t>
@@ -2081,19 +2081,19 @@
     <t xml:space="preserve">22.1565227508545</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0610218048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3475284576416</t>
+    <t xml:space="preserve">22.0610198974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.347526550293</t>
   </si>
   <si>
     <t xml:space="preserve">21.0582466125488</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3897323608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2942276000977</t>
+    <t xml:space="preserve">20.3897304534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2942295074463</t>
   </si>
   <si>
     <t xml:space="preserve">20.1987247467041</t>
@@ -2120,7 +2120,7 @@
     <t xml:space="preserve">19.8167171478271</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2464771270752</t>
+    <t xml:space="preserve">20.2464790344238</t>
   </si>
   <si>
     <t xml:space="preserve">20.6762371063232</t>
@@ -2144,25 +2144,25 @@
     <t xml:space="preserve">22.5862827301025</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8727893829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5385322570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6817855834961</t>
+    <t xml:space="preserve">22.8727912902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5385341644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6817836761475</t>
   </si>
   <si>
     <t xml:space="preserve">23.0160427093506</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3025512695312</t>
+    <t xml:space="preserve">23.3025493621826</t>
   </si>
   <si>
     <t xml:space="preserve">24.4485778808594</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7323112487793</t>
+    <t xml:space="preserve">23.7323093414307</t>
   </si>
   <si>
     <t xml:space="preserve">23.9710655212402</t>
@@ -2171,10 +2171,10 @@
     <t xml:space="preserve">24.2098217010498</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0665664672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1143188476562</t>
+    <t xml:space="preserve">24.0665683746338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1143207550049</t>
   </si>
   <si>
     <t xml:space="preserve">24.4008235931396</t>
@@ -2192,10 +2192,10 @@
     <t xml:space="preserve">25.0693416595459</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5440788269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9260883331299</t>
+    <t xml:space="preserve">24.5440807342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9260864257812</t>
   </si>
   <si>
     <t xml:space="preserve">25.3558464050293</t>
@@ -2228,10 +2228,10 @@
     <t xml:space="preserve">25.7378578186035</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7856063842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0721130371094</t>
+    <t xml:space="preserve">25.785608291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.072114944458</t>
   </si>
   <si>
     <t xml:space="preserve">26.2631187438965</t>
@@ -2243,7 +2243,7 @@
     <t xml:space="preserve">25.928861618042</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5946044921875</t>
+    <t xml:space="preserve">25.5946025848389</t>
   </si>
   <si>
     <t xml:space="preserve">25.6901073455811</t>
@@ -2255,22 +2255,22 @@
     <t xml:space="preserve">26.4541263580322</t>
   </si>
   <si>
-    <t xml:space="preserve">26.740629196167</t>
+    <t xml:space="preserve">26.7406311035156</t>
   </si>
   <si>
     <t xml:space="preserve">27.0748901367188</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1703929901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6506748199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3219661712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8922023773193</t>
+    <t xml:space="preserve">27.1703910827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6506767272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.321964263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.892204284668</t>
   </si>
   <si>
     <t xml:space="preserve">29.9877071380615</t>
@@ -2309,10 +2309,10 @@
     <t xml:space="preserve">29.0804386138916</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6984252929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9849338531494</t>
+    <t xml:space="preserve">28.6984272003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.984935760498</t>
   </si>
   <si>
     <t xml:space="preserve">28.3641700744629</t>
@@ -2324,25 +2324,25 @@
     <t xml:space="preserve">29.2714385986328</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8389072418213</t>
+    <t xml:space="preserve">27.8389053344727</t>
   </si>
   <si>
     <t xml:space="preserve">27.6479034423828</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6029262542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4119186401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3669414520264</t>
+    <t xml:space="preserve">28.6029243469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4119205474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.366943359375</t>
   </si>
   <si>
     <t xml:space="preserve">29.4146938323975</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0354595184326</t>
+    <t xml:space="preserve">30.0354614257812</t>
   </si>
   <si>
     <t xml:space="preserve">29.748950958252</t>
@@ -2357,10 +2357,10 @@
     <t xml:space="preserve">29.7012023925781</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5579490661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.796703338623</t>
+    <t xml:space="preserve">29.5579471588135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7967014312744</t>
   </si>
   <si>
     <t xml:space="preserve">28.2209148406982</t>
@@ -3423,6 +3423,9 @@
   </si>
   <si>
     <t xml:space="preserve">39.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.5999984741211</t>
   </si>
 </sst>
 </file>
@@ -69333,7 +69336,7 @@
     </row>
     <row r="2523">
       <c r="A2523" s="1" t="n">
-        <v>45992.69125</v>
+        <v>45992.3333333333</v>
       </c>
       <c r="B2523" t="n">
         <v>6574</v>
@@ -69354,6 +69357,32 @@
         <v>1136</v>
       </c>
       <c r="H2523" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2524">
+      <c r="A2524" s="1" t="n">
+        <v>45993.6910069444</v>
+      </c>
+      <c r="B2524" t="n">
+        <v>13353</v>
+      </c>
+      <c r="C2524" t="n">
+        <v>39.6500015258789</v>
+      </c>
+      <c r="D2524" t="n">
+        <v>38.7000007629395</v>
+      </c>
+      <c r="E2524" t="n">
+        <v>39.6500015258789</v>
+      </c>
+      <c r="F2524" t="n">
+        <v>39.5999984741211</v>
+      </c>
+      <c r="G2524" t="s">
+        <v>1137</v>
+      </c>
+      <c r="H2524" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LUVE.MI.xlsx
+++ b/data/LUVE.MI.xlsx
@@ -38,28 +38,28 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30043315887451</t>
+    <t xml:space="preserve">8.30043411254883</t>
   </si>
   <si>
     <t xml:space="preserve">LUVE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31703567504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28383255004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09292316436768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19667816162109</t>
+    <t xml:space="preserve">8.3170337677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28383159637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09292125701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19667720794678</t>
   </si>
   <si>
     <t xml:space="preserve">8.07632064819336</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15102386474609</t>
+    <t xml:space="preserve">8.15102577209473</t>
   </si>
   <si>
     <t xml:space="preserve">8.17177772521973</t>
@@ -68,70 +68,70 @@
     <t xml:space="preserve">8.03896999359131</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08462142944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06802082061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96841812133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01821708679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99746799468994</t>
+    <t xml:space="preserve">8.08462238311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06801986694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96841716766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01821899414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99746894836426</t>
   </si>
   <si>
     <t xml:space="preserve">7.91861295700073</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91446304321289</t>
+    <t xml:space="preserve">7.91446256637573</t>
   </si>
   <si>
     <t xml:space="preserve">7.91031312942505</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88541221618652</t>
+    <t xml:space="preserve">7.88541173934937</t>
   </si>
   <si>
     <t xml:space="preserve">7.87711191177368</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85220909118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.648850440979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71940326690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70280170440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69035243988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61979818344116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55754470825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55339431762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63639879226685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76920461654663</t>
+    <t xml:space="preserve">7.85220956802368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64884948730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7194037437439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70280265808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69035196304321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61979722976685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55754423141479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55339527130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63639783859253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76920557022095</t>
   </si>
   <si>
     <t xml:space="preserve">7.80240774154663</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93521404266357</t>
+    <t xml:space="preserve">7.93521451950073</t>
   </si>
   <si>
     <t xml:space="preserve">8.10122394561768</t>
@@ -140,34 +140,34 @@
     <t xml:space="preserve">8.05142021179199</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18422794342041</t>
+    <t xml:space="preserve">8.18422603607178</t>
   </si>
   <si>
     <t xml:space="preserve">8.13442516326904</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00161838531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9601149559021</t>
+    <t xml:space="preserve">8.00161743164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96011543273926</t>
   </si>
   <si>
     <t xml:space="preserve">8.21742916107178</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35853481292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32533550262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29213237762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20082855224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15932464599609</t>
+    <t xml:space="preserve">8.35853576660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3253345489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29213333129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20082759857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15932559967041</t>
   </si>
   <si>
     <t xml:space="preserve">8.30336380004883</t>
@@ -176,67 +176,67 @@
     <t xml:space="preserve">8.36267375946045</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43045616149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15085220336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17627143859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20592594146729</t>
+    <t xml:space="preserve">8.43045520782471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15085411071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17627239227295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2059268951416</t>
   </si>
   <si>
     <t xml:space="preserve">8.13390922546387</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11696243286133</t>
+    <t xml:space="preserve">8.11696338653564</t>
   </si>
   <si>
     <t xml:space="preserve">8.21863555908203</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21016216278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21439838409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20169162750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26100158691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09154224395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10848808288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04917907714844</t>
+    <t xml:space="preserve">8.21016311645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21440029144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20168876647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26099872589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09154319763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10848712921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04917812347412</t>
   </si>
   <si>
     <t xml:space="preserve">7.9644513130188</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9220871925354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87972259521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8373589515686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12543487548828</t>
+    <t xml:space="preserve">7.92208671569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87972354888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83735752105713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12543392181396</t>
   </si>
   <si>
     <t xml:space="preserve">7.93479633331299</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75263023376465</t>
+    <t xml:space="preserve">7.75263071060181</t>
   </si>
   <si>
     <t xml:space="preserve">7.71026706695557</t>
@@ -245,31 +245,31 @@
     <t xml:space="preserve">7.93903160095215</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81194067001343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79499483108521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62553930282593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66790342330933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84583187103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19321823120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47281932830811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5151834487915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52365779876709</t>
+    <t xml:space="preserve">7.81194114685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79499435424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62553834915161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66790246963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84583139419556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19321727752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47282028198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51518535614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52365589141846</t>
   </si>
   <si>
     <t xml:space="preserve">8.59991264343262</t>
@@ -284,16 +284,16 @@
     <t xml:space="preserve">8.50671195983887</t>
   </si>
   <si>
-    <t xml:space="preserve">8.540602684021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46858310699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46434593200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55754852294922</t>
+    <t xml:space="preserve">8.54060363769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46858215332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46434783935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55754947662354</t>
   </si>
   <si>
     <t xml:space="preserve">8.57449436187744</t>
@@ -308,25 +308,25 @@
     <t xml:space="preserve">8.6422758102417</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89646244049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02355289459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09980773925781</t>
+    <t xml:space="preserve">8.89646053314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0235538482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09980964660645</t>
   </si>
   <si>
     <t xml:space="preserve">9.06591796875</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1082820892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27773761749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19300842285156</t>
+    <t xml:space="preserve">9.10828304290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27773857116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1930103302002</t>
   </si>
   <si>
     <t xml:space="preserve">9.18453693389893</t>
@@ -335,13 +335,13 @@
     <t xml:space="preserve">9.07439041137695</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09133434295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30315685272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32010269165039</t>
+    <t xml:space="preserve">9.09133529663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30315589904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32010173797607</t>
   </si>
   <si>
     <t xml:space="preserve">9.1252269744873</t>
@@ -350,13 +350,13 @@
     <t xml:space="preserve">9.60817813873291</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40483093261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48955917358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38788414001465</t>
+    <t xml:space="preserve">9.40482997894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48955821990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38788509368896</t>
   </si>
   <si>
     <t xml:space="preserve">9.53192329406738</t>
@@ -371,7 +371,7 @@
     <t xml:space="preserve">9.54039573669434</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57428550720215</t>
+    <t xml:space="preserve">9.5742883682251</t>
   </si>
   <si>
     <t xml:space="preserve">9.47261333465576</t>
@@ -386,79 +386,79 @@
     <t xml:space="preserve">9.51497745513916</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5658130645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74374389648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.065710067749</t>
+    <t xml:space="preserve">9.56581401824951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74374485015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0657110214233</t>
   </si>
   <si>
     <t xml:space="preserve">10.2521123886108</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1334924697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99792957305908</t>
+    <t xml:space="preserve">10.1334915161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99792671203613</t>
   </si>
   <si>
     <t xml:space="preserve">9.95556354522705</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98098278045654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88778114318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91320037841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0148725509644</t>
+    <t xml:space="preserve">9.98098182678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88778018951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91320133209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0148735046387</t>
   </si>
   <si>
     <t xml:space="preserve">10.1589117050171</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0402936935425</t>
+    <t xml:space="preserve">10.0402917861938</t>
   </si>
   <si>
     <t xml:space="preserve">9.70137977600098</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73526859283447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70985412597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0826568603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8623628616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1250200271606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2944755554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4808769226074</t>
+    <t xml:space="preserve">9.73526954650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70985221862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0826559066772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86236095428467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.125020980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2944765090942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4808788299561</t>
   </si>
   <si>
     <t xml:space="preserve">10.5317163467407</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5147705078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8028469085693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9129934310913</t>
+    <t xml:space="preserve">10.5147695541382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.802845954895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.912992477417</t>
   </si>
   <si>
     <t xml:space="preserve">10.8621559143066</t>
@@ -467,19 +467,19 @@
     <t xml:space="preserve">11.014666557312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0570297241211</t>
+    <t xml:space="preserve">11.0570306777954</t>
   </si>
   <si>
     <t xml:space="preserve">11.2773246765137</t>
   </si>
   <si>
-    <t xml:space="preserve">11.438307762146</t>
+    <t xml:space="preserve">11.4383068084717</t>
   </si>
   <si>
     <t xml:space="preserve">11.6586008071899</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5823450088501</t>
+    <t xml:space="preserve">11.5823459625244</t>
   </si>
   <si>
     <t xml:space="preserve">11.4806718826294</t>
@@ -488,121 +488,121 @@
     <t xml:space="preserve">11.5908184051514</t>
   </si>
   <si>
-    <t xml:space="preserve">11.700963973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7772188186646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.811110496521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8365306854248</t>
+    <t xml:space="preserve">11.7009649276733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7772197723389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8111114501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8365297317505</t>
   </si>
   <si>
     <t xml:space="preserve">11.6670742034912</t>
   </si>
   <si>
-    <t xml:space="preserve">11.599289894104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5230369567871</t>
+    <t xml:space="preserve">11.5992918014526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5230360031128</t>
   </si>
   <si>
     <t xml:space="preserve">11.6077642440796</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6263799667358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7297267913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6952781677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6780548095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.798623085022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8847465515137</t>
+    <t xml:space="preserve">11.6263809204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7297286987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6952791213989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.678053855896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7986240386963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8847455978394</t>
   </si>
   <si>
     <t xml:space="preserve">11.9105815887451</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0655994415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3153533935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3584127426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0569887161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1431083679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9967031478882</t>
+    <t xml:space="preserve">12.065601348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3153524398804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3584136962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0569877624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1431102752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9967021942139</t>
   </si>
   <si>
     <t xml:space="preserve">11.8416843414307</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7555627822876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7125034332275</t>
+    <t xml:space="preserve">11.7555618286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7125024795532</t>
   </si>
   <si>
     <t xml:space="preserve">11.8502960205078</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9191942214966</t>
+    <t xml:space="preserve">11.9191932678223</t>
   </si>
   <si>
     <t xml:space="preserve">11.962254524231</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0397634506226</t>
+    <t xml:space="preserve">12.0397624969482</t>
   </si>
   <si>
     <t xml:space="preserve">12.0483751296997</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7900114059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0311517715454</t>
+    <t xml:space="preserve">11.7900123596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0311508178711</t>
   </si>
   <si>
     <t xml:space="preserve">11.9450302124023</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8158493041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8933572769165</t>
+    <t xml:space="preserve">11.8158473968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8933582305908</t>
   </si>
   <si>
     <t xml:space="preserve">11.8761329650879</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8244600296021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8675203323364</t>
+    <t xml:space="preserve">11.8244590759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8675212860107</t>
   </si>
   <si>
     <t xml:space="preserve">11.901969909668</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9278059005737</t>
+    <t xml:space="preserve">11.9278078079224</t>
   </si>
   <si>
     <t xml:space="preserve">11.7211141586304</t>
@@ -614,18 +614,15 @@
     <t xml:space="preserve">11.6349935531616</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6091556549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5747079849243</t>
+    <t xml:space="preserve">11.6091566085815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.57470703125</t>
   </si>
   <si>
     <t xml:space="preserve">11.5316476821899</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5230360031128</t>
-  </si>
-  <si>
     <t xml:space="preserve">11.3680171966553</t>
   </si>
   <si>
@@ -635,64 +632,64 @@
     <t xml:space="preserve">11.2818965911865</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2302217483521</t>
+    <t xml:space="preserve">11.2302227020264</t>
   </si>
   <si>
     <t xml:space="preserve">11.1957740783691</t>
   </si>
   <si>
-    <t xml:space="preserve">11.187162399292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1096534729004</t>
+    <t xml:space="preserve">11.1871614456177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1096525192261</t>
   </si>
   <si>
     <t xml:space="preserve">11.0579805374146</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1785488128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.126877784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9374113082886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.066593170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.023530960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0838165283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1354904174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2043876647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3163452148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.454137802124</t>
+    <t xml:space="preserve">11.1785507202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1268768310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9374094009399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0665922164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0235319137573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0838174819946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1354894638062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2043857574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3163461685181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4541387557983</t>
   </si>
   <si>
     <t xml:space="preserve">11.5402603149414</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4110765457153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2905073165894</t>
+    <t xml:space="preserve">11.4110774993896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2905082702637</t>
   </si>
   <si>
     <t xml:space="preserve">11.1613254547119</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2646722793579</t>
+    <t xml:space="preserve">11.2646713256836</t>
   </si>
   <si>
     <t xml:space="preserve">11.1527137756348</t>
@@ -704,16 +701,16 @@
     <t xml:space="preserve">11.4196901321411</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2216100692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2388343811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3421812057495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9546346664429</t>
+    <t xml:space="preserve">11.2216110229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2388353347778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3421792984009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9546356201172</t>
   </si>
   <si>
     <t xml:space="preserve">10.96324634552</t>
@@ -722,55 +719,55 @@
     <t xml:space="preserve">11.0063066482544</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0924282073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74032306671143</t>
+    <t xml:space="preserve">11.0924291610718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74032402038574</t>
   </si>
   <si>
     <t xml:space="preserve">9.01690578460693</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2149829864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37861633300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49057197570801</t>
+    <t xml:space="preserve">9.21498394012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37861442565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49057292938232</t>
   </si>
   <si>
     <t xml:space="preserve">9.5077953338623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59391784667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60252952575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68865013122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56808090209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39583778381348</t>
+    <t xml:space="preserve">9.593918800354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60253047943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6886510848999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56808185577393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39583873748779</t>
   </si>
   <si>
     <t xml:space="preserve">9.34416580200195</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2580451965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30110454559326</t>
+    <t xml:space="preserve">9.25804424285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30110549926758</t>
   </si>
   <si>
     <t xml:space="preserve">9.41306304931641</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28388023376465</t>
+    <t xml:space="preserve">9.28387928009033</t>
   </si>
   <si>
     <t xml:space="preserve">9.24081897735596</t>
@@ -779,52 +776,52 @@
     <t xml:space="preserve">9.12886142730713</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02551651000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20637130737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26665782928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69726371765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65420341491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66281414031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64559078216553</t>
+    <t xml:space="preserve">9.02551746368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20637035369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26665687561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69726276397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65420246124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66281604766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64558982849121</t>
   </si>
   <si>
     <t xml:space="preserve">9.67142677307129</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75754928588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71448612213135</t>
+    <t xml:space="preserve">9.75754737854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71448707580566</t>
   </si>
   <si>
     <t xml:space="preserve">9.09441471099854</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93939685821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14608669281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1202507019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83505821228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73171138763428</t>
+    <t xml:space="preserve">8.93939590454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14608573913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12024974822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83505630493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73171234130859</t>
   </si>
   <si>
     <t xml:space="preserve">9.90395545959473</t>
@@ -833,10 +830,10 @@
     <t xml:space="preserve">9.77477264404297</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53363227844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49918460845947</t>
+    <t xml:space="preserve">9.53363132476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49918365478516</t>
   </si>
   <si>
     <t xml:space="preserve">9.57669353485107</t>
@@ -845,118 +842,118 @@
     <t xml:space="preserve">9.58530616760254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47334671020508</t>
+    <t xml:space="preserve">9.47334575653076</t>
   </si>
   <si>
     <t xml:space="preserve">9.43028736114502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54224395751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17192268371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23220920562744</t>
+    <t xml:space="preserve">9.54224491119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17192363739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23220825195312</t>
   </si>
   <si>
     <t xml:space="preserve">9.55946826934814</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51640701293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8608922958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.956618309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91355800628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08580207824707</t>
+    <t xml:space="preserve">9.51640796661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86089324951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95661926269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91355895996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08580017089844</t>
   </si>
   <si>
     <t xml:space="preserve">9.04274082183838</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99968147277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82743740081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69825649261475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87049865722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78437805175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7413158416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61213397979736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59490966796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65519428253174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45711421966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06314373016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10713958740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0191478729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97515296936035</t>
+    <t xml:space="preserve">8.999680519104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82743835449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69825553894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87049770355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78437614440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74131679534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61213493347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59490871429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65519523620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45711517333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06314468383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10714054107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01914978027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97515201568604</t>
   </si>
   <si>
     <t xml:space="preserve">8.93115711212158</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88716125488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84316539764404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76397323608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48240089416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71117687225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62318706512451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58798980712891</t>
+    <t xml:space="preserve">8.88716220855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84316635131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76397228240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48239898681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71117782592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6231861114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58799076080322</t>
   </si>
   <si>
     <t xml:space="preserve">8.65838241577148</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60558795928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72877597808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69357967376709</t>
+    <t xml:space="preserve">8.60558891296387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7287769317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69357872009277</t>
   </si>
   <si>
     <t xml:space="preserve">8.74637413024902</t>
@@ -965,7 +962,7 @@
     <t xml:space="preserve">8.53519439697266</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44720268249512</t>
+    <t xml:space="preserve">8.44720363616943</t>
   </si>
   <si>
     <t xml:space="preserve">8.27121925354004</t>
@@ -977,13 +974,13 @@
     <t xml:space="preserve">8.288818359375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.781569480896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64078521728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79916763305664</t>
+    <t xml:space="preserve">8.78157043457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64078426361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79916954040527</t>
   </si>
   <si>
     <t xml:space="preserve">8.67598056793213</t>
@@ -992,40 +989,40 @@
     <t xml:space="preserve">9.23912811279297</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37111568450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32711982727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19513130187988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15113639831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46480083465576</t>
+    <t xml:space="preserve">9.37111663818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32711887359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1951322555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15113544464111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46480178833008</t>
   </si>
   <si>
     <t xml:space="preserve">8.41200637817383</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49999809265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34161281585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23602294921875</t>
+    <t xml:space="preserve">8.49999713897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34161186218262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23602199554443</t>
   </si>
   <si>
     <t xml:space="preserve">8.30641555786133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13043117523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1832275390625</t>
+    <t xml:space="preserve">8.13043308258057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18322849273682</t>
   </si>
   <si>
     <t xml:space="preserve">8.16562938690186</t>
@@ -1034,7 +1031,7 @@
     <t xml:space="preserve">8.21842479705811</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25362110137939</t>
+    <t xml:space="preserve">8.25362205505371</t>
   </si>
   <si>
     <t xml:space="preserve">8.37681007385254</t>
@@ -1043,25 +1040,25 @@
     <t xml:space="preserve">8.5175952911377</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28312492370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41511249542236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63509178161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59109401702881</t>
+    <t xml:space="preserve">9.28312301635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41511154174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63509082794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59109497070312</t>
   </si>
   <si>
     <t xml:space="preserve">9.89906597137451</t>
   </si>
   <si>
-    <t xml:space="preserve">10.119044303894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1630411148071</t>
+    <t xml:space="preserve">10.1190462112427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1630401611328</t>
   </si>
   <si>
     <t xml:space="preserve">10.2070360183716</t>
@@ -1070,13 +1067,13 @@
     <t xml:space="preserve">10.3390235900879</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2950286865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3830194473267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2510328292847</t>
+    <t xml:space="preserve">10.2950296401978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3830184936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2510318756104</t>
   </si>
   <si>
     <t xml:space="preserve">10.4270162582397</t>
@@ -1091,37 +1088,40 @@
     <t xml:space="preserve">10.6498155593872</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4700717926025</t>
+    <t xml:space="preserve">10.4700708389282</t>
   </si>
   <si>
     <t xml:space="preserve">10.694751739502</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6048793792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3802003860474</t>
+    <t xml:space="preserve">10.6048784255981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.380199432373</t>
   </si>
   <si>
     <t xml:space="preserve">10.2453918457031</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0656490325928</t>
+    <t xml:space="preserve">10.0656480789185</t>
   </si>
   <si>
     <t xml:space="preserve">10.4251356124878</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3352632522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2903270721436</t>
+    <t xml:space="preserve">10.5150089263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3352651596069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2903280258179</t>
   </si>
   <si>
     <t xml:space="preserve">10.200457572937</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97577857971191</t>
+    <t xml:space="preserve">9.97577667236328</t>
   </si>
   <si>
     <t xml:space="preserve">10.1105842590332</t>
@@ -1130,13 +1130,13 @@
     <t xml:space="preserve">9.93084049224854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88590431213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1555204391479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0207118988037</t>
+    <t xml:space="preserve">9.88590335845947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1555213928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.020712852478</t>
   </si>
   <si>
     <t xml:space="preserve">9.75109767913818</t>
@@ -1145,7 +1145,7 @@
     <t xml:space="preserve">9.70616149902344</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34667205810547</t>
+    <t xml:space="preserve">9.34667301177979</t>
   </si>
   <si>
     <t xml:space="preserve">9.30173778533936</t>
@@ -1160,19 +1160,19 @@
     <t xml:space="preserve">9.61628913879395</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52641773223877</t>
+    <t xml:space="preserve">9.52641677856445</t>
   </si>
   <si>
     <t xml:space="preserve">9.43654537200928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12199306488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0321216583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16693019866943</t>
+    <t xml:space="preserve">9.12199401855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03212261199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16692924499512</t>
   </si>
   <si>
     <t xml:space="preserve">9.07705879211426</t>
@@ -1184,37 +1184,37 @@
     <t xml:space="preserve">8.98718643188477</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5713529586792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66122627258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7960319519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9643669128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4586620330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5035982131958</t>
+    <t xml:space="preserve">9.57135391235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66122531890869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79603290557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9643678665161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4586629867554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5035991668701</t>
   </si>
   <si>
     <t xml:space="preserve">11.233983039856</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1441106796265</t>
+    <t xml:space="preserve">11.1441097259521</t>
   </si>
   <si>
     <t xml:space="preserve">10.9194307327271</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8744964599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0093040466309</t>
+    <t xml:space="preserve">10.8744955062866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0093030929565</t>
   </si>
   <si>
     <t xml:space="preserve">11.278920173645</t>
@@ -1223,16 +1223,16 @@
     <t xml:space="preserve">11.4137258529663</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5485343933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6833429336548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7732152938843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9080228805542</t>
+    <t xml:space="preserve">11.5485334396362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6833419799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.77321434021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9080219268799</t>
   </si>
   <si>
     <t xml:space="preserve">12.132700920105</t>
@@ -1256,37 +1256,37 @@
     <t xml:space="preserve">12.9415483474731</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8067398071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7618036270142</t>
+    <t xml:space="preserve">12.8067407608032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7618045806885</t>
   </si>
   <si>
     <t xml:space="preserve">13.0763559341431</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4472532272339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5371246337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2675085067749</t>
+    <t xml:space="preserve">12.4472541809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5371236801147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2675075531006</t>
   </si>
   <si>
     <t xml:space="preserve">12.4023170471191</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6269960403442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.671932220459</t>
+    <t xml:space="preserve">12.6269969940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6719331741333</t>
   </si>
   <si>
     <t xml:space="preserve">12.8966131210327</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7282772064209</t>
+    <t xml:space="preserve">11.7282781600952</t>
   </si>
   <si>
     <t xml:space="preserve">10.7846240997314</t>
@@ -1298,67 +1298,67 @@
     <t xml:space="preserve">8.89731407165527</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98062181472778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81885194778442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53126239776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89074945449829</t>
+    <t xml:space="preserve">7.98062086105347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81885099411011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53126192092896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89074897766113</t>
   </si>
   <si>
     <t xml:space="preserve">8.53782653808594</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96264600753784</t>
+    <t xml:space="preserve">7.962646484375</t>
   </si>
   <si>
     <t xml:space="preserve">8.44795513153076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6097240447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66364860534668</t>
+    <t xml:space="preserve">8.60972499847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66364669799805</t>
   </si>
   <si>
     <t xml:space="preserve">8.86136531829834</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21186542510986</t>
+    <t xml:space="preserve">9.21186637878418</t>
   </si>
   <si>
     <t xml:space="preserve">9.93848991394043</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80045413970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89247798919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66241931915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7084321975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84646701812744</t>
+    <t xml:space="preserve">9.80045604705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89247894287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66242027282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70843124389648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84646606445312</t>
   </si>
   <si>
     <t xml:space="preserve">10.1225357055664</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75444412231445</t>
+    <t xml:space="preserve">9.75444316864014</t>
   </si>
   <si>
     <t xml:space="preserve">10.3986053466797</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3065805435181</t>
+    <t xml:space="preserve">10.3065814971924</t>
   </si>
   <si>
     <t xml:space="preserve">10.720685005188</t>
@@ -1367,22 +1367,22 @@
     <t xml:space="preserve">10.5826501846313</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8587207794189</t>
+    <t xml:space="preserve">10.8587198257446</t>
   </si>
   <si>
     <t xml:space="preserve">10.6746740341187</t>
   </si>
   <si>
-    <t xml:space="preserve">10.996753692627</t>
+    <t xml:space="preserve">10.9967546463013</t>
   </si>
   <si>
     <t xml:space="preserve">10.628662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7666969299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4906272888184</t>
+    <t xml:space="preserve">10.766697883606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4906282424927</t>
   </si>
   <si>
     <t xml:space="preserve">11.1347894668579</t>
@@ -1394,10 +1394,10 @@
     <t xml:space="preserve">11.5028820037842</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1808004379272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0427675247192</t>
+    <t xml:space="preserve">11.1807994842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0427656173706</t>
   </si>
   <si>
     <t xml:space="preserve">11.2728233337402</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">11.0887775421143</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8127088546753</t>
+    <t xml:space="preserve">10.812707901001</t>
   </si>
   <si>
     <t xml:space="preserve">10.9047317504883</t>
@@ -1421,28 +1421,28 @@
     <t xml:space="preserve">11.4568700790405</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2268114089966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3648471832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5488920211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5949048995972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6869258880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9629964828491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7789506912231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0090074539185</t>
+    <t xml:space="preserve">11.2268123626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3648481369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5488929748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5949039459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6869277954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9629974365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7789516448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0090093612671</t>
   </si>
   <si>
     <t xml:space="preserve">12.1010313034058</t>
@@ -1451,13 +1451,13 @@
     <t xml:space="preserve">11.7329397201538</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8249626159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0550203323364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8709745407104</t>
+    <t xml:space="preserve">11.8249616622925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0550193786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8709735870361</t>
   </si>
   <si>
     <t xml:space="preserve">11.9169845581055</t>
@@ -1469,7 +1469,7 @@
     <t xml:space="preserve">12.1470422744751</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6991815567017</t>
+    <t xml:space="preserve">12.6991806030273</t>
   </si>
   <si>
     <t xml:space="preserve">12.7912034988403</t>
@@ -1484,25 +1484,25 @@
     <t xml:space="preserve">12.9292392730713</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2053079605103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2513189315796</t>
+    <t xml:space="preserve">13.2053089141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2513198852539</t>
   </si>
   <si>
     <t xml:space="preserve">13.1132850646973</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1592969894409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3893556594849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2973299026489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9752502441406</t>
+    <t xml:space="preserve">13.1592960357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3893537521362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2973308563232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9752521514893</t>
   </si>
   <si>
     <t xml:space="preserve">13.7114343643188</t>
@@ -1523,13 +1523,13 @@
     <t xml:space="preserve">12.7451934814453</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6531686782837</t>
+    <t xml:space="preserve">12.653169631958</t>
   </si>
   <si>
     <t xml:space="preserve">13.3433427810669</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6194124221802</t>
+    <t xml:space="preserve">13.6194114685059</t>
   </si>
   <si>
     <t xml:space="preserve">13.8494691848755</t>
@@ -1541,37 +1541,37 @@
     <t xml:space="preserve">14.1715497970581</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3555955886841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1255388259888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4936294555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7236890792847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6776762008667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.815710067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8617219924927</t>
+    <t xml:space="preserve">14.3555965423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1255378723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.493631362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7236881256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.677677154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8157119750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.861722946167</t>
   </si>
   <si>
     <t xml:space="preserve">15.045768737793</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5396413803101</t>
+    <t xml:space="preserve">14.5396423339844</t>
   </si>
   <si>
     <t xml:space="preserve">14.6316652297974</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4476203918457</t>
+    <t xml:space="preserve">14.4476194381714</t>
   </si>
   <si>
     <t xml:space="preserve">14.2635726928711</t>
@@ -1586,31 +1586,31 @@
     <t xml:space="preserve">13.6654233932495</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8034582138062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5733995437622</t>
+    <t xml:space="preserve">13.8034563064575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5734004974365</t>
   </si>
   <si>
     <t xml:space="preserve">13.7574462890625</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9537448883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0335149765015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4269771575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3801383972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4738187789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7080240249634</t>
+    <t xml:space="preserve">14.95374584198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0335140228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4269781112671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3801374435425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.473819732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7080230712891</t>
   </si>
   <si>
     <t xml:space="preserve">14.8485460281372</t>
@@ -1619,40 +1619,40 @@
     <t xml:space="preserve">15.0359086990356</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0827493667603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8953866958618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9422264099121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1764326095581</t>
+    <t xml:space="preserve">15.0827503204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8953857421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9422283172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1764316558838</t>
   </si>
   <si>
     <t xml:space="preserve">15.1295900344849</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9890689849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6611824035645</t>
+    <t xml:space="preserve">14.989068031311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6611804962158</t>
   </si>
   <si>
     <t xml:space="preserve">15.3169546127319</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7548627853394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8017044067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2232723236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5043163299561</t>
+    <t xml:space="preserve">14.7548637390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8017053604126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2232713699341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5043172836304</t>
   </si>
   <si>
     <t xml:space="preserve">16.0664081573486</t>
@@ -1661,22 +1661,22 @@
     <t xml:space="preserve">15.6916809082031</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7385215759277</t>
+    <t xml:space="preserve">15.7385206222534</t>
   </si>
   <si>
     <t xml:space="preserve">15.9727249145508</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9258861541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.785364151001</t>
+    <t xml:space="preserve">15.9258842468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7853631973267</t>
   </si>
   <si>
     <t xml:space="preserve">16.1132488250732</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8322019577026</t>
+    <t xml:space="preserve">15.8322038650513</t>
   </si>
   <si>
     <t xml:space="preserve">16.5348148345947</t>
@@ -1691,16 +1691,16 @@
     <t xml:space="preserve">16.581657409668</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2069301605225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2842712402344</t>
+    <t xml:space="preserve">16.2069282531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.284273147583</t>
   </si>
   <si>
     <t xml:space="preserve">17.7995185852051</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4716339111328</t>
+    <t xml:space="preserve">17.4716300964355</t>
   </si>
   <si>
     <t xml:space="preserve">16.8158626556396</t>
@@ -1709,22 +1709,22 @@
     <t xml:space="preserve">16.6284980773926</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0969047546387</t>
+    <t xml:space="preserve">17.0969066619873</t>
   </si>
   <si>
     <t xml:space="preserve">17.5184745788574</t>
   </si>
   <si>
-    <t xml:space="preserve">17.612154006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0337219238281</t>
+    <t xml:space="preserve">17.6121559143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0337238311768</t>
   </si>
   <si>
     <t xml:space="preserve">18.5489711761475</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7363357543945</t>
+    <t xml:space="preserve">18.7363376617432</t>
   </si>
   <si>
     <t xml:space="preserve">18.923698425293</t>
@@ -1742,58 +1742,58 @@
     <t xml:space="preserve">19.1110610961914</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6731510162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2984237670898</t>
+    <t xml:space="preserve">19.673152923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2984256744385</t>
   </si>
   <si>
     <t xml:space="preserve">19.4857883453369</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8605175018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3289222717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9846935272217</t>
+    <t xml:space="preserve">19.8605155944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3289241790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9846954345703</t>
   </si>
   <si>
     <t xml:space="preserve">21.2657413482666</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0783786773682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4531059265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7973346710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8278312683105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1088790893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7341480255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.015193939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2962379455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4836044311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6404666900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5467834472656</t>
+    <t xml:space="preserve">21.0783748626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.453104019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7973327636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8278293609619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1088752746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7341499328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0151920318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.296236038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4836025238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6404685974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5467853546143</t>
   </si>
   <si>
     <t xml:space="preserve">20.2352428436279</t>
@@ -1808,7 +1808,7 @@
     <t xml:space="preserve">20.6099681854248</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9215106964111</t>
+    <t xml:space="preserve">21.9215145111084</t>
   </si>
   <si>
     <t xml:space="preserve">22.7646465301514</t>
@@ -1820,7 +1820,7 @@
     <t xml:space="preserve">21.1720600128174</t>
   </si>
   <si>
-    <t xml:space="preserve">20.703649520874</t>
+    <t xml:space="preserve">20.7036514282227</t>
   </si>
   <si>
     <t xml:space="preserve">21.3594207763672</t>
@@ -1829,43 +1829,43 @@
     <t xml:space="preserve">20.5162868499756</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0478801727295</t>
+    <t xml:space="preserve">20.0478763580322</t>
   </si>
   <si>
     <t xml:space="preserve">22.6709671020508</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2025566101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3899192810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.954195022583</t>
+    <t xml:space="preserve">22.2025585174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3899211883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9541969299316</t>
   </si>
   <si>
     <t xml:space="preserve">20.4226055145264</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8910121917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3921089172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8300189971924</t>
+    <t xml:space="preserve">20.8910160064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3921070098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8300170898438</t>
   </si>
   <si>
     <t xml:space="preserve">18.361608505249</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9563846588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6589965820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7526760101318</t>
+    <t xml:space="preserve">16.9563827514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6589946746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7526798248291</t>
   </si>
   <si>
     <t xml:space="preserve">17.377950668335</t>
@@ -1877,7 +1877,7 @@
     <t xml:space="preserve">17.9400405883789</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2679252624512</t>
+    <t xml:space="preserve">18.2679271697998</t>
   </si>
   <si>
     <t xml:space="preserve">18.8768577575684</t>
@@ -1886,10 +1886,10 @@
     <t xml:space="preserve">18.6426544189453</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3241348266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2117195129395</t>
+    <t xml:space="preserve">18.3241367340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2117156982422</t>
   </si>
   <si>
     <t xml:space="preserve">18.2304534912109</t>
@@ -1898,7 +1898,7 @@
     <t xml:space="preserve">18.4552898406982</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9494113922119</t>
+    <t xml:space="preserve">17.9494094848633</t>
   </si>
   <si>
     <t xml:space="preserve">18.1180362701416</t>
@@ -1907,7 +1907,7 @@
     <t xml:space="preserve">18.9705390930176</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2820816040039</t>
+    <t xml:space="preserve">20.2820835113525</t>
   </si>
   <si>
     <t xml:space="preserve">20.0947208404541</t>
@@ -1916,7 +1916,7 @@
     <t xml:space="preserve">20.1884002685547</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1415615081787</t>
+    <t xml:space="preserve">20.1415596008301</t>
   </si>
   <si>
     <t xml:space="preserve">18.4927616119385</t>
@@ -1925,19 +1925,19 @@
     <t xml:space="preserve">17.5559463500977</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1999568939209</t>
+    <t xml:space="preserve">17.1999549865723</t>
   </si>
   <si>
     <t xml:space="preserve">16.8847980499268</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7634181976318</t>
+    <t xml:space="preserve">17.7634201049805</t>
   </si>
   <si>
     <t xml:space="preserve">18.0308246612549</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9285449981689</t>
+    <t xml:space="preserve">18.9285469055176</t>
   </si>
   <si>
     <t xml:space="preserve">18.4319343566895</t>
@@ -1964,7 +1964,7 @@
     <t xml:space="preserve">20.0077228546143</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0554714202881</t>
+    <t xml:space="preserve">20.0554752349854</t>
   </si>
   <si>
     <t xml:space="preserve">20.5329856872559</t>
@@ -1973,16 +1973,16 @@
     <t xml:space="preserve">20.9149932861328</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1509761810303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4374828338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0104942321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4880084991455</t>
+    <t xml:space="preserve">20.1509742736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4374809265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0104961395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4880065917969</t>
   </si>
   <si>
     <t xml:space="preserve">19.5779628753662</t>
@@ -1997,7 +1997,7 @@
     <t xml:space="preserve">19.2914562225342</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3392066955566</t>
+    <t xml:space="preserve">19.339204788208</t>
   </si>
   <si>
     <t xml:space="preserve">18.813943862915</t>
@@ -2024,7 +2024,7 @@
     <t xml:space="preserve">19.9599704742432</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4852333068848</t>
+    <t xml:space="preserve">20.4852352142334</t>
   </si>
   <si>
     <t xml:space="preserve">21.1059970855713</t>
@@ -2033,37 +2033,37 @@
     <t xml:space="preserve">21.8700160980225</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3925037384033</t>
+    <t xml:space="preserve">21.392505645752</t>
   </si>
   <si>
     <t xml:space="preserve">21.1537494659424</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7745113372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6790103912354</t>
+    <t xml:space="preserve">21.7745132446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.679012298584</t>
   </si>
   <si>
     <t xml:space="preserve">21.9177684783936</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2970008850098</t>
+    <t xml:space="preserve">21.2970027923584</t>
   </si>
   <si>
     <t xml:space="preserve">21.7267627716064</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5835113525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5807342529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1032238006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6257133483887</t>
+    <t xml:space="preserve">21.5835094451904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5807323455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1032218933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.62571144104</t>
   </si>
   <si>
     <t xml:space="preserve">19.8644676208496</t>
@@ -2084,19 +2084,19 @@
     <t xml:space="preserve">22.0610198974609</t>
   </si>
   <si>
-    <t xml:space="preserve">22.347526550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0582466125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3897304534912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2942295074463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1987247467041</t>
+    <t xml:space="preserve">22.3475284576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0582447052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3897323608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2942276000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1987266540527</t>
   </si>
   <si>
     <t xml:space="preserve">20.8194904327393</t>
@@ -2105,7 +2105,7 @@
     <t xml:space="preserve">20.8672428131104</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0499248504639</t>
+    <t xml:space="preserve">18.0499267578125</t>
   </si>
   <si>
     <t xml:space="preserve">18.833044052124</t>
@@ -2120,7 +2120,7 @@
     <t xml:space="preserve">19.8167171478271</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2464790344238</t>
+    <t xml:space="preserve">20.2464771270752</t>
   </si>
   <si>
     <t xml:space="preserve">20.6762371063232</t>
@@ -2129,7 +2129,7 @@
     <t xml:space="preserve">19.7689666748047</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4402561187744</t>
+    <t xml:space="preserve">21.440258026123</t>
   </si>
   <si>
     <t xml:space="preserve">22.6340351104736</t>
@@ -2141,28 +2141,28 @@
     <t xml:space="preserve">22.7295341491699</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5862827301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8727912902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5385341644287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6817836761475</t>
+    <t xml:space="preserve">22.5862808227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8727893829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5385303497314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6817855834961</t>
   </si>
   <si>
     <t xml:space="preserve">23.0160427093506</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3025493621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4485778808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7323093414307</t>
+    <t xml:space="preserve">23.3025512695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4485759735107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7323112487793</t>
   </si>
   <si>
     <t xml:space="preserve">23.9710655212402</t>
@@ -2171,16 +2171,16 @@
     <t xml:space="preserve">24.2098217010498</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0665683746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1143207550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4008235931396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3080959320068</t>
+    <t xml:space="preserve">24.0665664672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1143188476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4008255004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3080978393555</t>
   </si>
   <si>
     <t xml:space="preserve">23.7800598144531</t>
@@ -2192,22 +2192,22 @@
     <t xml:space="preserve">25.0693416595459</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5440807342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9260864257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3558464050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.403600692749</t>
+    <t xml:space="preserve">24.5440788269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9260883331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3558483123779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4035987854004</t>
   </si>
   <si>
     <t xml:space="preserve">25.8333587646484</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8838844299316</t>
+    <t xml:space="preserve">26.883882522583</t>
   </si>
   <si>
     <t xml:space="preserve">26.7883815765381</t>
@@ -2219,40 +2219,40 @@
     <t xml:space="preserve">24.5918292999268</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8305854797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2603454589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7378578186035</t>
+    <t xml:space="preserve">24.830587387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.260347366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7378597259521</t>
   </si>
   <si>
     <t xml:space="preserve">25.785608291626</t>
   </si>
   <si>
-    <t xml:space="preserve">26.072114944458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2631187438965</t>
+    <t xml:space="preserve">26.0721130371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2631206512451</t>
   </si>
   <si>
     <t xml:space="preserve">25.4513492584229</t>
   </si>
   <si>
-    <t xml:space="preserve">25.928861618042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5946025848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6901073455811</t>
+    <t xml:space="preserve">25.9288597106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5946044921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6901054382324</t>
   </si>
   <si>
     <t xml:space="preserve">25.5468521118164</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4541263580322</t>
+    <t xml:space="preserve">26.4541244506836</t>
   </si>
   <si>
     <t xml:space="preserve">26.7406311035156</t>
@@ -2264,13 +2264,13 @@
     <t xml:space="preserve">27.1703910827637</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6506767272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.321964263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.892204284668</t>
+    <t xml:space="preserve">28.6506748199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3219661712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8922023773193</t>
   </si>
   <si>
     <t xml:space="preserve">29.9877071380615</t>
@@ -2279,7 +2279,7 @@
     <t xml:space="preserve">30.1309604644775</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6534481048584</t>
+    <t xml:space="preserve">29.653450012207</t>
   </si>
   <si>
     <t xml:space="preserve">29.510196685791</t>
@@ -2288,7 +2288,7 @@
     <t xml:space="preserve">28.5074214935303</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3191928863525</t>
+    <t xml:space="preserve">29.3191909790039</t>
   </si>
   <si>
     <t xml:space="preserve">28.9371814727783</t>
@@ -2297,25 +2297,25 @@
     <t xml:space="preserve">28.8416805267334</t>
   </si>
   <si>
-    <t xml:space="preserve">29.223690032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1281852722168</t>
+    <t xml:space="preserve">29.2236919403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1281871795654</t>
   </si>
   <si>
     <t xml:space="preserve">29.1759376525879</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0804386138916</t>
+    <t xml:space="preserve">29.080436706543</t>
   </si>
   <si>
     <t xml:space="preserve">28.6984272003174</t>
   </si>
   <si>
-    <t xml:space="preserve">28.984935760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3641700744629</t>
+    <t xml:space="preserve">28.9849338531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3641681671143</t>
   </si>
   <si>
     <t xml:space="preserve">27.8866577148438</t>
@@ -2330,7 +2330,7 @@
     <t xml:space="preserve">27.6479034423828</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6029243469238</t>
+    <t xml:space="preserve">28.6029262542725</t>
   </si>
   <si>
     <t xml:space="preserve">28.4119205474854</t>
@@ -2342,25 +2342,25 @@
     <t xml:space="preserve">29.4146938323975</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0354614257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.748950958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7039756774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2742156982422</t>
+    <t xml:space="preserve">30.0354595184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7489490509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7039737701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2742137908936</t>
   </si>
   <si>
     <t xml:space="preserve">29.7012023925781</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5579471588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7967014312744</t>
+    <t xml:space="preserve">29.5579490661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.796703338623</t>
   </si>
   <si>
     <t xml:space="preserve">28.2209148406982</t>
@@ -13948,7 +13948,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G392" t="s">
-        <v>203</v>
+        <v>164</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -13974,7 +13974,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G393" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -14000,7 +14000,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G394" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -14026,7 +14026,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G395" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -14052,7 +14052,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G396" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -14078,7 +14078,7 @@
         <v>13</v>
       </c>
       <c r="G397" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -14104,7 +14104,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G398" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -14130,7 +14130,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G399" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -14156,7 +14156,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G400" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -14182,7 +14182,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G401" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -14208,7 +14208,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G402" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -14234,7 +14234,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G403" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -14260,7 +14260,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G404" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -14286,7 +14286,7 @@
         <v>13</v>
       </c>
       <c r="G405" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -14312,7 +14312,7 @@
         <v>13</v>
       </c>
       <c r="G406" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -14338,7 +14338,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G407" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -14364,7 +14364,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G408" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -14390,7 +14390,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G409" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -14416,7 +14416,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G410" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -14442,7 +14442,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G411" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -14468,7 +14468,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G412" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -14494,7 +14494,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G413" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -14520,7 +14520,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G414" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -14546,7 +14546,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G415" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -14572,7 +14572,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G416" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -14598,7 +14598,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G417" t="s">
-        <v>203</v>
+        <v>164</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -14624,7 +14624,7 @@
         <v>13.25</v>
       </c>
       <c r="G418" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -14650,7 +14650,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G419" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -14676,7 +14676,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G420" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -14702,7 +14702,7 @@
         <v>13</v>
       </c>
       <c r="G421" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -14728,7 +14728,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G422" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -14754,7 +14754,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G423" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -14780,7 +14780,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G424" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -14806,7 +14806,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G425" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -14832,7 +14832,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G426" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -14858,7 +14858,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G427" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -14884,7 +14884,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G428" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -14910,7 +14910,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G429" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -14936,7 +14936,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G430" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -14962,7 +14962,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G431" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -14988,7 +14988,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G432" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -15014,7 +15014,7 @@
         <v>13.1700000762939</v>
       </c>
       <c r="G433" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -15040,7 +15040,7 @@
         <v>13</v>
       </c>
       <c r="G434" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -15066,7 +15066,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G435" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -15092,7 +15092,7 @@
         <v>12.7299995422363</v>
       </c>
       <c r="G436" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -15118,7 +15118,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G437" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -15144,7 +15144,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G438" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -15170,7 +15170,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G439" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -15196,7 +15196,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G440" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -15222,7 +15222,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G441" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -15248,7 +15248,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G442" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -15274,7 +15274,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G443" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -15300,7 +15300,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G444" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -15326,7 +15326,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G445" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -15352,7 +15352,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G446" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -15378,7 +15378,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G447" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -15404,7 +15404,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G448" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -15430,7 +15430,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G449" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -15456,7 +15456,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G450" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -15482,7 +15482,7 @@
         <v>11.25</v>
       </c>
       <c r="G451" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -15508,7 +15508,7 @@
         <v>11.1099996566772</v>
       </c>
       <c r="G452" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -15534,7 +15534,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G453" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -15560,7 +15560,7 @@
         <v>11.25</v>
       </c>
       <c r="G454" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -15586,7 +15586,7 @@
         <v>10.9099998474121</v>
       </c>
       <c r="G455" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -15612,7 +15612,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G456" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -15638,7 +15638,7 @@
         <v>10.75</v>
       </c>
       <c r="G457" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -15664,7 +15664,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G458" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -15690,7 +15690,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G459" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -15716,7 +15716,7 @@
         <v>10.9300003051758</v>
       </c>
       <c r="G460" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -15742,7 +15742,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G461" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -15768,7 +15768,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G462" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -15794,7 +15794,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G463" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -15820,7 +15820,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G464" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -15846,7 +15846,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G465" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -15872,7 +15872,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G466" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -15898,7 +15898,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G467" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -15924,7 +15924,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G468" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -15950,7 +15950,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G469" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -15976,7 +15976,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G470" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -16002,7 +16002,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G471" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -16028,7 +16028,7 @@
         <v>11.2299995422363</v>
       </c>
       <c r="G472" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -16054,7 +16054,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G473" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -16080,7 +16080,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G474" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -16106,7 +16106,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G475" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -16132,7 +16132,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G476" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -16158,7 +16158,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G477" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -16184,7 +16184,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G478" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -16210,7 +16210,7 @@
         <v>10.75</v>
       </c>
       <c r="G479" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -16236,7 +16236,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G480" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -16262,7 +16262,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G481" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -16288,7 +16288,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G482" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -16314,7 +16314,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G483" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -16340,7 +16340,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G484" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -16366,7 +16366,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G485" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -16392,7 +16392,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G486" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -16418,7 +16418,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G487" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -16444,7 +16444,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G488" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -16470,7 +16470,7 @@
         <v>11.5</v>
       </c>
       <c r="G489" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -16496,7 +16496,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G490" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -16522,7 +16522,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G491" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -16548,7 +16548,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G492" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -16574,7 +16574,7 @@
         <v>11.0699996948242</v>
       </c>
       <c r="G493" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -16600,7 +16600,7 @@
         <v>11.2299995422363</v>
       </c>
       <c r="G494" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -16626,7 +16626,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G495" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -16652,7 +16652,7 @@
         <v>10.9300003051758</v>
       </c>
       <c r="G496" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -16678,7 +16678,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G497" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -16704,7 +16704,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G498" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -16730,7 +16730,7 @@
         <v>11.25</v>
       </c>
       <c r="G499" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -16756,7 +16756,7 @@
         <v>11.1300001144409</v>
       </c>
       <c r="G500" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -16782,7 +16782,7 @@
         <v>11</v>
       </c>
       <c r="G501" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -16808,7 +16808,7 @@
         <v>11.0699996948242</v>
       </c>
       <c r="G502" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -16834,7 +16834,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G503" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -16860,7 +16860,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G504" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -16886,7 +16886,7 @@
         <v>11</v>
       </c>
       <c r="G505" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -16912,7 +16912,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G506" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -16938,7 +16938,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G507" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -16964,7 +16964,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G508" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -16990,7 +16990,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G509" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -17016,7 +17016,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G510" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -17042,7 +17042,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G511" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -17068,7 +17068,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G512" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -17094,7 +17094,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G513" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -17120,7 +17120,7 @@
         <v>10.75</v>
       </c>
       <c r="G514" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -17146,7 +17146,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G515" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -17172,7 +17172,7 @@
         <v>10.75</v>
       </c>
       <c r="G516" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -17198,7 +17198,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G517" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -17224,7 +17224,7 @@
         <v>11</v>
       </c>
       <c r="G518" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -17250,7 +17250,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G519" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -17276,7 +17276,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G520" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -17302,7 +17302,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G521" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -17328,7 +17328,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G522" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -17354,7 +17354,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G523" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -17380,7 +17380,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G524" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -17406,7 +17406,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G525" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -17432,7 +17432,7 @@
         <v>11.25</v>
       </c>
       <c r="G526" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -17458,7 +17458,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G527" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -17484,7 +17484,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G528" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -17510,7 +17510,7 @@
         <v>11.25</v>
       </c>
       <c r="G529" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -17536,7 +17536,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G530" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -17562,7 +17562,7 @@
         <v>11.5</v>
       </c>
       <c r="G531" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -17588,7 +17588,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G532" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -17614,7 +17614,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G533" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -17640,7 +17640,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G534" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -17666,7 +17666,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G535" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -17692,7 +17692,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G536" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -17718,7 +17718,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G537" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -17744,7 +17744,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G538" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -17770,7 +17770,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G539" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -17796,7 +17796,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G540" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -17822,7 +17822,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G541" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -17848,7 +17848,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G542" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -17874,7 +17874,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G543" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -17900,7 +17900,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G544" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -17926,7 +17926,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G545" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -17952,7 +17952,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G546" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -17978,7 +17978,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G547" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -18004,7 +18004,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G548" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -18030,7 +18030,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G549" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -18056,7 +18056,7 @@
         <v>10.5</v>
       </c>
       <c r="G550" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -18082,7 +18082,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G551" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -18108,7 +18108,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G552" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -18134,7 +18134,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G553" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -18160,7 +18160,7 @@
         <v>10.25</v>
       </c>
       <c r="G554" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -18186,7 +18186,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G555" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -18212,7 +18212,7 @@
         <v>10.25</v>
       </c>
       <c r="G556" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -18238,7 +18238,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G557" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -18264,7 +18264,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G558" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -18290,7 +18290,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G559" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -18316,7 +18316,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G560" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -18342,7 +18342,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G561" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -18368,7 +18368,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G562" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -18394,7 +18394,7 @@
         <v>10.5</v>
       </c>
       <c r="G563" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -18420,7 +18420,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G564" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -18446,7 +18446,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G565" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -18472,7 +18472,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G566" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -18498,7 +18498,7 @@
         <v>10.25</v>
       </c>
       <c r="G567" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -18524,7 +18524,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G568" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -18550,7 +18550,7 @@
         <v>10.25</v>
       </c>
       <c r="G569" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -18576,7 +18576,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G570" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -18602,7 +18602,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G571" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -18628,7 +18628,7 @@
         <v>10</v>
       </c>
       <c r="G572" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -18654,7 +18654,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G573" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -18680,7 +18680,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G574" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -18706,7 +18706,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G575" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -18732,7 +18732,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G576" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -18758,7 +18758,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G577" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -18784,7 +18784,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G578" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -18810,7 +18810,7 @@
         <v>10</v>
       </c>
       <c r="G579" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -18836,7 +18836,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G580" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -18862,7 +18862,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G581" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -18888,7 +18888,7 @@
         <v>10.25</v>
       </c>
       <c r="G582" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -18914,7 +18914,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G583" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -18940,7 +18940,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G584" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -18966,7 +18966,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G585" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -18992,7 +18992,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G586" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -19018,7 +19018,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G587" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -19044,7 +19044,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G588" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -19070,7 +19070,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G589" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -19096,7 +19096,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G590" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -19122,7 +19122,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G591" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -19148,7 +19148,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G592" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -19174,7 +19174,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G593" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -19200,7 +19200,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G594" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -19226,7 +19226,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G595" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -19252,7 +19252,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G596" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -19278,7 +19278,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G597" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -19304,7 +19304,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G598" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -19330,7 +19330,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G599" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -19356,7 +19356,7 @@
         <v>10.25</v>
       </c>
       <c r="G600" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -19382,7 +19382,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G601" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -19408,7 +19408,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G602" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -19434,7 +19434,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G603" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -19460,7 +19460,7 @@
         <v>10.25</v>
       </c>
       <c r="G604" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -19486,7 +19486,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G605" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -19512,7 +19512,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G606" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -19538,7 +19538,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G607" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -19564,7 +19564,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G608" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19590,7 +19590,7 @@
         <v>10.25</v>
       </c>
       <c r="G609" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19616,7 +19616,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G610" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19642,7 +19642,7 @@
         <v>10.25</v>
       </c>
       <c r="G611" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19668,7 +19668,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G612" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19694,7 +19694,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G613" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19720,7 +19720,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G614" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19746,7 +19746,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G615" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19772,7 +19772,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G616" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19798,7 +19798,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G617" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19824,7 +19824,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G618" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19850,7 +19850,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G619" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19876,7 +19876,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G620" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19902,7 +19902,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G621" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19928,7 +19928,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G622" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19954,7 +19954,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G623" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19980,7 +19980,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G624" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -20006,7 +20006,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G625" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -20032,7 +20032,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G626" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -20058,7 +20058,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G627" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -20084,7 +20084,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G628" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -20110,7 +20110,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G629" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -20136,7 +20136,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G630" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -20162,7 +20162,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G631" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -20188,7 +20188,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G632" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -20214,7 +20214,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G633" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -20240,7 +20240,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G634" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -20266,7 +20266,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G635" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -20292,7 +20292,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G636" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -20318,7 +20318,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G637" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -20344,7 +20344,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G638" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -20370,7 +20370,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G639" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -20396,7 +20396,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G640" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -20422,7 +20422,7 @@
         <v>10</v>
       </c>
       <c r="G641" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -20448,7 +20448,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G642" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -20474,7 +20474,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G643" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -20500,7 +20500,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G644" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -20526,7 +20526,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G645" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -20552,7 +20552,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G646" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -20578,7 +20578,7 @@
         <v>10</v>
       </c>
       <c r="G647" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -20604,7 +20604,7 @@
         <v>10</v>
       </c>
       <c r="G648" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -20630,7 +20630,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G649" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -20656,7 +20656,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G650" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -20682,7 +20682,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G651" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -20708,7 +20708,7 @@
         <v>10</v>
       </c>
       <c r="G652" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -20734,7 +20734,7 @@
         <v>10</v>
       </c>
       <c r="G653" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -20760,7 +20760,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G654" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -20786,7 +20786,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G655" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -20812,7 +20812,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G656" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -20838,7 +20838,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G657" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -20864,7 +20864,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G658" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -20890,7 +20890,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G659" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -20916,7 +20916,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G660" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -20942,7 +20942,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G661" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -20968,7 +20968,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G662" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -20994,7 +20994,7 @@
         <v>10</v>
       </c>
       <c r="G663" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -21020,7 +21020,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G664" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -21046,7 +21046,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G665" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -21072,7 +21072,7 @@
         <v>10.25</v>
       </c>
       <c r="G666" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -21098,7 +21098,7 @@
         <v>10</v>
       </c>
       <c r="G667" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -21124,7 +21124,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G668" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -21150,7 +21150,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G669" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -21176,7 +21176,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G670" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -21202,7 +21202,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G671" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -21228,7 +21228,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G672" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -21254,7 +21254,7 @@
         <v>10</v>
       </c>
       <c r="G673" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -21280,7 +21280,7 @@
         <v>10</v>
       </c>
       <c r="G674" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -21306,7 +21306,7 @@
         <v>10</v>
       </c>
       <c r="G675" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -21332,7 +21332,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G676" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -21358,7 +21358,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G677" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -21384,7 +21384,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G678" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -21410,7 +21410,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G679" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -21436,7 +21436,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G680" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -21462,7 +21462,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G681" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -21488,7 +21488,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G682" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -21514,7 +21514,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G683" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -21540,7 +21540,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G684" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -21566,7 +21566,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G685" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -21592,7 +21592,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G686" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -21618,7 +21618,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G687" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -21644,7 +21644,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G688" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -21670,7 +21670,7 @@
         <v>10</v>
       </c>
       <c r="G689" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -21696,7 +21696,7 @@
         <v>10</v>
       </c>
       <c r="G690" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -21722,7 +21722,7 @@
         <v>10</v>
       </c>
       <c r="G691" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -21748,7 +21748,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G692" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -21774,7 +21774,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G693" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -21800,7 +21800,7 @@
         <v>10</v>
       </c>
       <c r="G694" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -21826,7 +21826,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G695" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -21852,7 +21852,7 @@
         <v>10</v>
       </c>
       <c r="G696" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -21878,7 +21878,7 @@
         <v>10</v>
       </c>
       <c r="G697" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -21904,7 +21904,7 @@
         <v>10.5</v>
       </c>
       <c r="G698" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -21930,7 +21930,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G699" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -21956,7 +21956,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G700" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -21982,7 +21982,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G701" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -22008,7 +22008,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G702" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -22034,7 +22034,7 @@
         <v>10.25</v>
       </c>
       <c r="G703" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -22060,7 +22060,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G704" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -22086,7 +22086,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G705" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -22112,7 +22112,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G706" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -22138,7 +22138,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G707" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -22164,7 +22164,7 @@
         <v>10</v>
       </c>
       <c r="G708" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -22190,7 +22190,7 @@
         <v>10</v>
       </c>
       <c r="G709" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -22216,7 +22216,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G710" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -22242,7 +22242,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G711" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -22268,7 +22268,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G712" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -22294,7 +22294,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G713" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -22320,7 +22320,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G714" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -22346,7 +22346,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G715" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -22372,7 +22372,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G716" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -22398,7 +22398,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G717" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -22424,7 +22424,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G718" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -22450,7 +22450,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G719" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -22476,7 +22476,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G720" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -22502,7 +22502,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G721" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -22528,7 +22528,7 @@
         <v>10</v>
       </c>
       <c r="G722" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -22554,7 +22554,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G723" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -22580,7 +22580,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G724" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -22606,7 +22606,7 @@
         <v>10</v>
       </c>
       <c r="G725" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -22632,7 +22632,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G726" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -22658,7 +22658,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G727" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -22684,7 +22684,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G728" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -22710,7 +22710,7 @@
         <v>10</v>
       </c>
       <c r="G729" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -22736,7 +22736,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G730" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -22762,7 +22762,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G731" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -22788,7 +22788,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G732" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -22814,7 +22814,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G733" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -22840,7 +22840,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G734" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -22866,7 +22866,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G735" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -22892,7 +22892,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G736" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -22918,7 +22918,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G737" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -22944,7 +22944,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G738" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -22970,7 +22970,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G739" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -22996,7 +22996,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G740" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -23022,7 +23022,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G741" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -23048,7 +23048,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G742" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -23074,7 +23074,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G743" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -23100,7 +23100,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G744" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -23126,7 +23126,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G745" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -23152,7 +23152,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G746" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -23178,7 +23178,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G747" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -23204,7 +23204,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G748" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -23230,7 +23230,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G749" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -23256,7 +23256,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G750" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -23282,7 +23282,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G751" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -23308,7 +23308,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G752" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -23334,7 +23334,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G753" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -23360,7 +23360,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G754" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -23386,7 +23386,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G755" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -23412,7 +23412,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G756" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -23438,7 +23438,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G757" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -23464,7 +23464,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G758" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -23490,7 +23490,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G759" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -23516,7 +23516,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G760" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -23542,7 +23542,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G761" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -23568,7 +23568,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G762" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -23594,7 +23594,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G763" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -23620,7 +23620,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G764" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -23646,7 +23646,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G765" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -23672,7 +23672,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G766" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -23698,7 +23698,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G767" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -23724,7 +23724,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G768" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -23750,7 +23750,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G769" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -23776,7 +23776,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G770" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -23802,7 +23802,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G771" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -23828,7 +23828,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G772" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -23854,7 +23854,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G773" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -23880,7 +23880,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G774" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -23906,7 +23906,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G775" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -23932,7 +23932,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G776" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -23958,7 +23958,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G777" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -23984,7 +23984,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G778" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -24010,7 +24010,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G779" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -24036,7 +24036,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G780" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -24062,7 +24062,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G781" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -24088,7 +24088,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G782" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -24114,7 +24114,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G783" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -24140,7 +24140,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G784" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -24166,7 +24166,7 @@
         <v>10</v>
       </c>
       <c r="G785" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -24192,7 +24192,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G786" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -24218,7 +24218,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G787" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -24244,7 +24244,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G788" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -24270,7 +24270,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G789" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -24296,7 +24296,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G790" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -24322,7 +24322,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G791" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -24348,7 +24348,7 @@
         <v>10</v>
       </c>
       <c r="G792" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -24374,7 +24374,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G793" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -24400,7 +24400,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G794" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -24426,7 +24426,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G795" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -24452,7 +24452,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G796" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -24478,7 +24478,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G797" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -24504,7 +24504,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G798" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -24530,7 +24530,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G799" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -24556,7 +24556,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G800" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -24582,7 +24582,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G801" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -24608,7 +24608,7 @@
         <v>10.25</v>
       </c>
       <c r="G802" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -24634,7 +24634,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G803" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -24660,7 +24660,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G804" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -24686,7 +24686,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G805" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -24712,7 +24712,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G806" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -24738,7 +24738,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G807" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -24764,7 +24764,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G808" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -24790,7 +24790,7 @@
         <v>10.5</v>
       </c>
       <c r="G809" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -24816,7 +24816,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G810" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -24842,7 +24842,7 @@
         <v>10</v>
       </c>
       <c r="G811" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -24868,7 +24868,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G812" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -24894,7 +24894,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G813" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -24920,7 +24920,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G814" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -24946,7 +24946,7 @@
         <v>10.5</v>
       </c>
       <c r="G815" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -24972,7 +24972,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G816" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -24998,7 +24998,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G817" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -25024,7 +25024,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G818" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -25050,7 +25050,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G819" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -25076,7 +25076,7 @@
         <v>11.25</v>
       </c>
       <c r="G820" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -25102,7 +25102,7 @@
         <v>11.5</v>
       </c>
       <c r="G821" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -25128,7 +25128,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G822" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -25154,7 +25154,7 @@
         <v>11.5</v>
       </c>
       <c r="G823" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -25180,7 +25180,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G824" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -25206,7 +25206,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G825" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -25232,7 +25232,7 @@
         <v>11.75</v>
       </c>
       <c r="G826" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -25258,7 +25258,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G827" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -25284,7 +25284,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G828" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -25310,7 +25310,7 @@
         <v>11.75</v>
       </c>
       <c r="G829" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -25336,7 +25336,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G830" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -25362,7 +25362,7 @@
         <v>11.75</v>
       </c>
       <c r="G831" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -25388,7 +25388,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G832" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -25414,7 +25414,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G833" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -25440,7 +25440,7 @@
         <v>11.75</v>
       </c>
       <c r="G834" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -25466,7 +25466,7 @@
         <v>11.75</v>
       </c>
       <c r="G835" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -25492,7 +25492,7 @@
         <v>11.75</v>
       </c>
       <c r="G836" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -25518,7 +25518,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G837" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -25544,7 +25544,7 @@
         <v>11.75</v>
       </c>
       <c r="G838" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -25570,7 +25570,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G839" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -25596,7 +25596,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G840" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -25622,7 +25622,7 @@
         <v>11.25</v>
       </c>
       <c r="G841" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -25648,7 +25648,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G842" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -25674,7 +25674,7 @@
         <v>11.5</v>
       </c>
       <c r="G843" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -25700,7 +25700,7 @@
         <v>11.5</v>
       </c>
       <c r="G844" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -25726,7 +25726,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G845" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -25752,7 +25752,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G846" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -25778,7 +25778,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G847" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -25804,7 +25804,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G848" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -25830,7 +25830,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G849" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -25856,7 +25856,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G850" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -25882,7 +25882,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G851" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -25908,7 +25908,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G852" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -25934,7 +25934,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G853" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -25960,7 +25960,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G854" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -25986,7 +25986,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G855" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -26012,7 +26012,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G856" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -26038,7 +26038,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G857" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -26064,7 +26064,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G858" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -26090,7 +26090,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G859" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -26116,7 +26116,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G860" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -26142,7 +26142,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G861" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -26168,7 +26168,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G862" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -26194,7 +26194,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G863" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -26220,7 +26220,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G864" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -26246,7 +26246,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G865" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -26272,7 +26272,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G866" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -26298,7 +26298,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G867" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -26324,7 +26324,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G868" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -26350,7 +26350,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G869" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -26376,7 +26376,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G870" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -26610,7 +26610,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G879" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -26714,7 +26714,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G883" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -26766,7 +26766,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G885" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -26896,7 +26896,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G890" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -27000,7 +27000,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G894" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -27052,7 +27052,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G896" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -27078,7 +27078,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G897" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -27338,7 +27338,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G907" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -27416,7 +27416,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G910" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -27442,7 +27442,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G911" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -27468,7 +27468,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G912" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -27572,7 +27572,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G916" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -27624,7 +27624,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G918" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -29470,7 +29470,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G989" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -29548,7 +29548,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G992" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -31420,7 +31420,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1064" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -32278,7 +32278,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1097" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -32330,7 +32330,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G1099" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -69362,7 +69362,7 @@
     </row>
     <row r="2524">
       <c r="A2524" s="1" t="n">
-        <v>45993.6910069444</v>
+        <v>45993.3333333333</v>
       </c>
       <c r="B2524" t="n">
         <v>13353</v>
@@ -69383,6 +69383,32 @@
         <v>1137</v>
       </c>
       <c r="H2524" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2525">
+      <c r="A2525" s="1" t="n">
+        <v>45994.6911111111</v>
+      </c>
+      <c r="B2525" t="n">
+        <v>16982</v>
+      </c>
+      <c r="C2525" t="n">
+        <v>39.75</v>
+      </c>
+      <c r="D2525" t="n">
+        <v>39</v>
+      </c>
+      <c r="E2525" t="n">
+        <v>39.3499984741211</v>
+      </c>
+      <c r="F2525" t="n">
+        <v>39.5999984741211</v>
+      </c>
+      <c r="G2525" t="s">
+        <v>1137</v>
+      </c>
+      <c r="H2525" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LUVE.MI.xlsx
+++ b/data/LUVE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1138" uniqueCount="1138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1139" uniqueCount="1139">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,31 +38,31 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30043411254883</t>
+    <t xml:space="preserve">8.30043506622314</t>
   </si>
   <si>
     <t xml:space="preserve">LUVE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3170337677002</t>
+    <t xml:space="preserve">8.31703472137451</t>
   </si>
   <si>
     <t xml:space="preserve">8.28383159637451</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09292125701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19667720794678</t>
+    <t xml:space="preserve">8.09292316436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19667816162109</t>
   </si>
   <si>
     <t xml:space="preserve">8.07632064819336</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15102577209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17177772521973</t>
+    <t xml:space="preserve">8.15102481842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17177677154541</t>
   </si>
   <si>
     <t xml:space="preserve">8.03896999359131</t>
@@ -71,40 +71,40 @@
     <t xml:space="preserve">8.08462238311768</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06801986694336</t>
+    <t xml:space="preserve">8.06802177429199</t>
   </si>
   <si>
     <t xml:space="preserve">7.96841716766357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01821899414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99746894836426</t>
+    <t xml:space="preserve">8.01821994781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99746704101562</t>
   </si>
   <si>
     <t xml:space="preserve">7.91861295700073</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91446256637573</t>
+    <t xml:space="preserve">7.91446399688721</t>
   </si>
   <si>
     <t xml:space="preserve">7.91031312942505</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88541173934937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87711191177368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85220956802368</t>
+    <t xml:space="preserve">7.88541221618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87711000442505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85221099853516</t>
   </si>
   <si>
     <t xml:space="preserve">7.64884948730469</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7194037437439</t>
+    <t xml:space="preserve">7.71940279006958</t>
   </si>
   <si>
     <t xml:space="preserve">7.70280265808105</t>
@@ -113,154 +113,154 @@
     <t xml:space="preserve">7.69035196304321</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61979722976685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55754423141479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55339527130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63639783859253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76920557022095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80240774154663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93521451950073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10122394561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05142021179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18422603607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13442516326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00161743164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96011543273926</t>
+    <t xml:space="preserve">7.61979818344116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55754518508911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55339431762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63639736175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76920509338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.802405834198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93521499633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10122299194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05142211914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18422794342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13442611694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00161838531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96011590957642</t>
   </si>
   <si>
     <t xml:space="preserve">8.21742916107178</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35853576660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3253345489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29213333129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20082759857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15932559967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30336380004883</t>
+    <t xml:space="preserve">8.35853672027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32533359527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29213237762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20082855224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15932464599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30336475372314</t>
   </si>
   <si>
     <t xml:space="preserve">8.36267375946045</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43045520782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15085411071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17627239227295</t>
+    <t xml:space="preserve">8.43045616149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15085315704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17627143859863</t>
   </si>
   <si>
     <t xml:space="preserve">8.2059268951416</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13390922546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11696338653564</t>
+    <t xml:space="preserve">8.13390827178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11696147918701</t>
   </si>
   <si>
     <t xml:space="preserve">8.21863555908203</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21016311645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21440029144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20168876647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26099872589111</t>
+    <t xml:space="preserve">8.21016216278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21439838409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20169067382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26100063323975</t>
   </si>
   <si>
     <t xml:space="preserve">8.09154319763184</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10848712921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04917812347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9644513130188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92208671569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87972354888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83735752105713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12543392181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93479633331299</t>
+    <t xml:space="preserve">8.10848808288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04917907714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96445035934448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92208623886108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87972259521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83735799789429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1254358291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93479537963867</t>
   </si>
   <si>
     <t xml:space="preserve">7.75263071060181</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71026706695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93903160095215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81194114685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79499435424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62553834915161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66790246963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84583139419556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19321727752686</t>
+    <t xml:space="preserve">7.71026611328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93903255462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81194067001343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79499340057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62553691864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66790151596069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84583187103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19321918487549</t>
   </si>
   <si>
     <t xml:space="preserve">8.47282028198242</t>
@@ -269,7 +269,7 @@
     <t xml:space="preserve">8.51518535614014</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52365589141846</t>
+    <t xml:space="preserve">8.52365684509277</t>
   </si>
   <si>
     <t xml:space="preserve">8.59991264343262</t>
@@ -278,49 +278,49 @@
     <t xml:space="preserve">8.78631496429443</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71853256225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50671195983887</t>
+    <t xml:space="preserve">8.71853351593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50671100616455</t>
   </si>
   <si>
     <t xml:space="preserve">8.54060363769531</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46858215332031</t>
+    <t xml:space="preserve">8.46858406066895</t>
   </si>
   <si>
     <t xml:space="preserve">8.46434783935547</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55754947662354</t>
+    <t xml:space="preserve">8.55754852294922</t>
   </si>
   <si>
     <t xml:space="preserve">8.57449436187744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81173229217529</t>
+    <t xml:space="preserve">8.81173324584961</t>
   </si>
   <si>
     <t xml:space="preserve">8.72700500488281</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6422758102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89646053314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0235538482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09980964660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06591796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10828304290771</t>
+    <t xml:space="preserve">8.64227676391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89646244049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02355289459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09980773925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06591892242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1082820892334</t>
   </si>
   <si>
     <t xml:space="preserve">9.27773857116699</t>
@@ -329,10 +329,10 @@
     <t xml:space="preserve">9.1930103302002</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18453693389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07439041137695</t>
+    <t xml:space="preserve">9.18453788757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07439136505127</t>
   </si>
   <si>
     <t xml:space="preserve">9.09133529663086</t>
@@ -341,25 +341,25 @@
     <t xml:space="preserve">9.30315589904785</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32010173797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1252269744873</t>
+    <t xml:space="preserve">9.32010269165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12522792816162</t>
   </si>
   <si>
     <t xml:space="preserve">9.60817813873291</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40482997894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48955821990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38788509368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53192329406738</t>
+    <t xml:space="preserve">9.4048318862915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48955726623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38788414001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5319242477417</t>
   </si>
   <si>
     <t xml:space="preserve">9.48108577728271</t>
@@ -368,52 +368,52 @@
     <t xml:space="preserve">9.44719505310059</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54039573669434</t>
+    <t xml:space="preserve">9.54039478302002</t>
   </si>
   <si>
     <t xml:space="preserve">9.5742883682251</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47261333465576</t>
+    <t xml:space="preserve">9.47261428833008</t>
   </si>
   <si>
     <t xml:space="preserve">9.41330337524414</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42177677154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51497745513916</t>
+    <t xml:space="preserve">9.42177486419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51497650146484</t>
   </si>
   <si>
     <t xml:space="preserve">9.56581401824951</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74374485015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0657110214233</t>
+    <t xml:space="preserve">9.74374294281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.065710067749</t>
   </si>
   <si>
     <t xml:space="preserve">10.2521123886108</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1334915161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99792671203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95556354522705</t>
+    <t xml:space="preserve">10.1334924697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99792861938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95556259155273</t>
   </si>
   <si>
     <t xml:space="preserve">9.98098182678223</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88778018951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91320133209229</t>
+    <t xml:space="preserve">9.88778114318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91319942474365</t>
   </si>
   <si>
     <t xml:space="preserve">10.0148735046387</t>
@@ -425,31 +425,31 @@
     <t xml:space="preserve">10.0402917861938</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70137977600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73526954650879</t>
+    <t xml:space="preserve">9.70137786865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73527145385742</t>
   </si>
   <si>
     <t xml:space="preserve">9.70985221862793</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0826559066772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86236095428467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.125020980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2944765090942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4808788299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5317163467407</t>
+    <t xml:space="preserve">10.0826549530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86236381530762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1250200271606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2944755554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4808778762817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5317153930664</t>
   </si>
   <si>
     <t xml:space="preserve">10.5147695541382</t>
@@ -458,28 +458,28 @@
     <t xml:space="preserve">10.802845954895</t>
   </si>
   <si>
-    <t xml:space="preserve">10.912992477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8621559143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.014666557312</t>
+    <t xml:space="preserve">10.9129934310913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.862156867981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0146656036377</t>
   </si>
   <si>
     <t xml:space="preserve">11.0570306777954</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2773246765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4383068084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6586008071899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5823459625244</t>
+    <t xml:space="preserve">11.277325630188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.438307762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6586017608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5823450088501</t>
   </si>
   <si>
     <t xml:space="preserve">11.4806718826294</t>
@@ -494,7 +494,7 @@
     <t xml:space="preserve">11.7772197723389</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8111114501953</t>
+    <t xml:space="preserve">11.811110496521</t>
   </si>
   <si>
     <t xml:space="preserve">11.8365297317505</t>
@@ -503,106 +503,106 @@
     <t xml:space="preserve">11.6670742034912</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5992918014526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5230360031128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6077642440796</t>
+    <t xml:space="preserve">11.599289894104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5230350494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6077651977539</t>
   </si>
   <si>
     <t xml:space="preserve">11.6263809204102</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7297286987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6952791213989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.678053855896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7986240386963</t>
+    <t xml:space="preserve">11.7297258377075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6952781677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6780548095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7986249923706</t>
   </si>
   <si>
     <t xml:space="preserve">11.8847455978394</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9105815887451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.065601348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3153524398804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3584136962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0569877624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1431102752686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9967021942139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8416843414307</t>
+    <t xml:space="preserve">11.9105806350708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0656003952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3153514862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3584127426147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0569887161255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1431093215942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9967031478882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.841685295105</t>
   </si>
   <si>
     <t xml:space="preserve">11.7555618286133</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7125024795532</t>
+    <t xml:space="preserve">11.7125034332275</t>
   </si>
   <si>
     <t xml:space="preserve">11.8502960205078</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9191932678223</t>
+    <t xml:space="preserve">11.9191923141479</t>
   </si>
   <si>
     <t xml:space="preserve">11.962254524231</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0397624969482</t>
+    <t xml:space="preserve">12.0397634506226</t>
   </si>
   <si>
     <t xml:space="preserve">12.0483751296997</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7900123596191</t>
+    <t xml:space="preserve">11.7900094985962</t>
   </si>
   <si>
     <t xml:space="preserve">12.0311508178711</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9450302124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8158473968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8933582305908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8761329650879</t>
+    <t xml:space="preserve">11.945029258728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8158483505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8933572769165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8761320114136</t>
   </si>
   <si>
     <t xml:space="preserve">11.8244590759277</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8675212860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.901969909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9278078079224</t>
+    <t xml:space="preserve">11.8675203323364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9019689559937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.927806854248</t>
   </si>
   <si>
     <t xml:space="preserve">11.7211141586304</t>
@@ -620,13 +620,16 @@
     <t xml:space="preserve">11.57470703125</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5316476821899</t>
+    <t xml:space="preserve">11.5316467285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5230340957642</t>
   </si>
   <si>
     <t xml:space="preserve">11.3680171966553</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3594045639038</t>
+    <t xml:space="preserve">11.3594036102295</t>
   </si>
   <si>
     <t xml:space="preserve">11.2818965911865</t>
@@ -641,19 +644,19 @@
     <t xml:space="preserve">11.1871614456177</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1096525192261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0579805374146</t>
+    <t xml:space="preserve">11.1096534729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0579814910889</t>
   </si>
   <si>
     <t xml:space="preserve">11.1785507202148</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1268768310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9374094009399</t>
+    <t xml:space="preserve">11.126877784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9374103546143</t>
   </si>
   <si>
     <t xml:space="preserve">11.0665922164917</t>
@@ -662,31 +665,31 @@
     <t xml:space="preserve">11.0235319137573</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0838174819946</t>
+    <t xml:space="preserve">11.0838165283203</t>
   </si>
   <si>
     <t xml:space="preserve">11.1354894638062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2043857574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3163461685181</t>
+    <t xml:space="preserve">11.2043876647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3163452148438</t>
   </si>
   <si>
     <t xml:space="preserve">11.4541387557983</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5402603149414</t>
+    <t xml:space="preserve">11.5402612686157</t>
   </si>
   <si>
     <t xml:space="preserve">11.4110774993896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2905082702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1613254547119</t>
+    <t xml:space="preserve">11.2905073165894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1613264083862</t>
   </si>
   <si>
     <t xml:space="preserve">11.2646713256836</t>
@@ -695,91 +698,91 @@
     <t xml:space="preserve">11.1527137756348</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0407562255859</t>
+    <t xml:space="preserve">11.0407571792603</t>
   </si>
   <si>
     <t xml:space="preserve">11.4196901321411</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2216110229492</t>
+    <t xml:space="preserve">11.2216100692749</t>
   </si>
   <si>
     <t xml:space="preserve">11.2388353347778</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3421792984009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9546356201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.96324634552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0063066482544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0924291610718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74032402038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01690578460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21498394012451</t>
+    <t xml:space="preserve">11.3421802520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9546365737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9632453918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0063076019287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0924301147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74032306671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01690483093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21498489379883</t>
   </si>
   <si>
     <t xml:space="preserve">9.37861442565918</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49057292938232</t>
+    <t xml:space="preserve">9.49057102203369</t>
   </si>
   <si>
     <t xml:space="preserve">9.5077953338623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.593918800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60253047943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6886510848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56808185577393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39583873748779</t>
+    <t xml:space="preserve">9.59391784667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60252952575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68865013122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56807994842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39583683013916</t>
   </si>
   <si>
     <t xml:space="preserve">9.34416580200195</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25804424285889</t>
+    <t xml:space="preserve">9.2580451965332</t>
   </si>
   <si>
     <t xml:space="preserve">9.30110549926758</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41306304931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28387928009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24081897735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12886142730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02551746368408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20637035369873</t>
+    <t xml:space="preserve">9.41306114196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28388118743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24081993103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12886238098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02551555633545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20637130737305</t>
   </si>
   <si>
     <t xml:space="preserve">9.26665687561035</t>
@@ -788,19 +791,19 @@
     <t xml:space="preserve">9.69726276397705</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65420246124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66281604766846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64558982849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67142677307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75754737854004</t>
+    <t xml:space="preserve">9.65420150756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66281509399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64559078216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67142581939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75754833221436</t>
   </si>
   <si>
     <t xml:space="preserve">9.71448707580566</t>
@@ -812,10 +815,10 @@
     <t xml:space="preserve">8.93939590454102</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14608573913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12024974822998</t>
+    <t xml:space="preserve">9.14608764648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1202507019043</t>
   </si>
   <si>
     <t xml:space="preserve">9.83505630493164</t>
@@ -824,31 +827,31 @@
     <t xml:space="preserve">9.73171234130859</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90395545959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77477264404297</t>
+    <t xml:space="preserve">9.90395355224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77477169036865</t>
   </si>
   <si>
     <t xml:space="preserve">9.53363132476807</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49918365478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57669353485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58530616760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47334575653076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43028736114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54224491119385</t>
+    <t xml:space="preserve">9.49918460845947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57669162750244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58530521392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47334766387939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4302864074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54224586486816</t>
   </si>
   <si>
     <t xml:space="preserve">9.17192363739014</t>
@@ -857,73 +860,73 @@
     <t xml:space="preserve">9.23220825195312</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55946826934814</t>
+    <t xml:space="preserve">9.55946922302246</t>
   </si>
   <si>
     <t xml:space="preserve">9.51640796661377</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86089324951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95661926269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91355895996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08580017089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04274082183838</t>
+    <t xml:space="preserve">9.8608922958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95662021636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91355991363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08580112457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0427417755127</t>
   </si>
   <si>
     <t xml:space="preserve">8.999680519104</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82743835449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69825553894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87049770355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78437614440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74131679534912</t>
+    <t xml:space="preserve">8.82743740081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69825649261475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87049865722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7843770980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74131488800049</t>
   </si>
   <si>
     <t xml:space="preserve">8.61213493347168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59490871429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65519523620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45711517333984</t>
+    <t xml:space="preserve">8.59490966796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65519618988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45711612701416</t>
   </si>
   <si>
     <t xml:space="preserve">9.06314468383789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10714054107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01914978027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97515201568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93115711212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88716220855713</t>
+    <t xml:space="preserve">9.10714149475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01914882659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97515296936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93115615844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88716316223145</t>
   </si>
   <si>
     <t xml:space="preserve">8.84316635131836</t>
@@ -932,25 +935,25 @@
     <t xml:space="preserve">8.76397228240967</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48239898681641</t>
+    <t xml:space="preserve">8.48239994049072</t>
   </si>
   <si>
     <t xml:space="preserve">8.71117782592773</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6231861114502</t>
+    <t xml:space="preserve">8.62318706512451</t>
   </si>
   <si>
     <t xml:space="preserve">8.58799076080322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65838241577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60558891296387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7287769317627</t>
+    <t xml:space="preserve">8.6583833694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60558700561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72877597808838</t>
   </si>
   <si>
     <t xml:space="preserve">8.69357872009277</t>
@@ -968,13 +971,13 @@
     <t xml:space="preserve">8.27121925354004</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32401371002197</t>
+    <t xml:space="preserve">8.32401466369629</t>
   </si>
   <si>
     <t xml:space="preserve">8.288818359375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78157043457031</t>
+    <t xml:space="preserve">8.781569480896</t>
   </si>
   <si>
     <t xml:space="preserve">8.64078426361084</t>
@@ -986,28 +989,28 @@
     <t xml:space="preserve">8.67598056793213</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23912811279297</t>
+    <t xml:space="preserve">9.23912906646729</t>
   </si>
   <si>
     <t xml:space="preserve">9.37111663818359</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32711887359619</t>
+    <t xml:space="preserve">9.32712078094482</t>
   </si>
   <si>
     <t xml:space="preserve">9.1951322555542</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15113544464111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46480178833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41200637817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49999713897705</t>
+    <t xml:space="preserve">9.15113735198975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46479988098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41200733184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49999809265137</t>
   </si>
   <si>
     <t xml:space="preserve">8.34161186218262</t>
@@ -1019,58 +1022,58 @@
     <t xml:space="preserve">8.30641555786133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13043308258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18322849273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16562938690186</t>
+    <t xml:space="preserve">8.13043212890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18322658538818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16562843322754</t>
   </si>
   <si>
     <t xml:space="preserve">8.21842479705811</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25362205505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37681007385254</t>
+    <t xml:space="preserve">8.25362014770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37680912017822</t>
   </si>
   <si>
     <t xml:space="preserve">8.5175952911377</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28312301635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41511154174805</t>
+    <t xml:space="preserve">9.28312492370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41511249542236</t>
   </si>
   <si>
     <t xml:space="preserve">9.63509082794189</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59109497070312</t>
+    <t xml:space="preserve">9.59109401702881</t>
   </si>
   <si>
     <t xml:space="preserve">9.89906597137451</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1190462112427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1630401611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2070360183716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3390235900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2950296401978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3830184936523</t>
+    <t xml:space="preserve">10.119044303894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1630411148071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2070369720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3390226364136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2950286865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3830194473267</t>
   </si>
   <si>
     <t xml:space="preserve">10.2510318756104</t>
@@ -1079,28 +1082,28 @@
     <t xml:space="preserve">10.4270162582397</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0750494003296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5150079727173</t>
+    <t xml:space="preserve">10.0750484466553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.515007019043</t>
   </si>
   <si>
     <t xml:space="preserve">10.6498155593872</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4700708389282</t>
+    <t xml:space="preserve">10.4700727462769</t>
   </si>
   <si>
     <t xml:space="preserve">10.694751739502</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6048784255981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.380199432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2453918457031</t>
+    <t xml:space="preserve">10.6048803329468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3802003860474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2453908920288</t>
   </si>
   <si>
     <t xml:space="preserve">10.0656480789185</t>
@@ -1109,19 +1112,16 @@
     <t xml:space="preserve">10.4251356124878</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5150089263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3352651596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2903280258179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.200457572937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97577667236328</t>
+    <t xml:space="preserve">10.3352632522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2903289794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2004556655884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9757776260376</t>
   </si>
   <si>
     <t xml:space="preserve">10.1105842590332</t>
@@ -1130,22 +1130,22 @@
     <t xml:space="preserve">9.93084049224854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88590335845947</t>
+    <t xml:space="preserve">9.88590431213379</t>
   </si>
   <si>
     <t xml:space="preserve">10.1555213928223</t>
   </si>
   <si>
-    <t xml:space="preserve">10.020712852478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75109767913818</t>
+    <t xml:space="preserve">10.0207118988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75109672546387</t>
   </si>
   <si>
     <t xml:space="preserve">9.70616149902344</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34667301177979</t>
+    <t xml:space="preserve">9.3466739654541</t>
   </si>
   <si>
     <t xml:space="preserve">9.30173778533936</t>
@@ -1154,7 +1154,7 @@
     <t xml:space="preserve">9.39160919189453</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48148059844971</t>
+    <t xml:space="preserve">9.48148155212402</t>
   </si>
   <si>
     <t xml:space="preserve">9.61628913879395</t>
@@ -1163,19 +1163,19 @@
     <t xml:space="preserve">9.52641677856445</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43654537200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12199401855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03212261199951</t>
+    <t xml:space="preserve">9.43654441833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12199306488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0321216583252</t>
   </si>
   <si>
     <t xml:space="preserve">9.16692924499512</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07705879211426</t>
+    <t xml:space="preserve">9.07705783843994</t>
   </si>
   <si>
     <t xml:space="preserve">9.25680160522461</t>
@@ -1184,28 +1184,28 @@
     <t xml:space="preserve">8.98718643188477</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57135391235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66122531890869</t>
+    <t xml:space="preserve">9.5713529586792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66122627258301</t>
   </si>
   <si>
     <t xml:space="preserve">9.79603290557861</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9643678665161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4586629867554</t>
+    <t xml:space="preserve">10.9643669128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4586620330811</t>
   </si>
   <si>
     <t xml:space="preserve">11.5035991668701</t>
   </si>
   <si>
-    <t xml:space="preserve">11.233983039856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1441097259521</t>
+    <t xml:space="preserve">11.2339820861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1441106796265</t>
   </si>
   <si>
     <t xml:space="preserve">10.9194307327271</t>
@@ -1217,31 +1217,31 @@
     <t xml:space="preserve">11.0093030929565</t>
   </si>
   <si>
-    <t xml:space="preserve">11.278920173645</t>
+    <t xml:space="preserve">11.2789192199707</t>
   </si>
   <si>
     <t xml:space="preserve">11.4137258529663</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5485334396362</t>
+    <t xml:space="preserve">11.5485343933105</t>
   </si>
   <si>
     <t xml:space="preserve">11.6833419799805</t>
   </si>
   <si>
-    <t xml:space="preserve">11.77321434021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9080219268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.132700920105</t>
+    <t xml:space="preserve">11.7732152938843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9080209732056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1327018737793</t>
   </si>
   <si>
     <t xml:space="preserve">11.9978942871094</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8181505203247</t>
+    <t xml:space="preserve">11.8181495666504</t>
   </si>
   <si>
     <t xml:space="preserve">11.593469619751</t>
@@ -1250,10 +1250,10 @@
     <t xml:space="preserve">12.312445640564</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5820608139038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9415483474731</t>
+    <t xml:space="preserve">12.5820617675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9415473937988</t>
   </si>
   <si>
     <t xml:space="preserve">12.8067407608032</t>
@@ -1265,13 +1265,13 @@
     <t xml:space="preserve">13.0763559341431</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4472541809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5371236801147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2675075531006</t>
+    <t xml:space="preserve">12.4472532272339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5371246337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2675085067749</t>
   </si>
   <si>
     <t xml:space="preserve">12.4023170471191</t>
@@ -1280,10 +1280,10 @@
     <t xml:space="preserve">12.6269969940186</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6719331741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8966131210327</t>
+    <t xml:space="preserve">12.671932220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.896614074707</t>
   </si>
   <si>
     <t xml:space="preserve">11.7282781600952</t>
@@ -1298,31 +1298,31 @@
     <t xml:space="preserve">8.89731407165527</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98062086105347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81885099411011</t>
+    <t xml:space="preserve">7.98062181472778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81885242462158</t>
   </si>
   <si>
     <t xml:space="preserve">7.53126192092896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89074897766113</t>
+    <t xml:space="preserve">7.89074850082397</t>
   </si>
   <si>
     <t xml:space="preserve">8.53782653808594</t>
   </si>
   <si>
-    <t xml:space="preserve">7.962646484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44795513153076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60972499847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66364669799805</t>
+    <t xml:space="preserve">7.96264600753784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44795417785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60972595214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66364765167236</t>
   </si>
   <si>
     <t xml:space="preserve">8.86136531829834</t>
@@ -1334,25 +1334,25 @@
     <t xml:space="preserve">9.93848991394043</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80045604705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89247894287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66242027282715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70843124389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84646606445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1225357055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75444316864014</t>
+    <t xml:space="preserve">9.80045413970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89247798919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66241931915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7084321975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84646701812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1225347518921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75444412231445</t>
   </si>
   <si>
     <t xml:space="preserve">10.3986053466797</t>
@@ -1364,10 +1364,10 @@
     <t xml:space="preserve">10.720685005188</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5826501846313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8587198257446</t>
+    <t xml:space="preserve">10.5826511383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8587207794189</t>
   </si>
   <si>
     <t xml:space="preserve">10.6746740341187</t>
@@ -1379,10 +1379,10 @@
     <t xml:space="preserve">10.628662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">10.766697883606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4906282424927</t>
+    <t xml:space="preserve">10.7666959762573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.490626335144</t>
   </si>
   <si>
     <t xml:space="preserve">11.1347894668579</t>
@@ -1394,55 +1394,55 @@
     <t xml:space="preserve">11.5028820037842</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1807994842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0427656173706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2728233337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9507417678833</t>
+    <t xml:space="preserve">11.1808004379272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0427675247192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2728242874146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9507427215576</t>
   </si>
   <si>
     <t xml:space="preserve">11.0887775421143</t>
   </si>
   <si>
-    <t xml:space="preserve">10.812707901001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9047317504883</t>
+    <t xml:space="preserve">10.8127088546753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9047327041626</t>
   </si>
   <si>
     <t xml:space="preserve">11.4108581542969</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4568700790405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2268123626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3648481369019</t>
+    <t xml:space="preserve">11.4568691253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2268114089966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3648471832275</t>
   </si>
   <si>
     <t xml:space="preserve">11.5488929748535</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5949039459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6869277954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9629974365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7789516448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0090093612671</t>
+    <t xml:space="preserve">11.5949048995972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6869268417358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9629964828491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7789506912231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0090074539185</t>
   </si>
   <si>
     <t xml:space="preserve">12.1010313034058</t>
@@ -1451,10 +1451,10 @@
     <t xml:space="preserve">11.7329397201538</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8249616622925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0550193786621</t>
+    <t xml:space="preserve">11.8249626159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0550203323364</t>
   </si>
   <si>
     <t xml:space="preserve">11.8709735870361</t>
@@ -1463,7 +1463,7 @@
     <t xml:space="preserve">11.9169845581055</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6409158706665</t>
+    <t xml:space="preserve">11.6409168243408</t>
   </si>
   <si>
     <t xml:space="preserve">12.1470422744751</t>
@@ -1472,13 +1472,13 @@
     <t xml:space="preserve">12.6991806030273</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7912034988403</t>
+    <t xml:space="preserve">12.7912044525146</t>
   </si>
   <si>
     <t xml:space="preserve">13.0672731399536</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8832273483276</t>
+    <t xml:space="preserve">12.883228302002</t>
   </si>
   <si>
     <t xml:space="preserve">12.9292392730713</t>
@@ -1487,22 +1487,22 @@
     <t xml:space="preserve">13.2053089141846</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2513198852539</t>
+    <t xml:space="preserve">13.2513189315796</t>
   </si>
   <si>
     <t xml:space="preserve">13.1132850646973</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1592960357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3893537521362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2973308563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9752521514893</t>
+    <t xml:space="preserve">13.1592969894409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3893547058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2973299026489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9752502441406</t>
   </si>
   <si>
     <t xml:space="preserve">13.7114343643188</t>
@@ -1514,25 +1514,25 @@
     <t xml:space="preserve">12.5151348114014</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3770999908447</t>
+    <t xml:space="preserve">12.377100944519</t>
   </si>
   <si>
     <t xml:space="preserve">12.837215423584</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7451934814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.653169631958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3433427810669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6194114685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8494691848755</t>
+    <t xml:space="preserve">12.745192527771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6531686782837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3433418273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6194124221802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8494701385498</t>
   </si>
   <si>
     <t xml:space="preserve">13.9414920806885</t>
@@ -1541,31 +1541,31 @@
     <t xml:space="preserve">14.1715497970581</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3555965423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1255378723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.493631362915</t>
+    <t xml:space="preserve">14.3555955886841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1255388259888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4936294555664</t>
   </si>
   <si>
     <t xml:space="preserve">14.7236881256104</t>
   </si>
   <si>
-    <t xml:space="preserve">14.677677154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8157119750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.861722946167</t>
+    <t xml:space="preserve">14.6776762008667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8157110214233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8617219924927</t>
   </si>
   <si>
     <t xml:space="preserve">15.045768737793</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5396423339844</t>
+    <t xml:space="preserve">14.5396413803101</t>
   </si>
   <si>
     <t xml:space="preserve">14.6316652297974</t>
@@ -1574,7 +1574,7 @@
     <t xml:space="preserve">14.4476194381714</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2635726928711</t>
+    <t xml:space="preserve">14.2635736465454</t>
   </si>
   <si>
     <t xml:space="preserve">13.9875040054321</t>
@@ -1586,13 +1586,13 @@
     <t xml:space="preserve">13.6654233932495</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8034563064575</t>
+    <t xml:space="preserve">13.8034572601318</t>
   </si>
   <si>
     <t xml:space="preserve">13.5734004974365</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7574462890625</t>
+    <t xml:space="preserve">13.7574453353882</t>
   </si>
   <si>
     <t xml:space="preserve">14.95374584198</t>
@@ -1601,16 +1601,16 @@
     <t xml:space="preserve">14.0335140228271</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4269781112671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3801374435425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.473819732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7080230712891</t>
+    <t xml:space="preserve">14.4269771575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3801383972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4738187789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7080240249634</t>
   </si>
   <si>
     <t xml:space="preserve">14.8485460281372</t>
@@ -1619,40 +1619,40 @@
     <t xml:space="preserve">15.0359086990356</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0827503204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8953857421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9422283172607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1764316558838</t>
+    <t xml:space="preserve">15.0827493667603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8953866958618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9422264099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1764326095581</t>
   </si>
   <si>
     <t xml:space="preserve">15.1295900344849</t>
   </si>
   <si>
-    <t xml:space="preserve">14.989068031311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6611804962158</t>
+    <t xml:space="preserve">14.9890689849854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6611824035645</t>
   </si>
   <si>
     <t xml:space="preserve">15.3169546127319</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7548637390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8017053604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2232713699341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5043172836304</t>
+    <t xml:space="preserve">14.7548627853394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8017044067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2232723236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5043163299561</t>
   </si>
   <si>
     <t xml:space="preserve">16.0664081573486</t>
@@ -1661,22 +1661,22 @@
     <t xml:space="preserve">15.6916809082031</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7385206222534</t>
+    <t xml:space="preserve">15.7385215759277</t>
   </si>
   <si>
     <t xml:space="preserve">15.9727249145508</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9258842468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7853631973267</t>
+    <t xml:space="preserve">15.9258861541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.785364151001</t>
   </si>
   <si>
     <t xml:space="preserve">16.1132488250732</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8322038650513</t>
+    <t xml:space="preserve">15.8322019577026</t>
   </si>
   <si>
     <t xml:space="preserve">16.5348148345947</t>
@@ -1691,16 +1691,16 @@
     <t xml:space="preserve">16.581657409668</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2069282531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.284273147583</t>
+    <t xml:space="preserve">16.2069301605225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2842712402344</t>
   </si>
   <si>
     <t xml:space="preserve">17.7995185852051</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4716300964355</t>
+    <t xml:space="preserve">17.4716339111328</t>
   </si>
   <si>
     <t xml:space="preserve">16.8158626556396</t>
@@ -1709,22 +1709,22 @@
     <t xml:space="preserve">16.6284980773926</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0969066619873</t>
+    <t xml:space="preserve">17.0969047546387</t>
   </si>
   <si>
     <t xml:space="preserve">17.5184745788574</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6121559143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0337238311768</t>
+    <t xml:space="preserve">17.612154006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0337219238281</t>
   </si>
   <si>
     <t xml:space="preserve">18.5489711761475</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7363376617432</t>
+    <t xml:space="preserve">18.7363357543945</t>
   </si>
   <si>
     <t xml:space="preserve">18.923698425293</t>
@@ -1742,58 +1742,58 @@
     <t xml:space="preserve">19.1110610961914</t>
   </si>
   <si>
-    <t xml:space="preserve">19.673152923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2984256744385</t>
+    <t xml:space="preserve">19.6731510162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2984237670898</t>
   </si>
   <si>
     <t xml:space="preserve">19.4857883453369</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8605155944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3289241790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9846954345703</t>
+    <t xml:space="preserve">19.8605175018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3289222717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9846935272217</t>
   </si>
   <si>
     <t xml:space="preserve">21.2657413482666</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0783748626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.453104019165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7973327636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8278293609619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1088752746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7341499328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0151920318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.296236038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4836025238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6404685974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5467853546143</t>
+    <t xml:space="preserve">21.0783786773682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4531059265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7973346710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8278312683105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1088790893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7341480255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.015193939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2962379455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4836044311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6404666900635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5467834472656</t>
   </si>
   <si>
     <t xml:space="preserve">20.2352428436279</t>
@@ -1808,7 +1808,7 @@
     <t xml:space="preserve">20.6099681854248</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9215145111084</t>
+    <t xml:space="preserve">21.9215106964111</t>
   </si>
   <si>
     <t xml:space="preserve">22.7646465301514</t>
@@ -1820,7 +1820,7 @@
     <t xml:space="preserve">21.1720600128174</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7036514282227</t>
+    <t xml:space="preserve">20.703649520874</t>
   </si>
   <si>
     <t xml:space="preserve">21.3594207763672</t>
@@ -1829,43 +1829,43 @@
     <t xml:space="preserve">20.5162868499756</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0478763580322</t>
+    <t xml:space="preserve">20.0478801727295</t>
   </si>
   <si>
     <t xml:space="preserve">22.6709671020508</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2025585174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3899211883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9541969299316</t>
+    <t xml:space="preserve">22.2025566101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3899192810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.954195022583</t>
   </si>
   <si>
     <t xml:space="preserve">20.4226055145264</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8910160064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3921070098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8300170898438</t>
+    <t xml:space="preserve">20.8910121917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3921089172363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8300189971924</t>
   </si>
   <si>
     <t xml:space="preserve">18.361608505249</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9563827514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6589946746826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7526798248291</t>
+    <t xml:space="preserve">16.9563846588135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6589965820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7526760101318</t>
   </si>
   <si>
     <t xml:space="preserve">17.377950668335</t>
@@ -1877,7 +1877,7 @@
     <t xml:space="preserve">17.9400405883789</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2679271697998</t>
+    <t xml:space="preserve">18.2679252624512</t>
   </si>
   <si>
     <t xml:space="preserve">18.8768577575684</t>
@@ -1886,10 +1886,10 @@
     <t xml:space="preserve">18.6426544189453</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3241367340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2117156982422</t>
+    <t xml:space="preserve">18.3241348266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2117195129395</t>
   </si>
   <si>
     <t xml:space="preserve">18.2304534912109</t>
@@ -1898,7 +1898,7 @@
     <t xml:space="preserve">18.4552898406982</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9494094848633</t>
+    <t xml:space="preserve">17.9494113922119</t>
   </si>
   <si>
     <t xml:space="preserve">18.1180362701416</t>
@@ -1907,7 +1907,7 @@
     <t xml:space="preserve">18.9705390930176</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2820835113525</t>
+    <t xml:space="preserve">20.2820816040039</t>
   </si>
   <si>
     <t xml:space="preserve">20.0947208404541</t>
@@ -1916,7 +1916,7 @@
     <t xml:space="preserve">20.1884002685547</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1415596008301</t>
+    <t xml:space="preserve">20.1415615081787</t>
   </si>
   <si>
     <t xml:space="preserve">18.4927616119385</t>
@@ -1925,19 +1925,19 @@
     <t xml:space="preserve">17.5559463500977</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1999549865723</t>
+    <t xml:space="preserve">17.1999568939209</t>
   </si>
   <si>
     <t xml:space="preserve">16.8847980499268</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7634201049805</t>
+    <t xml:space="preserve">17.7634181976318</t>
   </si>
   <si>
     <t xml:space="preserve">18.0308246612549</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9285469055176</t>
+    <t xml:space="preserve">18.9285449981689</t>
   </si>
   <si>
     <t xml:space="preserve">18.4319343566895</t>
@@ -1964,7 +1964,7 @@
     <t xml:space="preserve">20.0077228546143</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0554752349854</t>
+    <t xml:space="preserve">20.0554714202881</t>
   </si>
   <si>
     <t xml:space="preserve">20.5329856872559</t>
@@ -1973,16 +1973,16 @@
     <t xml:space="preserve">20.9149932861328</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1509742736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4374809265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0104961395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4880065917969</t>
+    <t xml:space="preserve">20.1509761810303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4374828338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0104942321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4880084991455</t>
   </si>
   <si>
     <t xml:space="preserve">19.5779628753662</t>
@@ -1997,7 +1997,7 @@
     <t xml:space="preserve">19.2914562225342</t>
   </si>
   <si>
-    <t xml:space="preserve">19.339204788208</t>
+    <t xml:space="preserve">19.3392066955566</t>
   </si>
   <si>
     <t xml:space="preserve">18.813943862915</t>
@@ -2024,7 +2024,7 @@
     <t xml:space="preserve">19.9599704742432</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4852352142334</t>
+    <t xml:space="preserve">20.4852333068848</t>
   </si>
   <si>
     <t xml:space="preserve">21.1059970855713</t>
@@ -2033,37 +2033,37 @@
     <t xml:space="preserve">21.8700160980225</t>
   </si>
   <si>
-    <t xml:space="preserve">21.392505645752</t>
+    <t xml:space="preserve">21.3925037384033</t>
   </si>
   <si>
     <t xml:space="preserve">21.1537494659424</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7745132446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.679012298584</t>
+    <t xml:space="preserve">21.7745113372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6790103912354</t>
   </si>
   <si>
     <t xml:space="preserve">21.9177684783936</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2970027923584</t>
+    <t xml:space="preserve">21.2970008850098</t>
   </si>
   <si>
     <t xml:space="preserve">21.7267627716064</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5835094451904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5807323455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1032218933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.62571144104</t>
+    <t xml:space="preserve">21.5835113525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5807342529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1032238006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6257133483887</t>
   </si>
   <si>
     <t xml:space="preserve">19.8644676208496</t>
@@ -2084,19 +2084,19 @@
     <t xml:space="preserve">22.0610198974609</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3475284576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0582447052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3897323608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2942276000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1987266540527</t>
+    <t xml:space="preserve">22.347526550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0582466125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3897304534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2942295074463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1987247467041</t>
   </si>
   <si>
     <t xml:space="preserve">20.8194904327393</t>
@@ -2105,7 +2105,7 @@
     <t xml:space="preserve">20.8672428131104</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0499267578125</t>
+    <t xml:space="preserve">18.0499248504639</t>
   </si>
   <si>
     <t xml:space="preserve">18.833044052124</t>
@@ -2120,7 +2120,7 @@
     <t xml:space="preserve">19.8167171478271</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2464771270752</t>
+    <t xml:space="preserve">20.2464790344238</t>
   </si>
   <si>
     <t xml:space="preserve">20.6762371063232</t>
@@ -2129,7 +2129,7 @@
     <t xml:space="preserve">19.7689666748047</t>
   </si>
   <si>
-    <t xml:space="preserve">21.440258026123</t>
+    <t xml:space="preserve">21.4402561187744</t>
   </si>
   <si>
     <t xml:space="preserve">22.6340351104736</t>
@@ -2141,28 +2141,28 @@
     <t xml:space="preserve">22.7295341491699</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5862808227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8727893829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5385303497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6817855834961</t>
+    <t xml:space="preserve">22.5862827301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8727912902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5385341644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6817836761475</t>
   </si>
   <si>
     <t xml:space="preserve">23.0160427093506</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3025512695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4485759735107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7323112487793</t>
+    <t xml:space="preserve">23.3025493621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4485778808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7323093414307</t>
   </si>
   <si>
     <t xml:space="preserve">23.9710655212402</t>
@@ -2171,16 +2171,16 @@
     <t xml:space="preserve">24.2098217010498</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0665664672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1143188476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4008255004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3080978393555</t>
+    <t xml:space="preserve">24.0665683746338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1143207550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4008235931396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3080959320068</t>
   </si>
   <si>
     <t xml:space="preserve">23.7800598144531</t>
@@ -2192,22 +2192,22 @@
     <t xml:space="preserve">25.0693416595459</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5440788269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9260883331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3558483123779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4035987854004</t>
+    <t xml:space="preserve">24.5440807342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9260864257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3558464050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.403600692749</t>
   </si>
   <si>
     <t xml:space="preserve">25.8333587646484</t>
   </si>
   <si>
-    <t xml:space="preserve">26.883882522583</t>
+    <t xml:space="preserve">26.8838844299316</t>
   </si>
   <si>
     <t xml:space="preserve">26.7883815765381</t>
@@ -2219,40 +2219,40 @@
     <t xml:space="preserve">24.5918292999268</t>
   </si>
   <si>
-    <t xml:space="preserve">24.830587387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.260347366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7378597259521</t>
+    <t xml:space="preserve">24.8305854797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2603454589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7378578186035</t>
   </si>
   <si>
     <t xml:space="preserve">25.785608291626</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0721130371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2631206512451</t>
+    <t xml:space="preserve">26.072114944458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2631187438965</t>
   </si>
   <si>
     <t xml:space="preserve">25.4513492584229</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9288597106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5946044921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6901054382324</t>
+    <t xml:space="preserve">25.928861618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5946025848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6901073455811</t>
   </si>
   <si>
     <t xml:space="preserve">25.5468521118164</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4541244506836</t>
+    <t xml:space="preserve">26.4541263580322</t>
   </si>
   <si>
     <t xml:space="preserve">26.7406311035156</t>
@@ -2264,13 +2264,13 @@
     <t xml:space="preserve">27.1703910827637</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6506748199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3219661712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8922023773193</t>
+    <t xml:space="preserve">28.6506767272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.321964263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.892204284668</t>
   </si>
   <si>
     <t xml:space="preserve">29.9877071380615</t>
@@ -2279,7 +2279,7 @@
     <t xml:space="preserve">30.1309604644775</t>
   </si>
   <si>
-    <t xml:space="preserve">29.653450012207</t>
+    <t xml:space="preserve">29.6534481048584</t>
   </si>
   <si>
     <t xml:space="preserve">29.510196685791</t>
@@ -2288,7 +2288,7 @@
     <t xml:space="preserve">28.5074214935303</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3191909790039</t>
+    <t xml:space="preserve">29.3191928863525</t>
   </si>
   <si>
     <t xml:space="preserve">28.9371814727783</t>
@@ -2297,25 +2297,25 @@
     <t xml:space="preserve">28.8416805267334</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2236919403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1281871795654</t>
+    <t xml:space="preserve">29.223690032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1281852722168</t>
   </si>
   <si>
     <t xml:space="preserve">29.1759376525879</t>
   </si>
   <si>
-    <t xml:space="preserve">29.080436706543</t>
+    <t xml:space="preserve">29.0804386138916</t>
   </si>
   <si>
     <t xml:space="preserve">28.6984272003174</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9849338531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3641681671143</t>
+    <t xml:space="preserve">28.984935760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3641700744629</t>
   </si>
   <si>
     <t xml:space="preserve">27.8866577148438</t>
@@ -2330,7 +2330,7 @@
     <t xml:space="preserve">27.6479034423828</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6029262542725</t>
+    <t xml:space="preserve">28.6029243469238</t>
   </si>
   <si>
     <t xml:space="preserve">28.4119205474854</t>
@@ -2342,25 +2342,25 @@
     <t xml:space="preserve">29.4146938323975</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0354595184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7489490509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7039737701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2742137908936</t>
+    <t xml:space="preserve">30.0354614257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.748950958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7039756774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2742156982422</t>
   </si>
   <si>
     <t xml:space="preserve">29.7012023925781</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5579490661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.796703338623</t>
+    <t xml:space="preserve">29.5579471588135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7967014312744</t>
   </si>
   <si>
     <t xml:space="preserve">28.2209148406982</t>
@@ -3426,6 +3426,9 @@
   </si>
   <si>
     <t xml:space="preserve">39.5999984741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.7999992370605</t>
   </si>
 </sst>
 </file>
@@ -13948,7 +13951,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G392" t="s">
-        <v>164</v>
+        <v>203</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -13974,7 +13977,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G393" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -14000,7 +14003,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G394" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -14026,7 +14029,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G395" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -14052,7 +14055,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G396" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -14078,7 +14081,7 @@
         <v>13</v>
       </c>
       <c r="G397" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -14104,7 +14107,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G398" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -14130,7 +14133,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G399" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -14156,7 +14159,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G400" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -14182,7 +14185,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G401" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -14208,7 +14211,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G402" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -14234,7 +14237,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G403" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -14260,7 +14263,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G404" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -14286,7 +14289,7 @@
         <v>13</v>
       </c>
       <c r="G405" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -14312,7 +14315,7 @@
         <v>13</v>
       </c>
       <c r="G406" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -14338,7 +14341,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G407" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -14364,7 +14367,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G408" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -14390,7 +14393,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G409" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -14416,7 +14419,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G410" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -14442,7 +14445,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G411" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -14468,7 +14471,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G412" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -14494,7 +14497,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G413" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -14520,7 +14523,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G414" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -14546,7 +14549,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G415" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -14572,7 +14575,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G416" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -14598,7 +14601,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G417" t="s">
-        <v>164</v>
+        <v>203</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -14624,7 +14627,7 @@
         <v>13.25</v>
       </c>
       <c r="G418" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -14650,7 +14653,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G419" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -14676,7 +14679,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G420" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -14702,7 +14705,7 @@
         <v>13</v>
       </c>
       <c r="G421" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -14728,7 +14731,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G422" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -14754,7 +14757,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G423" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -14780,7 +14783,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G424" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -14806,7 +14809,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G425" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -14832,7 +14835,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G426" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -14858,7 +14861,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G427" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -14884,7 +14887,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G428" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -14910,7 +14913,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G429" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -14936,7 +14939,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G430" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -14962,7 +14965,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G431" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -14988,7 +14991,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G432" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -15014,7 +15017,7 @@
         <v>13.1700000762939</v>
       </c>
       <c r="G433" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -15040,7 +15043,7 @@
         <v>13</v>
       </c>
       <c r="G434" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -15066,7 +15069,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G435" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -15092,7 +15095,7 @@
         <v>12.7299995422363</v>
       </c>
       <c r="G436" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -15118,7 +15121,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G437" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -15144,7 +15147,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G438" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -15170,7 +15173,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G439" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -15196,7 +15199,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G440" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -15222,7 +15225,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G441" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -15248,7 +15251,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G442" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -15274,7 +15277,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G443" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -15300,7 +15303,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G444" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -15326,7 +15329,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G445" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -15352,7 +15355,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G446" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -15378,7 +15381,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G447" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -15404,7 +15407,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G448" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -15430,7 +15433,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G449" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -15456,7 +15459,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G450" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -15482,7 +15485,7 @@
         <v>11.25</v>
       </c>
       <c r="G451" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -15508,7 +15511,7 @@
         <v>11.1099996566772</v>
       </c>
       <c r="G452" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -15534,7 +15537,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G453" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -15560,7 +15563,7 @@
         <v>11.25</v>
       </c>
       <c r="G454" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -15586,7 +15589,7 @@
         <v>10.9099998474121</v>
       </c>
       <c r="G455" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -15612,7 +15615,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G456" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -15638,7 +15641,7 @@
         <v>10.75</v>
       </c>
       <c r="G457" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -15664,7 +15667,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G458" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -15690,7 +15693,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G459" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -15716,7 +15719,7 @@
         <v>10.9300003051758</v>
       </c>
       <c r="G460" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -15742,7 +15745,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G461" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -15768,7 +15771,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G462" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -15794,7 +15797,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G463" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -15820,7 +15823,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G464" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -15846,7 +15849,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G465" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -15872,7 +15875,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G466" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -15898,7 +15901,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G467" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -15924,7 +15927,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G468" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -15950,7 +15953,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G469" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -15976,7 +15979,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G470" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -16002,7 +16005,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G471" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -16028,7 +16031,7 @@
         <v>11.2299995422363</v>
       </c>
       <c r="G472" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -16054,7 +16057,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G473" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -16080,7 +16083,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G474" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -16106,7 +16109,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G475" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -16132,7 +16135,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G476" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -16158,7 +16161,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G477" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -16184,7 +16187,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G478" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -16210,7 +16213,7 @@
         <v>10.75</v>
       </c>
       <c r="G479" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -16236,7 +16239,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G480" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -16262,7 +16265,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G481" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -16288,7 +16291,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G482" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -16314,7 +16317,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G483" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -16340,7 +16343,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G484" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -16366,7 +16369,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G485" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -16392,7 +16395,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G486" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -16418,7 +16421,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G487" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -16444,7 +16447,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G488" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -16470,7 +16473,7 @@
         <v>11.5</v>
       </c>
       <c r="G489" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -16496,7 +16499,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G490" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -16522,7 +16525,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G491" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -16548,7 +16551,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G492" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -16574,7 +16577,7 @@
         <v>11.0699996948242</v>
       </c>
       <c r="G493" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -16600,7 +16603,7 @@
         <v>11.2299995422363</v>
       </c>
       <c r="G494" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -16626,7 +16629,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G495" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -16652,7 +16655,7 @@
         <v>10.9300003051758</v>
       </c>
       <c r="G496" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -16678,7 +16681,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G497" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -16704,7 +16707,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G498" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -16730,7 +16733,7 @@
         <v>11.25</v>
       </c>
       <c r="G499" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -16756,7 +16759,7 @@
         <v>11.1300001144409</v>
       </c>
       <c r="G500" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -16782,7 +16785,7 @@
         <v>11</v>
       </c>
       <c r="G501" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -16808,7 +16811,7 @@
         <v>11.0699996948242</v>
       </c>
       <c r="G502" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -16834,7 +16837,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G503" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -16860,7 +16863,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G504" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -16886,7 +16889,7 @@
         <v>11</v>
       </c>
       <c r="G505" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -16912,7 +16915,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G506" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -16938,7 +16941,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G507" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -16964,7 +16967,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G508" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -16990,7 +16993,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G509" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -17016,7 +17019,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G510" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -17042,7 +17045,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G511" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -17068,7 +17071,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G512" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -17094,7 +17097,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G513" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -17120,7 +17123,7 @@
         <v>10.75</v>
       </c>
       <c r="G514" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -17146,7 +17149,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G515" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -17172,7 +17175,7 @@
         <v>10.75</v>
       </c>
       <c r="G516" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -17198,7 +17201,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G517" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -17224,7 +17227,7 @@
         <v>11</v>
       </c>
       <c r="G518" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -17250,7 +17253,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G519" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -17276,7 +17279,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G520" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -17302,7 +17305,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G521" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -17328,7 +17331,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G522" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -17354,7 +17357,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G523" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -17380,7 +17383,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G524" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -17406,7 +17409,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G525" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -17432,7 +17435,7 @@
         <v>11.25</v>
       </c>
       <c r="G526" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -17458,7 +17461,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G527" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -17484,7 +17487,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G528" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -17510,7 +17513,7 @@
         <v>11.25</v>
       </c>
       <c r="G529" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -17536,7 +17539,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G530" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -17562,7 +17565,7 @@
         <v>11.5</v>
       </c>
       <c r="G531" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -17588,7 +17591,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G532" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -17614,7 +17617,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G533" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -17640,7 +17643,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G534" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -17666,7 +17669,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G535" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -17692,7 +17695,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G536" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -17718,7 +17721,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G537" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -17744,7 +17747,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G538" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -17770,7 +17773,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G539" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -17796,7 +17799,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G540" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -17822,7 +17825,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G541" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -17848,7 +17851,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G542" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -17874,7 +17877,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G543" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -17900,7 +17903,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G544" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -17926,7 +17929,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G545" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -17952,7 +17955,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G546" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -17978,7 +17981,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G547" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -18004,7 +18007,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G548" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -18030,7 +18033,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G549" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -18056,7 +18059,7 @@
         <v>10.5</v>
       </c>
       <c r="G550" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -18082,7 +18085,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G551" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -18108,7 +18111,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G552" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -18134,7 +18137,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G553" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -18160,7 +18163,7 @@
         <v>10.25</v>
       </c>
       <c r="G554" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -18186,7 +18189,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G555" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -18212,7 +18215,7 @@
         <v>10.25</v>
       </c>
       <c r="G556" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -18238,7 +18241,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G557" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -18264,7 +18267,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G558" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -18290,7 +18293,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G559" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -18316,7 +18319,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G560" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -18342,7 +18345,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G561" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -18368,7 +18371,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G562" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -18394,7 +18397,7 @@
         <v>10.5</v>
       </c>
       <c r="G563" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -18420,7 +18423,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G564" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -18446,7 +18449,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G565" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -18472,7 +18475,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G566" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -18498,7 +18501,7 @@
         <v>10.25</v>
       </c>
       <c r="G567" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -18524,7 +18527,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G568" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -18550,7 +18553,7 @@
         <v>10.25</v>
       </c>
       <c r="G569" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -18576,7 +18579,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G570" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -18602,7 +18605,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G571" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -18628,7 +18631,7 @@
         <v>10</v>
       </c>
       <c r="G572" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -18654,7 +18657,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G573" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -18680,7 +18683,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G574" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -18706,7 +18709,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G575" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -18732,7 +18735,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G576" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -18758,7 +18761,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G577" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -18784,7 +18787,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G578" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -18810,7 +18813,7 @@
         <v>10</v>
       </c>
       <c r="G579" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -18836,7 +18839,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G580" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -18862,7 +18865,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G581" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -18888,7 +18891,7 @@
         <v>10.25</v>
       </c>
       <c r="G582" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -18914,7 +18917,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G583" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -18940,7 +18943,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G584" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -18966,7 +18969,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G585" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -18992,7 +18995,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G586" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -19018,7 +19021,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G587" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -19044,7 +19047,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G588" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -19070,7 +19073,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G589" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -19096,7 +19099,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G590" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -19122,7 +19125,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G591" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -19148,7 +19151,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G592" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -19174,7 +19177,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G593" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -19200,7 +19203,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G594" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -19226,7 +19229,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G595" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -19252,7 +19255,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G596" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -19278,7 +19281,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G597" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -19304,7 +19307,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G598" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -19330,7 +19333,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G599" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -19356,7 +19359,7 @@
         <v>10.25</v>
       </c>
       <c r="G600" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -19382,7 +19385,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G601" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -19408,7 +19411,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G602" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -19434,7 +19437,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G603" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -19460,7 +19463,7 @@
         <v>10.25</v>
       </c>
       <c r="G604" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -19486,7 +19489,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G605" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -19512,7 +19515,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G606" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -19538,7 +19541,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G607" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -19564,7 +19567,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G608" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19590,7 +19593,7 @@
         <v>10.25</v>
       </c>
       <c r="G609" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19616,7 +19619,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G610" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19642,7 +19645,7 @@
         <v>10.25</v>
       </c>
       <c r="G611" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19668,7 +19671,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G612" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19694,7 +19697,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G613" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19720,7 +19723,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G614" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19746,7 +19749,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G615" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19772,7 +19775,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G616" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19798,7 +19801,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G617" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19824,7 +19827,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G618" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19850,7 +19853,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G619" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19876,7 +19879,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G620" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19902,7 +19905,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G621" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19928,7 +19931,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G622" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19954,7 +19957,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G623" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19980,7 +19983,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G624" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -20006,7 +20009,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G625" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -20032,7 +20035,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G626" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -20058,7 +20061,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G627" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -20084,7 +20087,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G628" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -20110,7 +20113,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G629" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -20136,7 +20139,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G630" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -20162,7 +20165,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G631" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -20188,7 +20191,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G632" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -20214,7 +20217,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G633" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -20240,7 +20243,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G634" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -20266,7 +20269,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G635" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -20292,7 +20295,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G636" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -20318,7 +20321,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G637" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -20344,7 +20347,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G638" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -20370,7 +20373,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G639" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -20396,7 +20399,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G640" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -20422,7 +20425,7 @@
         <v>10</v>
       </c>
       <c r="G641" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -20448,7 +20451,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G642" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -20474,7 +20477,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G643" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -20500,7 +20503,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G644" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -20526,7 +20529,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G645" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -20552,7 +20555,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G646" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -20578,7 +20581,7 @@
         <v>10</v>
       </c>
       <c r="G647" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -20604,7 +20607,7 @@
         <v>10</v>
       </c>
       <c r="G648" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -20630,7 +20633,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G649" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -20656,7 +20659,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G650" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -20682,7 +20685,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G651" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -20708,7 +20711,7 @@
         <v>10</v>
       </c>
       <c r="G652" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -20734,7 +20737,7 @@
         <v>10</v>
       </c>
       <c r="G653" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -20760,7 +20763,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G654" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -20786,7 +20789,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G655" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -20812,7 +20815,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G656" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -20838,7 +20841,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G657" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -20864,7 +20867,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G658" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -20890,7 +20893,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G659" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -20916,7 +20919,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G660" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -20942,7 +20945,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G661" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -20968,7 +20971,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G662" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -20994,7 +20997,7 @@
         <v>10</v>
       </c>
       <c r="G663" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -21020,7 +21023,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G664" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -21046,7 +21049,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G665" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -21072,7 +21075,7 @@
         <v>10.25</v>
       </c>
       <c r="G666" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -21098,7 +21101,7 @@
         <v>10</v>
       </c>
       <c r="G667" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -21124,7 +21127,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G668" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -21150,7 +21153,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G669" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -21176,7 +21179,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G670" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -21202,7 +21205,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G671" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -21228,7 +21231,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G672" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -21254,7 +21257,7 @@
         <v>10</v>
       </c>
       <c r="G673" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -21280,7 +21283,7 @@
         <v>10</v>
       </c>
       <c r="G674" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -21306,7 +21309,7 @@
         <v>10</v>
       </c>
       <c r="G675" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -21332,7 +21335,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G676" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -21358,7 +21361,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G677" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -21384,7 +21387,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G678" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -21410,7 +21413,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G679" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -21436,7 +21439,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G680" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -21462,7 +21465,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G681" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -21488,7 +21491,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G682" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -21514,7 +21517,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G683" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -21540,7 +21543,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G684" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -21566,7 +21569,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G685" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -21592,7 +21595,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G686" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -21618,7 +21621,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G687" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -21644,7 +21647,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G688" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -21670,7 +21673,7 @@
         <v>10</v>
       </c>
       <c r="G689" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -21696,7 +21699,7 @@
         <v>10</v>
       </c>
       <c r="G690" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -21722,7 +21725,7 @@
         <v>10</v>
       </c>
       <c r="G691" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -21748,7 +21751,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G692" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -21774,7 +21777,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G693" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -21800,7 +21803,7 @@
         <v>10</v>
       </c>
       <c r="G694" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -21826,7 +21829,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G695" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -21852,7 +21855,7 @@
         <v>10</v>
       </c>
       <c r="G696" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -21878,7 +21881,7 @@
         <v>10</v>
       </c>
       <c r="G697" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -21904,7 +21907,7 @@
         <v>10.5</v>
       </c>
       <c r="G698" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -21930,7 +21933,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G699" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -21956,7 +21959,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G700" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -21982,7 +21985,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G701" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -22008,7 +22011,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G702" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -22034,7 +22037,7 @@
         <v>10.25</v>
       </c>
       <c r="G703" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -22060,7 +22063,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G704" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -22086,7 +22089,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G705" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -22112,7 +22115,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G706" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -22138,7 +22141,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G707" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -22164,7 +22167,7 @@
         <v>10</v>
       </c>
       <c r="G708" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -22190,7 +22193,7 @@
         <v>10</v>
       </c>
       <c r="G709" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -22216,7 +22219,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G710" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -22242,7 +22245,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G711" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -22268,7 +22271,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G712" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -22294,7 +22297,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G713" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -22320,7 +22323,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G714" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -22346,7 +22349,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G715" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -22372,7 +22375,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G716" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -22398,7 +22401,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G717" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -22424,7 +22427,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G718" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -22450,7 +22453,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G719" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -22476,7 +22479,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G720" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -22502,7 +22505,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G721" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -22528,7 +22531,7 @@
         <v>10</v>
       </c>
       <c r="G722" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -22554,7 +22557,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G723" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -22580,7 +22583,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G724" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -22606,7 +22609,7 @@
         <v>10</v>
       </c>
       <c r="G725" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -22632,7 +22635,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G726" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -22658,7 +22661,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G727" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -22684,7 +22687,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G728" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -22710,7 +22713,7 @@
         <v>10</v>
       </c>
       <c r="G729" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -22736,7 +22739,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G730" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -22762,7 +22765,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G731" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -22788,7 +22791,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G732" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -22814,7 +22817,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G733" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -22840,7 +22843,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G734" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -22866,7 +22869,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G735" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -22892,7 +22895,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G736" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -22918,7 +22921,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G737" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -22944,7 +22947,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G738" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -22970,7 +22973,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G739" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -22996,7 +22999,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G740" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -23022,7 +23025,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G741" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -23048,7 +23051,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G742" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -23074,7 +23077,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G743" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -23100,7 +23103,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G744" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -23126,7 +23129,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G745" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -23152,7 +23155,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G746" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -23178,7 +23181,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G747" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -23204,7 +23207,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G748" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -23230,7 +23233,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G749" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -23256,7 +23259,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G750" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -23282,7 +23285,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G751" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -23308,7 +23311,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G752" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -23334,7 +23337,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G753" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -23360,7 +23363,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G754" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -23386,7 +23389,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G755" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -23412,7 +23415,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G756" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -23438,7 +23441,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G757" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -23464,7 +23467,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G758" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -23490,7 +23493,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G759" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -23516,7 +23519,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G760" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -23542,7 +23545,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G761" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -23568,7 +23571,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G762" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -23594,7 +23597,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G763" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -23620,7 +23623,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G764" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -23646,7 +23649,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G765" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -23672,7 +23675,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G766" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -23698,7 +23701,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G767" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -23724,7 +23727,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G768" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -23750,7 +23753,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G769" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -23776,7 +23779,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G770" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -23802,7 +23805,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G771" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -23828,7 +23831,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G772" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -23854,7 +23857,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G773" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -23880,7 +23883,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G774" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -23906,7 +23909,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G775" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -23932,7 +23935,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G776" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -23958,7 +23961,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G777" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -23984,7 +23987,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G778" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -24010,7 +24013,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G779" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -24036,7 +24039,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G780" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -24062,7 +24065,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G781" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -24088,7 +24091,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G782" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -24114,7 +24117,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G783" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -24140,7 +24143,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G784" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -24166,7 +24169,7 @@
         <v>10</v>
       </c>
       <c r="G785" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -24192,7 +24195,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G786" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -24218,7 +24221,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G787" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -24244,7 +24247,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G788" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -24270,7 +24273,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G789" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -24296,7 +24299,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G790" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -24322,7 +24325,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G791" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -24348,7 +24351,7 @@
         <v>10</v>
       </c>
       <c r="G792" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -24374,7 +24377,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G793" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -24400,7 +24403,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G794" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -24426,7 +24429,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G795" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -24452,7 +24455,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G796" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -24478,7 +24481,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G797" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -24504,7 +24507,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G798" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -24530,7 +24533,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G799" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -24556,7 +24559,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G800" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -24582,7 +24585,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G801" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -24608,7 +24611,7 @@
         <v>10.25</v>
       </c>
       <c r="G802" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -24634,7 +24637,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G803" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -24660,7 +24663,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G804" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -24686,7 +24689,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G805" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -24712,7 +24715,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G806" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -24738,7 +24741,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G807" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -24764,7 +24767,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G808" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -24790,7 +24793,7 @@
         <v>10.5</v>
       </c>
       <c r="G809" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -24816,7 +24819,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G810" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -24842,7 +24845,7 @@
         <v>10</v>
       </c>
       <c r="G811" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -24868,7 +24871,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G812" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -24894,7 +24897,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G813" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -24920,7 +24923,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G814" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -24946,7 +24949,7 @@
         <v>10.5</v>
       </c>
       <c r="G815" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -24972,7 +24975,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G816" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -24998,7 +25001,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G817" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -25024,7 +25027,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G818" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -25050,7 +25053,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G819" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -25076,7 +25079,7 @@
         <v>11.25</v>
       </c>
       <c r="G820" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -25102,7 +25105,7 @@
         <v>11.5</v>
       </c>
       <c r="G821" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -25128,7 +25131,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G822" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -25154,7 +25157,7 @@
         <v>11.5</v>
       </c>
       <c r="G823" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -25180,7 +25183,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G824" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -25206,7 +25209,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G825" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -25232,7 +25235,7 @@
         <v>11.75</v>
       </c>
       <c r="G826" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -25258,7 +25261,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G827" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -25284,7 +25287,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G828" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -25310,7 +25313,7 @@
         <v>11.75</v>
       </c>
       <c r="G829" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -25336,7 +25339,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G830" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -25362,7 +25365,7 @@
         <v>11.75</v>
       </c>
       <c r="G831" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -25388,7 +25391,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G832" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -25414,7 +25417,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G833" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -25440,7 +25443,7 @@
         <v>11.75</v>
       </c>
       <c r="G834" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -25466,7 +25469,7 @@
         <v>11.75</v>
       </c>
       <c r="G835" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -25492,7 +25495,7 @@
         <v>11.75</v>
       </c>
       <c r="G836" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -25518,7 +25521,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G837" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -25544,7 +25547,7 @@
         <v>11.75</v>
       </c>
       <c r="G838" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -25570,7 +25573,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G839" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -25596,7 +25599,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G840" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -25622,7 +25625,7 @@
         <v>11.25</v>
       </c>
       <c r="G841" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -25648,7 +25651,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G842" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -25674,7 +25677,7 @@
         <v>11.5</v>
       </c>
       <c r="G843" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -25700,7 +25703,7 @@
         <v>11.5</v>
       </c>
       <c r="G844" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -25726,7 +25729,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G845" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -25752,7 +25755,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G846" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -25778,7 +25781,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G847" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -25804,7 +25807,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G848" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -25830,7 +25833,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G849" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -25856,7 +25859,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G850" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -25882,7 +25885,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G851" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -25908,7 +25911,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G852" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -25934,7 +25937,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G853" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -25960,7 +25963,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G854" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -25986,7 +25989,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G855" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -26012,7 +26015,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G856" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -26038,7 +26041,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G857" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -26064,7 +26067,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G858" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -26090,7 +26093,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G859" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -26116,7 +26119,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G860" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -26142,7 +26145,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G861" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -26168,7 +26171,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G862" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -26194,7 +26197,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G863" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -26220,7 +26223,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G864" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -26246,7 +26249,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G865" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -26272,7 +26275,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G866" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -26298,7 +26301,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G867" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -26324,7 +26327,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G868" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -26350,7 +26353,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G869" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -26376,7 +26379,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G870" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -26610,7 +26613,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G879" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -26714,7 +26717,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G883" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -26766,7 +26769,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G885" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -26896,7 +26899,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G890" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -27000,7 +27003,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G894" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -27052,7 +27055,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G896" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -27078,7 +27081,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G897" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -27338,7 +27341,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G907" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -27416,7 +27419,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G910" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -27442,7 +27445,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G911" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -27468,7 +27471,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G912" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -27572,7 +27575,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G916" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -27624,7 +27627,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G918" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -29470,7 +29473,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G989" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -29548,7 +29551,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G992" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -31420,7 +31423,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1064" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -32278,7 +32281,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1097" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -32330,7 +32333,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G1099" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -69388,7 +69391,7 @@
     </row>
     <row r="2525">
       <c r="A2525" s="1" t="n">
-        <v>45994.6911111111</v>
+        <v>45994.3333333333</v>
       </c>
       <c r="B2525" t="n">
         <v>16982</v>
@@ -69409,6 +69412,32 @@
         <v>1137</v>
       </c>
       <c r="H2525" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2526">
+      <c r="A2526" s="1" t="n">
+        <v>45995.6911689815</v>
+      </c>
+      <c r="B2526" t="n">
+        <v>145102</v>
+      </c>
+      <c r="C2526" t="n">
+        <v>39.75</v>
+      </c>
+      <c r="D2526" t="n">
+        <v>38.7000007629395</v>
+      </c>
+      <c r="E2526" t="n">
+        <v>39.5999984741211</v>
+      </c>
+      <c r="F2526" t="n">
+        <v>38.7999992370605</v>
+      </c>
+      <c r="G2526" t="s">
+        <v>1138</v>
+      </c>
+      <c r="H2526" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LUVE.MI.xlsx
+++ b/data/LUVE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1139" uniqueCount="1139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1140" uniqueCount="1140">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,136 +38,136 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30043506622314</t>
+    <t xml:space="preserve">8.30043315887451</t>
   </si>
   <si>
     <t xml:space="preserve">LUVE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31703472137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28383159637451</t>
+    <t xml:space="preserve">8.31703567504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28383255004883</t>
   </si>
   <si>
     <t xml:space="preserve">8.09292316436768</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19667816162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07632064819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15102481842041</t>
+    <t xml:space="preserve">8.19667911529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07632160186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15102577209473</t>
   </si>
   <si>
     <t xml:space="preserve">8.17177677154541</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03896999359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08462238311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06802177429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96841716766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01821994781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99746704101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91861295700073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91446399688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91031312942505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88541221618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87711000442505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85221099853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64884948730469</t>
+    <t xml:space="preserve">8.03896903991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08462047576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06802272796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96841764450073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01821899414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99746894836426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91861391067505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91446352005005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91031265258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88541078567505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87711143493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.852210521698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.648850440979</t>
   </si>
   <si>
     <t xml:space="preserve">7.71940279006958</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70280265808105</t>
+    <t xml:space="preserve">7.70280122756958</t>
   </si>
   <si>
     <t xml:space="preserve">7.69035196304321</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61979818344116</t>
+    <t xml:space="preserve">7.619797706604</t>
   </si>
   <si>
     <t xml:space="preserve">7.55754518508911</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55339431762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63639736175537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76920509338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.802405834198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93521499633789</t>
+    <t xml:space="preserve">7.55339384078979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63639879226685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76920604705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80240678787231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93521356582642</t>
   </si>
   <si>
     <t xml:space="preserve">8.10122299194336</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05142211914062</t>
+    <t xml:space="preserve">8.05142116546631</t>
   </si>
   <si>
     <t xml:space="preserve">8.18422794342041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13442611694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00161838531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96011590957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21742916107178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35853672027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32533359527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29213237762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20082855224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15932464599609</t>
+    <t xml:space="preserve">8.13442516326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00161933898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9601149559021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21742725372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35853576660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32533550262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2921314239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20082950592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15932559967041</t>
   </si>
   <si>
     <t xml:space="preserve">8.30336475372314</t>
@@ -179,28 +179,28 @@
     <t xml:space="preserve">8.43045616149902</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15085315704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17627143859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2059268951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13390827178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11696147918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21863555908203</t>
+    <t xml:space="preserve">8.15085124969482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17627048492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20592594146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13390922546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11696243286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21863651275635</t>
   </si>
   <si>
     <t xml:space="preserve">8.21016216278076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21439838409424</t>
+    <t xml:space="preserve">8.21439743041992</t>
   </si>
   <si>
     <t xml:space="preserve">8.20169067382812</t>
@@ -209,34 +209,34 @@
     <t xml:space="preserve">8.26100063323975</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09154319763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10848808288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04917907714844</t>
+    <t xml:space="preserve">8.09154415130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10848903656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04917812347412</t>
   </si>
   <si>
     <t xml:space="preserve">7.96445035934448</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92208623886108</t>
+    <t xml:space="preserve">7.92208814620972</t>
   </si>
   <si>
     <t xml:space="preserve">7.87972259521484</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83735799789429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1254358291626</t>
+    <t xml:space="preserve">7.83735847473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12543392181396</t>
   </si>
   <si>
     <t xml:space="preserve">7.93479537963867</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75263071060181</t>
+    <t xml:space="preserve">7.75263023376465</t>
   </si>
   <si>
     <t xml:space="preserve">7.71026611328125</t>
@@ -248,49 +248,49 @@
     <t xml:space="preserve">7.81194067001343</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79499340057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62553691864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66790151596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84583187103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19321918487549</t>
+    <t xml:space="preserve">7.79499483108521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62553834915161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66790342330933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8458309173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19321727752686</t>
   </si>
   <si>
     <t xml:space="preserve">8.47282028198242</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51518535614014</t>
+    <t xml:space="preserve">8.5151834487915</t>
   </si>
   <si>
     <t xml:space="preserve">8.52365684509277</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59991264343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78631496429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71853351593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50671100616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54060363769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46858406066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46434783935547</t>
+    <t xml:space="preserve">8.59991359710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78631591796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71853160858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50671291351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.540602684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46858310699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46434593200684</t>
   </si>
   <si>
     <t xml:space="preserve">8.55754852294922</t>
@@ -299,91 +299,91 @@
     <t xml:space="preserve">8.57449436187744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81173324584961</t>
+    <t xml:space="preserve">8.81173133850098</t>
   </si>
   <si>
     <t xml:space="preserve">8.72700500488281</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64227676391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89646244049072</t>
+    <t xml:space="preserve">8.6422758102417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89646148681641</t>
   </si>
   <si>
     <t xml:space="preserve">9.02355289459229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09980773925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06591892242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1082820892334</t>
+    <t xml:space="preserve">9.09980869293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06591796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10828304290771</t>
   </si>
   <si>
     <t xml:space="preserve">9.27773857116699</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1930103302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18453788757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07439136505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09133529663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30315589904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32010269165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12522792816162</t>
+    <t xml:space="preserve">9.19300937652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18453693389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07439041137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09133434295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30315685272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32010173797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12522888183594</t>
   </si>
   <si>
     <t xml:space="preserve">9.60817813873291</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4048318862915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48955726623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38788414001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5319242477417</t>
+    <t xml:space="preserve">9.40483093261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48955917358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38788509368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53192329406738</t>
   </si>
   <si>
     <t xml:space="preserve">9.48108577728271</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44719505310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54039478302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5742883682251</t>
+    <t xml:space="preserve">9.44719314575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54039669036865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57428646087646</t>
   </si>
   <si>
     <t xml:space="preserve">9.47261428833008</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41330337524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42177486419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51497650146484</t>
+    <t xml:space="preserve">9.41330528259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42177581787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51497745513916</t>
   </si>
   <si>
     <t xml:space="preserve">9.56581401824951</t>
@@ -392,25 +392,25 @@
     <t xml:space="preserve">9.74374294281006</t>
   </si>
   <si>
-    <t xml:space="preserve">10.065710067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2521123886108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1334924697876</t>
+    <t xml:space="preserve">10.0657110214233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2521133422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1334915161133</t>
   </si>
   <si>
     <t xml:space="preserve">9.99792861938477</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95556259155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98098182678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88778114318848</t>
+    <t xml:space="preserve">9.95556354522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98098278045654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88778209686279</t>
   </si>
   <si>
     <t xml:space="preserve">9.91319942474365</t>
@@ -422,67 +422,67 @@
     <t xml:space="preserve">10.1589117050171</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0402917861938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70137786865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73527145385742</t>
+    <t xml:space="preserve">10.0402936935425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70137882232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73526954650879</t>
   </si>
   <si>
     <t xml:space="preserve">9.70985221862793</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0826549530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86236381530762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1250200271606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2944755554199</t>
+    <t xml:space="preserve">10.0826559066772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8623628616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1250190734863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2944765090942</t>
   </si>
   <si>
     <t xml:space="preserve">10.4808778762817</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5317153930664</t>
+    <t xml:space="preserve">10.531717300415</t>
   </si>
   <si>
     <t xml:space="preserve">10.5147695541382</t>
   </si>
   <si>
-    <t xml:space="preserve">10.802845954895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9129934310913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.862156867981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0146656036377</t>
+    <t xml:space="preserve">10.8028450012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.912992477417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8621559143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.014666557312</t>
   </si>
   <si>
     <t xml:space="preserve">11.0570306777954</t>
   </si>
   <si>
-    <t xml:space="preserve">11.277325630188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.438307762146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6586017608643</t>
+    <t xml:space="preserve">11.2773246765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4383068084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6586008071899</t>
   </si>
   <si>
     <t xml:space="preserve">11.5823450088501</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4806718826294</t>
+    <t xml:space="preserve">11.4806728363037</t>
   </si>
   <si>
     <t xml:space="preserve">11.5908184051514</t>
@@ -494,37 +494,37 @@
     <t xml:space="preserve">11.7772197723389</t>
   </si>
   <si>
-    <t xml:space="preserve">11.811110496521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8365297317505</t>
+    <t xml:space="preserve">11.8111114501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8365316390991</t>
   </si>
   <si>
     <t xml:space="preserve">11.6670742034912</t>
   </si>
   <si>
-    <t xml:space="preserve">11.599289894104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5230350494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6077651977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6263809204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7297258377075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6952781677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6780548095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7986249923706</t>
+    <t xml:space="preserve">11.5992908477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5230369567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6077642440796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6263799667358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7297267913818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6952772140503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.678053855896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.798623085022</t>
   </si>
   <si>
     <t xml:space="preserve">11.8847455978394</t>
@@ -533,37 +533,37 @@
     <t xml:space="preserve">11.9105806350708</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0656003952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3153514862061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3584127426147</t>
+    <t xml:space="preserve">12.0655994415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3153524398804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3584117889404</t>
   </si>
   <si>
     <t xml:space="preserve">12.0569887161255</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1431093215942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9967031478882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.841685295105</t>
+    <t xml:space="preserve">12.1431083679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9967041015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8416833877563</t>
   </si>
   <si>
     <t xml:space="preserve">11.7555618286133</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7125034332275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8502960205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9191923141479</t>
+    <t xml:space="preserve">11.7125024795532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8502969741821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9191932678223</t>
   </si>
   <si>
     <t xml:space="preserve">11.962254524231</t>
@@ -572,13 +572,13 @@
     <t xml:space="preserve">12.0397634506226</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0483751296997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7900094985962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0311508178711</t>
+    <t xml:space="preserve">12.048376083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7900114059448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0311527252197</t>
   </si>
   <si>
     <t xml:space="preserve">11.945029258728</t>
@@ -587,13 +587,13 @@
     <t xml:space="preserve">11.8158483505249</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8933572769165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8761320114136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8244590759277</t>
+    <t xml:space="preserve">11.8933582305908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8761329650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8244600296021</t>
   </si>
   <si>
     <t xml:space="preserve">11.8675203323364</t>
@@ -608,49 +608,49 @@
     <t xml:space="preserve">11.7211141586304</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6694421768188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6349935531616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6091566085815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.57470703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5316467285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5230340957642</t>
+    <t xml:space="preserve">11.6694412231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6349925994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6091556549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5747079849243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5316476821899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5230360031128</t>
   </si>
   <si>
     <t xml:space="preserve">11.3680171966553</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3594036102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2818965911865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2302227020264</t>
+    <t xml:space="preserve">11.3594045639038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2818956375122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2302217483521</t>
   </si>
   <si>
     <t xml:space="preserve">11.1957740783691</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1871614456177</t>
+    <t xml:space="preserve">11.187162399292</t>
   </si>
   <si>
     <t xml:space="preserve">11.1096534729004</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0579814910889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1785507202148</t>
+    <t xml:space="preserve">11.0579805374146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1785488128662</t>
   </si>
   <si>
     <t xml:space="preserve">11.126877784729</t>
@@ -668,13 +668,13 @@
     <t xml:space="preserve">11.0838165283203</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1354894638062</t>
+    <t xml:space="preserve">11.1354885101318</t>
   </si>
   <si>
     <t xml:space="preserve">11.2043876647949</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3163452148438</t>
+    <t xml:space="preserve">11.3163461685181</t>
   </si>
   <si>
     <t xml:space="preserve">11.4541387557983</t>
@@ -683,7 +683,7 @@
     <t xml:space="preserve">11.5402612686157</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4110774993896</t>
+    <t xml:space="preserve">11.411078453064</t>
   </si>
   <si>
     <t xml:space="preserve">11.2905073165894</t>
@@ -692,13 +692,13 @@
     <t xml:space="preserve">11.1613264083862</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2646713256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1527137756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0407571792603</t>
+    <t xml:space="preserve">11.2646722793579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1527128219604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0407562255859</t>
   </si>
   <si>
     <t xml:space="preserve">11.4196901321411</t>
@@ -713,31 +713,31 @@
     <t xml:space="preserve">11.3421802520752</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9546365737915</t>
+    <t xml:space="preserve">10.9546337127686</t>
   </si>
   <si>
     <t xml:space="preserve">10.9632453918457</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0063076019287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0924301147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74032306671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01690483093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21498489379883</t>
+    <t xml:space="preserve">11.0063066482544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0924291610718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74032402038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0169038772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2149829864502</t>
   </si>
   <si>
     <t xml:space="preserve">9.37861442565918</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49057102203369</t>
+    <t xml:space="preserve">9.49057197570801</t>
   </si>
   <si>
     <t xml:space="preserve">9.5077953338623</t>
@@ -746,13 +746,13 @@
     <t xml:space="preserve">9.59391784667969</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60252952575684</t>
+    <t xml:space="preserve">9.60252857208252</t>
   </si>
   <si>
     <t xml:space="preserve">9.68865013122559</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56807994842529</t>
+    <t xml:space="preserve">9.56808185577393</t>
   </si>
   <si>
     <t xml:space="preserve">9.39583683013916</t>
@@ -761,13 +761,13 @@
     <t xml:space="preserve">9.34416580200195</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2580451965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30110549926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41306114196777</t>
+    <t xml:space="preserve">9.25804424285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30110454559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41306209564209</t>
   </si>
   <si>
     <t xml:space="preserve">9.28388118743896</t>
@@ -779,22 +779,22 @@
     <t xml:space="preserve">9.12886238098145</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02551555633545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20637130737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26665687561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69726276397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65420150756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66281509399414</t>
+    <t xml:space="preserve">9.02551460266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20637226104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26665782928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69726371765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65420246124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66281414031982</t>
   </si>
   <si>
     <t xml:space="preserve">9.64559078216553</t>
@@ -806,13 +806,13 @@
     <t xml:space="preserve">9.75754833221436</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71448707580566</t>
+    <t xml:space="preserve">9.71448612213135</t>
   </si>
   <si>
     <t xml:space="preserve">9.09441471099854</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93939590454102</t>
+    <t xml:space="preserve">8.9393949508667</t>
   </si>
   <si>
     <t xml:space="preserve">9.14608764648438</t>
@@ -821,40 +821,40 @@
     <t xml:space="preserve">9.1202507019043</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83505630493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73171234130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90395355224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77477169036865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53363132476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49918460845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57669162750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58530521392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47334766387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4302864074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54224586486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17192363739014</t>
+    <t xml:space="preserve">9.83505821228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73171138763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90395450592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77477359771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53363227844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49918365478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57669258117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58530426025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47334671020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43028831481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54224491119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17192268371582</t>
   </si>
   <si>
     <t xml:space="preserve">9.23220825195312</t>
@@ -866,16 +866,16 @@
     <t xml:space="preserve">9.51640796661377</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8608922958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95662021636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91355991363525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08580112457275</t>
+    <t xml:space="preserve">9.86089324951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95661926269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91355895996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08580207824707</t>
   </si>
   <si>
     <t xml:space="preserve">9.0427417755127</t>
@@ -887,67 +887,67 @@
     <t xml:space="preserve">8.82743740081787</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69825649261475</t>
+    <t xml:space="preserve">8.69825553894043</t>
   </si>
   <si>
     <t xml:space="preserve">8.87049865722656</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7843770980835</t>
+    <t xml:space="preserve">8.78437614440918</t>
   </si>
   <si>
     <t xml:space="preserve">8.74131488800049</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61213493347168</t>
+    <t xml:space="preserve">8.61213397979736</t>
   </si>
   <si>
     <t xml:space="preserve">8.59490966796875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65519618988037</t>
+    <t xml:space="preserve">8.65519428253174</t>
   </si>
   <si>
     <t xml:space="preserve">8.45711612701416</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06314468383789</t>
+    <t xml:space="preserve">9.06314373016357</t>
   </si>
   <si>
     <t xml:space="preserve">9.10714149475098</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01914882659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97515296936035</t>
+    <t xml:space="preserve">9.0191478729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97515392303467</t>
   </si>
   <si>
     <t xml:space="preserve">8.93115615844727</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88716316223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84316635131836</t>
+    <t xml:space="preserve">8.88716220855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84316539764404</t>
   </si>
   <si>
     <t xml:space="preserve">8.76397228240967</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48239994049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71117782592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62318706512451</t>
+    <t xml:space="preserve">8.48240089416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71117687225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62318801879883</t>
   </si>
   <si>
     <t xml:space="preserve">8.58799076080322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6583833694458</t>
+    <t xml:space="preserve">8.65838146209717</t>
   </si>
   <si>
     <t xml:space="preserve">8.60558700561523</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">8.72877597808838</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69357872009277</t>
+    <t xml:space="preserve">8.69358062744141</t>
   </si>
   <si>
     <t xml:space="preserve">8.74637413024902</t>
@@ -965,10 +965,10 @@
     <t xml:space="preserve">8.53519439697266</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44720363616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27121925354004</t>
+    <t xml:space="preserve">8.44720268249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27121829986572</t>
   </si>
   <si>
     <t xml:space="preserve">8.32401466369629</t>
@@ -977,13 +977,13 @@
     <t xml:space="preserve">8.288818359375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.781569480896</t>
+    <t xml:space="preserve">8.78157043457031</t>
   </si>
   <si>
     <t xml:space="preserve">8.64078426361084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79916954040527</t>
+    <t xml:space="preserve">8.79916858673096</t>
   </si>
   <si>
     <t xml:space="preserve">8.67598056793213</t>
@@ -992,31 +992,31 @@
     <t xml:space="preserve">9.23912906646729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37111663818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32712078094482</t>
+    <t xml:space="preserve">9.37111473083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32711982727051</t>
   </si>
   <si>
     <t xml:space="preserve">9.1951322555542</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15113735198975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46479988098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41200733184814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49999809265137</t>
+    <t xml:space="preserve">9.15113544464111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46480083465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41200637817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49999713897705</t>
   </si>
   <si>
     <t xml:space="preserve">8.34161186218262</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23602199554443</t>
+    <t xml:space="preserve">8.23602104187012</t>
   </si>
   <si>
     <t xml:space="preserve">8.30641555786133</t>
@@ -1025,31 +1025,31 @@
     <t xml:space="preserve">8.13043212890625</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18322658538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16562843322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21842479705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25362014770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37680912017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5175952911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28312492370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41511249542236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63509082794189</t>
+    <t xml:space="preserve">8.1832275390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16562938690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21842384338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25362205505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37681007385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51759624481201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28312301635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41511154174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63509178161621</t>
   </si>
   <si>
     <t xml:space="preserve">9.59109401702881</t>
@@ -1058,22 +1058,22 @@
     <t xml:space="preserve">9.89906597137451</t>
   </si>
   <si>
-    <t xml:space="preserve">10.119044303894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1630411148071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2070369720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3390226364136</t>
+    <t xml:space="preserve">10.1190452575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1630401611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2070360183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3390245437622</t>
   </si>
   <si>
     <t xml:space="preserve">10.2950286865234</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3830194473267</t>
+    <t xml:space="preserve">10.383020401001</t>
   </si>
   <si>
     <t xml:space="preserve">10.2510318756104</t>
@@ -1082,7 +1082,7 @@
     <t xml:space="preserve">10.4270162582397</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0750484466553</t>
+    <t xml:space="preserve">10.0750494003296</t>
   </si>
   <si>
     <t xml:space="preserve">10.515007019043</t>
@@ -1091,13 +1091,13 @@
     <t xml:space="preserve">10.6498155593872</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4700727462769</t>
+    <t xml:space="preserve">10.4700708389282</t>
   </si>
   <si>
     <t xml:space="preserve">10.694751739502</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6048803329468</t>
+    <t xml:space="preserve">10.6048793792725</t>
   </si>
   <si>
     <t xml:space="preserve">10.3802003860474</t>
@@ -1106,82 +1106,82 @@
     <t xml:space="preserve">10.2453908920288</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0656480789185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4251356124878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3352632522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2903289794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2004556655884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9757776260376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1105842590332</t>
+    <t xml:space="preserve">10.0656490325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4251365661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3352642059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2903270721436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.200457572937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97577857971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1105852127075</t>
   </si>
   <si>
     <t xml:space="preserve">9.93084049224854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88590431213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1555213928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0207118988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75109672546387</t>
+    <t xml:space="preserve">9.88590526580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1555204391479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0207109451294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75109767913818</t>
   </si>
   <si>
     <t xml:space="preserve">9.70616149902344</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3466739654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30173778533936</t>
+    <t xml:space="preserve">9.34667205810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30173873901367</t>
   </si>
   <si>
     <t xml:space="preserve">9.39160919189453</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48148155212402</t>
+    <t xml:space="preserve">9.48148059844971</t>
   </si>
   <si>
     <t xml:space="preserve">9.61628913879395</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52641677856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43654441833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12199306488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0321216583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16692924499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07705783843994</t>
+    <t xml:space="preserve">9.52641773223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43654537200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12199211120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03212261199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16693019866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07705974578857</t>
   </si>
   <si>
     <t xml:space="preserve">9.25680160522461</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98718643188477</t>
+    <t xml:space="preserve">8.98718547821045</t>
   </si>
   <si>
     <t xml:space="preserve">9.5713529586792</t>
@@ -1190,7 +1190,7 @@
     <t xml:space="preserve">9.66122627258301</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79603290557861</t>
+    <t xml:space="preserve">9.7960319519043</t>
   </si>
   <si>
     <t xml:space="preserve">10.9643669128418</t>
@@ -1199,10 +1199,10 @@
     <t xml:space="preserve">11.4586620330811</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5035991668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2339820861816</t>
+    <t xml:space="preserve">11.5035982131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.233983039856</t>
   </si>
   <si>
     <t xml:space="preserve">11.1441106796265</t>
@@ -1211,10 +1211,10 @@
     <t xml:space="preserve">10.9194307327271</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8744955062866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0093030929565</t>
+    <t xml:space="preserve">10.8744974136353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0093040466309</t>
   </si>
   <si>
     <t xml:space="preserve">11.2789192199707</t>
@@ -1226,55 +1226,55 @@
     <t xml:space="preserve">11.5485343933105</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6833419799805</t>
+    <t xml:space="preserve">11.6833429336548</t>
   </si>
   <si>
     <t xml:space="preserve">11.7732152938843</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9080209732056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1327018737793</t>
+    <t xml:space="preserve">11.9080228805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.132700920105</t>
   </si>
   <si>
     <t xml:space="preserve">11.9978942871094</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8181495666504</t>
+    <t xml:space="preserve">11.8181505203247</t>
   </si>
   <si>
     <t xml:space="preserve">11.593469619751</t>
   </si>
   <si>
-    <t xml:space="preserve">12.312445640564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5820617675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9415473937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8067407608032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7618045806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0763559341431</t>
+    <t xml:space="preserve">12.3124446868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5820608139038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9415483474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8067398071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7618026733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0763568878174</t>
   </si>
   <si>
     <t xml:space="preserve">12.4472532272339</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5371246337891</t>
+    <t xml:space="preserve">12.5371236801147</t>
   </si>
   <si>
     <t xml:space="preserve">12.2675085067749</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4023170471191</t>
+    <t xml:space="preserve">12.4023180007935</t>
   </si>
   <si>
     <t xml:space="preserve">12.6269969940186</t>
@@ -1283,28 +1283,28 @@
     <t xml:space="preserve">12.671932220459</t>
   </si>
   <si>
-    <t xml:space="preserve">12.896614074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7282781600952</t>
+    <t xml:space="preserve">12.8966131210327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7282772064209</t>
   </si>
   <si>
     <t xml:space="preserve">10.7846240997314</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5599431991577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89731407165527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98062181472778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81885242462158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53126192092896</t>
+    <t xml:space="preserve">10.559944152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89731311798096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98062086105347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81885194778442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53126239776611</t>
   </si>
   <si>
     <t xml:space="preserve">7.89074850082397</t>
@@ -1313,43 +1313,43 @@
     <t xml:space="preserve">8.53782653808594</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96264600753784</t>
+    <t xml:space="preserve">7.96264696121216</t>
   </si>
   <si>
     <t xml:space="preserve">8.44795417785645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60972595214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66364765167236</t>
+    <t xml:space="preserve">8.6097240447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66364860534668</t>
   </si>
   <si>
     <t xml:space="preserve">8.86136531829834</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21186637878418</t>
+    <t xml:space="preserve">9.21186447143555</t>
   </si>
   <si>
     <t xml:space="preserve">9.93848991394043</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80045413970947</t>
+    <t xml:space="preserve">9.80045509338379</t>
   </si>
   <si>
     <t xml:space="preserve">9.89247798919678</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66241931915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7084321975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84646701812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1225347518921</t>
+    <t xml:space="preserve">9.66242027282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70843124389648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84646606445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1225357055664</t>
   </si>
   <si>
     <t xml:space="preserve">9.75444412231445</t>
@@ -1367,10 +1367,10 @@
     <t xml:space="preserve">10.5826511383057</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8587207794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6746740341187</t>
+    <t xml:space="preserve">10.8587198257446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.674674987793</t>
   </si>
   <si>
     <t xml:space="preserve">10.9967546463013</t>
@@ -1379,16 +1379,16 @@
     <t xml:space="preserve">10.628662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7666959762573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.490626335144</t>
+    <t xml:space="preserve">10.7666969299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4906272888184</t>
   </si>
   <si>
     <t xml:space="preserve">11.1347894668579</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3188352584839</t>
+    <t xml:space="preserve">11.3188362121582</t>
   </si>
   <si>
     <t xml:space="preserve">11.5028820037842</t>
@@ -1397,13 +1397,13 @@
     <t xml:space="preserve">11.1808004379272</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0427675247192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2728242874146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9507427215576</t>
+    <t xml:space="preserve">11.0427665710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2728233337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9507417678833</t>
   </si>
   <si>
     <t xml:space="preserve">11.0887775421143</t>
@@ -1418,16 +1418,16 @@
     <t xml:space="preserve">11.4108581542969</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4568691253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2268114089966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3648471832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5488929748535</t>
+    <t xml:space="preserve">11.4568700790405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2268123626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3648462295532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5488920211792</t>
   </si>
   <si>
     <t xml:space="preserve">11.5949048995972</t>
@@ -1442,7 +1442,7 @@
     <t xml:space="preserve">11.7789506912231</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0090074539185</t>
+    <t xml:space="preserve">12.0090084075928</t>
   </si>
   <si>
     <t xml:space="preserve">12.1010313034058</t>
@@ -1454,7 +1454,7 @@
     <t xml:space="preserve">11.8249626159668</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0550203323364</t>
+    <t xml:space="preserve">12.0550193786621</t>
   </si>
   <si>
     <t xml:space="preserve">11.8709735870361</t>
@@ -1463,28 +1463,28 @@
     <t xml:space="preserve">11.9169845581055</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6409168243408</t>
+    <t xml:space="preserve">11.6409158706665</t>
   </si>
   <si>
     <t xml:space="preserve">12.1470422744751</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6991806030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7912044525146</t>
+    <t xml:space="preserve">12.6991815567017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7912034988403</t>
   </si>
   <si>
     <t xml:space="preserve">13.0672731399536</t>
   </si>
   <si>
-    <t xml:space="preserve">12.883228302002</t>
+    <t xml:space="preserve">12.8832273483276</t>
   </si>
   <si>
     <t xml:space="preserve">12.9292392730713</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2053089141846</t>
+    <t xml:space="preserve">13.2053079605103</t>
   </si>
   <si>
     <t xml:space="preserve">13.2513189315796</t>
@@ -1505,7 +1505,7 @@
     <t xml:space="preserve">12.9752502441406</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7114343643188</t>
+    <t xml:space="preserve">13.7114334106445</t>
   </si>
   <si>
     <t xml:space="preserve">13.4353656768799</t>
@@ -1514,19 +1514,19 @@
     <t xml:space="preserve">12.5151348114014</t>
   </si>
   <si>
-    <t xml:space="preserve">12.377100944519</t>
+    <t xml:space="preserve">12.3770990371704</t>
   </si>
   <si>
     <t xml:space="preserve">12.837215423584</t>
   </si>
   <si>
-    <t xml:space="preserve">12.745192527771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6531686782837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3433418273926</t>
+    <t xml:space="preserve">12.7451934814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.653169631958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3433437347412</t>
   </si>
   <si>
     <t xml:space="preserve">13.6194124221802</t>
@@ -1538,7 +1538,7 @@
     <t xml:space="preserve">13.9414920806885</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1715497970581</t>
+    <t xml:space="preserve">14.1715507507324</t>
   </si>
   <si>
     <t xml:space="preserve">14.3555955886841</t>
@@ -1553,28 +1553,28 @@
     <t xml:space="preserve">14.7236881256104</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6776762008667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8157110214233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8617219924927</t>
+    <t xml:space="preserve">14.677677154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.815710067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.861722946167</t>
   </si>
   <si>
     <t xml:space="preserve">15.045768737793</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5396413803101</t>
+    <t xml:space="preserve">14.5396423339844</t>
   </si>
   <si>
     <t xml:space="preserve">14.6316652297974</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4476194381714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2635736465454</t>
+    <t xml:space="preserve">14.4476203918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2635726928711</t>
   </si>
   <si>
     <t xml:space="preserve">13.9875040054321</t>
@@ -1583,25 +1583,25 @@
     <t xml:space="preserve">14.3095855712891</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6654233932495</t>
+    <t xml:space="preserve">13.6654243469238</t>
   </si>
   <si>
     <t xml:space="preserve">13.8034572601318</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5734004974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7574453353882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.95374584198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0335140228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4269771575928</t>
+    <t xml:space="preserve">13.5733995437622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7574462890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9537448883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0335149765015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4269781112671</t>
   </si>
   <si>
     <t xml:space="preserve">14.3801383972168</t>
@@ -1613,7 +1613,7 @@
     <t xml:space="preserve">14.7080240249634</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8485460281372</t>
+    <t xml:space="preserve">14.8485450744629</t>
   </si>
   <si>
     <t xml:space="preserve">15.0359086990356</t>
@@ -1625,19 +1625,19 @@
     <t xml:space="preserve">14.8953866958618</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9422264099121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1764326095581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1295900344849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9890689849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6611824035645</t>
+    <t xml:space="preserve">14.9422273635864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1764316558838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1295909881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.989068031311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6611814498901</t>
   </si>
   <si>
     <t xml:space="preserve">15.3169546127319</t>
@@ -1646,7 +1646,7 @@
     <t xml:space="preserve">14.7548627853394</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8017044067383</t>
+    <t xml:space="preserve">14.8017053604126</t>
   </si>
   <si>
     <t xml:space="preserve">15.2232723236084</t>
@@ -1667,7 +1667,7 @@
     <t xml:space="preserve">15.9727249145508</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9258861541748</t>
+    <t xml:space="preserve">15.9258842468262</t>
   </si>
   <si>
     <t xml:space="preserve">15.785364151001</t>
@@ -1676,7 +1676,7 @@
     <t xml:space="preserve">16.1132488250732</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8322019577026</t>
+    <t xml:space="preserve">15.8322038650513</t>
   </si>
   <si>
     <t xml:space="preserve">16.5348148345947</t>
@@ -1688,13 +1688,13 @@
     <t xml:space="preserve">17.1437454223633</t>
   </si>
   <si>
-    <t xml:space="preserve">16.581657409668</t>
+    <t xml:space="preserve">16.5816593170166</t>
   </si>
   <si>
     <t xml:space="preserve">16.2069301605225</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2842712402344</t>
+    <t xml:space="preserve">17.2842693328857</t>
   </si>
   <si>
     <t xml:space="preserve">17.7995185852051</t>
@@ -1703,7 +1703,7 @@
     <t xml:space="preserve">17.4716339111328</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8158626556396</t>
+    <t xml:space="preserve">16.815860748291</t>
   </si>
   <si>
     <t xml:space="preserve">16.6284980773926</t>
@@ -1712,10 +1712,10 @@
     <t xml:space="preserve">17.0969047546387</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5184745788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.612154006958</t>
+    <t xml:space="preserve">17.5184726715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6121559143066</t>
   </si>
   <si>
     <t xml:space="preserve">18.0337219238281</t>
@@ -1724,13 +1724,13 @@
     <t xml:space="preserve">18.5489711761475</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7363357543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.923698425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7668342590332</t>
+    <t xml:space="preserve">18.7363338470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9237003326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7668323516846</t>
   </si>
   <si>
     <t xml:space="preserve">19.5794696807861</t>
@@ -1742,7 +1742,7 @@
     <t xml:space="preserve">19.1110610961914</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6731510162354</t>
+    <t xml:space="preserve">19.673152923584</t>
   </si>
   <si>
     <t xml:space="preserve">19.2984237670898</t>
@@ -1754,10 +1754,10 @@
     <t xml:space="preserve">19.8605175018311</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3289222717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9846935272217</t>
+    <t xml:space="preserve">20.3289241790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9846954345703</t>
   </si>
   <si>
     <t xml:space="preserve">21.2657413482666</t>
@@ -1766,19 +1766,19 @@
     <t xml:space="preserve">21.0783786773682</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4531059265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7973346710205</t>
+    <t xml:space="preserve">21.453104019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7973327636719</t>
   </si>
   <si>
     <t xml:space="preserve">21.8278312683105</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1088790893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7341480255127</t>
+    <t xml:space="preserve">22.1088771820068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7341499328613</t>
   </si>
   <si>
     <t xml:space="preserve">22.015193939209</t>
@@ -1787,13 +1787,13 @@
     <t xml:space="preserve">22.2962379455566</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4836044311523</t>
+    <t xml:space="preserve">22.4836025238037</t>
   </si>
   <si>
     <t xml:space="preserve">21.6404666900635</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5467834472656</t>
+    <t xml:space="preserve">21.5467853546143</t>
   </si>
   <si>
     <t xml:space="preserve">20.2352428436279</t>
@@ -1829,28 +1829,28 @@
     <t xml:space="preserve">20.5162868499756</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0478801727295</t>
+    <t xml:space="preserve">20.0478782653809</t>
   </si>
   <si>
     <t xml:space="preserve">22.6709671020508</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2025566101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3899192810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.954195022583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4226055145264</t>
+    <t xml:space="preserve">22.2025585174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3899211883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9541969299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4226036071777</t>
   </si>
   <si>
     <t xml:space="preserve">20.8910121917725</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3921089172363</t>
+    <t xml:space="preserve">19.3921070098877</t>
   </si>
   <si>
     <t xml:space="preserve">18.8300189971924</t>
@@ -1862,7 +1862,7 @@
     <t xml:space="preserve">16.9563846588135</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6589965820312</t>
+    <t xml:space="preserve">17.6589984893799</t>
   </si>
   <si>
     <t xml:space="preserve">17.7526760101318</t>
@@ -1871,13 +1871,13 @@
     <t xml:space="preserve">17.377950668335</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8931999206543</t>
+    <t xml:space="preserve">17.8932018280029</t>
   </si>
   <si>
     <t xml:space="preserve">17.9400405883789</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2679252624512</t>
+    <t xml:space="preserve">18.2679271697998</t>
   </si>
   <si>
     <t xml:space="preserve">18.8768577575684</t>
@@ -1901,7 +1901,7 @@
     <t xml:space="preserve">17.9494113922119</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1180362701416</t>
+    <t xml:space="preserve">18.118034362793</t>
   </si>
   <si>
     <t xml:space="preserve">18.9705390930176</t>
@@ -1925,7 +1925,7 @@
     <t xml:space="preserve">17.5559463500977</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1999568939209</t>
+    <t xml:space="preserve">17.1999549865723</t>
   </si>
   <si>
     <t xml:space="preserve">16.8847980499268</t>
@@ -3429,6 +3429,9 @@
   </si>
   <si>
     <t xml:space="preserve">38.7999992370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0499992370605</t>
   </si>
 </sst>
 </file>
@@ -69417,7 +69420,7 @@
     </row>
     <row r="2526">
       <c r="A2526" s="1" t="n">
-        <v>45995.6911689815</v>
+        <v>45995.3333333333</v>
       </c>
       <c r="B2526" t="n">
         <v>145102</v>
@@ -69438,6 +69441,32 @@
         <v>1138</v>
       </c>
       <c r="H2526" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2527">
+      <c r="A2527" s="1" t="n">
+        <v>45996.6911342593</v>
+      </c>
+      <c r="B2527" t="n">
+        <v>7511</v>
+      </c>
+      <c r="C2527" t="n">
+        <v>39.25</v>
+      </c>
+      <c r="D2527" t="n">
+        <v>38.7000007629395</v>
+      </c>
+      <c r="E2527" t="n">
+        <v>39.0999984741211</v>
+      </c>
+      <c r="F2527" t="n">
+        <v>39.0499992370605</v>
+      </c>
+      <c r="G2527" t="s">
+        <v>1139</v>
+      </c>
+      <c r="H2527" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LUVE.MI.xlsx
+++ b/data/LUVE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1140" uniqueCount="1140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1141" uniqueCount="1141">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30043315887451</t>
+    <t xml:space="preserve">8.30043411254883</t>
   </si>
   <si>
     <t xml:space="preserve">LUVE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31703567504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28383255004883</t>
+    <t xml:space="preserve">8.3170337677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28383159637451</t>
   </si>
   <si>
     <t xml:space="preserve">8.09292316436768</t>
@@ -62,49 +62,49 @@
     <t xml:space="preserve">8.15102577209473</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17177677154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03896903991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08462047576904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06802272796631</t>
+    <t xml:space="preserve">8.17177581787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03897094726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08462238311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06802082061768</t>
   </si>
   <si>
     <t xml:space="preserve">7.96841764450073</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01821899414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99746894836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91861391067505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91446352005005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91031265258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88541078567505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87711143493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.852210521698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.648850440979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71940279006958</t>
+    <t xml:space="preserve">8.01821708679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99746751785278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91861438751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91446208953857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91031217575073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88541221618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87711191177368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85221004486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64884996414185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71940231323242</t>
   </si>
   <si>
     <t xml:space="preserve">7.70280122756958</t>
@@ -113,82 +113,82 @@
     <t xml:space="preserve">7.69035196304321</t>
   </si>
   <si>
-    <t xml:space="preserve">7.619797706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55754518508911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55339384078979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63639879226685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76920604705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80240678787231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93521356582642</t>
+    <t xml:space="preserve">7.61979866027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55754423141479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55339431762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63639783859253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76920509338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80240631103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93521547317505</t>
   </si>
   <si>
     <t xml:space="preserve">8.10122299194336</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05142116546631</t>
+    <t xml:space="preserve">8.05142021179199</t>
   </si>
   <si>
     <t xml:space="preserve">8.18422794342041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13442516326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00161933898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9601149559021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21742725372314</t>
+    <t xml:space="preserve">8.13442611694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00161743164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96011638641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21742820739746</t>
   </si>
   <si>
     <t xml:space="preserve">8.35853576660156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32533550262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2921314239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20082950592041</t>
+    <t xml:space="preserve">8.32533359527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29213237762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20082759857178</t>
   </si>
   <si>
     <t xml:space="preserve">8.15932559967041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30336475372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36267375946045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43045616149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15085124969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17627048492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20592594146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13390922546387</t>
+    <t xml:space="preserve">8.30336380004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36267280578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43045520782471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15085315704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17627143859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2059268951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13390827178955</t>
   </si>
   <si>
     <t xml:space="preserve">8.11696243286133</t>
@@ -197,52 +197,52 @@
     <t xml:space="preserve">8.21863651275635</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21016216278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21439743041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20169067382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26100063323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09154415130615</t>
+    <t xml:space="preserve">8.21016407012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21439933776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20169162750244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26099872589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09154319763184</t>
   </si>
   <si>
     <t xml:space="preserve">8.10848903656006</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04917812347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96445035934448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92208814620972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87972259521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83735847473145</t>
+    <t xml:space="preserve">8.04917907714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96445178985596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92208671569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.879723072052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8373589515686</t>
   </si>
   <si>
     <t xml:space="preserve">8.12543392181396</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93479537963867</t>
+    <t xml:space="preserve">7.93479633331299</t>
   </si>
   <si>
     <t xml:space="preserve">7.75263023376465</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71026611328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93903255462646</t>
+    <t xml:space="preserve">7.71026706695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93903112411499</t>
   </si>
   <si>
     <t xml:space="preserve">7.81194067001343</t>
@@ -251,64 +251,64 @@
     <t xml:space="preserve">7.79499483108521</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62553834915161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66790342330933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8458309173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19321727752686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47282028198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5151834487915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52365684509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59991359710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78631591796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71853160858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50671291351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.540602684021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46858310699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46434593200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55754852294922</t>
+    <t xml:space="preserve">7.62553882598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66790294647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84583187103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19321823120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47281932830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51518535614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52365875244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5999116897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7863130569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71853065490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50671195983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54060173034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46858406066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46434688568115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55754947662354</t>
   </si>
   <si>
     <t xml:space="preserve">8.57449436187744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81173133850098</t>
+    <t xml:space="preserve">8.81173229217529</t>
   </si>
   <si>
     <t xml:space="preserve">8.72700500488281</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6422758102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89646148681641</t>
+    <t xml:space="preserve">8.64227676391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89646053314209</t>
   </si>
   <si>
     <t xml:space="preserve">9.02355289459229</t>
@@ -317,40 +317,40 @@
     <t xml:space="preserve">9.09980869293213</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06591796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10828304290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27773857116699</t>
+    <t xml:space="preserve">9.06591701507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1082820892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27773666381836</t>
   </si>
   <si>
     <t xml:space="preserve">9.19300937652588</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18453693389893</t>
+    <t xml:space="preserve">9.18453788757324</t>
   </si>
   <si>
     <t xml:space="preserve">9.07439041137695</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09133434295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30315685272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32010173797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12522888183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60817813873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40483093261719</t>
+    <t xml:space="preserve">9.09133529663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30315589904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32010269165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12522602081299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60817909240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4048318862915</t>
   </si>
   <si>
     <t xml:space="preserve">9.48955917358398</t>
@@ -359,97 +359,97 @@
     <t xml:space="preserve">9.38788509368896</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53192329406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48108577728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44719314575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54039669036865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57428646087646</t>
+    <t xml:space="preserve">9.5319242477417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48108386993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44719409942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54039573669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57428741455078</t>
   </si>
   <si>
     <t xml:space="preserve">9.47261428833008</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41330528259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42177581787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51497745513916</t>
+    <t xml:space="preserve">9.41330242156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42177677154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51497650146484</t>
   </si>
   <si>
     <t xml:space="preserve">9.56581401824951</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74374294281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0657110214233</t>
+    <t xml:space="preserve">9.74374389648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.065710067749</t>
   </si>
   <si>
     <t xml:space="preserve">10.2521133422852</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1334915161133</t>
+    <t xml:space="preserve">10.1334924697876</t>
   </si>
   <si>
     <t xml:space="preserve">9.99792861938477</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95556354522705</t>
+    <t xml:space="preserve">9.95556259155273</t>
   </si>
   <si>
     <t xml:space="preserve">9.98098278045654</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88778209686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91319942474365</t>
+    <t xml:space="preserve">9.88778114318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91320133209229</t>
   </si>
   <si>
     <t xml:space="preserve">10.0148735046387</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1589117050171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0402936935425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70137882232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73526954650879</t>
+    <t xml:space="preserve">10.1589126586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0402917861938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70137977600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73527050018311</t>
   </si>
   <si>
     <t xml:space="preserve">9.70985221862793</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0826559066772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8623628616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1250190734863</t>
+    <t xml:space="preserve">10.0826568603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86236190795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1250200271606</t>
   </si>
   <si>
     <t xml:space="preserve">10.2944765090942</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4808778762817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.531717300415</t>
+    <t xml:space="preserve">10.4808769226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5317163467407</t>
   </si>
   <si>
     <t xml:space="preserve">10.5147695541382</t>
@@ -461,31 +461,31 @@
     <t xml:space="preserve">10.912992477417</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8621559143066</t>
+    <t xml:space="preserve">10.8621549606323</t>
   </si>
   <si>
     <t xml:space="preserve">11.014666557312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0570306777954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2773246765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4383068084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6586008071899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5823450088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4806728363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5908184051514</t>
+    <t xml:space="preserve">11.0570316314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2773237228394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.438307762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6586017608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5823459625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4806718826294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5908193588257</t>
   </si>
   <si>
     <t xml:space="preserve">11.7009649276733</t>
@@ -497,64 +497,64 @@
     <t xml:space="preserve">11.8111114501953</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8365316390991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6670742034912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5992908477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5230369567871</t>
+    <t xml:space="preserve">11.8365297317505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6670732498169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.599289894104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5230350494385</t>
   </si>
   <si>
     <t xml:space="preserve">11.6077642440796</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6263799667358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7297267913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6952772140503</t>
+    <t xml:space="preserve">11.6263809204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7297248840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6952781677246</t>
   </si>
   <si>
     <t xml:space="preserve">11.678053855896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.798623085022</t>
+    <t xml:space="preserve">11.7986240386963</t>
   </si>
   <si>
     <t xml:space="preserve">11.8847455978394</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9105806350708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0655994415283</t>
+    <t xml:space="preserve">11.9105815887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.065598487854</t>
   </si>
   <si>
     <t xml:space="preserve">12.3153524398804</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3584117889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0569887161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1431083679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9967041015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8416833877563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7555618286133</t>
+    <t xml:space="preserve">12.3584127426147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0569877624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1431102752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9967031478882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.841685295105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7555637359619</t>
   </si>
   <si>
     <t xml:space="preserve">11.7125024795532</t>
@@ -569,31 +569,31 @@
     <t xml:space="preserve">11.962254524231</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0397634506226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.048376083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7900114059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0311527252197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.945029258728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8158483505249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8933582305908</t>
+    <t xml:space="preserve">12.0397644042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0483770370483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7900104522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0311517715454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9450302124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8158473968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8933572769165</t>
   </si>
   <si>
     <t xml:space="preserve">11.8761329650879</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8244600296021</t>
+    <t xml:space="preserve">11.8244581222534</t>
   </si>
   <si>
     <t xml:space="preserve">11.8675203323364</t>
@@ -602,37 +602,34 @@
     <t xml:space="preserve">11.9019689559937</t>
   </si>
   <si>
-    <t xml:space="preserve">11.927806854248</t>
+    <t xml:space="preserve">11.9278059005737</t>
   </si>
   <si>
     <t xml:space="preserve">11.7211141586304</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6694412231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6349925994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6091556549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5747079849243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5316476821899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5230360031128</t>
+    <t xml:space="preserve">11.6694421768188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6349935531616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6091566085815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.57470703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5316486358643</t>
   </si>
   <si>
     <t xml:space="preserve">11.3680171966553</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3594045639038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2818956375122</t>
+    <t xml:space="preserve">11.3594055175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2818965911865</t>
   </si>
   <si>
     <t xml:space="preserve">11.2302217483521</t>
@@ -641,25 +638,25 @@
     <t xml:space="preserve">11.1957740783691</t>
   </si>
   <si>
-    <t xml:space="preserve">11.187162399292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1096534729004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0579805374146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1785488128662</t>
+    <t xml:space="preserve">11.1871633529663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1096525192261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0579814910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1785497665405</t>
   </si>
   <si>
     <t xml:space="preserve">11.126877784729</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9374103546143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0665922164917</t>
+    <t xml:space="preserve">10.9374113082886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.066593170166</t>
   </si>
   <si>
     <t xml:space="preserve">11.0235319137573</t>
@@ -668,22 +665,22 @@
     <t xml:space="preserve">11.0838165283203</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1354885101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2043876647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3163461685181</t>
+    <t xml:space="preserve">11.1354894638062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2043867111206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3163433074951</t>
   </si>
   <si>
     <t xml:space="preserve">11.4541387557983</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5402612686157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.411078453064</t>
+    <t xml:space="preserve">11.5402593612671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4110774993896</t>
   </si>
   <si>
     <t xml:space="preserve">11.2905073165894</t>
@@ -692,13 +689,13 @@
     <t xml:space="preserve">11.1613264083862</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2646722793579</t>
+    <t xml:space="preserve">11.2646713256836</t>
   </si>
   <si>
     <t xml:space="preserve">11.1527128219604</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0407562255859</t>
+    <t xml:space="preserve">11.0407552719116</t>
   </si>
   <si>
     <t xml:space="preserve">11.4196901321411</t>
@@ -707,16 +704,16 @@
     <t xml:space="preserve">11.2216100692749</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2388353347778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3421802520752</t>
+    <t xml:space="preserve">11.2388343811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3421792984009</t>
   </si>
   <si>
     <t xml:space="preserve">10.9546337127686</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9632453918457</t>
+    <t xml:space="preserve">10.96324634552</t>
   </si>
   <si>
     <t xml:space="preserve">11.0063066482544</t>
@@ -725,40 +722,40 @@
     <t xml:space="preserve">11.0924291610718</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74032402038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0169038772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2149829864502</t>
+    <t xml:space="preserve">9.74032306671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01690483093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21498394012451</t>
   </si>
   <si>
     <t xml:space="preserve">9.37861442565918</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49057197570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5077953338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59391784667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60252857208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68865013122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56808185577393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39583683013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34416580200195</t>
+    <t xml:space="preserve">9.49057102203369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50779628753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59391689300537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60252952575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6886510848999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56808090209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39583873748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34416484832764</t>
   </si>
   <si>
     <t xml:space="preserve">9.25804424285889</t>
@@ -767,25 +764,25 @@
     <t xml:space="preserve">9.30110454559326</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41306209564209</t>
+    <t xml:space="preserve">9.41306304931641</t>
   </si>
   <si>
     <t xml:space="preserve">9.28388118743896</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24081993103027</t>
+    <t xml:space="preserve">9.24081897735596</t>
   </si>
   <si>
     <t xml:space="preserve">9.12886238098145</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02551460266113</t>
+    <t xml:space="preserve">9.02551555633545</t>
   </si>
   <si>
     <t xml:space="preserve">9.20637226104736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26665782928467</t>
+    <t xml:space="preserve">9.26665687561035</t>
   </si>
   <si>
     <t xml:space="preserve">9.69726371765137</t>
@@ -794,34 +791,34 @@
     <t xml:space="preserve">9.65420246124268</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66281414031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64559078216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67142581939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75754833221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71448612213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09441471099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9393949508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14608764648438</t>
+    <t xml:space="preserve">9.66281509399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64558982849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67142677307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75754737854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71448707580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09441375732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93939590454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14608669281006</t>
   </si>
   <si>
     <t xml:space="preserve">9.1202507019043</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83505821228027</t>
+    <t xml:space="preserve">9.83505725860596</t>
   </si>
   <si>
     <t xml:space="preserve">9.73171138763428</t>
@@ -830,10 +827,10 @@
     <t xml:space="preserve">9.90395450592041</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77477359771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53363227844238</t>
+    <t xml:space="preserve">9.77477264404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5336332321167</t>
   </si>
   <si>
     <t xml:space="preserve">9.49918365478516</t>
@@ -848,19 +845,19 @@
     <t xml:space="preserve">9.47334671020508</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43028831481934</t>
+    <t xml:space="preserve">9.4302864074707</t>
   </si>
   <si>
     <t xml:space="preserve">9.54224491119385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17192268371582</t>
+    <t xml:space="preserve">9.17192363739014</t>
   </si>
   <si>
     <t xml:space="preserve">9.23220825195312</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55946922302246</t>
+    <t xml:space="preserve">9.55947017669678</t>
   </si>
   <si>
     <t xml:space="preserve">9.51640796661377</t>
@@ -875,22 +872,22 @@
     <t xml:space="preserve">8.91355895996094</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08580207824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0427417755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.999680519104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82743740081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69825553894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87049865722656</t>
+    <t xml:space="preserve">9.08580112457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04274082183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99967956542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8274393081665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69825458526611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87049770355225</t>
   </si>
   <si>
     <t xml:space="preserve">8.78437614440918</t>
@@ -905,58 +902,58 @@
     <t xml:space="preserve">8.59490966796875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65519428253174</t>
+    <t xml:space="preserve">8.65519618988037</t>
   </si>
   <si>
     <t xml:space="preserve">8.45711612701416</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06314373016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10714149475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0191478729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97515392303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93115615844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88716220855713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84316539764404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76397228240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48240089416504</t>
+    <t xml:space="preserve">9.06314468383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10714054107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01914978027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97515201568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93115711212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8871603012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84316635131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76397323608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48239994049072</t>
   </si>
   <si>
     <t xml:space="preserve">8.71117687225342</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62318801879883</t>
+    <t xml:space="preserve">8.62318706512451</t>
   </si>
   <si>
     <t xml:space="preserve">8.58799076080322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65838146209717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60558700561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72877597808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69358062744141</t>
+    <t xml:space="preserve">8.65838241577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60558795928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7287769317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69357967376709</t>
   </si>
   <si>
     <t xml:space="preserve">8.74637413024902</t>
@@ -965,10 +962,10 @@
     <t xml:space="preserve">8.53519439697266</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44720268249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27121829986572</t>
+    <t xml:space="preserve">8.44720458984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27121925354004</t>
   </si>
   <si>
     <t xml:space="preserve">8.32401466369629</t>
@@ -977,22 +974,22 @@
     <t xml:space="preserve">8.288818359375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78157043457031</t>
+    <t xml:space="preserve">8.78157138824463</t>
   </si>
   <si>
     <t xml:space="preserve">8.64078426361084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79916858673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67598056793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23912906646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37111473083496</t>
+    <t xml:space="preserve">8.79916954040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67598152160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23912811279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37111663818359</t>
   </si>
   <si>
     <t xml:space="preserve">9.32711982727051</t>
@@ -1010,13 +1007,13 @@
     <t xml:space="preserve">8.41200637817383</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49999713897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34161186218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23602104187012</t>
+    <t xml:space="preserve">8.49999809265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34161376953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23602199554443</t>
   </si>
   <si>
     <t xml:space="preserve">8.30641555786133</t>
@@ -1028,13 +1025,13 @@
     <t xml:space="preserve">8.1832275390625</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16562938690186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21842384338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25362205505371</t>
+    <t xml:space="preserve">8.16562843322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21842479705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25362014770508</t>
   </si>
   <si>
     <t xml:space="preserve">8.37681007385254</t>
@@ -1049,22 +1046,22 @@
     <t xml:space="preserve">9.41511154174805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63509178161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59109401702881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89906597137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1190452575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1630401611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2070360183716</t>
+    <t xml:space="preserve">9.63508987426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59109497070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8990650177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.119044303894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1630411148071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2070369720459</t>
   </si>
   <si>
     <t xml:space="preserve">10.3390245437622</t>
@@ -1073,16 +1070,16 @@
     <t xml:space="preserve">10.2950286865234</t>
   </si>
   <si>
-    <t xml:space="preserve">10.383020401001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2510318756104</t>
+    <t xml:space="preserve">10.3830194473267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2510328292847</t>
   </si>
   <si>
     <t xml:space="preserve">10.4270162582397</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0750494003296</t>
+    <t xml:space="preserve">10.0750484466553</t>
   </si>
   <si>
     <t xml:space="preserve">10.515007019043</t>
@@ -1091,52 +1088,55 @@
     <t xml:space="preserve">10.6498155593872</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4700708389282</t>
+    <t xml:space="preserve">10.4700717926025</t>
   </si>
   <si>
     <t xml:space="preserve">10.694751739502</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6048793792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3802003860474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2453908920288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0656490325928</t>
+    <t xml:space="preserve">10.6048803329468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.380199432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2453918457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0656471252441</t>
   </si>
   <si>
     <t xml:space="preserve">10.4251365661621</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3352642059326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2903270721436</t>
+    <t xml:space="preserve">10.5150089263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3352651596069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2903289794922</t>
   </si>
   <si>
     <t xml:space="preserve">10.200457572937</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97577857971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1105852127075</t>
+    <t xml:space="preserve">9.97577667236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1105842590332</t>
   </si>
   <si>
     <t xml:space="preserve">9.93084049224854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88590526580811</t>
+    <t xml:space="preserve">9.88590431213379</t>
   </si>
   <si>
     <t xml:space="preserve">10.1555204391479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0207109451294</t>
+    <t xml:space="preserve">10.020712852478</t>
   </si>
   <si>
     <t xml:space="preserve">9.75109767913818</t>
@@ -1145,16 +1145,16 @@
     <t xml:space="preserve">9.70616149902344</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34667205810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30173873901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39160919189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48148059844971</t>
+    <t xml:space="preserve">9.34667301177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30173778533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39160823822021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48148155212402</t>
   </si>
   <si>
     <t xml:space="preserve">9.61628913879395</t>
@@ -1166,31 +1166,31 @@
     <t xml:space="preserve">9.43654537200928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12199211120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03212261199951</t>
+    <t xml:space="preserve">9.12199306488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03212356567383</t>
   </si>
   <si>
     <t xml:space="preserve">9.16693019866943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07705974578857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25680160522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98718547821045</t>
+    <t xml:space="preserve">9.07705783843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25680065155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98718643188477</t>
   </si>
   <si>
     <t xml:space="preserve">9.5713529586792</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66122627258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7960319519043</t>
+    <t xml:space="preserve">9.66122531890869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79603290557861</t>
   </si>
   <si>
     <t xml:space="preserve">10.9643669128418</t>
@@ -1202,7 +1202,7 @@
     <t xml:space="preserve">11.5035982131958</t>
   </si>
   <si>
-    <t xml:space="preserve">11.233983039856</t>
+    <t xml:space="preserve">11.2339820861816</t>
   </si>
   <si>
     <t xml:space="preserve">11.1441106796265</t>
@@ -1211,7 +1211,7 @@
     <t xml:space="preserve">10.9194307327271</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8744974136353</t>
+    <t xml:space="preserve">10.8744964599609</t>
   </si>
   <si>
     <t xml:space="preserve">11.0093040466309</t>
@@ -1220,118 +1220,118 @@
     <t xml:space="preserve">11.2789192199707</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4137258529663</t>
+    <t xml:space="preserve">11.413724899292</t>
   </si>
   <si>
     <t xml:space="preserve">11.5485343933105</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6833429336548</t>
+    <t xml:space="preserve">11.6833419799805</t>
   </si>
   <si>
     <t xml:space="preserve">11.7732152938843</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9080228805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.132700920105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9978942871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8181505203247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.593469619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3124446868896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5820608139038</t>
+    <t xml:space="preserve">11.9080209732056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1327018737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9978933334351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8181486129761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5934705734253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.312445640564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5820598602295</t>
   </si>
   <si>
     <t xml:space="preserve">12.9415483474731</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8067398071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7618026733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0763568878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4472532272339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5371236801147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2675085067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4023180007935</t>
+    <t xml:space="preserve">12.8067407608032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7618036270142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0763559341431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4472541809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5371246337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2675094604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4023160934448</t>
   </si>
   <si>
     <t xml:space="preserve">12.6269969940186</t>
   </si>
   <si>
-    <t xml:space="preserve">12.671932220459</t>
+    <t xml:space="preserve">12.6719312667847</t>
   </si>
   <si>
     <t xml:space="preserve">12.8966131210327</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7282772064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7846240997314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.559944152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89731311798096</t>
+    <t xml:space="preserve">11.7282781600952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7846231460571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5599422454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89731502532959</t>
   </si>
   <si>
     <t xml:space="preserve">7.98062086105347</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81885194778442</t>
+    <t xml:space="preserve">7.81885147094727</t>
   </si>
   <si>
     <t xml:space="preserve">7.53126239776611</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89074850082397</t>
+    <t xml:space="preserve">7.89074897766113</t>
   </si>
   <si>
     <t xml:space="preserve">8.53782653808594</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96264696121216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44795417785645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6097240447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66364860534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86136531829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21186447143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93848991394043</t>
+    <t xml:space="preserve">7.962646484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44795513153076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60972499847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66364765167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86136627197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21186637878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93848896026611</t>
   </si>
   <si>
     <t xml:space="preserve">9.80045509338379</t>
@@ -1340,10 +1340,10 @@
     <t xml:space="preserve">9.89247798919678</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66242027282715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70843124389648</t>
+    <t xml:space="preserve">9.66242122650146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7084321975708</t>
   </si>
   <si>
     <t xml:space="preserve">9.84646606445312</t>
@@ -1364,13 +1364,13 @@
     <t xml:space="preserve">10.720685005188</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5826511383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8587198257446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.674674987793</t>
+    <t xml:space="preserve">10.582649230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8587207794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6746730804443</t>
   </si>
   <si>
     <t xml:space="preserve">10.9967546463013</t>
@@ -1379,19 +1379,19 @@
     <t xml:space="preserve">10.628662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7666969299316</t>
+    <t xml:space="preserve">10.766697883606</t>
   </si>
   <si>
     <t xml:space="preserve">10.4906272888184</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1347894668579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3188362121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5028820037842</t>
+    <t xml:space="preserve">11.1347904205322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3188352584839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5028810501099</t>
   </si>
   <si>
     <t xml:space="preserve">11.1808004379272</t>
@@ -1403,16 +1403,16 @@
     <t xml:space="preserve">11.2728233337402</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9507417678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0887775421143</t>
+    <t xml:space="preserve">10.9507427215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0887784957886</t>
   </si>
   <si>
     <t xml:space="preserve">10.8127088546753</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9047327041626</t>
+    <t xml:space="preserve">10.904730796814</t>
   </si>
   <si>
     <t xml:space="preserve">11.4108581542969</t>
@@ -1421,22 +1421,22 @@
     <t xml:space="preserve">11.4568700790405</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2268123626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3648462295532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5488920211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5949048995972</t>
+    <t xml:space="preserve">11.2268114089966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3648471832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5488929748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5949039459229</t>
   </si>
   <si>
     <t xml:space="preserve">11.6869268417358</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9629964828491</t>
+    <t xml:space="preserve">11.9629974365234</t>
   </si>
   <si>
     <t xml:space="preserve">11.7789506912231</t>
@@ -1445,7 +1445,7 @@
     <t xml:space="preserve">12.0090084075928</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1010313034058</t>
+    <t xml:space="preserve">12.1010303497314</t>
   </si>
   <si>
     <t xml:space="preserve">11.7329397201538</t>
@@ -1454,13 +1454,13 @@
     <t xml:space="preserve">11.8249626159668</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0550193786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8709735870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9169845581055</t>
+    <t xml:space="preserve">12.0550203323364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8709726333618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9169855117798</t>
   </si>
   <si>
     <t xml:space="preserve">11.6409158706665</t>
@@ -1472,13 +1472,13 @@
     <t xml:space="preserve">12.6991815567017</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7912034988403</t>
+    <t xml:space="preserve">12.791202545166</t>
   </si>
   <si>
     <t xml:space="preserve">13.0672731399536</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8832273483276</t>
+    <t xml:space="preserve">12.8832263946533</t>
   </si>
   <si>
     <t xml:space="preserve">12.9292392730713</t>
@@ -1487,19 +1487,19 @@
     <t xml:space="preserve">13.2053079605103</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2513189315796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1132850646973</t>
+    <t xml:space="preserve">13.2513198852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1132841110229</t>
   </si>
   <si>
     <t xml:space="preserve">13.1592969894409</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3893547058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2973299026489</t>
+    <t xml:space="preserve">13.3893537521362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2973308563232</t>
   </si>
   <si>
     <t xml:space="preserve">12.9752502441406</t>
@@ -1514,7 +1514,7 @@
     <t xml:space="preserve">12.5151348114014</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3770990371704</t>
+    <t xml:space="preserve">12.3770999908447</t>
   </si>
   <si>
     <t xml:space="preserve">12.837215423584</t>
@@ -1523,46 +1523,46 @@
     <t xml:space="preserve">12.7451934814453</t>
   </si>
   <si>
-    <t xml:space="preserve">12.653169631958</t>
+    <t xml:space="preserve">12.6531705856323</t>
   </si>
   <si>
     <t xml:space="preserve">13.3433437347412</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6194124221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8494701385498</t>
+    <t xml:space="preserve">13.6194114685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8494691848755</t>
   </si>
   <si>
     <t xml:space="preserve">13.9414920806885</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1715507507324</t>
+    <t xml:space="preserve">14.1715497970581</t>
   </si>
   <si>
     <t xml:space="preserve">14.3555955886841</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1255388259888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4936294555664</t>
+    <t xml:space="preserve">14.1255397796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4936304092407</t>
   </si>
   <si>
     <t xml:space="preserve">14.7236881256104</t>
   </si>
   <si>
-    <t xml:space="preserve">14.677677154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.815710067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.861722946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.045768737793</t>
+    <t xml:space="preserve">14.6776762008667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8157119750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8617238998413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0457677841187</t>
   </si>
   <si>
     <t xml:space="preserve">14.5396423339844</t>
@@ -1571,7 +1571,7 @@
     <t xml:space="preserve">14.6316652297974</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4476203918457</t>
+    <t xml:space="preserve">14.4476194381714</t>
   </si>
   <si>
     <t xml:space="preserve">14.2635726928711</t>
@@ -1580,7 +1580,7 @@
     <t xml:space="preserve">13.9875040054321</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3095855712891</t>
+    <t xml:space="preserve">14.3095846176147</t>
   </si>
   <si>
     <t xml:space="preserve">13.6654243469238</t>
@@ -1595,13 +1595,13 @@
     <t xml:space="preserve">13.7574462890625</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9537448883057</t>
+    <t xml:space="preserve">14.95374584198</t>
   </si>
   <si>
     <t xml:space="preserve">14.0335149765015</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4269781112671</t>
+    <t xml:space="preserve">14.4269771575928</t>
   </si>
   <si>
     <t xml:space="preserve">14.3801383972168</t>
@@ -1616,13 +1616,13 @@
     <t xml:space="preserve">14.8485450744629</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0359086990356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0827493667603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8953866958618</t>
+    <t xml:space="preserve">15.03590965271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0827503204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8953857421875</t>
   </si>
   <si>
     <t xml:space="preserve">14.9422273635864</t>
@@ -1640,10 +1640,10 @@
     <t xml:space="preserve">14.6611814498901</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3169546127319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7548627853394</t>
+    <t xml:space="preserve">15.3169536590576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7548637390137</t>
   </si>
   <si>
     <t xml:space="preserve">14.8017053604126</t>
@@ -1652,31 +1652,31 @@
     <t xml:space="preserve">15.2232723236084</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5043163299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0664081573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6916809082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7385215759277</t>
+    <t xml:space="preserve">15.5043153762817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0664100646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6916818618774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7385206222534</t>
   </si>
   <si>
     <t xml:space="preserve">15.9727249145508</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9258842468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.785364151001</t>
+    <t xml:space="preserve">15.9258861541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7853631973267</t>
   </si>
   <si>
     <t xml:space="preserve">16.1132488250732</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8322038650513</t>
+    <t xml:space="preserve">15.8322019577026</t>
   </si>
   <si>
     <t xml:space="preserve">16.5348148345947</t>
@@ -1694,43 +1694,43 @@
     <t xml:space="preserve">16.2069301605225</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2842693328857</t>
+    <t xml:space="preserve">17.2842712402344</t>
   </si>
   <si>
     <t xml:space="preserve">17.7995185852051</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4716339111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.815860748291</t>
+    <t xml:space="preserve">17.4716320037842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8158626556396</t>
   </si>
   <si>
     <t xml:space="preserve">16.6284980773926</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0969047546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5184726715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6121559143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0337219238281</t>
+    <t xml:space="preserve">17.0969066619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5184764862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.612154006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0337238311768</t>
   </si>
   <si>
     <t xml:space="preserve">18.5489711761475</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7363338470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9237003326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7668323516846</t>
+    <t xml:space="preserve">18.7363357543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.923698425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7668342590332</t>
   </si>
   <si>
     <t xml:space="preserve">19.5794696807861</t>
@@ -1739,19 +1739,19 @@
     <t xml:space="preserve">19.2047443389893</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1110610961914</t>
+    <t xml:space="preserve">19.1110591888428</t>
   </si>
   <si>
     <t xml:space="preserve">19.673152923584</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2984237670898</t>
+    <t xml:space="preserve">19.2984256744385</t>
   </si>
   <si>
     <t xml:space="preserve">19.4857883453369</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8605175018311</t>
+    <t xml:space="preserve">19.8605155944824</t>
   </si>
   <si>
     <t xml:space="preserve">20.3289241790771</t>
@@ -1760,10 +1760,10 @@
     <t xml:space="preserve">20.9846954345703</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2657413482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0783786773682</t>
+    <t xml:space="preserve">21.2657432556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0783767700195</t>
   </si>
   <si>
     <t xml:space="preserve">21.453104019165</t>
@@ -1772,13 +1772,13 @@
     <t xml:space="preserve">20.7973327636719</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8278312683105</t>
+    <t xml:space="preserve">21.8278293609619</t>
   </si>
   <si>
     <t xml:space="preserve">22.1088771820068</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7341499328613</t>
+    <t xml:space="preserve">21.7341480255127</t>
   </si>
   <si>
     <t xml:space="preserve">22.015193939209</t>
@@ -1790,10 +1790,10 @@
     <t xml:space="preserve">22.4836025238037</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6404666900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5467853546143</t>
+    <t xml:space="preserve">21.6404685974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5467834472656</t>
   </si>
   <si>
     <t xml:space="preserve">20.2352428436279</t>
@@ -1802,13 +1802,13 @@
     <t xml:space="preserve">18.3147678375244</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0173797607422</t>
+    <t xml:space="preserve">19.0173816680908</t>
   </si>
   <si>
     <t xml:space="preserve">20.6099681854248</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9215106964111</t>
+    <t xml:space="preserve">21.9215145111084</t>
   </si>
   <si>
     <t xml:space="preserve">22.7646465301514</t>
@@ -1823,7 +1823,7 @@
     <t xml:space="preserve">20.703649520874</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3594207763672</t>
+    <t xml:space="preserve">21.3594188690186</t>
   </si>
   <si>
     <t xml:space="preserve">20.5162868499756</t>
@@ -1835,7 +1835,7 @@
     <t xml:space="preserve">22.6709671020508</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2025585174561</t>
+    <t xml:space="preserve">22.2025566101074</t>
   </si>
   <si>
     <t xml:space="preserve">22.3899211883545</t>
@@ -1844,10 +1844,10 @@
     <t xml:space="preserve">19.9541969299316</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4226036071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8910121917725</t>
+    <t xml:space="preserve">20.4226055145264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8910140991211</t>
   </si>
   <si>
     <t xml:space="preserve">19.3921070098877</t>
@@ -1859,19 +1859,19 @@
     <t xml:space="preserve">18.361608505249</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9563846588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6589984893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7526760101318</t>
+    <t xml:space="preserve">16.9563827514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6589946746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7526779174805</t>
   </si>
   <si>
     <t xml:space="preserve">17.377950668335</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8932018280029</t>
+    <t xml:space="preserve">17.8931999206543</t>
   </si>
   <si>
     <t xml:space="preserve">17.9400405883789</t>
@@ -1883,43 +1883,43 @@
     <t xml:space="preserve">18.8768577575684</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6426544189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3241348266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2117195129395</t>
+    <t xml:space="preserve">18.6426525115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3241367340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2117176055908</t>
   </si>
   <si>
     <t xml:space="preserve">18.2304534912109</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4552898406982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9494113922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.118034362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9705390930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2820816040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0947208404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1884002685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1415615081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4927616119385</t>
+    <t xml:space="preserve">18.4552879333496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9494094848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1180362701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9705410003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2820835113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0947189331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1884021759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1415596008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4927635192871</t>
   </si>
   <si>
     <t xml:space="preserve">17.5559463500977</t>
@@ -1931,13 +1931,13 @@
     <t xml:space="preserve">16.8847980499268</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7634181976318</t>
+    <t xml:space="preserve">17.7634201049805</t>
   </si>
   <si>
     <t xml:space="preserve">18.0308246612549</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9285449981689</t>
+    <t xml:space="preserve">18.9285469055176</t>
   </si>
   <si>
     <t xml:space="preserve">18.4319343566895</t>
@@ -1964,7 +1964,7 @@
     <t xml:space="preserve">20.0077228546143</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0554714202881</t>
+    <t xml:space="preserve">20.0554752349854</t>
   </si>
   <si>
     <t xml:space="preserve">20.5329856872559</t>
@@ -1973,16 +1973,16 @@
     <t xml:space="preserve">20.9149932861328</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1509761810303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4374828338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0104942321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4880084991455</t>
+    <t xml:space="preserve">20.1509742736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4374809265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0104961395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4880065917969</t>
   </si>
   <si>
     <t xml:space="preserve">19.5779628753662</t>
@@ -1997,7 +1997,7 @@
     <t xml:space="preserve">19.2914562225342</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3392066955566</t>
+    <t xml:space="preserve">19.339204788208</t>
   </si>
   <si>
     <t xml:space="preserve">18.813943862915</t>
@@ -2024,7 +2024,7 @@
     <t xml:space="preserve">19.9599704742432</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4852333068848</t>
+    <t xml:space="preserve">20.4852352142334</t>
   </si>
   <si>
     <t xml:space="preserve">21.1059970855713</t>
@@ -2033,37 +2033,37 @@
     <t xml:space="preserve">21.8700160980225</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3925037384033</t>
+    <t xml:space="preserve">21.392505645752</t>
   </si>
   <si>
     <t xml:space="preserve">21.1537494659424</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7745113372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6790103912354</t>
+    <t xml:space="preserve">21.7745132446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.679012298584</t>
   </si>
   <si>
     <t xml:space="preserve">21.9177684783936</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2970008850098</t>
+    <t xml:space="preserve">21.2970027923584</t>
   </si>
   <si>
     <t xml:space="preserve">21.7267627716064</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5835113525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5807342529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1032238006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6257133483887</t>
+    <t xml:space="preserve">21.5835094451904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5807323455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1032218933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.62571144104</t>
   </si>
   <si>
     <t xml:space="preserve">19.8644676208496</t>
@@ -2084,19 +2084,19 @@
     <t xml:space="preserve">22.0610198974609</t>
   </si>
   <si>
-    <t xml:space="preserve">22.347526550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0582466125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3897304534912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2942295074463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1987247467041</t>
+    <t xml:space="preserve">22.3475284576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0582447052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3897323608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2942276000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1987266540527</t>
   </si>
   <si>
     <t xml:space="preserve">20.8194904327393</t>
@@ -2105,7 +2105,7 @@
     <t xml:space="preserve">20.8672428131104</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0499248504639</t>
+    <t xml:space="preserve">18.0499267578125</t>
   </si>
   <si>
     <t xml:space="preserve">18.833044052124</t>
@@ -2120,7 +2120,7 @@
     <t xml:space="preserve">19.8167171478271</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2464790344238</t>
+    <t xml:space="preserve">20.2464771270752</t>
   </si>
   <si>
     <t xml:space="preserve">20.6762371063232</t>
@@ -2129,7 +2129,7 @@
     <t xml:space="preserve">19.7689666748047</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4402561187744</t>
+    <t xml:space="preserve">21.440258026123</t>
   </si>
   <si>
     <t xml:space="preserve">22.6340351104736</t>
@@ -2141,28 +2141,28 @@
     <t xml:space="preserve">22.7295341491699</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5862827301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8727912902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5385341644287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6817836761475</t>
+    <t xml:space="preserve">22.5862808227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8727893829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5385303497314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6817855834961</t>
   </si>
   <si>
     <t xml:space="preserve">23.0160427093506</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3025493621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4485778808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7323093414307</t>
+    <t xml:space="preserve">23.3025512695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4485759735107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7323112487793</t>
   </si>
   <si>
     <t xml:space="preserve">23.9710655212402</t>
@@ -2171,16 +2171,16 @@
     <t xml:space="preserve">24.2098217010498</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0665683746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1143207550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4008235931396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3080959320068</t>
+    <t xml:space="preserve">24.0665664672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1143188476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4008255004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3080978393555</t>
   </si>
   <si>
     <t xml:space="preserve">23.7800598144531</t>
@@ -2192,22 +2192,22 @@
     <t xml:space="preserve">25.0693416595459</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5440807342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9260864257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3558464050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.403600692749</t>
+    <t xml:space="preserve">24.5440788269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9260883331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3558483123779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4035987854004</t>
   </si>
   <si>
     <t xml:space="preserve">25.8333587646484</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8838844299316</t>
+    <t xml:space="preserve">26.883882522583</t>
   </si>
   <si>
     <t xml:space="preserve">26.7883815765381</t>
@@ -2219,40 +2219,40 @@
     <t xml:space="preserve">24.5918292999268</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8305854797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2603454589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7378578186035</t>
+    <t xml:space="preserve">24.830587387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.260347366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7378597259521</t>
   </si>
   <si>
     <t xml:space="preserve">25.785608291626</t>
   </si>
   <si>
-    <t xml:space="preserve">26.072114944458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2631187438965</t>
+    <t xml:space="preserve">26.0721130371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2631206512451</t>
   </si>
   <si>
     <t xml:space="preserve">25.4513492584229</t>
   </si>
   <si>
-    <t xml:space="preserve">25.928861618042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5946025848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6901073455811</t>
+    <t xml:space="preserve">25.9288597106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5946044921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6901054382324</t>
   </si>
   <si>
     <t xml:space="preserve">25.5468521118164</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4541263580322</t>
+    <t xml:space="preserve">26.4541244506836</t>
   </si>
   <si>
     <t xml:space="preserve">26.7406311035156</t>
@@ -2264,13 +2264,13 @@
     <t xml:space="preserve">27.1703910827637</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6506767272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.321964263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.892204284668</t>
+    <t xml:space="preserve">28.6506748199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3219661712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8922023773193</t>
   </si>
   <si>
     <t xml:space="preserve">29.9877071380615</t>
@@ -2279,7 +2279,7 @@
     <t xml:space="preserve">30.1309604644775</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6534481048584</t>
+    <t xml:space="preserve">29.653450012207</t>
   </si>
   <si>
     <t xml:space="preserve">29.510196685791</t>
@@ -2288,7 +2288,7 @@
     <t xml:space="preserve">28.5074214935303</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3191928863525</t>
+    <t xml:space="preserve">29.3191909790039</t>
   </si>
   <si>
     <t xml:space="preserve">28.9371814727783</t>
@@ -2297,25 +2297,25 @@
     <t xml:space="preserve">28.8416805267334</t>
   </si>
   <si>
-    <t xml:space="preserve">29.223690032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1281852722168</t>
+    <t xml:space="preserve">29.2236919403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1281871795654</t>
   </si>
   <si>
     <t xml:space="preserve">29.1759376525879</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0804386138916</t>
+    <t xml:space="preserve">29.080436706543</t>
   </si>
   <si>
     <t xml:space="preserve">28.6984272003174</t>
   </si>
   <si>
-    <t xml:space="preserve">28.984935760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3641700744629</t>
+    <t xml:space="preserve">28.9849338531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3641681671143</t>
   </si>
   <si>
     <t xml:space="preserve">27.8866577148438</t>
@@ -2330,7 +2330,7 @@
     <t xml:space="preserve">27.6479034423828</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6029243469238</t>
+    <t xml:space="preserve">28.6029262542725</t>
   </si>
   <si>
     <t xml:space="preserve">28.4119205474854</t>
@@ -2342,25 +2342,25 @@
     <t xml:space="preserve">29.4146938323975</t>
   </si>
   <si>
-    <t xml:space="preserve">30.0354614257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.748950958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7039756774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2742156982422</t>
+    <t xml:space="preserve">30.0354595184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7489490509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7039737701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2742137908936</t>
   </si>
   <si>
     <t xml:space="preserve">29.7012023925781</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5579471588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7967014312744</t>
+    <t xml:space="preserve">29.5579490661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.796703338623</t>
   </si>
   <si>
     <t xml:space="preserve">28.2209148406982</t>
@@ -3432,6 +3432,9 @@
   </si>
   <si>
     <t xml:space="preserve">39.0499992370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.4500007629395</t>
   </si>
 </sst>
 </file>
@@ -13954,7 +13957,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G392" t="s">
-        <v>203</v>
+        <v>164</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -13980,7 +13983,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G393" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -14006,7 +14009,7 @@
         <v>13.1899995803833</v>
       </c>
       <c r="G394" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -14032,7 +14035,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G395" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -14058,7 +14061,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G396" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -14084,7 +14087,7 @@
         <v>13</v>
       </c>
       <c r="G397" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -14110,7 +14113,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G398" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -14136,7 +14139,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G399" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -14162,7 +14165,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G400" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -14188,7 +14191,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G401" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -14214,7 +14217,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G402" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -14240,7 +14243,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G403" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -14266,7 +14269,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G404" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -14292,7 +14295,7 @@
         <v>13</v>
       </c>
       <c r="G405" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -14318,7 +14321,7 @@
         <v>13</v>
       </c>
       <c r="G406" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -14344,7 +14347,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G407" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -14370,7 +14373,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G408" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -14396,7 +14399,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G409" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -14422,7 +14425,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G410" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -14448,7 +14451,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G411" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -14474,7 +14477,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G412" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -14500,7 +14503,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G413" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -14526,7 +14529,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G414" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -14552,7 +14555,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G415" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -14578,7 +14581,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G416" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -14604,7 +14607,7 @@
         <v>13.3800001144409</v>
       </c>
       <c r="G417" t="s">
-        <v>203</v>
+        <v>164</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -14630,7 +14633,7 @@
         <v>13.25</v>
       </c>
       <c r="G418" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -14656,7 +14659,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G419" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -14682,7 +14685,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G420" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -14708,7 +14711,7 @@
         <v>13</v>
       </c>
       <c r="G421" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -14734,7 +14737,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G422" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -14760,7 +14763,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G423" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -14786,7 +14789,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G424" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -14812,7 +14815,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G425" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -14838,7 +14841,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G426" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -14864,7 +14867,7 @@
         <v>13.0100002288818</v>
       </c>
       <c r="G427" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -14890,7 +14893,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G428" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -14916,7 +14919,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G429" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -14942,7 +14945,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G430" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -14968,7 +14971,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G431" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -14994,7 +14997,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G432" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -15020,7 +15023,7 @@
         <v>13.1700000762939</v>
       </c>
       <c r="G433" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -15046,7 +15049,7 @@
         <v>13</v>
       </c>
       <c r="G434" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -15072,7 +15075,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G435" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -15098,7 +15101,7 @@
         <v>12.7299995422363</v>
       </c>
       <c r="G436" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -15124,7 +15127,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G437" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -15150,7 +15153,7 @@
         <v>13.1999998092651</v>
       </c>
       <c r="G438" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -15176,7 +15179,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G439" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -15202,7 +15205,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G440" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -15228,7 +15231,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G441" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -15254,7 +15257,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G442" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -15280,7 +15283,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G443" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -15306,7 +15309,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G444" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -15332,7 +15335,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G445" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -15358,7 +15361,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G446" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -15384,7 +15387,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G447" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -15410,7 +15413,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G448" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -15436,7 +15439,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G449" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -15462,7 +15465,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G450" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -15488,7 +15491,7 @@
         <v>11.25</v>
       </c>
       <c r="G451" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -15514,7 +15517,7 @@
         <v>11.1099996566772</v>
       </c>
       <c r="G452" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -15540,7 +15543,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G453" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -15566,7 +15569,7 @@
         <v>11.25</v>
       </c>
       <c r="G454" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -15592,7 +15595,7 @@
         <v>10.9099998474121</v>
       </c>
       <c r="G455" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -15618,7 +15621,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G456" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -15644,7 +15647,7 @@
         <v>10.75</v>
       </c>
       <c r="G457" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -15670,7 +15673,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G458" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -15696,7 +15699,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G459" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -15722,7 +15725,7 @@
         <v>10.9300003051758</v>
       </c>
       <c r="G460" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -15748,7 +15751,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G461" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -15774,7 +15777,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G462" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -15800,7 +15803,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G463" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -15826,7 +15829,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G464" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -15852,7 +15855,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G465" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -15878,7 +15881,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G466" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -15904,7 +15907,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G467" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -15930,7 +15933,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G468" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -15956,7 +15959,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G469" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -15982,7 +15985,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G470" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -16008,7 +16011,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G471" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -16034,7 +16037,7 @@
         <v>11.2299995422363</v>
       </c>
       <c r="G472" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -16060,7 +16063,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G473" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -16086,7 +16089,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G474" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -16112,7 +16115,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G475" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -16138,7 +16141,7 @@
         <v>10.6899995803833</v>
       </c>
       <c r="G476" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -16164,7 +16167,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G477" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -16190,7 +16193,7 @@
         <v>10.7299995422363</v>
       </c>
       <c r="G478" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -16216,7 +16219,7 @@
         <v>10.75</v>
       </c>
       <c r="G479" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -16242,7 +16245,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G480" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -16268,7 +16271,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G481" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -16294,7 +16297,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G482" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -16320,7 +16323,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G483" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -16346,7 +16349,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G484" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -16372,7 +16375,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G485" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -16398,7 +16401,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G486" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -16424,7 +16427,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G487" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -16450,7 +16453,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G488" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -16476,7 +16479,7 @@
         <v>11.5</v>
       </c>
       <c r="G489" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -16502,7 +16505,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G490" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -16528,7 +16531,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G491" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -16554,7 +16557,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G492" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -16580,7 +16583,7 @@
         <v>11.0699996948242</v>
       </c>
       <c r="G493" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -16606,7 +16609,7 @@
         <v>11.2299995422363</v>
       </c>
       <c r="G494" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -16632,7 +16635,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G495" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -16658,7 +16661,7 @@
         <v>10.9300003051758</v>
       </c>
       <c r="G496" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -16684,7 +16687,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G497" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -16710,7 +16713,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G498" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -16736,7 +16739,7 @@
         <v>11.25</v>
       </c>
       <c r="G499" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -16762,7 +16765,7 @@
         <v>11.1300001144409</v>
       </c>
       <c r="G500" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -16788,7 +16791,7 @@
         <v>11</v>
       </c>
       <c r="G501" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -16814,7 +16817,7 @@
         <v>11.0699996948242</v>
       </c>
       <c r="G502" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -16840,7 +16843,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G503" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -16866,7 +16869,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G504" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -16892,7 +16895,7 @@
         <v>11</v>
       </c>
       <c r="G505" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -16918,7 +16921,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G506" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -16944,7 +16947,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G507" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -16970,7 +16973,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G508" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -16996,7 +16999,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G509" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -17022,7 +17025,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G510" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -17048,7 +17051,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G511" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -17074,7 +17077,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G512" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -17100,7 +17103,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G513" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -17126,7 +17129,7 @@
         <v>10.75</v>
       </c>
       <c r="G514" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -17152,7 +17155,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G515" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -17178,7 +17181,7 @@
         <v>10.75</v>
       </c>
       <c r="G516" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -17204,7 +17207,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G517" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -17230,7 +17233,7 @@
         <v>11</v>
       </c>
       <c r="G518" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -17256,7 +17259,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G519" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -17282,7 +17285,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G520" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -17308,7 +17311,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G521" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -17334,7 +17337,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G522" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -17360,7 +17363,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G523" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -17386,7 +17389,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G524" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -17412,7 +17415,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G525" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -17438,7 +17441,7 @@
         <v>11.25</v>
       </c>
       <c r="G526" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -17464,7 +17467,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G527" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -17490,7 +17493,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G528" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -17516,7 +17519,7 @@
         <v>11.25</v>
       </c>
       <c r="G529" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -17542,7 +17545,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G530" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -17568,7 +17571,7 @@
         <v>11.5</v>
       </c>
       <c r="G531" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -17594,7 +17597,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G532" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -17620,7 +17623,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G533" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -17646,7 +17649,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G534" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -17672,7 +17675,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G535" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -17698,7 +17701,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G536" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -17724,7 +17727,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G537" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -17750,7 +17753,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G538" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -17776,7 +17779,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G539" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -17802,7 +17805,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G540" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -17828,7 +17831,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G541" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -17854,7 +17857,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G542" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -17880,7 +17883,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G543" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -17906,7 +17909,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G544" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -17932,7 +17935,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G545" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -17958,7 +17961,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G546" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -17984,7 +17987,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G547" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -18010,7 +18013,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G548" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -18036,7 +18039,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G549" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -18062,7 +18065,7 @@
         <v>10.5</v>
       </c>
       <c r="G550" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -18088,7 +18091,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G551" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -18114,7 +18117,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G552" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -18140,7 +18143,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G553" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -18166,7 +18169,7 @@
         <v>10.25</v>
       </c>
       <c r="G554" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -18192,7 +18195,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G555" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -18218,7 +18221,7 @@
         <v>10.25</v>
       </c>
       <c r="G556" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -18244,7 +18247,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G557" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -18270,7 +18273,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G558" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -18296,7 +18299,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G559" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -18322,7 +18325,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G560" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -18348,7 +18351,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G561" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -18374,7 +18377,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G562" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -18400,7 +18403,7 @@
         <v>10.5</v>
       </c>
       <c r="G563" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -18426,7 +18429,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G564" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -18452,7 +18455,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G565" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -18478,7 +18481,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G566" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -18504,7 +18507,7 @@
         <v>10.25</v>
       </c>
       <c r="G567" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -18530,7 +18533,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G568" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -18556,7 +18559,7 @@
         <v>10.25</v>
       </c>
       <c r="G569" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -18582,7 +18585,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G570" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -18608,7 +18611,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G571" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -18634,7 +18637,7 @@
         <v>10</v>
       </c>
       <c r="G572" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -18660,7 +18663,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G573" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -18686,7 +18689,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G574" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -18712,7 +18715,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G575" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -18738,7 +18741,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G576" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -18764,7 +18767,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G577" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -18790,7 +18793,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G578" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -18816,7 +18819,7 @@
         <v>10</v>
       </c>
       <c r="G579" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -18842,7 +18845,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G580" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -18868,7 +18871,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G581" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -18894,7 +18897,7 @@
         <v>10.25</v>
       </c>
       <c r="G582" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -18920,7 +18923,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G583" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -18946,7 +18949,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G584" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -18972,7 +18975,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G585" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -18998,7 +19001,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G586" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -19024,7 +19027,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G587" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -19050,7 +19053,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G588" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -19076,7 +19079,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G589" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -19102,7 +19105,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G590" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -19128,7 +19131,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G591" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -19154,7 +19157,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G592" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -19180,7 +19183,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G593" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -19206,7 +19209,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G594" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -19232,7 +19235,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G595" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -19258,7 +19261,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G596" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -19284,7 +19287,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G597" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -19310,7 +19313,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G598" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -19336,7 +19339,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G599" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -19362,7 +19365,7 @@
         <v>10.25</v>
       </c>
       <c r="G600" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -19388,7 +19391,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G601" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -19414,7 +19417,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G602" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -19440,7 +19443,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G603" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -19466,7 +19469,7 @@
         <v>10.25</v>
       </c>
       <c r="G604" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -19492,7 +19495,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G605" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -19518,7 +19521,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G606" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -19544,7 +19547,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G607" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -19570,7 +19573,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G608" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19596,7 +19599,7 @@
         <v>10.25</v>
       </c>
       <c r="G609" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19622,7 +19625,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G610" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19648,7 +19651,7 @@
         <v>10.25</v>
       </c>
       <c r="G611" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19674,7 +19677,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G612" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19700,7 +19703,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G613" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19726,7 +19729,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G614" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19752,7 +19755,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G615" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19778,7 +19781,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G616" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19804,7 +19807,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G617" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19830,7 +19833,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G618" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19856,7 +19859,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G619" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19882,7 +19885,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G620" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19908,7 +19911,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G621" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19934,7 +19937,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G622" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19960,7 +19963,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G623" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19986,7 +19989,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G624" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -20012,7 +20015,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G625" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -20038,7 +20041,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G626" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -20064,7 +20067,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G627" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -20090,7 +20093,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G628" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -20116,7 +20119,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G629" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -20142,7 +20145,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G630" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -20168,7 +20171,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G631" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -20194,7 +20197,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G632" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -20220,7 +20223,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G633" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -20246,7 +20249,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G634" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -20272,7 +20275,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G635" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -20298,7 +20301,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G636" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -20324,7 +20327,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G637" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -20350,7 +20353,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G638" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -20376,7 +20379,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G639" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -20402,7 +20405,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G640" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -20428,7 +20431,7 @@
         <v>10</v>
       </c>
       <c r="G641" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -20454,7 +20457,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G642" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -20480,7 +20483,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G643" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -20506,7 +20509,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G644" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -20532,7 +20535,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G645" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -20558,7 +20561,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G646" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -20584,7 +20587,7 @@
         <v>10</v>
       </c>
       <c r="G647" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -20610,7 +20613,7 @@
         <v>10</v>
       </c>
       <c r="G648" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -20636,7 +20639,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G649" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -20662,7 +20665,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G650" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -20688,7 +20691,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G651" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -20714,7 +20717,7 @@
         <v>10</v>
       </c>
       <c r="G652" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -20740,7 +20743,7 @@
         <v>10</v>
       </c>
       <c r="G653" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -20766,7 +20769,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G654" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -20792,7 +20795,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G655" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -20818,7 +20821,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G656" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -20844,7 +20847,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G657" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -20870,7 +20873,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G658" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -20896,7 +20899,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G659" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -20922,7 +20925,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G660" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -20948,7 +20951,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G661" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -20974,7 +20977,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G662" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -21000,7 +21003,7 @@
         <v>10</v>
       </c>
       <c r="G663" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -21026,7 +21029,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G664" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -21052,7 +21055,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G665" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -21078,7 +21081,7 @@
         <v>10.25</v>
       </c>
       <c r="G666" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -21104,7 +21107,7 @@
         <v>10</v>
       </c>
       <c r="G667" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -21130,7 +21133,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G668" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -21156,7 +21159,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G669" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -21182,7 +21185,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G670" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -21208,7 +21211,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G671" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -21234,7 +21237,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G672" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -21260,7 +21263,7 @@
         <v>10</v>
       </c>
       <c r="G673" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -21286,7 +21289,7 @@
         <v>10</v>
       </c>
       <c r="G674" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -21312,7 +21315,7 @@
         <v>10</v>
       </c>
       <c r="G675" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -21338,7 +21341,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G676" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -21364,7 +21367,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G677" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -21390,7 +21393,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G678" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -21416,7 +21419,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G679" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -21442,7 +21445,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G680" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -21468,7 +21471,7 @@
         <v>9.81999969482422</v>
       </c>
       <c r="G681" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -21494,7 +21497,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G682" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -21520,7 +21523,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G683" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -21546,7 +21549,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G684" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -21572,7 +21575,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G685" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -21598,7 +21601,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G686" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -21624,7 +21627,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G687" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -21650,7 +21653,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G688" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -21676,7 +21679,7 @@
         <v>10</v>
       </c>
       <c r="G689" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -21702,7 +21705,7 @@
         <v>10</v>
       </c>
       <c r="G690" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -21728,7 +21731,7 @@
         <v>10</v>
       </c>
       <c r="G691" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -21754,7 +21757,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G692" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -21780,7 +21783,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G693" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -21806,7 +21809,7 @@
         <v>10</v>
       </c>
       <c r="G694" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -21832,7 +21835,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G695" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -21858,7 +21861,7 @@
         <v>10</v>
       </c>
       <c r="G696" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -21884,7 +21887,7 @@
         <v>10</v>
       </c>
       <c r="G697" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -21910,7 +21913,7 @@
         <v>10.5</v>
       </c>
       <c r="G698" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -21936,7 +21939,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G699" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -21962,7 +21965,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G700" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -21988,7 +21991,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G701" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -22014,7 +22017,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G702" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -22040,7 +22043,7 @@
         <v>10.25</v>
       </c>
       <c r="G703" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -22066,7 +22069,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G704" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -22092,7 +22095,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G705" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -22118,7 +22121,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G706" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -22144,7 +22147,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G707" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -22170,7 +22173,7 @@
         <v>10</v>
       </c>
       <c r="G708" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -22196,7 +22199,7 @@
         <v>10</v>
       </c>
       <c r="G709" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -22222,7 +22225,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G710" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -22248,7 +22251,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G711" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -22274,7 +22277,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G712" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -22300,7 +22303,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G713" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -22326,7 +22329,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G714" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -22352,7 +22355,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G715" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -22378,7 +22381,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G716" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -22404,7 +22407,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G717" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -22430,7 +22433,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G718" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -22456,7 +22459,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G719" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -22482,7 +22485,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G720" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -22508,7 +22511,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G721" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -22534,7 +22537,7 @@
         <v>10</v>
       </c>
       <c r="G722" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -22560,7 +22563,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G723" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -22586,7 +22589,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G724" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -22612,7 +22615,7 @@
         <v>10</v>
       </c>
       <c r="G725" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -22638,7 +22641,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G726" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -22664,7 +22667,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G727" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -22690,7 +22693,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G728" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -22716,7 +22719,7 @@
         <v>10</v>
       </c>
       <c r="G729" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -22742,7 +22745,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G730" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -22768,7 +22771,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G731" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -22794,7 +22797,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G732" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -22820,7 +22823,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G733" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -22846,7 +22849,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G734" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -22872,7 +22875,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="G735" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -22898,7 +22901,7 @@
         <v>9.65999984741211</v>
       </c>
       <c r="G736" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -22924,7 +22927,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G737" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -22950,7 +22953,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G738" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -22976,7 +22979,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G739" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -23002,7 +23005,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G740" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -23028,7 +23031,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G741" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -23054,7 +23057,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G742" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -23080,7 +23083,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G743" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -23106,7 +23109,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G744" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -23132,7 +23135,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G745" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -23158,7 +23161,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G746" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -23184,7 +23187,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G747" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -23210,7 +23213,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G748" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -23236,7 +23239,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G749" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -23262,7 +23265,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G750" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -23288,7 +23291,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G751" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -23314,7 +23317,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G752" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -23340,7 +23343,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G753" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -23366,7 +23369,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G754" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -23392,7 +23395,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G755" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -23418,7 +23421,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G756" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -23444,7 +23447,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G757" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -23470,7 +23473,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G758" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -23496,7 +23499,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G759" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -23522,7 +23525,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G760" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -23548,7 +23551,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G761" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -23574,7 +23577,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G762" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -23600,7 +23603,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G763" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -23626,7 +23629,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G764" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -23652,7 +23655,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G765" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -23678,7 +23681,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G766" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -23704,7 +23707,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G767" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -23730,7 +23733,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G768" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -23756,7 +23759,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G769" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -23782,7 +23785,7 @@
         <v>9.68000030517578</v>
       </c>
       <c r="G770" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -23808,7 +23811,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G771" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -23834,7 +23837,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G772" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -23860,7 +23863,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G773" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -23886,7 +23889,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G774" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -23912,7 +23915,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G775" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -23938,7 +23941,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G776" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -23964,7 +23967,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G777" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -23990,7 +23993,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G778" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -24016,7 +24019,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G779" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -24042,7 +24045,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G780" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -24068,7 +24071,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G781" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -24094,7 +24097,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G782" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -24120,7 +24123,7 @@
         <v>10.1499996185303</v>
       <